--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB73CEAD-2EC5-4C44-AD3B-103D2F1E6072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFD31AD-02BA-440F-B801-B0CE1A7240F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1176,11 +1176,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1191,17 +1191,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1212,77 +1305,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1299,15 +1329,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1317,40 +1338,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1723,70 +1723,70 @@
   </cols>
   <sheetData>
     <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="76" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="72" t="s">
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="76" t="s">
+      <c r="U2" s="83"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="78"/>
-      <c r="AJ2" s="71" t="s">
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="71"/>
-      <c r="AN2" s="74" t="s">
+      <c r="AK2" s="81"/>
+      <c r="AN2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="75" t="s">
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AQ2" s="84"/>
+      <c r="AR2" s="84"/>
+      <c r="AS2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="75"/>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="75"/>
-      <c r="AY2" s="71" t="s">
+      <c r="AT2" s="85"/>
+      <c r="AU2" s="85"/>
+      <c r="AV2" s="85"/>
+      <c r="AW2" s="85"/>
+      <c r="AX2" s="85"/>
+      <c r="AY2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71" t="s">
+      <c r="BB2" s="81"/>
+      <c r="BC2" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="71"/>
+      <c r="BD2" s="81"/>
     </row>
     <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I3" s="1" t="s">
@@ -1804,12 +1804,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="85"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="87"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="74"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1834,12 +1834,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="81"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="88"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1861,12 +1861,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="75"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1879,13 +1879,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="71" t="s">
+      <c r="BC3" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="71"/>
+      <c r="BD3" s="81"/>
     </row>
     <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I4" s="92">
+      <c r="I4" s="62">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1914,10 +1914,10 @@
       <c r="U4" s="6"/>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="35">
+      <c r="X4" s="40">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="88">
+      <c r="Y4" s="50">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1946,7 +1946,7 @@
       <c r="AK4" s="6"/>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="68">
+      <c r="AN4" s="90">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1975,11 +1975,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
+      <c r="BC4" s="35"/>
+      <c r="BD4" s="35"/>
     </row>
     <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I5" s="69"/>
+      <c r="I5" s="63"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1992,7 +1992,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="N5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2006,8 +2006,8 @@
       <c r="U5" s="6"/>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="89"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="51"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2020,21 +2020,21 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="91" t="s">
+      <c r="AD5" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46"/>
+      <c r="AE5" s="76"/>
+      <c r="AF5" s="76"/>
+      <c r="AG5" s="76"/>
+      <c r="AH5" s="76"/>
+      <c r="AI5" s="77"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
       <c r="AK5" s="6"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="69"/>
+      <c r="AN5" s="63"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2047,7 +2047,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="66" t="s">
+      <c r="AS5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2061,11 +2061,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="46"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="77"/>
     </row>
     <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I6" s="70"/>
+      <c r="I6" s="64"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2092,8 +2092,8 @@
       <c r="U6" s="6"/>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="90"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="79"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2106,21 +2106,21 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AD6" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="77"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
       <c r="AK6" s="6"/>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="70"/>
+      <c r="AN6" s="64"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2147,11 +2147,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="64"/>
-      <c r="BD6" s="64"/>
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="35"/>
     </row>
     <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="35">
+      <c r="I7" s="40">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2186,17 +2186,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="45"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="76"/>
+      <c r="AG7" s="76"/>
+      <c r="AH7" s="76"/>
+      <c r="AI7" s="77"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="35">
+      <c r="AN7" s="40">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2225,11 +2225,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
     </row>
     <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I8" s="36"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2256,10 +2256,10 @@
       <c r="U8" s="6"/>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="52">
+      <c r="X8" s="42">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="88">
+      <c r="Y8" s="50">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2288,7 +2288,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="55"/>
+      <c r="AN8" s="48"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2315,11 +2315,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="64"/>
-      <c r="BD8" s="64"/>
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="35"/>
     </row>
     <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="35">
+      <c r="I9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2348,8 +2348,8 @@
       <c r="U9" s="6"/>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="89"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="51"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2376,7 +2376,7 @@
       <c r="AK9" s="6"/>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="35">
+      <c r="AN9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2405,11 +2405,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="64"/>
-      <c r="BD9" s="64"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="35"/>
     </row>
     <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I10" s="36"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2442,17 +2442,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="77"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="55"/>
+      <c r="AN10" s="48"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2479,11 +2479,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="64"/>
-      <c r="BD10" s="64"/>
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="35"/>
     </row>
     <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I11" s="35">
+      <c r="I11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2498,7 +2498,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="66" t="s">
+      <c r="N11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2512,10 +2512,10 @@
       <c r="U11" s="6"/>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="52">
+      <c r="X11" s="42">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="42">
+      <c r="Y11" s="46">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2544,7 +2544,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="35">
+      <c r="AN11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2559,7 +2559,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="66" t="s">
+      <c r="AS11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2573,11 +2573,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="64"/>
-      <c r="BD11" s="64"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="35"/>
     </row>
     <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I12" s="55"/>
+      <c r="I12" s="48"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2604,8 +2604,8 @@
       <c r="U12" s="6"/>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="43"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="47"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2632,7 +2632,7 @@
       <c r="AK12" s="6"/>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="55"/>
+      <c r="AN12" s="48"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2645,7 +2645,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="66" t="s">
+      <c r="AS12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2659,11 +2659,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="64"/>
-      <c r="BD12" s="64"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
     </row>
     <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I13" s="36"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2696,17 +2696,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="45"/>
-      <c r="AF13" s="45"/>
-      <c r="AG13" s="45"/>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="46"/>
+      <c r="AD13" s="75"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="77"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="36"/>
+      <c r="AN13" s="41"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2733,11 +2733,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="64"/>
-      <c r="BD13" s="64"/>
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="35"/>
     </row>
     <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I14" s="35">
+      <c r="I14" s="40">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2766,10 +2766,10 @@
       <c r="U14" s="6"/>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="52">
+      <c r="X14" s="42">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="40">
+      <c r="Y14" s="52">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2784,7 +2784,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="66" t="s">
+      <c r="AD14" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2798,7 +2798,7 @@
       <c r="AK14" s="6"/>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="35">
+      <c r="AN14" s="40">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2827,11 +2827,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="64"/>
-      <c r="BD14" s="64"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="35"/>
     </row>
     <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="55"/>
+      <c r="I15" s="48"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2858,8 +2858,8 @@
       <c r="U15" s="6"/>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="62"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="78"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2872,7 +2872,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="66" t="s">
+      <c r="AD15" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2886,7 +2886,7 @@
       <c r="AK15" s="6"/>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="55"/>
+      <c r="AN15" s="48"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2913,11 +2913,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="64"/>
-      <c r="BD15" s="64"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="35"/>
     </row>
     <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I16" s="36"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2944,8 +2944,8 @@
       <c r="U16" s="6"/>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="41"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="53"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="AK16" s="6"/>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="55"/>
+      <c r="AN16" s="48"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -2999,11 +2999,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="65"/>
-      <c r="BD16" s="65"/>
+      <c r="BC16" s="36"/>
+      <c r="BD16" s="36"/>
     </row>
     <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="53">
+      <c r="I17" s="92">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3038,17 +3038,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="46"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="77"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="93">
+      <c r="AN17" s="49">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3077,11 +3077,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="64"/>
-      <c r="BD17" s="64"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="35"/>
     </row>
     <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I18" s="54"/>
+      <c r="I18" s="93"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3108,10 +3108,10 @@
       <c r="U18" s="6"/>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="52">
+      <c r="X18" s="42">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="40">
+      <c r="Y18" s="52">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3140,7 +3140,7 @@
       <c r="AK18" s="6"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="93"/>
+      <c r="AN18" s="49"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3167,11 +3167,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="64"/>
-      <c r="BD18" s="64"/>
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="35"/>
     </row>
     <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I19" s="35" t="s">
+      <c r="I19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3194,8 +3194,8 @@
       <c r="U19" s="6"/>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="62"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="78"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3222,7 +3222,7 @@
       <c r="AK19" s="6"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="35" t="s">
+      <c r="AN19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3245,11 +3245,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="64"/>
-      <c r="BD19" s="64"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
     </row>
     <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I20" s="36"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3270,8 +3270,8 @@
       <c r="U20" s="7"/>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="52"/>
-      <c r="Y20" s="41"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="53"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3298,7 +3298,7 @@
       <c r="AK20" s="7"/>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="36"/>
+      <c r="AN20" s="41"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3319,11 +3319,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="64"/>
-      <c r="BD20" s="64"/>
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="35"/>
     </row>
     <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I21" s="35">
+      <c r="I21" s="40">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3360,17 +3360,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="46"/>
+      <c r="AD21" s="75"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="77"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="35">
+      <c r="AN21" s="40">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3401,11 +3401,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="64"/>
-      <c r="BD21" s="64"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="35"/>
     </row>
     <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I22" s="55"/>
+      <c r="I22" s="48"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3434,10 +3434,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="93">
+      <c r="X22" s="49">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="40">
+      <c r="Y22" s="52">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3466,7 +3466,7 @@
       <c r="AK22" s="7"/>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="55"/>
+      <c r="AN22" s="48"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3495,11 +3495,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="35"/>
     </row>
     <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I23" s="36"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3528,8 +3528,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="93"/>
-      <c r="Y23" s="41"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="53"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="AK23" s="7"/>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="36"/>
+      <c r="AN23" s="41"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3585,11 +3585,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="64"/>
-      <c r="BD23" s="64"/>
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="35"/>
     </row>
     <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3626,17 +3626,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="44"/>
-      <c r="AE24" s="45"/>
-      <c r="AF24" s="45"/>
-      <c r="AG24" s="45"/>
-      <c r="AH24" s="45"/>
-      <c r="AI24" s="46"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="76"/>
+      <c r="AF24" s="76"/>
+      <c r="AG24" s="76"/>
+      <c r="AH24" s="76"/>
+      <c r="AI24" s="77"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="35" t="s">
+      <c r="AN24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3667,11 +3667,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="64"/>
-      <c r="BD24" s="64"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="35"/>
     </row>
     <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I25" s="36"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3700,10 +3700,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="35" t="s">
+      <c r="X25" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="42">
+      <c r="Y25" s="46">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3726,7 +3726,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="36"/>
+      <c r="AN25" s="41"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3755,11 +3755,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="64"/>
-      <c r="BD25" s="64"/>
+      <c r="BC25" s="35"/>
+      <c r="BD25" s="35"/>
     </row>
     <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I26" s="35" t="s">
+      <c r="I26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3790,8 +3790,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="43"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="47"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3812,7 +3812,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="35" t="s">
+      <c r="AN26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3843,11 +3843,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="64"/>
-      <c r="BD26" s="64"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
     </row>
     <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I27" s="36"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3882,17 +3882,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="44"/>
-      <c r="AE27" s="45"/>
-      <c r="AF27" s="45"/>
-      <c r="AG27" s="45"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="46"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="77"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="36"/>
+      <c r="AN27" s="41"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3921,11 +3921,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="64"/>
-      <c r="BD27" s="64"/>
+      <c r="BC27" s="35"/>
+      <c r="BD27" s="35"/>
     </row>
     <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I28" s="35" t="s">
+      <c r="I28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3956,10 +3956,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="35">
+      <c r="X28" s="40">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="58">
+      <c r="Y28" s="60">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="35" t="s">
+      <c r="AN28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4021,11 +4021,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="65"/>
-      <c r="BD28" s="65"/>
+      <c r="BC28" s="36"/>
+      <c r="BD28" s="36"/>
     </row>
     <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I29" s="55"/>
+      <c r="I29" s="48"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4054,8 +4054,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="63"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="91"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="55"/>
+      <c r="AN29" s="48"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4113,11 +4113,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="64"/>
-      <c r="BD29" s="64"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
     </row>
     <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I30" s="36"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4146,8 +4146,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="59"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="61"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="36"/>
+      <c r="AN30" s="41"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4205,11 +4205,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="64"/>
-      <c r="BD30" s="64"/>
+      <c r="BC30" s="35"/>
+      <c r="BD30" s="35"/>
     </row>
     <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I31" s="35">
+      <c r="I31" s="40">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4246,17 +4246,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="44"/>
-      <c r="AE31" s="45"/>
-      <c r="AF31" s="45"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="45"/>
-      <c r="AI31" s="46"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="77"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="35">
+      <c r="AN31" s="40">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4287,11 +4287,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="64"/>
-      <c r="BD31" s="64"/>
+      <c r="BC31" s="35"/>
+      <c r="BD31" s="35"/>
     </row>
     <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="36"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4320,10 +4320,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="35">
+      <c r="X32" s="40">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="58">
+      <c r="Y32" s="60">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="36"/>
+      <c r="AN32" s="41"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4383,11 +4383,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="64"/>
-      <c r="BD32" s="64"/>
+      <c r="BC32" s="35"/>
+      <c r="BD32" s="35"/>
     </row>
     <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I33" s="35">
+      <c r="I33" s="40">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4418,8 +4418,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="59"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="61"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="35">
+      <c r="AN33" s="40">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4479,11 +4479,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="64"/>
-      <c r="BD33" s="64"/>
+      <c r="BC33" s="35"/>
+      <c r="BD33" s="35"/>
     </row>
     <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I34" s="36"/>
+      <c r="I34" s="41"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4518,17 +4518,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="44"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="46"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="36"/>
+      <c r="AN34" s="41"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4557,11 +4557,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="64"/>
-      <c r="BD34" s="64"/>
+      <c r="BC34" s="35"/>
+      <c r="BD34" s="35"/>
     </row>
     <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I35" s="35">
+      <c r="I35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4592,10 +4592,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="35" t="s">
+      <c r="X35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="42">
+      <c r="Y35" s="46">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="35">
+      <c r="AN35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="64"/>
-      <c r="BD35" s="64"/>
+      <c r="BC35" s="35"/>
+      <c r="BD35" s="35"/>
     </row>
     <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I36" s="36"/>
+      <c r="I36" s="41"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4690,8 +4690,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="43"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="47"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="36"/>
+      <c r="AN36" s="41"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4749,11 +4749,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="64"/>
-      <c r="BD36" s="64"/>
+      <c r="BC36" s="35"/>
+      <c r="BD36" s="35"/>
     </row>
     <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I37" s="35">
+      <c r="I37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4790,17 +4790,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="44"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="46"/>
+      <c r="AD37" s="75"/>
+      <c r="AE37" s="76"/>
+      <c r="AF37" s="76"/>
+      <c r="AG37" s="76"/>
+      <c r="AH37" s="76"/>
+      <c r="AI37" s="77"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="35">
+      <c r="AN37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4831,11 +4831,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="64"/>
-      <c r="BD37" s="64"/>
+      <c r="BC37" s="35"/>
+      <c r="BD37" s="35"/>
     </row>
     <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I38" s="36"/>
+      <c r="I38" s="41"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4864,10 +4864,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="35" t="s">
+      <c r="X38" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="40">
+      <c r="Y38" s="52">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="36"/>
+      <c r="AN38" s="41"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4927,8 +4927,8 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="64"/>
-      <c r="BD38" s="64"/>
+      <c r="BC38" s="35"/>
+      <c r="BD38" s="35"/>
     </row>
     <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="9">
@@ -4962,8 +4962,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="62"/>
+      <c r="X39" s="48"/>
+      <c r="Y39" s="78"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5023,11 +5023,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="64"/>
-      <c r="BD39" s="64"/>
+      <c r="BC39" s="35"/>
+      <c r="BD39" s="35"/>
     </row>
     <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I40" s="35">
+      <c r="I40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5058,8 +5058,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="36"/>
-      <c r="Y40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="53"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="35">
+      <c r="AN40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5119,11 +5119,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="65"/>
-      <c r="BD40" s="65"/>
+      <c r="BC40" s="36"/>
+      <c r="BD40" s="36"/>
     </row>
     <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="36"/>
+      <c r="I41" s="41"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5136,14 +5136,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="47" t="s">
+      <c r="N41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="49"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="45"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5158,17 +5158,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="44"/>
-      <c r="AE41" s="45"/>
-      <c r="AF41" s="45"/>
-      <c r="AG41" s="45"/>
-      <c r="AH41" s="45"/>
-      <c r="AI41" s="46"/>
+      <c r="AD41" s="75"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="76"/>
+      <c r="AG41" s="76"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="77"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="36"/>
+      <c r="AN41" s="41"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5181,14 +5181,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="47" t="s">
+      <c r="AS41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="48"/>
-      <c r="AU41" s="48"/>
-      <c r="AV41" s="48"/>
-      <c r="AW41" s="48"/>
-      <c r="AX41" s="49"/>
+      <c r="AT41" s="44"/>
+      <c r="AU41" s="44"/>
+      <c r="AV41" s="44"/>
+      <c r="AW41" s="44"/>
+      <c r="AX41" s="45"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5197,8 +5197,8 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="64"/>
-      <c r="BD41" s="64"/>
+      <c r="BC41" s="35"/>
+      <c r="BD41" s="35"/>
     </row>
     <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="9">
@@ -5232,10 +5232,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="35">
+      <c r="X42" s="40">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="40">
+      <c r="Y42" s="52">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5297,11 +5297,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="64"/>
-      <c r="BD42" s="64"/>
+      <c r="BC42" s="35"/>
+      <c r="BD42" s="35"/>
     </row>
     <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="35">
+      <c r="I43" s="40">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5332,8 +5332,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="53"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="35">
+      <c r="AN43" s="40">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="64"/>
-      <c r="BD43" s="64"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
     </row>
     <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="36"/>
+      <c r="I44" s="41"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5432,17 +5432,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="44"/>
-      <c r="AE44" s="45"/>
-      <c r="AF44" s="45"/>
-      <c r="AG44" s="45"/>
-      <c r="AH44" s="45"/>
-      <c r="AI44" s="46"/>
+      <c r="AD44" s="75"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="76"/>
+      <c r="AG44" s="76"/>
+      <c r="AH44" s="76"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="36"/>
+      <c r="AN44" s="41"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5471,8 +5471,8 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="64"/>
-      <c r="BD44" s="64"/>
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
     </row>
     <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I45" s="9">
@@ -5506,10 +5506,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="35">
+      <c r="X45" s="40">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="58">
+      <c r="Y45" s="60">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5571,11 +5571,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="64"/>
-      <c r="BD45" s="64"/>
+      <c r="BC45" s="35"/>
+      <c r="BD45" s="35"/>
     </row>
     <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="35" t="s">
+      <c r="I46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5606,8 +5606,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="59"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="61"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="35" t="s">
+      <c r="AN46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5667,11 +5667,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="64"/>
-      <c r="BD46" s="64"/>
+      <c r="BC46" s="35"/>
+      <c r="BD46" s="35"/>
     </row>
     <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="36"/>
+      <c r="I47" s="41"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5706,17 +5706,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="45"/>
-      <c r="AF47" s="45"/>
-      <c r="AG47" s="45"/>
-      <c r="AH47" s="45"/>
-      <c r="AI47" s="46"/>
+      <c r="AD47" s="75"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="76"/>
+      <c r="AG47" s="76"/>
+      <c r="AH47" s="76"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="36"/>
+      <c r="AN47" s="41"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5745,11 +5745,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="64"/>
-      <c r="BD47" s="64"/>
+      <c r="BC47" s="35"/>
+      <c r="BD47" s="35"/>
     </row>
     <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="35" t="s">
+      <c r="I48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5780,10 +5780,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="35">
+      <c r="X48" s="40">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="42">
+      <c r="Y48" s="46">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="35" t="s">
+      <c r="AN48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="64"/>
-      <c r="BD48" s="64"/>
+      <c r="BC48" s="35"/>
+      <c r="BD48" s="35"/>
     </row>
     <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="36"/>
+      <c r="I49" s="41"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5878,8 +5878,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="43"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="47"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="36"/>
+      <c r="AN49" s="41"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="64"/>
-      <c r="BD49" s="64"/>
+      <c r="BC49" s="35"/>
+      <c r="BD49" s="35"/>
     </row>
     <row r="50" spans="8:56" x14ac:dyDescent="0.25">
       <c r="H50" s="10"/>
-      <c r="I50" s="35">
+      <c r="I50" s="40">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -5957,14 +5957,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="47" t="s">
+      <c r="N50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-      <c r="R50" s="48"/>
-      <c r="S50" s="49"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="45"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -5979,17 +5979,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="45"/>
-      <c r="AG50" s="45"/>
-      <c r="AH50" s="45"/>
-      <c r="AI50" s="46"/>
+      <c r="AD50" s="75"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="76"/>
+      <c r="AH50" s="76"/>
+      <c r="AI50" s="77"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="35">
+      <c r="AN50" s="40">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6000,23 +6000,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="47" t="s">
+      <c r="AS50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="48"/>
-      <c r="AU50" s="48"/>
-      <c r="AV50" s="48"/>
-      <c r="AW50" s="48"/>
-      <c r="AX50" s="49"/>
+      <c r="AT50" s="44"/>
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="45"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="64"/>
-      <c r="BD50" s="64"/>
+      <c r="BC50" s="35"/>
+      <c r="BD50" s="35"/>
     </row>
     <row r="51" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I51" s="36"/>
+      <c r="I51" s="41"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6029,14 +6029,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="47" t="s">
+      <c r="N51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="49"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="45"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6045,10 +6045,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="35">
+      <c r="X51" s="40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="40">
+      <c r="Y51" s="52">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="36"/>
+      <c r="AN51" s="41"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6088,23 +6088,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="47" t="s">
+      <c r="AS51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="48"/>
-      <c r="AU51" s="48"/>
-      <c r="AV51" s="48"/>
-      <c r="AW51" s="48"/>
-      <c r="AX51" s="49"/>
+      <c r="AT51" s="44"/>
+      <c r="AU51" s="44"/>
+      <c r="AV51" s="44"/>
+      <c r="AW51" s="44"/>
+      <c r="AX51" s="45"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="64"/>
-      <c r="BD51" s="64"/>
+      <c r="BC51" s="35"/>
+      <c r="BD51" s="35"/>
     </row>
     <row r="52" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I52" s="35">
+      <c r="I52" s="40">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6135,8 +6135,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="36"/>
-      <c r="Y52" s="41"/>
+      <c r="X52" s="41"/>
+      <c r="Y52" s="53"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="35">
+      <c r="AN52" s="40">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6188,11 +6188,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="65"/>
-      <c r="BD52" s="65"/>
+      <c r="BC52" s="36"/>
+      <c r="BD52" s="36"/>
     </row>
     <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I53" s="36"/>
+      <c r="I53" s="41"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6227,17 +6227,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="44"/>
-      <c r="AE53" s="45"/>
-      <c r="AF53" s="45"/>
-      <c r="AG53" s="45"/>
-      <c r="AH53" s="45"/>
-      <c r="AI53" s="46"/>
+      <c r="AD53" s="75"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="76"/>
+      <c r="AG53" s="76"/>
+      <c r="AH53" s="76"/>
+      <c r="AI53" s="77"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="36"/>
+      <c r="AN53" s="41"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6258,11 +6258,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="64"/>
-      <c r="BD53" s="64"/>
+      <c r="BC53" s="35"/>
+      <c r="BD53" s="35"/>
     </row>
     <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I54" s="35">
+      <c r="I54" s="40">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="35">
+      <c r="AN54" s="40">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6350,11 +6350,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="64"/>
-      <c r="BD54" s="64"/>
+      <c r="BC54" s="35"/>
+      <c r="BD54" s="35"/>
     </row>
     <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I55" s="36"/>
+      <c r="I55" s="41"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6389,17 +6389,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="44"/>
-      <c r="AE55" s="45"/>
-      <c r="AF55" s="45"/>
-      <c r="AG55" s="45"/>
-      <c r="AH55" s="45"/>
-      <c r="AI55" s="46"/>
+      <c r="AD55" s="75"/>
+      <c r="AE55" s="76"/>
+      <c r="AF55" s="76"/>
+      <c r="AG55" s="76"/>
+      <c r="AH55" s="76"/>
+      <c r="AI55" s="77"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="36"/>
+      <c r="AN55" s="41"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6420,8 +6420,8 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="64"/>
-      <c r="BD55" s="64"/>
+      <c r="BC55" s="35"/>
+      <c r="BD55" s="35"/>
     </row>
     <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="9">
@@ -6455,10 +6455,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="35">
+      <c r="X56" s="40">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="58">
+      <c r="Y56" s="60">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6512,11 +6512,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="64"/>
-      <c r="BD56" s="64"/>
+      <c r="BC56" s="35"/>
+      <c r="BD56" s="35"/>
     </row>
     <row r="57" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I57" s="35">
+      <c r="I57" s="40">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6547,8 +6547,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="36"/>
-      <c r="Y57" s="59"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="61"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6559,14 +6559,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="47" t="s">
+      <c r="AD57" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="48"/>
-      <c r="AF57" s="48"/>
-      <c r="AG57" s="48"/>
-      <c r="AH57" s="48"/>
-      <c r="AI57" s="49"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="44"/>
+      <c r="AI57" s="45"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="35">
+      <c r="AN57" s="40">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6598,11 +6598,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="64"/>
-      <c r="BD57" s="64"/>
+      <c r="BC57" s="35"/>
+      <c r="BD57" s="35"/>
     </row>
     <row r="58" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I58" s="36"/>
+      <c r="I58" s="41"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6637,17 +6637,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="44"/>
-      <c r="AE58" s="45"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="45"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
+      <c r="AD58" s="75"/>
+      <c r="AE58" s="76"/>
+      <c r="AF58" s="76"/>
+      <c r="AG58" s="76"/>
+      <c r="AH58" s="76"/>
+      <c r="AI58" s="77"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="36"/>
+      <c r="AN58" s="41"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6668,11 +6668,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="64"/>
-      <c r="BD58" s="64"/>
+      <c r="BC58" s="35"/>
+      <c r="BD58" s="35"/>
     </row>
     <row r="59" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I59" s="35">
+      <c r="I59" s="40">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="35">
+      <c r="AN59" s="40">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6760,11 +6760,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="64"/>
-      <c r="BD59" s="64"/>
+      <c r="BC59" s="35"/>
+      <c r="BD59" s="35"/>
     </row>
     <row r="60" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I60" s="36"/>
+      <c r="I60" s="41"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6799,17 +6799,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="44"/>
-      <c r="AE60" s="45"/>
-      <c r="AF60" s="45"/>
-      <c r="AG60" s="45"/>
-      <c r="AH60" s="45"/>
-      <c r="AI60" s="46"/>
+      <c r="AD60" s="75"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="77"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="36"/>
+      <c r="AN60" s="41"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6830,11 +6830,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="64"/>
-      <c r="BD60" s="64"/>
+      <c r="BC60" s="35"/>
+      <c r="BD60" s="35"/>
     </row>
     <row r="61" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I61" s="35" t="s">
+      <c r="I61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6865,10 +6865,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="35">
+      <c r="X61" s="40">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="60">
+      <c r="Y61" s="58">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="35" t="s">
+      <c r="AN61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6922,11 +6922,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="64"/>
-      <c r="BD61" s="64"/>
+      <c r="BC61" s="35"/>
+      <c r="BD61" s="35"/>
     </row>
     <row r="62" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I62" s="36"/>
+      <c r="I62" s="41"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -6955,8 +6955,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="61"/>
+      <c r="X62" s="41"/>
+      <c r="Y62" s="59"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="36"/>
+      <c r="AN62" s="41"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7006,11 +7006,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="64"/>
-      <c r="BD62" s="64"/>
+      <c r="BC62" s="35"/>
+      <c r="BD62" s="35"/>
     </row>
     <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I63" s="35">
+      <c r="I63" s="40">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7047,17 +7047,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="44"/>
-      <c r="AE63" s="45"/>
-      <c r="AF63" s="45"/>
-      <c r="AG63" s="45"/>
-      <c r="AH63" s="45"/>
-      <c r="AI63" s="46"/>
+      <c r="AD63" s="75"/>
+      <c r="AE63" s="76"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="76"/>
+      <c r="AH63" s="76"/>
+      <c r="AI63" s="77"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="35">
+      <c r="AN63" s="40">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7080,11 +7080,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="64"/>
-      <c r="BD63" s="64"/>
+      <c r="BC63" s="35"/>
+      <c r="BD63" s="35"/>
     </row>
     <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I64" s="36"/>
+      <c r="I64" s="41"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="36"/>
+      <c r="AN64" s="41"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7168,11 +7168,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="65"/>
-      <c r="BD64" s="65"/>
+      <c r="BC64" s="36"/>
+      <c r="BD64" s="36"/>
     </row>
     <row r="65" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I65" s="35">
+      <c r="I65" s="40">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7201,17 +7201,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="44"/>
-      <c r="AE65" s="45"/>
-      <c r="AF65" s="45"/>
-      <c r="AG65" s="45"/>
-      <c r="AH65" s="45"/>
-      <c r="AI65" s="46"/>
+      <c r="AD65" s="75"/>
+      <c r="AE65" s="76"/>
+      <c r="AF65" s="76"/>
+      <c r="AG65" s="76"/>
+      <c r="AH65" s="76"/>
+      <c r="AI65" s="77"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="35">
+      <c r="AN65" s="40">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7234,11 +7234,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="64"/>
-      <c r="BD65" s="64"/>
+      <c r="BC65" s="35"/>
+      <c r="BD65" s="35"/>
     </row>
     <row r="66" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I66" s="36"/>
+      <c r="I66" s="41"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7259,10 +7259,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="35" t="s">
+      <c r="X66" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="56">
+      <c r="Y66" s="54">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="36"/>
+      <c r="AN66" s="41"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7314,8 +7314,8 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="64"/>
-      <c r="BD66" s="64"/>
+      <c r="BC66" s="35"/>
+      <c r="BD66" s="35"/>
     </row>
     <row r="67" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I67" s="9">
@@ -7341,8 +7341,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="36"/>
-      <c r="Y67" s="57"/>
+      <c r="X67" s="41"/>
+      <c r="Y67" s="55"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7394,11 +7394,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="64"/>
-      <c r="BD67" s="64"/>
+      <c r="BC67" s="35"/>
+      <c r="BD67" s="35"/>
     </row>
     <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I68" s="35">
+      <c r="I68" s="40">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7427,17 +7427,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="44"/>
-      <c r="AE68" s="45"/>
-      <c r="AF68" s="45"/>
-      <c r="AG68" s="45"/>
-      <c r="AH68" s="45"/>
-      <c r="AI68" s="46"/>
+      <c r="AD68" s="75"/>
+      <c r="AE68" s="76"/>
+      <c r="AF68" s="76"/>
+      <c r="AG68" s="76"/>
+      <c r="AH68" s="76"/>
+      <c r="AI68" s="77"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="35">
+      <c r="AN68" s="40">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7460,11 +7460,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="64"/>
-      <c r="BD68" s="64"/>
+      <c r="BC68" s="35"/>
+      <c r="BD68" s="35"/>
     </row>
     <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I69" s="36"/>
+      <c r="I69" s="41"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7485,10 +7485,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="35" t="s">
+      <c r="X69" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="56">
+      <c r="Y69" s="54">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="36"/>
+      <c r="AN69" s="41"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7540,8 +7540,8 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="64"/>
-      <c r="BD69" s="64"/>
+      <c r="BC69" s="35"/>
+      <c r="BD69" s="35"/>
     </row>
     <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="9">
@@ -7567,8 +7567,8 @@
       <c r="U70" s="6"/>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="36"/>
-      <c r="Y70" s="57"/>
+      <c r="X70" s="41"/>
+      <c r="Y70" s="55"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7620,11 +7620,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="64"/>
-      <c r="BD70" s="64"/>
+      <c r="BC70" s="35"/>
+      <c r="BD70" s="35"/>
     </row>
     <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I71" s="35">
+      <c r="I71" s="40">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7653,17 +7653,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="44"/>
-      <c r="AE71" s="45"/>
-      <c r="AF71" s="45"/>
-      <c r="AG71" s="45"/>
-      <c r="AH71" s="45"/>
-      <c r="AI71" s="46"/>
+      <c r="AD71" s="75"/>
+      <c r="AE71" s="76"/>
+      <c r="AF71" s="76"/>
+      <c r="AG71" s="76"/>
+      <c r="AH71" s="76"/>
+      <c r="AI71" s="77"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="35">
+      <c r="AN71" s="40">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7686,11 +7686,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="64"/>
-      <c r="BD71" s="64"/>
+      <c r="BC71" s="35"/>
+      <c r="BD71" s="35"/>
     </row>
     <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I72" s="36"/>
+      <c r="I72" s="41"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7711,10 +7711,10 @@
       <c r="U72" s="6"/>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="35">
+      <c r="X72" s="40">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="40">
+      <c r="Y72" s="52">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7729,19 +7729,23 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="47" t="s">
+      <c r="AD72" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="48"/>
-      <c r="AF72" s="48"/>
-      <c r="AG72" s="48"/>
-      <c r="AH72" s="48"/>
-      <c r="AI72" s="49"/>
-      <c r="AJ72" s="19"/>
-      <c r="AK72" s="19"/>
+      <c r="AE72" s="44"/>
+      <c r="AF72" s="44"/>
+      <c r="AG72" s="44"/>
+      <c r="AH72" s="44"/>
+      <c r="AI72" s="45"/>
+      <c r="AJ72" s="7">
+        <v>45907</v>
+      </c>
+      <c r="AK72" s="7">
+        <v>45908</v>
+      </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="36"/>
+      <c r="AN72" s="41"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7762,11 +7766,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="64"/>
-      <c r="BD72" s="64"/>
+      <c r="BC72" s="35"/>
+      <c r="BD72" s="35"/>
     </row>
     <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I73" s="35">
+      <c r="I73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7777,20 +7781,20 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="47" t="s">
+      <c r="N73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="48"/>
-      <c r="P73" s="48"/>
-      <c r="Q73" s="48"/>
-      <c r="R73" s="48"/>
-      <c r="S73" s="49"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="44"/>
+      <c r="S73" s="45"/>
       <c r="T73" s="7"/>
       <c r="U73" s="6"/>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="36"/>
-      <c r="Y73" s="41"/>
+      <c r="X73" s="41"/>
+      <c r="Y73" s="53"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7803,19 +7807,23 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="47" t="s">
+      <c r="AD73" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="48"/>
-      <c r="AF73" s="48"/>
-      <c r="AG73" s="48"/>
-      <c r="AH73" s="48"/>
-      <c r="AI73" s="49"/>
-      <c r="AJ73" s="19"/>
-      <c r="AK73" s="19"/>
+      <c r="AE73" s="44"/>
+      <c r="AF73" s="44"/>
+      <c r="AG73" s="44"/>
+      <c r="AH73" s="44"/>
+      <c r="AI73" s="45"/>
+      <c r="AJ73" s="7">
+        <v>45907</v>
+      </c>
+      <c r="AK73" s="7">
+        <v>45908</v>
+      </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="35">
+      <c r="AN73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7826,23 +7834,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="47" t="s">
+      <c r="AS73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="48"/>
-      <c r="AU73" s="48"/>
-      <c r="AV73" s="48"/>
-      <c r="AW73" s="48"/>
-      <c r="AX73" s="49"/>
+      <c r="AT73" s="44"/>
+      <c r="AU73" s="44"/>
+      <c r="AV73" s="44"/>
+      <c r="AW73" s="44"/>
+      <c r="AX73" s="45"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="64"/>
-      <c r="BD73" s="64"/>
+      <c r="BC73" s="35"/>
+      <c r="BD73" s="35"/>
     </row>
     <row r="74" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I74" s="36"/>
+      <c r="I74" s="41"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7869,17 +7877,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="44"/>
-      <c r="AE74" s="45"/>
-      <c r="AF74" s="45"/>
-      <c r="AG74" s="45"/>
-      <c r="AH74" s="45"/>
-      <c r="AI74" s="46"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="76"/>
+      <c r="AF74" s="76"/>
+      <c r="AG74" s="76"/>
+      <c r="AH74" s="76"/>
+      <c r="AI74" s="77"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="36"/>
+      <c r="AN74" s="41"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7900,11 +7908,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="64"/>
-      <c r="BD74" s="64"/>
+      <c r="BC74" s="35"/>
+      <c r="BD74" s="35"/>
     </row>
     <row r="75" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I75" s="35">
+      <c r="I75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7915,22 +7923,22 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="47" t="s">
+      <c r="N75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="49"/>
+      <c r="O75" s="44"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="44"/>
+      <c r="R75" s="44"/>
+      <c r="S75" s="45"/>
       <c r="T75" s="7"/>
       <c r="U75" s="6"/>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="35">
+      <c r="X75" s="40">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="58">
+      <c r="Y75" s="60">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -7953,11 +7961,15 @@
       <c r="AG75" s="38"/>
       <c r="AH75" s="38"/>
       <c r="AI75" s="39"/>
-      <c r="AJ75" s="19"/>
-      <c r="AK75" s="19"/>
+      <c r="AJ75" s="7">
+        <v>45907</v>
+      </c>
+      <c r="AK75" s="7">
+        <v>45908</v>
+      </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="35">
+      <c r="AN75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -7968,23 +7980,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="47" t="s">
+      <c r="AS75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="48"/>
-      <c r="AU75" s="48"/>
-      <c r="AV75" s="48"/>
-      <c r="AW75" s="48"/>
-      <c r="AX75" s="49"/>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="44"/>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="44"/>
+      <c r="AX75" s="45"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="64"/>
-      <c r="BD75" s="64"/>
+      <c r="BC75" s="35"/>
+      <c r="BD75" s="35"/>
     </row>
     <row r="76" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I76" s="36"/>
+      <c r="I76" s="41"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8005,8 +8017,8 @@
       <c r="U76" s="6"/>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="36"/>
-      <c r="Y76" s="59"/>
+      <c r="X76" s="41"/>
+      <c r="Y76" s="61"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8027,11 +8039,15 @@
       <c r="AG76" s="38"/>
       <c r="AH76" s="38"/>
       <c r="AI76" s="39"/>
-      <c r="AJ76" s="19"/>
-      <c r="AK76" s="19"/>
+      <c r="AJ76" s="7">
+        <v>45907</v>
+      </c>
+      <c r="AK76" s="7">
+        <v>45908</v>
+      </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="36"/>
+      <c r="AN76" s="41"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8052,11 +8068,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="65"/>
-      <c r="BD76" s="65"/>
+      <c r="BC76" s="36"/>
+      <c r="BD76" s="36"/>
     </row>
     <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I77" s="35">
+      <c r="I77" s="40">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8085,17 +8101,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="44"/>
-      <c r="AE77" s="45"/>
-      <c r="AF77" s="45"/>
-      <c r="AG77" s="45"/>
-      <c r="AH77" s="45"/>
-      <c r="AI77" s="46"/>
+      <c r="AD77" s="75"/>
+      <c r="AE77" s="76"/>
+      <c r="AF77" s="76"/>
+      <c r="AG77" s="76"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="77"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="35">
+      <c r="AN77" s="40">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8118,11 +8134,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="64"/>
-      <c r="BD77" s="64"/>
+      <c r="BC77" s="35"/>
+      <c r="BD77" s="35"/>
     </row>
     <row r="78" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I78" s="36"/>
+      <c r="I78" s="41"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8143,10 +8159,10 @@
       <c r="U78" s="6"/>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="35">
+      <c r="X78" s="40">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="40">
+      <c r="Y78" s="52">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8169,11 +8185,15 @@
       <c r="AG78" s="38"/>
       <c r="AH78" s="38"/>
       <c r="AI78" s="39"/>
-      <c r="AJ78" s="19"/>
-      <c r="AK78" s="19"/>
+      <c r="AJ78" s="7">
+        <v>45908</v>
+      </c>
+      <c r="AK78" s="7">
+        <v>45909</v>
+      </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="36"/>
+      <c r="AN78" s="41"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8194,11 +8214,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="64"/>
-      <c r="BD78" s="64"/>
+      <c r="BC78" s="35"/>
+      <c r="BD78" s="35"/>
     </row>
     <row r="79" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I79" s="35">
+      <c r="I79" s="40">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8209,20 +8229,20 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="47" t="s">
+      <c r="N79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="48"/>
-      <c r="P79" s="48"/>
-      <c r="Q79" s="48"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="49"/>
+      <c r="O79" s="44"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="44"/>
+      <c r="R79" s="44"/>
+      <c r="S79" s="45"/>
       <c r="T79" s="7"/>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="36"/>
-      <c r="Y79" s="41"/>
+      <c r="X79" s="41"/>
+      <c r="Y79" s="53"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8243,11 +8263,15 @@
       <c r="AG79" s="38"/>
       <c r="AH79" s="38"/>
       <c r="AI79" s="39"/>
-      <c r="AJ79" s="19"/>
-      <c r="AK79" s="19"/>
+      <c r="AJ79" s="7">
+        <v>45908</v>
+      </c>
+      <c r="AK79" s="7">
+        <v>45909</v>
+      </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="35">
+      <c r="AN79" s="40">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8258,23 +8282,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="47" t="s">
+      <c r="AS79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="48"/>
-      <c r="AU79" s="48"/>
-      <c r="AV79" s="48"/>
-      <c r="AW79" s="48"/>
-      <c r="AX79" s="49"/>
+      <c r="AT79" s="44"/>
+      <c r="AU79" s="44"/>
+      <c r="AV79" s="44"/>
+      <c r="AW79" s="44"/>
+      <c r="AX79" s="45"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="64"/>
-      <c r="BD79" s="64"/>
+      <c r="BC79" s="35"/>
+      <c r="BD79" s="35"/>
     </row>
     <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I80" s="36"/>
+      <c r="I80" s="41"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8301,17 +8325,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="44"/>
-      <c r="AE80" s="45"/>
-      <c r="AF80" s="45"/>
-      <c r="AG80" s="45"/>
-      <c r="AH80" s="45"/>
-      <c r="AI80" s="46"/>
+      <c r="AD80" s="75"/>
+      <c r="AE80" s="76"/>
+      <c r="AF80" s="76"/>
+      <c r="AG80" s="76"/>
+      <c r="AH80" s="76"/>
+      <c r="AI80" s="77"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="36"/>
+      <c r="AN80" s="41"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8332,11 +8356,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="64"/>
-      <c r="BD80" s="64"/>
+      <c r="BC80" s="35"/>
+      <c r="BD80" s="35"/>
     </row>
     <row r="81" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I81" s="35">
+      <c r="I81" s="40">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8385,11 +8409,15 @@
       <c r="AG81" s="38"/>
       <c r="AH81" s="38"/>
       <c r="AI81" s="39"/>
-      <c r="AJ81" s="19"/>
-      <c r="AK81" s="19"/>
+      <c r="AJ81" s="7">
+        <v>45908</v>
+      </c>
+      <c r="AK81" s="7">
+        <v>45909</v>
+      </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="35">
+      <c r="AN81" s="40">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8412,11 +8440,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="64"/>
-      <c r="BD81" s="64"/>
+      <c r="BC81" s="35"/>
+      <c r="BD81" s="35"/>
     </row>
     <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I82" s="36"/>
+      <c r="I82" s="41"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8425,14 +8453,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="47" t="s">
+      <c r="N82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="48"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="48"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="49"/>
+      <c r="O82" s="44"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="44"/>
+      <c r="R82" s="44"/>
+      <c r="S82" s="45"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8443,17 +8471,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="44"/>
-      <c r="AE82" s="45"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="45"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
+      <c r="AD82" s="75"/>
+      <c r="AE82" s="76"/>
+      <c r="AF82" s="76"/>
+      <c r="AG82" s="76"/>
+      <c r="AH82" s="76"/>
+      <c r="AI82" s="77"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="36"/>
+      <c r="AN82" s="41"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8462,23 +8490,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="47" t="s">
+      <c r="AS82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="48"/>
-      <c r="AU82" s="48"/>
-      <c r="AV82" s="48"/>
-      <c r="AW82" s="48"/>
-      <c r="AX82" s="49"/>
+      <c r="AT82" s="44"/>
+      <c r="AU82" s="44"/>
+      <c r="AV82" s="44"/>
+      <c r="AW82" s="44"/>
+      <c r="AX82" s="45"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="64"/>
-      <c r="BD82" s="64"/>
+      <c r="BC82" s="35"/>
+      <c r="BD82" s="35"/>
     </row>
     <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I83" s="35">
+      <c r="I83" s="40">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8509,10 +8537,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="35">
+      <c r="X83" s="40">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="56">
+      <c r="Y83" s="54">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8535,11 +8563,15 @@
       <c r="AG83" s="38"/>
       <c r="AH83" s="38"/>
       <c r="AI83" s="39"/>
-      <c r="AJ83" s="19"/>
-      <c r="AK83" s="19"/>
+      <c r="AJ83" s="7">
+        <v>45909</v>
+      </c>
+      <c r="AK83" s="7">
+        <v>45910</v>
+      </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="35">
+      <c r="AN83" s="40">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8568,11 +8600,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="64"/>
-      <c r="BD83" s="64"/>
+      <c r="BC83" s="35"/>
+      <c r="BD83" s="35"/>
     </row>
     <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I84" s="36"/>
+      <c r="I84" s="41"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8601,8 +8633,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="36"/>
-      <c r="Y84" s="57"/>
+      <c r="X84" s="41"/>
+      <c r="Y84" s="55"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8623,11 +8655,15 @@
       <c r="AG84" s="38"/>
       <c r="AH84" s="38"/>
       <c r="AI84" s="39"/>
-      <c r="AJ84" s="19"/>
-      <c r="AK84" s="19"/>
+      <c r="AJ84" s="7">
+        <v>45909</v>
+      </c>
+      <c r="AK84" s="7">
+        <v>45910</v>
+      </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="36"/>
+      <c r="AN84" s="41"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8654,8 +8690,8 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="64"/>
-      <c r="BD84" s="64"/>
+      <c r="BC84" s="35"/>
+      <c r="BD84" s="35"/>
     </row>
     <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="9">
@@ -8687,12 +8723,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="44"/>
-      <c r="AE85" s="45"/>
-      <c r="AF85" s="45"/>
-      <c r="AG85" s="45"/>
-      <c r="AH85" s="45"/>
-      <c r="AI85" s="46"/>
+      <c r="AD85" s="75"/>
+      <c r="AE85" s="76"/>
+      <c r="AF85" s="76"/>
+      <c r="AG85" s="76"/>
+      <c r="AH85" s="76"/>
+      <c r="AI85" s="77"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8720,11 +8756,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="64"/>
-      <c r="BD85" s="64"/>
+      <c r="BC85" s="35"/>
+      <c r="BD85" s="35"/>
     </row>
     <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I86" s="35">
+      <c r="I86" s="40">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8747,10 +8783,10 @@
       <c r="U86" s="6"/>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="35">
+      <c r="X86" s="40">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="50">
+      <c r="Y86" s="56">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8773,11 +8809,15 @@
       <c r="AG86" s="38"/>
       <c r="AH86" s="38"/>
       <c r="AI86" s="39"/>
-      <c r="AJ86" s="19"/>
-      <c r="AK86" s="19"/>
+      <c r="AJ86" s="7">
+        <v>45909</v>
+      </c>
+      <c r="AK86" s="7">
+        <v>45910</v>
+      </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="35">
+      <c r="AN86" s="40">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8800,11 +8840,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="64"/>
-      <c r="BD86" s="64"/>
+      <c r="BC86" s="35"/>
+      <c r="BD86" s="35"/>
     </row>
     <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I87" s="36"/>
+      <c r="I87" s="41"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8825,8 +8865,8 @@
       <c r="U87" s="6"/>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="36"/>
-      <c r="Y87" s="51"/>
+      <c r="X87" s="41"/>
+      <c r="Y87" s="57"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8847,11 +8887,15 @@
       <c r="AG87" s="38"/>
       <c r="AH87" s="38"/>
       <c r="AI87" s="39"/>
-      <c r="AJ87" s="19"/>
-      <c r="AK87" s="19"/>
+      <c r="AJ87" s="7">
+        <v>45909</v>
+      </c>
+      <c r="AK87" s="7">
+        <v>45910</v>
+      </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="36"/>
+      <c r="AN87" s="41"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8872,11 +8916,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="64"/>
-      <c r="BD87" s="64"/>
+      <c r="BC87" s="35"/>
+      <c r="BD87" s="35"/>
     </row>
     <row r="88" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I88" s="35" t="s">
+      <c r="I88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -8905,17 +8949,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="44"/>
-      <c r="AE88" s="45"/>
-      <c r="AF88" s="45"/>
-      <c r="AG88" s="45"/>
-      <c r="AH88" s="45"/>
-      <c r="AI88" s="46"/>
+      <c r="AD88" s="75"/>
+      <c r="AE88" s="76"/>
+      <c r="AF88" s="76"/>
+      <c r="AG88" s="76"/>
+      <c r="AH88" s="76"/>
+      <c r="AI88" s="77"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="35" t="s">
+      <c r="AN88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -8938,11 +8982,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="65"/>
-      <c r="BD88" s="65"/>
+      <c r="BC88" s="36"/>
+      <c r="BD88" s="36"/>
     </row>
     <row r="89" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I89" s="36"/>
+      <c r="I89" s="41"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -8963,10 +9007,10 @@
       <c r="U89" s="6"/>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="35" t="s">
+      <c r="X89" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="50">
+      <c r="Y89" s="56">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -8989,11 +9033,15 @@
       <c r="AG89" s="38"/>
       <c r="AH89" s="38"/>
       <c r="AI89" s="39"/>
-      <c r="AJ89" s="19"/>
-      <c r="AK89" s="19"/>
+      <c r="AJ89" s="7">
+        <v>45909</v>
+      </c>
+      <c r="AK89" s="7">
+        <v>45911</v>
+      </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="36"/>
+      <c r="AN89" s="41"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9014,8 +9062,8 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="64"/>
-      <c r="BD89" s="64"/>
+      <c r="BC89" s="35"/>
+      <c r="BD89" s="35"/>
     </row>
     <row r="90" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I90" s="6">
@@ -9029,20 +9077,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="52" t="s">
+      <c r="N90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
+      <c r="O90" s="42"/>
+      <c r="P90" s="42"/>
+      <c r="Q90" s="42"/>
+      <c r="R90" s="42"/>
+      <c r="S90" s="42"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="36"/>
-      <c r="Y90" s="51"/>
+      <c r="X90" s="41"/>
+      <c r="Y90" s="57"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9063,8 +9111,12 @@
       <c r="AG90" s="38"/>
       <c r="AH90" s="38"/>
       <c r="AI90" s="39"/>
-      <c r="AJ90" s="19"/>
-      <c r="AK90" s="19"/>
+      <c r="AJ90" s="7">
+        <v>45910</v>
+      </c>
+      <c r="AK90" s="7">
+        <v>45911</v>
+      </c>
       <c r="AL90" s="20"/>
       <c r="AM90" s="20"/>
       <c r="AN90" s="6">
@@ -9078,20 +9130,20 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="52" t="s">
+      <c r="AS90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
+      <c r="AT90" s="42"/>
+      <c r="AU90" s="42"/>
+      <c r="AV90" s="42"/>
+      <c r="AW90" s="42"/>
+      <c r="AX90" s="42"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="64"/>
-      <c r="BD90" s="64"/>
+      <c r="BC90" s="35"/>
+      <c r="BD90" s="35"/>
     </row>
     <row r="91" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I91" s="20"/>
@@ -9115,12 +9167,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="44"/>
-      <c r="AE91" s="45"/>
-      <c r="AF91" s="45"/>
-      <c r="AG91" s="45"/>
-      <c r="AH91" s="45"/>
-      <c r="AI91" s="46"/>
+      <c r="AD91" s="75"/>
+      <c r="AE91" s="76"/>
+      <c r="AF91" s="76"/>
+      <c r="AG91" s="76"/>
+      <c r="AH91" s="76"/>
+      <c r="AI91" s="77"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9159,10 +9211,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="35">
+      <c r="X92" s="40">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="58">
+      <c r="Y92" s="60">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9185,8 +9237,12 @@
       <c r="AG92" s="38"/>
       <c r="AH92" s="38"/>
       <c r="AI92" s="39"/>
-      <c r="AJ92" s="19"/>
-      <c r="AK92" s="19"/>
+      <c r="AJ92" s="7">
+        <v>45910</v>
+      </c>
+      <c r="AK92" s="7">
+        <v>45911</v>
+      </c>
       <c r="AL92" s="20"/>
       <c r="AM92" s="20"/>
       <c r="AN92" s="20"/>
@@ -9223,8 +9279,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="36"/>
-      <c r="Y93" s="59"/>
+      <c r="X93" s="41"/>
+      <c r="Y93" s="61"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9245,8 +9301,12 @@
       <c r="AG93" s="38"/>
       <c r="AH93" s="38"/>
       <c r="AI93" s="39"/>
-      <c r="AJ93" s="19"/>
-      <c r="AK93" s="19"/>
+      <c r="AJ93" s="7">
+        <v>45911</v>
+      </c>
+      <c r="AK93" s="7">
+        <v>45912</v>
+      </c>
       <c r="AL93" s="20"/>
       <c r="AM93" s="20"/>
       <c r="AN93" s="20"/>
@@ -9289,12 +9349,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="44"/>
-      <c r="AE94" s="45"/>
-      <c r="AF94" s="45"/>
-      <c r="AG94" s="45"/>
-      <c r="AH94" s="45"/>
-      <c r="AI94" s="46"/>
+      <c r="AD94" s="75"/>
+      <c r="AE94" s="76"/>
+      <c r="AF94" s="76"/>
+      <c r="AG94" s="76"/>
+      <c r="AH94" s="76"/>
+      <c r="AI94" s="77"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9333,10 +9393,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="35">
+      <c r="X95" s="40">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="60">
+      <c r="Y95" s="58">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9393,8 +9453,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="36"/>
-      <c r="Y96" s="61"/>
+      <c r="X96" s="41"/>
+      <c r="Y96" s="59"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9455,12 +9515,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="44"/>
-      <c r="AE97" s="45"/>
-      <c r="AF97" s="45"/>
-      <c r="AG97" s="45"/>
-      <c r="AH97" s="45"/>
-      <c r="AI97" s="46"/>
+      <c r="AD97" s="75"/>
+      <c r="AE97" s="76"/>
+      <c r="AF97" s="76"/>
+      <c r="AG97" s="76"/>
+      <c r="AH97" s="76"/>
+      <c r="AI97" s="77"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9565,12 +9625,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="44"/>
-      <c r="AE99" s="45"/>
-      <c r="AF99" s="45"/>
-      <c r="AG99" s="45"/>
-      <c r="AH99" s="45"/>
-      <c r="AI99" s="46"/>
+      <c r="AD99" s="75"/>
+      <c r="AE99" s="76"/>
+      <c r="AF99" s="76"/>
+      <c r="AG99" s="76"/>
+      <c r="AH99" s="76"/>
+      <c r="AI99" s="77"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9609,10 +9669,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="35">
+      <c r="X100" s="40">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="40">
+      <c r="Y100" s="52">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9669,8 +9729,8 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="36"/>
-      <c r="Y101" s="41"/>
+      <c r="X101" s="41"/>
+      <c r="Y101" s="53"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
@@ -9731,12 +9791,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="44"/>
-      <c r="AE102" s="45"/>
-      <c r="AF102" s="45"/>
-      <c r="AG102" s="45"/>
-      <c r="AH102" s="45"/>
-      <c r="AI102" s="46"/>
+      <c r="AD102" s="75"/>
+      <c r="AE102" s="76"/>
+      <c r="AF102" s="76"/>
+      <c r="AG102" s="76"/>
+      <c r="AH102" s="76"/>
+      <c r="AI102" s="77"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9841,12 +9901,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="44"/>
-      <c r="AE104" s="45"/>
-      <c r="AF104" s="45"/>
-      <c r="AG104" s="45"/>
-      <c r="AH104" s="45"/>
-      <c r="AI104" s="46"/>
+      <c r="AD104" s="75"/>
+      <c r="AE104" s="76"/>
+      <c r="AF104" s="76"/>
+      <c r="AG104" s="76"/>
+      <c r="AH104" s="76"/>
+      <c r="AI104" s="77"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -9886,10 +9946,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="35">
+      <c r="X105" s="40">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="50">
+      <c r="Y105" s="56">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -9946,8 +10006,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="36"/>
-      <c r="Y106" s="51"/>
+      <c r="X106" s="41"/>
+      <c r="Y106" s="57"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10008,12 +10068,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="44"/>
-      <c r="AE107" s="45"/>
-      <c r="AF107" s="45"/>
-      <c r="AG107" s="45"/>
-      <c r="AH107" s="45"/>
-      <c r="AI107" s="46"/>
+      <c r="AD107" s="75"/>
+      <c r="AE107" s="76"/>
+      <c r="AF107" s="76"/>
+      <c r="AG107" s="76"/>
+      <c r="AH107" s="76"/>
+      <c r="AI107" s="77"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10052,10 +10112,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="35">
+      <c r="X108" s="40">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="50">
+      <c r="Y108" s="56">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10066,14 +10126,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="47" t="s">
+      <c r="AD108" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="48"/>
-      <c r="AF108" s="48"/>
-      <c r="AG108" s="48"/>
-      <c r="AH108" s="48"/>
-      <c r="AI108" s="49"/>
+      <c r="AE108" s="44"/>
+      <c r="AF108" s="44"/>
+      <c r="AG108" s="44"/>
+      <c r="AH108" s="44"/>
+      <c r="AI108" s="45"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10112,8 +10172,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="36"/>
-      <c r="Y109" s="51"/>
+      <c r="X109" s="41"/>
+      <c r="Y109" s="57"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10174,12 +10234,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="44"/>
-      <c r="AE110" s="45"/>
-      <c r="AF110" s="45"/>
-      <c r="AG110" s="45"/>
-      <c r="AH110" s="45"/>
-      <c r="AI110" s="46"/>
+      <c r="AD110" s="75"/>
+      <c r="AE110" s="76"/>
+      <c r="AF110" s="76"/>
+      <c r="AG110" s="76"/>
+      <c r="AH110" s="76"/>
+      <c r="AI110" s="77"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10218,10 +10278,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="35">
+      <c r="X111" s="40">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="50">
+      <c r="Y111" s="56">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10232,14 +10292,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="47" t="s">
+      <c r="AD111" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="48"/>
-      <c r="AF111" s="48"/>
-      <c r="AG111" s="48"/>
-      <c r="AH111" s="48"/>
-      <c r="AI111" s="49"/>
+      <c r="AE111" s="44"/>
+      <c r="AF111" s="44"/>
+      <c r="AG111" s="44"/>
+      <c r="AH111" s="44"/>
+      <c r="AI111" s="45"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10278,8 +10338,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="36"/>
-      <c r="Y112" s="51"/>
+      <c r="X112" s="41"/>
+      <c r="Y112" s="57"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10340,12 +10400,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="44"/>
-      <c r="AE113" s="45"/>
-      <c r="AF113" s="45"/>
-      <c r="AG113" s="45"/>
-      <c r="AH113" s="45"/>
-      <c r="AI113" s="46"/>
+      <c r="AD113" s="75"/>
+      <c r="AE113" s="76"/>
+      <c r="AF113" s="76"/>
+      <c r="AG113" s="76"/>
+      <c r="AH113" s="76"/>
+      <c r="AI113" s="77"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10384,10 +10444,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="35">
+      <c r="X114" s="40">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="50">
+      <c r="Y114" s="56">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10444,8 +10504,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="36"/>
-      <c r="Y115" s="51"/>
+      <c r="X115" s="41"/>
+      <c r="Y115" s="57"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10506,12 +10566,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="44"/>
-      <c r="AE116" s="45"/>
-      <c r="AF116" s="45"/>
-      <c r="AG116" s="45"/>
-      <c r="AH116" s="45"/>
-      <c r="AI116" s="46"/>
+      <c r="AD116" s="75"/>
+      <c r="AE116" s="76"/>
+      <c r="AF116" s="76"/>
+      <c r="AG116" s="76"/>
+      <c r="AH116" s="76"/>
+      <c r="AI116" s="77"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10550,10 +10610,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="35">
+      <c r="X117" s="40">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="50">
+      <c r="Y117" s="56">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10564,14 +10624,14 @@
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="47" t="s">
+      <c r="AD117" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="48"/>
-      <c r="AF117" s="48"/>
-      <c r="AG117" s="48"/>
-      <c r="AH117" s="48"/>
-      <c r="AI117" s="49"/>
+      <c r="AE117" s="44"/>
+      <c r="AF117" s="44"/>
+      <c r="AG117" s="44"/>
+      <c r="AH117" s="44"/>
+      <c r="AI117" s="45"/>
       <c r="AJ117" s="19"/>
       <c r="AK117" s="19"/>
       <c r="AL117" s="20"/>
@@ -10610,8 +10670,8 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="36"/>
-      <c r="Y118" s="51"/>
+      <c r="X118" s="41"/>
+      <c r="Y118" s="57"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
@@ -10672,12 +10732,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="44"/>
-      <c r="AE119" s="45"/>
-      <c r="AF119" s="45"/>
-      <c r="AG119" s="45"/>
-      <c r="AH119" s="45"/>
-      <c r="AI119" s="46"/>
+      <c r="AD119" s="75"/>
+      <c r="AE119" s="76"/>
+      <c r="AF119" s="76"/>
+      <c r="AG119" s="76"/>
+      <c r="AH119" s="76"/>
+      <c r="AI119" s="77"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10716,10 +10776,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="35">
+      <c r="X120" s="40">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="56">
+      <c r="Y120" s="54">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10776,8 +10836,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="36"/>
-      <c r="Y121" s="57"/>
+      <c r="X121" s="41"/>
+      <c r="Y121" s="55"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10786,14 +10846,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="47" t="s">
+      <c r="AD121" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="48"/>
-      <c r="AF121" s="48"/>
-      <c r="AG121" s="48"/>
-      <c r="AH121" s="48"/>
-      <c r="AI121" s="49"/>
+      <c r="AE121" s="44"/>
+      <c r="AF121" s="44"/>
+      <c r="AG121" s="44"/>
+      <c r="AH121" s="44"/>
+      <c r="AI121" s="45"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10838,12 +10898,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="44"/>
-      <c r="AE122" s="45"/>
-      <c r="AF122" s="45"/>
-      <c r="AG122" s="45"/>
-      <c r="AH122" s="45"/>
-      <c r="AI122" s="46"/>
+      <c r="AD122" s="75"/>
+      <c r="AE122" s="76"/>
+      <c r="AF122" s="76"/>
+      <c r="AG122" s="76"/>
+      <c r="AH122" s="76"/>
+      <c r="AI122" s="77"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -10882,10 +10942,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="35">
+      <c r="X123" s="40">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="42">
+      <c r="Y123" s="46">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -10950,8 +11010,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="36"/>
-      <c r="Y124" s="43"/>
+      <c r="X124" s="41"/>
+      <c r="Y124" s="47"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11020,12 +11080,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="44"/>
-      <c r="AE125" s="45"/>
-      <c r="AF125" s="45"/>
-      <c r="AG125" s="45"/>
-      <c r="AH125" s="45"/>
-      <c r="AI125" s="46"/>
+      <c r="AD125" s="75"/>
+      <c r="AE125" s="76"/>
+      <c r="AF125" s="76"/>
+      <c r="AG125" s="76"/>
+      <c r="AH125" s="76"/>
+      <c r="AI125" s="77"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11067,7 +11127,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="42">
+      <c r="Y126" s="46">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11125,17 +11185,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="43"/>
+      <c r="Y127" s="47"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="44"/>
-      <c r="AE127" s="45"/>
-      <c r="AF127" s="45"/>
-      <c r="AG127" s="45"/>
-      <c r="AH127" s="45"/>
-      <c r="AI127" s="46"/>
+      <c r="AD127" s="75"/>
+      <c r="AE127" s="76"/>
+      <c r="AF127" s="76"/>
+      <c r="AG127" s="76"/>
+      <c r="AH127" s="76"/>
+      <c r="AI127" s="77"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11174,10 +11234,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="35">
+      <c r="X128" s="40">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="40">
+      <c r="Y128" s="52">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11234,8 +11294,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="36"/>
-      <c r="Y129" s="41"/>
+      <c r="X129" s="41"/>
+      <c r="Y129" s="53"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11296,12 +11356,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="44"/>
-      <c r="AE130" s="45"/>
-      <c r="AF130" s="45"/>
-      <c r="AG130" s="45"/>
-      <c r="AH130" s="45"/>
-      <c r="AI130" s="46"/>
+      <c r="AD130" s="75"/>
+      <c r="AE130" s="76"/>
+      <c r="AF130" s="76"/>
+      <c r="AG130" s="76"/>
+      <c r="AH130" s="76"/>
+      <c r="AI130" s="77"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11340,10 +11400,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="35" t="s">
+      <c r="X131" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="42">
+      <c r="Y131" s="46">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11400,8 +11460,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="36"/>
-      <c r="Y132" s="43"/>
+      <c r="X132" s="41"/>
+      <c r="Y132" s="47"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11462,12 +11522,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="44"/>
-      <c r="AE133" s="45"/>
-      <c r="AF133" s="45"/>
-      <c r="AG133" s="45"/>
-      <c r="AH133" s="45"/>
-      <c r="AI133" s="46"/>
+      <c r="AD133" s="75"/>
+      <c r="AE133" s="76"/>
+      <c r="AF133" s="76"/>
+      <c r="AG133" s="76"/>
+      <c r="AH133" s="76"/>
+      <c r="AI133" s="77"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11520,14 +11580,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="52" t="s">
+      <c r="AD134" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="52"/>
-      <c r="AF134" s="52"/>
-      <c r="AG134" s="52"/>
-      <c r="AH134" s="52"/>
-      <c r="AI134" s="52"/>
+      <c r="AE134" s="42"/>
+      <c r="AF134" s="42"/>
+      <c r="AG134" s="42"/>
+      <c r="AH134" s="42"/>
+      <c r="AI134" s="42"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11565,8 +11625,8 @@
     <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G153" s="67"/>
-      <c r="H153" s="67"/>
+      <c r="G153" s="89"/>
+      <c r="H153" s="89"/>
     </row>
     <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11604,61 +11664,481 @@
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="X131:X132"/>
+    <mergeCell ref="X128:X129"/>
+    <mergeCell ref="AD129:AI129"/>
+    <mergeCell ref="AD132:AI132"/>
+    <mergeCell ref="Y128:Y129"/>
+    <mergeCell ref="Y131:Y132"/>
+    <mergeCell ref="AD115:AI115"/>
+    <mergeCell ref="AD116:AI116"/>
+    <mergeCell ref="AD117:AI117"/>
+    <mergeCell ref="AD118:AI118"/>
+    <mergeCell ref="AD119:AI119"/>
+    <mergeCell ref="AD120:AI120"/>
+    <mergeCell ref="AD109:AI109"/>
+    <mergeCell ref="AD110:AI110"/>
+    <mergeCell ref="AD111:AI111"/>
+    <mergeCell ref="AD104:AI104"/>
+    <mergeCell ref="AD105:AI105"/>
+    <mergeCell ref="AD106:AI106"/>
+    <mergeCell ref="X108:X109"/>
+    <mergeCell ref="Y108:Y109"/>
+    <mergeCell ref="X105:X106"/>
+    <mergeCell ref="AD88:AI88"/>
+    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
     <mergeCell ref="AS85:AX85"/>
     <mergeCell ref="AN86:AN87"/>
     <mergeCell ref="AS86:AX86"/>
@@ -11683,481 +12163,61 @@
     <mergeCell ref="BC33:BD33"/>
     <mergeCell ref="BC34:BD34"/>
     <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="X131:X132"/>
-    <mergeCell ref="X128:X129"/>
-    <mergeCell ref="AD129:AI129"/>
-    <mergeCell ref="AD132:AI132"/>
-    <mergeCell ref="Y128:Y129"/>
-    <mergeCell ref="Y131:Y132"/>
-    <mergeCell ref="AD115:AI115"/>
-    <mergeCell ref="AD116:AI116"/>
-    <mergeCell ref="AD117:AI117"/>
-    <mergeCell ref="AD118:AI118"/>
-    <mergeCell ref="AD119:AI119"/>
-    <mergeCell ref="AD120:AI120"/>
-    <mergeCell ref="AD109:AI109"/>
-    <mergeCell ref="AD110:AI110"/>
-    <mergeCell ref="AD111:AI111"/>
-    <mergeCell ref="AD104:AI104"/>
-    <mergeCell ref="AD105:AI105"/>
-    <mergeCell ref="AD106:AI106"/>
-    <mergeCell ref="X108:X109"/>
-    <mergeCell ref="Y108:Y109"/>
-    <mergeCell ref="X105:X106"/>
-    <mergeCell ref="AD88:AI88"/>
-    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB73CEAD-2EC5-4C44-AD3B-103D2F1E6072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4D993C-6C32-41E7-8329-5647AE1CAC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="217">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -696,7 +697,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,11 +1177,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1191,17 +1192,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1212,77 +1306,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1299,15 +1330,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1317,40 +1339,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1687,108 +1688,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="G2:BD230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="105.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.375" customWidth="1"/>
+    <col min="9" max="9" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="105.875" customWidth="1"/>
+    <col min="11" max="11" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.85546875" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.875" customWidth="1"/>
+    <col min="20" max="20" width="13.125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="104.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.28515625" customWidth="1"/>
+    <col min="22" max="22" width="11.125" customWidth="1"/>
+    <col min="23" max="23" width="10.625" customWidth="1"/>
+    <col min="24" max="24" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="104.25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.25" customWidth="1"/>
     <col min="35" max="35" width="37" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.85546875" customWidth="1"/>
-    <col min="39" max="39" width="6.85546875" customWidth="1"/>
-    <col min="40" max="40" width="13.5703125" customWidth="1"/>
-    <col min="41" max="41" width="105.5703125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.875" customWidth="1"/>
+    <col min="39" max="39" width="6.875" customWidth="1"/>
+    <col min="40" max="40" width="13.625" customWidth="1"/>
+    <col min="41" max="41" width="105.625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.375" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="45.85546875" customWidth="1"/>
-    <col min="51" max="51" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="16373" max="16373" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="45.875" customWidth="1"/>
+    <col min="51" max="51" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16373" max="16373" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I2" s="82" t="s">
+    <row r="2" spans="9:56" ht="18" customHeight="1">
+      <c r="I2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="76" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="72" t="s">
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="76" t="s">
+      <c r="U2" s="83"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="78"/>
-      <c r="AJ2" s="71" t="s">
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="71"/>
-      <c r="AN2" s="74" t="s">
+      <c r="AK2" s="81"/>
+      <c r="AN2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="75" t="s">
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AQ2" s="84"/>
+      <c r="AR2" s="84"/>
+      <c r="AS2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="75"/>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="75"/>
-      <c r="AY2" s="71" t="s">
+      <c r="AT2" s="85"/>
+      <c r="AU2" s="85"/>
+      <c r="AV2" s="85"/>
+      <c r="AW2" s="85"/>
+      <c r="AX2" s="85"/>
+      <c r="AY2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71" t="s">
+      <c r="BB2" s="81"/>
+      <c r="BC2" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="71"/>
-    </row>
-    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BD2" s="81"/>
+    </row>
+    <row r="3" spans="9:56" ht="18" customHeight="1">
       <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1804,12 +1806,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="85"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="87"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="74"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1834,12 +1836,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="81"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="88"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1861,12 +1863,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="75"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1879,13 +1881,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="71" t="s">
+      <c r="BC3" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="71"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I4" s="92">
+      <c r="BD3" s="81"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" hidden="1" customHeight="1">
+      <c r="I4" s="62">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1914,10 +1916,10 @@
       <c r="U4" s="6"/>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="35">
+      <c r="X4" s="40">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="88">
+      <c r="Y4" s="50">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1946,7 +1948,7 @@
       <c r="AK4" s="6"/>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="68">
+      <c r="AN4" s="90">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1975,11 +1977,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I5" s="69"/>
+      <c r="BC4" s="35"/>
+      <c r="BD4" s="35"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" hidden="1" customHeight="1">
+      <c r="I5" s="63"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1992,7 +1994,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="N5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2006,8 +2008,8 @@
       <c r="U5" s="6"/>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="89"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="51"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2020,21 +2022,21 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="91" t="s">
+      <c r="AD5" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46"/>
+      <c r="AE5" s="76"/>
+      <c r="AF5" s="76"/>
+      <c r="AG5" s="76"/>
+      <c r="AH5" s="76"/>
+      <c r="AI5" s="77"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
       <c r="AK5" s="6"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="69"/>
+      <c r="AN5" s="63"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2047,7 +2049,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="66" t="s">
+      <c r="AS5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2061,11 +2063,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="46"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I6" s="70"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="77"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" hidden="1" customHeight="1">
+      <c r="I6" s="64"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2092,8 +2094,8 @@
       <c r="U6" s="6"/>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="90"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="79"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2106,21 +2108,21 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AD6" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="77"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
       <c r="AK6" s="6"/>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="70"/>
+      <c r="AN6" s="64"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2147,11 +2149,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="64"/>
-      <c r="BD6" s="64"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="35">
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="35"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" customHeight="1">
+      <c r="I7" s="40">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2186,17 +2188,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="45"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="76"/>
+      <c r="AG7" s="76"/>
+      <c r="AH7" s="76"/>
+      <c r="AI7" s="77"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="35">
+      <c r="AN7" s="40">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2225,11 +2227,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I8" s="36"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" hidden="1" customHeight="1">
+      <c r="I8" s="41"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2256,10 +2258,10 @@
       <c r="U8" s="6"/>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="52">
+      <c r="X8" s="42">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="88">
+      <c r="Y8" s="50">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2288,7 +2290,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="55"/>
+      <c r="AN8" s="48"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2315,11 +2317,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="64"/>
-      <c r="BD8" s="64"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="35">
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="35"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" hidden="1" customHeight="1">
+      <c r="I9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2348,8 +2350,8 @@
       <c r="U9" s="6"/>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="89"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="51"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2376,7 +2378,7 @@
       <c r="AK9" s="6"/>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="35">
+      <c r="AN9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2405,11 +2407,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="64"/>
-      <c r="BD9" s="64"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I10" s="36"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="35"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" customHeight="1">
+      <c r="I10" s="41"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2442,17 +2444,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="77"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="55"/>
+      <c r="AN10" s="48"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2479,11 +2481,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="64"/>
-      <c r="BD10" s="64"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I11" s="35">
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="35"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" hidden="1" customHeight="1">
+      <c r="I11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2498,7 +2500,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="66" t="s">
+      <c r="N11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2512,10 +2514,10 @@
       <c r="U11" s="6"/>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="52">
+      <c r="X11" s="42">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="42">
+      <c r="Y11" s="46">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2544,7 +2546,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="35">
+      <c r="AN11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2559,7 +2561,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="66" t="s">
+      <c r="AS11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2573,11 +2575,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="64"/>
-      <c r="BD11" s="64"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I12" s="55"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="35"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" hidden="1" customHeight="1">
+      <c r="I12" s="48"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2590,7 +2592,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2604,8 +2606,8 @@
       <c r="U12" s="6"/>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="43"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="47"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2632,7 +2634,7 @@
       <c r="AK12" s="6"/>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="55"/>
+      <c r="AN12" s="48"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2645,7 +2647,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="66" t="s">
+      <c r="AS12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2659,11 +2661,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="64"/>
-      <c r="BD12" s="64"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I13" s="36"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" customHeight="1">
+      <c r="I13" s="41"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2696,17 +2698,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="45"/>
-      <c r="AF13" s="45"/>
-      <c r="AG13" s="45"/>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="46"/>
+      <c r="AD13" s="75"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="77"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="36"/>
+      <c r="AN13" s="41"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2733,11 +2735,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="64"/>
-      <c r="BD13" s="64"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I14" s="35">
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="35"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I14" s="40">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2766,10 +2768,10 @@
       <c r="U14" s="6"/>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="52">
+      <c r="X14" s="42">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="40">
+      <c r="Y14" s="52">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2784,7 +2786,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="66" t="s">
+      <c r="AD14" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2798,7 +2800,7 @@
       <c r="AK14" s="6"/>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="35">
+      <c r="AN14" s="40">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2827,11 +2829,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="64"/>
-      <c r="BD14" s="64"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="55"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="35"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I15" s="48"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2858,8 +2860,8 @@
       <c r="U15" s="6"/>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="62"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="78"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2872,7 +2874,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="66" t="s">
+      <c r="AD15" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2886,7 +2888,7 @@
       <c r="AK15" s="6"/>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="55"/>
+      <c r="AN15" s="48"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2913,11 +2915,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="64"/>
-      <c r="BD15" s="64"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I16" s="36"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="35"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I16" s="41"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2944,8 +2946,8 @@
       <c r="U16" s="6"/>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="41"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="53"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2972,7 +2974,7 @@
       <c r="AK16" s="6"/>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="55"/>
+      <c r="AN16" s="48"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -2999,11 +3001,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="65"/>
-      <c r="BD16" s="65"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="53">
+      <c r="BC16" s="36"/>
+      <c r="BD16" s="36"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" customHeight="1">
+      <c r="I17" s="92">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3038,17 +3040,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="46"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="77"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="93">
+      <c r="AN17" s="49">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3077,11 +3079,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="64"/>
-      <c r="BD17" s="64"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I18" s="54"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="35"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I18" s="93"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3108,10 +3110,10 @@
       <c r="U18" s="6"/>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="52">
+      <c r="X18" s="42">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="40">
+      <c r="Y18" s="52">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3140,7 +3142,7 @@
       <c r="AK18" s="6"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="93"/>
+      <c r="AN18" s="49"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3167,11 +3169,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="64"/>
-      <c r="BD18" s="64"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I19" s="35" t="s">
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="35"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3194,8 +3196,8 @@
       <c r="U19" s="6"/>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="62"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="78"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3222,7 +3224,7 @@
       <c r="AK19" s="6"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="35" t="s">
+      <c r="AN19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3245,11 +3247,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="64"/>
-      <c r="BD19" s="64"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I20" s="36"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I20" s="41"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3270,8 +3272,8 @@
       <c r="U20" s="7"/>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="52"/>
-      <c r="Y20" s="41"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="53"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3298,7 +3300,7 @@
       <c r="AK20" s="7"/>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="36"/>
+      <c r="AN20" s="41"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3319,11 +3321,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="64"/>
-      <c r="BD20" s="64"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I21" s="35">
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="35"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" customHeight="1">
+      <c r="I21" s="40">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3360,17 +3362,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="46"/>
+      <c r="AD21" s="75"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="77"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="35">
+      <c r="AN21" s="40">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3401,11 +3403,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="64"/>
-      <c r="BD21" s="64"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I22" s="55"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="35"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I22" s="48"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3434,10 +3436,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="93">
+      <c r="X22" s="49">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="40">
+      <c r="Y22" s="52">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3466,7 +3468,7 @@
       <c r="AK22" s="7"/>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="55"/>
+      <c r="AN22" s="48"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3495,11 +3497,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I23" s="36"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="35"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I23" s="41"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3528,8 +3530,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="93"/>
-      <c r="Y23" s="41"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="53"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3556,7 +3558,7 @@
       <c r="AK23" s="7"/>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="36"/>
+      <c r="AN23" s="41"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3585,11 +3587,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="64"/>
-      <c r="BD23" s="64"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I24" s="35" t="s">
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="35"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" customHeight="1">
+      <c r="I24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3626,17 +3628,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="44"/>
-      <c r="AE24" s="45"/>
-      <c r="AF24" s="45"/>
-      <c r="AG24" s="45"/>
-      <c r="AH24" s="45"/>
-      <c r="AI24" s="46"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="76"/>
+      <c r="AF24" s="76"/>
+      <c r="AG24" s="76"/>
+      <c r="AH24" s="76"/>
+      <c r="AI24" s="77"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="35" t="s">
+      <c r="AN24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3667,11 +3669,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="64"/>
-      <c r="BD24" s="64"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I25" s="36"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="35"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" customHeight="1">
+      <c r="I25" s="41"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3700,10 +3702,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="35" t="s">
+      <c r="X25" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="42">
+      <c r="Y25" s="46">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3726,7 +3728,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="36"/>
+      <c r="AN25" s="41"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3755,11 +3757,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="64"/>
-      <c r="BD25" s="64"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I26" s="35" t="s">
+      <c r="BC25" s="35"/>
+      <c r="BD25" s="35"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" customHeight="1">
+      <c r="I26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3790,8 +3792,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="43"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="47"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3812,7 +3814,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="35" t="s">
+      <c r="AN26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3843,11 +3845,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="64"/>
-      <c r="BD26" s="64"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I27" s="36"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" customHeight="1">
+      <c r="I27" s="41"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3882,17 +3884,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="44"/>
-      <c r="AE27" s="45"/>
-      <c r="AF27" s="45"/>
-      <c r="AG27" s="45"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="46"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="77"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="36"/>
+      <c r="AN27" s="41"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3921,11 +3923,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="64"/>
-      <c r="BD27" s="64"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I28" s="35" t="s">
+      <c r="BC27" s="35"/>
+      <c r="BD27" s="35"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3956,10 +3958,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="35">
+      <c r="X28" s="40">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="58">
+      <c r="Y28" s="60">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -3990,7 +3992,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="35" t="s">
+      <c r="AN28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4021,11 +4023,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="65"/>
-      <c r="BD28" s="65"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I29" s="55"/>
+      <c r="BC28" s="36"/>
+      <c r="BD28" s="36"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I29" s="48"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4054,8 +4056,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="63"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="91"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4084,7 +4086,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="55"/>
+      <c r="AN29" s="48"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4113,11 +4115,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="64"/>
-      <c r="BD29" s="64"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I30" s="36"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I30" s="41"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4146,8 +4148,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="59"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="61"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4176,7 +4178,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="36"/>
+      <c r="AN30" s="41"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4205,11 +4207,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="64"/>
-      <c r="BD30" s="64"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I31" s="35">
+      <c r="BC30" s="35"/>
+      <c r="BD30" s="35"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" customHeight="1">
+      <c r="I31" s="40">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4246,17 +4248,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="44"/>
-      <c r="AE31" s="45"/>
-      <c r="AF31" s="45"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="45"/>
-      <c r="AI31" s="46"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="77"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="35">
+      <c r="AN31" s="40">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4287,11 +4289,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="64"/>
-      <c r="BD31" s="64"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="36"/>
+      <c r="BC31" s="35"/>
+      <c r="BD31" s="35"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I32" s="41"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4320,10 +4322,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="35">
+      <c r="X32" s="40">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="58">
+      <c r="Y32" s="60">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4354,7 +4356,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="36"/>
+      <c r="AN32" s="41"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4383,11 +4385,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="64"/>
-      <c r="BD32" s="64"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I33" s="35">
+      <c r="BC32" s="35"/>
+      <c r="BD32" s="35"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I33" s="40">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4418,8 +4420,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="59"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="61"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4448,7 +4450,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="35">
+      <c r="AN33" s="40">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4479,11 +4481,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="64"/>
-      <c r="BD33" s="64"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I34" s="36"/>
+      <c r="BC33" s="35"/>
+      <c r="BD33" s="35"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" customHeight="1">
+      <c r="I34" s="41"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4518,17 +4520,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="44"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="46"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="36"/>
+      <c r="AN34" s="41"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4557,11 +4559,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="64"/>
-      <c r="BD34" s="64"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I35" s="35">
+      <c r="BC34" s="35"/>
+      <c r="BD34" s="35"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4592,10 +4594,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="35" t="s">
+      <c r="X35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="42">
+      <c r="Y35" s="46">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4626,7 +4628,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="35">
+      <c r="AN35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4657,11 +4659,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="64"/>
-      <c r="BD35" s="64"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I36" s="36"/>
+      <c r="BC35" s="35"/>
+      <c r="BD35" s="35"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I36" s="41"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4690,8 +4692,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="43"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="47"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4720,7 +4722,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="36"/>
+      <c r="AN36" s="41"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4749,11 +4751,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="64"/>
-      <c r="BD36" s="64"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I37" s="35">
+      <c r="BC36" s="35"/>
+      <c r="BD36" s="35"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" customHeight="1">
+      <c r="I37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4790,17 +4792,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="44"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="46"/>
+      <c r="AD37" s="75"/>
+      <c r="AE37" s="76"/>
+      <c r="AF37" s="76"/>
+      <c r="AG37" s="76"/>
+      <c r="AH37" s="76"/>
+      <c r="AI37" s="77"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="35">
+      <c r="AN37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4831,11 +4833,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="64"/>
-      <c r="BD37" s="64"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I38" s="36"/>
+      <c r="BC37" s="35"/>
+      <c r="BD37" s="35"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I38" s="41"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4864,10 +4866,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="35" t="s">
+      <c r="X38" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="40">
+      <c r="Y38" s="52">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4898,7 +4900,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="36"/>
+      <c r="AN38" s="41"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4927,10 +4929,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="64"/>
-      <c r="BD38" s="64"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC38" s="35"/>
+      <c r="BD38" s="35"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" hidden="1" customHeight="1">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -4962,8 +4964,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="62"/>
+      <c r="X39" s="48"/>
+      <c r="Y39" s="78"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5023,11 +5025,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="64"/>
-      <c r="BD39" s="64"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I40" s="35">
+      <c r="BC39" s="35"/>
+      <c r="BD39" s="35"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5058,8 +5060,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="36"/>
-      <c r="Y40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="53"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5088,7 +5090,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="35">
+      <c r="AN40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5119,11 +5121,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="65"/>
-      <c r="BD40" s="65"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="36"/>
+      <c r="BC40" s="36"/>
+      <c r="BD40" s="36"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" customHeight="1">
+      <c r="I41" s="41"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5136,14 +5138,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="47" t="s">
+      <c r="N41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="49"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="45"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5158,17 +5160,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="44"/>
-      <c r="AE41" s="45"/>
-      <c r="AF41" s="45"/>
-      <c r="AG41" s="45"/>
-      <c r="AH41" s="45"/>
-      <c r="AI41" s="46"/>
+      <c r="AD41" s="75"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="76"/>
+      <c r="AG41" s="76"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="77"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="36"/>
+      <c r="AN41" s="41"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5181,14 +5183,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="47" t="s">
+      <c r="AS41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="48"/>
-      <c r="AU41" s="48"/>
-      <c r="AV41" s="48"/>
-      <c r="AW41" s="48"/>
-      <c r="AX41" s="49"/>
+      <c r="AT41" s="44"/>
+      <c r="AU41" s="44"/>
+      <c r="AV41" s="44"/>
+      <c r="AW41" s="44"/>
+      <c r="AX41" s="45"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5197,10 +5199,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="64"/>
-      <c r="BD41" s="64"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC41" s="35"/>
+      <c r="BD41" s="35"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" hidden="1" customHeight="1">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5232,10 +5234,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="35">
+      <c r="X42" s="40">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="40">
+      <c r="Y42" s="52">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5297,11 +5299,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="64"/>
-      <c r="BD42" s="64"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="35">
+      <c r="BC42" s="35"/>
+      <c r="BD42" s="35"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I43" s="40">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5332,8 +5334,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="53"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5362,7 +5364,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="35">
+      <c r="AN43" s="40">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5393,11 +5395,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="64"/>
-      <c r="BD43" s="64"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="36"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" customHeight="1">
+      <c r="I44" s="41"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5432,17 +5434,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="44"/>
-      <c r="AE44" s="45"/>
-      <c r="AF44" s="45"/>
-      <c r="AG44" s="45"/>
-      <c r="AH44" s="45"/>
-      <c r="AI44" s="46"/>
+      <c r="AD44" s="75"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="76"/>
+      <c r="AG44" s="76"/>
+      <c r="AH44" s="76"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="36"/>
+      <c r="AN44" s="41"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5471,10 +5473,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="64"/>
-      <c r="BD44" s="64"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" hidden="1" customHeight="1">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5506,10 +5508,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="35">
+      <c r="X45" s="40">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="58">
+      <c r="Y45" s="60">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5571,11 +5573,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="64"/>
-      <c r="BD45" s="64"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="35" t="s">
+      <c r="BC45" s="35"/>
+      <c r="BD45" s="35"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5606,8 +5608,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="59"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="61"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5636,7 +5638,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="35" t="s">
+      <c r="AN46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5667,11 +5669,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="64"/>
-      <c r="BD46" s="64"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="36"/>
+      <c r="BC46" s="35"/>
+      <c r="BD46" s="35"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" customHeight="1">
+      <c r="I47" s="41"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5706,17 +5708,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="45"/>
-      <c r="AF47" s="45"/>
-      <c r="AG47" s="45"/>
-      <c r="AH47" s="45"/>
-      <c r="AI47" s="46"/>
+      <c r="AD47" s="75"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="76"/>
+      <c r="AG47" s="76"/>
+      <c r="AH47" s="76"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="36"/>
+      <c r="AN47" s="41"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5745,11 +5747,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="64"/>
-      <c r="BD47" s="64"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="35" t="s">
+      <c r="BC47" s="35"/>
+      <c r="BD47" s="35"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" hidden="1" customHeight="1">
+      <c r="I48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5780,10 +5782,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="35">
+      <c r="X48" s="40">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="42">
+      <c r="Y48" s="46">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5814,7 +5816,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="35" t="s">
+      <c r="AN48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5845,11 +5847,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="64"/>
-      <c r="BD48" s="64"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="36"/>
+      <c r="BC48" s="35"/>
+      <c r="BD48" s="35"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" hidden="1" customHeight="1">
+      <c r="I49" s="41"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5878,8 +5880,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="43"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="47"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5908,7 +5910,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="36"/>
+      <c r="AN49" s="41"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5937,12 +5939,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="64"/>
-      <c r="BD49" s="64"/>
-    </row>
-    <row r="50" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="BC49" s="35"/>
+      <c r="BD49" s="35"/>
+    </row>
+    <row r="50" spans="8:56">
       <c r="H50" s="10"/>
-      <c r="I50" s="35">
+      <c r="I50" s="40">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -5957,14 +5959,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="47" t="s">
+      <c r="N50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-      <c r="R50" s="48"/>
-      <c r="S50" s="49"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="45"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -5979,17 +5981,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="45"/>
-      <c r="AG50" s="45"/>
-      <c r="AH50" s="45"/>
-      <c r="AI50" s="46"/>
+      <c r="AD50" s="75"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="76"/>
+      <c r="AH50" s="76"/>
+      <c r="AI50" s="77"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="35">
+      <c r="AN50" s="40">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6000,23 +6002,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="47" t="s">
+      <c r="AS50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="48"/>
-      <c r="AU50" s="48"/>
-      <c r="AV50" s="48"/>
-      <c r="AW50" s="48"/>
-      <c r="AX50" s="49"/>
+      <c r="AT50" s="44"/>
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="45"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="64"/>
-      <c r="BD50" s="64"/>
-    </row>
-    <row r="51" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I51" s="36"/>
+      <c r="BC50" s="35"/>
+      <c r="BD50" s="35"/>
+    </row>
+    <row r="51" spans="8:56" hidden="1">
+      <c r="I51" s="41"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6029,14 +6031,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="47" t="s">
+      <c r="N51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="49"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="45"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6045,10 +6047,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="35">
+      <c r="X51" s="40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="40">
+      <c r="Y51" s="52">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6079,7 +6081,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="36"/>
+      <c r="AN51" s="41"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6088,23 +6090,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="47" t="s">
+      <c r="AS51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="48"/>
-      <c r="AU51" s="48"/>
-      <c r="AV51" s="48"/>
-      <c r="AW51" s="48"/>
-      <c r="AX51" s="49"/>
+      <c r="AT51" s="44"/>
+      <c r="AU51" s="44"/>
+      <c r="AV51" s="44"/>
+      <c r="AW51" s="44"/>
+      <c r="AX51" s="45"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="64"/>
-      <c r="BD51" s="64"/>
-    </row>
-    <row r="52" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I52" s="35">
+      <c r="BC51" s="35"/>
+      <c r="BD51" s="35"/>
+    </row>
+    <row r="52" spans="8:56" hidden="1">
+      <c r="I52" s="40">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6135,8 +6137,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="36"/>
-      <c r="Y52" s="41"/>
+      <c r="X52" s="41"/>
+      <c r="Y52" s="53"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6165,7 +6167,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="35">
+      <c r="AN52" s="40">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6188,11 +6190,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="65"/>
-      <c r="BD52" s="65"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I53" s="36"/>
+      <c r="BC52" s="36"/>
+      <c r="BD52" s="36"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" customHeight="1">
+      <c r="I53" s="41"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6227,17 +6229,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="44"/>
-      <c r="AE53" s="45"/>
-      <c r="AF53" s="45"/>
-      <c r="AG53" s="45"/>
-      <c r="AH53" s="45"/>
-      <c r="AI53" s="46"/>
+      <c r="AD53" s="75"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="76"/>
+      <c r="AG53" s="76"/>
+      <c r="AH53" s="76"/>
+      <c r="AI53" s="77"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="36"/>
+      <c r="AN53" s="41"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6258,11 +6260,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="64"/>
-      <c r="BD53" s="64"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I54" s="35">
+      <c r="BC53" s="35"/>
+      <c r="BD53" s="35"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" hidden="1" customHeight="1">
+      <c r="I54" s="40">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6327,7 +6329,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="35">
+      <c r="AN54" s="40">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6350,11 +6352,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="64"/>
-      <c r="BD54" s="64"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I55" s="36"/>
+      <c r="BC54" s="35"/>
+      <c r="BD54" s="35"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" customHeight="1">
+      <c r="I55" s="41"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6389,17 +6391,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="44"/>
-      <c r="AE55" s="45"/>
-      <c r="AF55" s="45"/>
-      <c r="AG55" s="45"/>
-      <c r="AH55" s="45"/>
-      <c r="AI55" s="46"/>
+      <c r="AD55" s="75"/>
+      <c r="AE55" s="76"/>
+      <c r="AF55" s="76"/>
+      <c r="AG55" s="76"/>
+      <c r="AH55" s="76"/>
+      <c r="AI55" s="77"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="36"/>
+      <c r="AN55" s="41"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6420,10 +6422,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="64"/>
-      <c r="BD55" s="64"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC55" s="35"/>
+      <c r="BD55" s="35"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" hidden="1" customHeight="1">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6455,10 +6457,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="35">
+      <c r="X56" s="40">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="58">
+      <c r="Y56" s="60">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6512,11 +6514,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="64"/>
-      <c r="BD56" s="64"/>
-    </row>
-    <row r="57" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I57" s="35">
+      <c r="BC56" s="35"/>
+      <c r="BD56" s="35"/>
+    </row>
+    <row r="57" spans="8:56" hidden="1">
+      <c r="I57" s="40">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6547,8 +6549,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="36"/>
-      <c r="Y57" s="59"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="61"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6559,14 +6561,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="47" t="s">
+      <c r="AD57" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="48"/>
-      <c r="AF57" s="48"/>
-      <c r="AG57" s="48"/>
-      <c r="AH57" s="48"/>
-      <c r="AI57" s="49"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="44"/>
+      <c r="AI57" s="45"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6575,7 +6577,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="35">
+      <c r="AN57" s="40">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6598,11 +6600,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="64"/>
-      <c r="BD57" s="64"/>
-    </row>
-    <row r="58" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I58" s="36"/>
+      <c r="BC57" s="35"/>
+      <c r="BD57" s="35"/>
+    </row>
+    <row r="58" spans="8:56">
+      <c r="I58" s="41"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6637,17 +6639,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="44"/>
-      <c r="AE58" s="45"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="45"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
+      <c r="AD58" s="75"/>
+      <c r="AE58" s="76"/>
+      <c r="AF58" s="76"/>
+      <c r="AG58" s="76"/>
+      <c r="AH58" s="76"/>
+      <c r="AI58" s="77"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="36"/>
+      <c r="AN58" s="41"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6668,11 +6670,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="64"/>
-      <c r="BD58" s="64"/>
-    </row>
-    <row r="59" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I59" s="35">
+      <c r="BC58" s="35"/>
+      <c r="BD58" s="35"/>
+    </row>
+    <row r="59" spans="8:56" hidden="1">
+      <c r="I59" s="40">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6737,7 +6739,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="35">
+      <c r="AN59" s="40">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6760,11 +6762,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="64"/>
-      <c r="BD59" s="64"/>
-    </row>
-    <row r="60" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I60" s="36"/>
+      <c r="BC59" s="35"/>
+      <c r="BD59" s="35"/>
+    </row>
+    <row r="60" spans="8:56">
+      <c r="I60" s="41"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6799,17 +6801,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="44"/>
-      <c r="AE60" s="45"/>
-      <c r="AF60" s="45"/>
-      <c r="AG60" s="45"/>
-      <c r="AH60" s="45"/>
-      <c r="AI60" s="46"/>
+      <c r="AD60" s="75"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="77"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="36"/>
+      <c r="AN60" s="41"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6830,11 +6832,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="64"/>
-      <c r="BD60" s="64"/>
-    </row>
-    <row r="61" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I61" s="35" t="s">
+      <c r="BC60" s="35"/>
+      <c r="BD60" s="35"/>
+    </row>
+    <row r="61" spans="8:56" hidden="1">
+      <c r="I61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6865,10 +6867,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="35">
+      <c r="X61" s="40">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="60">
+      <c r="Y61" s="58">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6899,7 +6901,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="35" t="s">
+      <c r="AN61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6922,11 +6924,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="64"/>
-      <c r="BD61" s="64"/>
-    </row>
-    <row r="62" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I62" s="36"/>
+      <c r="BC61" s="35"/>
+      <c r="BD61" s="35"/>
+    </row>
+    <row r="62" spans="8:56" hidden="1">
+      <c r="I62" s="41"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -6955,8 +6957,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="61"/>
+      <c r="X62" s="41"/>
+      <c r="Y62" s="59"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -6985,7 +6987,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="36"/>
+      <c r="AN62" s="41"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7006,11 +7008,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="64"/>
-      <c r="BD62" s="64"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I63" s="35">
+      <c r="BC62" s="35"/>
+      <c r="BD62" s="35"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" customHeight="1">
+      <c r="I63" s="40">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7047,17 +7049,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="44"/>
-      <c r="AE63" s="45"/>
-      <c r="AF63" s="45"/>
-      <c r="AG63" s="45"/>
-      <c r="AH63" s="45"/>
-      <c r="AI63" s="46"/>
+      <c r="AD63" s="75"/>
+      <c r="AE63" s="76"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="76"/>
+      <c r="AH63" s="76"/>
+      <c r="AI63" s="77"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="35">
+      <c r="AN63" s="40">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7080,11 +7082,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="64"/>
-      <c r="BD63" s="64"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I64" s="36"/>
+      <c r="BC63" s="35"/>
+      <c r="BD63" s="35"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" hidden="1" customHeight="1">
+      <c r="I64" s="41"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7147,7 +7149,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="36"/>
+      <c r="AN64" s="41"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7168,11 +7170,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="65"/>
-      <c r="BD64" s="65"/>
-    </row>
-    <row r="65" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I65" s="35">
+      <c r="BC64" s="36"/>
+      <c r="BD64" s="36"/>
+    </row>
+    <row r="65" spans="9:56">
+      <c r="I65" s="40">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7201,17 +7203,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="44"/>
-      <c r="AE65" s="45"/>
-      <c r="AF65" s="45"/>
-      <c r="AG65" s="45"/>
-      <c r="AH65" s="45"/>
-      <c r="AI65" s="46"/>
+      <c r="AD65" s="75"/>
+      <c r="AE65" s="76"/>
+      <c r="AF65" s="76"/>
+      <c r="AG65" s="76"/>
+      <c r="AH65" s="76"/>
+      <c r="AI65" s="77"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="35">
+      <c r="AN65" s="40">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7234,11 +7236,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="64"/>
-      <c r="BD65" s="64"/>
-    </row>
-    <row r="66" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I66" s="36"/>
+      <c r="BC65" s="35"/>
+      <c r="BD65" s="35"/>
+    </row>
+    <row r="66" spans="9:56" hidden="1">
+      <c r="I66" s="41"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7259,10 +7261,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="35" t="s">
+      <c r="X66" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="56">
+      <c r="Y66" s="54">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7293,7 +7295,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="36"/>
+      <c r="AN66" s="41"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7314,10 +7316,10 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="64"/>
-      <c r="BD66" s="64"/>
-    </row>
-    <row r="67" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC66" s="35"/>
+      <c r="BD66" s="35"/>
+    </row>
+    <row r="67" spans="9:56" hidden="1">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
@@ -7341,8 +7343,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="36"/>
-      <c r="Y67" s="57"/>
+      <c r="X67" s="41"/>
+      <c r="Y67" s="55"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7394,11 +7396,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="64"/>
-      <c r="BD67" s="64"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I68" s="35">
+      <c r="BC67" s="35"/>
+      <c r="BD67" s="35"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" customHeight="1">
+      <c r="I68" s="40">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7427,17 +7429,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="44"/>
-      <c r="AE68" s="45"/>
-      <c r="AF68" s="45"/>
-      <c r="AG68" s="45"/>
-      <c r="AH68" s="45"/>
-      <c r="AI68" s="46"/>
+      <c r="AD68" s="75"/>
+      <c r="AE68" s="76"/>
+      <c r="AF68" s="76"/>
+      <c r="AG68" s="76"/>
+      <c r="AH68" s="76"/>
+      <c r="AI68" s="77"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="35">
+      <c r="AN68" s="40">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7460,11 +7462,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="64"/>
-      <c r="BD68" s="64"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I69" s="36"/>
+      <c r="BC68" s="35"/>
+      <c r="BD68" s="35"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" hidden="1" customHeight="1">
+      <c r="I69" s="41"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7485,10 +7487,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="35" t="s">
+      <c r="X69" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="56">
+      <c r="Y69" s="54">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7519,7 +7521,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="36"/>
+      <c r="AN69" s="41"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7540,10 +7542,10 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="64"/>
-      <c r="BD69" s="64"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC69" s="35"/>
+      <c r="BD69" s="35"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" hidden="1" customHeight="1">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
@@ -7567,8 +7569,8 @@
       <c r="U70" s="6"/>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="36"/>
-      <c r="Y70" s="57"/>
+      <c r="X70" s="41"/>
+      <c r="Y70" s="55"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7620,11 +7622,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="64"/>
-      <c r="BD70" s="64"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I71" s="35">
+      <c r="BC70" s="35"/>
+      <c r="BD70" s="35"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" customHeight="1">
+      <c r="I71" s="40">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7653,17 +7655,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="44"/>
-      <c r="AE71" s="45"/>
-      <c r="AF71" s="45"/>
-      <c r="AG71" s="45"/>
-      <c r="AH71" s="45"/>
-      <c r="AI71" s="46"/>
+      <c r="AD71" s="75"/>
+      <c r="AE71" s="76"/>
+      <c r="AF71" s="76"/>
+      <c r="AG71" s="76"/>
+      <c r="AH71" s="76"/>
+      <c r="AI71" s="77"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="35">
+      <c r="AN71" s="40">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7686,11 +7688,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="64"/>
-      <c r="BD71" s="64"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I72" s="36"/>
+      <c r="BC71" s="35"/>
+      <c r="BD71" s="35"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" hidden="1" customHeight="1">
+      <c r="I72" s="41"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7711,10 +7713,10 @@
       <c r="U72" s="6"/>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="35">
+      <c r="X72" s="40">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="40">
+      <c r="Y72" s="52">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7729,19 +7731,19 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="47" t="s">
+      <c r="AD72" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="48"/>
-      <c r="AF72" s="48"/>
-      <c r="AG72" s="48"/>
-      <c r="AH72" s="48"/>
-      <c r="AI72" s="49"/>
+      <c r="AE72" s="44"/>
+      <c r="AF72" s="44"/>
+      <c r="AG72" s="44"/>
+      <c r="AH72" s="44"/>
+      <c r="AI72" s="45"/>
       <c r="AJ72" s="19"/>
       <c r="AK72" s="19"/>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="36"/>
+      <c r="AN72" s="41"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7762,11 +7764,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="64"/>
-      <c r="BD72" s="64"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I73" s="35">
+      <c r="BC72" s="35"/>
+      <c r="BD72" s="35"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" hidden="1" customHeight="1">
+      <c r="I73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7777,20 +7779,20 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="47" t="s">
+      <c r="N73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="48"/>
-      <c r="P73" s="48"/>
-      <c r="Q73" s="48"/>
-      <c r="R73" s="48"/>
-      <c r="S73" s="49"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="44"/>
+      <c r="S73" s="45"/>
       <c r="T73" s="7"/>
       <c r="U73" s="6"/>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="36"/>
-      <c r="Y73" s="41"/>
+      <c r="X73" s="41"/>
+      <c r="Y73" s="53"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7803,19 +7805,19 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="47" t="s">
+      <c r="AD73" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="48"/>
-      <c r="AF73" s="48"/>
-      <c r="AG73" s="48"/>
-      <c r="AH73" s="48"/>
-      <c r="AI73" s="49"/>
+      <c r="AE73" s="44"/>
+      <c r="AF73" s="44"/>
+      <c r="AG73" s="44"/>
+      <c r="AH73" s="44"/>
+      <c r="AI73" s="45"/>
       <c r="AJ73" s="19"/>
       <c r="AK73" s="19"/>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="35">
+      <c r="AN73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7826,23 +7828,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="47" t="s">
+      <c r="AS73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="48"/>
-      <c r="AU73" s="48"/>
-      <c r="AV73" s="48"/>
-      <c r="AW73" s="48"/>
-      <c r="AX73" s="49"/>
+      <c r="AT73" s="44"/>
+      <c r="AU73" s="44"/>
+      <c r="AV73" s="44"/>
+      <c r="AW73" s="44"/>
+      <c r="AX73" s="45"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="64"/>
-      <c r="BD73" s="64"/>
-    </row>
-    <row r="74" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I74" s="36"/>
+      <c r="BC73" s="35"/>
+      <c r="BD73" s="35"/>
+    </row>
+    <row r="74" spans="9:56">
+      <c r="I74" s="41"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7869,17 +7871,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="44"/>
-      <c r="AE74" s="45"/>
-      <c r="AF74" s="45"/>
-      <c r="AG74" s="45"/>
-      <c r="AH74" s="45"/>
-      <c r="AI74" s="46"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="76"/>
+      <c r="AF74" s="76"/>
+      <c r="AG74" s="76"/>
+      <c r="AH74" s="76"/>
+      <c r="AI74" s="77"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="36"/>
+      <c r="AN74" s="41"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7900,11 +7902,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="64"/>
-      <c r="BD74" s="64"/>
-    </row>
-    <row r="75" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I75" s="35">
+      <c r="BC74" s="35"/>
+      <c r="BD74" s="35"/>
+    </row>
+    <row r="75" spans="9:56" hidden="1">
+      <c r="I75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7915,22 +7917,22 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="47" t="s">
+      <c r="N75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="49"/>
+      <c r="O75" s="44"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="44"/>
+      <c r="R75" s="44"/>
+      <c r="S75" s="45"/>
       <c r="T75" s="7"/>
       <c r="U75" s="6"/>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="35">
+      <c r="X75" s="40">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="58">
+      <c r="Y75" s="60">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -7957,7 +7959,7 @@
       <c r="AK75" s="19"/>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="35">
+      <c r="AN75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -7968,23 +7970,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="47" t="s">
+      <c r="AS75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="48"/>
-      <c r="AU75" s="48"/>
-      <c r="AV75" s="48"/>
-      <c r="AW75" s="48"/>
-      <c r="AX75" s="49"/>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="44"/>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="44"/>
+      <c r="AX75" s="45"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="64"/>
-      <c r="BD75" s="64"/>
-    </row>
-    <row r="76" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I76" s="36"/>
+      <c r="BC75" s="35"/>
+      <c r="BD75" s="35"/>
+    </row>
+    <row r="76" spans="9:56" hidden="1">
+      <c r="I76" s="41"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8005,8 +8007,8 @@
       <c r="U76" s="6"/>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="36"/>
-      <c r="Y76" s="59"/>
+      <c r="X76" s="41"/>
+      <c r="Y76" s="61"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8031,7 +8033,7 @@
       <c r="AK76" s="19"/>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="36"/>
+      <c r="AN76" s="41"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8052,11 +8054,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="65"/>
-      <c r="BD76" s="65"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I77" s="35">
+      <c r="BC76" s="36"/>
+      <c r="BD76" s="36"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" customHeight="1">
+      <c r="I77" s="40">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8085,17 +8087,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="44"/>
-      <c r="AE77" s="45"/>
-      <c r="AF77" s="45"/>
-      <c r="AG77" s="45"/>
-      <c r="AH77" s="45"/>
-      <c r="AI77" s="46"/>
+      <c r="AD77" s="75"/>
+      <c r="AE77" s="76"/>
+      <c r="AF77" s="76"/>
+      <c r="AG77" s="76"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="77"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="35">
+      <c r="AN77" s="40">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8118,11 +8120,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="64"/>
-      <c r="BD77" s="64"/>
-    </row>
-    <row r="78" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I78" s="36"/>
+      <c r="BC77" s="35"/>
+      <c r="BD77" s="35"/>
+    </row>
+    <row r="78" spans="9:56" hidden="1">
+      <c r="I78" s="41"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8143,10 +8145,10 @@
       <c r="U78" s="6"/>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="35">
+      <c r="X78" s="40">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="40">
+      <c r="Y78" s="52">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8173,7 +8175,7 @@
       <c r="AK78" s="19"/>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="36"/>
+      <c r="AN78" s="41"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8194,11 +8196,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="64"/>
-      <c r="BD78" s="64"/>
-    </row>
-    <row r="79" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I79" s="35">
+      <c r="BC78" s="35"/>
+      <c r="BD78" s="35"/>
+    </row>
+    <row r="79" spans="9:56" hidden="1">
+      <c r="I79" s="40">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8209,20 +8211,20 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="47" t="s">
+      <c r="N79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="48"/>
-      <c r="P79" s="48"/>
-      <c r="Q79" s="48"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="49"/>
+      <c r="O79" s="44"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="44"/>
+      <c r="R79" s="44"/>
+      <c r="S79" s="45"/>
       <c r="T79" s="7"/>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="36"/>
-      <c r="Y79" s="41"/>
+      <c r="X79" s="41"/>
+      <c r="Y79" s="53"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8247,7 +8249,7 @@
       <c r="AK79" s="19"/>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="35">
+      <c r="AN79" s="40">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8258,23 +8260,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="47" t="s">
+      <c r="AS79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="48"/>
-      <c r="AU79" s="48"/>
-      <c r="AV79" s="48"/>
-      <c r="AW79" s="48"/>
-      <c r="AX79" s="49"/>
+      <c r="AT79" s="44"/>
+      <c r="AU79" s="44"/>
+      <c r="AV79" s="44"/>
+      <c r="AW79" s="44"/>
+      <c r="AX79" s="45"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="64"/>
-      <c r="BD79" s="64"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I80" s="36"/>
+      <c r="BC79" s="35"/>
+      <c r="BD79" s="35"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" customHeight="1">
+      <c r="I80" s="41"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8301,17 +8303,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="44"/>
-      <c r="AE80" s="45"/>
-      <c r="AF80" s="45"/>
-      <c r="AG80" s="45"/>
-      <c r="AH80" s="45"/>
-      <c r="AI80" s="46"/>
+      <c r="AD80" s="75"/>
+      <c r="AE80" s="76"/>
+      <c r="AF80" s="76"/>
+      <c r="AG80" s="76"/>
+      <c r="AH80" s="76"/>
+      <c r="AI80" s="77"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="36"/>
+      <c r="AN80" s="41"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8332,11 +8334,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="64"/>
-      <c r="BD80" s="64"/>
-    </row>
-    <row r="81" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I81" s="35">
+      <c r="BC80" s="35"/>
+      <c r="BD80" s="35"/>
+    </row>
+    <row r="81" spans="9:56" hidden="1">
+      <c r="I81" s="40">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8389,7 +8391,7 @@
       <c r="AK81" s="19"/>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="35">
+      <c r="AN81" s="40">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8412,11 +8414,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="64"/>
-      <c r="BD81" s="64"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I82" s="36"/>
+      <c r="BC81" s="35"/>
+      <c r="BD81" s="35"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" customHeight="1">
+      <c r="I82" s="41"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8425,14 +8427,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="47" t="s">
+      <c r="N82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="48"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="48"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="49"/>
+      <c r="O82" s="44"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="44"/>
+      <c r="R82" s="44"/>
+      <c r="S82" s="45"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8443,17 +8445,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="44"/>
-      <c r="AE82" s="45"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="45"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
+      <c r="AD82" s="75"/>
+      <c r="AE82" s="76"/>
+      <c r="AF82" s="76"/>
+      <c r="AG82" s="76"/>
+      <c r="AH82" s="76"/>
+      <c r="AI82" s="77"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="36"/>
+      <c r="AN82" s="41"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8462,23 +8464,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="47" t="s">
+      <c r="AS82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="48"/>
-      <c r="AU82" s="48"/>
-      <c r="AV82" s="48"/>
-      <c r="AW82" s="48"/>
-      <c r="AX82" s="49"/>
+      <c r="AT82" s="44"/>
+      <c r="AU82" s="44"/>
+      <c r="AV82" s="44"/>
+      <c r="AW82" s="44"/>
+      <c r="AX82" s="45"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="64"/>
-      <c r="BD82" s="64"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I83" s="35">
+      <c r="BC82" s="35"/>
+      <c r="BD82" s="35"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" hidden="1" customHeight="1">
+      <c r="I83" s="40">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8509,10 +8511,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="35">
+      <c r="X83" s="40">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="56">
+      <c r="Y83" s="54">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8539,7 +8541,7 @@
       <c r="AK83" s="19"/>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="35">
+      <c r="AN83" s="40">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8568,11 +8570,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="64"/>
-      <c r="BD83" s="64"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I84" s="36"/>
+      <c r="BC83" s="35"/>
+      <c r="BD83" s="35"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" hidden="1" customHeight="1">
+      <c r="I84" s="41"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8601,8 +8603,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="36"/>
-      <c r="Y84" s="57"/>
+      <c r="X84" s="41"/>
+      <c r="Y84" s="55"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8627,7 +8629,7 @@
       <c r="AK84" s="19"/>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="36"/>
+      <c r="AN84" s="41"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8654,10 +8656,10 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="64"/>
-      <c r="BD84" s="64"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC84" s="35"/>
+      <c r="BD84" s="35"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" customHeight="1">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
@@ -8687,12 +8689,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="44"/>
-      <c r="AE85" s="45"/>
-      <c r="AF85" s="45"/>
-      <c r="AG85" s="45"/>
-      <c r="AH85" s="45"/>
-      <c r="AI85" s="46"/>
+      <c r="AD85" s="75"/>
+      <c r="AE85" s="76"/>
+      <c r="AF85" s="76"/>
+      <c r="AG85" s="76"/>
+      <c r="AH85" s="76"/>
+      <c r="AI85" s="77"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8720,11 +8722,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="64"/>
-      <c r="BD85" s="64"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I86" s="35">
+      <c r="BC85" s="35"/>
+      <c r="BD85" s="35"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" hidden="1" customHeight="1">
+      <c r="I86" s="40">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8747,10 +8749,10 @@
       <c r="U86" s="6"/>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="35">
+      <c r="X86" s="40">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="50">
+      <c r="Y86" s="56">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8777,7 +8779,7 @@
       <c r="AK86" s="19"/>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="35">
+      <c r="AN86" s="40">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8800,11 +8802,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="64"/>
-      <c r="BD86" s="64"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I87" s="36"/>
+      <c r="BC86" s="35"/>
+      <c r="BD86" s="35"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" hidden="1" customHeight="1">
+      <c r="I87" s="41"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8825,8 +8827,8 @@
       <c r="U87" s="6"/>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="36"/>
-      <c r="Y87" s="51"/>
+      <c r="X87" s="41"/>
+      <c r="Y87" s="57"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8851,7 +8853,7 @@
       <c r="AK87" s="19"/>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="36"/>
+      <c r="AN87" s="41"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8872,11 +8874,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="64"/>
-      <c r="BD87" s="64"/>
-    </row>
-    <row r="88" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I88" s="35" t="s">
+      <c r="BC87" s="35"/>
+      <c r="BD87" s="35"/>
+    </row>
+    <row r="88" spans="9:56">
+      <c r="I88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -8905,17 +8907,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="44"/>
-      <c r="AE88" s="45"/>
-      <c r="AF88" s="45"/>
-      <c r="AG88" s="45"/>
-      <c r="AH88" s="45"/>
-      <c r="AI88" s="46"/>
+      <c r="AD88" s="75"/>
+      <c r="AE88" s="76"/>
+      <c r="AF88" s="76"/>
+      <c r="AG88" s="76"/>
+      <c r="AH88" s="76"/>
+      <c r="AI88" s="77"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="35" t="s">
+      <c r="AN88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -8938,11 +8940,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="65"/>
-      <c r="BD88" s="65"/>
-    </row>
-    <row r="89" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I89" s="36"/>
+      <c r="BC88" s="36"/>
+      <c r="BD88" s="36"/>
+    </row>
+    <row r="89" spans="9:56" hidden="1">
+      <c r="I89" s="41"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -8963,10 +8965,10 @@
       <c r="U89" s="6"/>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="35" t="s">
+      <c r="X89" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="50">
+      <c r="Y89" s="56">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -8993,7 +8995,7 @@
       <c r="AK89" s="19"/>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="36"/>
+      <c r="AN89" s="41"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9014,10 +9016,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="64"/>
-      <c r="BD89" s="64"/>
-    </row>
-    <row r="90" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC89" s="35"/>
+      <c r="BD89" s="35"/>
+    </row>
+    <row r="90" spans="9:56" hidden="1">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9029,20 +9031,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="52" t="s">
+      <c r="N90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
+      <c r="O90" s="42"/>
+      <c r="P90" s="42"/>
+      <c r="Q90" s="42"/>
+      <c r="R90" s="42"/>
+      <c r="S90" s="42"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="36"/>
-      <c r="Y90" s="51"/>
+      <c r="X90" s="41"/>
+      <c r="Y90" s="57"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9078,22 +9080,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="52" t="s">
+      <c r="AS90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
+      <c r="AT90" s="42"/>
+      <c r="AU90" s="42"/>
+      <c r="AV90" s="42"/>
+      <c r="AW90" s="42"/>
+      <c r="AX90" s="42"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="64"/>
-      <c r="BD90" s="64"/>
-    </row>
-    <row r="91" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC90" s="35"/>
+      <c r="BD90" s="35"/>
+    </row>
+    <row r="91" spans="9:56">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9115,12 +9117,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="44"/>
-      <c r="AE91" s="45"/>
-      <c r="AF91" s="45"/>
-      <c r="AG91" s="45"/>
-      <c r="AH91" s="45"/>
-      <c r="AI91" s="46"/>
+      <c r="AD91" s="75"/>
+      <c r="AE91" s="76"/>
+      <c r="AF91" s="76"/>
+      <c r="AG91" s="76"/>
+      <c r="AH91" s="76"/>
+      <c r="AI91" s="77"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9143,7 +9145,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="92" spans="9:56" hidden="1">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9159,10 +9161,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="35">
+      <c r="X92" s="40">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="58">
+      <c r="Y92" s="60">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9207,7 +9209,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="93" spans="9:56" hidden="1">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9223,8 +9225,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="36"/>
-      <c r="Y93" s="59"/>
+      <c r="X93" s="41"/>
+      <c r="Y93" s="61"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9267,7 +9269,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="9:56" ht="15" customHeight="1">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9289,12 +9291,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="44"/>
-      <c r="AE94" s="45"/>
-      <c r="AF94" s="45"/>
-      <c r="AG94" s="45"/>
-      <c r="AH94" s="45"/>
-      <c r="AI94" s="46"/>
+      <c r="AD94" s="75"/>
+      <c r="AE94" s="76"/>
+      <c r="AF94" s="76"/>
+      <c r="AG94" s="76"/>
+      <c r="AH94" s="76"/>
+      <c r="AI94" s="77"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9317,7 +9319,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="95" spans="9:56">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9333,10 +9335,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="35">
+      <c r="X95" s="40">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="60">
+      <c r="Y95" s="58">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9377,7 +9379,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="96" spans="9:56">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9393,8 +9395,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="36"/>
-      <c r="Y96" s="61"/>
+      <c r="X96" s="41"/>
+      <c r="Y96" s="59"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9433,7 +9435,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:56" ht="29.25" customHeight="1">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9455,12 +9457,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="44"/>
-      <c r="AE97" s="45"/>
-      <c r="AF97" s="45"/>
-      <c r="AG97" s="45"/>
-      <c r="AH97" s="45"/>
-      <c r="AI97" s="46"/>
+      <c r="AD97" s="75"/>
+      <c r="AE97" s="76"/>
+      <c r="AF97" s="76"/>
+      <c r="AG97" s="76"/>
+      <c r="AH97" s="76"/>
+      <c r="AI97" s="77"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9483,7 +9485,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:56">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9543,7 +9545,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:56">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9565,12 +9567,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="44"/>
-      <c r="AE99" s="45"/>
-      <c r="AF99" s="45"/>
-      <c r="AG99" s="45"/>
-      <c r="AH99" s="45"/>
-      <c r="AI99" s="46"/>
+      <c r="AD99" s="75"/>
+      <c r="AE99" s="76"/>
+      <c r="AF99" s="76"/>
+      <c r="AG99" s="76"/>
+      <c r="AH99" s="76"/>
+      <c r="AI99" s="77"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9593,7 +9595,7 @@
       <c r="BC99" s="20"/>
       <c r="BD99" s="20"/>
     </row>
-    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:56" ht="19.5" customHeight="1">
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -9609,16 +9611,18 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="35">
+      <c r="X100" s="40">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="40">
+      <c r="Y100" s="52">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AA100" s="33"/>
+      <c r="AA100" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB100" s="33"/>
       <c r="AC100" s="4" t="s">
         <v>13</v>
@@ -9653,7 +9657,7 @@
       <c r="BC100" s="20"/>
       <c r="BD100" s="20"/>
     </row>
-    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:56" ht="29.25" customHeight="1">
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -9669,12 +9673,14 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="36"/>
-      <c r="Y101" s="41"/>
+      <c r="X101" s="41"/>
+      <c r="Y101" s="53"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AA101" s="33"/>
+      <c r="AA101" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB101" s="33"/>
       <c r="AC101" s="4" t="s">
         <v>13</v>
@@ -9709,7 +9715,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:56">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -9731,12 +9737,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="44"/>
-      <c r="AE102" s="45"/>
-      <c r="AF102" s="45"/>
-      <c r="AG102" s="45"/>
-      <c r="AH102" s="45"/>
-      <c r="AI102" s="46"/>
+      <c r="AD102" s="75"/>
+      <c r="AE102" s="76"/>
+      <c r="AF102" s="76"/>
+      <c r="AG102" s="76"/>
+      <c r="AH102" s="76"/>
+      <c r="AI102" s="77"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9759,7 +9765,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:56" ht="15.75" customHeight="1">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -9819,7 +9825,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:56">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -9841,12 +9847,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="44"/>
-      <c r="AE104" s="45"/>
-      <c r="AF104" s="45"/>
-      <c r="AG104" s="45"/>
-      <c r="AH104" s="45"/>
-      <c r="AI104" s="46"/>
+      <c r="AD104" s="75"/>
+      <c r="AE104" s="76"/>
+      <c r="AF104" s="76"/>
+      <c r="AG104" s="76"/>
+      <c r="AH104" s="76"/>
+      <c r="AI104" s="77"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -9869,7 +9875,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:56" ht="14.25" customHeight="1">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -9886,10 +9892,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="35">
+      <c r="X105" s="40">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="50">
+      <c r="Y105" s="56">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -9930,7 +9936,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:56" ht="13.5" customHeight="1">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -9946,8 +9952,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="36"/>
-      <c r="Y106" s="51"/>
+      <c r="X106" s="41"/>
+      <c r="Y106" s="57"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -9986,7 +9992,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:56" ht="15" customHeight="1">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10008,12 +10014,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="44"/>
-      <c r="AE107" s="45"/>
-      <c r="AF107" s="45"/>
-      <c r="AG107" s="45"/>
-      <c r="AH107" s="45"/>
-      <c r="AI107" s="46"/>
+      <c r="AD107" s="75"/>
+      <c r="AE107" s="76"/>
+      <c r="AF107" s="76"/>
+      <c r="AG107" s="76"/>
+      <c r="AH107" s="76"/>
+      <c r="AI107" s="77"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10036,7 +10042,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:56">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10052,10 +10058,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="35">
+      <c r="X108" s="40">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="50">
+      <c r="Y108" s="56">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10066,14 +10072,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="47" t="s">
+      <c r="AD108" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="48"/>
-      <c r="AF108" s="48"/>
-      <c r="AG108" s="48"/>
-      <c r="AH108" s="48"/>
-      <c r="AI108" s="49"/>
+      <c r="AE108" s="44"/>
+      <c r="AF108" s="44"/>
+      <c r="AG108" s="44"/>
+      <c r="AH108" s="44"/>
+      <c r="AI108" s="45"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10096,7 +10102,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:56" ht="15" customHeight="1">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10112,8 +10118,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="36"/>
-      <c r="Y109" s="51"/>
+      <c r="X109" s="41"/>
+      <c r="Y109" s="57"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10152,7 +10158,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:56">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10174,12 +10180,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="44"/>
-      <c r="AE110" s="45"/>
-      <c r="AF110" s="45"/>
-      <c r="AG110" s="45"/>
-      <c r="AH110" s="45"/>
-      <c r="AI110" s="46"/>
+      <c r="AD110" s="75"/>
+      <c r="AE110" s="76"/>
+      <c r="AF110" s="76"/>
+      <c r="AG110" s="76"/>
+      <c r="AH110" s="76"/>
+      <c r="AI110" s="77"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10202,7 +10208,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:56">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10218,10 +10224,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="35">
+      <c r="X111" s="40">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="50">
+      <c r="Y111" s="56">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10232,14 +10238,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="47" t="s">
+      <c r="AD111" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="48"/>
-      <c r="AF111" s="48"/>
-      <c r="AG111" s="48"/>
-      <c r="AH111" s="48"/>
-      <c r="AI111" s="49"/>
+      <c r="AE111" s="44"/>
+      <c r="AF111" s="44"/>
+      <c r="AG111" s="44"/>
+      <c r="AH111" s="44"/>
+      <c r="AI111" s="45"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10262,7 +10268,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:56" ht="15" customHeight="1">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10278,8 +10284,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="36"/>
-      <c r="Y112" s="51"/>
+      <c r="X112" s="41"/>
+      <c r="Y112" s="57"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10318,7 +10324,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="113" spans="9:56">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10340,12 +10346,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="44"/>
-      <c r="AE113" s="45"/>
-      <c r="AF113" s="45"/>
-      <c r="AG113" s="45"/>
-      <c r="AH113" s="45"/>
-      <c r="AI113" s="46"/>
+      <c r="AD113" s="75"/>
+      <c r="AE113" s="76"/>
+      <c r="AF113" s="76"/>
+      <c r="AG113" s="76"/>
+      <c r="AH113" s="76"/>
+      <c r="AI113" s="77"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10368,7 +10374,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="9:56" ht="14.25" customHeight="1">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10384,10 +10390,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="35">
+      <c r="X114" s="40">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="50">
+      <c r="Y114" s="56">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10428,7 +10434,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="9:56" ht="13.5" customHeight="1">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10444,8 +10450,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="36"/>
-      <c r="Y115" s="51"/>
+      <c r="X115" s="41"/>
+      <c r="Y115" s="57"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10484,7 +10490,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="116" spans="9:56">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10506,12 +10512,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="44"/>
-      <c r="AE116" s="45"/>
-      <c r="AF116" s="45"/>
-      <c r="AG116" s="45"/>
-      <c r="AH116" s="45"/>
-      <c r="AI116" s="46"/>
+      <c r="AD116" s="75"/>
+      <c r="AE116" s="76"/>
+      <c r="AF116" s="76"/>
+      <c r="AG116" s="76"/>
+      <c r="AH116" s="76"/>
+      <c r="AI116" s="77"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10534,7 +10540,7 @@
       <c r="BC116" s="20"/>
       <c r="BD116" s="20"/>
     </row>
-    <row r="117" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="117" spans="9:56">
       <c r="I117" s="20"/>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -10550,28 +10556,30 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="35">
+      <c r="X117" s="40">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="50">
+      <c r="Y117" s="56">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AA117" s="33"/>
+      <c r="AA117" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB117" s="33"/>
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="47" t="s">
+      <c r="AD117" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="48"/>
-      <c r="AF117" s="48"/>
-      <c r="AG117" s="48"/>
-      <c r="AH117" s="48"/>
-      <c r="AI117" s="49"/>
+      <c r="AE117" s="44"/>
+      <c r="AF117" s="44"/>
+      <c r="AG117" s="44"/>
+      <c r="AH117" s="44"/>
+      <c r="AI117" s="45"/>
       <c r="AJ117" s="19"/>
       <c r="AK117" s="19"/>
       <c r="AL117" s="20"/>
@@ -10594,7 +10602,7 @@
       <c r="BC117" s="20"/>
       <c r="BD117" s="20"/>
     </row>
-    <row r="118" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="118" spans="9:56">
       <c r="I118" s="20"/>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -10610,12 +10618,14 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="36"/>
-      <c r="Y118" s="51"/>
+      <c r="X118" s="41"/>
+      <c r="Y118" s="57"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AA118" s="33"/>
+      <c r="AA118" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB118" s="33"/>
       <c r="AC118" s="4" t="s">
         <v>13</v>
@@ -10650,7 +10660,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="9:56" ht="28.5" customHeight="1">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10672,12 +10682,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="44"/>
-      <c r="AE119" s="45"/>
-      <c r="AF119" s="45"/>
-      <c r="AG119" s="45"/>
-      <c r="AH119" s="45"/>
-      <c r="AI119" s="46"/>
+      <c r="AD119" s="75"/>
+      <c r="AE119" s="76"/>
+      <c r="AF119" s="76"/>
+      <c r="AG119" s="76"/>
+      <c r="AH119" s="76"/>
+      <c r="AI119" s="77"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10700,7 +10710,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="9:56" ht="15" customHeight="1">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -10716,10 +10726,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="35">
+      <c r="X120" s="40">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="56">
+      <c r="Y120" s="54">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10760,7 +10770,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="9:56" ht="27.75" customHeight="1">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -10776,8 +10786,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="36"/>
-      <c r="Y121" s="57"/>
+      <c r="X121" s="41"/>
+      <c r="Y121" s="55"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10786,14 +10796,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="47" t="s">
+      <c r="AD121" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="48"/>
-      <c r="AF121" s="48"/>
-      <c r="AG121" s="48"/>
-      <c r="AH121" s="48"/>
-      <c r="AI121" s="49"/>
+      <c r="AE121" s="44"/>
+      <c r="AF121" s="44"/>
+      <c r="AG121" s="44"/>
+      <c r="AH121" s="44"/>
+      <c r="AI121" s="45"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10816,7 +10826,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="122" spans="9:56">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -10838,12 +10848,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="44"/>
-      <c r="AE122" s="45"/>
-      <c r="AF122" s="45"/>
-      <c r="AG122" s="45"/>
-      <c r="AH122" s="45"/>
-      <c r="AI122" s="46"/>
+      <c r="AD122" s="75"/>
+      <c r="AE122" s="76"/>
+      <c r="AF122" s="76"/>
+      <c r="AG122" s="76"/>
+      <c r="AH122" s="76"/>
+      <c r="AI122" s="77"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -10866,7 +10876,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="9:56" ht="15" hidden="1" customHeight="1">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -10882,10 +10892,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="35">
+      <c r="X123" s="40">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="42">
+      <c r="Y123" s="46">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -10934,7 +10944,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="9:56" ht="15" hidden="1" customHeight="1">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -10950,8 +10960,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="36"/>
-      <c r="Y124" s="43"/>
+      <c r="X124" s="41"/>
+      <c r="Y124" s="47"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -10998,7 +11008,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="9:56" ht="30" customHeight="1">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11020,12 +11030,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="44"/>
-      <c r="AE125" s="45"/>
-      <c r="AF125" s="45"/>
-      <c r="AG125" s="45"/>
-      <c r="AH125" s="45"/>
-      <c r="AI125" s="46"/>
+      <c r="AD125" s="75"/>
+      <c r="AE125" s="76"/>
+      <c r="AF125" s="76"/>
+      <c r="AG125" s="76"/>
+      <c r="AH125" s="76"/>
+      <c r="AI125" s="77"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11048,7 +11058,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="126" spans="9:56">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11067,7 +11077,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="42">
+      <c r="Y126" s="46">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11108,7 +11118,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="9:56" ht="15" customHeight="1">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11125,17 +11135,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="43"/>
+      <c r="Y127" s="47"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="44"/>
-      <c r="AE127" s="45"/>
-      <c r="AF127" s="45"/>
-      <c r="AG127" s="45"/>
-      <c r="AH127" s="45"/>
-      <c r="AI127" s="46"/>
+      <c r="AD127" s="75"/>
+      <c r="AE127" s="76"/>
+      <c r="AF127" s="76"/>
+      <c r="AG127" s="76"/>
+      <c r="AH127" s="76"/>
+      <c r="AI127" s="77"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11158,7 +11168,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="9:56" ht="30.75" customHeight="1">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11174,10 +11184,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="35">
+      <c r="X128" s="40">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="40">
+      <c r="Y128" s="52">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11218,7 +11228,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:56" ht="15" customHeight="1">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11234,8 +11244,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="36"/>
-      <c r="Y129" s="41"/>
+      <c r="X129" s="41"/>
+      <c r="Y129" s="53"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11274,7 +11284,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:56">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11296,12 +11306,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="44"/>
-      <c r="AE130" s="45"/>
-      <c r="AF130" s="45"/>
-      <c r="AG130" s="45"/>
-      <c r="AH130" s="45"/>
-      <c r="AI130" s="46"/>
+      <c r="AD130" s="75"/>
+      <c r="AE130" s="76"/>
+      <c r="AF130" s="76"/>
+      <c r="AG130" s="76"/>
+      <c r="AH130" s="76"/>
+      <c r="AI130" s="77"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11324,7 +11334,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:56" ht="15" customHeight="1">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11340,10 +11350,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="35" t="s">
+      <c r="X131" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="42">
+      <c r="Y131" s="46">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11384,7 +11394,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="9:56" ht="15" customHeight="1">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11400,8 +11410,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="36"/>
-      <c r="Y132" s="43"/>
+      <c r="X132" s="41"/>
+      <c r="Y132" s="47"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11440,7 +11450,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="9:56" ht="15" customHeight="1">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11462,12 +11472,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="44"/>
-      <c r="AE133" s="45"/>
-      <c r="AF133" s="45"/>
-      <c r="AG133" s="45"/>
-      <c r="AH133" s="45"/>
-      <c r="AI133" s="46"/>
+      <c r="AD133" s="75"/>
+      <c r="AE133" s="76"/>
+      <c r="AF133" s="76"/>
+      <c r="AG133" s="76"/>
+      <c r="AH133" s="76"/>
+      <c r="AI133" s="77"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11490,7 +11500,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="134" spans="9:56">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11520,14 +11530,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="52" t="s">
+      <c r="AD134" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="52"/>
-      <c r="AF134" s="52"/>
-      <c r="AG134" s="52"/>
-      <c r="AH134" s="52"/>
-      <c r="AI134" s="52"/>
+      <c r="AE134" s="42"/>
+      <c r="AF134" s="42"/>
+      <c r="AG134" s="42"/>
+      <c r="AH134" s="42"/>
+      <c r="AI134" s="42"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11550,115 +11560,539 @@
       <c r="BC134" s="20"/>
       <c r="BD134" s="20"/>
     </row>
-    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G153" s="67"/>
-      <c r="H153" s="67"/>
-    </row>
-    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="9:56" ht="15" customHeight="1"/>
+    <row r="136" spans="9:56" ht="18" customHeight="1"/>
+    <row r="137" spans="9:56" ht="15.75" customHeight="1"/>
+    <row r="139" spans="9:56" ht="15" customHeight="1"/>
+    <row r="140" spans="9:56" ht="15" customHeight="1"/>
+    <row r="141" spans="9:56" ht="15" customHeight="1"/>
+    <row r="143" spans="9:56" ht="15" customHeight="1"/>
+    <row r="144" spans="9:56" ht="15" customHeight="1"/>
+    <row r="145" spans="7:8" ht="15" customHeight="1"/>
+    <row r="147" spans="7:8" ht="15" customHeight="1"/>
+    <row r="148" spans="7:8" ht="15" customHeight="1"/>
+    <row r="149" spans="7:8" ht="15" customHeight="1"/>
+    <row r="151" spans="7:8" ht="15" customHeight="1"/>
+    <row r="152" spans="7:8" ht="15" customHeight="1"/>
+    <row r="153" spans="7:8" ht="15" customHeight="1">
+      <c r="G153" s="89"/>
+      <c r="H153" s="89"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" customHeight="1"/>
+    <row r="156" spans="7:8" ht="15" customHeight="1"/>
+    <row r="157" spans="7:8" ht="14.25" customHeight="1"/>
+    <row r="158" spans="7:8" ht="17.25" customHeight="1"/>
+    <row r="159" spans="7:8" ht="18" customHeight="1"/>
+    <row r="160" spans="7:8" ht="15" customHeight="1"/>
+    <row r="161" ht="15" customHeight="1"/>
+    <row r="162" ht="15" customHeight="1"/>
+    <row r="164" ht="15" customHeight="1"/>
+    <row r="165" ht="15" customHeight="1"/>
+    <row r="166" ht="15" customHeight="1"/>
+    <row r="167" ht="15" customHeight="1"/>
+    <row r="168" ht="15" customHeight="1"/>
+    <row r="169" ht="15" customHeight="1"/>
+    <row r="170" ht="15" customHeight="1"/>
+    <row r="171" ht="15" customHeight="1"/>
+    <row r="172" ht="15" customHeight="1"/>
+    <row r="173" ht="15" customHeight="1"/>
+    <row r="174" ht="15" customHeight="1"/>
+    <row r="176" ht="15" customHeight="1"/>
+    <row r="177" spans="23:23" ht="15" customHeight="1"/>
+    <row r="178" spans="23:23" ht="15" customHeight="1"/>
+    <row r="183" spans="23:23" ht="15.75" customHeight="1"/>
+    <row r="192" spans="23:23" ht="13.5" customHeight="1">
       <c r="W192" s="12"/>
     </row>
-    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="25.5" customHeight="1"/>
+    <row r="226" ht="22.5" customHeight="1"/>
+    <row r="228" ht="21.75" customHeight="1"/>
+    <row r="230" ht="22.5" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="X131:X132"/>
+    <mergeCell ref="X128:X129"/>
+    <mergeCell ref="AD129:AI129"/>
+    <mergeCell ref="AD132:AI132"/>
+    <mergeCell ref="Y128:Y129"/>
+    <mergeCell ref="Y131:Y132"/>
+    <mergeCell ref="AD115:AI115"/>
+    <mergeCell ref="AD116:AI116"/>
+    <mergeCell ref="AD117:AI117"/>
+    <mergeCell ref="AD118:AI118"/>
+    <mergeCell ref="AD119:AI119"/>
+    <mergeCell ref="AD120:AI120"/>
+    <mergeCell ref="AD109:AI109"/>
+    <mergeCell ref="AD110:AI110"/>
+    <mergeCell ref="AD111:AI111"/>
+    <mergeCell ref="AD104:AI104"/>
+    <mergeCell ref="AD105:AI105"/>
+    <mergeCell ref="AD106:AI106"/>
+    <mergeCell ref="X108:X109"/>
+    <mergeCell ref="Y108:Y109"/>
+    <mergeCell ref="X105:X106"/>
+    <mergeCell ref="AD88:AI88"/>
+    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
     <mergeCell ref="AS85:AX85"/>
     <mergeCell ref="AN86:AN87"/>
     <mergeCell ref="AS86:AX86"/>
@@ -11683,481 +12117,61 @@
     <mergeCell ref="BC33:BD33"/>
     <mergeCell ref="BC34:BD34"/>
     <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="X131:X132"/>
-    <mergeCell ref="X128:X129"/>
-    <mergeCell ref="AD129:AI129"/>
-    <mergeCell ref="AD132:AI132"/>
-    <mergeCell ref="Y128:Y129"/>
-    <mergeCell ref="Y131:Y132"/>
-    <mergeCell ref="AD115:AI115"/>
-    <mergeCell ref="AD116:AI116"/>
-    <mergeCell ref="AD117:AI117"/>
-    <mergeCell ref="AD118:AI118"/>
-    <mergeCell ref="AD119:AI119"/>
-    <mergeCell ref="AD120:AI120"/>
-    <mergeCell ref="AD109:AI109"/>
-    <mergeCell ref="AD110:AI110"/>
-    <mergeCell ref="AD111:AI111"/>
-    <mergeCell ref="AD104:AI104"/>
-    <mergeCell ref="AD105:AI105"/>
-    <mergeCell ref="AD106:AI106"/>
-    <mergeCell ref="X108:X109"/>
-    <mergeCell ref="Y108:Y109"/>
-    <mergeCell ref="X105:X106"/>
-    <mergeCell ref="AD88:AI88"/>
-    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFD31AD-02BA-440F-B801-B0CE1A7240F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A795F0-7A33-48E4-A6BF-3D609E066F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="217">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -1176,11 +1177,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1191,14 +1192,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1209,28 +1222,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1239,10 +1246,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1251,13 +1258,25 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1265,54 +1284,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1329,6 +1300,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1338,19 +1318,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1687,108 +1688,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="G2:BD230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="105.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.375" customWidth="1"/>
+    <col min="9" max="9" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="105.875" customWidth="1"/>
+    <col min="11" max="11" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.85546875" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.875" customWidth="1"/>
+    <col min="20" max="20" width="13.125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="104.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.28515625" customWidth="1"/>
+    <col min="22" max="22" width="11.125" customWidth="1"/>
+    <col min="23" max="23" width="10.625" customWidth="1"/>
+    <col min="24" max="24" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="104.25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.25" customWidth="1"/>
     <col min="35" max="35" width="37" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.85546875" customWidth="1"/>
-    <col min="39" max="39" width="6.85546875" customWidth="1"/>
-    <col min="40" max="40" width="13.5703125" customWidth="1"/>
-    <col min="41" max="41" width="105.5703125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.875" customWidth="1"/>
+    <col min="39" max="39" width="6.875" customWidth="1"/>
+    <col min="40" max="40" width="13.625" customWidth="1"/>
+    <col min="41" max="41" width="105.625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.375" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="45.85546875" customWidth="1"/>
-    <col min="51" max="51" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="16373" max="16373" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="45.875" customWidth="1"/>
+    <col min="51" max="51" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16373" max="16373" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I2" s="66" t="s">
+    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="69" t="s">
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="82" t="s">
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="83"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="69" t="s">
+      <c r="U2" s="73"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="74"/>
+      <c r="AA2" s="74"/>
+      <c r="AB2" s="74"/>
+      <c r="AC2" s="74"/>
+      <c r="AD2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="81" t="s">
+      <c r="AE2" s="77"/>
+      <c r="AF2" s="77"/>
+      <c r="AG2" s="77"/>
+      <c r="AH2" s="77"/>
+      <c r="AI2" s="78"/>
+      <c r="AJ2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="81"/>
-      <c r="AN2" s="84" t="s">
+      <c r="AK2" s="71"/>
+      <c r="AN2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="84"/>
-      <c r="AP2" s="84"/>
-      <c r="AQ2" s="84"/>
-      <c r="AR2" s="84"/>
-      <c r="AS2" s="85" t="s">
+      <c r="AO2" s="74"/>
+      <c r="AP2" s="74"/>
+      <c r="AQ2" s="74"/>
+      <c r="AR2" s="74"/>
+      <c r="AS2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="85"/>
-      <c r="AU2" s="85"/>
-      <c r="AV2" s="85"/>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="85"/>
-      <c r="AY2" s="81" t="s">
+      <c r="AT2" s="75"/>
+      <c r="AU2" s="75"/>
+      <c r="AV2" s="75"/>
+      <c r="AW2" s="75"/>
+      <c r="AX2" s="75"/>
+      <c r="AY2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="81"/>
-      <c r="BA2" s="81" t="s">
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="81"/>
-      <c r="BC2" s="81" t="s">
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="81"/>
-    </row>
-    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BD2" s="71"/>
+    </row>
+    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1804,12 +1806,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="72"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="74"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="87"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1834,12 +1836,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="88"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="81"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1861,12 +1863,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
+      <c r="AS3" s="75"/>
+      <c r="AT3" s="75"/>
+      <c r="AU3" s="75"/>
+      <c r="AV3" s="75"/>
+      <c r="AW3" s="75"/>
+      <c r="AX3" s="75"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1879,13 +1881,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="81" t="s">
+      <c r="BC3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="81"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I4" s="62">
+      <c r="BD3" s="71"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="92">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1914,10 +1916,10 @@
       <c r="U4" s="6"/>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="40">
+      <c r="X4" s="35">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="50">
+      <c r="Y4" s="88">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1946,7 +1948,7 @@
       <c r="AK4" s="6"/>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="90">
+      <c r="AN4" s="68">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1975,11 +1977,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I5" s="63"/>
+      <c r="BC4" s="64"/>
+      <c r="BD4" s="64"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="69"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1992,7 +1994,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2006,8 +2008,8 @@
       <c r="U5" s="6"/>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="51"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="89"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2020,21 +2022,21 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="80" t="s">
+      <c r="AD5" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="77"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="46"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
       <c r="AK5" s="6"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="63"/>
+      <c r="AN5" s="69"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2047,7 +2049,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="65" t="s">
+      <c r="AS5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2061,11 +2063,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="75"/>
-      <c r="BD5" s="77"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I6" s="64"/>
+      <c r="BC5" s="44"/>
+      <c r="BD5" s="46"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="70"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2092,8 +2094,8 @@
       <c r="U6" s="6"/>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="79"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="90"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2106,21 +2108,21 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="75" t="s">
+      <c r="AD6" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="76"/>
-      <c r="AI6" s="77"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="46"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
       <c r="AK6" s="6"/>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="64"/>
+      <c r="AN6" s="70"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2147,11 +2149,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="40">
+      <c r="BC6" s="64"/>
+      <c r="BD6" s="64"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I7" s="35">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2186,17 +2188,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="76"/>
-      <c r="AG7" s="76"/>
-      <c r="AH7" s="76"/>
-      <c r="AI7" s="77"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="45"/>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="45"/>
+      <c r="AH7" s="45"/>
+      <c r="AI7" s="46"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="40">
+      <c r="AN7" s="35">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2225,11 +2227,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="35"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I8" s="41"/>
+      <c r="BC7" s="64"/>
+      <c r="BD7" s="64"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="36"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2256,10 +2258,10 @@
       <c r="U8" s="6"/>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="42">
+      <c r="X8" s="52">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="50">
+      <c r="Y8" s="88">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2288,7 +2290,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="48"/>
+      <c r="AN8" s="55"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2315,11 +2317,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="35"/>
-      <c r="BD8" s="35"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="40">
+      <c r="BC8" s="64"/>
+      <c r="BD8" s="64"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2348,8 +2350,8 @@
       <c r="U9" s="6"/>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="51"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="89"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2376,7 +2378,7 @@
       <c r="AK9" s="6"/>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="40">
+      <c r="AN9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2405,11 +2407,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="35"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I10" s="41"/>
+      <c r="BC9" s="64"/>
+      <c r="BD9" s="64"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="36"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2442,17 +2444,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="76"/>
-      <c r="AG10" s="76"/>
-      <c r="AH10" s="76"/>
-      <c r="AI10" s="77"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="46"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="48"/>
+      <c r="AN10" s="55"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2479,11 +2481,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="35"/>
-      <c r="BD10" s="35"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I11" s="40">
+      <c r="BC10" s="64"/>
+      <c r="BD10" s="64"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2498,7 +2500,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="65" t="s">
+      <c r="N11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2512,10 +2514,10 @@
       <c r="U11" s="6"/>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="42">
+      <c r="X11" s="52">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="46">
+      <c r="Y11" s="42">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2544,7 +2546,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="40">
+      <c r="AN11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2559,7 +2561,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="65" t="s">
+      <c r="AS11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2573,11 +2575,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="35"/>
-      <c r="BD11" s="35"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I12" s="48"/>
+      <c r="BC11" s="64"/>
+      <c r="BD11" s="64"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="55"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2590,7 +2592,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="65" t="s">
+      <c r="N12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2604,8 +2606,8 @@
       <c r="U12" s="6"/>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="47"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="43"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2632,7 +2634,7 @@
       <c r="AK12" s="6"/>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="48"/>
+      <c r="AN12" s="55"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2645,7 +2647,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="65" t="s">
+      <c r="AS12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2659,11 +2661,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="35"/>
-      <c r="BD12" s="35"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I13" s="41"/>
+      <c r="BC12" s="64"/>
+      <c r="BD12" s="64"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" s="36"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2696,17 +2698,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="76"/>
-      <c r="AH13" s="76"/>
-      <c r="AI13" s="77"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="45"/>
+      <c r="AH13" s="45"/>
+      <c r="AI13" s="46"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="41"/>
+      <c r="AN13" s="36"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2733,11 +2735,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="35"/>
-      <c r="BD13" s="35"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I14" s="40">
+      <c r="BC13" s="64"/>
+      <c r="BD13" s="64"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I14" s="35">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2766,10 +2768,10 @@
       <c r="U14" s="6"/>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="42">
+      <c r="X14" s="52">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="52">
+      <c r="Y14" s="40">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2784,7 +2786,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="65" t="s">
+      <c r="AD14" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2798,7 +2800,7 @@
       <c r="AK14" s="6"/>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="40">
+      <c r="AN14" s="35">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2827,11 +2829,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="35"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="48"/>
+      <c r="BC14" s="64"/>
+      <c r="BD14" s="64"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I15" s="55"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2858,8 +2860,8 @@
       <c r="U15" s="6"/>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="78"/>
+      <c r="X15" s="52"/>
+      <c r="Y15" s="62"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2872,7 +2874,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="65" t="s">
+      <c r="AD15" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2886,7 +2888,7 @@
       <c r="AK15" s="6"/>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="48"/>
+      <c r="AN15" s="55"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2913,11 +2915,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="35"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I16" s="41"/>
+      <c r="BC15" s="64"/>
+      <c r="BD15" s="64"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="36"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2944,8 +2946,8 @@
       <c r="U16" s="6"/>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="53"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="41"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2972,7 +2974,7 @@
       <c r="AK16" s="6"/>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="48"/>
+      <c r="AN16" s="55"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -2999,11 +3001,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="36"/>
-      <c r="BD16" s="36"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="92">
+      <c r="BC16" s="65"/>
+      <c r="BD16" s="65"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I17" s="53">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3038,17 +3040,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76"/>
-      <c r="AH17" s="76"/>
-      <c r="AI17" s="77"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="45"/>
+      <c r="AF17" s="45"/>
+      <c r="AG17" s="45"/>
+      <c r="AH17" s="45"/>
+      <c r="AI17" s="46"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="49">
+      <c r="AN17" s="93">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3077,11 +3079,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="35"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I18" s="93"/>
+      <c r="BC17" s="64"/>
+      <c r="BD17" s="64"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I18" s="54"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3108,10 +3110,10 @@
       <c r="U18" s="6"/>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="42">
+      <c r="X18" s="52">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="52">
+      <c r="Y18" s="40">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3140,7 +3142,7 @@
       <c r="AK18" s="6"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="49"/>
+      <c r="AN18" s="93"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3167,11 +3169,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="35"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I19" s="40" t="s">
+      <c r="BC18" s="64"/>
+      <c r="BD18" s="64"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3194,8 +3196,8 @@
       <c r="U19" s="6"/>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="78"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="62"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3222,7 +3224,7 @@
       <c r="AK19" s="6"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="40" t="s">
+      <c r="AN19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3245,11 +3247,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="35"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I20" s="41"/>
+      <c r="BC19" s="64"/>
+      <c r="BD19" s="64"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="36"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3270,8 +3272,8 @@
       <c r="U20" s="7"/>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="53"/>
+      <c r="X20" s="52"/>
+      <c r="Y20" s="41"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3298,7 +3300,7 @@
       <c r="AK20" s="7"/>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="41"/>
+      <c r="AN20" s="36"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3319,11 +3321,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="35"/>
-      <c r="BD20" s="35"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I21" s="40">
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="64"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I21" s="35">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3360,17 +3362,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="76"/>
-      <c r="AG21" s="76"/>
-      <c r="AH21" s="76"/>
-      <c r="AI21" s="77"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="46"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="40">
+      <c r="AN21" s="35">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3401,11 +3403,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="35"/>
-      <c r="BD21" s="35"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I22" s="48"/>
+      <c r="BC21" s="64"/>
+      <c r="BD21" s="64"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I22" s="55"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3434,10 +3436,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="49">
+      <c r="X22" s="93">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="52">
+      <c r="Y22" s="40">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3466,7 +3468,7 @@
       <c r="AK22" s="7"/>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="48"/>
+      <c r="AN22" s="55"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3495,11 +3497,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="35"/>
-      <c r="BD22" s="35"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I23" s="41"/>
+      <c r="BC22" s="64"/>
+      <c r="BD22" s="64"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" s="36"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3528,8 +3530,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="53"/>
+      <c r="X23" s="93"/>
+      <c r="Y23" s="41"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3556,7 +3558,7 @@
       <c r="AK23" s="7"/>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="41"/>
+      <c r="AN23" s="36"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3585,11 +3587,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="35"/>
-      <c r="BD23" s="35"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I24" s="40" t="s">
+      <c r="BC23" s="64"/>
+      <c r="BD23" s="64"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3626,17 +3628,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="76"/>
-      <c r="AG24" s="76"/>
-      <c r="AH24" s="76"/>
-      <c r="AI24" s="77"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="45"/>
+      <c r="AI24" s="46"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="40" t="s">
+      <c r="AN24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3667,11 +3669,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="35"/>
-      <c r="BD24" s="35"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I25" s="41"/>
+      <c r="BC24" s="64"/>
+      <c r="BD24" s="64"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I25" s="36"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3700,10 +3702,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="40" t="s">
+      <c r="X25" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="46">
+      <c r="Y25" s="42">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3726,7 +3728,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="41"/>
+      <c r="AN25" s="36"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3755,11 +3757,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="35"/>
-      <c r="BD25" s="35"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I26" s="40" t="s">
+      <c r="BC25" s="64"/>
+      <c r="BD25" s="64"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3790,8 +3792,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="47"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="43"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3812,7 +3814,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="40" t="s">
+      <c r="AN26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3843,11 +3845,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="35"/>
-      <c r="BD26" s="35"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I27" s="41"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I27" s="36"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3882,17 +3884,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="76"/>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="77"/>
+      <c r="AD27" s="44"/>
+      <c r="AE27" s="45"/>
+      <c r="AF27" s="45"/>
+      <c r="AG27" s="45"/>
+      <c r="AH27" s="45"/>
+      <c r="AI27" s="46"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="41"/>
+      <c r="AN27" s="36"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3921,11 +3923,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="35"/>
-      <c r="BD27" s="35"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I28" s="40" t="s">
+      <c r="BC27" s="64"/>
+      <c r="BD27" s="64"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3956,10 +3958,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="40">
+      <c r="X28" s="35">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="60">
+      <c r="Y28" s="58">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -3990,7 +3992,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="40" t="s">
+      <c r="AN28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4021,11 +4023,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="36"/>
-      <c r="BD28" s="36"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I29" s="48"/>
+      <c r="BC28" s="65"/>
+      <c r="BD28" s="65"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="55"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4054,8 +4056,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="91"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="63"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4084,7 +4086,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="48"/>
+      <c r="AN29" s="55"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4113,11 +4115,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="35"/>
-      <c r="BD29" s="35"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I30" s="41"/>
+      <c r="BC29" s="64"/>
+      <c r="BD29" s="64"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I30" s="36"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4146,8 +4148,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="61"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="59"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4176,7 +4178,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="41"/>
+      <c r="AN30" s="36"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4205,11 +4207,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="35"/>
-      <c r="BD30" s="35"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I31" s="40">
+      <c r="BC30" s="64"/>
+      <c r="BD30" s="64"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I31" s="35">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4246,17 +4248,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="76"/>
-      <c r="AG31" s="76"/>
-      <c r="AH31" s="76"/>
-      <c r="AI31" s="77"/>
+      <c r="AD31" s="44"/>
+      <c r="AE31" s="45"/>
+      <c r="AF31" s="45"/>
+      <c r="AG31" s="45"/>
+      <c r="AH31" s="45"/>
+      <c r="AI31" s="46"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="40">
+      <c r="AN31" s="35">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4287,11 +4289,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="35"/>
-      <c r="BD31" s="35"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="41"/>
+      <c r="BC31" s="64"/>
+      <c r="BD31" s="64"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I32" s="36"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4320,10 +4322,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="40">
+      <c r="X32" s="35">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="60">
+      <c r="Y32" s="58">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4354,7 +4356,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="41"/>
+      <c r="AN32" s="36"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4383,11 +4385,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="35"/>
-      <c r="BD32" s="35"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I33" s="40">
+      <c r="BC32" s="64"/>
+      <c r="BD32" s="64"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I33" s="35">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4418,8 +4420,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="61"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="59"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4448,7 +4450,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="40">
+      <c r="AN33" s="35">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4479,11 +4481,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="35"/>
-      <c r="BD33" s="35"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I34" s="41"/>
+      <c r="BC33" s="64"/>
+      <c r="BD33" s="64"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I34" s="36"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4518,17 +4520,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="75"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
-      <c r="AI34" s="77"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="45"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="45"/>
+      <c r="AI34" s="46"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="41"/>
+      <c r="AN34" s="36"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4557,11 +4559,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="35"/>
-      <c r="BD34" s="35"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I35" s="40">
+      <c r="BC34" s="64"/>
+      <c r="BD34" s="64"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4592,10 +4594,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="40" t="s">
+      <c r="X35" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="46">
+      <c r="Y35" s="42">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4626,7 +4628,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="40">
+      <c r="AN35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4657,11 +4659,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="35"/>
-      <c r="BD35" s="35"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I36" s="41"/>
+      <c r="BC35" s="64"/>
+      <c r="BD35" s="64"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36" s="36"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4690,8 +4692,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="47"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="43"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4720,7 +4722,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="41"/>
+      <c r="AN36" s="36"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4749,11 +4751,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="35"/>
-      <c r="BD36" s="35"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I37" s="40">
+      <c r="BC36" s="64"/>
+      <c r="BD36" s="64"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4790,17 +4792,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="75"/>
-      <c r="AE37" s="76"/>
-      <c r="AF37" s="76"/>
-      <c r="AG37" s="76"/>
-      <c r="AH37" s="76"/>
-      <c r="AI37" s="77"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="45"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="46"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="40">
+      <c r="AN37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4831,11 +4833,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="35"/>
-      <c r="BD37" s="35"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I38" s="41"/>
+      <c r="BC37" s="64"/>
+      <c r="BD37" s="64"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" s="36"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4864,10 +4866,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="40" t="s">
+      <c r="X38" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="52">
+      <c r="Y38" s="40">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4898,7 +4900,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="41"/>
+      <c r="AN38" s="36"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4927,10 +4929,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="35"/>
-      <c r="BD38" s="35"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC38" s="64"/>
+      <c r="BD38" s="64"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -4962,8 +4964,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="78"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="62"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5023,11 +5025,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="35"/>
-      <c r="BD39" s="35"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I40" s="40">
+      <c r="BC39" s="64"/>
+      <c r="BD39" s="64"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5058,8 +5060,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="41"/>
-      <c r="Y40" s="53"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="41"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5088,7 +5090,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="40">
+      <c r="AN40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5119,11 +5121,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="36"/>
-      <c r="BD40" s="36"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="41"/>
+      <c r="BC40" s="65"/>
+      <c r="BD40" s="65"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I41" s="36"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5136,14 +5138,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="45"/>
+      <c r="O41" s="48"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="49"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5158,17 +5160,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="75"/>
-      <c r="AE41" s="76"/>
-      <c r="AF41" s="76"/>
-      <c r="AG41" s="76"/>
-      <c r="AH41" s="76"/>
-      <c r="AI41" s="77"/>
+      <c r="AD41" s="44"/>
+      <c r="AE41" s="45"/>
+      <c r="AF41" s="45"/>
+      <c r="AG41" s="45"/>
+      <c r="AH41" s="45"/>
+      <c r="AI41" s="46"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="41"/>
+      <c r="AN41" s="36"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5181,14 +5183,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="43" t="s">
+      <c r="AS41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="44"/>
-      <c r="AU41" s="44"/>
-      <c r="AV41" s="44"/>
-      <c r="AW41" s="44"/>
-      <c r="AX41" s="45"/>
+      <c r="AT41" s="48"/>
+      <c r="AU41" s="48"/>
+      <c r="AV41" s="48"/>
+      <c r="AW41" s="48"/>
+      <c r="AX41" s="49"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5197,10 +5199,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="35"/>
-      <c r="BD41" s="35"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC41" s="64"/>
+      <c r="BD41" s="64"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5232,10 +5234,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="40">
+      <c r="X42" s="35">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="52">
+      <c r="Y42" s="40">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5297,11 +5299,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="35"/>
-      <c r="BD42" s="35"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="40">
+      <c r="BC42" s="64"/>
+      <c r="BD42" s="64"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" s="35">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5332,8 +5334,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="53"/>
+      <c r="X43" s="36"/>
+      <c r="Y43" s="41"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5362,7 +5364,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="40">
+      <c r="AN43" s="35">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5393,11 +5395,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="35"/>
-      <c r="BD43" s="35"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="41"/>
+      <c r="BC43" s="64"/>
+      <c r="BD43" s="64"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I44" s="36"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5432,17 +5434,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="75"/>
-      <c r="AE44" s="76"/>
-      <c r="AF44" s="76"/>
-      <c r="AG44" s="76"/>
-      <c r="AH44" s="76"/>
-      <c r="AI44" s="77"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="45"/>
+      <c r="AG44" s="45"/>
+      <c r="AH44" s="45"/>
+      <c r="AI44" s="46"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="41"/>
+      <c r="AN44" s="36"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5471,10 +5473,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="35"/>
-      <c r="BD44" s="35"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC44" s="64"/>
+      <c r="BD44" s="64"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5506,10 +5508,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="40">
+      <c r="X45" s="35">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="60">
+      <c r="Y45" s="58">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5571,11 +5573,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="35"/>
-      <c r="BD45" s="35"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="40" t="s">
+      <c r="BC45" s="64"/>
+      <c r="BD45" s="64"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5606,8 +5608,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="61"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="59"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5636,7 +5638,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="40" t="s">
+      <c r="AN46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5667,11 +5669,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="35"/>
-      <c r="BD46" s="35"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="41"/>
+      <c r="BC46" s="64"/>
+      <c r="BD46" s="64"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I47" s="36"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5706,17 +5708,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="75"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="76"/>
-      <c r="AG47" s="76"/>
-      <c r="AH47" s="76"/>
-      <c r="AI47" s="77"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="45"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="45"/>
+      <c r="AI47" s="46"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="41"/>
+      <c r="AN47" s="36"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5745,11 +5747,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="35"/>
-      <c r="BD47" s="35"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="40" t="s">
+      <c r="BC47" s="64"/>
+      <c r="BD47" s="64"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5780,10 +5782,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="40">
+      <c r="X48" s="35">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="46">
+      <c r="Y48" s="42">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5814,7 +5816,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="40" t="s">
+      <c r="AN48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5845,11 +5847,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="35"/>
-      <c r="BD48" s="35"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="41"/>
+      <c r="BC48" s="64"/>
+      <c r="BD48" s="64"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I49" s="36"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5878,8 +5880,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="47"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="43"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5908,7 +5910,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="41"/>
+      <c r="AN49" s="36"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5937,12 +5939,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="35"/>
-      <c r="BD49" s="35"/>
-    </row>
-    <row r="50" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="BC49" s="64"/>
+      <c r="BD49" s="64"/>
+    </row>
+    <row r="50" spans="8:56" x14ac:dyDescent="0.2">
       <c r="H50" s="10"/>
-      <c r="I50" s="40">
+      <c r="I50" s="35">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -5957,14 +5959,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="43" t="s">
+      <c r="N50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="45"/>
+      <c r="O50" s="48"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="48"/>
+      <c r="R50" s="48"/>
+      <c r="S50" s="49"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -5979,17 +5981,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="75"/>
-      <c r="AE50" s="76"/>
-      <c r="AF50" s="76"/>
-      <c r="AG50" s="76"/>
-      <c r="AH50" s="76"/>
-      <c r="AI50" s="77"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="45"/>
+      <c r="AI50" s="46"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="40">
+      <c r="AN50" s="35">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6000,23 +6002,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="43" t="s">
+      <c r="AS50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="44"/>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="44"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="45"/>
+      <c r="AT50" s="48"/>
+      <c r="AU50" s="48"/>
+      <c r="AV50" s="48"/>
+      <c r="AW50" s="48"/>
+      <c r="AX50" s="49"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="35"/>
-      <c r="BD50" s="35"/>
-    </row>
-    <row r="51" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I51" s="41"/>
+      <c r="BC50" s="64"/>
+      <c r="BD50" s="64"/>
+    </row>
+    <row r="51" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I51" s="36"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6029,14 +6031,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="43" t="s">
+      <c r="N51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="45"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="49"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6045,10 +6047,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="40">
+      <c r="X51" s="35">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="52">
+      <c r="Y51" s="40">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6079,7 +6081,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="41"/>
+      <c r="AN51" s="36"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6088,23 +6090,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="43" t="s">
+      <c r="AS51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="44"/>
-      <c r="AU51" s="44"/>
-      <c r="AV51" s="44"/>
-      <c r="AW51" s="44"/>
-      <c r="AX51" s="45"/>
+      <c r="AT51" s="48"/>
+      <c r="AU51" s="48"/>
+      <c r="AV51" s="48"/>
+      <c r="AW51" s="48"/>
+      <c r="AX51" s="49"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="35"/>
-      <c r="BD51" s="35"/>
-    </row>
-    <row r="52" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I52" s="40">
+      <c r="BC51" s="64"/>
+      <c r="BD51" s="64"/>
+    </row>
+    <row r="52" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I52" s="35">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6135,8 +6137,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="53"/>
+      <c r="X52" s="36"/>
+      <c r="Y52" s="41"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6165,7 +6167,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="40">
+      <c r="AN52" s="35">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6188,11 +6190,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="36"/>
-      <c r="BD52" s="36"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I53" s="41"/>
+      <c r="BC52" s="65"/>
+      <c r="BD52" s="65"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I53" s="36"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6227,17 +6229,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="75"/>
-      <c r="AE53" s="76"/>
-      <c r="AF53" s="76"/>
-      <c r="AG53" s="76"/>
-      <c r="AH53" s="76"/>
-      <c r="AI53" s="77"/>
+      <c r="AD53" s="44"/>
+      <c r="AE53" s="45"/>
+      <c r="AF53" s="45"/>
+      <c r="AG53" s="45"/>
+      <c r="AH53" s="45"/>
+      <c r="AI53" s="46"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="41"/>
+      <c r="AN53" s="36"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6258,11 +6260,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="35"/>
-      <c r="BD53" s="35"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I54" s="40">
+      <c r="BC53" s="64"/>
+      <c r="BD53" s="64"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" s="35">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6327,7 +6329,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="40">
+      <c r="AN54" s="35">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6350,11 +6352,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="35"/>
-      <c r="BD54" s="35"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I55" s="41"/>
+      <c r="BC54" s="64"/>
+      <c r="BD54" s="64"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I55" s="36"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6389,17 +6391,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="75"/>
-      <c r="AE55" s="76"/>
-      <c r="AF55" s="76"/>
-      <c r="AG55" s="76"/>
-      <c r="AH55" s="76"/>
-      <c r="AI55" s="77"/>
+      <c r="AD55" s="44"/>
+      <c r="AE55" s="45"/>
+      <c r="AF55" s="45"/>
+      <c r="AG55" s="45"/>
+      <c r="AH55" s="45"/>
+      <c r="AI55" s="46"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="41"/>
+      <c r="AN55" s="36"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6420,10 +6422,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="35"/>
-      <c r="BD55" s="35"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC55" s="64"/>
+      <c r="BD55" s="64"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6455,10 +6457,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="40">
+      <c r="X56" s="35">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="60">
+      <c r="Y56" s="58">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6512,11 +6514,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="35"/>
-      <c r="BD56" s="35"/>
-    </row>
-    <row r="57" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I57" s="40">
+      <c r="BC56" s="64"/>
+      <c r="BD56" s="64"/>
+    </row>
+    <row r="57" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I57" s="35">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6547,8 +6549,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="41"/>
-      <c r="Y57" s="61"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="59"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6559,14 +6561,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="43" t="s">
+      <c r="AD57" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="44"/>
-      <c r="AF57" s="44"/>
-      <c r="AG57" s="44"/>
-      <c r="AH57" s="44"/>
-      <c r="AI57" s="45"/>
+      <c r="AE57" s="48"/>
+      <c r="AF57" s="48"/>
+      <c r="AG57" s="48"/>
+      <c r="AH57" s="48"/>
+      <c r="AI57" s="49"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6575,7 +6577,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="40">
+      <c r="AN57" s="35">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6598,11 +6600,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="35"/>
-      <c r="BD57" s="35"/>
-    </row>
-    <row r="58" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I58" s="41"/>
+      <c r="BC57" s="64"/>
+      <c r="BD57" s="64"/>
+    </row>
+    <row r="58" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I58" s="36"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6637,17 +6639,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="75"/>
-      <c r="AE58" s="76"/>
-      <c r="AF58" s="76"/>
-      <c r="AG58" s="76"/>
-      <c r="AH58" s="76"/>
-      <c r="AI58" s="77"/>
+      <c r="AD58" s="44"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="46"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="41"/>
+      <c r="AN58" s="36"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6668,11 +6670,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="35"/>
-      <c r="BD58" s="35"/>
-    </row>
-    <row r="59" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I59" s="40">
+      <c r="BC58" s="64"/>
+      <c r="BD58" s="64"/>
+    </row>
+    <row r="59" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I59" s="35">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6737,7 +6739,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="40">
+      <c r="AN59" s="35">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6760,11 +6762,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="35"/>
-      <c r="BD59" s="35"/>
-    </row>
-    <row r="60" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I60" s="41"/>
+      <c r="BC59" s="64"/>
+      <c r="BD59" s="64"/>
+    </row>
+    <row r="60" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I60" s="36"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6799,17 +6801,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="75"/>
-      <c r="AE60" s="76"/>
-      <c r="AF60" s="76"/>
-      <c r="AG60" s="76"/>
-      <c r="AH60" s="76"/>
-      <c r="AI60" s="77"/>
+      <c r="AD60" s="44"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="45"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="45"/>
+      <c r="AI60" s="46"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="41"/>
+      <c r="AN60" s="36"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6830,11 +6832,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="35"/>
-      <c r="BD60" s="35"/>
-    </row>
-    <row r="61" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I61" s="40" t="s">
+      <c r="BC60" s="64"/>
+      <c r="BD60" s="64"/>
+    </row>
+    <row r="61" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6865,10 +6867,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="40">
+      <c r="X61" s="35">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="58">
+      <c r="Y61" s="60">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6899,7 +6901,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="40" t="s">
+      <c r="AN61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6922,11 +6924,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="35"/>
-      <c r="BD61" s="35"/>
-    </row>
-    <row r="62" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I62" s="41"/>
+      <c r="BC61" s="64"/>
+      <c r="BD61" s="64"/>
+    </row>
+    <row r="62" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I62" s="36"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -6955,8 +6957,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="41"/>
-      <c r="Y62" s="59"/>
+      <c r="X62" s="36"/>
+      <c r="Y62" s="61"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -6985,7 +6987,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="41"/>
+      <c r="AN62" s="36"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7006,11 +7008,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="35"/>
-      <c r="BD62" s="35"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I63" s="40">
+      <c r="BC62" s="64"/>
+      <c r="BD62" s="64"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I63" s="35">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7047,17 +7049,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="75"/>
-      <c r="AE63" s="76"/>
-      <c r="AF63" s="76"/>
-      <c r="AG63" s="76"/>
-      <c r="AH63" s="76"/>
-      <c r="AI63" s="77"/>
+      <c r="AD63" s="44"/>
+      <c r="AE63" s="45"/>
+      <c r="AF63" s="45"/>
+      <c r="AG63" s="45"/>
+      <c r="AH63" s="45"/>
+      <c r="AI63" s="46"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="40">
+      <c r="AN63" s="35">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7080,11 +7082,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="35"/>
-      <c r="BD63" s="35"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I64" s="41"/>
+      <c r="BC63" s="64"/>
+      <c r="BD63" s="64"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I64" s="36"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7147,7 +7149,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="41"/>
+      <c r="AN64" s="36"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7168,11 +7170,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="36"/>
-      <c r="BD64" s="36"/>
-    </row>
-    <row r="65" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I65" s="40">
+      <c r="BC64" s="65"/>
+      <c r="BD64" s="65"/>
+    </row>
+    <row r="65" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I65" s="35">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7201,17 +7203,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="75"/>
-      <c r="AE65" s="76"/>
-      <c r="AF65" s="76"/>
-      <c r="AG65" s="76"/>
-      <c r="AH65" s="76"/>
-      <c r="AI65" s="77"/>
+      <c r="AD65" s="44"/>
+      <c r="AE65" s="45"/>
+      <c r="AF65" s="45"/>
+      <c r="AG65" s="45"/>
+      <c r="AH65" s="45"/>
+      <c r="AI65" s="46"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="40">
+      <c r="AN65" s="35">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7234,11 +7236,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="35"/>
-      <c r="BD65" s="35"/>
-    </row>
-    <row r="66" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I66" s="41"/>
+      <c r="BC65" s="64"/>
+      <c r="BD65" s="64"/>
+    </row>
+    <row r="66" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I66" s="36"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7259,10 +7261,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="40" t="s">
+      <c r="X66" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="54">
+      <c r="Y66" s="56">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7293,7 +7295,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="41"/>
+      <c r="AN66" s="36"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7314,10 +7316,10 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="35"/>
-      <c r="BD66" s="35"/>
-    </row>
-    <row r="67" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC66" s="64"/>
+      <c r="BD66" s="64"/>
+    </row>
+    <row r="67" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
@@ -7341,8 +7343,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="41"/>
-      <c r="Y67" s="55"/>
+      <c r="X67" s="36"/>
+      <c r="Y67" s="57"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7394,11 +7396,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="35"/>
-      <c r="BD67" s="35"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I68" s="40">
+      <c r="BC67" s="64"/>
+      <c r="BD67" s="64"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I68" s="35">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7427,17 +7429,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="76"/>
-      <c r="AG68" s="76"/>
-      <c r="AH68" s="76"/>
-      <c r="AI68" s="77"/>
+      <c r="AD68" s="44"/>
+      <c r="AE68" s="45"/>
+      <c r="AF68" s="45"/>
+      <c r="AG68" s="45"/>
+      <c r="AH68" s="45"/>
+      <c r="AI68" s="46"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="40">
+      <c r="AN68" s="35">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7460,11 +7462,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="35"/>
-      <c r="BD68" s="35"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I69" s="41"/>
+      <c r="BC68" s="64"/>
+      <c r="BD68" s="64"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I69" s="36"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7485,10 +7487,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="40" t="s">
+      <c r="X69" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="54">
+      <c r="Y69" s="56">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7519,7 +7521,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="41"/>
+      <c r="AN69" s="36"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7540,10 +7542,10 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="35"/>
-      <c r="BD69" s="35"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC69" s="64"/>
+      <c r="BD69" s="64"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
@@ -7567,8 +7569,8 @@
       <c r="U70" s="6"/>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="41"/>
-      <c r="Y70" s="55"/>
+      <c r="X70" s="36"/>
+      <c r="Y70" s="57"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7620,11 +7622,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="35"/>
-      <c r="BD70" s="35"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I71" s="40">
+      <c r="BC70" s="64"/>
+      <c r="BD70" s="64"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I71" s="35">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7653,17 +7655,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="75"/>
-      <c r="AE71" s="76"/>
-      <c r="AF71" s="76"/>
-      <c r="AG71" s="76"/>
-      <c r="AH71" s="76"/>
-      <c r="AI71" s="77"/>
+      <c r="AD71" s="44"/>
+      <c r="AE71" s="45"/>
+      <c r="AF71" s="45"/>
+      <c r="AG71" s="45"/>
+      <c r="AH71" s="45"/>
+      <c r="AI71" s="46"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="40">
+      <c r="AN71" s="35">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7686,11 +7688,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="35"/>
-      <c r="BD71" s="35"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I72" s="41"/>
+      <c r="BC71" s="64"/>
+      <c r="BD71" s="64"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I72" s="36"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7711,10 +7713,10 @@
       <c r="U72" s="6"/>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="40">
+      <c r="X72" s="35">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="52">
+      <c r="Y72" s="40">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7729,14 +7731,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="43" t="s">
+      <c r="AD72" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
-      <c r="AH72" s="44"/>
-      <c r="AI72" s="45"/>
+      <c r="AE72" s="48"/>
+      <c r="AF72" s="48"/>
+      <c r="AG72" s="48"/>
+      <c r="AH72" s="48"/>
+      <c r="AI72" s="49"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7745,7 +7747,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="41"/>
+      <c r="AN72" s="36"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7766,11 +7768,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="35"/>
-      <c r="BD72" s="35"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I73" s="40">
+      <c r="BC72" s="64"/>
+      <c r="BD72" s="64"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7781,20 +7783,20 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="43" t="s">
+      <c r="N73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
-      <c r="R73" s="44"/>
-      <c r="S73" s="45"/>
+      <c r="O73" s="48"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="48"/>
+      <c r="R73" s="48"/>
+      <c r="S73" s="49"/>
       <c r="T73" s="7"/>
       <c r="U73" s="6"/>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="41"/>
-      <c r="Y73" s="53"/>
+      <c r="X73" s="36"/>
+      <c r="Y73" s="41"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7807,14 +7809,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="43" t="s">
+      <c r="AD73" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
-      <c r="AH73" s="44"/>
-      <c r="AI73" s="45"/>
+      <c r="AE73" s="48"/>
+      <c r="AF73" s="48"/>
+      <c r="AG73" s="48"/>
+      <c r="AH73" s="48"/>
+      <c r="AI73" s="49"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7823,7 +7825,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="40">
+      <c r="AN73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7834,23 +7836,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="43" t="s">
+      <c r="AS73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="44"/>
-      <c r="AU73" s="44"/>
-      <c r="AV73" s="44"/>
-      <c r="AW73" s="44"/>
-      <c r="AX73" s="45"/>
+      <c r="AT73" s="48"/>
+      <c r="AU73" s="48"/>
+      <c r="AV73" s="48"/>
+      <c r="AW73" s="48"/>
+      <c r="AX73" s="49"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="35"/>
-      <c r="BD73" s="35"/>
-    </row>
-    <row r="74" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I74" s="41"/>
+      <c r="BC73" s="64"/>
+      <c r="BD73" s="64"/>
+    </row>
+    <row r="74" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I74" s="36"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7877,17 +7879,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="75"/>
-      <c r="AE74" s="76"/>
-      <c r="AF74" s="76"/>
-      <c r="AG74" s="76"/>
-      <c r="AH74" s="76"/>
-      <c r="AI74" s="77"/>
+      <c r="AD74" s="44"/>
+      <c r="AE74" s="45"/>
+      <c r="AF74" s="45"/>
+      <c r="AG74" s="45"/>
+      <c r="AH74" s="45"/>
+      <c r="AI74" s="46"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="41"/>
+      <c r="AN74" s="36"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7908,11 +7910,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="35"/>
-      <c r="BD74" s="35"/>
-    </row>
-    <row r="75" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I75" s="40">
+      <c r="BC74" s="64"/>
+      <c r="BD74" s="64"/>
+    </row>
+    <row r="75" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7923,22 +7925,22 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="43" t="s">
+      <c r="N75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="44"/>
-      <c r="P75" s="44"/>
-      <c r="Q75" s="44"/>
-      <c r="R75" s="44"/>
-      <c r="S75" s="45"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="49"/>
       <c r="T75" s="7"/>
       <c r="U75" s="6"/>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="40">
+      <c r="X75" s="35">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="60">
+      <c r="Y75" s="58">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -7969,7 +7971,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="40">
+      <c r="AN75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -7980,23 +7982,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="43" t="s">
+      <c r="AS75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="44"/>
-      <c r="AU75" s="44"/>
-      <c r="AV75" s="44"/>
-      <c r="AW75" s="44"/>
-      <c r="AX75" s="45"/>
+      <c r="AT75" s="48"/>
+      <c r="AU75" s="48"/>
+      <c r="AV75" s="48"/>
+      <c r="AW75" s="48"/>
+      <c r="AX75" s="49"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="35"/>
-      <c r="BD75" s="35"/>
-    </row>
-    <row r="76" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I76" s="41"/>
+      <c r="BC75" s="64"/>
+      <c r="BD75" s="64"/>
+    </row>
+    <row r="76" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I76" s="36"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8017,8 +8019,8 @@
       <c r="U76" s="6"/>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="41"/>
-      <c r="Y76" s="61"/>
+      <c r="X76" s="36"/>
+      <c r="Y76" s="59"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8047,7 +8049,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="41"/>
+      <c r="AN76" s="36"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8068,11 +8070,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="36"/>
-      <c r="BD76" s="36"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I77" s="40">
+      <c r="BC76" s="65"/>
+      <c r="BD76" s="65"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I77" s="35">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8101,17 +8103,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="75"/>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="76"/>
-      <c r="AG77" s="76"/>
-      <c r="AH77" s="76"/>
-      <c r="AI77" s="77"/>
+      <c r="AD77" s="44"/>
+      <c r="AE77" s="45"/>
+      <c r="AF77" s="45"/>
+      <c r="AG77" s="45"/>
+      <c r="AH77" s="45"/>
+      <c r="AI77" s="46"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="40">
+      <c r="AN77" s="35">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8134,11 +8136,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="35"/>
-      <c r="BD77" s="35"/>
-    </row>
-    <row r="78" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I78" s="41"/>
+      <c r="BC77" s="64"/>
+      <c r="BD77" s="64"/>
+    </row>
+    <row r="78" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I78" s="36"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8159,10 +8161,10 @@
       <c r="U78" s="6"/>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="40">
+      <c r="X78" s="35">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="52">
+      <c r="Y78" s="40">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8193,7 +8195,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="41"/>
+      <c r="AN78" s="36"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8214,11 +8216,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="35"/>
-      <c r="BD78" s="35"/>
-    </row>
-    <row r="79" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I79" s="40">
+      <c r="BC78" s="64"/>
+      <c r="BD78" s="64"/>
+    </row>
+    <row r="79" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I79" s="35">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8229,20 +8231,20 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="43" t="s">
+      <c r="N79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
-      <c r="R79" s="44"/>
-      <c r="S79" s="45"/>
+      <c r="O79" s="48"/>
+      <c r="P79" s="48"/>
+      <c r="Q79" s="48"/>
+      <c r="R79" s="48"/>
+      <c r="S79" s="49"/>
       <c r="T79" s="7"/>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="41"/>
-      <c r="Y79" s="53"/>
+      <c r="X79" s="36"/>
+      <c r="Y79" s="41"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8271,7 +8273,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="40">
+      <c r="AN79" s="35">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8282,23 +8284,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="43" t="s">
+      <c r="AS79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="44"/>
-      <c r="AU79" s="44"/>
-      <c r="AV79" s="44"/>
-      <c r="AW79" s="44"/>
-      <c r="AX79" s="45"/>
+      <c r="AT79" s="48"/>
+      <c r="AU79" s="48"/>
+      <c r="AV79" s="48"/>
+      <c r="AW79" s="48"/>
+      <c r="AX79" s="49"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="35"/>
-      <c r="BD79" s="35"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I80" s="41"/>
+      <c r="BC79" s="64"/>
+      <c r="BD79" s="64"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I80" s="36"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8325,17 +8327,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="75"/>
-      <c r="AE80" s="76"/>
-      <c r="AF80" s="76"/>
-      <c r="AG80" s="76"/>
-      <c r="AH80" s="76"/>
-      <c r="AI80" s="77"/>
+      <c r="AD80" s="44"/>
+      <c r="AE80" s="45"/>
+      <c r="AF80" s="45"/>
+      <c r="AG80" s="45"/>
+      <c r="AH80" s="45"/>
+      <c r="AI80" s="46"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="41"/>
+      <c r="AN80" s="36"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8356,11 +8358,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="35"/>
-      <c r="BD80" s="35"/>
-    </row>
-    <row r="81" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I81" s="40">
+      <c r="BC80" s="64"/>
+      <c r="BD80" s="64"/>
+    </row>
+    <row r="81" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I81" s="35">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8417,7 +8419,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="40">
+      <c r="AN81" s="35">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8440,11 +8442,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="35"/>
-      <c r="BD81" s="35"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I82" s="41"/>
+      <c r="BC81" s="64"/>
+      <c r="BD81" s="64"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I82" s="36"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8453,14 +8455,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="43" t="s">
+      <c r="N82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="44"/>
-      <c r="P82" s="44"/>
-      <c r="Q82" s="44"/>
-      <c r="R82" s="44"/>
-      <c r="S82" s="45"/>
+      <c r="O82" s="48"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="48"/>
+      <c r="R82" s="48"/>
+      <c r="S82" s="49"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8471,17 +8473,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="75"/>
-      <c r="AE82" s="76"/>
-      <c r="AF82" s="76"/>
-      <c r="AG82" s="76"/>
-      <c r="AH82" s="76"/>
-      <c r="AI82" s="77"/>
+      <c r="AD82" s="44"/>
+      <c r="AE82" s="45"/>
+      <c r="AF82" s="45"/>
+      <c r="AG82" s="45"/>
+      <c r="AH82" s="45"/>
+      <c r="AI82" s="46"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="41"/>
+      <c r="AN82" s="36"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8490,23 +8492,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="43" t="s">
+      <c r="AS82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="44"/>
-      <c r="AU82" s="44"/>
-      <c r="AV82" s="44"/>
-      <c r="AW82" s="44"/>
-      <c r="AX82" s="45"/>
+      <c r="AT82" s="48"/>
+      <c r="AU82" s="48"/>
+      <c r="AV82" s="48"/>
+      <c r="AW82" s="48"/>
+      <c r="AX82" s="49"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="35"/>
-      <c r="BD82" s="35"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I83" s="40">
+      <c r="BC82" s="64"/>
+      <c r="BD82" s="64"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I83" s="35">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8537,10 +8539,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="40">
+      <c r="X83" s="35">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="54">
+      <c r="Y83" s="56">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8571,7 +8573,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="40">
+      <c r="AN83" s="35">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8600,11 +8602,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="35"/>
-      <c r="BD83" s="35"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I84" s="41"/>
+      <c r="BC83" s="64"/>
+      <c r="BD83" s="64"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I84" s="36"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8633,8 +8635,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="41"/>
-      <c r="Y84" s="55"/>
+      <c r="X84" s="36"/>
+      <c r="Y84" s="57"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8663,7 +8665,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="41"/>
+      <c r="AN84" s="36"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8690,10 +8692,10 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="35"/>
-      <c r="BD84" s="35"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC84" s="64"/>
+      <c r="BD84" s="64"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
@@ -8723,12 +8725,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="75"/>
-      <c r="AE85" s="76"/>
-      <c r="AF85" s="76"/>
-      <c r="AG85" s="76"/>
-      <c r="AH85" s="76"/>
-      <c r="AI85" s="77"/>
+      <c r="AD85" s="44"/>
+      <c r="AE85" s="45"/>
+      <c r="AF85" s="45"/>
+      <c r="AG85" s="45"/>
+      <c r="AH85" s="45"/>
+      <c r="AI85" s="46"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8756,11 +8758,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="35"/>
-      <c r="BD85" s="35"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I86" s="40">
+      <c r="BC85" s="64"/>
+      <c r="BD85" s="64"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I86" s="35">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8783,10 +8785,10 @@
       <c r="U86" s="6"/>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="40">
+      <c r="X86" s="35">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="56">
+      <c r="Y86" s="50">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8817,7 +8819,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="40">
+      <c r="AN86" s="35">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8840,11 +8842,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="35"/>
-      <c r="BD86" s="35"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I87" s="41"/>
+      <c r="BC86" s="64"/>
+      <c r="BD86" s="64"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I87" s="36"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8865,8 +8867,8 @@
       <c r="U87" s="6"/>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="41"/>
-      <c r="Y87" s="57"/>
+      <c r="X87" s="36"/>
+      <c r="Y87" s="51"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8895,7 +8897,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="41"/>
+      <c r="AN87" s="36"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8916,11 +8918,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="35"/>
-      <c r="BD87" s="35"/>
-    </row>
-    <row r="88" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I88" s="40" t="s">
+      <c r="BC87" s="64"/>
+      <c r="BD87" s="64"/>
+    </row>
+    <row r="88" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -8949,17 +8951,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="75"/>
-      <c r="AE88" s="76"/>
-      <c r="AF88" s="76"/>
-      <c r="AG88" s="76"/>
-      <c r="AH88" s="76"/>
-      <c r="AI88" s="77"/>
+      <c r="AD88" s="44"/>
+      <c r="AE88" s="45"/>
+      <c r="AF88" s="45"/>
+      <c r="AG88" s="45"/>
+      <c r="AH88" s="45"/>
+      <c r="AI88" s="46"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="40" t="s">
+      <c r="AN88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -8982,11 +8984,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="36"/>
-      <c r="BD88" s="36"/>
-    </row>
-    <row r="89" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I89" s="41"/>
+      <c r="BC88" s="65"/>
+      <c r="BD88" s="65"/>
+    </row>
+    <row r="89" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I89" s="36"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -9007,10 +9009,10 @@
       <c r="U89" s="6"/>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="40" t="s">
+      <c r="X89" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="56">
+      <c r="Y89" s="50">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9041,7 +9043,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="41"/>
+      <c r="AN89" s="36"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9062,10 +9064,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="35"/>
-      <c r="BD89" s="35"/>
-    </row>
-    <row r="90" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC89" s="64"/>
+      <c r="BD89" s="64"/>
+    </row>
+    <row r="90" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9077,20 +9079,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="42" t="s">
+      <c r="N90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="42"/>
-      <c r="P90" s="42"/>
-      <c r="Q90" s="42"/>
-      <c r="R90" s="42"/>
-      <c r="S90" s="42"/>
+      <c r="O90" s="52"/>
+      <c r="P90" s="52"/>
+      <c r="Q90" s="52"/>
+      <c r="R90" s="52"/>
+      <c r="S90" s="52"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="41"/>
-      <c r="Y90" s="57"/>
+      <c r="X90" s="36"/>
+      <c r="Y90" s="51"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9130,22 +9132,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="42" t="s">
+      <c r="AS90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="42"/>
-      <c r="AU90" s="42"/>
-      <c r="AV90" s="42"/>
-      <c r="AW90" s="42"/>
-      <c r="AX90" s="42"/>
+      <c r="AT90" s="52"/>
+      <c r="AU90" s="52"/>
+      <c r="AV90" s="52"/>
+      <c r="AW90" s="52"/>
+      <c r="AX90" s="52"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="35"/>
-      <c r="BD90" s="35"/>
-    </row>
-    <row r="91" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC90" s="64"/>
+      <c r="BD90" s="64"/>
+    </row>
+    <row r="91" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9167,12 +9169,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="75"/>
-      <c r="AE91" s="76"/>
-      <c r="AF91" s="76"/>
-      <c r="AG91" s="76"/>
-      <c r="AH91" s="76"/>
-      <c r="AI91" s="77"/>
+      <c r="AD91" s="44"/>
+      <c r="AE91" s="45"/>
+      <c r="AF91" s="45"/>
+      <c r="AG91" s="45"/>
+      <c r="AH91" s="45"/>
+      <c r="AI91" s="46"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9195,7 +9197,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="92" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9211,10 +9213,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="40">
+      <c r="X92" s="35">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="60">
+      <c r="Y92" s="58">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9263,7 +9265,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="93" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9279,8 +9281,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="41"/>
-      <c r="Y93" s="61"/>
+      <c r="X93" s="36"/>
+      <c r="Y93" s="59"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9327,7 +9329,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9349,12 +9351,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="75"/>
-      <c r="AE94" s="76"/>
-      <c r="AF94" s="76"/>
-      <c r="AG94" s="76"/>
-      <c r="AH94" s="76"/>
-      <c r="AI94" s="77"/>
+      <c r="AD94" s="44"/>
+      <c r="AE94" s="45"/>
+      <c r="AF94" s="45"/>
+      <c r="AG94" s="45"/>
+      <c r="AH94" s="45"/>
+      <c r="AI94" s="46"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9377,7 +9379,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="95" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9393,10 +9395,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="40">
+      <c r="X95" s="35">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="58">
+      <c r="Y95" s="60">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9437,7 +9439,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="96" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9453,8 +9455,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="41"/>
-      <c r="Y96" s="59"/>
+      <c r="X96" s="36"/>
+      <c r="Y96" s="61"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9493,7 +9495,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9515,12 +9517,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="75"/>
-      <c r="AE97" s="76"/>
-      <c r="AF97" s="76"/>
-      <c r="AG97" s="76"/>
-      <c r="AH97" s="76"/>
-      <c r="AI97" s="77"/>
+      <c r="AD97" s="44"/>
+      <c r="AE97" s="45"/>
+      <c r="AF97" s="45"/>
+      <c r="AG97" s="45"/>
+      <c r="AH97" s="45"/>
+      <c r="AI97" s="46"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9543,7 +9545,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9603,7 +9605,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9625,12 +9627,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="75"/>
-      <c r="AE99" s="76"/>
-      <c r="AF99" s="76"/>
-      <c r="AG99" s="76"/>
-      <c r="AH99" s="76"/>
-      <c r="AI99" s="77"/>
+      <c r="AD99" s="44"/>
+      <c r="AE99" s="45"/>
+      <c r="AF99" s="45"/>
+      <c r="AG99" s="45"/>
+      <c r="AH99" s="45"/>
+      <c r="AI99" s="46"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9653,7 +9655,7 @@
       <c r="BC99" s="20"/>
       <c r="BD99" s="20"/>
     </row>
-    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -9669,16 +9671,18 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="40">
+      <c r="X100" s="35">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="52">
+      <c r="Y100" s="40">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AA100" s="33"/>
+      <c r="AA100" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB100" s="33"/>
       <c r="AC100" s="4" t="s">
         <v>13</v>
@@ -9713,7 +9717,7 @@
       <c r="BC100" s="20"/>
       <c r="BD100" s="20"/>
     </row>
-    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -9729,12 +9733,14 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="41"/>
-      <c r="Y101" s="53"/>
+      <c r="X101" s="36"/>
+      <c r="Y101" s="41"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AA101" s="33"/>
+      <c r="AA101" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB101" s="33"/>
       <c r="AC101" s="4" t="s">
         <v>13</v>
@@ -9769,7 +9775,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -9791,12 +9797,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="75"/>
-      <c r="AE102" s="76"/>
-      <c r="AF102" s="76"/>
-      <c r="AG102" s="76"/>
-      <c r="AH102" s="76"/>
-      <c r="AI102" s="77"/>
+      <c r="AD102" s="44"/>
+      <c r="AE102" s="45"/>
+      <c r="AF102" s="45"/>
+      <c r="AG102" s="45"/>
+      <c r="AH102" s="45"/>
+      <c r="AI102" s="46"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9819,7 +9825,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -9879,7 +9885,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -9901,12 +9907,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="75"/>
-      <c r="AE104" s="76"/>
-      <c r="AF104" s="76"/>
-      <c r="AG104" s="76"/>
-      <c r="AH104" s="76"/>
-      <c r="AI104" s="77"/>
+      <c r="AD104" s="44"/>
+      <c r="AE104" s="45"/>
+      <c r="AF104" s="45"/>
+      <c r="AG104" s="45"/>
+      <c r="AH104" s="45"/>
+      <c r="AI104" s="46"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -9929,7 +9935,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -9946,10 +9952,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="40">
+      <c r="X105" s="35">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="56">
+      <c r="Y105" s="50">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -9990,7 +9996,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -10006,8 +10012,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="41"/>
-      <c r="Y106" s="57"/>
+      <c r="X106" s="36"/>
+      <c r="Y106" s="51"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10046,7 +10052,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10068,12 +10074,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="75"/>
-      <c r="AE107" s="76"/>
-      <c r="AF107" s="76"/>
-      <c r="AG107" s="76"/>
-      <c r="AH107" s="76"/>
-      <c r="AI107" s="77"/>
+      <c r="AD107" s="44"/>
+      <c r="AE107" s="45"/>
+      <c r="AF107" s="45"/>
+      <c r="AG107" s="45"/>
+      <c r="AH107" s="45"/>
+      <c r="AI107" s="46"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10096,7 +10102,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10112,10 +10118,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="40">
+      <c r="X108" s="35">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="56">
+      <c r="Y108" s="50">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10126,14 +10132,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="43" t="s">
+      <c r="AD108" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="44"/>
-      <c r="AF108" s="44"/>
-      <c r="AG108" s="44"/>
-      <c r="AH108" s="44"/>
-      <c r="AI108" s="45"/>
+      <c r="AE108" s="48"/>
+      <c r="AF108" s="48"/>
+      <c r="AG108" s="48"/>
+      <c r="AH108" s="48"/>
+      <c r="AI108" s="49"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10156,7 +10162,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10172,8 +10178,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="41"/>
-      <c r="Y109" s="57"/>
+      <c r="X109" s="36"/>
+      <c r="Y109" s="51"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10212,7 +10218,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10234,12 +10240,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="75"/>
-      <c r="AE110" s="76"/>
-      <c r="AF110" s="76"/>
-      <c r="AG110" s="76"/>
-      <c r="AH110" s="76"/>
-      <c r="AI110" s="77"/>
+      <c r="AD110" s="44"/>
+      <c r="AE110" s="45"/>
+      <c r="AF110" s="45"/>
+      <c r="AG110" s="45"/>
+      <c r="AH110" s="45"/>
+      <c r="AI110" s="46"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10262,7 +10268,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:56" x14ac:dyDescent="0.2">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10278,10 +10284,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="40">
+      <c r="X111" s="35">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="56">
+      <c r="Y111" s="50">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10292,14 +10298,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="43" t="s">
+      <c r="AD111" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="44"/>
-      <c r="AF111" s="44"/>
-      <c r="AG111" s="44"/>
-      <c r="AH111" s="44"/>
-      <c r="AI111" s="45"/>
+      <c r="AE111" s="48"/>
+      <c r="AF111" s="48"/>
+      <c r="AG111" s="48"/>
+      <c r="AH111" s="48"/>
+      <c r="AI111" s="49"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10322,7 +10328,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10338,8 +10344,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="41"/>
-      <c r="Y112" s="57"/>
+      <c r="X112" s="36"/>
+      <c r="Y112" s="51"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10378,7 +10384,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="113" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10400,12 +10406,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="75"/>
-      <c r="AE113" s="76"/>
-      <c r="AF113" s="76"/>
-      <c r="AG113" s="76"/>
-      <c r="AH113" s="76"/>
-      <c r="AI113" s="77"/>
+      <c r="AD113" s="44"/>
+      <c r="AE113" s="45"/>
+      <c r="AF113" s="45"/>
+      <c r="AG113" s="45"/>
+      <c r="AH113" s="45"/>
+      <c r="AI113" s="46"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10428,7 +10434,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10444,10 +10450,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="40">
+      <c r="X114" s="35">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="56">
+      <c r="Y114" s="50">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10488,7 +10494,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10504,8 +10510,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="41"/>
-      <c r="Y115" s="57"/>
+      <c r="X115" s="36"/>
+      <c r="Y115" s="51"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10544,7 +10550,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="116" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10566,12 +10572,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="75"/>
-      <c r="AE116" s="76"/>
-      <c r="AF116" s="76"/>
-      <c r="AG116" s="76"/>
-      <c r="AH116" s="76"/>
-      <c r="AI116" s="77"/>
+      <c r="AD116" s="44"/>
+      <c r="AE116" s="45"/>
+      <c r="AF116" s="45"/>
+      <c r="AG116" s="45"/>
+      <c r="AH116" s="45"/>
+      <c r="AI116" s="46"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10594,7 +10600,7 @@
       <c r="BC116" s="20"/>
       <c r="BD116" s="20"/>
     </row>
-    <row r="117" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="117" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I117" s="20"/>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -10610,28 +10616,30 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="40">
+      <c r="X117" s="35">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="56">
+      <c r="Y117" s="50">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AA117" s="33"/>
+      <c r="AA117" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB117" s="33"/>
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="43" t="s">
+      <c r="AD117" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="44"/>
-      <c r="AF117" s="44"/>
-      <c r="AG117" s="44"/>
-      <c r="AH117" s="44"/>
-      <c r="AI117" s="45"/>
+      <c r="AE117" s="48"/>
+      <c r="AF117" s="48"/>
+      <c r="AG117" s="48"/>
+      <c r="AH117" s="48"/>
+      <c r="AI117" s="49"/>
       <c r="AJ117" s="19"/>
       <c r="AK117" s="19"/>
       <c r="AL117" s="20"/>
@@ -10654,7 +10662,7 @@
       <c r="BC117" s="20"/>
       <c r="BD117" s="20"/>
     </row>
-    <row r="118" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="118" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I118" s="20"/>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -10670,12 +10678,14 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="41"/>
-      <c r="Y118" s="57"/>
+      <c r="X118" s="36"/>
+      <c r="Y118" s="51"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AA118" s="33"/>
+      <c r="AA118" s="33" t="s">
+        <v>12</v>
+      </c>
       <c r="AB118" s="33"/>
       <c r="AC118" s="4" t="s">
         <v>13</v>
@@ -10710,7 +10720,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10732,12 +10742,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="75"/>
-      <c r="AE119" s="76"/>
-      <c r="AF119" s="76"/>
-      <c r="AG119" s="76"/>
-      <c r="AH119" s="76"/>
-      <c r="AI119" s="77"/>
+      <c r="AD119" s="44"/>
+      <c r="AE119" s="45"/>
+      <c r="AF119" s="45"/>
+      <c r="AG119" s="45"/>
+      <c r="AH119" s="45"/>
+      <c r="AI119" s="46"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10760,7 +10770,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -10776,10 +10786,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="40">
+      <c r="X120" s="35">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="54">
+      <c r="Y120" s="56">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10820,7 +10830,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -10836,8 +10846,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="41"/>
-      <c r="Y121" s="55"/>
+      <c r="X121" s="36"/>
+      <c r="Y121" s="57"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10846,14 +10856,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="43" t="s">
+      <c r="AD121" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="44"/>
-      <c r="AF121" s="44"/>
-      <c r="AG121" s="44"/>
-      <c r="AH121" s="44"/>
-      <c r="AI121" s="45"/>
+      <c r="AE121" s="48"/>
+      <c r="AF121" s="48"/>
+      <c r="AG121" s="48"/>
+      <c r="AH121" s="48"/>
+      <c r="AI121" s="49"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10876,7 +10886,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="122" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -10898,12 +10908,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="75"/>
-      <c r="AE122" s="76"/>
-      <c r="AF122" s="76"/>
-      <c r="AG122" s="76"/>
-      <c r="AH122" s="76"/>
-      <c r="AI122" s="77"/>
+      <c r="AD122" s="44"/>
+      <c r="AE122" s="45"/>
+      <c r="AF122" s="45"/>
+      <c r="AG122" s="45"/>
+      <c r="AH122" s="45"/>
+      <c r="AI122" s="46"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -10926,7 +10936,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -10942,10 +10952,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="40">
+      <c r="X123" s="35">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="46">
+      <c r="Y123" s="42">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -10994,7 +11004,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11010,8 +11020,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="41"/>
-      <c r="Y124" s="47"/>
+      <c r="X124" s="36"/>
+      <c r="Y124" s="43"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11058,7 +11068,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11080,12 +11090,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="75"/>
-      <c r="AE125" s="76"/>
-      <c r="AF125" s="76"/>
-      <c r="AG125" s="76"/>
-      <c r="AH125" s="76"/>
-      <c r="AI125" s="77"/>
+      <c r="AD125" s="44"/>
+      <c r="AE125" s="45"/>
+      <c r="AF125" s="45"/>
+      <c r="AG125" s="45"/>
+      <c r="AH125" s="45"/>
+      <c r="AI125" s="46"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11108,7 +11118,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="126" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11127,7 +11137,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="46">
+      <c r="Y126" s="42">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11168,7 +11178,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11185,17 +11195,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="47"/>
+      <c r="Y127" s="43"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="75"/>
-      <c r="AE127" s="76"/>
-      <c r="AF127" s="76"/>
-      <c r="AG127" s="76"/>
-      <c r="AH127" s="76"/>
-      <c r="AI127" s="77"/>
+      <c r="AD127" s="44"/>
+      <c r="AE127" s="45"/>
+      <c r="AF127" s="45"/>
+      <c r="AG127" s="45"/>
+      <c r="AH127" s="45"/>
+      <c r="AI127" s="46"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11218,7 +11228,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11234,10 +11244,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="40">
+      <c r="X128" s="35">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="52">
+      <c r="Y128" s="40">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11278,7 +11288,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11294,8 +11304,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="41"/>
-      <c r="Y129" s="53"/>
+      <c r="X129" s="36"/>
+      <c r="Y129" s="41"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11334,7 +11344,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11356,12 +11366,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="75"/>
-      <c r="AE130" s="76"/>
-      <c r="AF130" s="76"/>
-      <c r="AG130" s="76"/>
-      <c r="AH130" s="76"/>
-      <c r="AI130" s="77"/>
+      <c r="AD130" s="44"/>
+      <c r="AE130" s="45"/>
+      <c r="AF130" s="45"/>
+      <c r="AG130" s="45"/>
+      <c r="AH130" s="45"/>
+      <c r="AI130" s="46"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11384,7 +11394,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11400,10 +11410,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="40" t="s">
+      <c r="X131" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="46">
+      <c r="Y131" s="42">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11444,7 +11454,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11460,8 +11470,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="41"/>
-      <c r="Y132" s="47"/>
+      <c r="X132" s="36"/>
+      <c r="Y132" s="43"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11500,7 +11510,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11522,12 +11532,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="75"/>
-      <c r="AE133" s="76"/>
-      <c r="AF133" s="76"/>
-      <c r="AG133" s="76"/>
-      <c r="AH133" s="76"/>
-      <c r="AI133" s="77"/>
+      <c r="AD133" s="44"/>
+      <c r="AE133" s="45"/>
+      <c r="AF133" s="45"/>
+      <c r="AG133" s="45"/>
+      <c r="AH133" s="45"/>
+      <c r="AI133" s="46"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11550,7 +11560,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="134" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11580,14 +11590,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="42" t="s">
+      <c r="AD134" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="42"/>
-      <c r="AF134" s="42"/>
-      <c r="AG134" s="42"/>
-      <c r="AH134" s="42"/>
-      <c r="AI134" s="42"/>
+      <c r="AE134" s="52"/>
+      <c r="AF134" s="52"/>
+      <c r="AG134" s="52"/>
+      <c r="AH134" s="52"/>
+      <c r="AI134" s="52"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11610,60 +11620,594 @@
       <c r="BC134" s="20"/>
       <c r="BD134" s="20"/>
     </row>
-    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G153" s="89"/>
-      <c r="H153" s="89"/>
-    </row>
-    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G153" s="67"/>
+      <c r="H153" s="67"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="W192" s="12"/>
     </row>
-    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="AS85:AX85"/>
+    <mergeCell ref="AN86:AN87"/>
+    <mergeCell ref="AS86:AX86"/>
+    <mergeCell ref="AS87:AX87"/>
+    <mergeCell ref="AN88:AN89"/>
+    <mergeCell ref="AS88:AX88"/>
+    <mergeCell ref="AS89:AX89"/>
+    <mergeCell ref="AS90:AX90"/>
+    <mergeCell ref="BC19:BD19"/>
+    <mergeCell ref="BC21:BD21"/>
+    <mergeCell ref="BC22:BD22"/>
+    <mergeCell ref="BC23:BD23"/>
+    <mergeCell ref="BC24:BD24"/>
+    <mergeCell ref="BC25:BD25"/>
+    <mergeCell ref="BC26:BD26"/>
+    <mergeCell ref="BC27:BD27"/>
+    <mergeCell ref="BC28:BD28"/>
+    <mergeCell ref="BC29:BD29"/>
+    <mergeCell ref="BC30:BD30"/>
+    <mergeCell ref="BC31:BD31"/>
+    <mergeCell ref="BC32:BD32"/>
+    <mergeCell ref="BC33:BD33"/>
+    <mergeCell ref="BC34:BD34"/>
+    <mergeCell ref="BC35:BD35"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
     <mergeCell ref="I86:I87"/>
     <mergeCell ref="X131:X132"/>
     <mergeCell ref="X128:X129"/>
@@ -11688,536 +12232,6 @@
     <mergeCell ref="X105:X106"/>
     <mergeCell ref="AD88:AI88"/>
     <mergeCell ref="AD89:AI89"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AS85:AX85"/>
-    <mergeCell ref="AN86:AN87"/>
-    <mergeCell ref="AS86:AX86"/>
-    <mergeCell ref="AS87:AX87"/>
-    <mergeCell ref="AN88:AN89"/>
-    <mergeCell ref="AS88:AX88"/>
-    <mergeCell ref="AS89:AX89"/>
-    <mergeCell ref="AS90:AX90"/>
-    <mergeCell ref="BC19:BD19"/>
-    <mergeCell ref="BC21:BD21"/>
-    <mergeCell ref="BC22:BD22"/>
-    <mergeCell ref="BC23:BD23"/>
-    <mergeCell ref="BC24:BD24"/>
-    <mergeCell ref="BC25:BD25"/>
-    <mergeCell ref="BC26:BD26"/>
-    <mergeCell ref="BC27:BD27"/>
-    <mergeCell ref="BC28:BD28"/>
-    <mergeCell ref="BC29:BD29"/>
-    <mergeCell ref="BC30:BD30"/>
-    <mergeCell ref="BC31:BD31"/>
-    <mergeCell ref="BC32:BD32"/>
-    <mergeCell ref="BC33:BD33"/>
-    <mergeCell ref="BC34:BD34"/>
-    <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A795F0-7A33-48E4-A6BF-3D609E066F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C159EEC-DB16-4D4A-B634-5C5570F08074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="218">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -691,6 +691,9 @@
   </si>
   <si>
     <t>El sistema debe permitir la edición o actualización de cambios realizados a los turnos de los trabajadores</t>
+  </si>
+  <si>
+    <t>06-07.2025</t>
   </si>
 </sst>
 </file>
@@ -1177,11 +1180,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1192,17 +1195,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1213,77 +1309,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1300,15 +1333,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1318,40 +1342,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1688,7 +1691,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="G2:BD230"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1725,70 +1727,70 @@
   </cols>
   <sheetData>
     <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="76" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="72" t="s">
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="76" t="s">
+      <c r="U2" s="83"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="78"/>
-      <c r="AJ2" s="71" t="s">
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="71"/>
-      <c r="AN2" s="74" t="s">
+      <c r="AK2" s="81"/>
+      <c r="AN2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="75" t="s">
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AQ2" s="84"/>
+      <c r="AR2" s="84"/>
+      <c r="AS2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="75"/>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="75"/>
-      <c r="AY2" s="71" t="s">
+      <c r="AT2" s="85"/>
+      <c r="AU2" s="85"/>
+      <c r="AV2" s="85"/>
+      <c r="AW2" s="85"/>
+      <c r="AX2" s="85"/>
+      <c r="AY2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71" t="s">
+      <c r="BB2" s="81"/>
+      <c r="BC2" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="71"/>
+      <c r="BD2" s="81"/>
     </row>
     <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I3" s="1" t="s">
@@ -1806,12 +1808,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="85"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="87"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="74"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1836,12 +1838,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="81"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="88"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1863,12 +1865,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="75"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1881,13 +1883,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="71" t="s">
+      <c r="BC3" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="71"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I4" s="92">
+      <c r="BD3" s="81"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="62">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1913,13 +1915,15 @@
       <c r="T4" s="7">
         <v>45839</v>
       </c>
-      <c r="U4" s="6"/>
+      <c r="U4" s="7">
+        <v>45839</v>
+      </c>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="35">
+      <c r="X4" s="40">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="88">
+      <c r="Y4" s="50">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1945,10 +1949,12 @@
       <c r="AJ4" s="7">
         <v>45839</v>
       </c>
-      <c r="AK4" s="6"/>
+      <c r="AK4" s="7">
+        <v>45839</v>
+      </c>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="68">
+      <c r="AN4" s="90">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1977,11 +1983,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I5" s="69"/>
+      <c r="BC4" s="35"/>
+      <c r="BD4" s="35"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="63"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1994,7 +2000,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="N5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2005,11 +2011,13 @@
       <c r="T5" s="7">
         <v>45839</v>
       </c>
-      <c r="U5" s="6"/>
+      <c r="U5" s="7">
+        <v>45839</v>
+      </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="89"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="51"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2022,21 +2030,23 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="91" t="s">
+      <c r="AD5" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46"/>
+      <c r="AE5" s="76"/>
+      <c r="AF5" s="76"/>
+      <c r="AG5" s="76"/>
+      <c r="AH5" s="76"/>
+      <c r="AI5" s="77"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
-      <c r="AK5" s="6"/>
+      <c r="AK5" s="7">
+        <v>45839</v>
+      </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="69"/>
+      <c r="AN5" s="63"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2049,7 +2059,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="66" t="s">
+      <c r="AS5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2063,11 +2073,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="46"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I6" s="70"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="77"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="64"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2091,11 +2101,13 @@
       <c r="T6" s="7">
         <v>45839</v>
       </c>
-      <c r="U6" s="6"/>
+      <c r="U6" s="7">
+        <v>45839</v>
+      </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="90"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="79"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2108,21 +2120,23 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AD6" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="77"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
-      <c r="AK6" s="6"/>
+      <c r="AK6" s="7">
+        <v>45840</v>
+      </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="70"/>
+      <c r="AN6" s="64"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2149,11 +2163,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="64"/>
-      <c r="BD6" s="64"/>
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="35"/>
     </row>
     <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I7" s="35">
+      <c r="I7" s="40">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2179,7 +2193,9 @@
       <c r="T7" s="8">
         <v>45840</v>
       </c>
-      <c r="U7" s="6"/>
+      <c r="U7" s="7">
+        <v>45840</v>
+      </c>
       <c r="V7" s="20"/>
       <c r="W7" s="20"/>
       <c r="X7" s="6"/>
@@ -2188,17 +2204,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="45"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="76"/>
+      <c r="AG7" s="76"/>
+      <c r="AH7" s="76"/>
+      <c r="AI7" s="77"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="35">
+      <c r="AN7" s="40">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2227,11 +2243,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I8" s="36"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="41"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2255,13 +2271,15 @@
       <c r="T8" s="8">
         <v>45840</v>
       </c>
-      <c r="U8" s="6"/>
+      <c r="U8" s="7">
+        <v>45840</v>
+      </c>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="52">
+      <c r="X8" s="42">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="88">
+      <c r="Y8" s="50">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2287,10 +2305,12 @@
       <c r="AJ8" s="8">
         <v>45840</v>
       </c>
-      <c r="AK8" s="6"/>
+      <c r="AK8" s="7">
+        <v>45840</v>
+      </c>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="55"/>
+      <c r="AN8" s="48"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2317,11 +2337,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="64"/>
-      <c r="BD8" s="64"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I9" s="35">
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="35"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2347,11 +2367,13 @@
       <c r="T9" s="8">
         <v>45841</v>
       </c>
-      <c r="U9" s="6"/>
+      <c r="U9" s="7">
+        <v>45841</v>
+      </c>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="89"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="51"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2375,10 +2397,12 @@
       <c r="AJ9" s="8">
         <v>45840</v>
       </c>
-      <c r="AK9" s="6"/>
+      <c r="AK9" s="7">
+        <v>45840</v>
+      </c>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="35">
+      <c r="AN9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2407,11 +2431,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="64"/>
-      <c r="BD9" s="64"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="35"/>
     </row>
     <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I10" s="36"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2435,7 +2459,9 @@
       <c r="T10" s="8">
         <v>45841</v>
       </c>
-      <c r="U10" s="6"/>
+      <c r="U10" s="7">
+        <v>45841</v>
+      </c>
       <c r="V10" s="20"/>
       <c r="W10" s="21"/>
       <c r="X10" s="6"/>
@@ -2444,17 +2470,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="77"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="55"/>
+      <c r="AN10" s="48"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2481,11 +2507,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="64"/>
-      <c r="BD10" s="64"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I11" s="35">
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="35"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2500,7 +2526,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="66" t="s">
+      <c r="N11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2511,13 +2537,15 @@
       <c r="T11" s="8">
         <v>45842</v>
       </c>
-      <c r="U11" s="6"/>
+      <c r="U11" s="7">
+        <v>45844</v>
+      </c>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="52">
+      <c r="X11" s="42">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="42">
+      <c r="Y11" s="46">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2543,10 +2571,12 @@
       <c r="AJ11" s="8">
         <v>45841</v>
       </c>
-      <c r="AK11" s="6"/>
+      <c r="AK11" s="7">
+        <v>45841</v>
+      </c>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="35">
+      <c r="AN11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2561,7 +2591,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="66" t="s">
+      <c r="AS11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2575,11 +2605,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="64"/>
-      <c r="BD11" s="64"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I12" s="55"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="35"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="48"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2592,7 +2622,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2603,11 +2633,13 @@
       <c r="T12" s="8">
         <v>45842</v>
       </c>
-      <c r="U12" s="6"/>
+      <c r="U12" s="7">
+        <v>45844</v>
+      </c>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="43"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="47"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2631,10 +2663,12 @@
       <c r="AJ12" s="8">
         <v>45841</v>
       </c>
-      <c r="AK12" s="6"/>
+      <c r="AK12" s="7">
+        <v>45841</v>
+      </c>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="55"/>
+      <c r="AN12" s="48"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2647,7 +2681,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="66" t="s">
+      <c r="AS12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2661,11 +2695,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="64"/>
-      <c r="BD12" s="64"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
     </row>
     <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I13" s="36"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2689,7 +2723,9 @@
       <c r="T13" s="8">
         <v>45842</v>
       </c>
-      <c r="U13" s="6"/>
+      <c r="U13" s="7">
+        <v>45844</v>
+      </c>
       <c r="V13" s="20"/>
       <c r="W13" s="21"/>
       <c r="X13" s="6"/>
@@ -2698,17 +2734,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="45"/>
-      <c r="AF13" s="45"/>
-      <c r="AG13" s="45"/>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="46"/>
+      <c r="AD13" s="75"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="77"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="36"/>
+      <c r="AN13" s="41"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2735,11 +2771,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="64"/>
-      <c r="BD13" s="64"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I14" s="35">
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="35"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I14" s="40">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2765,13 +2801,15 @@
       <c r="T14" s="8">
         <v>45843</v>
       </c>
-      <c r="U14" s="6"/>
+      <c r="U14" s="7">
+        <v>45844</v>
+      </c>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="52">
+      <c r="X14" s="42">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="40">
+      <c r="Y14" s="52">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2786,7 +2824,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="66" t="s">
+      <c r="AD14" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2797,10 +2835,12 @@
       <c r="AJ14" s="8">
         <v>45842</v>
       </c>
-      <c r="AK14" s="6"/>
+      <c r="AK14" s="7">
+        <v>45842</v>
+      </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="35">
+      <c r="AN14" s="40">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2829,11 +2869,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="64"/>
-      <c r="BD14" s="64"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I15" s="55"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="35"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I15" s="48"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2857,11 +2897,13 @@
       <c r="T15" s="8">
         <v>45843</v>
       </c>
-      <c r="U15" s="6"/>
+      <c r="U15" s="7">
+        <v>45844</v>
+      </c>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="62"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="78"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2874,7 +2916,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="66" t="s">
+      <c r="AD15" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2885,10 +2927,12 @@
       <c r="AJ15" s="8">
         <v>45842</v>
       </c>
-      <c r="AK15" s="6"/>
+      <c r="AK15" s="7">
+        <v>45842</v>
+      </c>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="55"/>
+      <c r="AN15" s="48"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2915,11 +2959,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="64"/>
-      <c r="BD15" s="64"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I16" s="36"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="35"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="41"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2943,11 +2987,13 @@
       <c r="T16" s="17">
         <v>45843</v>
       </c>
-      <c r="U16" s="6"/>
+      <c r="U16" s="7">
+        <v>45844</v>
+      </c>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="41"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="53"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2971,10 +3017,12 @@
       <c r="AJ16" s="8">
         <v>45842</v>
       </c>
-      <c r="AK16" s="6"/>
+      <c r="AK16" s="7">
+        <v>45842</v>
+      </c>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="55"/>
+      <c r="AN16" s="48"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3001,11 +3049,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="65"/>
-      <c r="BD16" s="65"/>
+      <c r="BC16" s="36"/>
+      <c r="BD16" s="36"/>
     </row>
     <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I17" s="53">
+      <c r="I17" s="92">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3031,7 +3079,9 @@
       <c r="T17" s="8">
         <v>45844</v>
       </c>
-      <c r="U17" s="6"/>
+      <c r="U17" s="7">
+        <v>45844</v>
+      </c>
       <c r="V17" s="20"/>
       <c r="W17" s="21"/>
       <c r="X17" s="6"/>
@@ -3040,17 +3090,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="46"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="77"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="93">
+      <c r="AN17" s="49">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3079,11 +3129,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="64"/>
-      <c r="BD17" s="64"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I18" s="54"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="35"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I18" s="93"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3107,13 +3157,15 @@
       <c r="T18" s="8">
         <v>45844</v>
       </c>
-      <c r="U18" s="6"/>
+      <c r="U18" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="52">
+      <c r="X18" s="42">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="40">
+      <c r="Y18" s="52">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3139,10 +3191,12 @@
       <c r="AJ18" s="8">
         <v>45843</v>
       </c>
-      <c r="AK18" s="6"/>
+      <c r="AK18" s="7">
+        <v>45843</v>
+      </c>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="93"/>
+      <c r="AN18" s="49"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3169,11 +3223,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="64"/>
-      <c r="BD18" s="64"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I19" s="35" t="s">
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="35"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3196,8 +3250,8 @@
       <c r="U19" s="6"/>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="62"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="78"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3221,10 +3275,12 @@
       <c r="AJ19" s="8">
         <v>45843</v>
       </c>
-      <c r="AK19" s="6"/>
+      <c r="AK19" s="7">
+        <v>45843</v>
+      </c>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="35" t="s">
+      <c r="AN19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3247,11 +3303,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="64"/>
-      <c r="BD19" s="64"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I20" s="36"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="41"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3272,8 +3328,8 @@
       <c r="U20" s="7"/>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="52"/>
-      <c r="Y20" s="41"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="53"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3297,10 +3353,12 @@
       <c r="AJ20" s="17">
         <v>45843</v>
       </c>
-      <c r="AK20" s="7"/>
+      <c r="AK20" s="7">
+        <v>45843</v>
+      </c>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="36"/>
+      <c r="AN20" s="41"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3321,11 +3379,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="64"/>
-      <c r="BD20" s="64"/>
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="35"/>
     </row>
     <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I21" s="35">
+      <c r="I21" s="40">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3362,17 +3420,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="46"/>
+      <c r="AD21" s="75"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="77"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="35">
+      <c r="AN21" s="40">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3403,11 +3461,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="64"/>
-      <c r="BD21" s="64"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I22" s="55"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="35"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I22" s="48"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3436,10 +3494,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="93">
+      <c r="X22" s="49">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="40">
+      <c r="Y22" s="52">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3465,10 +3523,12 @@
       <c r="AJ22" s="8">
         <v>45844</v>
       </c>
-      <c r="AK22" s="7"/>
+      <c r="AK22" s="7">
+        <v>45844</v>
+      </c>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="55"/>
+      <c r="AN22" s="48"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3497,11 +3557,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I23" s="36"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="35"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" s="41"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3530,8 +3590,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="93"/>
-      <c r="Y23" s="41"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="53"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3555,10 +3615,12 @@
       <c r="AJ23" s="8">
         <v>45844</v>
       </c>
-      <c r="AK23" s="7"/>
+      <c r="AK23" s="7">
+        <v>45845</v>
+      </c>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="36"/>
+      <c r="AN23" s="41"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3587,11 +3649,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="64"/>
-      <c r="BD23" s="64"/>
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="35"/>
     </row>
     <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3628,17 +3690,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="44"/>
-      <c r="AE24" s="45"/>
-      <c r="AF24" s="45"/>
-      <c r="AG24" s="45"/>
-      <c r="AH24" s="45"/>
-      <c r="AI24" s="46"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="76"/>
+      <c r="AF24" s="76"/>
+      <c r="AG24" s="76"/>
+      <c r="AH24" s="76"/>
+      <c r="AI24" s="77"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="35" t="s">
+      <c r="AN24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3669,11 +3731,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="64"/>
-      <c r="BD24" s="64"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="35"/>
     </row>
     <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I25" s="36"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3702,10 +3764,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="35" t="s">
+      <c r="X25" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="42">
+      <c r="Y25" s="46">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3728,7 +3790,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="36"/>
+      <c r="AN25" s="41"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3757,11 +3819,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="64"/>
-      <c r="BD25" s="64"/>
+      <c r="BC25" s="35"/>
+      <c r="BD25" s="35"/>
     </row>
     <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I26" s="35" t="s">
+      <c r="I26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3792,8 +3854,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="43"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="47"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3814,7 +3876,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="35" t="s">
+      <c r="AN26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3845,11 +3907,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="64"/>
-      <c r="BD26" s="64"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
     </row>
     <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I27" s="36"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3884,17 +3946,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="44"/>
-      <c r="AE27" s="45"/>
-      <c r="AF27" s="45"/>
-      <c r="AG27" s="45"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="46"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="77"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="36"/>
+      <c r="AN27" s="41"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3923,11 +3985,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="64"/>
-      <c r="BD27" s="64"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I28" s="35" t="s">
+      <c r="BC27" s="35"/>
+      <c r="BD27" s="35"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3958,10 +4020,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="35">
+      <c r="X28" s="40">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="58">
+      <c r="Y28" s="60">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -3992,7 +4054,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="35" t="s">
+      <c r="AN28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4023,11 +4085,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="65"/>
-      <c r="BD28" s="65"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I29" s="55"/>
+      <c r="BC28" s="36"/>
+      <c r="BD28" s="36"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="48"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4056,8 +4118,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="63"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="91"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4086,7 +4148,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="55"/>
+      <c r="AN29" s="48"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4115,11 +4177,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="64"/>
-      <c r="BD29" s="64"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I30" s="36"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I30" s="41"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4148,8 +4210,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="59"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="61"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4178,7 +4240,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="36"/>
+      <c r="AN30" s="41"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4207,11 +4269,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="64"/>
-      <c r="BD30" s="64"/>
+      <c r="BC30" s="35"/>
+      <c r="BD30" s="35"/>
     </row>
     <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I31" s="35">
+      <c r="I31" s="40">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4248,17 +4310,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="44"/>
-      <c r="AE31" s="45"/>
-      <c r="AF31" s="45"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="45"/>
-      <c r="AI31" s="46"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="77"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="35">
+      <c r="AN31" s="40">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4289,11 +4351,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="64"/>
-      <c r="BD31" s="64"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I32" s="36"/>
+      <c r="BC31" s="35"/>
+      <c r="BD31" s="35"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I32" s="41"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4322,10 +4384,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="35">
+      <c r="X32" s="40">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="58">
+      <c r="Y32" s="60">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4356,7 +4418,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="36"/>
+      <c r="AN32" s="41"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4385,11 +4447,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="64"/>
-      <c r="BD32" s="64"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I33" s="35">
+      <c r="BC32" s="35"/>
+      <c r="BD32" s="35"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I33" s="40">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4420,8 +4482,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="59"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="61"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4450,7 +4512,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="35">
+      <c r="AN33" s="40">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4481,11 +4543,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="64"/>
-      <c r="BD33" s="64"/>
+      <c r="BC33" s="35"/>
+      <c r="BD33" s="35"/>
     </row>
     <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I34" s="36"/>
+      <c r="I34" s="41"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4520,17 +4582,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="44"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="46"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="36"/>
+      <c r="AN34" s="41"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4559,11 +4621,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="64"/>
-      <c r="BD34" s="64"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I35" s="35">
+      <c r="BC34" s="35"/>
+      <c r="BD34" s="35"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4594,10 +4656,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="35" t="s">
+      <c r="X35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="42">
+      <c r="Y35" s="46">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4628,7 +4690,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="35">
+      <c r="AN35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4659,11 +4721,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="64"/>
-      <c r="BD35" s="64"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I36" s="36"/>
+      <c r="BC35" s="35"/>
+      <c r="BD35" s="35"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36" s="41"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4692,8 +4754,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="43"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="47"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4722,7 +4784,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="36"/>
+      <c r="AN36" s="41"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4751,11 +4813,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="64"/>
-      <c r="BD36" s="64"/>
+      <c r="BC36" s="35"/>
+      <c r="BD36" s="35"/>
     </row>
     <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I37" s="35">
+      <c r="I37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4792,17 +4854,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="44"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="46"/>
+      <c r="AD37" s="75"/>
+      <c r="AE37" s="76"/>
+      <c r="AF37" s="76"/>
+      <c r="AG37" s="76"/>
+      <c r="AH37" s="76"/>
+      <c r="AI37" s="77"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="35">
+      <c r="AN37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4833,11 +4895,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="64"/>
-      <c r="BD37" s="64"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I38" s="36"/>
+      <c r="BC37" s="35"/>
+      <c r="BD37" s="35"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" s="41"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4866,10 +4928,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="35" t="s">
+      <c r="X38" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="40">
+      <c r="Y38" s="52">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4900,7 +4962,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="36"/>
+      <c r="AN38" s="41"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4929,10 +4991,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="64"/>
-      <c r="BD38" s="64"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC38" s="35"/>
+      <c r="BD38" s="35"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -4964,8 +5026,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="62"/>
+      <c r="X39" s="48"/>
+      <c r="Y39" s="78"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5025,11 +5087,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="64"/>
-      <c r="BD39" s="64"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I40" s="35">
+      <c r="BC39" s="35"/>
+      <c r="BD39" s="35"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5060,8 +5122,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="36"/>
-      <c r="Y40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="53"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5090,7 +5152,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="35">
+      <c r="AN40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5121,11 +5183,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="65"/>
-      <c r="BD40" s="65"/>
+      <c r="BC40" s="36"/>
+      <c r="BD40" s="36"/>
     </row>
     <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I41" s="36"/>
+      <c r="I41" s="41"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5138,14 +5200,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="47" t="s">
+      <c r="N41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="49"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="45"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5160,17 +5222,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="44"/>
-      <c r="AE41" s="45"/>
-      <c r="AF41" s="45"/>
-      <c r="AG41" s="45"/>
-      <c r="AH41" s="45"/>
-      <c r="AI41" s="46"/>
+      <c r="AD41" s="75"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="76"/>
+      <c r="AG41" s="76"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="77"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="36"/>
+      <c r="AN41" s="41"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5183,14 +5245,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="47" t="s">
+      <c r="AS41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="48"/>
-      <c r="AU41" s="48"/>
-      <c r="AV41" s="48"/>
-      <c r="AW41" s="48"/>
-      <c r="AX41" s="49"/>
+      <c r="AT41" s="44"/>
+      <c r="AU41" s="44"/>
+      <c r="AV41" s="44"/>
+      <c r="AW41" s="44"/>
+      <c r="AX41" s="45"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5199,10 +5261,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="64"/>
-      <c r="BD41" s="64"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC41" s="35"/>
+      <c r="BD41" s="35"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5234,10 +5296,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="35">
+      <c r="X42" s="40">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="40">
+      <c r="Y42" s="52">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5299,11 +5361,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="64"/>
-      <c r="BD42" s="64"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I43" s="35">
+      <c r="BC42" s="35"/>
+      <c r="BD42" s="35"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" s="40">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5334,8 +5396,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="53"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5364,7 +5426,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="35">
+      <c r="AN43" s="40">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5395,11 +5457,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="64"/>
-      <c r="BD43" s="64"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
     </row>
     <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I44" s="36"/>
+      <c r="I44" s="41"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5434,17 +5496,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="44"/>
-      <c r="AE44" s="45"/>
-      <c r="AF44" s="45"/>
-      <c r="AG44" s="45"/>
-      <c r="AH44" s="45"/>
-      <c r="AI44" s="46"/>
+      <c r="AD44" s="75"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="76"/>
+      <c r="AG44" s="76"/>
+      <c r="AH44" s="76"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="36"/>
+      <c r="AN44" s="41"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5473,10 +5535,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="64"/>
-      <c r="BD44" s="64"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5508,10 +5570,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="35">
+      <c r="X45" s="40">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="58">
+      <c r="Y45" s="60">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5573,11 +5635,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="64"/>
-      <c r="BD45" s="64"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I46" s="35" t="s">
+      <c r="BC45" s="35"/>
+      <c r="BD45" s="35"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5608,8 +5670,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="59"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="61"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5638,7 +5700,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="35" t="s">
+      <c r="AN46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5669,11 +5731,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="64"/>
-      <c r="BD46" s="64"/>
+      <c r="BC46" s="35"/>
+      <c r="BD46" s="35"/>
     </row>
     <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I47" s="36"/>
+      <c r="I47" s="41"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5708,17 +5770,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="45"/>
-      <c r="AF47" s="45"/>
-      <c r="AG47" s="45"/>
-      <c r="AH47" s="45"/>
-      <c r="AI47" s="46"/>
+      <c r="AD47" s="75"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="76"/>
+      <c r="AG47" s="76"/>
+      <c r="AH47" s="76"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="36"/>
+      <c r="AN47" s="41"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5747,11 +5809,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="64"/>
-      <c r="BD47" s="64"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I48" s="35" t="s">
+      <c r="BC47" s="35"/>
+      <c r="BD47" s="35"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5782,10 +5844,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="35">
+      <c r="X48" s="40">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="42">
+      <c r="Y48" s="46">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5816,7 +5878,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="35" t="s">
+      <c r="AN48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5847,11 +5909,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="64"/>
-      <c r="BD48" s="64"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I49" s="36"/>
+      <c r="BC48" s="35"/>
+      <c r="BD48" s="35"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I49" s="41"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5880,8 +5942,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="43"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="47"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5910,7 +5972,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="36"/>
+      <c r="AN49" s="41"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5939,12 +6001,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="64"/>
-      <c r="BD49" s="64"/>
+      <c r="BC49" s="35"/>
+      <c r="BD49" s="35"/>
     </row>
     <row r="50" spans="8:56" x14ac:dyDescent="0.2">
       <c r="H50" s="10"/>
-      <c r="I50" s="35">
+      <c r="I50" s="40">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -5959,14 +6021,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="47" t="s">
+      <c r="N50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-      <c r="R50" s="48"/>
-      <c r="S50" s="49"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="45"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -5981,17 +6043,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="45"/>
-      <c r="AG50" s="45"/>
-      <c r="AH50" s="45"/>
-      <c r="AI50" s="46"/>
+      <c r="AD50" s="75"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="76"/>
+      <c r="AH50" s="76"/>
+      <c r="AI50" s="77"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="35">
+      <c r="AN50" s="40">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6002,23 +6064,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="47" t="s">
+      <c r="AS50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="48"/>
-      <c r="AU50" s="48"/>
-      <c r="AV50" s="48"/>
-      <c r="AW50" s="48"/>
-      <c r="AX50" s="49"/>
+      <c r="AT50" s="44"/>
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="45"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="64"/>
-      <c r="BD50" s="64"/>
-    </row>
-    <row r="51" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I51" s="36"/>
+      <c r="BC50" s="35"/>
+      <c r="BD50" s="35"/>
+    </row>
+    <row r="51" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I51" s="41"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6031,14 +6093,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="47" t="s">
+      <c r="N51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="49"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="45"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6047,10 +6109,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="35">
+      <c r="X51" s="40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="40">
+      <c r="Y51" s="52">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6081,7 +6143,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="36"/>
+      <c r="AN51" s="41"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6090,23 +6152,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="47" t="s">
+      <c r="AS51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="48"/>
-      <c r="AU51" s="48"/>
-      <c r="AV51" s="48"/>
-      <c r="AW51" s="48"/>
-      <c r="AX51" s="49"/>
+      <c r="AT51" s="44"/>
+      <c r="AU51" s="44"/>
+      <c r="AV51" s="44"/>
+      <c r="AW51" s="44"/>
+      <c r="AX51" s="45"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="64"/>
-      <c r="BD51" s="64"/>
-    </row>
-    <row r="52" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I52" s="35">
+      <c r="BC51" s="35"/>
+      <c r="BD51" s="35"/>
+    </row>
+    <row r="52" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I52" s="40">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6137,8 +6199,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="36"/>
-      <c r="Y52" s="41"/>
+      <c r="X52" s="41"/>
+      <c r="Y52" s="53"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6167,7 +6229,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="35">
+      <c r="AN52" s="40">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6190,11 +6252,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="65"/>
-      <c r="BD52" s="65"/>
+      <c r="BC52" s="36"/>
+      <c r="BD52" s="36"/>
     </row>
     <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I53" s="36"/>
+      <c r="I53" s="41"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6229,17 +6291,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="44"/>
-      <c r="AE53" s="45"/>
-      <c r="AF53" s="45"/>
-      <c r="AG53" s="45"/>
-      <c r="AH53" s="45"/>
-      <c r="AI53" s="46"/>
+      <c r="AD53" s="75"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="76"/>
+      <c r="AG53" s="76"/>
+      <c r="AH53" s="76"/>
+      <c r="AI53" s="77"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="36"/>
+      <c r="AN53" s="41"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6260,11 +6322,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="64"/>
-      <c r="BD53" s="64"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I54" s="35">
+      <c r="BC53" s="35"/>
+      <c r="BD53" s="35"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" s="40">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6329,7 +6391,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="35">
+      <c r="AN54" s="40">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6352,11 +6414,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="64"/>
-      <c r="BD54" s="64"/>
+      <c r="BC54" s="35"/>
+      <c r="BD54" s="35"/>
     </row>
     <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I55" s="36"/>
+      <c r="I55" s="41"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6391,17 +6453,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="44"/>
-      <c r="AE55" s="45"/>
-      <c r="AF55" s="45"/>
-      <c r="AG55" s="45"/>
-      <c r="AH55" s="45"/>
-      <c r="AI55" s="46"/>
+      <c r="AD55" s="75"/>
+      <c r="AE55" s="76"/>
+      <c r="AF55" s="76"/>
+      <c r="AG55" s="76"/>
+      <c r="AH55" s="76"/>
+      <c r="AI55" s="77"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="36"/>
+      <c r="AN55" s="41"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6422,10 +6484,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="64"/>
-      <c r="BD55" s="64"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC55" s="35"/>
+      <c r="BD55" s="35"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6457,10 +6519,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="35">
+      <c r="X56" s="40">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="58">
+      <c r="Y56" s="60">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6514,11 +6576,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="64"/>
-      <c r="BD56" s="64"/>
-    </row>
-    <row r="57" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I57" s="35">
+      <c r="BC56" s="35"/>
+      <c r="BD56" s="35"/>
+    </row>
+    <row r="57" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I57" s="40">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6549,8 +6611,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="36"/>
-      <c r="Y57" s="59"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="61"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6561,14 +6623,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="47" t="s">
+      <c r="AD57" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="48"/>
-      <c r="AF57" s="48"/>
-      <c r="AG57" s="48"/>
-      <c r="AH57" s="48"/>
-      <c r="AI57" s="49"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="44"/>
+      <c r="AI57" s="45"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6577,7 +6639,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="35">
+      <c r="AN57" s="40">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6600,11 +6662,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="64"/>
-      <c r="BD57" s="64"/>
+      <c r="BC57" s="35"/>
+      <c r="BD57" s="35"/>
     </row>
     <row r="58" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I58" s="36"/>
+      <c r="I58" s="41"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6639,17 +6701,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="44"/>
-      <c r="AE58" s="45"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="45"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
+      <c r="AD58" s="75"/>
+      <c r="AE58" s="76"/>
+      <c r="AF58" s="76"/>
+      <c r="AG58" s="76"/>
+      <c r="AH58" s="76"/>
+      <c r="AI58" s="77"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="36"/>
+      <c r="AN58" s="41"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6670,11 +6732,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="64"/>
-      <c r="BD58" s="64"/>
-    </row>
-    <row r="59" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I59" s="35">
+      <c r="BC58" s="35"/>
+      <c r="BD58" s="35"/>
+    </row>
+    <row r="59" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I59" s="40">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6739,7 +6801,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="35">
+      <c r="AN59" s="40">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6762,11 +6824,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="64"/>
-      <c r="BD59" s="64"/>
+      <c r="BC59" s="35"/>
+      <c r="BD59" s="35"/>
     </row>
     <row r="60" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I60" s="36"/>
+      <c r="I60" s="41"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6801,17 +6863,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="44"/>
-      <c r="AE60" s="45"/>
-      <c r="AF60" s="45"/>
-      <c r="AG60" s="45"/>
-      <c r="AH60" s="45"/>
-      <c r="AI60" s="46"/>
+      <c r="AD60" s="75"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="77"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="36"/>
+      <c r="AN60" s="41"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6832,11 +6894,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="64"/>
-      <c r="BD60" s="64"/>
-    </row>
-    <row r="61" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I61" s="35" t="s">
+      <c r="BC60" s="35"/>
+      <c r="BD60" s="35"/>
+    </row>
+    <row r="61" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6867,10 +6929,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="35">
+      <c r="X61" s="40">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="60">
+      <c r="Y61" s="58">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6901,7 +6963,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="35" t="s">
+      <c r="AN61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6924,11 +6986,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="64"/>
-      <c r="BD61" s="64"/>
-    </row>
-    <row r="62" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I62" s="36"/>
+      <c r="BC61" s="35"/>
+      <c r="BD61" s="35"/>
+    </row>
+    <row r="62" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="I62" s="41"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -6957,8 +7019,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="61"/>
+      <c r="X62" s="41"/>
+      <c r="Y62" s="59"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -6987,7 +7049,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="36"/>
+      <c r="AN62" s="41"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7008,11 +7070,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="64"/>
-      <c r="BD62" s="64"/>
+      <c r="BC62" s="35"/>
+      <c r="BD62" s="35"/>
     </row>
     <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I63" s="35">
+      <c r="I63" s="40">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7049,17 +7111,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="44"/>
-      <c r="AE63" s="45"/>
-      <c r="AF63" s="45"/>
-      <c r="AG63" s="45"/>
-      <c r="AH63" s="45"/>
-      <c r="AI63" s="46"/>
+      <c r="AD63" s="75"/>
+      <c r="AE63" s="76"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="76"/>
+      <c r="AH63" s="76"/>
+      <c r="AI63" s="77"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="35">
+      <c r="AN63" s="40">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7082,11 +7144,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="64"/>
-      <c r="BD63" s="64"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I64" s="36"/>
+      <c r="BC63" s="35"/>
+      <c r="BD63" s="35"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I64" s="41"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7149,7 +7211,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="36"/>
+      <c r="AN64" s="41"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7170,11 +7232,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="65"/>
-      <c r="BD64" s="65"/>
+      <c r="BC64" s="36"/>
+      <c r="BD64" s="36"/>
     </row>
     <row r="65" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I65" s="35">
+      <c r="I65" s="40">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7203,17 +7265,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="44"/>
-      <c r="AE65" s="45"/>
-      <c r="AF65" s="45"/>
-      <c r="AG65" s="45"/>
-      <c r="AH65" s="45"/>
-      <c r="AI65" s="46"/>
+      <c r="AD65" s="75"/>
+      <c r="AE65" s="76"/>
+      <c r="AF65" s="76"/>
+      <c r="AG65" s="76"/>
+      <c r="AH65" s="76"/>
+      <c r="AI65" s="77"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="35">
+      <c r="AN65" s="40">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7236,11 +7298,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="64"/>
-      <c r="BD65" s="64"/>
-    </row>
-    <row r="66" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I66" s="36"/>
+      <c r="BC65" s="35"/>
+      <c r="BD65" s="35"/>
+    </row>
+    <row r="66" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I66" s="41"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7261,10 +7323,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="35" t="s">
+      <c r="X66" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="56">
+      <c r="Y66" s="54">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7295,7 +7357,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="36"/>
+      <c r="AN66" s="41"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7316,10 +7378,10 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="64"/>
-      <c r="BD66" s="64"/>
-    </row>
-    <row r="67" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC66" s="35"/>
+      <c r="BD66" s="35"/>
+    </row>
+    <row r="67" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
@@ -7343,8 +7405,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="36"/>
-      <c r="Y67" s="57"/>
+      <c r="X67" s="41"/>
+      <c r="Y67" s="55"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7396,17 +7458,19 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="64"/>
-      <c r="BD67" s="64"/>
+      <c r="BC67" s="35"/>
+      <c r="BD67" s="35"/>
     </row>
     <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I68" s="35">
+      <c r="I68" s="40">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="K68" s="6"/>
+      <c r="K68" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="L68" s="19"/>
       <c r="M68" s="6" t="s">
         <v>13</v>
@@ -7419,7 +7483,9 @@
       <c r="Q68" s="38"/>
       <c r="R68" s="38"/>
       <c r="S68" s="39"/>
-      <c r="T68" s="7"/>
+      <c r="T68" s="7">
+        <v>45903</v>
+      </c>
       <c r="U68" s="6"/>
       <c r="V68" s="20"/>
       <c r="W68" s="20"/>
@@ -7429,17 +7495,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="44"/>
-      <c r="AE68" s="45"/>
-      <c r="AF68" s="45"/>
-      <c r="AG68" s="45"/>
-      <c r="AH68" s="45"/>
-      <c r="AI68" s="46"/>
+      <c r="AD68" s="75"/>
+      <c r="AE68" s="76"/>
+      <c r="AF68" s="76"/>
+      <c r="AG68" s="76"/>
+      <c r="AH68" s="76"/>
+      <c r="AI68" s="77"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="35">
+      <c r="AN68" s="40">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7462,15 +7528,17 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="64"/>
-      <c r="BD68" s="64"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I69" s="36"/>
+      <c r="BC68" s="35"/>
+      <c r="BD68" s="35"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I69" s="41"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K69" s="6"/>
+      <c r="K69" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="L69" s="19"/>
       <c r="M69" s="6" t="s">
         <v>13</v>
@@ -7483,14 +7551,16 @@
       <c r="Q69" s="38"/>
       <c r="R69" s="38"/>
       <c r="S69" s="39"/>
-      <c r="T69" s="7"/>
+      <c r="T69" s="7">
+        <v>45903</v>
+      </c>
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="35" t="s">
+      <c r="X69" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="56">
+      <c r="Y69" s="54">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7521,7 +7591,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="36"/>
+      <c r="AN69" s="41"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7542,10 +7612,10 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="64"/>
-      <c r="BD69" s="64"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC69" s="35"/>
+      <c r="BD69" s="35"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
@@ -7569,8 +7639,8 @@
       <c r="U70" s="6"/>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="36"/>
-      <c r="Y70" s="57"/>
+      <c r="X70" s="41"/>
+      <c r="Y70" s="55"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7622,11 +7692,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="64"/>
-      <c r="BD70" s="64"/>
+      <c r="BC70" s="35"/>
+      <c r="BD70" s="35"/>
     </row>
     <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I71" s="35">
+      <c r="I71" s="40">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7655,17 +7725,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="44"/>
-      <c r="AE71" s="45"/>
-      <c r="AF71" s="45"/>
-      <c r="AG71" s="45"/>
-      <c r="AH71" s="45"/>
-      <c r="AI71" s="46"/>
+      <c r="AD71" s="75"/>
+      <c r="AE71" s="76"/>
+      <c r="AF71" s="76"/>
+      <c r="AG71" s="76"/>
+      <c r="AH71" s="76"/>
+      <c r="AI71" s="77"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="35">
+      <c r="AN71" s="40">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7688,11 +7758,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="64"/>
-      <c r="BD71" s="64"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I72" s="36"/>
+      <c r="BC71" s="35"/>
+      <c r="BD71" s="35"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I72" s="41"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7713,10 +7783,10 @@
       <c r="U72" s="6"/>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="35">
+      <c r="X72" s="40">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="40">
+      <c r="Y72" s="52">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7731,14 +7801,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="47" t="s">
+      <c r="AD72" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="48"/>
-      <c r="AF72" s="48"/>
-      <c r="AG72" s="48"/>
-      <c r="AH72" s="48"/>
-      <c r="AI72" s="49"/>
+      <c r="AE72" s="44"/>
+      <c r="AF72" s="44"/>
+      <c r="AG72" s="44"/>
+      <c r="AH72" s="44"/>
+      <c r="AI72" s="45"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7747,7 +7817,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="36"/>
+      <c r="AN72" s="41"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7768,11 +7838,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="64"/>
-      <c r="BD72" s="64"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I73" s="35">
+      <c r="BC72" s="35"/>
+      <c r="BD72" s="35"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7783,20 +7853,20 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="47" t="s">
+      <c r="N73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="48"/>
-      <c r="P73" s="48"/>
-      <c r="Q73" s="48"/>
-      <c r="R73" s="48"/>
-      <c r="S73" s="49"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="44"/>
+      <c r="S73" s="45"/>
       <c r="T73" s="7"/>
       <c r="U73" s="6"/>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="36"/>
-      <c r="Y73" s="41"/>
+      <c r="X73" s="41"/>
+      <c r="Y73" s="53"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7809,14 +7879,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="47" t="s">
+      <c r="AD73" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="48"/>
-      <c r="AF73" s="48"/>
-      <c r="AG73" s="48"/>
-      <c r="AH73" s="48"/>
-      <c r="AI73" s="49"/>
+      <c r="AE73" s="44"/>
+      <c r="AF73" s="44"/>
+      <c r="AG73" s="44"/>
+      <c r="AH73" s="44"/>
+      <c r="AI73" s="45"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7825,7 +7895,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="35">
+      <c r="AN73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7836,23 +7906,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="47" t="s">
+      <c r="AS73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="48"/>
-      <c r="AU73" s="48"/>
-      <c r="AV73" s="48"/>
-      <c r="AW73" s="48"/>
-      <c r="AX73" s="49"/>
+      <c r="AT73" s="44"/>
+      <c r="AU73" s="44"/>
+      <c r="AV73" s="44"/>
+      <c r="AW73" s="44"/>
+      <c r="AX73" s="45"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="64"/>
-      <c r="BD73" s="64"/>
+      <c r="BC73" s="35"/>
+      <c r="BD73" s="35"/>
     </row>
     <row r="74" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I74" s="36"/>
+      <c r="I74" s="41"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7879,17 +7949,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="44"/>
-      <c r="AE74" s="45"/>
-      <c r="AF74" s="45"/>
-      <c r="AG74" s="45"/>
-      <c r="AH74" s="45"/>
-      <c r="AI74" s="46"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="76"/>
+      <c r="AF74" s="76"/>
+      <c r="AG74" s="76"/>
+      <c r="AH74" s="76"/>
+      <c r="AI74" s="77"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="36"/>
+      <c r="AN74" s="41"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7910,11 +7980,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="64"/>
-      <c r="BD74" s="64"/>
-    </row>
-    <row r="75" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I75" s="35">
+      <c r="BC74" s="35"/>
+      <c r="BD74" s="35"/>
+    </row>
+    <row r="75" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7925,22 +7995,22 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="47" t="s">
+      <c r="N75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="49"/>
+      <c r="O75" s="44"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="44"/>
+      <c r="R75" s="44"/>
+      <c r="S75" s="45"/>
       <c r="T75" s="7"/>
       <c r="U75" s="6"/>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="35">
+      <c r="X75" s="40">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="58">
+      <c r="Y75" s="60">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -7971,7 +8041,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="35">
+      <c r="AN75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -7982,23 +8052,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="47" t="s">
+      <c r="AS75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="48"/>
-      <c r="AU75" s="48"/>
-      <c r="AV75" s="48"/>
-      <c r="AW75" s="48"/>
-      <c r="AX75" s="49"/>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="44"/>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="44"/>
+      <c r="AX75" s="45"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="64"/>
-      <c r="BD75" s="64"/>
-    </row>
-    <row r="76" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I76" s="36"/>
+      <c r="BC75" s="35"/>
+      <c r="BD75" s="35"/>
+    </row>
+    <row r="76" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I76" s="41"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8019,8 +8089,8 @@
       <c r="U76" s="6"/>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="36"/>
-      <c r="Y76" s="59"/>
+      <c r="X76" s="41"/>
+      <c r="Y76" s="61"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8049,7 +8119,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="36"/>
+      <c r="AN76" s="41"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8070,11 +8140,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="65"/>
-      <c r="BD76" s="65"/>
+      <c r="BC76" s="36"/>
+      <c r="BD76" s="36"/>
     </row>
     <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I77" s="35">
+      <c r="I77" s="40">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8103,17 +8173,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="44"/>
-      <c r="AE77" s="45"/>
-      <c r="AF77" s="45"/>
-      <c r="AG77" s="45"/>
-      <c r="AH77" s="45"/>
-      <c r="AI77" s="46"/>
+      <c r="AD77" s="75"/>
+      <c r="AE77" s="76"/>
+      <c r="AF77" s="76"/>
+      <c r="AG77" s="76"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="77"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="35">
+      <c r="AN77" s="40">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8136,11 +8206,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="64"/>
-      <c r="BD77" s="64"/>
-    </row>
-    <row r="78" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I78" s="36"/>
+      <c r="BC77" s="35"/>
+      <c r="BD77" s="35"/>
+    </row>
+    <row r="78" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I78" s="41"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8161,10 +8231,10 @@
       <c r="U78" s="6"/>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="35">
+      <c r="X78" s="40">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="40">
+      <c r="Y78" s="52">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8195,7 +8265,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="36"/>
+      <c r="AN78" s="41"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8216,35 +8286,39 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="64"/>
-      <c r="BD78" s="64"/>
-    </row>
-    <row r="79" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I79" s="35">
+      <c r="BC78" s="35"/>
+      <c r="BD78" s="35"/>
+    </row>
+    <row r="79" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I79" s="40">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K79" s="6"/>
+      <c r="K79" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="L79" s="19"/>
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="47" t="s">
+      <c r="N79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="48"/>
-      <c r="P79" s="48"/>
-      <c r="Q79" s="48"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="49"/>
-      <c r="T79" s="7"/>
+      <c r="O79" s="44"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="44"/>
+      <c r="R79" s="44"/>
+      <c r="S79" s="45"/>
+      <c r="T79" s="7">
+        <v>45905</v>
+      </c>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="36"/>
-      <c r="Y79" s="41"/>
+      <c r="X79" s="41"/>
+      <c r="Y79" s="53"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8273,7 +8347,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="35">
+      <c r="AN79" s="40">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8284,27 +8358,29 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="47" t="s">
+      <c r="AS79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="48"/>
-      <c r="AU79" s="48"/>
-      <c r="AV79" s="48"/>
-      <c r="AW79" s="48"/>
-      <c r="AX79" s="49"/>
+      <c r="AT79" s="44"/>
+      <c r="AU79" s="44"/>
+      <c r="AV79" s="44"/>
+      <c r="AW79" s="44"/>
+      <c r="AX79" s="45"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="64"/>
-      <c r="BD79" s="64"/>
+      <c r="BC79" s="35"/>
+      <c r="BD79" s="35"/>
     </row>
     <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I80" s="36"/>
+      <c r="I80" s="41"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="L80" s="19"/>
       <c r="M80" s="6" t="s">
         <v>13</v>
@@ -8317,7 +8393,9 @@
       <c r="Q80" s="38"/>
       <c r="R80" s="38"/>
       <c r="S80" s="39"/>
-      <c r="T80" s="7"/>
+      <c r="T80" s="7">
+        <v>45905</v>
+      </c>
       <c r="U80" s="6"/>
       <c r="V80" s="20"/>
       <c r="W80" s="20"/>
@@ -8327,17 +8405,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="44"/>
-      <c r="AE80" s="45"/>
-      <c r="AF80" s="45"/>
-      <c r="AG80" s="45"/>
-      <c r="AH80" s="45"/>
-      <c r="AI80" s="46"/>
+      <c r="AD80" s="75"/>
+      <c r="AE80" s="76"/>
+      <c r="AF80" s="76"/>
+      <c r="AG80" s="76"/>
+      <c r="AH80" s="76"/>
+      <c r="AI80" s="77"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="36"/>
+      <c r="AN80" s="41"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8358,11 +8436,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="64"/>
-      <c r="BD80" s="64"/>
-    </row>
-    <row r="81" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I81" s="35">
+      <c r="BC80" s="35"/>
+      <c r="BD80" s="35"/>
+    </row>
+    <row r="81" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I81" s="40">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8419,7 +8497,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="35">
+      <c r="AN81" s="40">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8442,11 +8520,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="64"/>
-      <c r="BD81" s="64"/>
+      <c r="BC81" s="35"/>
+      <c r="BD81" s="35"/>
     </row>
     <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I82" s="36"/>
+      <c r="I82" s="41"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8455,14 +8533,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="47" t="s">
+      <c r="N82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="48"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="48"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="49"/>
+      <c r="O82" s="44"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="44"/>
+      <c r="R82" s="44"/>
+      <c r="S82" s="45"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8473,17 +8551,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="44"/>
-      <c r="AE82" s="45"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="45"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
+      <c r="AD82" s="75"/>
+      <c r="AE82" s="76"/>
+      <c r="AF82" s="76"/>
+      <c r="AG82" s="76"/>
+      <c r="AH82" s="76"/>
+      <c r="AI82" s="77"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="36"/>
+      <c r="AN82" s="41"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8492,23 +8570,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="47" t="s">
+      <c r="AS82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="48"/>
-      <c r="AU82" s="48"/>
-      <c r="AV82" s="48"/>
-      <c r="AW82" s="48"/>
-      <c r="AX82" s="49"/>
+      <c r="AT82" s="44"/>
+      <c r="AU82" s="44"/>
+      <c r="AV82" s="44"/>
+      <c r="AW82" s="44"/>
+      <c r="AX82" s="45"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="64"/>
-      <c r="BD82" s="64"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I83" s="35">
+      <c r="BC82" s="35"/>
+      <c r="BD82" s="35"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I83" s="40">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8539,10 +8617,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="35">
+      <c r="X83" s="40">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="56">
+      <c r="Y83" s="54">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8573,7 +8651,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="35">
+      <c r="AN83" s="40">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8602,11 +8680,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="64"/>
-      <c r="BD83" s="64"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I84" s="36"/>
+      <c r="BC83" s="35"/>
+      <c r="BD83" s="35"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I84" s="41"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8635,8 +8713,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="36"/>
-      <c r="Y84" s="57"/>
+      <c r="X84" s="41"/>
+      <c r="Y84" s="55"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8665,7 +8743,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="36"/>
+      <c r="AN84" s="41"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8692,8 +8770,8 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="64"/>
-      <c r="BD84" s="64"/>
+      <c r="BC84" s="35"/>
+      <c r="BD84" s="35"/>
     </row>
     <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I85" s="9">
@@ -8725,12 +8803,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="44"/>
-      <c r="AE85" s="45"/>
-      <c r="AF85" s="45"/>
-      <c r="AG85" s="45"/>
-      <c r="AH85" s="45"/>
-      <c r="AI85" s="46"/>
+      <c r="AD85" s="75"/>
+      <c r="AE85" s="76"/>
+      <c r="AF85" s="76"/>
+      <c r="AG85" s="76"/>
+      <c r="AH85" s="76"/>
+      <c r="AI85" s="77"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8758,11 +8836,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="64"/>
-      <c r="BD85" s="64"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I86" s="35">
+      <c r="BC85" s="35"/>
+      <c r="BD85" s="35"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I86" s="40">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8785,10 +8863,10 @@
       <c r="U86" s="6"/>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="35">
+      <c r="X86" s="40">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="50">
+      <c r="Y86" s="56">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8819,7 +8897,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="35">
+      <c r="AN86" s="40">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8842,11 +8920,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="64"/>
-      <c r="BD86" s="64"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I87" s="36"/>
+      <c r="BC86" s="35"/>
+      <c r="BD86" s="35"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I87" s="41"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8867,8 +8945,8 @@
       <c r="U87" s="6"/>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="36"/>
-      <c r="Y87" s="51"/>
+      <c r="X87" s="41"/>
+      <c r="Y87" s="57"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8897,7 +8975,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="36"/>
+      <c r="AN87" s="41"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8918,11 +8996,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="64"/>
-      <c r="BD87" s="64"/>
+      <c r="BC87" s="35"/>
+      <c r="BD87" s="35"/>
     </row>
     <row r="88" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I88" s="35" t="s">
+      <c r="I88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -8951,17 +9029,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="44"/>
-      <c r="AE88" s="45"/>
-      <c r="AF88" s="45"/>
-      <c r="AG88" s="45"/>
-      <c r="AH88" s="45"/>
-      <c r="AI88" s="46"/>
+      <c r="AD88" s="75"/>
+      <c r="AE88" s="76"/>
+      <c r="AF88" s="76"/>
+      <c r="AG88" s="76"/>
+      <c r="AH88" s="76"/>
+      <c r="AI88" s="77"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="35" t="s">
+      <c r="AN88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -8984,11 +9062,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="65"/>
-      <c r="BD88" s="65"/>
-    </row>
-    <row r="89" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I89" s="36"/>
+      <c r="BC88" s="36"/>
+      <c r="BD88" s="36"/>
+    </row>
+    <row r="89" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="I89" s="41"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -9009,10 +9087,10 @@
       <c r="U89" s="6"/>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="35" t="s">
+      <c r="X89" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="50">
+      <c r="Y89" s="56">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9043,7 +9121,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="36"/>
+      <c r="AN89" s="41"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9064,10 +9142,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="64"/>
-      <c r="BD89" s="64"/>
-    </row>
-    <row r="90" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC89" s="35"/>
+      <c r="BD89" s="35"/>
+    </row>
+    <row r="90" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9079,20 +9157,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="52" t="s">
+      <c r="N90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
+      <c r="O90" s="42"/>
+      <c r="P90" s="42"/>
+      <c r="Q90" s="42"/>
+      <c r="R90" s="42"/>
+      <c r="S90" s="42"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="36"/>
-      <c r="Y90" s="51"/>
+      <c r="X90" s="41"/>
+      <c r="Y90" s="57"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9132,20 +9210,20 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="52" t="s">
+      <c r="AS90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
+      <c r="AT90" s="42"/>
+      <c r="AU90" s="42"/>
+      <c r="AV90" s="42"/>
+      <c r="AW90" s="42"/>
+      <c r="AX90" s="42"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="64"/>
-      <c r="BD90" s="64"/>
+      <c r="BC90" s="35"/>
+      <c r="BD90" s="35"/>
     </row>
     <row r="91" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I91" s="20"/>
@@ -9169,12 +9247,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="44"/>
-      <c r="AE91" s="45"/>
-      <c r="AF91" s="45"/>
-      <c r="AG91" s="45"/>
-      <c r="AH91" s="45"/>
-      <c r="AI91" s="46"/>
+      <c r="AD91" s="75"/>
+      <c r="AE91" s="76"/>
+      <c r="AF91" s="76"/>
+      <c r="AG91" s="76"/>
+      <c r="AH91" s="76"/>
+      <c r="AI91" s="77"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9197,7 +9275,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9213,10 +9291,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="35">
+      <c r="X92" s="40">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="58">
+      <c r="Y92" s="60">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9265,7 +9343,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="9:56" x14ac:dyDescent="0.2">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9281,8 +9359,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="36"/>
-      <c r="Y93" s="59"/>
+      <c r="X93" s="41"/>
+      <c r="Y93" s="61"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9351,12 +9429,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="44"/>
-      <c r="AE94" s="45"/>
-      <c r="AF94" s="45"/>
-      <c r="AG94" s="45"/>
-      <c r="AH94" s="45"/>
-      <c r="AI94" s="46"/>
+      <c r="AD94" s="75"/>
+      <c r="AE94" s="76"/>
+      <c r="AF94" s="76"/>
+      <c r="AG94" s="76"/>
+      <c r="AH94" s="76"/>
+      <c r="AI94" s="77"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9395,10 +9473,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="35">
+      <c r="X95" s="40">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="60">
+      <c r="Y95" s="58">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9455,8 +9533,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="36"/>
-      <c r="Y96" s="61"/>
+      <c r="X96" s="41"/>
+      <c r="Y96" s="59"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9517,12 +9595,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="44"/>
-      <c r="AE97" s="45"/>
-      <c r="AF97" s="45"/>
-      <c r="AG97" s="45"/>
-      <c r="AH97" s="45"/>
-      <c r="AI97" s="46"/>
+      <c r="AD97" s="75"/>
+      <c r="AE97" s="76"/>
+      <c r="AF97" s="76"/>
+      <c r="AG97" s="76"/>
+      <c r="AH97" s="76"/>
+      <c r="AI97" s="77"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9627,12 +9705,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="44"/>
-      <c r="AE99" s="45"/>
-      <c r="AF99" s="45"/>
-      <c r="AG99" s="45"/>
-      <c r="AH99" s="45"/>
-      <c r="AI99" s="46"/>
+      <c r="AD99" s="75"/>
+      <c r="AE99" s="76"/>
+      <c r="AF99" s="76"/>
+      <c r="AG99" s="76"/>
+      <c r="AH99" s="76"/>
+      <c r="AI99" s="77"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9671,10 +9749,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="35">
+      <c r="X100" s="40">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="40">
+      <c r="Y100" s="52">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9695,7 +9773,9 @@
       <c r="AG100" s="38"/>
       <c r="AH100" s="38"/>
       <c r="AI100" s="39"/>
-      <c r="AJ100" s="19"/>
+      <c r="AJ100" s="8">
+        <v>45903</v>
+      </c>
       <c r="AK100" s="19"/>
       <c r="AL100" s="20"/>
       <c r="AM100" s="20"/>
@@ -9733,8 +9813,8 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="36"/>
-      <c r="Y101" s="41"/>
+      <c r="X101" s="41"/>
+      <c r="Y101" s="53"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
@@ -9753,7 +9833,9 @@
       <c r="AG101" s="38"/>
       <c r="AH101" s="38"/>
       <c r="AI101" s="39"/>
-      <c r="AJ101" s="19"/>
+      <c r="AJ101" s="8">
+        <v>45903</v>
+      </c>
       <c r="AK101" s="19"/>
       <c r="AL101" s="20"/>
       <c r="AM101" s="20"/>
@@ -9797,12 +9879,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="44"/>
-      <c r="AE102" s="45"/>
-      <c r="AF102" s="45"/>
-      <c r="AG102" s="45"/>
-      <c r="AH102" s="45"/>
-      <c r="AI102" s="46"/>
+      <c r="AD102" s="75"/>
+      <c r="AE102" s="76"/>
+      <c r="AF102" s="76"/>
+      <c r="AG102" s="76"/>
+      <c r="AH102" s="76"/>
+      <c r="AI102" s="77"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9907,12 +9989,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="44"/>
-      <c r="AE104" s="45"/>
-      <c r="AF104" s="45"/>
-      <c r="AG104" s="45"/>
-      <c r="AH104" s="45"/>
-      <c r="AI104" s="46"/>
+      <c r="AD104" s="75"/>
+      <c r="AE104" s="76"/>
+      <c r="AF104" s="76"/>
+      <c r="AG104" s="76"/>
+      <c r="AH104" s="76"/>
+      <c r="AI104" s="77"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -9952,10 +10034,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="35">
+      <c r="X105" s="40">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="50">
+      <c r="Y105" s="56">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -10012,8 +10094,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="36"/>
-      <c r="Y106" s="51"/>
+      <c r="X106" s="41"/>
+      <c r="Y106" s="57"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10074,12 +10156,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="44"/>
-      <c r="AE107" s="45"/>
-      <c r="AF107" s="45"/>
-      <c r="AG107" s="45"/>
-      <c r="AH107" s="45"/>
-      <c r="AI107" s="46"/>
+      <c r="AD107" s="75"/>
+      <c r="AE107" s="76"/>
+      <c r="AF107" s="76"/>
+      <c r="AG107" s="76"/>
+      <c r="AH107" s="76"/>
+      <c r="AI107" s="77"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10118,10 +10200,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="35">
+      <c r="X108" s="40">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="50">
+      <c r="Y108" s="56">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10132,14 +10214,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="47" t="s">
+      <c r="AD108" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="48"/>
-      <c r="AF108" s="48"/>
-      <c r="AG108" s="48"/>
-      <c r="AH108" s="48"/>
-      <c r="AI108" s="49"/>
+      <c r="AE108" s="44"/>
+      <c r="AF108" s="44"/>
+      <c r="AG108" s="44"/>
+      <c r="AH108" s="44"/>
+      <c r="AI108" s="45"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10178,8 +10260,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="36"/>
-      <c r="Y109" s="51"/>
+      <c r="X109" s="41"/>
+      <c r="Y109" s="57"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10240,12 +10322,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="44"/>
-      <c r="AE110" s="45"/>
-      <c r="AF110" s="45"/>
-      <c r="AG110" s="45"/>
-      <c r="AH110" s="45"/>
-      <c r="AI110" s="46"/>
+      <c r="AD110" s="75"/>
+      <c r="AE110" s="76"/>
+      <c r="AF110" s="76"/>
+      <c r="AG110" s="76"/>
+      <c r="AH110" s="76"/>
+      <c r="AI110" s="77"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10284,10 +10366,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="35">
+      <c r="X111" s="40">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="50">
+      <c r="Y111" s="56">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10298,14 +10380,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="47" t="s">
+      <c r="AD111" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="48"/>
-      <c r="AF111" s="48"/>
-      <c r="AG111" s="48"/>
-      <c r="AH111" s="48"/>
-      <c r="AI111" s="49"/>
+      <c r="AE111" s="44"/>
+      <c r="AF111" s="44"/>
+      <c r="AG111" s="44"/>
+      <c r="AH111" s="44"/>
+      <c r="AI111" s="45"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10344,8 +10426,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="36"/>
-      <c r="Y112" s="51"/>
+      <c r="X112" s="41"/>
+      <c r="Y112" s="57"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10406,12 +10488,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="44"/>
-      <c r="AE113" s="45"/>
-      <c r="AF113" s="45"/>
-      <c r="AG113" s="45"/>
-      <c r="AH113" s="45"/>
-      <c r="AI113" s="46"/>
+      <c r="AD113" s="75"/>
+      <c r="AE113" s="76"/>
+      <c r="AF113" s="76"/>
+      <c r="AG113" s="76"/>
+      <c r="AH113" s="76"/>
+      <c r="AI113" s="77"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10450,10 +10532,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="35">
+      <c r="X114" s="40">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="50">
+      <c r="Y114" s="56">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10510,8 +10592,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="36"/>
-      <c r="Y115" s="51"/>
+      <c r="X115" s="41"/>
+      <c r="Y115" s="57"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10572,12 +10654,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="44"/>
-      <c r="AE116" s="45"/>
-      <c r="AF116" s="45"/>
-      <c r="AG116" s="45"/>
-      <c r="AH116" s="45"/>
-      <c r="AI116" s="46"/>
+      <c r="AD116" s="75"/>
+      <c r="AE116" s="76"/>
+      <c r="AF116" s="76"/>
+      <c r="AG116" s="76"/>
+      <c r="AH116" s="76"/>
+      <c r="AI116" s="77"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10616,10 +10698,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="35">
+      <c r="X117" s="40">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="50">
+      <c r="Y117" s="56">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10632,15 +10714,17 @@
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="47" t="s">
+      <c r="AD117" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="48"/>
-      <c r="AF117" s="48"/>
-      <c r="AG117" s="48"/>
-      <c r="AH117" s="48"/>
-      <c r="AI117" s="49"/>
-      <c r="AJ117" s="19"/>
+      <c r="AE117" s="44"/>
+      <c r="AF117" s="44"/>
+      <c r="AG117" s="44"/>
+      <c r="AH117" s="44"/>
+      <c r="AI117" s="45"/>
+      <c r="AJ117" s="8">
+        <v>45905</v>
+      </c>
       <c r="AK117" s="19"/>
       <c r="AL117" s="20"/>
       <c r="AM117" s="20"/>
@@ -10678,8 +10762,8 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="36"/>
-      <c r="Y118" s="51"/>
+      <c r="X118" s="41"/>
+      <c r="Y118" s="57"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
@@ -10698,7 +10782,9 @@
       <c r="AG118" s="38"/>
       <c r="AH118" s="38"/>
       <c r="AI118" s="39"/>
-      <c r="AJ118" s="19"/>
+      <c r="AJ118" s="8">
+        <v>45905</v>
+      </c>
       <c r="AK118" s="19"/>
       <c r="AL118" s="20"/>
       <c r="AM118" s="20"/>
@@ -10742,12 +10828,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="44"/>
-      <c r="AE119" s="45"/>
-      <c r="AF119" s="45"/>
-      <c r="AG119" s="45"/>
-      <c r="AH119" s="45"/>
-      <c r="AI119" s="46"/>
+      <c r="AD119" s="75"/>
+      <c r="AE119" s="76"/>
+      <c r="AF119" s="76"/>
+      <c r="AG119" s="76"/>
+      <c r="AH119" s="76"/>
+      <c r="AI119" s="77"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10786,10 +10872,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="35">
+      <c r="X120" s="40">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="56">
+      <c r="Y120" s="54">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10846,8 +10932,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="36"/>
-      <c r="Y121" s="57"/>
+      <c r="X121" s="41"/>
+      <c r="Y121" s="55"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10856,14 +10942,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="47" t="s">
+      <c r="AD121" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="48"/>
-      <c r="AF121" s="48"/>
-      <c r="AG121" s="48"/>
-      <c r="AH121" s="48"/>
-      <c r="AI121" s="49"/>
+      <c r="AE121" s="44"/>
+      <c r="AF121" s="44"/>
+      <c r="AG121" s="44"/>
+      <c r="AH121" s="44"/>
+      <c r="AI121" s="45"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10908,12 +10994,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="44"/>
-      <c r="AE122" s="45"/>
-      <c r="AF122" s="45"/>
-      <c r="AG122" s="45"/>
-      <c r="AH122" s="45"/>
-      <c r="AI122" s="46"/>
+      <c r="AD122" s="75"/>
+      <c r="AE122" s="76"/>
+      <c r="AF122" s="76"/>
+      <c r="AG122" s="76"/>
+      <c r="AH122" s="76"/>
+      <c r="AI122" s="77"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -10936,7 +11022,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -10952,10 +11038,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="35">
+      <c r="X123" s="40">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="42">
+      <c r="Y123" s="46">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -11004,7 +11090,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11020,8 +11106,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="36"/>
-      <c r="Y124" s="43"/>
+      <c r="X124" s="41"/>
+      <c r="Y124" s="47"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11090,12 +11176,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="44"/>
-      <c r="AE125" s="45"/>
-      <c r="AF125" s="45"/>
-      <c r="AG125" s="45"/>
-      <c r="AH125" s="45"/>
-      <c r="AI125" s="46"/>
+      <c r="AD125" s="75"/>
+      <c r="AE125" s="76"/>
+      <c r="AF125" s="76"/>
+      <c r="AG125" s="76"/>
+      <c r="AH125" s="76"/>
+      <c r="AI125" s="77"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11137,7 +11223,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="42">
+      <c r="Y126" s="46">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11195,17 +11281,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="43"/>
+      <c r="Y127" s="47"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="44"/>
-      <c r="AE127" s="45"/>
-      <c r="AF127" s="45"/>
-      <c r="AG127" s="45"/>
-      <c r="AH127" s="45"/>
-      <c r="AI127" s="46"/>
+      <c r="AD127" s="75"/>
+      <c r="AE127" s="76"/>
+      <c r="AF127" s="76"/>
+      <c r="AG127" s="76"/>
+      <c r="AH127" s="76"/>
+      <c r="AI127" s="77"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11244,10 +11330,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="35">
+      <c r="X128" s="40">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="40">
+      <c r="Y128" s="52">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11304,8 +11390,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="36"/>
-      <c r="Y129" s="41"/>
+      <c r="X129" s="41"/>
+      <c r="Y129" s="53"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11366,12 +11452,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="44"/>
-      <c r="AE130" s="45"/>
-      <c r="AF130" s="45"/>
-      <c r="AG130" s="45"/>
-      <c r="AH130" s="45"/>
-      <c r="AI130" s="46"/>
+      <c r="AD130" s="75"/>
+      <c r="AE130" s="76"/>
+      <c r="AF130" s="76"/>
+      <c r="AG130" s="76"/>
+      <c r="AH130" s="76"/>
+      <c r="AI130" s="77"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11410,10 +11496,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="35" t="s">
+      <c r="X131" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="42">
+      <c r="Y131" s="46">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11470,8 +11556,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="36"/>
-      <c r="Y132" s="43"/>
+      <c r="X132" s="41"/>
+      <c r="Y132" s="47"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11532,12 +11618,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="44"/>
-      <c r="AE133" s="45"/>
-      <c r="AF133" s="45"/>
-      <c r="AG133" s="45"/>
-      <c r="AH133" s="45"/>
-      <c r="AI133" s="46"/>
+      <c r="AD133" s="75"/>
+      <c r="AE133" s="76"/>
+      <c r="AF133" s="76"/>
+      <c r="AG133" s="76"/>
+      <c r="AH133" s="76"/>
+      <c r="AI133" s="77"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11590,14 +11676,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="52" t="s">
+      <c r="AD134" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="52"/>
-      <c r="AF134" s="52"/>
-      <c r="AG134" s="52"/>
-      <c r="AH134" s="52"/>
-      <c r="AI134" s="52"/>
+      <c r="AE134" s="42"/>
+      <c r="AF134" s="42"/>
+      <c r="AG134" s="42"/>
+      <c r="AH134" s="42"/>
+      <c r="AI134" s="42"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11635,8 +11721,8 @@
     <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G153" s="67"/>
-      <c r="H153" s="67"/>
+      <c r="G153" s="89"/>
+      <c r="H153" s="89"/>
     </row>
     <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -11669,70 +11755,486 @@
     <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="X131:X132"/>
+    <mergeCell ref="X128:X129"/>
+    <mergeCell ref="AD129:AI129"/>
+    <mergeCell ref="AD132:AI132"/>
+    <mergeCell ref="Y128:Y129"/>
+    <mergeCell ref="Y131:Y132"/>
+    <mergeCell ref="AD115:AI115"/>
+    <mergeCell ref="AD116:AI116"/>
+    <mergeCell ref="AD117:AI117"/>
+    <mergeCell ref="AD118:AI118"/>
+    <mergeCell ref="AD119:AI119"/>
+    <mergeCell ref="AD120:AI120"/>
+    <mergeCell ref="AD109:AI109"/>
+    <mergeCell ref="AD110:AI110"/>
+    <mergeCell ref="AD111:AI111"/>
+    <mergeCell ref="AD104:AI104"/>
+    <mergeCell ref="AD105:AI105"/>
+    <mergeCell ref="AD106:AI106"/>
+    <mergeCell ref="X108:X109"/>
+    <mergeCell ref="Y108:Y109"/>
+    <mergeCell ref="X105:X106"/>
+    <mergeCell ref="AD88:AI88"/>
+    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
     <mergeCell ref="AS85:AX85"/>
     <mergeCell ref="AN86:AN87"/>
     <mergeCell ref="AS86:AX86"/>
@@ -11757,481 +12259,61 @@
     <mergeCell ref="BC33:BD33"/>
     <mergeCell ref="BC34:BD34"/>
     <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="X131:X132"/>
-    <mergeCell ref="X128:X129"/>
-    <mergeCell ref="AD129:AI129"/>
-    <mergeCell ref="AD132:AI132"/>
-    <mergeCell ref="Y128:Y129"/>
-    <mergeCell ref="Y131:Y132"/>
-    <mergeCell ref="AD115:AI115"/>
-    <mergeCell ref="AD116:AI116"/>
-    <mergeCell ref="AD117:AI117"/>
-    <mergeCell ref="AD118:AI118"/>
-    <mergeCell ref="AD119:AI119"/>
-    <mergeCell ref="AD120:AI120"/>
-    <mergeCell ref="AD109:AI109"/>
-    <mergeCell ref="AD110:AI110"/>
-    <mergeCell ref="AD111:AI111"/>
-    <mergeCell ref="AD104:AI104"/>
-    <mergeCell ref="AD105:AI105"/>
-    <mergeCell ref="AD106:AI106"/>
-    <mergeCell ref="X108:X109"/>
-    <mergeCell ref="Y108:Y109"/>
-    <mergeCell ref="X105:X106"/>
-    <mergeCell ref="AD88:AI88"/>
-    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uandresbelloedu-my.sharepoint.com/personal/c_vidalgallardo_uandresbello_edu/Documents/Documents/GitHub/ING-DE-SOFTWARE/INCREMENTO2/Excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A795F0-7A33-48E4-A6BF-3D609E066F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{44A795F0-7A33-48E4-A6BF-3D609E066F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93A6781B-0202-4E3C-96EA-7F2F680B86A3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="218">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -691,6 +688,9 @@
   </si>
   <si>
     <t>El sistema debe permitir la edición o actualización de cambios realizados a los turnos de los trabajadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permitir que el sistema filtre datos de empleados . </t>
   </si>
 </sst>
 </file>
@@ -1177,11 +1177,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1192,17 +1192,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1213,77 +1306,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1300,15 +1330,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1318,40 +1339,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1688,109 +1688,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="G2:BD230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="8" max="8" width="8.375" customWidth="1"/>
-    <col min="9" max="9" width="13.125" customWidth="1"/>
-    <col min="10" max="10" width="105.875" customWidth="1"/>
-    <col min="11" max="11" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" customWidth="1"/>
+    <col min="10" max="10" width="105.86328125" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.875" customWidth="1"/>
-    <col min="20" max="20" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.86328125" customWidth="1"/>
+    <col min="20" max="20" width="13.1328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11.125" customWidth="1"/>
-    <col min="23" max="23" width="10.625" customWidth="1"/>
-    <col min="24" max="24" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="104.25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.25" customWidth="1"/>
+    <col min="22" max="22" width="11.1328125" customWidth="1"/>
+    <col min="23" max="23" width="10.59765625" customWidth="1"/>
+    <col min="24" max="24" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.86328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="104.265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.265625" customWidth="1"/>
     <col min="35" max="35" width="37" customWidth="1"/>
-    <col min="36" max="36" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.875" customWidth="1"/>
-    <col min="39" max="39" width="6.875" customWidth="1"/>
-    <col min="40" max="40" width="13.625" customWidth="1"/>
-    <col min="41" max="41" width="105.625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.86328125" customWidth="1"/>
+    <col min="39" max="39" width="6.86328125" customWidth="1"/>
+    <col min="40" max="40" width="13.59765625" customWidth="1"/>
+    <col min="41" max="41" width="105.59765625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="45.875" customWidth="1"/>
-    <col min="51" max="51" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16373" max="16373" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="45.86328125" customWidth="1"/>
+    <col min="51" max="51" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16373" max="16373" width="9.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I2" s="82" t="s">
+    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="76" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="72" t="s">
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="76" t="s">
+      <c r="U2" s="83"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="78"/>
-      <c r="AJ2" s="71" t="s">
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="71"/>
-      <c r="AN2" s="74" t="s">
+      <c r="AK2" s="81"/>
+      <c r="AN2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="75" t="s">
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AQ2" s="84"/>
+      <c r="AR2" s="84"/>
+      <c r="AS2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="75"/>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="75"/>
-      <c r="AY2" s="71" t="s">
+      <c r="AT2" s="85"/>
+      <c r="AU2" s="85"/>
+      <c r="AV2" s="85"/>
+      <c r="AW2" s="85"/>
+      <c r="AX2" s="85"/>
+      <c r="AY2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71" t="s">
+      <c r="BB2" s="81"/>
+      <c r="BC2" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="71"/>
-    </row>
-    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BD2" s="81"/>
+    </row>
+    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1806,12 +1805,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="85"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="87"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="74"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1836,12 +1835,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="81"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="88"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1863,12 +1862,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="75"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1881,13 +1880,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="71" t="s">
+      <c r="BC3" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="71"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I4" s="92">
+      <c r="BD3" s="81"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="62">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1916,10 +1915,10 @@
       <c r="U4" s="6"/>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="35">
+      <c r="X4" s="40">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="88">
+      <c r="Y4" s="50">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1948,7 +1947,7 @@
       <c r="AK4" s="6"/>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="68">
+      <c r="AN4" s="90">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1977,11 +1976,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I5" s="69"/>
+      <c r="BC4" s="35"/>
+      <c r="BD4" s="35"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I5" s="63"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1994,7 +1993,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="N5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2008,8 +2007,8 @@
       <c r="U5" s="6"/>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="89"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="51"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2022,21 +2021,21 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="91" t="s">
+      <c r="AD5" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46"/>
+      <c r="AE5" s="76"/>
+      <c r="AF5" s="76"/>
+      <c r="AG5" s="76"/>
+      <c r="AH5" s="76"/>
+      <c r="AI5" s="77"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
       <c r="AK5" s="6"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="69"/>
+      <c r="AN5" s="63"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2049,7 +2048,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="66" t="s">
+      <c r="AS5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2063,11 +2062,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="46"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I6" s="70"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="77"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I6" s="64"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2094,8 +2093,8 @@
       <c r="U6" s="6"/>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="90"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="79"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2108,21 +2107,21 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AD6" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="77"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
       <c r="AK6" s="6"/>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="70"/>
+      <c r="AN6" s="64"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2149,11 +2148,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="64"/>
-      <c r="BD6" s="64"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I7" s="35">
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="35"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I7" s="40">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2188,17 +2187,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="45"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="76"/>
+      <c r="AG7" s="76"/>
+      <c r="AH7" s="76"/>
+      <c r="AI7" s="77"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="35">
+      <c r="AN7" s="40">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2227,11 +2226,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I8" s="36"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I8" s="41"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2258,10 +2257,10 @@
       <c r="U8" s="6"/>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="52">
+      <c r="X8" s="42">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="88">
+      <c r="Y8" s="50">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2290,7 +2289,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="55"/>
+      <c r="AN8" s="48"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2317,11 +2316,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="64"/>
-      <c r="BD8" s="64"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I9" s="35">
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="35"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2350,8 +2349,8 @@
       <c r="U9" s="6"/>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="89"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="51"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2378,7 +2377,7 @@
       <c r="AK9" s="6"/>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="35">
+      <c r="AN9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2407,11 +2406,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="64"/>
-      <c r="BD9" s="64"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I10" s="36"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="35"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I10" s="41"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2444,17 +2443,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="77"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="55"/>
+      <c r="AN10" s="48"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2481,11 +2480,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="64"/>
-      <c r="BD10" s="64"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I11" s="35">
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="35"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2500,7 +2499,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="66" t="s">
+      <c r="N11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2514,10 +2513,10 @@
       <c r="U11" s="6"/>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="52">
+      <c r="X11" s="42">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="42">
+      <c r="Y11" s="46">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2546,7 +2545,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="35">
+      <c r="AN11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2561,7 +2560,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="66" t="s">
+      <c r="AS11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2575,11 +2574,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="64"/>
-      <c r="BD11" s="64"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I12" s="55"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="35"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I12" s="48"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2592,7 +2591,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2606,8 +2605,8 @@
       <c r="U12" s="6"/>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="43"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="47"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2634,7 +2633,7 @@
       <c r="AK12" s="6"/>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="55"/>
+      <c r="AN12" s="48"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2647,7 +2646,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="66" t="s">
+      <c r="AS12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2661,11 +2660,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="64"/>
-      <c r="BD12" s="64"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I13" s="36"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I13" s="41"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2698,17 +2697,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="45"/>
-      <c r="AF13" s="45"/>
-      <c r="AG13" s="45"/>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="46"/>
+      <c r="AD13" s="75"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="77"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="36"/>
+      <c r="AN13" s="41"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2735,11 +2734,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="64"/>
-      <c r="BD13" s="64"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I14" s="35">
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="35"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I14" s="40">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2768,10 +2767,10 @@
       <c r="U14" s="6"/>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="52">
+      <c r="X14" s="42">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="40">
+      <c r="Y14" s="52">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2786,7 +2785,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="66" t="s">
+      <c r="AD14" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2800,7 +2799,7 @@
       <c r="AK14" s="6"/>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="35">
+      <c r="AN14" s="40">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2829,11 +2828,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="64"/>
-      <c r="BD14" s="64"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I15" s="55"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="35"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I15" s="48"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2860,8 +2859,8 @@
       <c r="U15" s="6"/>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="62"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="78"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2874,7 +2873,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="66" t="s">
+      <c r="AD15" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2888,7 +2887,7 @@
       <c r="AK15" s="6"/>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="55"/>
+      <c r="AN15" s="48"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2915,11 +2914,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="64"/>
-      <c r="BD15" s="64"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I16" s="36"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="35"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I16" s="41"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2946,8 +2945,8 @@
       <c r="U16" s="6"/>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="41"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="53"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2974,7 +2973,7 @@
       <c r="AK16" s="6"/>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="55"/>
+      <c r="AN16" s="48"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3001,11 +3000,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="65"/>
-      <c r="BD16" s="65"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I17" s="53">
+      <c r="BC16" s="36"/>
+      <c r="BD16" s="36"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I17" s="92">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3040,17 +3039,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="46"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="77"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="93">
+      <c r="AN17" s="49">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3079,11 +3078,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="64"/>
-      <c r="BD17" s="64"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I18" s="54"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="35"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I18" s="93"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3110,10 +3109,10 @@
       <c r="U18" s="6"/>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="52">
+      <c r="X18" s="42">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="40">
+      <c r="Y18" s="52">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3142,7 +3141,7 @@
       <c r="AK18" s="6"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="93"/>
+      <c r="AN18" s="49"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3169,11 +3168,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="64"/>
-      <c r="BD18" s="64"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I19" s="35" t="s">
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="35"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3196,8 +3195,8 @@
       <c r="U19" s="6"/>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="62"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="78"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3224,7 +3223,7 @@
       <c r="AK19" s="6"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="35" t="s">
+      <c r="AN19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3247,11 +3246,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="64"/>
-      <c r="BD19" s="64"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I20" s="36"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I20" s="41"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3272,8 +3271,8 @@
       <c r="U20" s="7"/>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="52"/>
-      <c r="Y20" s="41"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="53"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3300,7 +3299,7 @@
       <c r="AK20" s="7"/>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="36"/>
+      <c r="AN20" s="41"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3321,11 +3320,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="64"/>
-      <c r="BD20" s="64"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I21" s="35">
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="35"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I21" s="40">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3362,17 +3361,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="46"/>
+      <c r="AD21" s="75"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="77"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="35">
+      <c r="AN21" s="40">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3403,11 +3402,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="64"/>
-      <c r="BD21" s="64"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I22" s="55"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="35"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I22" s="48"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3436,10 +3435,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="93">
+      <c r="X22" s="49">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="40">
+      <c r="Y22" s="52">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3468,7 +3467,7 @@
       <c r="AK22" s="7"/>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="55"/>
+      <c r="AN22" s="48"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3497,11 +3496,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I23" s="36"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="35"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I23" s="41"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3530,8 +3529,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="93"/>
-      <c r="Y23" s="41"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="53"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3558,7 +3557,7 @@
       <c r="AK23" s="7"/>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="36"/>
+      <c r="AN23" s="41"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3587,11 +3586,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="64"/>
-      <c r="BD23" s="64"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I24" s="35" t="s">
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="35"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3628,17 +3627,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="44"/>
-      <c r="AE24" s="45"/>
-      <c r="AF24" s="45"/>
-      <c r="AG24" s="45"/>
-      <c r="AH24" s="45"/>
-      <c r="AI24" s="46"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="76"/>
+      <c r="AF24" s="76"/>
+      <c r="AG24" s="76"/>
+      <c r="AH24" s="76"/>
+      <c r="AI24" s="77"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="35" t="s">
+      <c r="AN24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3669,11 +3668,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="64"/>
-      <c r="BD24" s="64"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I25" s="36"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="35"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I25" s="41"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3702,10 +3701,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="35" t="s">
+      <c r="X25" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="42">
+      <c r="Y25" s="46">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3728,7 +3727,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="36"/>
+      <c r="AN25" s="41"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3757,11 +3756,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="64"/>
-      <c r="BD25" s="64"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I26" s="35" t="s">
+      <c r="BC25" s="35"/>
+      <c r="BD25" s="35"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3792,8 +3791,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="43"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="47"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3814,7 +3813,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="35" t="s">
+      <c r="AN26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3845,11 +3844,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="64"/>
-      <c r="BD26" s="64"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I27" s="36"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I27" s="41"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3884,17 +3883,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="44"/>
-      <c r="AE27" s="45"/>
-      <c r="AF27" s="45"/>
-      <c r="AG27" s="45"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="46"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="77"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="36"/>
+      <c r="AN27" s="41"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3923,11 +3922,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="64"/>
-      <c r="BD27" s="64"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I28" s="35" t="s">
+      <c r="BC27" s="35"/>
+      <c r="BD27" s="35"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3958,10 +3957,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="35">
+      <c r="X28" s="40">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="58">
+      <c r="Y28" s="60">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -3992,7 +3991,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="35" t="s">
+      <c r="AN28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4023,11 +4022,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="65"/>
-      <c r="BD28" s="65"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I29" s="55"/>
+      <c r="BC28" s="36"/>
+      <c r="BD28" s="36"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I29" s="48"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4056,8 +4055,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="63"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="91"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4086,7 +4085,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="55"/>
+      <c r="AN29" s="48"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4115,11 +4114,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="64"/>
-      <c r="BD29" s="64"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I30" s="36"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I30" s="41"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4148,8 +4147,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="59"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="61"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4178,7 +4177,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="36"/>
+      <c r="AN30" s="41"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4207,11 +4206,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="64"/>
-      <c r="BD30" s="64"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I31" s="35">
+      <c r="BC30" s="35"/>
+      <c r="BD30" s="35"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I31" s="40">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4248,17 +4247,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="44"/>
-      <c r="AE31" s="45"/>
-      <c r="AF31" s="45"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="45"/>
-      <c r="AI31" s="46"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="77"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="35">
+      <c r="AN31" s="40">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4289,11 +4288,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="64"/>
-      <c r="BD31" s="64"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I32" s="36"/>
+      <c r="BC31" s="35"/>
+      <c r="BD31" s="35"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I32" s="41"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4322,10 +4321,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="35">
+      <c r="X32" s="40">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="58">
+      <c r="Y32" s="60">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4356,7 +4355,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="36"/>
+      <c r="AN32" s="41"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4385,11 +4384,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="64"/>
-      <c r="BD32" s="64"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I33" s="35">
+      <c r="BC32" s="35"/>
+      <c r="BD32" s="35"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I33" s="40">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4420,8 +4419,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="59"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="61"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4450,7 +4449,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="35">
+      <c r="AN33" s="40">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4481,11 +4480,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="64"/>
-      <c r="BD33" s="64"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I34" s="36"/>
+      <c r="BC33" s="35"/>
+      <c r="BD33" s="35"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I34" s="41"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4520,17 +4519,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="44"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="46"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="36"/>
+      <c r="AN34" s="41"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4559,11 +4558,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="64"/>
-      <c r="BD34" s="64"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I35" s="35">
+      <c r="BC34" s="35"/>
+      <c r="BD34" s="35"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4594,10 +4593,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="35" t="s">
+      <c r="X35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="42">
+      <c r="Y35" s="46">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4628,7 +4627,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="35">
+      <c r="AN35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4659,11 +4658,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="64"/>
-      <c r="BD35" s="64"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I36" s="36"/>
+      <c r="BC35" s="35"/>
+      <c r="BD35" s="35"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I36" s="41"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4692,8 +4691,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="43"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="47"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4722,7 +4721,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="36"/>
+      <c r="AN36" s="41"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4751,11 +4750,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="64"/>
-      <c r="BD36" s="64"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I37" s="35">
+      <c r="BC36" s="35"/>
+      <c r="BD36" s="35"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4792,17 +4791,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="44"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="46"/>
+      <c r="AD37" s="75"/>
+      <c r="AE37" s="76"/>
+      <c r="AF37" s="76"/>
+      <c r="AG37" s="76"/>
+      <c r="AH37" s="76"/>
+      <c r="AI37" s="77"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="35">
+      <c r="AN37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4833,11 +4832,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="64"/>
-      <c r="BD37" s="64"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I38" s="36"/>
+      <c r="BC37" s="35"/>
+      <c r="BD37" s="35"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I38" s="41"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4866,10 +4865,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="35" t="s">
+      <c r="X38" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="40">
+      <c r="Y38" s="52">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4900,7 +4899,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="36"/>
+      <c r="AN38" s="41"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4929,10 +4928,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="64"/>
-      <c r="BD38" s="64"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC38" s="35"/>
+      <c r="BD38" s="35"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -4964,8 +4963,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="62"/>
+      <c r="X39" s="48"/>
+      <c r="Y39" s="78"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5025,11 +5024,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="64"/>
-      <c r="BD39" s="64"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I40" s="35">
+      <c r="BC39" s="35"/>
+      <c r="BD39" s="35"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5060,8 +5059,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="36"/>
-      <c r="Y40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="53"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5090,7 +5089,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="35">
+      <c r="AN40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5121,11 +5120,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="65"/>
-      <c r="BD40" s="65"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I41" s="36"/>
+      <c r="BC40" s="36"/>
+      <c r="BD40" s="36"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I41" s="41"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5138,14 +5137,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="47" t="s">
+      <c r="N41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="49"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="45"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5160,17 +5159,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="44"/>
-      <c r="AE41" s="45"/>
-      <c r="AF41" s="45"/>
-      <c r="AG41" s="45"/>
-      <c r="AH41" s="45"/>
-      <c r="AI41" s="46"/>
+      <c r="AD41" s="75"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="76"/>
+      <c r="AG41" s="76"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="77"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="36"/>
+      <c r="AN41" s="41"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5183,14 +5182,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="47" t="s">
+      <c r="AS41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="48"/>
-      <c r="AU41" s="48"/>
-      <c r="AV41" s="48"/>
-      <c r="AW41" s="48"/>
-      <c r="AX41" s="49"/>
+      <c r="AT41" s="44"/>
+      <c r="AU41" s="44"/>
+      <c r="AV41" s="44"/>
+      <c r="AW41" s="44"/>
+      <c r="AX41" s="45"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5199,10 +5198,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="64"/>
-      <c r="BD41" s="64"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC41" s="35"/>
+      <c r="BD41" s="35"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5234,10 +5233,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="35">
+      <c r="X42" s="40">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="40">
+      <c r="Y42" s="52">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5299,11 +5298,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="64"/>
-      <c r="BD42" s="64"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I43" s="35">
+      <c r="BC42" s="35"/>
+      <c r="BD42" s="35"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I43" s="40">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5334,8 +5333,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="53"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5364,7 +5363,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="35">
+      <c r="AN43" s="40">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5395,11 +5394,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="64"/>
-      <c r="BD43" s="64"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I44" s="36"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I44" s="41"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5434,17 +5433,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="44"/>
-      <c r="AE44" s="45"/>
-      <c r="AF44" s="45"/>
-      <c r="AG44" s="45"/>
-      <c r="AH44" s="45"/>
-      <c r="AI44" s="46"/>
+      <c r="AD44" s="75"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="76"/>
+      <c r="AG44" s="76"/>
+      <c r="AH44" s="76"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="36"/>
+      <c r="AN44" s="41"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5473,10 +5472,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="64"/>
-      <c r="BD44" s="64"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5508,10 +5507,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="35">
+      <c r="X45" s="40">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="58">
+      <c r="Y45" s="60">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5573,11 +5572,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="64"/>
-      <c r="BD45" s="64"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I46" s="35" t="s">
+      <c r="BC45" s="35"/>
+      <c r="BD45" s="35"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5608,8 +5607,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="59"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="61"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5638,7 +5637,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="35" t="s">
+      <c r="AN46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5669,11 +5668,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="64"/>
-      <c r="BD46" s="64"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I47" s="36"/>
+      <c r="BC46" s="35"/>
+      <c r="BD46" s="35"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I47" s="41"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5708,17 +5707,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="45"/>
-      <c r="AF47" s="45"/>
-      <c r="AG47" s="45"/>
-      <c r="AH47" s="45"/>
-      <c r="AI47" s="46"/>
+      <c r="AD47" s="75"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="76"/>
+      <c r="AG47" s="76"/>
+      <c r="AH47" s="76"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="36"/>
+      <c r="AN47" s="41"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5747,11 +5746,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="64"/>
-      <c r="BD47" s="64"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I48" s="35" t="s">
+      <c r="BC47" s="35"/>
+      <c r="BD47" s="35"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5782,10 +5781,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="35">
+      <c r="X48" s="40">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="42">
+      <c r="Y48" s="46">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5816,7 +5815,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="35" t="s">
+      <c r="AN48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5847,11 +5846,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="64"/>
-      <c r="BD48" s="64"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I49" s="36"/>
+      <c r="BC48" s="35"/>
+      <c r="BD48" s="35"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I49" s="41"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5880,8 +5879,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="43"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="47"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5910,7 +5909,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="36"/>
+      <c r="AN49" s="41"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5939,12 +5938,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="64"/>
-      <c r="BD49" s="64"/>
-    </row>
-    <row r="50" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="BC49" s="35"/>
+      <c r="BD49" s="35"/>
+    </row>
+    <row r="50" spans="8:56" x14ac:dyDescent="0.45">
       <c r="H50" s="10"/>
-      <c r="I50" s="35">
+      <c r="I50" s="40">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -5959,14 +5958,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="47" t="s">
+      <c r="N50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-      <c r="R50" s="48"/>
-      <c r="S50" s="49"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="45"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -5981,17 +5980,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="45"/>
-      <c r="AG50" s="45"/>
-      <c r="AH50" s="45"/>
-      <c r="AI50" s="46"/>
+      <c r="AD50" s="75"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="76"/>
+      <c r="AH50" s="76"/>
+      <c r="AI50" s="77"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="35">
+      <c r="AN50" s="40">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6002,23 +6001,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="47" t="s">
+      <c r="AS50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="48"/>
-      <c r="AU50" s="48"/>
-      <c r="AV50" s="48"/>
-      <c r="AW50" s="48"/>
-      <c r="AX50" s="49"/>
+      <c r="AT50" s="44"/>
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="45"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="64"/>
-      <c r="BD50" s="64"/>
-    </row>
-    <row r="51" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I51" s="36"/>
+      <c r="BC50" s="35"/>
+      <c r="BD50" s="35"/>
+    </row>
+    <row r="51" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I51" s="41"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6031,14 +6030,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="47" t="s">
+      <c r="N51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="49"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="45"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6047,10 +6046,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="35">
+      <c r="X51" s="40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="40">
+      <c r="Y51" s="52">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6081,7 +6080,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="36"/>
+      <c r="AN51" s="41"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6090,23 +6089,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="47" t="s">
+      <c r="AS51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="48"/>
-      <c r="AU51" s="48"/>
-      <c r="AV51" s="48"/>
-      <c r="AW51" s="48"/>
-      <c r="AX51" s="49"/>
+      <c r="AT51" s="44"/>
+      <c r="AU51" s="44"/>
+      <c r="AV51" s="44"/>
+      <c r="AW51" s="44"/>
+      <c r="AX51" s="45"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="64"/>
-      <c r="BD51" s="64"/>
-    </row>
-    <row r="52" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I52" s="35">
+      <c r="BC51" s="35"/>
+      <c r="BD51" s="35"/>
+    </row>
+    <row r="52" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I52" s="40">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6137,8 +6136,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="36"/>
-      <c r="Y52" s="41"/>
+      <c r="X52" s="41"/>
+      <c r="Y52" s="53"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6167,7 +6166,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="35">
+      <c r="AN52" s="40">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6190,11 +6189,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="65"/>
-      <c r="BD52" s="65"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I53" s="36"/>
+      <c r="BC52" s="36"/>
+      <c r="BD52" s="36"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I53" s="41"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6229,17 +6228,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="44"/>
-      <c r="AE53" s="45"/>
-      <c r="AF53" s="45"/>
-      <c r="AG53" s="45"/>
-      <c r="AH53" s="45"/>
-      <c r="AI53" s="46"/>
+      <c r="AD53" s="75"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="76"/>
+      <c r="AG53" s="76"/>
+      <c r="AH53" s="76"/>
+      <c r="AI53" s="77"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="36"/>
+      <c r="AN53" s="41"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6260,11 +6259,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="64"/>
-      <c r="BD53" s="64"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I54" s="35">
+      <c r="BC53" s="35"/>
+      <c r="BD53" s="35"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I54" s="40">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6329,7 +6328,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="35">
+      <c r="AN54" s="40">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6352,11 +6351,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="64"/>
-      <c r="BD54" s="64"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I55" s="36"/>
+      <c r="BC54" s="35"/>
+      <c r="BD54" s="35"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I55" s="41"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6391,17 +6390,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="44"/>
-      <c r="AE55" s="45"/>
-      <c r="AF55" s="45"/>
-      <c r="AG55" s="45"/>
-      <c r="AH55" s="45"/>
-      <c r="AI55" s="46"/>
+      <c r="AD55" s="75"/>
+      <c r="AE55" s="76"/>
+      <c r="AF55" s="76"/>
+      <c r="AG55" s="76"/>
+      <c r="AH55" s="76"/>
+      <c r="AI55" s="77"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="36"/>
+      <c r="AN55" s="41"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6422,10 +6421,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="64"/>
-      <c r="BD55" s="64"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC55" s="35"/>
+      <c r="BD55" s="35"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6457,10 +6456,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="35">
+      <c r="X56" s="40">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="58">
+      <c r="Y56" s="60">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6514,11 +6513,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="64"/>
-      <c r="BD56" s="64"/>
-    </row>
-    <row r="57" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I57" s="35">
+      <c r="BC56" s="35"/>
+      <c r="BD56" s="35"/>
+    </row>
+    <row r="57" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I57" s="40">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6549,8 +6548,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="36"/>
-      <c r="Y57" s="59"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="61"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6561,14 +6560,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="47" t="s">
+      <c r="AD57" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="48"/>
-      <c r="AF57" s="48"/>
-      <c r="AG57" s="48"/>
-      <c r="AH57" s="48"/>
-      <c r="AI57" s="49"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="44"/>
+      <c r="AI57" s="45"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6577,7 +6576,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="35">
+      <c r="AN57" s="40">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6600,11 +6599,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="64"/>
-      <c r="BD57" s="64"/>
-    </row>
-    <row r="58" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I58" s="36"/>
+      <c r="BC57" s="35"/>
+      <c r="BD57" s="35"/>
+    </row>
+    <row r="58" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I58" s="41"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6639,17 +6638,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="44"/>
-      <c r="AE58" s="45"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="45"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
+      <c r="AD58" s="75"/>
+      <c r="AE58" s="76"/>
+      <c r="AF58" s="76"/>
+      <c r="AG58" s="76"/>
+      <c r="AH58" s="76"/>
+      <c r="AI58" s="77"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="36"/>
+      <c r="AN58" s="41"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6670,11 +6669,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="64"/>
-      <c r="BD58" s="64"/>
-    </row>
-    <row r="59" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I59" s="35">
+      <c r="BC58" s="35"/>
+      <c r="BD58" s="35"/>
+    </row>
+    <row r="59" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I59" s="40">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6739,7 +6738,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="35">
+      <c r="AN59" s="40">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6762,11 +6761,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="64"/>
-      <c r="BD59" s="64"/>
-    </row>
-    <row r="60" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I60" s="36"/>
+      <c r="BC59" s="35"/>
+      <c r="BD59" s="35"/>
+    </row>
+    <row r="60" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I60" s="41"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6801,17 +6800,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="44"/>
-      <c r="AE60" s="45"/>
-      <c r="AF60" s="45"/>
-      <c r="AG60" s="45"/>
-      <c r="AH60" s="45"/>
-      <c r="AI60" s="46"/>
+      <c r="AD60" s="75"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="77"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="36"/>
+      <c r="AN60" s="41"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6832,11 +6831,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="64"/>
-      <c r="BD60" s="64"/>
-    </row>
-    <row r="61" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I61" s="35" t="s">
+      <c r="BC60" s="35"/>
+      <c r="BD60" s="35"/>
+    </row>
+    <row r="61" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6867,10 +6866,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="35">
+      <c r="X61" s="40">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="60">
+      <c r="Y61" s="58">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6901,7 +6900,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="35" t="s">
+      <c r="AN61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6924,11 +6923,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="64"/>
-      <c r="BD61" s="64"/>
-    </row>
-    <row r="62" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I62" s="36"/>
+      <c r="BC61" s="35"/>
+      <c r="BD61" s="35"/>
+    </row>
+    <row r="62" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I62" s="41"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -6957,8 +6956,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="61"/>
+      <c r="X62" s="41"/>
+      <c r="Y62" s="59"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -6987,7 +6986,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="36"/>
+      <c r="AN62" s="41"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7008,11 +7007,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="64"/>
-      <c r="BD62" s="64"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I63" s="35">
+      <c r="BC62" s="35"/>
+      <c r="BD62" s="35"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I63" s="40">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7049,17 +7048,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="44"/>
-      <c r="AE63" s="45"/>
-      <c r="AF63" s="45"/>
-      <c r="AG63" s="45"/>
-      <c r="AH63" s="45"/>
-      <c r="AI63" s="46"/>
+      <c r="AD63" s="75"/>
+      <c r="AE63" s="76"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="76"/>
+      <c r="AH63" s="76"/>
+      <c r="AI63" s="77"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="35">
+      <c r="AN63" s="40">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7082,11 +7081,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="64"/>
-      <c r="BD63" s="64"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I64" s="36"/>
+      <c r="BC63" s="35"/>
+      <c r="BD63" s="35"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I64" s="41"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7149,7 +7148,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="36"/>
+      <c r="AN64" s="41"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7170,11 +7169,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="65"/>
-      <c r="BD64" s="65"/>
-    </row>
-    <row r="65" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I65" s="35">
+      <c r="BC64" s="36"/>
+      <c r="BD64" s="36"/>
+    </row>
+    <row r="65" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I65" s="40">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7203,17 +7202,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="44"/>
-      <c r="AE65" s="45"/>
-      <c r="AF65" s="45"/>
-      <c r="AG65" s="45"/>
-      <c r="AH65" s="45"/>
-      <c r="AI65" s="46"/>
+      <c r="AD65" s="75"/>
+      <c r="AE65" s="76"/>
+      <c r="AF65" s="76"/>
+      <c r="AG65" s="76"/>
+      <c r="AH65" s="76"/>
+      <c r="AI65" s="77"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="35">
+      <c r="AN65" s="40">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7236,11 +7235,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="64"/>
-      <c r="BD65" s="64"/>
-    </row>
-    <row r="66" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I66" s="36"/>
+      <c r="BC65" s="35"/>
+      <c r="BD65" s="35"/>
+    </row>
+    <row r="66" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I66" s="41"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7261,10 +7260,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="35" t="s">
+      <c r="X66" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="56">
+      <c r="Y66" s="54">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7295,7 +7294,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="36"/>
+      <c r="AN66" s="41"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7316,15 +7315,15 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="64"/>
-      <c r="BD66" s="64"/>
-    </row>
-    <row r="67" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC66" s="35"/>
+      <c r="BD66" s="35"/>
+    </row>
+    <row r="67" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="19"/>
@@ -7343,8 +7342,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="36"/>
-      <c r="Y67" s="57"/>
+      <c r="X67" s="41"/>
+      <c r="Y67" s="55"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7396,11 +7395,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="64"/>
-      <c r="BD67" s="64"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I68" s="35">
+      <c r="BC67" s="35"/>
+      <c r="BD67" s="35"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I68" s="40">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7429,17 +7428,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="44"/>
-      <c r="AE68" s="45"/>
-      <c r="AF68" s="45"/>
-      <c r="AG68" s="45"/>
-      <c r="AH68" s="45"/>
-      <c r="AI68" s="46"/>
+      <c r="AD68" s="75"/>
+      <c r="AE68" s="76"/>
+      <c r="AF68" s="76"/>
+      <c r="AG68" s="76"/>
+      <c r="AH68" s="76"/>
+      <c r="AI68" s="77"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="35">
+      <c r="AN68" s="40">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7462,11 +7461,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="64"/>
-      <c r="BD68" s="64"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I69" s="36"/>
+      <c r="BC68" s="35"/>
+      <c r="BD68" s="35"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I69" s="41"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7487,10 +7486,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="35" t="s">
+      <c r="X69" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="56">
+      <c r="Y69" s="54">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7521,7 +7520,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="36"/>
+      <c r="AN69" s="41"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7542,10 +7541,10 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="64"/>
-      <c r="BD69" s="64"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC69" s="35"/>
+      <c r="BD69" s="35"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
@@ -7569,8 +7568,8 @@
       <c r="U70" s="6"/>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="36"/>
-      <c r="Y70" s="57"/>
+      <c r="X70" s="41"/>
+      <c r="Y70" s="55"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7622,11 +7621,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="64"/>
-      <c r="BD70" s="64"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I71" s="35">
+      <c r="BC70" s="35"/>
+      <c r="BD70" s="35"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I71" s="40">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7655,17 +7654,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="44"/>
-      <c r="AE71" s="45"/>
-      <c r="AF71" s="45"/>
-      <c r="AG71" s="45"/>
-      <c r="AH71" s="45"/>
-      <c r="AI71" s="46"/>
+      <c r="AD71" s="75"/>
+      <c r="AE71" s="76"/>
+      <c r="AF71" s="76"/>
+      <c r="AG71" s="76"/>
+      <c r="AH71" s="76"/>
+      <c r="AI71" s="77"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="35">
+      <c r="AN71" s="40">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7688,11 +7687,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="64"/>
-      <c r="BD71" s="64"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I72" s="36"/>
+      <c r="BC71" s="35"/>
+      <c r="BD71" s="35"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I72" s="41"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7713,10 +7712,10 @@
       <c r="U72" s="6"/>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="35">
+      <c r="X72" s="40">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="40">
+      <c r="Y72" s="52">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7731,14 +7730,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="47" t="s">
+      <c r="AD72" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="48"/>
-      <c r="AF72" s="48"/>
-      <c r="AG72" s="48"/>
-      <c r="AH72" s="48"/>
-      <c r="AI72" s="49"/>
+      <c r="AE72" s="44"/>
+      <c r="AF72" s="44"/>
+      <c r="AG72" s="44"/>
+      <c r="AH72" s="44"/>
+      <c r="AI72" s="45"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7747,7 +7746,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="36"/>
+      <c r="AN72" s="41"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7768,11 +7767,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="64"/>
-      <c r="BD72" s="64"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I73" s="35">
+      <c r="BC72" s="35"/>
+      <c r="BD72" s="35"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7783,20 +7782,20 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="47" t="s">
+      <c r="N73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="48"/>
-      <c r="P73" s="48"/>
-      <c r="Q73" s="48"/>
-      <c r="R73" s="48"/>
-      <c r="S73" s="49"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="44"/>
+      <c r="S73" s="45"/>
       <c r="T73" s="7"/>
       <c r="U73" s="6"/>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="36"/>
-      <c r="Y73" s="41"/>
+      <c r="X73" s="41"/>
+      <c r="Y73" s="53"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7809,14 +7808,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="47" t="s">
+      <c r="AD73" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="48"/>
-      <c r="AF73" s="48"/>
-      <c r="AG73" s="48"/>
-      <c r="AH73" s="48"/>
-      <c r="AI73" s="49"/>
+      <c r="AE73" s="44"/>
+      <c r="AF73" s="44"/>
+      <c r="AG73" s="44"/>
+      <c r="AH73" s="44"/>
+      <c r="AI73" s="45"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7825,7 +7824,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="35">
+      <c r="AN73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7836,23 +7835,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="47" t="s">
+      <c r="AS73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="48"/>
-      <c r="AU73" s="48"/>
-      <c r="AV73" s="48"/>
-      <c r="AW73" s="48"/>
-      <c r="AX73" s="49"/>
+      <c r="AT73" s="44"/>
+      <c r="AU73" s="44"/>
+      <c r="AV73" s="44"/>
+      <c r="AW73" s="44"/>
+      <c r="AX73" s="45"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="64"/>
-      <c r="BD73" s="64"/>
-    </row>
-    <row r="74" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I74" s="36"/>
+      <c r="BC73" s="35"/>
+      <c r="BD73" s="35"/>
+    </row>
+    <row r="74" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I74" s="41"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7879,17 +7878,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="44"/>
-      <c r="AE74" s="45"/>
-      <c r="AF74" s="45"/>
-      <c r="AG74" s="45"/>
-      <c r="AH74" s="45"/>
-      <c r="AI74" s="46"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="76"/>
+      <c r="AF74" s="76"/>
+      <c r="AG74" s="76"/>
+      <c r="AH74" s="76"/>
+      <c r="AI74" s="77"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="36"/>
+      <c r="AN74" s="41"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7910,11 +7909,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="64"/>
-      <c r="BD74" s="64"/>
-    </row>
-    <row r="75" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I75" s="35">
+      <c r="BC74" s="35"/>
+      <c r="BD74" s="35"/>
+    </row>
+    <row r="75" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7925,22 +7924,22 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="47" t="s">
+      <c r="N75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="49"/>
+      <c r="O75" s="44"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="44"/>
+      <c r="R75" s="44"/>
+      <c r="S75" s="45"/>
       <c r="T75" s="7"/>
       <c r="U75" s="6"/>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="35">
+      <c r="X75" s="40">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="58">
+      <c r="Y75" s="60">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -7971,7 +7970,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="35">
+      <c r="AN75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -7982,23 +7981,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="47" t="s">
+      <c r="AS75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="48"/>
-      <c r="AU75" s="48"/>
-      <c r="AV75" s="48"/>
-      <c r="AW75" s="48"/>
-      <c r="AX75" s="49"/>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="44"/>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="44"/>
+      <c r="AX75" s="45"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="64"/>
-      <c r="BD75" s="64"/>
-    </row>
-    <row r="76" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I76" s="36"/>
+      <c r="BC75" s="35"/>
+      <c r="BD75" s="35"/>
+    </row>
+    <row r="76" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I76" s="41"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8019,8 +8018,8 @@
       <c r="U76" s="6"/>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="36"/>
-      <c r="Y76" s="59"/>
+      <c r="X76" s="41"/>
+      <c r="Y76" s="61"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8049,7 +8048,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="36"/>
+      <c r="AN76" s="41"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8070,11 +8069,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="65"/>
-      <c r="BD76" s="65"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I77" s="35">
+      <c r="BC76" s="36"/>
+      <c r="BD76" s="36"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I77" s="40">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8103,17 +8102,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="44"/>
-      <c r="AE77" s="45"/>
-      <c r="AF77" s="45"/>
-      <c r="AG77" s="45"/>
-      <c r="AH77" s="45"/>
-      <c r="AI77" s="46"/>
+      <c r="AD77" s="75"/>
+      <c r="AE77" s="76"/>
+      <c r="AF77" s="76"/>
+      <c r="AG77" s="76"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="77"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="35">
+      <c r="AN77" s="40">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8136,11 +8135,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="64"/>
-      <c r="BD77" s="64"/>
-    </row>
-    <row r="78" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I78" s="36"/>
+      <c r="BC77" s="35"/>
+      <c r="BD77" s="35"/>
+    </row>
+    <row r="78" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I78" s="41"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8161,10 +8160,10 @@
       <c r="U78" s="6"/>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="35">
+      <c r="X78" s="40">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="40">
+      <c r="Y78" s="52">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8195,7 +8194,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="36"/>
+      <c r="AN78" s="41"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8216,11 +8215,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="64"/>
-      <c r="BD78" s="64"/>
-    </row>
-    <row r="79" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I79" s="35">
+      <c r="BC78" s="35"/>
+      <c r="BD78" s="35"/>
+    </row>
+    <row r="79" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I79" s="40">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8231,20 +8230,20 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="47" t="s">
+      <c r="N79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="48"/>
-      <c r="P79" s="48"/>
-      <c r="Q79" s="48"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="49"/>
+      <c r="O79" s="44"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="44"/>
+      <c r="R79" s="44"/>
+      <c r="S79" s="45"/>
       <c r="T79" s="7"/>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="36"/>
-      <c r="Y79" s="41"/>
+      <c r="X79" s="41"/>
+      <c r="Y79" s="53"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8273,7 +8272,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="35">
+      <c r="AN79" s="40">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8284,23 +8283,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="47" t="s">
+      <c r="AS79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="48"/>
-      <c r="AU79" s="48"/>
-      <c r="AV79" s="48"/>
-      <c r="AW79" s="48"/>
-      <c r="AX79" s="49"/>
+      <c r="AT79" s="44"/>
+      <c r="AU79" s="44"/>
+      <c r="AV79" s="44"/>
+      <c r="AW79" s="44"/>
+      <c r="AX79" s="45"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="64"/>
-      <c r="BD79" s="64"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I80" s="36"/>
+      <c r="BC79" s="35"/>
+      <c r="BD79" s="35"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I80" s="41"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8327,17 +8326,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="44"/>
-      <c r="AE80" s="45"/>
-      <c r="AF80" s="45"/>
-      <c r="AG80" s="45"/>
-      <c r="AH80" s="45"/>
-      <c r="AI80" s="46"/>
+      <c r="AD80" s="75"/>
+      <c r="AE80" s="76"/>
+      <c r="AF80" s="76"/>
+      <c r="AG80" s="76"/>
+      <c r="AH80" s="76"/>
+      <c r="AI80" s="77"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="36"/>
+      <c r="AN80" s="41"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8358,11 +8357,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="64"/>
-      <c r="BD80" s="64"/>
-    </row>
-    <row r="81" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I81" s="35">
+      <c r="BC80" s="35"/>
+      <c r="BD80" s="35"/>
+    </row>
+    <row r="81" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I81" s="40">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8419,7 +8418,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="35">
+      <c r="AN81" s="40">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8442,11 +8441,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="64"/>
-      <c r="BD81" s="64"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I82" s="36"/>
+      <c r="BC81" s="35"/>
+      <c r="BD81" s="35"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I82" s="41"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8455,14 +8454,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="47" t="s">
+      <c r="N82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="48"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="48"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="49"/>
+      <c r="O82" s="44"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="44"/>
+      <c r="R82" s="44"/>
+      <c r="S82" s="45"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8473,17 +8472,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="44"/>
-      <c r="AE82" s="45"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="45"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
+      <c r="AD82" s="75"/>
+      <c r="AE82" s="76"/>
+      <c r="AF82" s="76"/>
+      <c r="AG82" s="76"/>
+      <c r="AH82" s="76"/>
+      <c r="AI82" s="77"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="36"/>
+      <c r="AN82" s="41"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8492,23 +8491,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="47" t="s">
+      <c r="AS82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="48"/>
-      <c r="AU82" s="48"/>
-      <c r="AV82" s="48"/>
-      <c r="AW82" s="48"/>
-      <c r="AX82" s="49"/>
+      <c r="AT82" s="44"/>
+      <c r="AU82" s="44"/>
+      <c r="AV82" s="44"/>
+      <c r="AW82" s="44"/>
+      <c r="AX82" s="45"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="64"/>
-      <c r="BD82" s="64"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I83" s="35">
+      <c r="BC82" s="35"/>
+      <c r="BD82" s="35"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I83" s="40">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8539,10 +8538,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="35">
+      <c r="X83" s="40">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="56">
+      <c r="Y83" s="54">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8573,7 +8572,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="35">
+      <c r="AN83" s="40">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8602,11 +8601,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="64"/>
-      <c r="BD83" s="64"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I84" s="36"/>
+      <c r="BC83" s="35"/>
+      <c r="BD83" s="35"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I84" s="41"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8635,8 +8634,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="36"/>
-      <c r="Y84" s="57"/>
+      <c r="X84" s="41"/>
+      <c r="Y84" s="55"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8665,7 +8664,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="36"/>
+      <c r="AN84" s="41"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8692,10 +8691,10 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="64"/>
-      <c r="BD84" s="64"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC84" s="35"/>
+      <c r="BD84" s="35"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
@@ -8725,12 +8724,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="44"/>
-      <c r="AE85" s="45"/>
-      <c r="AF85" s="45"/>
-      <c r="AG85" s="45"/>
-      <c r="AH85" s="45"/>
-      <c r="AI85" s="46"/>
+      <c r="AD85" s="75"/>
+      <c r="AE85" s="76"/>
+      <c r="AF85" s="76"/>
+      <c r="AG85" s="76"/>
+      <c r="AH85" s="76"/>
+      <c r="AI85" s="77"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8758,11 +8757,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="64"/>
-      <c r="BD85" s="64"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I86" s="35">
+      <c r="BC85" s="35"/>
+      <c r="BD85" s="35"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I86" s="40">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8785,10 +8784,10 @@
       <c r="U86" s="6"/>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="35">
+      <c r="X86" s="40">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="50">
+      <c r="Y86" s="56">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8819,7 +8818,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="35">
+      <c r="AN86" s="40">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8842,11 +8841,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="64"/>
-      <c r="BD86" s="64"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I87" s="36"/>
+      <c r="BC86" s="35"/>
+      <c r="BD86" s="35"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I87" s="41"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8867,8 +8866,8 @@
       <c r="U87" s="6"/>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="36"/>
-      <c r="Y87" s="51"/>
+      <c r="X87" s="41"/>
+      <c r="Y87" s="57"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8897,7 +8896,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="36"/>
+      <c r="AN87" s="41"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8918,11 +8917,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="64"/>
-      <c r="BD87" s="64"/>
-    </row>
-    <row r="88" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I88" s="35" t="s">
+      <c r="BC87" s="35"/>
+      <c r="BD87" s="35"/>
+    </row>
+    <row r="88" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -8951,17 +8950,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="44"/>
-      <c r="AE88" s="45"/>
-      <c r="AF88" s="45"/>
-      <c r="AG88" s="45"/>
-      <c r="AH88" s="45"/>
-      <c r="AI88" s="46"/>
+      <c r="AD88" s="75"/>
+      <c r="AE88" s="76"/>
+      <c r="AF88" s="76"/>
+      <c r="AG88" s="76"/>
+      <c r="AH88" s="76"/>
+      <c r="AI88" s="77"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="35" t="s">
+      <c r="AN88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -8984,11 +8983,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="65"/>
-      <c r="BD88" s="65"/>
-    </row>
-    <row r="89" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I89" s="36"/>
+      <c r="BC88" s="36"/>
+      <c r="BD88" s="36"/>
+    </row>
+    <row r="89" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I89" s="41"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -9009,10 +9008,10 @@
       <c r="U89" s="6"/>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="35" t="s">
+      <c r="X89" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="50">
+      <c r="Y89" s="56">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9043,7 +9042,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="36"/>
+      <c r="AN89" s="41"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9064,10 +9063,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="64"/>
-      <c r="BD89" s="64"/>
-    </row>
-    <row r="90" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC89" s="35"/>
+      <c r="BD89" s="35"/>
+    </row>
+    <row r="90" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9079,20 +9078,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="52" t="s">
+      <c r="N90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
+      <c r="O90" s="42"/>
+      <c r="P90" s="42"/>
+      <c r="Q90" s="42"/>
+      <c r="R90" s="42"/>
+      <c r="S90" s="42"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="36"/>
-      <c r="Y90" s="51"/>
+      <c r="X90" s="41"/>
+      <c r="Y90" s="57"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9132,22 +9131,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="52" t="s">
+      <c r="AS90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
+      <c r="AT90" s="42"/>
+      <c r="AU90" s="42"/>
+      <c r="AV90" s="42"/>
+      <c r="AW90" s="42"/>
+      <c r="AX90" s="42"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="64"/>
-      <c r="BD90" s="64"/>
-    </row>
-    <row r="91" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="BC90" s="35"/>
+      <c r="BD90" s="35"/>
+    </row>
+    <row r="91" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9169,12 +9168,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="44"/>
-      <c r="AE91" s="45"/>
-      <c r="AF91" s="45"/>
-      <c r="AG91" s="45"/>
-      <c r="AH91" s="45"/>
-      <c r="AI91" s="46"/>
+      <c r="AD91" s="75"/>
+      <c r="AE91" s="76"/>
+      <c r="AF91" s="76"/>
+      <c r="AG91" s="76"/>
+      <c r="AH91" s="76"/>
+      <c r="AI91" s="77"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9197,7 +9196,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9213,10 +9212,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="35">
+      <c r="X92" s="40">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="58">
+      <c r="Y92" s="60">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9265,7 +9264,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9281,8 +9280,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="36"/>
-      <c r="Y93" s="59"/>
+      <c r="X93" s="41"/>
+      <c r="Y93" s="61"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9329,7 +9328,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9351,12 +9350,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="44"/>
-      <c r="AE94" s="45"/>
-      <c r="AF94" s="45"/>
-      <c r="AG94" s="45"/>
-      <c r="AH94" s="45"/>
-      <c r="AI94" s="46"/>
+      <c r="AD94" s="75"/>
+      <c r="AE94" s="76"/>
+      <c r="AF94" s="76"/>
+      <c r="AG94" s="76"/>
+      <c r="AH94" s="76"/>
+      <c r="AI94" s="77"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9379,7 +9378,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="95" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9395,10 +9394,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="35">
+      <c r="X95" s="40">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="60">
+      <c r="Y95" s="58">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9439,7 +9438,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="96" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9455,8 +9454,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="36"/>
-      <c r="Y96" s="61"/>
+      <c r="X96" s="41"/>
+      <c r="Y96" s="59"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9495,7 +9494,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9517,12 +9516,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="44"/>
-      <c r="AE97" s="45"/>
-      <c r="AF97" s="45"/>
-      <c r="AG97" s="45"/>
-      <c r="AH97" s="45"/>
-      <c r="AI97" s="46"/>
+      <c r="AD97" s="75"/>
+      <c r="AE97" s="76"/>
+      <c r="AF97" s="76"/>
+      <c r="AG97" s="76"/>
+      <c r="AH97" s="76"/>
+      <c r="AI97" s="77"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9545,7 +9544,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="98" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9605,7 +9604,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="99" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9627,12 +9626,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="44"/>
-      <c r="AE99" s="45"/>
-      <c r="AF99" s="45"/>
-      <c r="AG99" s="45"/>
-      <c r="AH99" s="45"/>
-      <c r="AI99" s="46"/>
+      <c r="AD99" s="75"/>
+      <c r="AE99" s="76"/>
+      <c r="AF99" s="76"/>
+      <c r="AG99" s="76"/>
+      <c r="AH99" s="76"/>
+      <c r="AI99" s="77"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9655,7 +9654,7 @@
       <c r="BC99" s="20"/>
       <c r="BD99" s="20"/>
     </row>
-    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -9671,10 +9670,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="35">
+      <c r="X100" s="40">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="40">
+      <c r="Y100" s="52">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9717,7 +9716,7 @@
       <c r="BC100" s="20"/>
       <c r="BD100" s="20"/>
     </row>
-    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -9733,8 +9732,8 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="36"/>
-      <c r="Y101" s="41"/>
+      <c r="X101" s="41"/>
+      <c r="Y101" s="53"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
@@ -9775,7 +9774,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="102" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -9797,12 +9796,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="44"/>
-      <c r="AE102" s="45"/>
-      <c r="AF102" s="45"/>
-      <c r="AG102" s="45"/>
-      <c r="AH102" s="45"/>
-      <c r="AI102" s="46"/>
+      <c r="AD102" s="75"/>
+      <c r="AE102" s="76"/>
+      <c r="AF102" s="76"/>
+      <c r="AG102" s="76"/>
+      <c r="AH102" s="76"/>
+      <c r="AI102" s="77"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9825,7 +9824,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -9885,7 +9884,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="104" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -9907,12 +9906,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="44"/>
-      <c r="AE104" s="45"/>
-      <c r="AF104" s="45"/>
-      <c r="AG104" s="45"/>
-      <c r="AH104" s="45"/>
-      <c r="AI104" s="46"/>
+      <c r="AD104" s="75"/>
+      <c r="AE104" s="76"/>
+      <c r="AF104" s="76"/>
+      <c r="AG104" s="76"/>
+      <c r="AH104" s="76"/>
+      <c r="AI104" s="77"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -9935,7 +9934,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -9952,10 +9951,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="35">
+      <c r="X105" s="40">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="50">
+      <c r="Y105" s="56">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -9996,7 +9995,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -10012,8 +10011,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="36"/>
-      <c r="Y106" s="51"/>
+      <c r="X106" s="41"/>
+      <c r="Y106" s="57"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10052,7 +10051,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10074,12 +10073,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="44"/>
-      <c r="AE107" s="45"/>
-      <c r="AF107" s="45"/>
-      <c r="AG107" s="45"/>
-      <c r="AH107" s="45"/>
-      <c r="AI107" s="46"/>
+      <c r="AD107" s="75"/>
+      <c r="AE107" s="76"/>
+      <c r="AF107" s="76"/>
+      <c r="AG107" s="76"/>
+      <c r="AH107" s="76"/>
+      <c r="AI107" s="77"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10102,7 +10101,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="108" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10118,10 +10117,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="35">
+      <c r="X108" s="40">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="50">
+      <c r="Y108" s="56">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10132,14 +10131,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="47" t="s">
+      <c r="AD108" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="48"/>
-      <c r="AF108" s="48"/>
-      <c r="AG108" s="48"/>
-      <c r="AH108" s="48"/>
-      <c r="AI108" s="49"/>
+      <c r="AE108" s="44"/>
+      <c r="AF108" s="44"/>
+      <c r="AG108" s="44"/>
+      <c r="AH108" s="44"/>
+      <c r="AI108" s="45"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10162,7 +10161,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10178,8 +10177,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="36"/>
-      <c r="Y109" s="51"/>
+      <c r="X109" s="41"/>
+      <c r="Y109" s="57"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10218,7 +10217,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="110" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10240,12 +10239,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="44"/>
-      <c r="AE110" s="45"/>
-      <c r="AF110" s="45"/>
-      <c r="AG110" s="45"/>
-      <c r="AH110" s="45"/>
-      <c r="AI110" s="46"/>
+      <c r="AD110" s="75"/>
+      <c r="AE110" s="76"/>
+      <c r="AF110" s="76"/>
+      <c r="AG110" s="76"/>
+      <c r="AH110" s="76"/>
+      <c r="AI110" s="77"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10268,7 +10267,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="111" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10284,10 +10283,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="35">
+      <c r="X111" s="40">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="50">
+      <c r="Y111" s="56">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10298,14 +10297,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="47" t="s">
+      <c r="AD111" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="48"/>
-      <c r="AF111" s="48"/>
-      <c r="AG111" s="48"/>
-      <c r="AH111" s="48"/>
-      <c r="AI111" s="49"/>
+      <c r="AE111" s="44"/>
+      <c r="AF111" s="44"/>
+      <c r="AG111" s="44"/>
+      <c r="AH111" s="44"/>
+      <c r="AI111" s="45"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10328,7 +10327,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10344,8 +10343,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="36"/>
-      <c r="Y112" s="51"/>
+      <c r="X112" s="41"/>
+      <c r="Y112" s="57"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10384,7 +10383,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="113" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10406,12 +10405,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="44"/>
-      <c r="AE113" s="45"/>
-      <c r="AF113" s="45"/>
-      <c r="AG113" s="45"/>
-      <c r="AH113" s="45"/>
-      <c r="AI113" s="46"/>
+      <c r="AD113" s="75"/>
+      <c r="AE113" s="76"/>
+      <c r="AF113" s="76"/>
+      <c r="AG113" s="76"/>
+      <c r="AH113" s="76"/>
+      <c r="AI113" s="77"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10434,7 +10433,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10450,10 +10449,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="35">
+      <c r="X114" s="40">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="50">
+      <c r="Y114" s="56">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10494,7 +10493,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10510,8 +10509,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="36"/>
-      <c r="Y115" s="51"/>
+      <c r="X115" s="41"/>
+      <c r="Y115" s="57"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10550,7 +10549,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="116" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10572,12 +10571,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="44"/>
-      <c r="AE116" s="45"/>
-      <c r="AF116" s="45"/>
-      <c r="AG116" s="45"/>
-      <c r="AH116" s="45"/>
-      <c r="AI116" s="46"/>
+      <c r="AD116" s="75"/>
+      <c r="AE116" s="76"/>
+      <c r="AF116" s="76"/>
+      <c r="AG116" s="76"/>
+      <c r="AH116" s="76"/>
+      <c r="AI116" s="77"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10600,7 +10599,7 @@
       <c r="BC116" s="20"/>
       <c r="BD116" s="20"/>
     </row>
-    <row r="117" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="117" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I117" s="20"/>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -10616,10 +10615,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="35">
+      <c r="X117" s="40">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="50">
+      <c r="Y117" s="56">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10632,14 +10631,14 @@
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="47" t="s">
+      <c r="AD117" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="48"/>
-      <c r="AF117" s="48"/>
-      <c r="AG117" s="48"/>
-      <c r="AH117" s="48"/>
-      <c r="AI117" s="49"/>
+      <c r="AE117" s="44"/>
+      <c r="AF117" s="44"/>
+      <c r="AG117" s="44"/>
+      <c r="AH117" s="44"/>
+      <c r="AI117" s="45"/>
       <c r="AJ117" s="19"/>
       <c r="AK117" s="19"/>
       <c r="AL117" s="20"/>
@@ -10662,7 +10661,7 @@
       <c r="BC117" s="20"/>
       <c r="BD117" s="20"/>
     </row>
-    <row r="118" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="118" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I118" s="20"/>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -10678,8 +10677,8 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="36"/>
-      <c r="Y118" s="51"/>
+      <c r="X118" s="41"/>
+      <c r="Y118" s="57"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
@@ -10720,7 +10719,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10742,12 +10741,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="44"/>
-      <c r="AE119" s="45"/>
-      <c r="AF119" s="45"/>
-      <c r="AG119" s="45"/>
-      <c r="AH119" s="45"/>
-      <c r="AI119" s="46"/>
+      <c r="AD119" s="75"/>
+      <c r="AE119" s="76"/>
+      <c r="AF119" s="76"/>
+      <c r="AG119" s="76"/>
+      <c r="AH119" s="76"/>
+      <c r="AI119" s="77"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10770,7 +10769,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -10786,10 +10785,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="35">
+      <c r="X120" s="40">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="56">
+      <c r="Y120" s="54">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10830,7 +10829,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -10846,8 +10845,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="36"/>
-      <c r="Y121" s="57"/>
+      <c r="X121" s="41"/>
+      <c r="Y121" s="55"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10856,14 +10855,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="47" t="s">
+      <c r="AD121" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="48"/>
-      <c r="AF121" s="48"/>
-      <c r="AG121" s="48"/>
-      <c r="AH121" s="48"/>
-      <c r="AI121" s="49"/>
+      <c r="AE121" s="44"/>
+      <c r="AF121" s="44"/>
+      <c r="AG121" s="44"/>
+      <c r="AH121" s="44"/>
+      <c r="AI121" s="45"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10886,7 +10885,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="122" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -10908,12 +10907,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="44"/>
-      <c r="AE122" s="45"/>
-      <c r="AF122" s="45"/>
-      <c r="AG122" s="45"/>
-      <c r="AH122" s="45"/>
-      <c r="AI122" s="46"/>
+      <c r="AD122" s="75"/>
+      <c r="AE122" s="76"/>
+      <c r="AF122" s="76"/>
+      <c r="AG122" s="76"/>
+      <c r="AH122" s="76"/>
+      <c r="AI122" s="77"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -10936,7 +10935,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -10952,10 +10951,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="35">
+      <c r="X123" s="40">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="42">
+      <c r="Y123" s="46">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -11004,7 +11003,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11020,8 +11019,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="36"/>
-      <c r="Y124" s="43"/>
+      <c r="X124" s="41"/>
+      <c r="Y124" s="47"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11068,7 +11067,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11090,12 +11089,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="44"/>
-      <c r="AE125" s="45"/>
-      <c r="AF125" s="45"/>
-      <c r="AG125" s="45"/>
-      <c r="AH125" s="45"/>
-      <c r="AI125" s="46"/>
+      <c r="AD125" s="75"/>
+      <c r="AE125" s="76"/>
+      <c r="AF125" s="76"/>
+      <c r="AG125" s="76"/>
+      <c r="AH125" s="76"/>
+      <c r="AI125" s="77"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11118,7 +11117,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="126" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11137,7 +11136,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="42">
+      <c r="Y126" s="46">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11178,7 +11177,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11195,17 +11194,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="43"/>
+      <c r="Y127" s="47"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="44"/>
-      <c r="AE127" s="45"/>
-      <c r="AF127" s="45"/>
-      <c r="AG127" s="45"/>
-      <c r="AH127" s="45"/>
-      <c r="AI127" s="46"/>
+      <c r="AD127" s="75"/>
+      <c r="AE127" s="76"/>
+      <c r="AF127" s="76"/>
+      <c r="AG127" s="76"/>
+      <c r="AH127" s="76"/>
+      <c r="AI127" s="77"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11228,7 +11227,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11244,10 +11243,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="35">
+      <c r="X128" s="40">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="40">
+      <c r="Y128" s="52">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11288,7 +11287,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11304,8 +11303,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="36"/>
-      <c r="Y129" s="41"/>
+      <c r="X129" s="41"/>
+      <c r="Y129" s="53"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11344,7 +11343,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="130" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11366,12 +11365,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="44"/>
-      <c r="AE130" s="45"/>
-      <c r="AF130" s="45"/>
-      <c r="AG130" s="45"/>
-      <c r="AH130" s="45"/>
-      <c r="AI130" s="46"/>
+      <c r="AD130" s="75"/>
+      <c r="AE130" s="76"/>
+      <c r="AF130" s="76"/>
+      <c r="AG130" s="76"/>
+      <c r="AH130" s="76"/>
+      <c r="AI130" s="77"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11394,7 +11393,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11410,10 +11409,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="35" t="s">
+      <c r="X131" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="42">
+      <c r="Y131" s="46">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11454,7 +11453,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11470,8 +11469,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="36"/>
-      <c r="Y132" s="43"/>
+      <c r="X132" s="41"/>
+      <c r="Y132" s="47"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11510,7 +11509,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11532,12 +11531,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="44"/>
-      <c r="AE133" s="45"/>
-      <c r="AF133" s="45"/>
-      <c r="AG133" s="45"/>
-      <c r="AH133" s="45"/>
-      <c r="AI133" s="46"/>
+      <c r="AD133" s="75"/>
+      <c r="AE133" s="76"/>
+      <c r="AF133" s="76"/>
+      <c r="AG133" s="76"/>
+      <c r="AH133" s="76"/>
+      <c r="AI133" s="77"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11560,7 +11559,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="134" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11590,14 +11589,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="52" t="s">
+      <c r="AD134" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="52"/>
-      <c r="AF134" s="52"/>
-      <c r="AG134" s="52"/>
-      <c r="AH134" s="52"/>
-      <c r="AI134" s="52"/>
+      <c r="AE134" s="42"/>
+      <c r="AF134" s="42"/>
+      <c r="AG134" s="42"/>
+      <c r="AH134" s="42"/>
+      <c r="AI134" s="42"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11620,119 +11619,535 @@
       <c r="BC134" s="20"/>
       <c r="BD134" s="20"/>
     </row>
-    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G153" s="67"/>
-      <c r="H153" s="67"/>
-    </row>
-    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G153" s="89"/>
+      <c r="H153" s="89"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="W192" s="12"/>
     </row>
-    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="X131:X132"/>
+    <mergeCell ref="X128:X129"/>
+    <mergeCell ref="AD129:AI129"/>
+    <mergeCell ref="AD132:AI132"/>
+    <mergeCell ref="Y128:Y129"/>
+    <mergeCell ref="Y131:Y132"/>
+    <mergeCell ref="AD115:AI115"/>
+    <mergeCell ref="AD116:AI116"/>
+    <mergeCell ref="AD117:AI117"/>
+    <mergeCell ref="AD118:AI118"/>
+    <mergeCell ref="AD119:AI119"/>
+    <mergeCell ref="AD120:AI120"/>
+    <mergeCell ref="AD109:AI109"/>
+    <mergeCell ref="AD110:AI110"/>
+    <mergeCell ref="AD111:AI111"/>
+    <mergeCell ref="AD104:AI104"/>
+    <mergeCell ref="AD105:AI105"/>
+    <mergeCell ref="AD106:AI106"/>
+    <mergeCell ref="X108:X109"/>
+    <mergeCell ref="Y108:Y109"/>
+    <mergeCell ref="X105:X106"/>
+    <mergeCell ref="AD88:AI88"/>
+    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
     <mergeCell ref="AS85:AX85"/>
     <mergeCell ref="AN86:AN87"/>
     <mergeCell ref="AS86:AX86"/>
@@ -11757,481 +12172,61 @@
     <mergeCell ref="BC33:BD33"/>
     <mergeCell ref="BC34:BD34"/>
     <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="X131:X132"/>
-    <mergeCell ref="X128:X129"/>
-    <mergeCell ref="AD129:AI129"/>
-    <mergeCell ref="AD132:AI132"/>
-    <mergeCell ref="Y128:Y129"/>
-    <mergeCell ref="Y131:Y132"/>
-    <mergeCell ref="AD115:AI115"/>
-    <mergeCell ref="AD116:AI116"/>
-    <mergeCell ref="AD117:AI117"/>
-    <mergeCell ref="AD118:AI118"/>
-    <mergeCell ref="AD119:AI119"/>
-    <mergeCell ref="AD120:AI120"/>
-    <mergeCell ref="AD109:AI109"/>
-    <mergeCell ref="AD110:AI110"/>
-    <mergeCell ref="AD111:AI111"/>
-    <mergeCell ref="AD104:AI104"/>
-    <mergeCell ref="AD105:AI105"/>
-    <mergeCell ref="AD106:AI106"/>
-    <mergeCell ref="X108:X109"/>
-    <mergeCell ref="Y108:Y109"/>
-    <mergeCell ref="X105:X106"/>
-    <mergeCell ref="AD88:AI88"/>
-    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uandresbelloedu-my.sharepoint.com/personal/c_vidalgallardo_uandresbello_edu/Documents/Documents/GitHub/ING-DE-SOFTWARE/INCREMENTO2/Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ING-DE-SOFTWARE\INCREMENTO2\EXCELS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{44A795F0-7A33-48E4-A6BF-3D609E066F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93A6781B-0202-4E3C-96EA-7F2F680B86A3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028E72D6-8938-42F3-88D0-CBB24376CDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="219">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -691,6 +691,9 @@
   </si>
   <si>
     <t xml:space="preserve">Permitir que el sistema filtre datos de empleados . </t>
+  </si>
+  <si>
+    <t>Vicente</t>
   </si>
 </sst>
 </file>
@@ -1177,11 +1180,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1192,14 +1195,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1210,28 +1225,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1240,10 +1249,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1252,13 +1261,25 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1266,54 +1287,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1330,6 +1303,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1339,19 +1321,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1689,107 +1692,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="G2:BD230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="8.3984375" customWidth="1"/>
-    <col min="9" max="9" width="13.1328125" customWidth="1"/>
-    <col min="10" max="10" width="105.86328125" customWidth="1"/>
-    <col min="11" max="11" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="105.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.86328125" customWidth="1"/>
-    <col min="20" max="20" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.85546875" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11.1328125" customWidth="1"/>
-    <col min="23" max="23" width="10.59765625" customWidth="1"/>
-    <col min="24" max="24" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.86328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="104.265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.265625" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="104.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.28515625" customWidth="1"/>
     <col min="35" max="35" width="37" customWidth="1"/>
-    <col min="36" max="36" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.86328125" customWidth="1"/>
-    <col min="39" max="39" width="6.86328125" customWidth="1"/>
-    <col min="40" max="40" width="13.59765625" customWidth="1"/>
-    <col min="41" max="41" width="105.59765625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.85546875" customWidth="1"/>
+    <col min="39" max="39" width="6.85546875" customWidth="1"/>
+    <col min="40" max="40" width="13.5703125" customWidth="1"/>
+    <col min="41" max="41" width="105.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="45.86328125" customWidth="1"/>
-    <col min="51" max="51" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16373" max="16373" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="45.85546875" customWidth="1"/>
+    <col min="51" max="51" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16373" max="16373" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I2" s="66" t="s">
+    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="69" t="s">
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="82" t="s">
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="83"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="69" t="s">
+      <c r="U2" s="73"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="74"/>
+      <c r="AA2" s="74"/>
+      <c r="AB2" s="74"/>
+      <c r="AC2" s="74"/>
+      <c r="AD2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="81" t="s">
+      <c r="AE2" s="77"/>
+      <c r="AF2" s="77"/>
+      <c r="AG2" s="77"/>
+      <c r="AH2" s="77"/>
+      <c r="AI2" s="78"/>
+      <c r="AJ2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="81"/>
-      <c r="AN2" s="84" t="s">
+      <c r="AK2" s="71"/>
+      <c r="AN2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="84"/>
-      <c r="AP2" s="84"/>
-      <c r="AQ2" s="84"/>
-      <c r="AR2" s="84"/>
-      <c r="AS2" s="85" t="s">
+      <c r="AO2" s="74"/>
+      <c r="AP2" s="74"/>
+      <c r="AQ2" s="74"/>
+      <c r="AR2" s="74"/>
+      <c r="AS2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="85"/>
-      <c r="AU2" s="85"/>
-      <c r="AV2" s="85"/>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="85"/>
-      <c r="AY2" s="81" t="s">
+      <c r="AT2" s="75"/>
+      <c r="AU2" s="75"/>
+      <c r="AV2" s="75"/>
+      <c r="AW2" s="75"/>
+      <c r="AX2" s="75"/>
+      <c r="AY2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="81"/>
-      <c r="BA2" s="81" t="s">
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="81"/>
-      <c r="BC2" s="81" t="s">
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="81"/>
-    </row>
-    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BD2" s="71"/>
+    </row>
+    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1805,12 +1808,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="72"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="74"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="87"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1835,12 +1838,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="88"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="81"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1862,12 +1865,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
+      <c r="AS3" s="75"/>
+      <c r="AT3" s="75"/>
+      <c r="AU3" s="75"/>
+      <c r="AV3" s="75"/>
+      <c r="AW3" s="75"/>
+      <c r="AX3" s="75"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1880,13 +1883,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="81" t="s">
+      <c r="BC3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="81"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I4" s="62">
+      <c r="BD3" s="71"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="92">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1915,10 +1918,10 @@
       <c r="U4" s="6"/>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="40">
+      <c r="X4" s="35">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="50">
+      <c r="Y4" s="88">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1947,7 +1950,7 @@
       <c r="AK4" s="6"/>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="90">
+      <c r="AN4" s="68">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1976,11 +1979,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I5" s="63"/>
+      <c r="BC4" s="64"/>
+      <c r="BD4" s="64"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="69"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1993,7 +1996,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2007,8 +2010,8 @@
       <c r="U5" s="6"/>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="51"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="89"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2021,21 +2024,21 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="80" t="s">
+      <c r="AD5" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="77"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="46"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
       <c r="AK5" s="6"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="63"/>
+      <c r="AN5" s="69"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2048,7 +2051,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="65" t="s">
+      <c r="AS5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2062,11 +2065,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="75"/>
-      <c r="BD5" s="77"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I6" s="64"/>
+      <c r="BC5" s="44"/>
+      <c r="BD5" s="46"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="70"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2093,8 +2096,8 @@
       <c r="U6" s="6"/>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="79"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="90"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2107,21 +2110,21 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="75" t="s">
+      <c r="AD6" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="76"/>
-      <c r="AI6" s="77"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="46"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
       <c r="AK6" s="6"/>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="64"/>
+      <c r="AN6" s="70"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2148,11 +2151,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I7" s="40">
+      <c r="BC6" s="64"/>
+      <c r="BD6" s="64"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="35">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2187,17 +2190,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="76"/>
-      <c r="AG7" s="76"/>
-      <c r="AH7" s="76"/>
-      <c r="AI7" s="77"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="45"/>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="45"/>
+      <c r="AH7" s="45"/>
+      <c r="AI7" s="46"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="40">
+      <c r="AN7" s="35">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2226,11 +2229,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="35"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I8" s="41"/>
+      <c r="BC7" s="64"/>
+      <c r="BD7" s="64"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="36"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2257,10 +2260,10 @@
       <c r="U8" s="6"/>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="42">
+      <c r="X8" s="52">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="50">
+      <c r="Y8" s="88">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2289,7 +2292,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="48"/>
+      <c r="AN8" s="55"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2316,11 +2319,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="35"/>
-      <c r="BD8" s="35"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I9" s="40">
+      <c r="BC8" s="64"/>
+      <c r="BD8" s="64"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2349,8 +2352,8 @@
       <c r="U9" s="6"/>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="51"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="89"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2377,7 +2380,7 @@
       <c r="AK9" s="6"/>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="40">
+      <c r="AN9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2406,11 +2409,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="35"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I10" s="41"/>
+      <c r="BC9" s="64"/>
+      <c r="BD9" s="64"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="36"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2443,17 +2446,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="76"/>
-      <c r="AG10" s="76"/>
-      <c r="AH10" s="76"/>
-      <c r="AI10" s="77"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="46"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="48"/>
+      <c r="AN10" s="55"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2480,11 +2483,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="35"/>
-      <c r="BD10" s="35"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I11" s="40">
+      <c r="BC10" s="64"/>
+      <c r="BD10" s="64"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2499,7 +2502,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="65" t="s">
+      <c r="N11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2513,10 +2516,10 @@
       <c r="U11" s="6"/>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="42">
+      <c r="X11" s="52">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="46">
+      <c r="Y11" s="42">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2545,7 +2548,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="40">
+      <c r="AN11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2560,7 +2563,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="65" t="s">
+      <c r="AS11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2574,11 +2577,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="35"/>
-      <c r="BD11" s="35"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I12" s="48"/>
+      <c r="BC11" s="64"/>
+      <c r="BD11" s="64"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I12" s="55"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2591,7 +2594,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="65" t="s">
+      <c r="N12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2605,8 +2608,8 @@
       <c r="U12" s="6"/>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="47"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="43"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2633,7 +2636,7 @@
       <c r="AK12" s="6"/>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="48"/>
+      <c r="AN12" s="55"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2646,7 +2649,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="65" t="s">
+      <c r="AS12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2660,11 +2663,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="35"/>
-      <c r="BD12" s="35"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I13" s="41"/>
+      <c r="BC12" s="64"/>
+      <c r="BD12" s="64"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="36"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2697,17 +2700,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="76"/>
-      <c r="AH13" s="76"/>
-      <c r="AI13" s="77"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="45"/>
+      <c r="AH13" s="45"/>
+      <c r="AI13" s="46"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="41"/>
+      <c r="AN13" s="36"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2734,11 +2737,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="35"/>
-      <c r="BD13" s="35"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I14" s="40">
+      <c r="BC13" s="64"/>
+      <c r="BD13" s="64"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="35">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2767,10 +2770,10 @@
       <c r="U14" s="6"/>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="42">
+      <c r="X14" s="52">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="52">
+      <c r="Y14" s="40">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2785,7 +2788,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="65" t="s">
+      <c r="AD14" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2799,7 +2802,7 @@
       <c r="AK14" s="6"/>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="40">
+      <c r="AN14" s="35">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2828,11 +2831,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="35"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I15" s="48"/>
+      <c r="BC14" s="64"/>
+      <c r="BD14" s="64"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="55"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2859,8 +2862,8 @@
       <c r="U15" s="6"/>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="78"/>
+      <c r="X15" s="52"/>
+      <c r="Y15" s="62"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2873,7 +2876,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="65" t="s">
+      <c r="AD15" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2887,7 +2890,7 @@
       <c r="AK15" s="6"/>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="48"/>
+      <c r="AN15" s="55"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2914,11 +2917,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="35"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I16" s="41"/>
+      <c r="BC15" s="64"/>
+      <c r="BD15" s="64"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="36"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +2948,8 @@
       <c r="U16" s="6"/>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="53"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="41"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2973,7 +2976,7 @@
       <c r="AK16" s="6"/>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="48"/>
+      <c r="AN16" s="55"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3000,11 +3003,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="36"/>
-      <c r="BD16" s="36"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I17" s="92">
+      <c r="BC16" s="65"/>
+      <c r="BD16" s="65"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="53">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3039,17 +3042,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76"/>
-      <c r="AH17" s="76"/>
-      <c r="AI17" s="77"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="45"/>
+      <c r="AF17" s="45"/>
+      <c r="AG17" s="45"/>
+      <c r="AH17" s="45"/>
+      <c r="AI17" s="46"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="49">
+      <c r="AN17" s="93">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3078,11 +3081,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="35"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I18" s="93"/>
+      <c r="BC17" s="64"/>
+      <c r="BD17" s="64"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="54"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3109,10 +3112,10 @@
       <c r="U18" s="6"/>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="42">
+      <c r="X18" s="52">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="52">
+      <c r="Y18" s="40">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3141,7 +3144,7 @@
       <c r="AK18" s="6"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="49"/>
+      <c r="AN18" s="93"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3168,18 +3171,22 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="35"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I19" s="40" t="s">
+      <c r="BC18" s="64"/>
+      <c r="BD18" s="64"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="19"/>
+      <c r="K19" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L19" s="19">
+        <v>3</v>
+      </c>
       <c r="M19" s="6" t="s">
         <v>13</v>
       </c>
@@ -3191,12 +3198,16 @@
       <c r="Q19" s="38"/>
       <c r="R19" s="38"/>
       <c r="S19" s="39"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="6"/>
+      <c r="T19" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U19" s="7">
+        <v>45912</v>
+      </c>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="78"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="62"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3223,7 +3234,7 @@
       <c r="AK19" s="6"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="40" t="s">
+      <c r="AN19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3246,16 +3257,20 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="35"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I20" s="41"/>
+      <c r="BC19" s="64"/>
+      <c r="BD19" s="64"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="36"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="19"/>
+      <c r="K20" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L20" s="19">
+        <v>3</v>
+      </c>
       <c r="M20" s="6" t="s">
         <v>13</v>
       </c>
@@ -3267,12 +3282,16 @@
       <c r="Q20" s="38"/>
       <c r="R20" s="38"/>
       <c r="S20" s="39"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
+      <c r="T20" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U20" s="7">
+        <v>45912</v>
+      </c>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="53"/>
+      <c r="X20" s="52"/>
+      <c r="Y20" s="41"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3299,7 +3318,7 @@
       <c r="AK20" s="7"/>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="41"/>
+      <c r="AN20" s="36"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3320,11 +3339,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="35"/>
-      <c r="BD20" s="35"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I21" s="40">
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="64"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="35">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3361,17 +3380,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="76"/>
-      <c r="AG21" s="76"/>
-      <c r="AH21" s="76"/>
-      <c r="AI21" s="77"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="46"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="40">
+      <c r="AN21" s="35">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3402,11 +3421,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="35"/>
-      <c r="BD21" s="35"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I22" s="48"/>
+      <c r="BC21" s="64"/>
+      <c r="BD21" s="64"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="55"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3435,10 +3454,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="49">
+      <c r="X22" s="93">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="52">
+      <c r="Y22" s="40">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3467,7 +3486,7 @@
       <c r="AK22" s="7"/>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="48"/>
+      <c r="AN22" s="55"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3496,11 +3515,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="35"/>
-      <c r="BD22" s="35"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I23" s="41"/>
+      <c r="BC22" s="64"/>
+      <c r="BD22" s="64"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I23" s="36"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3529,8 +3548,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="53"/>
+      <c r="X23" s="93"/>
+      <c r="Y23" s="41"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3557,7 +3576,7 @@
       <c r="AK23" s="7"/>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="41"/>
+      <c r="AN23" s="36"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3586,11 +3605,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="35"/>
-      <c r="BD23" s="35"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I24" s="40" t="s">
+      <c r="BC23" s="64"/>
+      <c r="BD23" s="64"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3627,17 +3646,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="76"/>
-      <c r="AG24" s="76"/>
-      <c r="AH24" s="76"/>
-      <c r="AI24" s="77"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="45"/>
+      <c r="AI24" s="46"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="40" t="s">
+      <c r="AN24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3668,11 +3687,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="35"/>
-      <c r="BD24" s="35"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I25" s="41"/>
+      <c r="BC24" s="64"/>
+      <c r="BD24" s="64"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I25" s="36"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3701,10 +3720,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="40" t="s">
+      <c r="X25" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="46">
+      <c r="Y25" s="42">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3727,7 +3746,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="41"/>
+      <c r="AN25" s="36"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3756,11 +3775,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="35"/>
-      <c r="BD25" s="35"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I26" s="40" t="s">
+      <c r="BC25" s="64"/>
+      <c r="BD25" s="64"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3791,8 +3810,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="47"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="43"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3813,7 +3832,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="40" t="s">
+      <c r="AN26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3844,11 +3863,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="35"/>
-      <c r="BD26" s="35"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I27" s="41"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="36"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3883,17 +3902,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="76"/>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="77"/>
+      <c r="AD27" s="44"/>
+      <c r="AE27" s="45"/>
+      <c r="AF27" s="45"/>
+      <c r="AG27" s="45"/>
+      <c r="AH27" s="45"/>
+      <c r="AI27" s="46"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="41"/>
+      <c r="AN27" s="36"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3922,11 +3941,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="35"/>
-      <c r="BD27" s="35"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I28" s="40" t="s">
+      <c r="BC27" s="64"/>
+      <c r="BD27" s="64"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -3957,10 +3976,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="40">
+      <c r="X28" s="35">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="60">
+      <c r="Y28" s="58">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -3991,7 +4010,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="40" t="s">
+      <c r="AN28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4022,11 +4041,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="36"/>
-      <c r="BD28" s="36"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I29" s="48"/>
+      <c r="BC28" s="65"/>
+      <c r="BD28" s="65"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I29" s="55"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4055,8 +4074,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="91"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="63"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4085,7 +4104,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="48"/>
+      <c r="AN29" s="55"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4114,11 +4133,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="35"/>
-      <c r="BD29" s="35"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I30" s="41"/>
+      <c r="BC29" s="64"/>
+      <c r="BD29" s="64"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I30" s="36"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4147,8 +4166,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="61"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="59"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4177,7 +4196,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="41"/>
+      <c r="AN30" s="36"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4206,11 +4225,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="35"/>
-      <c r="BD30" s="35"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I31" s="40">
+      <c r="BC30" s="64"/>
+      <c r="BD30" s="64"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I31" s="35">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4247,17 +4266,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="76"/>
-      <c r="AG31" s="76"/>
-      <c r="AH31" s="76"/>
-      <c r="AI31" s="77"/>
+      <c r="AD31" s="44"/>
+      <c r="AE31" s="45"/>
+      <c r="AF31" s="45"/>
+      <c r="AG31" s="45"/>
+      <c r="AH31" s="45"/>
+      <c r="AI31" s="46"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="40">
+      <c r="AN31" s="35">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4288,11 +4307,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="35"/>
-      <c r="BD31" s="35"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I32" s="41"/>
+      <c r="BC31" s="64"/>
+      <c r="BD31" s="64"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I32" s="36"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4321,10 +4340,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="40">
+      <c r="X32" s="35">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="60">
+      <c r="Y32" s="58">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4355,7 +4374,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="41"/>
+      <c r="AN32" s="36"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4384,11 +4403,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="35"/>
-      <c r="BD32" s="35"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I33" s="40">
+      <c r="BC32" s="64"/>
+      <c r="BD32" s="64"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I33" s="35">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4419,8 +4438,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="61"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="59"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4449,7 +4468,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="40">
+      <c r="AN33" s="35">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4480,11 +4499,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="35"/>
-      <c r="BD33" s="35"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I34" s="41"/>
+      <c r="BC33" s="64"/>
+      <c r="BD33" s="64"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I34" s="36"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4519,17 +4538,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="75"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
-      <c r="AI34" s="77"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="45"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="45"/>
+      <c r="AI34" s="46"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="41"/>
+      <c r="AN34" s="36"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4558,11 +4577,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="35"/>
-      <c r="BD34" s="35"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I35" s="40">
+      <c r="BC34" s="64"/>
+      <c r="BD34" s="64"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4593,10 +4612,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="40" t="s">
+      <c r="X35" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="46">
+      <c r="Y35" s="42">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4627,7 +4646,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="40">
+      <c r="AN35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4658,11 +4677,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="35"/>
-      <c r="BD35" s="35"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I36" s="41"/>
+      <c r="BC35" s="64"/>
+      <c r="BD35" s="64"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I36" s="36"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4691,8 +4710,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="47"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="43"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4721,7 +4740,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="41"/>
+      <c r="AN36" s="36"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4750,11 +4769,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="35"/>
-      <c r="BD36" s="35"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I37" s="40">
+      <c r="BC36" s="64"/>
+      <c r="BD36" s="64"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4791,17 +4810,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="75"/>
-      <c r="AE37" s="76"/>
-      <c r="AF37" s="76"/>
-      <c r="AG37" s="76"/>
-      <c r="AH37" s="76"/>
-      <c r="AI37" s="77"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="45"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="46"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="40">
+      <c r="AN37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4832,11 +4851,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="35"/>
-      <c r="BD37" s="35"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I38" s="41"/>
+      <c r="BC37" s="64"/>
+      <c r="BD37" s="64"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I38" s="36"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4865,10 +4884,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="40" t="s">
+      <c r="X38" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="52">
+      <c r="Y38" s="40">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4899,7 +4918,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="41"/>
+      <c r="AN38" s="36"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4928,10 +4947,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="35"/>
-      <c r="BD38" s="35"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BC38" s="64"/>
+      <c r="BD38" s="64"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -4963,8 +4982,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="78"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="62"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5024,11 +5043,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="35"/>
-      <c r="BD39" s="35"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I40" s="40">
+      <c r="BC39" s="64"/>
+      <c r="BD39" s="64"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5059,8 +5078,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="41"/>
-      <c r="Y40" s="53"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="41"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5089,7 +5108,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="40">
+      <c r="AN40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5120,11 +5139,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="36"/>
-      <c r="BD40" s="36"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I41" s="41"/>
+      <c r="BC40" s="65"/>
+      <c r="BD40" s="65"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I41" s="36"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5137,14 +5156,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="45"/>
+      <c r="O41" s="48"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="49"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5159,17 +5178,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="75"/>
-      <c r="AE41" s="76"/>
-      <c r="AF41" s="76"/>
-      <c r="AG41" s="76"/>
-      <c r="AH41" s="76"/>
-      <c r="AI41" s="77"/>
+      <c r="AD41" s="44"/>
+      <c r="AE41" s="45"/>
+      <c r="AF41" s="45"/>
+      <c r="AG41" s="45"/>
+      <c r="AH41" s="45"/>
+      <c r="AI41" s="46"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="41"/>
+      <c r="AN41" s="36"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5182,14 +5201,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="43" t="s">
+      <c r="AS41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="44"/>
-      <c r="AU41" s="44"/>
-      <c r="AV41" s="44"/>
-      <c r="AW41" s="44"/>
-      <c r="AX41" s="45"/>
+      <c r="AT41" s="48"/>
+      <c r="AU41" s="48"/>
+      <c r="AV41" s="48"/>
+      <c r="AW41" s="48"/>
+      <c r="AX41" s="49"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5198,10 +5217,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="35"/>
-      <c r="BD41" s="35"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BC41" s="64"/>
+      <c r="BD41" s="64"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5233,10 +5252,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="40">
+      <c r="X42" s="35">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="52">
+      <c r="Y42" s="40">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5298,11 +5317,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="35"/>
-      <c r="BD42" s="35"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I43" s="40">
+      <c r="BC42" s="64"/>
+      <c r="BD42" s="64"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I43" s="35">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5333,8 +5352,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="53"/>
+      <c r="X43" s="36"/>
+      <c r="Y43" s="41"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5363,7 +5382,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="40">
+      <c r="AN43" s="35">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5394,11 +5413,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="35"/>
-      <c r="BD43" s="35"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I44" s="41"/>
+      <c r="BC43" s="64"/>
+      <c r="BD43" s="64"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="36"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5433,17 +5452,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="75"/>
-      <c r="AE44" s="76"/>
-      <c r="AF44" s="76"/>
-      <c r="AG44" s="76"/>
-      <c r="AH44" s="76"/>
-      <c r="AI44" s="77"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="45"/>
+      <c r="AG44" s="45"/>
+      <c r="AH44" s="45"/>
+      <c r="AI44" s="46"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="41"/>
+      <c r="AN44" s="36"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5472,10 +5491,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="35"/>
-      <c r="BD44" s="35"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BC44" s="64"/>
+      <c r="BD44" s="64"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5507,10 +5526,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="40">
+      <c r="X45" s="35">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="60">
+      <c r="Y45" s="58">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5572,11 +5591,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="35"/>
-      <c r="BD45" s="35"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I46" s="40" t="s">
+      <c r="BC45" s="64"/>
+      <c r="BD45" s="64"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5607,8 +5626,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="61"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="59"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5637,7 +5656,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="40" t="s">
+      <c r="AN46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5668,11 +5687,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="35"/>
-      <c r="BD46" s="35"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I47" s="41"/>
+      <c r="BC46" s="64"/>
+      <c r="BD46" s="64"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I47" s="36"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5707,17 +5726,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="75"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="76"/>
-      <c r="AG47" s="76"/>
-      <c r="AH47" s="76"/>
-      <c r="AI47" s="77"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="45"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="45"/>
+      <c r="AI47" s="46"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="41"/>
+      <c r="AN47" s="36"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5746,11 +5765,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="35"/>
-      <c r="BD47" s="35"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I48" s="40" t="s">
+      <c r="BC47" s="64"/>
+      <c r="BD47" s="64"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5781,10 +5800,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="40">
+      <c r="X48" s="35">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="46">
+      <c r="Y48" s="42">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5815,7 +5834,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="40" t="s">
+      <c r="AN48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5846,11 +5865,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="35"/>
-      <c r="BD48" s="35"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I49" s="41"/>
+      <c r="BC48" s="64"/>
+      <c r="BD48" s="64"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I49" s="36"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5879,8 +5898,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="47"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="43"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5909,7 +5928,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="41"/>
+      <c r="AN49" s="36"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5938,12 +5957,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="35"/>
-      <c r="BD49" s="35"/>
-    </row>
-    <row r="50" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="BC49" s="64"/>
+      <c r="BD49" s="64"/>
+    </row>
+    <row r="50" spans="8:56" x14ac:dyDescent="0.25">
       <c r="H50" s="10"/>
-      <c r="I50" s="40">
+      <c r="I50" s="35">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -5958,14 +5977,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="43" t="s">
+      <c r="N50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="45"/>
+      <c r="O50" s="48"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="48"/>
+      <c r="R50" s="48"/>
+      <c r="S50" s="49"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -5980,17 +5999,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="75"/>
-      <c r="AE50" s="76"/>
-      <c r="AF50" s="76"/>
-      <c r="AG50" s="76"/>
-      <c r="AH50" s="76"/>
-      <c r="AI50" s="77"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="45"/>
+      <c r="AI50" s="46"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="40">
+      <c r="AN50" s="35">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6001,23 +6020,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="43" t="s">
+      <c r="AS50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="44"/>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="44"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="45"/>
+      <c r="AT50" s="48"/>
+      <c r="AU50" s="48"/>
+      <c r="AV50" s="48"/>
+      <c r="AW50" s="48"/>
+      <c r="AX50" s="49"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="35"/>
-      <c r="BD50" s="35"/>
-    </row>
-    <row r="51" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I51" s="41"/>
+      <c r="BC50" s="64"/>
+      <c r="BD50" s="64"/>
+    </row>
+    <row r="51" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I51" s="36"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6030,14 +6049,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="43" t="s">
+      <c r="N51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="45"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="49"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6046,10 +6065,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="40">
+      <c r="X51" s="35">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="52">
+      <c r="Y51" s="40">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6080,7 +6099,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="41"/>
+      <c r="AN51" s="36"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6089,23 +6108,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="43" t="s">
+      <c r="AS51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="44"/>
-      <c r="AU51" s="44"/>
-      <c r="AV51" s="44"/>
-      <c r="AW51" s="44"/>
-      <c r="AX51" s="45"/>
+      <c r="AT51" s="48"/>
+      <c r="AU51" s="48"/>
+      <c r="AV51" s="48"/>
+      <c r="AW51" s="48"/>
+      <c r="AX51" s="49"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="35"/>
-      <c r="BD51" s="35"/>
-    </row>
-    <row r="52" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I52" s="40">
+      <c r="BC51" s="64"/>
+      <c r="BD51" s="64"/>
+    </row>
+    <row r="52" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I52" s="35">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6136,8 +6155,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="53"/>
+      <c r="X52" s="36"/>
+      <c r="Y52" s="41"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6166,7 +6185,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="40">
+      <c r="AN52" s="35">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6189,11 +6208,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="36"/>
-      <c r="BD52" s="36"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I53" s="41"/>
+      <c r="BC52" s="65"/>
+      <c r="BD52" s="65"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I53" s="36"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6228,17 +6247,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="75"/>
-      <c r="AE53" s="76"/>
-      <c r="AF53" s="76"/>
-      <c r="AG53" s="76"/>
-      <c r="AH53" s="76"/>
-      <c r="AI53" s="77"/>
+      <c r="AD53" s="44"/>
+      <c r="AE53" s="45"/>
+      <c r="AF53" s="45"/>
+      <c r="AG53" s="45"/>
+      <c r="AH53" s="45"/>
+      <c r="AI53" s="46"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="41"/>
+      <c r="AN53" s="36"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6259,11 +6278,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="35"/>
-      <c r="BD53" s="35"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I54" s="40">
+      <c r="BC53" s="64"/>
+      <c r="BD53" s="64"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I54" s="35">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6328,7 +6347,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="40">
+      <c r="AN54" s="35">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6351,11 +6370,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="35"/>
-      <c r="BD54" s="35"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I55" s="41"/>
+      <c r="BC54" s="64"/>
+      <c r="BD54" s="64"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I55" s="36"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6390,17 +6409,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="75"/>
-      <c r="AE55" s="76"/>
-      <c r="AF55" s="76"/>
-      <c r="AG55" s="76"/>
-      <c r="AH55" s="76"/>
-      <c r="AI55" s="77"/>
+      <c r="AD55" s="44"/>
+      <c r="AE55" s="45"/>
+      <c r="AF55" s="45"/>
+      <c r="AG55" s="45"/>
+      <c r="AH55" s="45"/>
+      <c r="AI55" s="46"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="41"/>
+      <c r="AN55" s="36"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6421,10 +6440,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="35"/>
-      <c r="BD55" s="35"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BC55" s="64"/>
+      <c r="BD55" s="64"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6456,10 +6475,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="40">
+      <c r="X56" s="35">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="60">
+      <c r="Y56" s="58">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6513,11 +6532,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="35"/>
-      <c r="BD56" s="35"/>
-    </row>
-    <row r="57" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I57" s="40">
+      <c r="BC56" s="64"/>
+      <c r="BD56" s="64"/>
+    </row>
+    <row r="57" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I57" s="35">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6548,8 +6567,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="41"/>
-      <c r="Y57" s="61"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="59"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6560,14 +6579,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="43" t="s">
+      <c r="AD57" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="44"/>
-      <c r="AF57" s="44"/>
-      <c r="AG57" s="44"/>
-      <c r="AH57" s="44"/>
-      <c r="AI57" s="45"/>
+      <c r="AE57" s="48"/>
+      <c r="AF57" s="48"/>
+      <c r="AG57" s="48"/>
+      <c r="AH57" s="48"/>
+      <c r="AI57" s="49"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6576,7 +6595,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="40">
+      <c r="AN57" s="35">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6599,11 +6618,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="35"/>
-      <c r="BD57" s="35"/>
-    </row>
-    <row r="58" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I58" s="41"/>
+      <c r="BC57" s="64"/>
+      <c r="BD57" s="64"/>
+    </row>
+    <row r="58" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I58" s="36"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6638,17 +6657,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="75"/>
-      <c r="AE58" s="76"/>
-      <c r="AF58" s="76"/>
-      <c r="AG58" s="76"/>
-      <c r="AH58" s="76"/>
-      <c r="AI58" s="77"/>
+      <c r="AD58" s="44"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="46"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="41"/>
+      <c r="AN58" s="36"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6669,11 +6688,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="35"/>
-      <c r="BD58" s="35"/>
-    </row>
-    <row r="59" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I59" s="40">
+      <c r="BC58" s="64"/>
+      <c r="BD58" s="64"/>
+    </row>
+    <row r="59" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I59" s="35">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6738,7 +6757,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="40">
+      <c r="AN59" s="35">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6761,11 +6780,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="35"/>
-      <c r="BD59" s="35"/>
-    </row>
-    <row r="60" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I60" s="41"/>
+      <c r="BC59" s="64"/>
+      <c r="BD59" s="64"/>
+    </row>
+    <row r="60" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I60" s="36"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6800,17 +6819,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="75"/>
-      <c r="AE60" s="76"/>
-      <c r="AF60" s="76"/>
-      <c r="AG60" s="76"/>
-      <c r="AH60" s="76"/>
-      <c r="AI60" s="77"/>
+      <c r="AD60" s="44"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="45"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="45"/>
+      <c r="AI60" s="46"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="41"/>
+      <c r="AN60" s="36"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6831,11 +6850,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="35"/>
-      <c r="BD60" s="35"/>
-    </row>
-    <row r="61" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I61" s="40" t="s">
+      <c r="BC60" s="64"/>
+      <c r="BD60" s="64"/>
+    </row>
+    <row r="61" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6866,10 +6885,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="40">
+      <c r="X61" s="35">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="58">
+      <c r="Y61" s="60">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6900,7 +6919,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="40" t="s">
+      <c r="AN61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6923,11 +6942,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="35"/>
-      <c r="BD61" s="35"/>
-    </row>
-    <row r="62" spans="8:56" x14ac:dyDescent="0.45">
-      <c r="I62" s="41"/>
+      <c r="BC61" s="64"/>
+      <c r="BD61" s="64"/>
+    </row>
+    <row r="62" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I62" s="36"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -6956,8 +6975,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="41"/>
-      <c r="Y62" s="59"/>
+      <c r="X62" s="36"/>
+      <c r="Y62" s="61"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -6986,7 +7005,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="41"/>
+      <c r="AN62" s="36"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7007,11 +7026,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="35"/>
-      <c r="BD62" s="35"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I63" s="40">
+      <c r="BC62" s="64"/>
+      <c r="BD62" s="64"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I63" s="35">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7048,17 +7067,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="75"/>
-      <c r="AE63" s="76"/>
-      <c r="AF63" s="76"/>
-      <c r="AG63" s="76"/>
-      <c r="AH63" s="76"/>
-      <c r="AI63" s="77"/>
+      <c r="AD63" s="44"/>
+      <c r="AE63" s="45"/>
+      <c r="AF63" s="45"/>
+      <c r="AG63" s="45"/>
+      <c r="AH63" s="45"/>
+      <c r="AI63" s="46"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="40">
+      <c r="AN63" s="35">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7081,11 +7100,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="35"/>
-      <c r="BD63" s="35"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I64" s="41"/>
+      <c r="BC63" s="64"/>
+      <c r="BD63" s="64"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I64" s="36"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7148,7 +7167,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="41"/>
+      <c r="AN64" s="36"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7169,11 +7188,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="36"/>
-      <c r="BD64" s="36"/>
-    </row>
-    <row r="65" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I65" s="40">
+      <c r="BC64" s="65"/>
+      <c r="BD64" s="65"/>
+    </row>
+    <row r="65" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I65" s="35">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7202,17 +7221,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="75"/>
-      <c r="AE65" s="76"/>
-      <c r="AF65" s="76"/>
-      <c r="AG65" s="76"/>
-      <c r="AH65" s="76"/>
-      <c r="AI65" s="77"/>
+      <c r="AD65" s="44"/>
+      <c r="AE65" s="45"/>
+      <c r="AF65" s="45"/>
+      <c r="AG65" s="45"/>
+      <c r="AH65" s="45"/>
+      <c r="AI65" s="46"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="40">
+      <c r="AN65" s="35">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7235,11 +7254,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="35"/>
-      <c r="BD65" s="35"/>
-    </row>
-    <row r="66" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I66" s="41"/>
+      <c r="BC65" s="64"/>
+      <c r="BD65" s="64"/>
+    </row>
+    <row r="66" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I66" s="36"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7260,10 +7279,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="40" t="s">
+      <c r="X66" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="54">
+      <c r="Y66" s="56">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7294,7 +7313,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="41"/>
+      <c r="AN66" s="36"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7315,10 +7334,10 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="35"/>
-      <c r="BD66" s="35"/>
-    </row>
-    <row r="67" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="BC66" s="64"/>
+      <c r="BD66" s="64"/>
+    </row>
+    <row r="67" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
@@ -7342,8 +7361,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="41"/>
-      <c r="Y67" s="55"/>
+      <c r="X67" s="36"/>
+      <c r="Y67" s="57"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7395,11 +7414,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="35"/>
-      <c r="BD67" s="35"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I68" s="40">
+      <c r="BC67" s="64"/>
+      <c r="BD67" s="64"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I68" s="35">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7428,17 +7447,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="76"/>
-      <c r="AG68" s="76"/>
-      <c r="AH68" s="76"/>
-      <c r="AI68" s="77"/>
+      <c r="AD68" s="44"/>
+      <c r="AE68" s="45"/>
+      <c r="AF68" s="45"/>
+      <c r="AG68" s="45"/>
+      <c r="AH68" s="45"/>
+      <c r="AI68" s="46"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="40">
+      <c r="AN68" s="35">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7461,11 +7480,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="35"/>
-      <c r="BD68" s="35"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I69" s="41"/>
+      <c r="BC68" s="64"/>
+      <c r="BD68" s="64"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I69" s="36"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7486,10 +7505,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="40" t="s">
+      <c r="X69" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="54">
+      <c r="Y69" s="56">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7520,7 +7539,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="41"/>
+      <c r="AN69" s="36"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7541,18 +7560,22 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="35"/>
-      <c r="BD69" s="35"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BC69" s="64"/>
+      <c r="BD69" s="64"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
       <c r="J70" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K70" s="6"/>
-      <c r="L70" s="19"/>
+      <c r="K70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L70">
+        <v>2</v>
+      </c>
       <c r="M70" s="6" t="s">
         <v>13</v>
       </c>
@@ -7564,12 +7587,16 @@
       <c r="Q70" s="38"/>
       <c r="R70" s="38"/>
       <c r="S70" s="39"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="6"/>
+      <c r="T70" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U70" s="7">
+        <v>45912</v>
+      </c>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="41"/>
-      <c r="Y70" s="55"/>
+      <c r="X70" s="36"/>
+      <c r="Y70" s="57"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7621,18 +7648,22 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="35"/>
-      <c r="BD70" s="35"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I71" s="40">
+      <c r="BC70" s="64"/>
+      <c r="BD70" s="64"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="35">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K71" s="6"/>
-      <c r="L71" s="19"/>
+      <c r="K71" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L71" s="19">
+        <v>2</v>
+      </c>
       <c r="M71" s="6" t="s">
         <v>13</v>
       </c>
@@ -7644,8 +7675,12 @@
       <c r="Q71" s="38"/>
       <c r="R71" s="38"/>
       <c r="S71" s="39"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="6"/>
+      <c r="T71" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U71" s="7">
+        <v>45912</v>
+      </c>
       <c r="V71" s="20"/>
       <c r="W71" s="20"/>
       <c r="X71" s="6"/>
@@ -7654,17 +7689,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="75"/>
-      <c r="AE71" s="76"/>
-      <c r="AF71" s="76"/>
-      <c r="AG71" s="76"/>
-      <c r="AH71" s="76"/>
-      <c r="AI71" s="77"/>
+      <c r="AD71" s="44"/>
+      <c r="AE71" s="45"/>
+      <c r="AF71" s="45"/>
+      <c r="AG71" s="45"/>
+      <c r="AH71" s="45"/>
+      <c r="AI71" s="46"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="40">
+      <c r="AN71" s="35">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7687,16 +7722,20 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="35"/>
-      <c r="BD71" s="35"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I72" s="41"/>
+      <c r="BC71" s="64"/>
+      <c r="BD71" s="64"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I72" s="36"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K72" s="6"/>
-      <c r="L72" s="19"/>
+      <c r="K72" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L72" s="19">
+        <v>2</v>
+      </c>
       <c r="M72" s="6" t="s">
         <v>13</v>
       </c>
@@ -7708,14 +7747,18 @@
       <c r="Q72" s="38"/>
       <c r="R72" s="38"/>
       <c r="S72" s="39"/>
-      <c r="T72" s="7"/>
-      <c r="U72" s="6"/>
+      <c r="T72" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U72" s="7">
+        <v>45912</v>
+      </c>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="40">
+      <c r="X72" s="35">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="52">
+      <c r="Y72" s="40">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7730,14 +7773,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="43" t="s">
+      <c r="AD72" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
-      <c r="AH72" s="44"/>
-      <c r="AI72" s="45"/>
+      <c r="AE72" s="48"/>
+      <c r="AF72" s="48"/>
+      <c r="AG72" s="48"/>
+      <c r="AH72" s="48"/>
+      <c r="AI72" s="49"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7746,7 +7789,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="41"/>
+      <c r="AN72" s="36"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7767,35 +7810,43 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="35"/>
-      <c r="BD72" s="35"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I73" s="40">
+      <c r="BC72" s="64"/>
+      <c r="BD72" s="64"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K73" s="6"/>
-      <c r="L73" s="19"/>
+      <c r="K73" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L73" s="19">
+        <v>3</v>
+      </c>
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="43" t="s">
+      <c r="N73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
-      <c r="R73" s="44"/>
-      <c r="S73" s="45"/>
-      <c r="T73" s="7"/>
-      <c r="U73" s="6"/>
+      <c r="O73" s="48"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="48"/>
+      <c r="R73" s="48"/>
+      <c r="S73" s="49"/>
+      <c r="T73" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U73" s="7">
+        <v>45912</v>
+      </c>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="41"/>
-      <c r="Y73" s="53"/>
+      <c r="X73" s="36"/>
+      <c r="Y73" s="41"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7808,14 +7859,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="43" t="s">
+      <c r="AD73" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
-      <c r="AH73" s="44"/>
-      <c r="AI73" s="45"/>
+      <c r="AE73" s="48"/>
+      <c r="AF73" s="48"/>
+      <c r="AG73" s="48"/>
+      <c r="AH73" s="48"/>
+      <c r="AI73" s="49"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7824,7 +7875,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="40">
+      <c r="AN73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7835,28 +7886,32 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="43" t="s">
+      <c r="AS73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="44"/>
-      <c r="AU73" s="44"/>
-      <c r="AV73" s="44"/>
-      <c r="AW73" s="44"/>
-      <c r="AX73" s="45"/>
+      <c r="AT73" s="48"/>
+      <c r="AU73" s="48"/>
+      <c r="AV73" s="48"/>
+      <c r="AW73" s="48"/>
+      <c r="AX73" s="49"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="35"/>
-      <c r="BD73" s="35"/>
-    </row>
-    <row r="74" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I74" s="41"/>
+      <c r="BC73" s="64"/>
+      <c r="BD73" s="64"/>
+    </row>
+    <row r="74" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I74" s="36"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K74" s="6"/>
-      <c r="L74" s="19"/>
+      <c r="K74" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L74" s="19">
+        <v>3</v>
+      </c>
       <c r="M74" s="6" t="s">
         <v>13</v>
       </c>
@@ -7868,8 +7923,12 @@
       <c r="Q74" s="38"/>
       <c r="R74" s="38"/>
       <c r="S74" s="39"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="6"/>
+      <c r="T74" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U74" s="7">
+        <v>45912</v>
+      </c>
       <c r="V74" s="20"/>
       <c r="W74" s="20"/>
       <c r="X74" s="6"/>
@@ -7878,17 +7937,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="75"/>
-      <c r="AE74" s="76"/>
-      <c r="AF74" s="76"/>
-      <c r="AG74" s="76"/>
-      <c r="AH74" s="76"/>
-      <c r="AI74" s="77"/>
+      <c r="AD74" s="44"/>
+      <c r="AE74" s="45"/>
+      <c r="AF74" s="45"/>
+      <c r="AG74" s="45"/>
+      <c r="AH74" s="45"/>
+      <c r="AI74" s="46"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="41"/>
+      <c r="AN74" s="36"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7909,37 +7968,45 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="35"/>
-      <c r="BD74" s="35"/>
-    </row>
-    <row r="75" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I75" s="40">
+      <c r="BC74" s="64"/>
+      <c r="BD74" s="64"/>
+    </row>
+    <row r="75" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="K75" s="6"/>
-      <c r="L75" s="19"/>
+      <c r="K75" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L75" s="19">
+        <v>3</v>
+      </c>
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="43" t="s">
+      <c r="N75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="44"/>
-      <c r="P75" s="44"/>
-      <c r="Q75" s="44"/>
-      <c r="R75" s="44"/>
-      <c r="S75" s="45"/>
-      <c r="T75" s="7"/>
-      <c r="U75" s="6"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="49"/>
+      <c r="T75" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U75" s="7">
+        <v>45912</v>
+      </c>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="40">
+      <c r="X75" s="35">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="60">
+      <c r="Y75" s="58">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -7970,7 +8037,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="40">
+      <c r="AN75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -7981,28 +8048,32 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="43" t="s">
+      <c r="AS75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="44"/>
-      <c r="AU75" s="44"/>
-      <c r="AV75" s="44"/>
-      <c r="AW75" s="44"/>
-      <c r="AX75" s="45"/>
+      <c r="AT75" s="48"/>
+      <c r="AU75" s="48"/>
+      <c r="AV75" s="48"/>
+      <c r="AW75" s="48"/>
+      <c r="AX75" s="49"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="35"/>
-      <c r="BD75" s="35"/>
-    </row>
-    <row r="76" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I76" s="41"/>
+      <c r="BC75" s="64"/>
+      <c r="BD75" s="64"/>
+    </row>
+    <row r="76" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I76" s="36"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="K76" s="6"/>
-      <c r="L76" s="19"/>
+      <c r="K76" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L76" s="19">
+        <v>3</v>
+      </c>
       <c r="M76" s="6" t="s">
         <v>13</v>
       </c>
@@ -8014,12 +8085,16 @@
       <c r="Q76" s="38"/>
       <c r="R76" s="38"/>
       <c r="S76" s="39"/>
-      <c r="T76" s="7"/>
-      <c r="U76" s="6"/>
+      <c r="T76" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U76" s="7">
+        <v>45912</v>
+      </c>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="41"/>
-      <c r="Y76" s="61"/>
+      <c r="X76" s="36"/>
+      <c r="Y76" s="59"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8048,7 +8123,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="41"/>
+      <c r="AN76" s="36"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8069,18 +8144,22 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="36"/>
-      <c r="BD76" s="36"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I77" s="40">
+      <c r="BC76" s="65"/>
+      <c r="BD76" s="65"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I77" s="35">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K77" s="6"/>
-      <c r="L77" s="19"/>
+      <c r="K77" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L77" s="19">
+        <v>3</v>
+      </c>
       <c r="M77" s="6" t="s">
         <v>13</v>
       </c>
@@ -8092,8 +8171,12 @@
       <c r="Q77" s="38"/>
       <c r="R77" s="38"/>
       <c r="S77" s="39"/>
-      <c r="T77" s="7"/>
-      <c r="U77" s="6"/>
+      <c r="T77" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U77" s="7">
+        <v>45912</v>
+      </c>
       <c r="V77" s="20"/>
       <c r="W77" s="20"/>
       <c r="X77" s="6"/>
@@ -8102,17 +8185,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="75"/>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="76"/>
-      <c r="AG77" s="76"/>
-      <c r="AH77" s="76"/>
-      <c r="AI77" s="77"/>
+      <c r="AD77" s="44"/>
+      <c r="AE77" s="45"/>
+      <c r="AF77" s="45"/>
+      <c r="AG77" s="45"/>
+      <c r="AH77" s="45"/>
+      <c r="AI77" s="46"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="40">
+      <c r="AN77" s="35">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8135,16 +8218,20 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="35"/>
-      <c r="BD77" s="35"/>
-    </row>
-    <row r="78" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I78" s="41"/>
+      <c r="BC77" s="64"/>
+      <c r="BD77" s="64"/>
+    </row>
+    <row r="78" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I78" s="36"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K78" s="6"/>
-      <c r="L78" s="19"/>
+      <c r="K78" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L78" s="19">
+        <v>3</v>
+      </c>
       <c r="M78" s="6" t="s">
         <v>13</v>
       </c>
@@ -8156,14 +8243,18 @@
       <c r="Q78" s="38"/>
       <c r="R78" s="38"/>
       <c r="S78" s="39"/>
-      <c r="T78" s="7"/>
-      <c r="U78" s="6"/>
+      <c r="T78" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U78" s="7">
+        <v>45912</v>
+      </c>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="40">
+      <c r="X78" s="35">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="52">
+      <c r="Y78" s="40">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8194,7 +8285,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="41"/>
+      <c r="AN78" s="36"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8215,11 +8306,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="35"/>
-      <c r="BD78" s="35"/>
-    </row>
-    <row r="79" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I79" s="40">
+      <c r="BC78" s="64"/>
+      <c r="BD78" s="64"/>
+    </row>
+    <row r="79" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I79" s="35">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8230,20 +8321,20 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="43" t="s">
+      <c r="N79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
-      <c r="R79" s="44"/>
-      <c r="S79" s="45"/>
-      <c r="T79" s="7"/>
-      <c r="U79" s="6"/>
+      <c r="O79" s="48"/>
+      <c r="P79" s="48"/>
+      <c r="Q79" s="48"/>
+      <c r="R79" s="48"/>
+      <c r="S79" s="49"/>
+      <c r="T79" s="8"/>
+      <c r="U79" s="7"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="41"/>
-      <c r="Y79" s="53"/>
+      <c r="X79" s="36"/>
+      <c r="Y79" s="41"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8272,7 +8363,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="40">
+      <c r="AN79" s="35">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8283,23 +8374,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="43" t="s">
+      <c r="AS79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="44"/>
-      <c r="AU79" s="44"/>
-      <c r="AV79" s="44"/>
-      <c r="AW79" s="44"/>
-      <c r="AX79" s="45"/>
+      <c r="AT79" s="48"/>
+      <c r="AU79" s="48"/>
+      <c r="AV79" s="48"/>
+      <c r="AW79" s="48"/>
+      <c r="AX79" s="49"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="35"/>
-      <c r="BD79" s="35"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I80" s="41"/>
+      <c r="BC79" s="64"/>
+      <c r="BD79" s="64"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I80" s="36"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8326,17 +8417,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="75"/>
-      <c r="AE80" s="76"/>
-      <c r="AF80" s="76"/>
-      <c r="AG80" s="76"/>
-      <c r="AH80" s="76"/>
-      <c r="AI80" s="77"/>
+      <c r="AD80" s="44"/>
+      <c r="AE80" s="45"/>
+      <c r="AF80" s="45"/>
+      <c r="AG80" s="45"/>
+      <c r="AH80" s="45"/>
+      <c r="AI80" s="46"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="41"/>
+      <c r="AN80" s="36"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8357,11 +8448,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="35"/>
-      <c r="BD80" s="35"/>
-    </row>
-    <row r="81" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I81" s="40">
+      <c r="BC80" s="64"/>
+      <c r="BD80" s="64"/>
+    </row>
+    <row r="81" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I81" s="35">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8418,7 +8509,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="40">
+      <c r="AN81" s="35">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8441,11 +8532,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="35"/>
-      <c r="BD81" s="35"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I82" s="41"/>
+      <c r="BC81" s="64"/>
+      <c r="BD81" s="64"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I82" s="36"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8454,14 +8545,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="43" t="s">
+      <c r="N82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="44"/>
-      <c r="P82" s="44"/>
-      <c r="Q82" s="44"/>
-      <c r="R82" s="44"/>
-      <c r="S82" s="45"/>
+      <c r="O82" s="48"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="48"/>
+      <c r="R82" s="48"/>
+      <c r="S82" s="49"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8472,17 +8563,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="75"/>
-      <c r="AE82" s="76"/>
-      <c r="AF82" s="76"/>
-      <c r="AG82" s="76"/>
-      <c r="AH82" s="76"/>
-      <c r="AI82" s="77"/>
+      <c r="AD82" s="44"/>
+      <c r="AE82" s="45"/>
+      <c r="AF82" s="45"/>
+      <c r="AG82" s="45"/>
+      <c r="AH82" s="45"/>
+      <c r="AI82" s="46"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="41"/>
+      <c r="AN82" s="36"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8491,23 +8582,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="43" t="s">
+      <c r="AS82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="44"/>
-      <c r="AU82" s="44"/>
-      <c r="AV82" s="44"/>
-      <c r="AW82" s="44"/>
-      <c r="AX82" s="45"/>
+      <c r="AT82" s="48"/>
+      <c r="AU82" s="48"/>
+      <c r="AV82" s="48"/>
+      <c r="AW82" s="48"/>
+      <c r="AX82" s="49"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="35"/>
-      <c r="BD82" s="35"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I83" s="40">
+      <c r="BC82" s="64"/>
+      <c r="BD82" s="64"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I83" s="35">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8538,10 +8629,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="40">
+      <c r="X83" s="35">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="54">
+      <c r="Y83" s="56">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8572,7 +8663,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="40">
+      <c r="AN83" s="35">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8601,11 +8692,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="35"/>
-      <c r="BD83" s="35"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I84" s="41"/>
+      <c r="BC83" s="64"/>
+      <c r="BD83" s="64"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I84" s="36"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8634,8 +8725,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="41"/>
-      <c r="Y84" s="55"/>
+      <c r="X84" s="36"/>
+      <c r="Y84" s="57"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8664,7 +8755,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="41"/>
+      <c r="AN84" s="36"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8691,10 +8782,10 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="35"/>
-      <c r="BD84" s="35"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="BC84" s="64"/>
+      <c r="BD84" s="64"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
@@ -8724,12 +8815,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="75"/>
-      <c r="AE85" s="76"/>
-      <c r="AF85" s="76"/>
-      <c r="AG85" s="76"/>
-      <c r="AH85" s="76"/>
-      <c r="AI85" s="77"/>
+      <c r="AD85" s="44"/>
+      <c r="AE85" s="45"/>
+      <c r="AF85" s="45"/>
+      <c r="AG85" s="45"/>
+      <c r="AH85" s="45"/>
+      <c r="AI85" s="46"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8757,18 +8848,22 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="35"/>
-      <c r="BD85" s="35"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I86" s="40">
+      <c r="BC85" s="64"/>
+      <c r="BD85" s="64"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I86" s="35">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K86" s="6"/>
-      <c r="L86" s="19"/>
+      <c r="K86" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L86" s="19">
+        <v>3</v>
+      </c>
       <c r="M86" s="6" t="s">
         <v>13</v>
       </c>
@@ -8780,14 +8875,18 @@
       <c r="Q86" s="38"/>
       <c r="R86" s="38"/>
       <c r="S86" s="39"/>
-      <c r="T86" s="7"/>
-      <c r="U86" s="6"/>
+      <c r="T86" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U86" s="7">
+        <v>45912</v>
+      </c>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="40">
+      <c r="X86" s="35">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="56">
+      <c r="Y86" s="50">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8818,7 +8917,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="40">
+      <c r="AN86" s="35">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8841,16 +8940,20 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="35"/>
-      <c r="BD86" s="35"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="I87" s="41"/>
+      <c r="BC86" s="64"/>
+      <c r="BD86" s="64"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I87" s="36"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K87" s="6"/>
-      <c r="L87" s="19"/>
+      <c r="K87" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L87" s="19">
+        <v>3</v>
+      </c>
       <c r="M87" s="6" t="s">
         <v>13</v>
       </c>
@@ -8862,12 +8965,16 @@
       <c r="Q87" s="38"/>
       <c r="R87" s="38"/>
       <c r="S87" s="39"/>
-      <c r="T87" s="7"/>
-      <c r="U87" s="6"/>
+      <c r="T87" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U87" s="7">
+        <v>45912</v>
+      </c>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="41"/>
-      <c r="Y87" s="57"/>
+      <c r="X87" s="36"/>
+      <c r="Y87" s="51"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8896,7 +9003,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="41"/>
+      <c r="AN87" s="36"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8917,18 +9024,22 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="35"/>
-      <c r="BD87" s="35"/>
-    </row>
-    <row r="88" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I88" s="40" t="s">
+      <c r="BC87" s="64"/>
+      <c r="BD87" s="64"/>
+    </row>
+    <row r="88" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K88" s="6"/>
-      <c r="L88" s="19"/>
+      <c r="K88" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L88" s="19">
+        <v>3</v>
+      </c>
       <c r="M88" s="6" t="s">
         <v>13</v>
       </c>
@@ -8940,8 +9051,12 @@
       <c r="Q88" s="38"/>
       <c r="R88" s="38"/>
       <c r="S88" s="39"/>
-      <c r="T88" s="7"/>
-      <c r="U88" s="6"/>
+      <c r="T88" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U88" s="7">
+        <v>45912</v>
+      </c>
       <c r="V88" s="20"/>
       <c r="W88" s="20"/>
       <c r="X88" s="6"/>
@@ -8950,17 +9065,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="75"/>
-      <c r="AE88" s="76"/>
-      <c r="AF88" s="76"/>
-      <c r="AG88" s="76"/>
-      <c r="AH88" s="76"/>
-      <c r="AI88" s="77"/>
+      <c r="AD88" s="44"/>
+      <c r="AE88" s="45"/>
+      <c r="AF88" s="45"/>
+      <c r="AG88" s="45"/>
+      <c r="AH88" s="45"/>
+      <c r="AI88" s="46"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="40" t="s">
+      <c r="AN88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -8983,16 +9098,20 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="36"/>
-      <c r="BD88" s="36"/>
-    </row>
-    <row r="89" spans="9:56" x14ac:dyDescent="0.45">
-      <c r="I89" s="41"/>
+      <c r="BC88" s="65"/>
+      <c r="BD88" s="65"/>
+    </row>
+    <row r="89" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I89" s="36"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="K89" s="6"/>
-      <c r="L89" s="19"/>
+      <c r="K89" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L89" s="19">
+        <v>3</v>
+      </c>
       <c r="M89" s="6" t="s">
         <v>13</v>
       </c>
@@ -9004,14 +9123,18 @@
       <c r="Q89" s="38"/>
       <c r="R89" s="38"/>
       <c r="S89" s="39"/>
-      <c r="T89" s="7"/>
-      <c r="U89" s="6"/>
+      <c r="T89" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U89" s="7">
+        <v>45912</v>
+      </c>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="40" t="s">
+      <c r="X89" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="56">
+      <c r="Y89" s="50">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9042,7 +9165,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="41"/>
+      <c r="AN89" s="36"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9063,10 +9186,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="35"/>
-      <c r="BD89" s="35"/>
-    </row>
-    <row r="90" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="BC89" s="64"/>
+      <c r="BD89" s="64"/>
+    </row>
+    <row r="90" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9078,20 +9201,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="42" t="s">
+      <c r="N90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="42"/>
-      <c r="P90" s="42"/>
-      <c r="Q90" s="42"/>
-      <c r="R90" s="42"/>
-      <c r="S90" s="42"/>
+      <c r="O90" s="52"/>
+      <c r="P90" s="52"/>
+      <c r="Q90" s="52"/>
+      <c r="R90" s="52"/>
+      <c r="S90" s="52"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="41"/>
-      <c r="Y90" s="57"/>
+      <c r="X90" s="36"/>
+      <c r="Y90" s="51"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9131,22 +9254,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="42" t="s">
+      <c r="AS90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="42"/>
-      <c r="AU90" s="42"/>
-      <c r="AV90" s="42"/>
-      <c r="AW90" s="42"/>
-      <c r="AX90" s="42"/>
+      <c r="AT90" s="52"/>
+      <c r="AU90" s="52"/>
+      <c r="AV90" s="52"/>
+      <c r="AW90" s="52"/>
+      <c r="AX90" s="52"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="35"/>
-      <c r="BD90" s="35"/>
-    </row>
-    <row r="91" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="BC90" s="64"/>
+      <c r="BD90" s="64"/>
+    </row>
+    <row r="91" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9168,12 +9291,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="75"/>
-      <c r="AE91" s="76"/>
-      <c r="AF91" s="76"/>
-      <c r="AG91" s="76"/>
-      <c r="AH91" s="76"/>
-      <c r="AI91" s="77"/>
+      <c r="AD91" s="44"/>
+      <c r="AE91" s="45"/>
+      <c r="AF91" s="45"/>
+      <c r="AG91" s="45"/>
+      <c r="AH91" s="45"/>
+      <c r="AI91" s="46"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9196,7 +9319,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="92" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9212,10 +9335,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="40">
+      <c r="X92" s="35">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="60">
+      <c r="Y92" s="58">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9264,7 +9387,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="93" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9280,8 +9403,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="41"/>
-      <c r="Y93" s="61"/>
+      <c r="X93" s="36"/>
+      <c r="Y93" s="59"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9328,7 +9451,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9350,12 +9473,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="75"/>
-      <c r="AE94" s="76"/>
-      <c r="AF94" s="76"/>
-      <c r="AG94" s="76"/>
-      <c r="AH94" s="76"/>
-      <c r="AI94" s="77"/>
+      <c r="AD94" s="44"/>
+      <c r="AE94" s="45"/>
+      <c r="AF94" s="45"/>
+      <c r="AG94" s="45"/>
+      <c r="AH94" s="45"/>
+      <c r="AI94" s="46"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9378,7 +9501,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="95" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9394,10 +9517,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="40">
+      <c r="X95" s="35">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="58">
+      <c r="Y95" s="60">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9438,7 +9561,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="96" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9454,8 +9577,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="41"/>
-      <c r="Y96" s="59"/>
+      <c r="X96" s="36"/>
+      <c r="Y96" s="61"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9494,7 +9617,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9516,12 +9639,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="75"/>
-      <c r="AE97" s="76"/>
-      <c r="AF97" s="76"/>
-      <c r="AG97" s="76"/>
-      <c r="AH97" s="76"/>
-      <c r="AI97" s="77"/>
+      <c r="AD97" s="44"/>
+      <c r="AE97" s="45"/>
+      <c r="AF97" s="45"/>
+      <c r="AG97" s="45"/>
+      <c r="AH97" s="45"/>
+      <c r="AI97" s="46"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9544,7 +9667,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="98" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9604,7 +9727,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="99" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9626,12 +9749,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="75"/>
-      <c r="AE99" s="76"/>
-      <c r="AF99" s="76"/>
-      <c r="AG99" s="76"/>
-      <c r="AH99" s="76"/>
-      <c r="AI99" s="77"/>
+      <c r="AD99" s="44"/>
+      <c r="AE99" s="45"/>
+      <c r="AF99" s="45"/>
+      <c r="AG99" s="45"/>
+      <c r="AH99" s="45"/>
+      <c r="AI99" s="46"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9654,7 +9777,7 @@
       <c r="BC99" s="20"/>
       <c r="BD99" s="20"/>
     </row>
-    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -9670,10 +9793,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="40">
+      <c r="X100" s="35">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="52">
+      <c r="Y100" s="40">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9716,7 +9839,7 @@
       <c r="BC100" s="20"/>
       <c r="BD100" s="20"/>
     </row>
-    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -9732,8 +9855,8 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="41"/>
-      <c r="Y101" s="53"/>
+      <c r="X101" s="36"/>
+      <c r="Y101" s="41"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
@@ -9774,7 +9897,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="102" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -9796,12 +9919,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="75"/>
-      <c r="AE102" s="76"/>
-      <c r="AF102" s="76"/>
-      <c r="AG102" s="76"/>
-      <c r="AH102" s="76"/>
-      <c r="AI102" s="77"/>
+      <c r="AD102" s="44"/>
+      <c r="AE102" s="45"/>
+      <c r="AF102" s="45"/>
+      <c r="AG102" s="45"/>
+      <c r="AH102" s="45"/>
+      <c r="AI102" s="46"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9824,7 +9947,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -9884,7 +10007,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="104" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -9906,12 +10029,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="75"/>
-      <c r="AE104" s="76"/>
-      <c r="AF104" s="76"/>
-      <c r="AG104" s="76"/>
-      <c r="AH104" s="76"/>
-      <c r="AI104" s="77"/>
+      <c r="AD104" s="44"/>
+      <c r="AE104" s="45"/>
+      <c r="AF104" s="45"/>
+      <c r="AG104" s="45"/>
+      <c r="AH104" s="45"/>
+      <c r="AI104" s="46"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -9934,7 +10057,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -9951,10 +10074,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="40">
+      <c r="X105" s="35">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="56">
+      <c r="Y105" s="50">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -9995,7 +10118,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -10011,8 +10134,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="41"/>
-      <c r="Y106" s="57"/>
+      <c r="X106" s="36"/>
+      <c r="Y106" s="51"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10051,7 +10174,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10073,12 +10196,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="75"/>
-      <c r="AE107" s="76"/>
-      <c r="AF107" s="76"/>
-      <c r="AG107" s="76"/>
-      <c r="AH107" s="76"/>
-      <c r="AI107" s="77"/>
+      <c r="AD107" s="44"/>
+      <c r="AE107" s="45"/>
+      <c r="AF107" s="45"/>
+      <c r="AG107" s="45"/>
+      <c r="AH107" s="45"/>
+      <c r="AI107" s="46"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10101,7 +10224,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="108" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10117,10 +10240,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="40">
+      <c r="X108" s="35">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="56">
+      <c r="Y108" s="50">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10131,14 +10254,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="43" t="s">
+      <c r="AD108" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="44"/>
-      <c r="AF108" s="44"/>
-      <c r="AG108" s="44"/>
-      <c r="AH108" s="44"/>
-      <c r="AI108" s="45"/>
+      <c r="AE108" s="48"/>
+      <c r="AF108" s="48"/>
+      <c r="AG108" s="48"/>
+      <c r="AH108" s="48"/>
+      <c r="AI108" s="49"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10161,7 +10284,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10177,8 +10300,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="41"/>
-      <c r="Y109" s="57"/>
+      <c r="X109" s="36"/>
+      <c r="Y109" s="51"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10217,7 +10340,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="110" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10239,12 +10362,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="75"/>
-      <c r="AE110" s="76"/>
-      <c r="AF110" s="76"/>
-      <c r="AG110" s="76"/>
-      <c r="AH110" s="76"/>
-      <c r="AI110" s="77"/>
+      <c r="AD110" s="44"/>
+      <c r="AE110" s="45"/>
+      <c r="AF110" s="45"/>
+      <c r="AG110" s="45"/>
+      <c r="AH110" s="45"/>
+      <c r="AI110" s="46"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10267,7 +10390,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" x14ac:dyDescent="0.45">
+    <row r="111" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10283,10 +10406,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="40">
+      <c r="X111" s="35">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="56">
+      <c r="Y111" s="50">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10297,14 +10420,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="43" t="s">
+      <c r="AD111" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="44"/>
-      <c r="AF111" s="44"/>
-      <c r="AG111" s="44"/>
-      <c r="AH111" s="44"/>
-      <c r="AI111" s="45"/>
+      <c r="AE111" s="48"/>
+      <c r="AF111" s="48"/>
+      <c r="AG111" s="48"/>
+      <c r="AH111" s="48"/>
+      <c r="AI111" s="49"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10327,7 +10450,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10343,8 +10466,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="41"/>
-      <c r="Y112" s="57"/>
+      <c r="X112" s="36"/>
+      <c r="Y112" s="51"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10383,7 +10506,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="113" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10405,12 +10528,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="75"/>
-      <c r="AE113" s="76"/>
-      <c r="AF113" s="76"/>
-      <c r="AG113" s="76"/>
-      <c r="AH113" s="76"/>
-      <c r="AI113" s="77"/>
+      <c r="AD113" s="44"/>
+      <c r="AE113" s="45"/>
+      <c r="AF113" s="45"/>
+      <c r="AG113" s="45"/>
+      <c r="AH113" s="45"/>
+      <c r="AI113" s="46"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10433,7 +10556,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10449,10 +10572,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="40">
+      <c r="X114" s="35">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="56">
+      <c r="Y114" s="50">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10493,7 +10616,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10509,8 +10632,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="41"/>
-      <c r="Y115" s="57"/>
+      <c r="X115" s="36"/>
+      <c r="Y115" s="51"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10549,7 +10672,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="116" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10571,12 +10694,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="75"/>
-      <c r="AE116" s="76"/>
-      <c r="AF116" s="76"/>
-      <c r="AG116" s="76"/>
-      <c r="AH116" s="76"/>
-      <c r="AI116" s="77"/>
+      <c r="AD116" s="44"/>
+      <c r="AE116" s="45"/>
+      <c r="AF116" s="45"/>
+      <c r="AG116" s="45"/>
+      <c r="AH116" s="45"/>
+      <c r="AI116" s="46"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10599,7 +10722,7 @@
       <c r="BC116" s="20"/>
       <c r="BD116" s="20"/>
     </row>
-    <row r="117" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="117" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I117" s="20"/>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -10615,10 +10738,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="40">
+      <c r="X117" s="35">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="56">
+      <c r="Y117" s="50">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10631,14 +10754,14 @@
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="43" t="s">
+      <c r="AD117" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="44"/>
-      <c r="AF117" s="44"/>
-      <c r="AG117" s="44"/>
-      <c r="AH117" s="44"/>
-      <c r="AI117" s="45"/>
+      <c r="AE117" s="48"/>
+      <c r="AF117" s="48"/>
+      <c r="AG117" s="48"/>
+      <c r="AH117" s="48"/>
+      <c r="AI117" s="49"/>
       <c r="AJ117" s="19"/>
       <c r="AK117" s="19"/>
       <c r="AL117" s="20"/>
@@ -10661,7 +10784,7 @@
       <c r="BC117" s="20"/>
       <c r="BD117" s="20"/>
     </row>
-    <row r="118" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="118" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I118" s="20"/>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -10677,8 +10800,8 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="41"/>
-      <c r="Y118" s="57"/>
+      <c r="X118" s="36"/>
+      <c r="Y118" s="51"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
@@ -10719,7 +10842,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10741,12 +10864,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="75"/>
-      <c r="AE119" s="76"/>
-      <c r="AF119" s="76"/>
-      <c r="AG119" s="76"/>
-      <c r="AH119" s="76"/>
-      <c r="AI119" s="77"/>
+      <c r="AD119" s="44"/>
+      <c r="AE119" s="45"/>
+      <c r="AF119" s="45"/>
+      <c r="AG119" s="45"/>
+      <c r="AH119" s="45"/>
+      <c r="AI119" s="46"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10769,7 +10892,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -10785,10 +10908,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="40">
+      <c r="X120" s="35">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="54">
+      <c r="Y120" s="56">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10829,7 +10952,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -10845,8 +10968,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="41"/>
-      <c r="Y121" s="55"/>
+      <c r="X121" s="36"/>
+      <c r="Y121" s="57"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10855,14 +10978,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="43" t="s">
+      <c r="AD121" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="44"/>
-      <c r="AF121" s="44"/>
-      <c r="AG121" s="44"/>
-      <c r="AH121" s="44"/>
-      <c r="AI121" s="45"/>
+      <c r="AE121" s="48"/>
+      <c r="AF121" s="48"/>
+      <c r="AG121" s="48"/>
+      <c r="AH121" s="48"/>
+      <c r="AI121" s="49"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10885,7 +11008,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="122" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -10907,12 +11030,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="75"/>
-      <c r="AE122" s="76"/>
-      <c r="AF122" s="76"/>
-      <c r="AG122" s="76"/>
-      <c r="AH122" s="76"/>
-      <c r="AI122" s="77"/>
+      <c r="AD122" s="44"/>
+      <c r="AE122" s="45"/>
+      <c r="AF122" s="45"/>
+      <c r="AG122" s="45"/>
+      <c r="AH122" s="45"/>
+      <c r="AI122" s="46"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -10935,7 +11058,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -10951,10 +11074,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="40">
+      <c r="X123" s="35">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="46">
+      <c r="Y123" s="42">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -11003,7 +11126,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11019,8 +11142,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="41"/>
-      <c r="Y124" s="47"/>
+      <c r="X124" s="36"/>
+      <c r="Y124" s="43"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11067,7 +11190,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11089,12 +11212,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="75"/>
-      <c r="AE125" s="76"/>
-      <c r="AF125" s="76"/>
-      <c r="AG125" s="76"/>
-      <c r="AH125" s="76"/>
-      <c r="AI125" s="77"/>
+      <c r="AD125" s="44"/>
+      <c r="AE125" s="45"/>
+      <c r="AF125" s="45"/>
+      <c r="AG125" s="45"/>
+      <c r="AH125" s="45"/>
+      <c r="AI125" s="46"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11117,7 +11240,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="126" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11136,7 +11259,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="46">
+      <c r="Y126" s="42">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11177,7 +11300,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11194,17 +11317,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="47"/>
+      <c r="Y127" s="43"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="75"/>
-      <c r="AE127" s="76"/>
-      <c r="AF127" s="76"/>
-      <c r="AG127" s="76"/>
-      <c r="AH127" s="76"/>
-      <c r="AI127" s="77"/>
+      <c r="AD127" s="44"/>
+      <c r="AE127" s="45"/>
+      <c r="AF127" s="45"/>
+      <c r="AG127" s="45"/>
+      <c r="AH127" s="45"/>
+      <c r="AI127" s="46"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11227,7 +11350,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11243,10 +11366,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="40">
+      <c r="X128" s="35">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="52">
+      <c r="Y128" s="40">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11287,7 +11410,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11303,8 +11426,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="41"/>
-      <c r="Y129" s="53"/>
+      <c r="X129" s="36"/>
+      <c r="Y129" s="41"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11343,7 +11466,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="130" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11365,12 +11488,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="75"/>
-      <c r="AE130" s="76"/>
-      <c r="AF130" s="76"/>
-      <c r="AG130" s="76"/>
-      <c r="AH130" s="76"/>
-      <c r="AI130" s="77"/>
+      <c r="AD130" s="44"/>
+      <c r="AE130" s="45"/>
+      <c r="AF130" s="45"/>
+      <c r="AG130" s="45"/>
+      <c r="AH130" s="45"/>
+      <c r="AI130" s="46"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11393,7 +11516,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11409,10 +11532,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="40" t="s">
+      <c r="X131" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="46">
+      <c r="Y131" s="42">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11453,7 +11576,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11469,8 +11592,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="41"/>
-      <c r="Y132" s="47"/>
+      <c r="X132" s="36"/>
+      <c r="Y132" s="43"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11509,7 +11632,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11531,12 +11654,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="75"/>
-      <c r="AE133" s="76"/>
-      <c r="AF133" s="76"/>
-      <c r="AG133" s="76"/>
-      <c r="AH133" s="76"/>
-      <c r="AI133" s="77"/>
+      <c r="AD133" s="44"/>
+      <c r="AE133" s="45"/>
+      <c r="AF133" s="45"/>
+      <c r="AG133" s="45"/>
+      <c r="AH133" s="45"/>
+      <c r="AI133" s="46"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11559,7 +11682,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" x14ac:dyDescent="0.45">
+    <row r="134" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11589,14 +11712,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="42" t="s">
+      <c r="AD134" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="42"/>
-      <c r="AF134" s="42"/>
-      <c r="AG134" s="42"/>
-      <c r="AH134" s="42"/>
-      <c r="AI134" s="42"/>
+      <c r="AE134" s="52"/>
+      <c r="AF134" s="52"/>
+      <c r="AG134" s="52"/>
+      <c r="AH134" s="52"/>
+      <c r="AI134" s="52"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11619,60 +11742,590 @@
       <c r="BC134" s="20"/>
       <c r="BD134" s="20"/>
     </row>
-    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G153" s="89"/>
-      <c r="H153" s="89"/>
-    </row>
-    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G153" s="67"/>
+      <c r="H153" s="67"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W192" s="12"/>
     </row>
-    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="AS85:AX85"/>
+    <mergeCell ref="AN86:AN87"/>
+    <mergeCell ref="AS86:AX86"/>
+    <mergeCell ref="AS87:AX87"/>
+    <mergeCell ref="AN88:AN89"/>
+    <mergeCell ref="AS88:AX88"/>
+    <mergeCell ref="AS89:AX89"/>
+    <mergeCell ref="AS90:AX90"/>
+    <mergeCell ref="BC19:BD19"/>
+    <mergeCell ref="BC21:BD21"/>
+    <mergeCell ref="BC22:BD22"/>
+    <mergeCell ref="BC23:BD23"/>
+    <mergeCell ref="BC24:BD24"/>
+    <mergeCell ref="BC25:BD25"/>
+    <mergeCell ref="BC26:BD26"/>
+    <mergeCell ref="BC27:BD27"/>
+    <mergeCell ref="BC28:BD28"/>
+    <mergeCell ref="BC29:BD29"/>
+    <mergeCell ref="BC30:BD30"/>
+    <mergeCell ref="BC31:BD31"/>
+    <mergeCell ref="BC32:BD32"/>
+    <mergeCell ref="BC33:BD33"/>
+    <mergeCell ref="BC34:BD34"/>
+    <mergeCell ref="BC35:BD35"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
     <mergeCell ref="I86:I87"/>
     <mergeCell ref="X131:X132"/>
     <mergeCell ref="X128:X129"/>
@@ -11697,536 +12350,6 @@
     <mergeCell ref="X105:X106"/>
     <mergeCell ref="AD88:AI88"/>
     <mergeCell ref="AD89:AI89"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AS85:AX85"/>
-    <mergeCell ref="AN86:AN87"/>
-    <mergeCell ref="AS86:AX86"/>
-    <mergeCell ref="AS87:AX87"/>
-    <mergeCell ref="AN88:AN89"/>
-    <mergeCell ref="AS88:AX88"/>
-    <mergeCell ref="AS89:AX89"/>
-    <mergeCell ref="AS90:AX90"/>
-    <mergeCell ref="BC19:BD19"/>
-    <mergeCell ref="BC21:BD21"/>
-    <mergeCell ref="BC22:BD22"/>
-    <mergeCell ref="BC23:BD23"/>
-    <mergeCell ref="BC24:BD24"/>
-    <mergeCell ref="BC25:BD25"/>
-    <mergeCell ref="BC26:BD26"/>
-    <mergeCell ref="BC27:BD27"/>
-    <mergeCell ref="BC28:BD28"/>
-    <mergeCell ref="BC29:BD29"/>
-    <mergeCell ref="BC30:BD30"/>
-    <mergeCell ref="BC31:BD31"/>
-    <mergeCell ref="BC32:BD32"/>
-    <mergeCell ref="BC33:BD33"/>
-    <mergeCell ref="BC34:BD34"/>
-    <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C159EEC-DB16-4D4A-B634-5C5570F08074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAE410C-7C32-4B1F-8D6B-B6D1959FC6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1180,11 +1180,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1195,14 +1195,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1213,28 +1225,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1243,10 +1249,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1255,13 +1261,25 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1269,54 +1287,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1333,6 +1303,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1342,19 +1321,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1691,6 +1691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="G2:BD230"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1727,70 +1728,70 @@
   </cols>
   <sheetData>
     <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="69" t="s">
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="82" t="s">
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="83"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="69" t="s">
+      <c r="U2" s="73"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="74"/>
+      <c r="AA2" s="74"/>
+      <c r="AB2" s="74"/>
+      <c r="AC2" s="74"/>
+      <c r="AD2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="81" t="s">
+      <c r="AE2" s="77"/>
+      <c r="AF2" s="77"/>
+      <c r="AG2" s="77"/>
+      <c r="AH2" s="77"/>
+      <c r="AI2" s="78"/>
+      <c r="AJ2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="81"/>
-      <c r="AN2" s="84" t="s">
+      <c r="AK2" s="71"/>
+      <c r="AN2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="84"/>
-      <c r="AP2" s="84"/>
-      <c r="AQ2" s="84"/>
-      <c r="AR2" s="84"/>
-      <c r="AS2" s="85" t="s">
+      <c r="AO2" s="74"/>
+      <c r="AP2" s="74"/>
+      <c r="AQ2" s="74"/>
+      <c r="AR2" s="74"/>
+      <c r="AS2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="85"/>
-      <c r="AU2" s="85"/>
-      <c r="AV2" s="85"/>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="85"/>
-      <c r="AY2" s="81" t="s">
+      <c r="AT2" s="75"/>
+      <c r="AU2" s="75"/>
+      <c r="AV2" s="75"/>
+      <c r="AW2" s="75"/>
+      <c r="AX2" s="75"/>
+      <c r="AY2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="81"/>
-      <c r="BA2" s="81" t="s">
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="81"/>
-      <c r="BC2" s="81" t="s">
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="81"/>
+      <c r="BD2" s="71"/>
     </row>
     <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I3" s="1" t="s">
@@ -1808,12 +1809,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="72"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="74"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="87"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1838,12 +1839,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="88"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="81"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1865,12 +1866,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
+      <c r="AS3" s="75"/>
+      <c r="AT3" s="75"/>
+      <c r="AU3" s="75"/>
+      <c r="AV3" s="75"/>
+      <c r="AW3" s="75"/>
+      <c r="AX3" s="75"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1883,13 +1884,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="81" t="s">
+      <c r="BC3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="81"/>
+      <c r="BD3" s="71"/>
     </row>
     <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I4" s="62">
+      <c r="I4" s="92">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1920,10 +1921,10 @@
       </c>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="40">
+      <c r="X4" s="35">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="50">
+      <c r="Y4" s="88">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1954,7 +1955,7 @@
       </c>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="90">
+      <c r="AN4" s="68">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1983,11 +1984,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
+      <c r="BC4" s="64"/>
+      <c r="BD4" s="64"/>
     </row>
     <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I5" s="63"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2000,7 +2001,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2016,8 +2017,8 @@
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="51"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="89"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2030,14 +2031,14 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="80" t="s">
+      <c r="AD5" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="77"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="46"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
@@ -2046,7 +2047,7 @@
       </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="63"/>
+      <c r="AN5" s="69"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2059,7 +2060,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="65" t="s">
+      <c r="AS5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2073,11 +2074,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="75"/>
-      <c r="BD5" s="77"/>
+      <c r="BC5" s="44"/>
+      <c r="BD5" s="46"/>
     </row>
     <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I6" s="64"/>
+      <c r="I6" s="70"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2106,8 +2107,8 @@
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="79"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="90"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2120,14 +2121,14 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="75" t="s">
+      <c r="AD6" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="76"/>
-      <c r="AI6" s="77"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="46"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
@@ -2136,7 +2137,7 @@
       </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="64"/>
+      <c r="AN6" s="70"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2163,11 +2164,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I7" s="40">
+      <c r="BC6" s="64"/>
+      <c r="BD6" s="64"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I7" s="35">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2204,17 +2205,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="76"/>
-      <c r="AG7" s="76"/>
-      <c r="AH7" s="76"/>
-      <c r="AI7" s="77"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="45"/>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="45"/>
+      <c r="AH7" s="45"/>
+      <c r="AI7" s="46"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="40">
+      <c r="AN7" s="35">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2243,11 +2244,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="35"/>
+      <c r="BC7" s="64"/>
+      <c r="BD7" s="64"/>
     </row>
     <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I8" s="41"/>
+      <c r="I8" s="36"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2276,10 +2277,10 @@
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="42">
+      <c r="X8" s="52">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="50">
+      <c r="Y8" s="88">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2310,7 +2311,7 @@
       </c>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="48"/>
+      <c r="AN8" s="55"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2337,11 +2338,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="35"/>
-      <c r="BD8" s="35"/>
+      <c r="BC8" s="64"/>
+      <c r="BD8" s="64"/>
     </row>
     <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I9" s="40">
+      <c r="I9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2372,8 +2373,8 @@
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="51"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="89"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2402,7 +2403,7 @@
       </c>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="40">
+      <c r="AN9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2431,11 +2432,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="35"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I10" s="41"/>
+      <c r="BC9" s="64"/>
+      <c r="BD9" s="64"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="36"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2470,17 +2471,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="76"/>
-      <c r="AG10" s="76"/>
-      <c r="AH10" s="76"/>
-      <c r="AI10" s="77"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="46"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="48"/>
+      <c r="AN10" s="55"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2507,11 +2508,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="35"/>
-      <c r="BD10" s="35"/>
+      <c r="BC10" s="64"/>
+      <c r="BD10" s="64"/>
     </row>
     <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I11" s="40">
+      <c r="I11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2526,7 +2527,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="65" t="s">
+      <c r="N11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2542,10 +2543,10 @@
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="42">
+      <c r="X11" s="52">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="46">
+      <c r="Y11" s="42">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2576,7 +2577,7 @@
       </c>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="40">
+      <c r="AN11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2591,7 +2592,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="65" t="s">
+      <c r="AS11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2605,11 +2606,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="35"/>
-      <c r="BD11" s="35"/>
+      <c r="BC11" s="64"/>
+      <c r="BD11" s="64"/>
     </row>
     <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I12" s="48"/>
+      <c r="I12" s="55"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2622,7 +2623,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="65" t="s">
+      <c r="N12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2638,8 +2639,8 @@
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="47"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="43"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2668,7 +2669,7 @@
       </c>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="48"/>
+      <c r="AN12" s="55"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2681,7 +2682,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="65" t="s">
+      <c r="AS12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2695,11 +2696,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="35"/>
-      <c r="BD12" s="35"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I13" s="41"/>
+      <c r="BC12" s="64"/>
+      <c r="BD12" s="64"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" s="36"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2734,17 +2735,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="76"/>
-      <c r="AH13" s="76"/>
-      <c r="AI13" s="77"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="45"/>
+      <c r="AH13" s="45"/>
+      <c r="AI13" s="46"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="41"/>
+      <c r="AN13" s="36"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2771,11 +2772,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="35"/>
-      <c r="BD13" s="35"/>
+      <c r="BC13" s="64"/>
+      <c r="BD13" s="64"/>
     </row>
     <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I14" s="40">
+      <c r="I14" s="35">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2806,10 +2807,10 @@
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="42">
+      <c r="X14" s="52">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="52">
+      <c r="Y14" s="40">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2824,7 +2825,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="65" t="s">
+      <c r="AD14" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2840,7 +2841,7 @@
       </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="40">
+      <c r="AN14" s="35">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2869,11 +2870,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="35"/>
+      <c r="BC14" s="64"/>
+      <c r="BD14" s="64"/>
     </row>
     <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I15" s="48"/>
+      <c r="I15" s="55"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2902,8 +2903,8 @@
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="78"/>
+      <c r="X15" s="52"/>
+      <c r="Y15" s="62"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2916,7 +2917,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="65" t="s">
+      <c r="AD15" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2932,7 +2933,7 @@
       </c>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="48"/>
+      <c r="AN15" s="55"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2959,11 +2960,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="35"/>
+      <c r="BC15" s="64"/>
+      <c r="BD15" s="64"/>
     </row>
     <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I16" s="41"/>
+      <c r="I16" s="36"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2992,8 +2993,8 @@
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="53"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="41"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -3022,7 +3023,7 @@
       </c>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="48"/>
+      <c r="AN16" s="55"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3049,11 +3050,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="36"/>
-      <c r="BD16" s="36"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I17" s="92">
+      <c r="BC16" s="65"/>
+      <c r="BD16" s="65"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I17" s="53">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3090,17 +3091,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76"/>
-      <c r="AH17" s="76"/>
-      <c r="AI17" s="77"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="45"/>
+      <c r="AF17" s="45"/>
+      <c r="AG17" s="45"/>
+      <c r="AH17" s="45"/>
+      <c r="AI17" s="46"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="49">
+      <c r="AN17" s="93">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3129,11 +3130,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="35"/>
+      <c r="BC17" s="64"/>
+      <c r="BD17" s="64"/>
     </row>
     <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I18" s="93"/>
+      <c r="I18" s="54"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3162,10 +3163,10 @@
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="42">
+      <c r="X18" s="52">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="52">
+      <c r="Y18" s="40">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3196,7 +3197,7 @@
       </c>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="49"/>
+      <c r="AN18" s="93"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3223,11 +3224,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="35"/>
+      <c r="BC18" s="64"/>
+      <c r="BD18" s="64"/>
     </row>
     <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3250,8 +3251,8 @@
       <c r="U19" s="6"/>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="78"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="62"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3280,7 +3281,7 @@
       </c>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="40" t="s">
+      <c r="AN19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3303,11 +3304,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="35"/>
+      <c r="BC19" s="64"/>
+      <c r="BD19" s="64"/>
     </row>
     <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I20" s="41"/>
+      <c r="I20" s="36"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3328,8 +3329,8 @@
       <c r="U20" s="7"/>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="53"/>
+      <c r="X20" s="52"/>
+      <c r="Y20" s="41"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3358,7 +3359,7 @@
       </c>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="41"/>
+      <c r="AN20" s="36"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3379,11 +3380,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="35"/>
-      <c r="BD20" s="35"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I21" s="40">
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="64"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I21" s="35">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3420,17 +3421,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="76"/>
-      <c r="AG21" s="76"/>
-      <c r="AH21" s="76"/>
-      <c r="AI21" s="77"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="46"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="40">
+      <c r="AN21" s="35">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3461,11 +3462,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="35"/>
-      <c r="BD21" s="35"/>
+      <c r="BC21" s="64"/>
+      <c r="BD21" s="64"/>
     </row>
     <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I22" s="48"/>
+      <c r="I22" s="55"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3494,10 +3495,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="49">
+      <c r="X22" s="93">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="52">
+      <c r="Y22" s="40">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3528,7 +3529,7 @@
       </c>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="48"/>
+      <c r="AN22" s="55"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3557,11 +3558,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="35"/>
-      <c r="BD22" s="35"/>
+      <c r="BC22" s="64"/>
+      <c r="BD22" s="64"/>
     </row>
     <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I23" s="41"/>
+      <c r="I23" s="36"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3590,8 +3591,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="53"/>
+      <c r="X23" s="93"/>
+      <c r="Y23" s="41"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3620,7 +3621,7 @@
       </c>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="41"/>
+      <c r="AN23" s="36"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3649,11 +3650,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="35"/>
-      <c r="BD23" s="35"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I24" s="40" t="s">
+      <c r="BC23" s="64"/>
+      <c r="BD23" s="64"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3690,17 +3691,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="76"/>
-      <c r="AG24" s="76"/>
-      <c r="AH24" s="76"/>
-      <c r="AI24" s="77"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="45"/>
+      <c r="AI24" s="46"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="40" t="s">
+      <c r="AN24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3731,11 +3732,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="35"/>
-      <c r="BD24" s="35"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I25" s="41"/>
+      <c r="BC24" s="64"/>
+      <c r="BD24" s="64"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I25" s="36"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3764,10 +3765,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="40" t="s">
+      <c r="X25" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="46">
+      <c r="Y25" s="42">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3790,7 +3791,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="41"/>
+      <c r="AN25" s="36"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3819,11 +3820,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="35"/>
-      <c r="BD25" s="35"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I26" s="40" t="s">
+      <c r="BC25" s="64"/>
+      <c r="BD25" s="64"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3854,8 +3855,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="47"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="43"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3876,7 +3877,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="40" t="s">
+      <c r="AN26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3907,11 +3908,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="35"/>
-      <c r="BD26" s="35"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I27" s="41"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I27" s="36"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3946,17 +3947,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="76"/>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="77"/>
+      <c r="AD27" s="44"/>
+      <c r="AE27" s="45"/>
+      <c r="AF27" s="45"/>
+      <c r="AG27" s="45"/>
+      <c r="AH27" s="45"/>
+      <c r="AI27" s="46"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="41"/>
+      <c r="AN27" s="36"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3985,11 +3986,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="35"/>
-      <c r="BD27" s="35"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I28" s="40" t="s">
+      <c r="BC27" s="64"/>
+      <c r="BD27" s="64"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -4020,10 +4021,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="40">
+      <c r="X28" s="35">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="60">
+      <c r="Y28" s="58">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -4054,7 +4055,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="40" t="s">
+      <c r="AN28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4085,11 +4086,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="36"/>
-      <c r="BD28" s="36"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I29" s="48"/>
+      <c r="BC28" s="65"/>
+      <c r="BD28" s="65"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="55"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4118,8 +4119,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="91"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="63"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4148,7 +4149,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="48"/>
+      <c r="AN29" s="55"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4177,11 +4178,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="35"/>
-      <c r="BD29" s="35"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I30" s="41"/>
+      <c r="BC29" s="64"/>
+      <c r="BD29" s="64"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I30" s="36"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4210,8 +4211,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="61"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="59"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4240,7 +4241,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="41"/>
+      <c r="AN30" s="36"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4269,11 +4270,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="35"/>
-      <c r="BD30" s="35"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I31" s="40">
+      <c r="BC30" s="64"/>
+      <c r="BD30" s="64"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I31" s="35">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4310,17 +4311,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="76"/>
-      <c r="AG31" s="76"/>
-      <c r="AH31" s="76"/>
-      <c r="AI31" s="77"/>
+      <c r="AD31" s="44"/>
+      <c r="AE31" s="45"/>
+      <c r="AF31" s="45"/>
+      <c r="AG31" s="45"/>
+      <c r="AH31" s="45"/>
+      <c r="AI31" s="46"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="40">
+      <c r="AN31" s="35">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4351,11 +4352,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="35"/>
-      <c r="BD31" s="35"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I32" s="41"/>
+      <c r="BC31" s="64"/>
+      <c r="BD31" s="64"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I32" s="36"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4384,10 +4385,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="40">
+      <c r="X32" s="35">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="60">
+      <c r="Y32" s="58">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4418,7 +4419,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="41"/>
+      <c r="AN32" s="36"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4447,11 +4448,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="35"/>
-      <c r="BD32" s="35"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I33" s="40">
+      <c r="BC32" s="64"/>
+      <c r="BD32" s="64"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I33" s="35">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4482,8 +4483,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="61"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="59"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4512,7 +4513,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="40">
+      <c r="AN33" s="35">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4543,11 +4544,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="35"/>
-      <c r="BD33" s="35"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I34" s="41"/>
+      <c r="BC33" s="64"/>
+      <c r="BD33" s="64"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I34" s="36"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4582,17 +4583,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="75"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
-      <c r="AI34" s="77"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="45"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="45"/>
+      <c r="AI34" s="46"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="41"/>
+      <c r="AN34" s="36"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4621,11 +4622,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="35"/>
-      <c r="BD34" s="35"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I35" s="40">
+      <c r="BC34" s="64"/>
+      <c r="BD34" s="64"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4656,10 +4657,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="40" t="s">
+      <c r="X35" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="46">
+      <c r="Y35" s="42">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4690,7 +4691,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="40">
+      <c r="AN35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4721,11 +4722,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="35"/>
-      <c r="BD35" s="35"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I36" s="41"/>
+      <c r="BC35" s="64"/>
+      <c r="BD35" s="64"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36" s="36"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4754,8 +4755,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="47"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="43"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4784,7 +4785,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="41"/>
+      <c r="AN36" s="36"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4813,11 +4814,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="35"/>
-      <c r="BD36" s="35"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I37" s="40">
+      <c r="BC36" s="64"/>
+      <c r="BD36" s="64"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4854,17 +4855,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="75"/>
-      <c r="AE37" s="76"/>
-      <c r="AF37" s="76"/>
-      <c r="AG37" s="76"/>
-      <c r="AH37" s="76"/>
-      <c r="AI37" s="77"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="45"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="46"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="40">
+      <c r="AN37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4895,11 +4896,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="35"/>
-      <c r="BD37" s="35"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I38" s="41"/>
+      <c r="BC37" s="64"/>
+      <c r="BD37" s="64"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" s="36"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4928,10 +4929,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="40" t="s">
+      <c r="X38" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="52">
+      <c r="Y38" s="40">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4962,7 +4963,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="41"/>
+      <c r="AN38" s="36"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4991,10 +4992,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="35"/>
-      <c r="BD38" s="35"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC38" s="64"/>
+      <c r="BD38" s="64"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -5026,8 +5027,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="78"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="62"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5087,11 +5088,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="35"/>
-      <c r="BD39" s="35"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I40" s="40">
+      <c r="BC39" s="64"/>
+      <c r="BD39" s="64"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5122,8 +5123,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="41"/>
-      <c r="Y40" s="53"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="41"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5152,7 +5153,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="40">
+      <c r="AN40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5183,11 +5184,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="36"/>
-      <c r="BD40" s="36"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I41" s="41"/>
+      <c r="BC40" s="65"/>
+      <c r="BD40" s="65"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I41" s="36"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5200,14 +5201,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="45"/>
+      <c r="O41" s="48"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="49"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5222,17 +5223,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="75"/>
-      <c r="AE41" s="76"/>
-      <c r="AF41" s="76"/>
-      <c r="AG41" s="76"/>
-      <c r="AH41" s="76"/>
-      <c r="AI41" s="77"/>
+      <c r="AD41" s="44"/>
+      <c r="AE41" s="45"/>
+      <c r="AF41" s="45"/>
+      <c r="AG41" s="45"/>
+      <c r="AH41" s="45"/>
+      <c r="AI41" s="46"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="41"/>
+      <c r="AN41" s="36"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5245,14 +5246,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="43" t="s">
+      <c r="AS41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="44"/>
-      <c r="AU41" s="44"/>
-      <c r="AV41" s="44"/>
-      <c r="AW41" s="44"/>
-      <c r="AX41" s="45"/>
+      <c r="AT41" s="48"/>
+      <c r="AU41" s="48"/>
+      <c r="AV41" s="48"/>
+      <c r="AW41" s="48"/>
+      <c r="AX41" s="49"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5261,10 +5262,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="35"/>
-      <c r="BD41" s="35"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC41" s="64"/>
+      <c r="BD41" s="64"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5296,10 +5297,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="40">
+      <c r="X42" s="35">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="52">
+      <c r="Y42" s="40">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5361,11 +5362,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="35"/>
-      <c r="BD42" s="35"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I43" s="40">
+      <c r="BC42" s="64"/>
+      <c r="BD42" s="64"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" s="35">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5396,8 +5397,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="53"/>
+      <c r="X43" s="36"/>
+      <c r="Y43" s="41"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5426,7 +5427,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="40">
+      <c r="AN43" s="35">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5457,11 +5458,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="35"/>
-      <c r="BD43" s="35"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I44" s="41"/>
+      <c r="BC43" s="64"/>
+      <c r="BD43" s="64"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I44" s="36"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5496,17 +5497,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="75"/>
-      <c r="AE44" s="76"/>
-      <c r="AF44" s="76"/>
-      <c r="AG44" s="76"/>
-      <c r="AH44" s="76"/>
-      <c r="AI44" s="77"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="45"/>
+      <c r="AG44" s="45"/>
+      <c r="AH44" s="45"/>
+      <c r="AI44" s="46"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="41"/>
+      <c r="AN44" s="36"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5535,10 +5536,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="35"/>
-      <c r="BD44" s="35"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC44" s="64"/>
+      <c r="BD44" s="64"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5570,10 +5571,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="40">
+      <c r="X45" s="35">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="60">
+      <c r="Y45" s="58">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5635,11 +5636,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="35"/>
-      <c r="BD45" s="35"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I46" s="40" t="s">
+      <c r="BC45" s="64"/>
+      <c r="BD45" s="64"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5670,8 +5671,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="61"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="59"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5700,7 +5701,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="40" t="s">
+      <c r="AN46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5731,11 +5732,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="35"/>
-      <c r="BD46" s="35"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I47" s="41"/>
+      <c r="BC46" s="64"/>
+      <c r="BD46" s="64"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I47" s="36"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5770,17 +5771,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="75"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="76"/>
-      <c r="AG47" s="76"/>
-      <c r="AH47" s="76"/>
-      <c r="AI47" s="77"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="45"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="45"/>
+      <c r="AI47" s="46"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="41"/>
+      <c r="AN47" s="36"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5809,11 +5810,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="35"/>
-      <c r="BD47" s="35"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I48" s="40" t="s">
+      <c r="BC47" s="64"/>
+      <c r="BD47" s="64"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5844,10 +5845,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="40">
+      <c r="X48" s="35">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="46">
+      <c r="Y48" s="42">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5878,7 +5879,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="40" t="s">
+      <c r="AN48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5909,11 +5910,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="35"/>
-      <c r="BD48" s="35"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I49" s="41"/>
+      <c r="BC48" s="64"/>
+      <c r="BD48" s="64"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I49" s="36"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5942,8 +5943,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="47"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="43"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5972,7 +5973,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="41"/>
+      <c r="AN49" s="36"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -6001,12 +6002,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="35"/>
-      <c r="BD49" s="35"/>
-    </row>
-    <row r="50" spans="8:56" x14ac:dyDescent="0.2">
+      <c r="BC49" s="64"/>
+      <c r="BD49" s="64"/>
+    </row>
+    <row r="50" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="H50" s="10"/>
-      <c r="I50" s="40">
+      <c r="I50" s="35">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -6021,14 +6022,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="43" t="s">
+      <c r="N50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="45"/>
+      <c r="O50" s="48"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="48"/>
+      <c r="R50" s="48"/>
+      <c r="S50" s="49"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -6043,17 +6044,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="75"/>
-      <c r="AE50" s="76"/>
-      <c r="AF50" s="76"/>
-      <c r="AG50" s="76"/>
-      <c r="AH50" s="76"/>
-      <c r="AI50" s="77"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="45"/>
+      <c r="AI50" s="46"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="40">
+      <c r="AN50" s="35">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6064,23 +6065,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="43" t="s">
+      <c r="AS50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="44"/>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="44"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="45"/>
+      <c r="AT50" s="48"/>
+      <c r="AU50" s="48"/>
+      <c r="AV50" s="48"/>
+      <c r="AW50" s="48"/>
+      <c r="AX50" s="49"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="35"/>
-      <c r="BD50" s="35"/>
-    </row>
-    <row r="51" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I51" s="41"/>
+      <c r="BC50" s="64"/>
+      <c r="BD50" s="64"/>
+    </row>
+    <row r="51" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I51" s="36"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6093,14 +6094,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="43" t="s">
+      <c r="N51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="45"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="49"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6109,10 +6110,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="40">
+      <c r="X51" s="35">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="52">
+      <c r="Y51" s="40">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6143,7 +6144,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="41"/>
+      <c r="AN51" s="36"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6152,23 +6153,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="43" t="s">
+      <c r="AS51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="44"/>
-      <c r="AU51" s="44"/>
-      <c r="AV51" s="44"/>
-      <c r="AW51" s="44"/>
-      <c r="AX51" s="45"/>
+      <c r="AT51" s="48"/>
+      <c r="AU51" s="48"/>
+      <c r="AV51" s="48"/>
+      <c r="AW51" s="48"/>
+      <c r="AX51" s="49"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="35"/>
-      <c r="BD51" s="35"/>
-    </row>
-    <row r="52" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I52" s="40">
+      <c r="BC51" s="64"/>
+      <c r="BD51" s="64"/>
+    </row>
+    <row r="52" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I52" s="35">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6199,8 +6200,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="53"/>
+      <c r="X52" s="36"/>
+      <c r="Y52" s="41"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6229,7 +6230,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="40">
+      <c r="AN52" s="35">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6252,11 +6253,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="36"/>
-      <c r="BD52" s="36"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I53" s="41"/>
+      <c r="BC52" s="65"/>
+      <c r="BD52" s="65"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I53" s="36"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6291,17 +6292,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="75"/>
-      <c r="AE53" s="76"/>
-      <c r="AF53" s="76"/>
-      <c r="AG53" s="76"/>
-      <c r="AH53" s="76"/>
-      <c r="AI53" s="77"/>
+      <c r="AD53" s="44"/>
+      <c r="AE53" s="45"/>
+      <c r="AF53" s="45"/>
+      <c r="AG53" s="45"/>
+      <c r="AH53" s="45"/>
+      <c r="AI53" s="46"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="41"/>
+      <c r="AN53" s="36"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6322,11 +6323,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="35"/>
-      <c r="BD53" s="35"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I54" s="40">
+      <c r="BC53" s="64"/>
+      <c r="BD53" s="64"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" s="35">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6391,7 +6392,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="40">
+      <c r="AN54" s="35">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6414,11 +6415,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="35"/>
-      <c r="BD54" s="35"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I55" s="41"/>
+      <c r="BC54" s="64"/>
+      <c r="BD54" s="64"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I55" s="36"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6453,17 +6454,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="75"/>
-      <c r="AE55" s="76"/>
-      <c r="AF55" s="76"/>
-      <c r="AG55" s="76"/>
-      <c r="AH55" s="76"/>
-      <c r="AI55" s="77"/>
+      <c r="AD55" s="44"/>
+      <c r="AE55" s="45"/>
+      <c r="AF55" s="45"/>
+      <c r="AG55" s="45"/>
+      <c r="AH55" s="45"/>
+      <c r="AI55" s="46"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="41"/>
+      <c r="AN55" s="36"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6484,10 +6485,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="35"/>
-      <c r="BD55" s="35"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC55" s="64"/>
+      <c r="BD55" s="64"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6519,10 +6520,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="40">
+      <c r="X56" s="35">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="60">
+      <c r="Y56" s="58">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6576,11 +6577,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="35"/>
-      <c r="BD56" s="35"/>
-    </row>
-    <row r="57" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I57" s="40">
+      <c r="BC56" s="64"/>
+      <c r="BD56" s="64"/>
+    </row>
+    <row r="57" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I57" s="35">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6611,8 +6612,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="41"/>
-      <c r="Y57" s="61"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="59"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6623,14 +6624,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="43" t="s">
+      <c r="AD57" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="44"/>
-      <c r="AF57" s="44"/>
-      <c r="AG57" s="44"/>
-      <c r="AH57" s="44"/>
-      <c r="AI57" s="45"/>
+      <c r="AE57" s="48"/>
+      <c r="AF57" s="48"/>
+      <c r="AG57" s="48"/>
+      <c r="AH57" s="48"/>
+      <c r="AI57" s="49"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6639,7 +6640,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="40">
+      <c r="AN57" s="35">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6662,11 +6663,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="35"/>
-      <c r="BD57" s="35"/>
-    </row>
-    <row r="58" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I58" s="41"/>
+      <c r="BC57" s="64"/>
+      <c r="BD57" s="64"/>
+    </row>
+    <row r="58" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I58" s="36"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6701,17 +6702,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="75"/>
-      <c r="AE58" s="76"/>
-      <c r="AF58" s="76"/>
-      <c r="AG58" s="76"/>
-      <c r="AH58" s="76"/>
-      <c r="AI58" s="77"/>
+      <c r="AD58" s="44"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="46"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="41"/>
+      <c r="AN58" s="36"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6732,11 +6733,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="35"/>
-      <c r="BD58" s="35"/>
-    </row>
-    <row r="59" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I59" s="40">
+      <c r="BC58" s="64"/>
+      <c r="BD58" s="64"/>
+    </row>
+    <row r="59" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I59" s="35">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6801,7 +6802,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="40">
+      <c r="AN59" s="35">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6824,11 +6825,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="35"/>
-      <c r="BD59" s="35"/>
-    </row>
-    <row r="60" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I60" s="41"/>
+      <c r="BC59" s="64"/>
+      <c r="BD59" s="64"/>
+    </row>
+    <row r="60" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I60" s="36"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6863,17 +6864,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="75"/>
-      <c r="AE60" s="76"/>
-      <c r="AF60" s="76"/>
-      <c r="AG60" s="76"/>
-      <c r="AH60" s="76"/>
-      <c r="AI60" s="77"/>
+      <c r="AD60" s="44"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="45"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="45"/>
+      <c r="AI60" s="46"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="41"/>
+      <c r="AN60" s="36"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6894,11 +6895,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="35"/>
-      <c r="BD60" s="35"/>
-    </row>
-    <row r="61" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I61" s="40" t="s">
+      <c r="BC60" s="64"/>
+      <c r="BD60" s="64"/>
+    </row>
+    <row r="61" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6929,10 +6930,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="40">
+      <c r="X61" s="35">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="58">
+      <c r="Y61" s="60">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6963,7 +6964,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="40" t="s">
+      <c r="AN61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6986,11 +6987,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="35"/>
-      <c r="BD61" s="35"/>
-    </row>
-    <row r="62" spans="8:56" x14ac:dyDescent="0.2">
-      <c r="I62" s="41"/>
+      <c r="BC61" s="64"/>
+      <c r="BD61" s="64"/>
+    </row>
+    <row r="62" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I62" s="36"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7019,8 +7020,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="41"/>
-      <c r="Y62" s="59"/>
+      <c r="X62" s="36"/>
+      <c r="Y62" s="61"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -7049,7 +7050,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="41"/>
+      <c r="AN62" s="36"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7070,11 +7071,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="35"/>
-      <c r="BD62" s="35"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I63" s="40">
+      <c r="BC62" s="64"/>
+      <c r="BD62" s="64"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I63" s="35">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7111,17 +7112,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="75"/>
-      <c r="AE63" s="76"/>
-      <c r="AF63" s="76"/>
-      <c r="AG63" s="76"/>
-      <c r="AH63" s="76"/>
-      <c r="AI63" s="77"/>
+      <c r="AD63" s="44"/>
+      <c r="AE63" s="45"/>
+      <c r="AF63" s="45"/>
+      <c r="AG63" s="45"/>
+      <c r="AH63" s="45"/>
+      <c r="AI63" s="46"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="40">
+      <c r="AN63" s="35">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7144,11 +7145,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="35"/>
-      <c r="BD63" s="35"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I64" s="41"/>
+      <c r="BC63" s="64"/>
+      <c r="BD63" s="64"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I64" s="36"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7211,7 +7212,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="41"/>
+      <c r="AN64" s="36"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7232,11 +7233,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="36"/>
-      <c r="BD64" s="36"/>
-    </row>
-    <row r="65" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I65" s="40">
+      <c r="BC64" s="65"/>
+      <c r="BD64" s="65"/>
+    </row>
+    <row r="65" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I65" s="35">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7265,17 +7266,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="75"/>
-      <c r="AE65" s="76"/>
-      <c r="AF65" s="76"/>
-      <c r="AG65" s="76"/>
-      <c r="AH65" s="76"/>
-      <c r="AI65" s="77"/>
+      <c r="AD65" s="44"/>
+      <c r="AE65" s="45"/>
+      <c r="AF65" s="45"/>
+      <c r="AG65" s="45"/>
+      <c r="AH65" s="45"/>
+      <c r="AI65" s="46"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="40">
+      <c r="AN65" s="35">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7298,11 +7299,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="35"/>
-      <c r="BD65" s="35"/>
-    </row>
-    <row r="66" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I66" s="41"/>
+      <c r="BC65" s="64"/>
+      <c r="BD65" s="64"/>
+    </row>
+    <row r="66" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I66" s="36"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7323,10 +7324,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="40" t="s">
+      <c r="X66" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="54">
+      <c r="Y66" s="56">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7357,7 +7358,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="41"/>
+      <c r="AN66" s="36"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7378,10 +7379,10 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="35"/>
-      <c r="BD66" s="35"/>
-    </row>
-    <row r="67" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="BC66" s="64"/>
+      <c r="BD66" s="64"/>
+    </row>
+    <row r="67" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
@@ -7405,8 +7406,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="41"/>
-      <c r="Y67" s="55"/>
+      <c r="X67" s="36"/>
+      <c r="Y67" s="57"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7458,11 +7459,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="35"/>
-      <c r="BD67" s="35"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I68" s="40">
+      <c r="BC67" s="64"/>
+      <c r="BD67" s="64"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I68" s="35">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7495,17 +7496,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="76"/>
-      <c r="AG68" s="76"/>
-      <c r="AH68" s="76"/>
-      <c r="AI68" s="77"/>
+      <c r="AD68" s="44"/>
+      <c r="AE68" s="45"/>
+      <c r="AF68" s="45"/>
+      <c r="AG68" s="45"/>
+      <c r="AH68" s="45"/>
+      <c r="AI68" s="46"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="40">
+      <c r="AN68" s="35">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7528,11 +7529,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="35"/>
-      <c r="BD68" s="35"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I69" s="41"/>
+      <c r="BC68" s="64"/>
+      <c r="BD68" s="64"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I69" s="36"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7557,10 +7558,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="40" t="s">
+      <c r="X69" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="54">
+      <c r="Y69" s="56">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7591,7 +7592,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="41"/>
+      <c r="AN69" s="36"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7612,10 +7613,10 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="35"/>
-      <c r="BD69" s="35"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC69" s="64"/>
+      <c r="BD69" s="64"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
@@ -7639,8 +7640,8 @@
       <c r="U70" s="6"/>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="41"/>
-      <c r="Y70" s="55"/>
+      <c r="X70" s="36"/>
+      <c r="Y70" s="57"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7692,11 +7693,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="35"/>
-      <c r="BD70" s="35"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I71" s="40">
+      <c r="BC70" s="64"/>
+      <c r="BD70" s="64"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I71" s="35">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7725,17 +7726,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="75"/>
-      <c r="AE71" s="76"/>
-      <c r="AF71" s="76"/>
-      <c r="AG71" s="76"/>
-      <c r="AH71" s="76"/>
-      <c r="AI71" s="77"/>
+      <c r="AD71" s="44"/>
+      <c r="AE71" s="45"/>
+      <c r="AF71" s="45"/>
+      <c r="AG71" s="45"/>
+      <c r="AH71" s="45"/>
+      <c r="AI71" s="46"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="40">
+      <c r="AN71" s="35">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7758,11 +7759,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="35"/>
-      <c r="BD71" s="35"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I72" s="41"/>
+      <c r="BC71" s="64"/>
+      <c r="BD71" s="64"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I72" s="36"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7783,10 +7784,10 @@
       <c r="U72" s="6"/>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="40">
+      <c r="X72" s="35">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="52">
+      <c r="Y72" s="40">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7801,14 +7802,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="43" t="s">
+      <c r="AD72" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
-      <c r="AH72" s="44"/>
-      <c r="AI72" s="45"/>
+      <c r="AE72" s="48"/>
+      <c r="AF72" s="48"/>
+      <c r="AG72" s="48"/>
+      <c r="AH72" s="48"/>
+      <c r="AI72" s="49"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7817,7 +7818,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="41"/>
+      <c r="AN72" s="36"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7838,11 +7839,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="35"/>
-      <c r="BD72" s="35"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I73" s="40">
+      <c r="BC72" s="64"/>
+      <c r="BD72" s="64"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7853,20 +7854,20 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="43" t="s">
+      <c r="N73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
-      <c r="R73" s="44"/>
-      <c r="S73" s="45"/>
+      <c r="O73" s="48"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="48"/>
+      <c r="R73" s="48"/>
+      <c r="S73" s="49"/>
       <c r="T73" s="7"/>
       <c r="U73" s="6"/>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="41"/>
-      <c r="Y73" s="53"/>
+      <c r="X73" s="36"/>
+      <c r="Y73" s="41"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7879,14 +7880,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="43" t="s">
+      <c r="AD73" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
-      <c r="AH73" s="44"/>
-      <c r="AI73" s="45"/>
+      <c r="AE73" s="48"/>
+      <c r="AF73" s="48"/>
+      <c r="AG73" s="48"/>
+      <c r="AH73" s="48"/>
+      <c r="AI73" s="49"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7895,7 +7896,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="40">
+      <c r="AN73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7906,23 +7907,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="43" t="s">
+      <c r="AS73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="44"/>
-      <c r="AU73" s="44"/>
-      <c r="AV73" s="44"/>
-      <c r="AW73" s="44"/>
-      <c r="AX73" s="45"/>
+      <c r="AT73" s="48"/>
+      <c r="AU73" s="48"/>
+      <c r="AV73" s="48"/>
+      <c r="AW73" s="48"/>
+      <c r="AX73" s="49"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="35"/>
-      <c r="BD73" s="35"/>
-    </row>
-    <row r="74" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I74" s="41"/>
+      <c r="BC73" s="64"/>
+      <c r="BD73" s="64"/>
+    </row>
+    <row r="74" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I74" s="36"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7949,17 +7950,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="75"/>
-      <c r="AE74" s="76"/>
-      <c r="AF74" s="76"/>
-      <c r="AG74" s="76"/>
-      <c r="AH74" s="76"/>
-      <c r="AI74" s="77"/>
+      <c r="AD74" s="44"/>
+      <c r="AE74" s="45"/>
+      <c r="AF74" s="45"/>
+      <c r="AG74" s="45"/>
+      <c r="AH74" s="45"/>
+      <c r="AI74" s="46"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="41"/>
+      <c r="AN74" s="36"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7980,11 +7981,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="35"/>
-      <c r="BD74" s="35"/>
-    </row>
-    <row r="75" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I75" s="40">
+      <c r="BC74" s="64"/>
+      <c r="BD74" s="64"/>
+    </row>
+    <row r="75" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7995,22 +7996,22 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="43" t="s">
+      <c r="N75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="44"/>
-      <c r="P75" s="44"/>
-      <c r="Q75" s="44"/>
-      <c r="R75" s="44"/>
-      <c r="S75" s="45"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="49"/>
       <c r="T75" s="7"/>
       <c r="U75" s="6"/>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="40">
+      <c r="X75" s="35">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="60">
+      <c r="Y75" s="58">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -8041,7 +8042,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="40">
+      <c r="AN75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -8052,23 +8053,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="43" t="s">
+      <c r="AS75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="44"/>
-      <c r="AU75" s="44"/>
-      <c r="AV75" s="44"/>
-      <c r="AW75" s="44"/>
-      <c r="AX75" s="45"/>
+      <c r="AT75" s="48"/>
+      <c r="AU75" s="48"/>
+      <c r="AV75" s="48"/>
+      <c r="AW75" s="48"/>
+      <c r="AX75" s="49"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="35"/>
-      <c r="BD75" s="35"/>
-    </row>
-    <row r="76" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I76" s="41"/>
+      <c r="BC75" s="64"/>
+      <c r="BD75" s="64"/>
+    </row>
+    <row r="76" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I76" s="36"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8089,8 +8090,8 @@
       <c r="U76" s="6"/>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="41"/>
-      <c r="Y76" s="61"/>
+      <c r="X76" s="36"/>
+      <c r="Y76" s="59"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8119,7 +8120,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="41"/>
+      <c r="AN76" s="36"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8140,11 +8141,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="36"/>
-      <c r="BD76" s="36"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I77" s="40">
+      <c r="BC76" s="65"/>
+      <c r="BD76" s="65"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I77" s="35">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8173,17 +8174,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="75"/>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="76"/>
-      <c r="AG77" s="76"/>
-      <c r="AH77" s="76"/>
-      <c r="AI77" s="77"/>
+      <c r="AD77" s="44"/>
+      <c r="AE77" s="45"/>
+      <c r="AF77" s="45"/>
+      <c r="AG77" s="45"/>
+      <c r="AH77" s="45"/>
+      <c r="AI77" s="46"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="40">
+      <c r="AN77" s="35">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8206,11 +8207,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="35"/>
-      <c r="BD77" s="35"/>
-    </row>
-    <row r="78" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I78" s="41"/>
+      <c r="BC77" s="64"/>
+      <c r="BD77" s="64"/>
+    </row>
+    <row r="78" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I78" s="36"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8231,10 +8232,10 @@
       <c r="U78" s="6"/>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="40">
+      <c r="X78" s="35">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="52">
+      <c r="Y78" s="40">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8265,7 +8266,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="41"/>
+      <c r="AN78" s="36"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8286,11 +8287,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="35"/>
-      <c r="BD78" s="35"/>
-    </row>
-    <row r="79" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I79" s="40">
+      <c r="BC78" s="64"/>
+      <c r="BD78" s="64"/>
+    </row>
+    <row r="79" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I79" s="35">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8303,22 +8304,22 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="43" t="s">
+      <c r="N79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
-      <c r="R79" s="44"/>
-      <c r="S79" s="45"/>
+      <c r="O79" s="48"/>
+      <c r="P79" s="48"/>
+      <c r="Q79" s="48"/>
+      <c r="R79" s="48"/>
+      <c r="S79" s="49"/>
       <c r="T79" s="7">
         <v>45905</v>
       </c>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="41"/>
-      <c r="Y79" s="53"/>
+      <c r="X79" s="36"/>
+      <c r="Y79" s="41"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="40">
+      <c r="AN79" s="35">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8358,23 +8359,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="43" t="s">
+      <c r="AS79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="44"/>
-      <c r="AU79" s="44"/>
-      <c r="AV79" s="44"/>
-      <c r="AW79" s="44"/>
-      <c r="AX79" s="45"/>
+      <c r="AT79" s="48"/>
+      <c r="AU79" s="48"/>
+      <c r="AV79" s="48"/>
+      <c r="AW79" s="48"/>
+      <c r="AX79" s="49"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="35"/>
-      <c r="BD79" s="35"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I80" s="41"/>
+      <c r="BC79" s="64"/>
+      <c r="BD79" s="64"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I80" s="36"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8405,17 +8406,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="75"/>
-      <c r="AE80" s="76"/>
-      <c r="AF80" s="76"/>
-      <c r="AG80" s="76"/>
-      <c r="AH80" s="76"/>
-      <c r="AI80" s="77"/>
+      <c r="AD80" s="44"/>
+      <c r="AE80" s="45"/>
+      <c r="AF80" s="45"/>
+      <c r="AG80" s="45"/>
+      <c r="AH80" s="45"/>
+      <c r="AI80" s="46"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="41"/>
+      <c r="AN80" s="36"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8436,11 +8437,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="35"/>
-      <c r="BD80" s="35"/>
-    </row>
-    <row r="81" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I81" s="40">
+      <c r="BC80" s="64"/>
+      <c r="BD80" s="64"/>
+    </row>
+    <row r="81" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I81" s="35">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8497,7 +8498,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="40">
+      <c r="AN81" s="35">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8520,11 +8521,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="35"/>
-      <c r="BD81" s="35"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I82" s="41"/>
+      <c r="BC81" s="64"/>
+      <c r="BD81" s="64"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I82" s="36"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8533,14 +8534,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="43" t="s">
+      <c r="N82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="44"/>
-      <c r="P82" s="44"/>
-      <c r="Q82" s="44"/>
-      <c r="R82" s="44"/>
-      <c r="S82" s="45"/>
+      <c r="O82" s="48"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="48"/>
+      <c r="R82" s="48"/>
+      <c r="S82" s="49"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8551,17 +8552,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="75"/>
-      <c r="AE82" s="76"/>
-      <c r="AF82" s="76"/>
-      <c r="AG82" s="76"/>
-      <c r="AH82" s="76"/>
-      <c r="AI82" s="77"/>
+      <c r="AD82" s="44"/>
+      <c r="AE82" s="45"/>
+      <c r="AF82" s="45"/>
+      <c r="AG82" s="45"/>
+      <c r="AH82" s="45"/>
+      <c r="AI82" s="46"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="41"/>
+      <c r="AN82" s="36"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8570,23 +8571,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="43" t="s">
+      <c r="AS82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="44"/>
-      <c r="AU82" s="44"/>
-      <c r="AV82" s="44"/>
-      <c r="AW82" s="44"/>
-      <c r="AX82" s="45"/>
+      <c r="AT82" s="48"/>
+      <c r="AU82" s="48"/>
+      <c r="AV82" s="48"/>
+      <c r="AW82" s="48"/>
+      <c r="AX82" s="49"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="35"/>
-      <c r="BD82" s="35"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I83" s="40">
+      <c r="BC82" s="64"/>
+      <c r="BD82" s="64"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I83" s="35">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8617,10 +8618,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="40">
+      <c r="X83" s="35">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="54">
+      <c r="Y83" s="56">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8651,7 +8652,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="40">
+      <c r="AN83" s="35">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8680,11 +8681,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="35"/>
-      <c r="BD83" s="35"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I84" s="41"/>
+      <c r="BC83" s="64"/>
+      <c r="BD83" s="64"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I84" s="36"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8713,8 +8714,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="41"/>
-      <c r="Y84" s="55"/>
+      <c r="X84" s="36"/>
+      <c r="Y84" s="57"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8743,7 +8744,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="41"/>
+      <c r="AN84" s="36"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8770,10 +8771,10 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="35"/>
-      <c r="BD84" s="35"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC84" s="64"/>
+      <c r="BD84" s="64"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
@@ -8803,12 +8804,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="75"/>
-      <c r="AE85" s="76"/>
-      <c r="AF85" s="76"/>
-      <c r="AG85" s="76"/>
-      <c r="AH85" s="76"/>
-      <c r="AI85" s="77"/>
+      <c r="AD85" s="44"/>
+      <c r="AE85" s="45"/>
+      <c r="AF85" s="45"/>
+      <c r="AG85" s="45"/>
+      <c r="AH85" s="45"/>
+      <c r="AI85" s="46"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8836,11 +8837,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="35"/>
-      <c r="BD85" s="35"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I86" s="40">
+      <c r="BC85" s="64"/>
+      <c r="BD85" s="64"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I86" s="35">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8863,10 +8864,10 @@
       <c r="U86" s="6"/>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="40">
+      <c r="X86" s="35">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="56">
+      <c r="Y86" s="50">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8897,7 +8898,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="40">
+      <c r="AN86" s="35">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8920,11 +8921,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="35"/>
-      <c r="BD86" s="35"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I87" s="41"/>
+      <c r="BC86" s="64"/>
+      <c r="BD86" s="64"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I87" s="36"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8945,8 +8946,8 @@
       <c r="U87" s="6"/>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="41"/>
-      <c r="Y87" s="57"/>
+      <c r="X87" s="36"/>
+      <c r="Y87" s="51"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8975,7 +8976,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="41"/>
+      <c r="AN87" s="36"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8996,11 +8997,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="35"/>
-      <c r="BD87" s="35"/>
-    </row>
-    <row r="88" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I88" s="40" t="s">
+      <c r="BC87" s="64"/>
+      <c r="BD87" s="64"/>
+    </row>
+    <row r="88" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -9029,17 +9030,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="75"/>
-      <c r="AE88" s="76"/>
-      <c r="AF88" s="76"/>
-      <c r="AG88" s="76"/>
-      <c r="AH88" s="76"/>
-      <c r="AI88" s="77"/>
+      <c r="AD88" s="44"/>
+      <c r="AE88" s="45"/>
+      <c r="AF88" s="45"/>
+      <c r="AG88" s="45"/>
+      <c r="AH88" s="45"/>
+      <c r="AI88" s="46"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="40" t="s">
+      <c r="AN88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -9062,11 +9063,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="36"/>
-      <c r="BD88" s="36"/>
-    </row>
-    <row r="89" spans="9:56" x14ac:dyDescent="0.2">
-      <c r="I89" s="41"/>
+      <c r="BC88" s="65"/>
+      <c r="BD88" s="65"/>
+    </row>
+    <row r="89" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I89" s="36"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -9087,10 +9088,10 @@
       <c r="U89" s="6"/>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="40" t="s">
+      <c r="X89" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="56">
+      <c r="Y89" s="50">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9121,7 +9122,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="41"/>
+      <c r="AN89" s="36"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9142,10 +9143,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="35"/>
-      <c r="BD89" s="35"/>
-    </row>
-    <row r="90" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="BC89" s="64"/>
+      <c r="BD89" s="64"/>
+    </row>
+    <row r="90" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9157,20 +9158,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="42" t="s">
+      <c r="N90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="42"/>
-      <c r="P90" s="42"/>
-      <c r="Q90" s="42"/>
-      <c r="R90" s="42"/>
-      <c r="S90" s="42"/>
+      <c r="O90" s="52"/>
+      <c r="P90" s="52"/>
+      <c r="Q90" s="52"/>
+      <c r="R90" s="52"/>
+      <c r="S90" s="52"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="41"/>
-      <c r="Y90" s="57"/>
+      <c r="X90" s="36"/>
+      <c r="Y90" s="51"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9210,22 +9211,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="42" t="s">
+      <c r="AS90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="42"/>
-      <c r="AU90" s="42"/>
-      <c r="AV90" s="42"/>
-      <c r="AW90" s="42"/>
-      <c r="AX90" s="42"/>
+      <c r="AT90" s="52"/>
+      <c r="AU90" s="52"/>
+      <c r="AV90" s="52"/>
+      <c r="AW90" s="52"/>
+      <c r="AX90" s="52"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="35"/>
-      <c r="BD90" s="35"/>
-    </row>
-    <row r="91" spans="9:56" x14ac:dyDescent="0.2">
+      <c r="BC90" s="64"/>
+      <c r="BD90" s="64"/>
+    </row>
+    <row r="91" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9247,12 +9248,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="75"/>
-      <c r="AE91" s="76"/>
-      <c r="AF91" s="76"/>
-      <c r="AG91" s="76"/>
-      <c r="AH91" s="76"/>
-      <c r="AI91" s="77"/>
+      <c r="AD91" s="44"/>
+      <c r="AE91" s="45"/>
+      <c r="AF91" s="45"/>
+      <c r="AG91" s="45"/>
+      <c r="AH91" s="45"/>
+      <c r="AI91" s="46"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9275,7 +9276,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="92" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9291,10 +9292,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="40">
+      <c r="X92" s="35">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="60">
+      <c r="Y92" s="58">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9343,7 +9344,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="93" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9359,8 +9360,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="41"/>
-      <c r="Y93" s="61"/>
+      <c r="X93" s="36"/>
+      <c r="Y93" s="59"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9407,7 +9408,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9429,12 +9430,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="75"/>
-      <c r="AE94" s="76"/>
-      <c r="AF94" s="76"/>
-      <c r="AG94" s="76"/>
-      <c r="AH94" s="76"/>
-      <c r="AI94" s="77"/>
+      <c r="AD94" s="44"/>
+      <c r="AE94" s="45"/>
+      <c r="AF94" s="45"/>
+      <c r="AG94" s="45"/>
+      <c r="AH94" s="45"/>
+      <c r="AI94" s="46"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9457,7 +9458,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="95" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9473,10 +9474,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="40">
+      <c r="X95" s="35">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="58">
+      <c r="Y95" s="60">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9517,7 +9518,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="96" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9533,8 +9534,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="41"/>
-      <c r="Y96" s="59"/>
+      <c r="X96" s="36"/>
+      <c r="Y96" s="61"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9573,7 +9574,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="8:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9595,12 +9596,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="75"/>
-      <c r="AE97" s="76"/>
-      <c r="AF97" s="76"/>
-      <c r="AG97" s="76"/>
-      <c r="AH97" s="76"/>
-      <c r="AI97" s="77"/>
+      <c r="AD97" s="44"/>
+      <c r="AE97" s="45"/>
+      <c r="AF97" s="45"/>
+      <c r="AG97" s="45"/>
+      <c r="AH97" s="45"/>
+      <c r="AI97" s="46"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9623,7 +9624,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="98" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9683,7 +9684,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="99" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9705,12 +9706,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="75"/>
-      <c r="AE99" s="76"/>
-      <c r="AF99" s="76"/>
-      <c r="AG99" s="76"/>
-      <c r="AH99" s="76"/>
-      <c r="AI99" s="77"/>
+      <c r="AD99" s="44"/>
+      <c r="AE99" s="45"/>
+      <c r="AF99" s="45"/>
+      <c r="AG99" s="45"/>
+      <c r="AH99" s="45"/>
+      <c r="AI99" s="46"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9749,10 +9750,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="40">
+      <c r="X100" s="35">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="52">
+      <c r="Y100" s="40">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9761,7 +9762,9 @@
       <c r="AA100" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AB100" s="33"/>
+      <c r="AB100" s="33">
+        <v>2</v>
+      </c>
       <c r="AC100" s="4" t="s">
         <v>13</v>
       </c>
@@ -9776,7 +9779,9 @@
       <c r="AJ100" s="8">
         <v>45903</v>
       </c>
-      <c r="AK100" s="19"/>
+      <c r="AK100" s="8">
+        <v>45905</v>
+      </c>
       <c r="AL100" s="20"/>
       <c r="AM100" s="20"/>
       <c r="AN100" s="20"/>
@@ -9813,15 +9818,17 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="41"/>
-      <c r="Y101" s="53"/>
+      <c r="X101" s="36"/>
+      <c r="Y101" s="41"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
       <c r="AA101" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AB101" s="33"/>
+      <c r="AB101" s="33">
+        <v>2</v>
+      </c>
       <c r="AC101" s="4" t="s">
         <v>13</v>
       </c>
@@ -9836,7 +9843,9 @@
       <c r="AJ101" s="8">
         <v>45903</v>
       </c>
-      <c r="AK101" s="19"/>
+      <c r="AK101" s="8">
+        <v>45905</v>
+      </c>
       <c r="AL101" s="20"/>
       <c r="AM101" s="20"/>
       <c r="AN101" s="20"/>
@@ -9857,7 +9866,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="102" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -9879,12 +9888,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="75"/>
-      <c r="AE102" s="76"/>
-      <c r="AF102" s="76"/>
-      <c r="AG102" s="76"/>
-      <c r="AH102" s="76"/>
-      <c r="AI102" s="77"/>
+      <c r="AD102" s="44"/>
+      <c r="AE102" s="45"/>
+      <c r="AF102" s="45"/>
+      <c r="AG102" s="45"/>
+      <c r="AH102" s="45"/>
+      <c r="AI102" s="46"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9907,7 +9916,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="8:56" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -9967,7 +9976,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="104" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -9989,12 +9998,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="75"/>
-      <c r="AE104" s="76"/>
-      <c r="AF104" s="76"/>
-      <c r="AG104" s="76"/>
-      <c r="AH104" s="76"/>
-      <c r="AI104" s="77"/>
+      <c r="AD104" s="44"/>
+      <c r="AE104" s="45"/>
+      <c r="AF104" s="45"/>
+      <c r="AG104" s="45"/>
+      <c r="AH104" s="45"/>
+      <c r="AI104" s="46"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -10017,7 +10026,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="8:56" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -10034,10 +10043,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="40">
+      <c r="X105" s="35">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="56">
+      <c r="Y105" s="50">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -10078,7 +10087,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="8:56" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -10094,8 +10103,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="41"/>
-      <c r="Y106" s="57"/>
+      <c r="X106" s="36"/>
+      <c r="Y106" s="51"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10134,7 +10143,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10156,12 +10165,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="75"/>
-      <c r="AE107" s="76"/>
-      <c r="AF107" s="76"/>
-      <c r="AG107" s="76"/>
-      <c r="AH107" s="76"/>
-      <c r="AI107" s="77"/>
+      <c r="AD107" s="44"/>
+      <c r="AE107" s="45"/>
+      <c r="AF107" s="45"/>
+      <c r="AG107" s="45"/>
+      <c r="AH107" s="45"/>
+      <c r="AI107" s="46"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10184,7 +10193,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="108" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10200,10 +10209,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="40">
+      <c r="X108" s="35">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="56">
+      <c r="Y108" s="50">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10214,14 +10223,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="43" t="s">
+      <c r="AD108" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="44"/>
-      <c r="AF108" s="44"/>
-      <c r="AG108" s="44"/>
-      <c r="AH108" s="44"/>
-      <c r="AI108" s="45"/>
+      <c r="AE108" s="48"/>
+      <c r="AF108" s="48"/>
+      <c r="AG108" s="48"/>
+      <c r="AH108" s="48"/>
+      <c r="AI108" s="49"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10244,7 +10253,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10260,8 +10269,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="41"/>
-      <c r="Y109" s="57"/>
+      <c r="X109" s="36"/>
+      <c r="Y109" s="51"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10300,7 +10309,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="110" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10322,12 +10331,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="75"/>
-      <c r="AE110" s="76"/>
-      <c r="AF110" s="76"/>
-      <c r="AG110" s="76"/>
-      <c r="AH110" s="76"/>
-      <c r="AI110" s="77"/>
+      <c r="AD110" s="44"/>
+      <c r="AE110" s="45"/>
+      <c r="AF110" s="45"/>
+      <c r="AG110" s="45"/>
+      <c r="AH110" s="45"/>
+      <c r="AI110" s="46"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10350,7 +10359,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" x14ac:dyDescent="0.2">
+    <row r="111" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10366,10 +10375,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="40">
+      <c r="X111" s="35">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="56">
+      <c r="Y111" s="50">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10380,14 +10389,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="43" t="s">
+      <c r="AD111" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="44"/>
-      <c r="AF111" s="44"/>
-      <c r="AG111" s="44"/>
-      <c r="AH111" s="44"/>
-      <c r="AI111" s="45"/>
+      <c r="AE111" s="48"/>
+      <c r="AF111" s="48"/>
+      <c r="AG111" s="48"/>
+      <c r="AH111" s="48"/>
+      <c r="AI111" s="49"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10410,7 +10419,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10426,8 +10435,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="41"/>
-      <c r="Y112" s="57"/>
+      <c r="X112" s="36"/>
+      <c r="Y112" s="51"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10466,7 +10475,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="113" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10488,12 +10497,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="75"/>
-      <c r="AE113" s="76"/>
-      <c r="AF113" s="76"/>
-      <c r="AG113" s="76"/>
-      <c r="AH113" s="76"/>
-      <c r="AI113" s="77"/>
+      <c r="AD113" s="44"/>
+      <c r="AE113" s="45"/>
+      <c r="AF113" s="45"/>
+      <c r="AG113" s="45"/>
+      <c r="AH113" s="45"/>
+      <c r="AI113" s="46"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10516,7 +10525,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="9:56" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10532,10 +10541,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="40">
+      <c r="X114" s="35">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="56">
+      <c r="Y114" s="50">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10576,7 +10585,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="9:56" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10592,8 +10601,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="41"/>
-      <c r="Y115" s="57"/>
+      <c r="X115" s="36"/>
+      <c r="Y115" s="51"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10632,7 +10641,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="116" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10654,12 +10663,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="75"/>
-      <c r="AE116" s="76"/>
-      <c r="AF116" s="76"/>
-      <c r="AG116" s="76"/>
-      <c r="AH116" s="76"/>
-      <c r="AI116" s="77"/>
+      <c r="AD116" s="44"/>
+      <c r="AE116" s="45"/>
+      <c r="AF116" s="45"/>
+      <c r="AG116" s="45"/>
+      <c r="AH116" s="45"/>
+      <c r="AI116" s="46"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10698,10 +10707,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="40">
+      <c r="X117" s="35">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="56">
+      <c r="Y117" s="50">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10710,22 +10719,26 @@
       <c r="AA117" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AB117" s="33"/>
+      <c r="AB117" s="33">
+        <v>2</v>
+      </c>
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="43" t="s">
+      <c r="AD117" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="44"/>
-      <c r="AF117" s="44"/>
-      <c r="AG117" s="44"/>
-      <c r="AH117" s="44"/>
-      <c r="AI117" s="45"/>
+      <c r="AE117" s="48"/>
+      <c r="AF117" s="48"/>
+      <c r="AG117" s="48"/>
+      <c r="AH117" s="48"/>
+      <c r="AI117" s="49"/>
       <c r="AJ117" s="8">
         <v>45905</v>
       </c>
-      <c r="AK117" s="19"/>
+      <c r="AK117" s="8">
+        <v>45907</v>
+      </c>
       <c r="AL117" s="20"/>
       <c r="AM117" s="20"/>
       <c r="AN117" s="20"/>
@@ -10762,15 +10775,17 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="41"/>
-      <c r="Y118" s="57"/>
+      <c r="X118" s="36"/>
+      <c r="Y118" s="51"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
       <c r="AA118" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AB118" s="33"/>
+      <c r="AB118" s="33">
+        <v>2</v>
+      </c>
       <c r="AC118" s="4" t="s">
         <v>13</v>
       </c>
@@ -10785,7 +10800,9 @@
       <c r="AJ118" s="8">
         <v>45905</v>
       </c>
-      <c r="AK118" s="19"/>
+      <c r="AK118" s="8">
+        <v>45907</v>
+      </c>
       <c r="AL118" s="20"/>
       <c r="AM118" s="20"/>
       <c r="AN118" s="20"/>
@@ -10806,7 +10823,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="9:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10828,12 +10845,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="75"/>
-      <c r="AE119" s="76"/>
-      <c r="AF119" s="76"/>
-      <c r="AG119" s="76"/>
-      <c r="AH119" s="76"/>
-      <c r="AI119" s="77"/>
+      <c r="AD119" s="44"/>
+      <c r="AE119" s="45"/>
+      <c r="AF119" s="45"/>
+      <c r="AG119" s="45"/>
+      <c r="AH119" s="45"/>
+      <c r="AI119" s="46"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10856,7 +10873,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -10872,10 +10889,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="40">
+      <c r="X120" s="35">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="54">
+      <c r="Y120" s="56">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10916,7 +10933,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -10932,8 +10949,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="41"/>
-      <c r="Y121" s="55"/>
+      <c r="X121" s="36"/>
+      <c r="Y121" s="57"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10942,14 +10959,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="43" t="s">
+      <c r="AD121" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="44"/>
-      <c r="AF121" s="44"/>
-      <c r="AG121" s="44"/>
-      <c r="AH121" s="44"/>
-      <c r="AI121" s="45"/>
+      <c r="AE121" s="48"/>
+      <c r="AF121" s="48"/>
+      <c r="AG121" s="48"/>
+      <c r="AH121" s="48"/>
+      <c r="AI121" s="49"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10972,7 +10989,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="122" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -10994,12 +11011,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="75"/>
-      <c r="AE122" s="76"/>
-      <c r="AF122" s="76"/>
-      <c r="AG122" s="76"/>
-      <c r="AH122" s="76"/>
-      <c r="AI122" s="77"/>
+      <c r="AD122" s="44"/>
+      <c r="AE122" s="45"/>
+      <c r="AF122" s="45"/>
+      <c r="AG122" s="45"/>
+      <c r="AH122" s="45"/>
+      <c r="AI122" s="46"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -11022,7 +11039,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -11038,10 +11055,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="40">
+      <c r="X123" s="35">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="46">
+      <c r="Y123" s="42">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -11090,7 +11107,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11106,8 +11123,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="41"/>
-      <c r="Y124" s="47"/>
+      <c r="X124" s="36"/>
+      <c r="Y124" s="43"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11154,7 +11171,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="9:56" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11176,12 +11193,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="75"/>
-      <c r="AE125" s="76"/>
-      <c r="AF125" s="76"/>
-      <c r="AG125" s="76"/>
-      <c r="AH125" s="76"/>
-      <c r="AI125" s="77"/>
+      <c r="AD125" s="44"/>
+      <c r="AE125" s="45"/>
+      <c r="AF125" s="45"/>
+      <c r="AG125" s="45"/>
+      <c r="AH125" s="45"/>
+      <c r="AI125" s="46"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11204,7 +11221,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="126" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11223,7 +11240,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="46">
+      <c r="Y126" s="42">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11264,7 +11281,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11281,17 +11298,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="47"/>
+      <c r="Y127" s="43"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="75"/>
-      <c r="AE127" s="76"/>
-      <c r="AF127" s="76"/>
-      <c r="AG127" s="76"/>
-      <c r="AH127" s="76"/>
-      <c r="AI127" s="77"/>
+      <c r="AD127" s="44"/>
+      <c r="AE127" s="45"/>
+      <c r="AF127" s="45"/>
+      <c r="AG127" s="45"/>
+      <c r="AH127" s="45"/>
+      <c r="AI127" s="46"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11314,7 +11331,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="9:56" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11330,10 +11347,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="40">
+      <c r="X128" s="35">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="52">
+      <c r="Y128" s="40">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11374,7 +11391,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11390,8 +11407,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="41"/>
-      <c r="Y129" s="53"/>
+      <c r="X129" s="36"/>
+      <c r="Y129" s="41"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11430,7 +11447,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="130" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11452,12 +11469,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="75"/>
-      <c r="AE130" s="76"/>
-      <c r="AF130" s="76"/>
-      <c r="AG130" s="76"/>
-      <c r="AH130" s="76"/>
-      <c r="AI130" s="77"/>
+      <c r="AD130" s="44"/>
+      <c r="AE130" s="45"/>
+      <c r="AF130" s="45"/>
+      <c r="AG130" s="45"/>
+      <c r="AH130" s="45"/>
+      <c r="AI130" s="46"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11480,7 +11497,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11496,10 +11513,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="40" t="s">
+      <c r="X131" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="46">
+      <c r="Y131" s="42">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11540,7 +11557,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11556,8 +11573,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="41"/>
-      <c r="Y132" s="47"/>
+      <c r="X132" s="36"/>
+      <c r="Y132" s="43"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11596,7 +11613,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11618,12 +11635,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="75"/>
-      <c r="AE133" s="76"/>
-      <c r="AF133" s="76"/>
-      <c r="AG133" s="76"/>
-      <c r="AH133" s="76"/>
-      <c r="AI133" s="77"/>
+      <c r="AD133" s="44"/>
+      <c r="AE133" s="45"/>
+      <c r="AF133" s="45"/>
+      <c r="AG133" s="45"/>
+      <c r="AH133" s="45"/>
+      <c r="AI133" s="46"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11646,7 +11663,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="134" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11676,14 +11693,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="42" t="s">
+      <c r="AD134" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="42"/>
-      <c r="AF134" s="42"/>
-      <c r="AG134" s="42"/>
-      <c r="AH134" s="42"/>
-      <c r="AI134" s="42"/>
+      <c r="AE134" s="52"/>
+      <c r="AF134" s="52"/>
+      <c r="AG134" s="52"/>
+      <c r="AH134" s="52"/>
+      <c r="AI134" s="52"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11721,8 +11738,8 @@
     <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G153" s="89"/>
-      <c r="H153" s="89"/>
+      <c r="G153" s="67"/>
+      <c r="H153" s="67"/>
     </row>
     <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -11755,11 +11772,547 @@
     <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Diego"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="AS85:AX85"/>
+    <mergeCell ref="AN86:AN87"/>
+    <mergeCell ref="AS86:AX86"/>
+    <mergeCell ref="AS87:AX87"/>
+    <mergeCell ref="AN88:AN89"/>
+    <mergeCell ref="AS88:AX88"/>
+    <mergeCell ref="AS89:AX89"/>
+    <mergeCell ref="AS90:AX90"/>
+    <mergeCell ref="BC19:BD19"/>
+    <mergeCell ref="BC21:BD21"/>
+    <mergeCell ref="BC22:BD22"/>
+    <mergeCell ref="BC23:BD23"/>
+    <mergeCell ref="BC24:BD24"/>
+    <mergeCell ref="BC25:BD25"/>
+    <mergeCell ref="BC26:BD26"/>
+    <mergeCell ref="BC27:BD27"/>
+    <mergeCell ref="BC28:BD28"/>
+    <mergeCell ref="BC29:BD29"/>
+    <mergeCell ref="BC30:BD30"/>
+    <mergeCell ref="BC31:BD31"/>
+    <mergeCell ref="BC32:BD32"/>
+    <mergeCell ref="BC33:BD33"/>
+    <mergeCell ref="BC34:BD34"/>
+    <mergeCell ref="BC35:BD35"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
     <mergeCell ref="I86:I87"/>
     <mergeCell ref="X131:X132"/>
     <mergeCell ref="X128:X129"/>
@@ -11784,536 +12337,6 @@
     <mergeCell ref="X105:X106"/>
     <mergeCell ref="AD88:AI88"/>
     <mergeCell ref="AD89:AI89"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AS85:AX85"/>
-    <mergeCell ref="AN86:AN87"/>
-    <mergeCell ref="AS86:AX86"/>
-    <mergeCell ref="AS87:AX87"/>
-    <mergeCell ref="AN88:AN89"/>
-    <mergeCell ref="AS88:AX88"/>
-    <mergeCell ref="AS89:AX89"/>
-    <mergeCell ref="AS90:AX90"/>
-    <mergeCell ref="BC19:BD19"/>
-    <mergeCell ref="BC21:BD21"/>
-    <mergeCell ref="BC22:BD22"/>
-    <mergeCell ref="BC23:BD23"/>
-    <mergeCell ref="BC24:BD24"/>
-    <mergeCell ref="BC25:BD25"/>
-    <mergeCell ref="BC26:BD26"/>
-    <mergeCell ref="BC27:BD27"/>
-    <mergeCell ref="BC28:BD28"/>
-    <mergeCell ref="BC29:BD29"/>
-    <mergeCell ref="BC30:BD30"/>
-    <mergeCell ref="BC31:BD31"/>
-    <mergeCell ref="BC32:BD32"/>
-    <mergeCell ref="BC33:BD33"/>
-    <mergeCell ref="BC34:BD34"/>
-    <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addan\OneDrive\Documentos\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAE410C-7C32-4B1F-8D6B-B6D1959FC6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65FECCC-2382-44BC-A71A-84A875C764F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="219">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -694,6 +691,9 @@
   </si>
   <si>
     <t>06-07.2025</t>
+  </si>
+  <si>
+    <t>Vicente</t>
   </si>
 </sst>
 </file>
@@ -1180,11 +1180,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1195,17 +1195,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1216,77 +1309,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1303,15 +1333,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1321,40 +1342,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1691,109 +1691,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="G2:BD230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="8.375" customWidth="1"/>
-    <col min="9" max="9" width="13.125" customWidth="1"/>
-    <col min="10" max="10" width="105.875" customWidth="1"/>
-    <col min="11" max="11" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="105.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.875" customWidth="1"/>
-    <col min="20" max="20" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11.125" customWidth="1"/>
-    <col min="23" max="23" width="10.625" customWidth="1"/>
-    <col min="24" max="24" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="104.25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.25" customWidth="1"/>
+    <col min="14" max="18" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.85546875" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="104.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.28515625" customWidth="1"/>
     <col min="35" max="35" width="37" customWidth="1"/>
-    <col min="36" max="36" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.875" customWidth="1"/>
-    <col min="39" max="39" width="6.875" customWidth="1"/>
-    <col min="40" max="40" width="13.625" customWidth="1"/>
-    <col min="41" max="41" width="105.625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.85546875" customWidth="1"/>
+    <col min="39" max="39" width="6.85546875" customWidth="1"/>
+    <col min="40" max="40" width="13.5703125" customWidth="1"/>
+    <col min="41" max="41" width="105.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="45.875" customWidth="1"/>
-    <col min="51" max="51" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16373" max="16373" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="45.85546875" customWidth="1"/>
+    <col min="51" max="51" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16373" max="16373" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I2" s="82" t="s">
+    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="76" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="72" t="s">
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="76" t="s">
+      <c r="U2" s="83"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="77"/>
-      <c r="AH2" s="77"/>
-      <c r="AI2" s="78"/>
-      <c r="AJ2" s="71" t="s">
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="71"/>
-      <c r="AN2" s="74" t="s">
+      <c r="AK2" s="81"/>
+      <c r="AN2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="74"/>
-      <c r="AP2" s="74"/>
-      <c r="AQ2" s="74"/>
-      <c r="AR2" s="74"/>
-      <c r="AS2" s="75" t="s">
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AQ2" s="84"/>
+      <c r="AR2" s="84"/>
+      <c r="AS2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="75"/>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="75"/>
-      <c r="AX2" s="75"/>
-      <c r="AY2" s="71" t="s">
+      <c r="AT2" s="85"/>
+      <c r="AU2" s="85"/>
+      <c r="AV2" s="85"/>
+      <c r="AW2" s="85"/>
+      <c r="AX2" s="85"/>
+      <c r="AY2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71" t="s">
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="71"/>
-      <c r="BC2" s="71" t="s">
+      <c r="BB2" s="81"/>
+      <c r="BC2" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="71"/>
-    </row>
-    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BD2" s="81"/>
+    </row>
+    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1809,12 +1807,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="85"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="87"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="74"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1839,12 +1837,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="81"/>
+      <c r="AD3" s="86"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="88"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1866,12 +1864,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="75"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
+      <c r="AS3" s="85"/>
+      <c r="AT3" s="85"/>
+      <c r="AU3" s="85"/>
+      <c r="AV3" s="85"/>
+      <c r="AW3" s="85"/>
+      <c r="AX3" s="85"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1884,13 +1882,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="71" t="s">
+      <c r="BC3" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="71"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I4" s="92">
+      <c r="BD3" s="81"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="62">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1921,10 +1919,10 @@
       </c>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="35">
+      <c r="X4" s="40">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="88">
+      <c r="Y4" s="50">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1955,7 +1953,7 @@
       </c>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="68">
+      <c r="AN4" s="90">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1984,11 +1982,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I5" s="69"/>
+      <c r="BC4" s="35"/>
+      <c r="BD4" s="35"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="63"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2001,7 +1999,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="66" t="s">
+      <c r="N5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2017,8 +2015,8 @@
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="89"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="51"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2031,14 +2029,14 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="91" t="s">
+      <c r="AD5" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46"/>
+      <c r="AE5" s="76"/>
+      <c r="AF5" s="76"/>
+      <c r="AG5" s="76"/>
+      <c r="AH5" s="76"/>
+      <c r="AI5" s="77"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
@@ -2047,7 +2045,7 @@
       </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="69"/>
+      <c r="AN5" s="63"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2060,7 +2058,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="66" t="s">
+      <c r="AS5" s="65" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2074,11 +2072,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="44"/>
-      <c r="BD5" s="46"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I6" s="70"/>
+      <c r="BC5" s="75"/>
+      <c r="BD5" s="77"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="64"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2107,8 +2105,8 @@
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="90"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="79"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2121,14 +2119,14 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AD6" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="77"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
@@ -2137,7 +2135,7 @@
       </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="70"/>
+      <c r="AN6" s="64"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2164,11 +2162,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="64"/>
-      <c r="BD6" s="64"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I7" s="35">
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="35"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="40">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2205,17 +2203,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="45"/>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="76"/>
+      <c r="AG7" s="76"/>
+      <c r="AH7" s="76"/>
+      <c r="AI7" s="77"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="35">
+      <c r="AN7" s="40">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2244,11 +2242,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="64"/>
-      <c r="BD7" s="64"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I8" s="36"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="41"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2277,10 +2275,10 @@
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="52">
+      <c r="X8" s="42">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="88">
+      <c r="Y8" s="50">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2311,7 +2309,7 @@
       </c>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="55"/>
+      <c r="AN8" s="48"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2338,11 +2336,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="64"/>
-      <c r="BD8" s="64"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I9" s="35">
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="35"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2373,8 +2371,8 @@
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="89"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="51"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2403,7 +2401,7 @@
       </c>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="35">
+      <c r="AN9" s="40">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2432,11 +2430,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="64"/>
-      <c r="BD9" s="64"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I10" s="36"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="35"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="41"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2471,17 +2469,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="77"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="55"/>
+      <c r="AN10" s="48"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2508,11 +2506,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="64"/>
-      <c r="BD10" s="64"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I11" s="35">
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="35"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2527,7 +2525,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="66" t="s">
+      <c r="N11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2543,10 +2541,10 @@
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="52">
+      <c r="X11" s="42">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="42">
+      <c r="Y11" s="46">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2577,7 +2575,7 @@
       </c>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="35">
+      <c r="AN11" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2592,7 +2590,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="66" t="s">
+      <c r="AS11" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2606,11 +2604,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="64"/>
-      <c r="BD11" s="64"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I12" s="55"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="35"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I12" s="48"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2623,7 +2621,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2639,8 +2637,8 @@
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="43"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="47"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2669,7 +2667,7 @@
       </c>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="55"/>
+      <c r="AN12" s="48"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2682,7 +2680,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="66" t="s">
+      <c r="AS12" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2696,11 +2694,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="64"/>
-      <c r="BD12" s="64"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I13" s="36"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="41"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2735,17 +2733,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="45"/>
-      <c r="AF13" s="45"/>
-      <c r="AG13" s="45"/>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="46"/>
+      <c r="AD13" s="75"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="77"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="36"/>
+      <c r="AN13" s="41"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2772,11 +2770,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="64"/>
-      <c r="BD13" s="64"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I14" s="35">
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="35"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="40">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2807,10 +2805,10 @@
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="52">
+      <c r="X14" s="42">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="40">
+      <c r="Y14" s="52">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2825,7 +2823,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="66" t="s">
+      <c r="AD14" s="65" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2841,7 +2839,7 @@
       </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="35">
+      <c r="AN14" s="40">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2870,11 +2868,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="64"/>
-      <c r="BD14" s="64"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I15" s="55"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="35"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="48"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2903,8 +2901,8 @@
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="62"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="78"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2917,7 +2915,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="66" t="s">
+      <c r="AD15" s="65" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2933,7 +2931,7 @@
       </c>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="55"/>
+      <c r="AN15" s="48"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2960,11 +2958,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="64"/>
-      <c r="BD15" s="64"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I16" s="36"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="35"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="41"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2993,8 +2991,8 @@
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="41"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="53"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -3023,7 +3021,7 @@
       </c>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="55"/>
+      <c r="AN16" s="48"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3050,11 +3048,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="65"/>
-      <c r="BD16" s="65"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I17" s="53">
+      <c r="BC16" s="36"/>
+      <c r="BD16" s="36"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="92">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3091,17 +3089,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45"/>
-      <c r="AG17" s="45"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="46"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="77"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="93">
+      <c r="AN17" s="49">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3130,11 +3128,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="64"/>
-      <c r="BD17" s="64"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I18" s="54"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="35"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="93"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3163,10 +3161,10 @@
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="52">
+      <c r="X18" s="42">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="40">
+      <c r="Y18" s="52">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3197,7 +3195,7 @@
       </c>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="93"/>
+      <c r="AN18" s="49"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3224,18 +3222,22 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="64"/>
-      <c r="BD18" s="64"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I19" s="35" t="s">
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="35"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="19"/>
+      <c r="K19" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L19" s="19">
+        <v>3</v>
+      </c>
       <c r="M19" s="6" t="s">
         <v>13</v>
       </c>
@@ -3247,12 +3249,16 @@
       <c r="Q19" s="38"/>
       <c r="R19" s="38"/>
       <c r="S19" s="39"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="6"/>
+      <c r="T19" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U19" s="7">
+        <v>45912</v>
+      </c>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="62"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="78"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3281,7 +3287,7 @@
       </c>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="35" t="s">
+      <c r="AN19" s="40" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3304,16 +3310,20 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="64"/>
-      <c r="BD19" s="64"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I20" s="36"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="35"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="41"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="19"/>
+      <c r="K20" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L20" s="19">
+        <v>3</v>
+      </c>
       <c r="M20" s="6" t="s">
         <v>13</v>
       </c>
@@ -3325,12 +3335,16 @@
       <c r="Q20" s="38"/>
       <c r="R20" s="38"/>
       <c r="S20" s="39"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
+      <c r="T20" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U20" s="7">
+        <v>45912</v>
+      </c>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="52"/>
-      <c r="Y20" s="41"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="53"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3359,7 +3373,7 @@
       </c>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="36"/>
+      <c r="AN20" s="41"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3380,11 +3394,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="64"/>
-      <c r="BD20" s="64"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I21" s="35">
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="35"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="40">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3421,17 +3435,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="46"/>
+      <c r="AD21" s="75"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="77"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="35">
+      <c r="AN21" s="40">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3462,11 +3476,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="64"/>
-      <c r="BD21" s="64"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I22" s="55"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="35"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="48"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3495,10 +3509,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="93">
+      <c r="X22" s="49">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="40">
+      <c r="Y22" s="52">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3529,7 +3543,7 @@
       </c>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="55"/>
+      <c r="AN22" s="48"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3558,11 +3572,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I23" s="36"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="35"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I23" s="41"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3591,8 +3605,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="93"/>
-      <c r="Y23" s="41"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="53"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3621,7 +3635,7 @@
       </c>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="36"/>
+      <c r="AN23" s="41"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3650,11 +3664,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="64"/>
-      <c r="BD23" s="64"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I24" s="35" t="s">
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="35"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3691,17 +3705,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="44"/>
-      <c r="AE24" s="45"/>
-      <c r="AF24" s="45"/>
-      <c r="AG24" s="45"/>
-      <c r="AH24" s="45"/>
-      <c r="AI24" s="46"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="76"/>
+      <c r="AF24" s="76"/>
+      <c r="AG24" s="76"/>
+      <c r="AH24" s="76"/>
+      <c r="AI24" s="77"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="35" t="s">
+      <c r="AN24" s="40" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3732,11 +3746,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="64"/>
-      <c r="BD24" s="64"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I25" s="36"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="35"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I25" s="41"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3765,10 +3779,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="35" t="s">
+      <c r="X25" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="42">
+      <c r="Y25" s="46">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3791,7 +3805,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="36"/>
+      <c r="AN25" s="41"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3820,11 +3834,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="64"/>
-      <c r="BD25" s="64"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I26" s="35" t="s">
+      <c r="BC25" s="35"/>
+      <c r="BD25" s="35"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3855,8 +3869,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="43"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="47"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3877,7 +3891,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="35" t="s">
+      <c r="AN26" s="40" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3908,11 +3922,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="64"/>
-      <c r="BD26" s="64"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I27" s="36"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="41"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3947,17 +3961,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="44"/>
-      <c r="AE27" s="45"/>
-      <c r="AF27" s="45"/>
-      <c r="AG27" s="45"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="46"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="77"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="36"/>
+      <c r="AN27" s="41"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3986,11 +4000,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="64"/>
-      <c r="BD27" s="64"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I28" s="35" t="s">
+      <c r="BC27" s="35"/>
+      <c r="BD27" s="35"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -4021,10 +4035,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="35">
+      <c r="X28" s="40">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="58">
+      <c r="Y28" s="60">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -4055,7 +4069,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="35" t="s">
+      <c r="AN28" s="40" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4086,11 +4100,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="65"/>
-      <c r="BD28" s="65"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I29" s="55"/>
+      <c r="BC28" s="36"/>
+      <c r="BD28" s="36"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I29" s="48"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4119,8 +4133,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="55"/>
-      <c r="Y29" s="63"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="91"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4149,7 +4163,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="55"/>
+      <c r="AN29" s="48"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4178,11 +4192,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="64"/>
-      <c r="BD29" s="64"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I30" s="36"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I30" s="41"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4211,8 +4225,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="59"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="61"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4241,7 +4255,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="36"/>
+      <c r="AN30" s="41"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4270,11 +4284,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="64"/>
-      <c r="BD30" s="64"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I31" s="35">
+      <c r="BC30" s="35"/>
+      <c r="BD30" s="35"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I31" s="40">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4311,17 +4325,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="44"/>
-      <c r="AE31" s="45"/>
-      <c r="AF31" s="45"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="45"/>
-      <c r="AI31" s="46"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="77"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="35">
+      <c r="AN31" s="40">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4352,11 +4366,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="64"/>
-      <c r="BD31" s="64"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I32" s="36"/>
+      <c r="BC31" s="35"/>
+      <c r="BD31" s="35"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I32" s="41"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4385,10 +4399,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="35">
+      <c r="X32" s="40">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="58">
+      <c r="Y32" s="60">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4419,7 +4433,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="36"/>
+      <c r="AN32" s="41"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4448,11 +4462,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="64"/>
-      <c r="BD32" s="64"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I33" s="35">
+      <c r="BC32" s="35"/>
+      <c r="BD32" s="35"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I33" s="40">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4483,8 +4497,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="59"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="61"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4513,7 +4527,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="35">
+      <c r="AN33" s="40">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4544,11 +4558,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="64"/>
-      <c r="BD33" s="64"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I34" s="36"/>
+      <c r="BC33" s="35"/>
+      <c r="BD33" s="35"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I34" s="41"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4583,17 +4597,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="44"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="45"/>
-      <c r="AG34" s="45"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="46"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="36"/>
+      <c r="AN34" s="41"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4622,11 +4636,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="64"/>
-      <c r="BD34" s="64"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I35" s="35">
+      <c r="BC34" s="35"/>
+      <c r="BD34" s="35"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4657,10 +4671,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="35" t="s">
+      <c r="X35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="42">
+      <c r="Y35" s="46">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4691,7 +4705,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="35">
+      <c r="AN35" s="40">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4722,11 +4736,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="64"/>
-      <c r="BD35" s="64"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I36" s="36"/>
+      <c r="BC35" s="35"/>
+      <c r="BD35" s="35"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I36" s="41"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4755,8 +4769,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="43"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="47"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4785,7 +4799,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="36"/>
+      <c r="AN36" s="41"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4814,11 +4828,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="64"/>
-      <c r="BD36" s="64"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I37" s="35">
+      <c r="BC36" s="35"/>
+      <c r="BD36" s="35"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4855,17 +4869,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="44"/>
-      <c r="AE37" s="45"/>
-      <c r="AF37" s="45"/>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="46"/>
+      <c r="AD37" s="75"/>
+      <c r="AE37" s="76"/>
+      <c r="AF37" s="76"/>
+      <c r="AG37" s="76"/>
+      <c r="AH37" s="76"/>
+      <c r="AI37" s="77"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="35">
+      <c r="AN37" s="40">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4896,11 +4910,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="64"/>
-      <c r="BD37" s="64"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I38" s="36"/>
+      <c r="BC37" s="35"/>
+      <c r="BD37" s="35"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I38" s="41"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4929,10 +4943,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="35" t="s">
+      <c r="X38" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="40">
+      <c r="Y38" s="52">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4963,7 +4977,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="36"/>
+      <c r="AN38" s="41"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4992,10 +5006,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="64"/>
-      <c r="BD38" s="64"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC38" s="35"/>
+      <c r="BD38" s="35"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -5027,8 +5041,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="55"/>
-      <c r="Y39" s="62"/>
+      <c r="X39" s="48"/>
+      <c r="Y39" s="78"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5088,11 +5102,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="64"/>
-      <c r="BD39" s="64"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I40" s="35">
+      <c r="BC39" s="35"/>
+      <c r="BD39" s="35"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5123,8 +5137,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="36"/>
-      <c r="Y40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="53"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5153,7 +5167,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="35">
+      <c r="AN40" s="40">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5184,11 +5198,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="65"/>
-      <c r="BD40" s="65"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I41" s="36"/>
+      <c r="BC40" s="36"/>
+      <c r="BD40" s="36"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I41" s="41"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5201,14 +5215,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="47" t="s">
+      <c r="N41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="49"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="45"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5223,17 +5237,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="44"/>
-      <c r="AE41" s="45"/>
-      <c r="AF41" s="45"/>
-      <c r="AG41" s="45"/>
-      <c r="AH41" s="45"/>
-      <c r="AI41" s="46"/>
+      <c r="AD41" s="75"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="76"/>
+      <c r="AG41" s="76"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="77"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="36"/>
+      <c r="AN41" s="41"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5246,14 +5260,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="47" t="s">
+      <c r="AS41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="48"/>
-      <c r="AU41" s="48"/>
-      <c r="AV41" s="48"/>
-      <c r="AW41" s="48"/>
-      <c r="AX41" s="49"/>
+      <c r="AT41" s="44"/>
+      <c r="AU41" s="44"/>
+      <c r="AV41" s="44"/>
+      <c r="AW41" s="44"/>
+      <c r="AX41" s="45"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5262,10 +5276,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="64"/>
-      <c r="BD41" s="64"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC41" s="35"/>
+      <c r="BD41" s="35"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5297,10 +5311,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="35">
+      <c r="X42" s="40">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="40">
+      <c r="Y42" s="52">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5362,11 +5376,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="64"/>
-      <c r="BD42" s="64"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I43" s="35">
+      <c r="BC42" s="35"/>
+      <c r="BD42" s="35"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I43" s="40">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5397,8 +5411,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="53"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5427,7 +5441,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="35">
+      <c r="AN43" s="40">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5458,11 +5472,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="64"/>
-      <c r="BD43" s="64"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I44" s="36"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="41"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5497,17 +5511,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="44"/>
-      <c r="AE44" s="45"/>
-      <c r="AF44" s="45"/>
-      <c r="AG44" s="45"/>
-      <c r="AH44" s="45"/>
-      <c r="AI44" s="46"/>
+      <c r="AD44" s="75"/>
+      <c r="AE44" s="76"/>
+      <c r="AF44" s="76"/>
+      <c r="AG44" s="76"/>
+      <c r="AH44" s="76"/>
+      <c r="AI44" s="77"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="36"/>
+      <c r="AN44" s="41"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5536,10 +5550,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="64"/>
-      <c r="BD44" s="64"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC44" s="35"/>
+      <c r="BD44" s="35"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5571,10 +5585,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="35">
+      <c r="X45" s="40">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="58">
+      <c r="Y45" s="60">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5636,11 +5650,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="64"/>
-      <c r="BD45" s="64"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I46" s="35" t="s">
+      <c r="BC45" s="35"/>
+      <c r="BD45" s="35"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5671,8 +5685,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="59"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="61"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5701,7 +5715,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="35" t="s">
+      <c r="AN46" s="40" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5732,11 +5746,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="64"/>
-      <c r="BD46" s="64"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I47" s="36"/>
+      <c r="BC46" s="35"/>
+      <c r="BD46" s="35"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I47" s="41"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5771,17 +5785,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="45"/>
-      <c r="AF47" s="45"/>
-      <c r="AG47" s="45"/>
-      <c r="AH47" s="45"/>
-      <c r="AI47" s="46"/>
+      <c r="AD47" s="75"/>
+      <c r="AE47" s="76"/>
+      <c r="AF47" s="76"/>
+      <c r="AG47" s="76"/>
+      <c r="AH47" s="76"/>
+      <c r="AI47" s="77"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="36"/>
+      <c r="AN47" s="41"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5810,11 +5824,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="64"/>
-      <c r="BD47" s="64"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I48" s="35" t="s">
+      <c r="BC47" s="35"/>
+      <c r="BD47" s="35"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5845,10 +5859,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="35">
+      <c r="X48" s="40">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="42">
+      <c r="Y48" s="46">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5879,7 +5893,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="35" t="s">
+      <c r="AN48" s="40" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5910,11 +5924,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="64"/>
-      <c r="BD48" s="64"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I49" s="36"/>
+      <c r="BC48" s="35"/>
+      <c r="BD48" s="35"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I49" s="41"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5943,8 +5957,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="36"/>
-      <c r="Y49" s="43"/>
+      <c r="X49" s="41"/>
+      <c r="Y49" s="47"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5973,7 +5987,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="36"/>
+      <c r="AN49" s="41"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -6002,12 +6016,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="64"/>
-      <c r="BD49" s="64"/>
-    </row>
-    <row r="50" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC49" s="35"/>
+      <c r="BD49" s="35"/>
+    </row>
+    <row r="50" spans="8:56" x14ac:dyDescent="0.25">
       <c r="H50" s="10"/>
-      <c r="I50" s="35">
+      <c r="I50" s="40">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -6022,14 +6036,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="47" t="s">
+      <c r="N50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-      <c r="R50" s="48"/>
-      <c r="S50" s="49"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="45"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -6044,17 +6058,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="45"/>
-      <c r="AG50" s="45"/>
-      <c r="AH50" s="45"/>
-      <c r="AI50" s="46"/>
+      <c r="AD50" s="75"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="76"/>
+      <c r="AH50" s="76"/>
+      <c r="AI50" s="77"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="35">
+      <c r="AN50" s="40">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6065,23 +6079,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="47" t="s">
+      <c r="AS50" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="48"/>
-      <c r="AU50" s="48"/>
-      <c r="AV50" s="48"/>
-      <c r="AW50" s="48"/>
-      <c r="AX50" s="49"/>
+      <c r="AT50" s="44"/>
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="45"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="64"/>
-      <c r="BD50" s="64"/>
-    </row>
-    <row r="51" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I51" s="36"/>
+      <c r="BC50" s="35"/>
+      <c r="BD50" s="35"/>
+    </row>
+    <row r="51" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I51" s="41"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6094,14 +6108,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="47" t="s">
+      <c r="N51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="49"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="45"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6110,10 +6124,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="35">
+      <c r="X51" s="40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="40">
+      <c r="Y51" s="52">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6144,7 +6158,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="36"/>
+      <c r="AN51" s="41"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6153,23 +6167,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="47" t="s">
+      <c r="AS51" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="48"/>
-      <c r="AU51" s="48"/>
-      <c r="AV51" s="48"/>
-      <c r="AW51" s="48"/>
-      <c r="AX51" s="49"/>
+      <c r="AT51" s="44"/>
+      <c r="AU51" s="44"/>
+      <c r="AV51" s="44"/>
+      <c r="AW51" s="44"/>
+      <c r="AX51" s="45"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="64"/>
-      <c r="BD51" s="64"/>
-    </row>
-    <row r="52" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I52" s="35">
+      <c r="BC51" s="35"/>
+      <c r="BD51" s="35"/>
+    </row>
+    <row r="52" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I52" s="40">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6200,8 +6214,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="36"/>
-      <c r="Y52" s="41"/>
+      <c r="X52" s="41"/>
+      <c r="Y52" s="53"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6230,7 +6244,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="35">
+      <c r="AN52" s="40">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6253,11 +6267,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="65"/>
-      <c r="BD52" s="65"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I53" s="36"/>
+      <c r="BC52" s="36"/>
+      <c r="BD52" s="36"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I53" s="41"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6292,17 +6306,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="44"/>
-      <c r="AE53" s="45"/>
-      <c r="AF53" s="45"/>
-      <c r="AG53" s="45"/>
-      <c r="AH53" s="45"/>
-      <c r="AI53" s="46"/>
+      <c r="AD53" s="75"/>
+      <c r="AE53" s="76"/>
+      <c r="AF53" s="76"/>
+      <c r="AG53" s="76"/>
+      <c r="AH53" s="76"/>
+      <c r="AI53" s="77"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="36"/>
+      <c r="AN53" s="41"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6323,11 +6337,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="64"/>
-      <c r="BD53" s="64"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I54" s="35">
+      <c r="BC53" s="35"/>
+      <c r="BD53" s="35"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I54" s="40">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6392,7 +6406,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="35">
+      <c r="AN54" s="40">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6415,11 +6429,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="64"/>
-      <c r="BD54" s="64"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I55" s="36"/>
+      <c r="BC54" s="35"/>
+      <c r="BD54" s="35"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I55" s="41"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6454,17 +6468,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="44"/>
-      <c r="AE55" s="45"/>
-      <c r="AF55" s="45"/>
-      <c r="AG55" s="45"/>
-      <c r="AH55" s="45"/>
-      <c r="AI55" s="46"/>
+      <c r="AD55" s="75"/>
+      <c r="AE55" s="76"/>
+      <c r="AF55" s="76"/>
+      <c r="AG55" s="76"/>
+      <c r="AH55" s="76"/>
+      <c r="AI55" s="77"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="36"/>
+      <c r="AN55" s="41"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6485,10 +6499,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="64"/>
-      <c r="BD55" s="64"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC55" s="35"/>
+      <c r="BD55" s="35"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6520,10 +6534,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="35">
+      <c r="X56" s="40">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="58">
+      <c r="Y56" s="60">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6577,11 +6591,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="64"/>
-      <c r="BD56" s="64"/>
-    </row>
-    <row r="57" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I57" s="35">
+      <c r="BC56" s="35"/>
+      <c r="BD56" s="35"/>
+    </row>
+    <row r="57" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I57" s="40">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6612,8 +6626,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="36"/>
-      <c r="Y57" s="59"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="61"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6624,14 +6638,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="47" t="s">
+      <c r="AD57" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="48"/>
-      <c r="AF57" s="48"/>
-      <c r="AG57" s="48"/>
-      <c r="AH57" s="48"/>
-      <c r="AI57" s="49"/>
+      <c r="AE57" s="44"/>
+      <c r="AF57" s="44"/>
+      <c r="AG57" s="44"/>
+      <c r="AH57" s="44"/>
+      <c r="AI57" s="45"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6640,7 +6654,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="35">
+      <c r="AN57" s="40">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6663,11 +6677,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="64"/>
-      <c r="BD57" s="64"/>
-    </row>
-    <row r="58" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I58" s="36"/>
+      <c r="BC57" s="35"/>
+      <c r="BD57" s="35"/>
+    </row>
+    <row r="58" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I58" s="41"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6702,17 +6716,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="44"/>
-      <c r="AE58" s="45"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="45"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
+      <c r="AD58" s="75"/>
+      <c r="AE58" s="76"/>
+      <c r="AF58" s="76"/>
+      <c r="AG58" s="76"/>
+      <c r="AH58" s="76"/>
+      <c r="AI58" s="77"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="36"/>
+      <c r="AN58" s="41"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6733,11 +6747,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="64"/>
-      <c r="BD58" s="64"/>
-    </row>
-    <row r="59" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I59" s="35">
+      <c r="BC58" s="35"/>
+      <c r="BD58" s="35"/>
+    </row>
+    <row r="59" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I59" s="40">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6802,7 +6816,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="35">
+      <c r="AN59" s="40">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6825,11 +6839,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="64"/>
-      <c r="BD59" s="64"/>
-    </row>
-    <row r="60" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I60" s="36"/>
+      <c r="BC59" s="35"/>
+      <c r="BD59" s="35"/>
+    </row>
+    <row r="60" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I60" s="41"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6864,17 +6878,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="44"/>
-      <c r="AE60" s="45"/>
-      <c r="AF60" s="45"/>
-      <c r="AG60" s="45"/>
-      <c r="AH60" s="45"/>
-      <c r="AI60" s="46"/>
+      <c r="AD60" s="75"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="77"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="36"/>
+      <c r="AN60" s="41"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6895,11 +6909,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="64"/>
-      <c r="BD60" s="64"/>
-    </row>
-    <row r="61" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I61" s="35" t="s">
+      <c r="BC60" s="35"/>
+      <c r="BD60" s="35"/>
+    </row>
+    <row r="61" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6930,10 +6944,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="35">
+      <c r="X61" s="40">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="60">
+      <c r="Y61" s="58">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6964,7 +6978,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="35" t="s">
+      <c r="AN61" s="40" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -6987,11 +7001,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="64"/>
-      <c r="BD61" s="64"/>
-    </row>
-    <row r="62" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I62" s="36"/>
+      <c r="BC61" s="35"/>
+      <c r="BD61" s="35"/>
+    </row>
+    <row r="62" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="I62" s="41"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7020,8 +7034,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="36"/>
-      <c r="Y62" s="61"/>
+      <c r="X62" s="41"/>
+      <c r="Y62" s="59"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -7050,7 +7064,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="36"/>
+      <c r="AN62" s="41"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7071,11 +7085,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="64"/>
-      <c r="BD62" s="64"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I63" s="35">
+      <c r="BC62" s="35"/>
+      <c r="BD62" s="35"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I63" s="40">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7112,17 +7126,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="44"/>
-      <c r="AE63" s="45"/>
-      <c r="AF63" s="45"/>
-      <c r="AG63" s="45"/>
-      <c r="AH63" s="45"/>
-      <c r="AI63" s="46"/>
+      <c r="AD63" s="75"/>
+      <c r="AE63" s="76"/>
+      <c r="AF63" s="76"/>
+      <c r="AG63" s="76"/>
+      <c r="AH63" s="76"/>
+      <c r="AI63" s="77"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="35">
+      <c r="AN63" s="40">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7145,11 +7159,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="64"/>
-      <c r="BD63" s="64"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I64" s="36"/>
+      <c r="BC63" s="35"/>
+      <c r="BD63" s="35"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I64" s="41"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7212,7 +7226,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="36"/>
+      <c r="AN64" s="41"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7233,11 +7247,11 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="65"/>
-      <c r="BD64" s="65"/>
-    </row>
-    <row r="65" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I65" s="35">
+      <c r="BC64" s="36"/>
+      <c r="BD64" s="36"/>
+    </row>
+    <row r="65" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I65" s="40">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7266,17 +7280,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="44"/>
-      <c r="AE65" s="45"/>
-      <c r="AF65" s="45"/>
-      <c r="AG65" s="45"/>
-      <c r="AH65" s="45"/>
-      <c r="AI65" s="46"/>
+      <c r="AD65" s="75"/>
+      <c r="AE65" s="76"/>
+      <c r="AF65" s="76"/>
+      <c r="AG65" s="76"/>
+      <c r="AH65" s="76"/>
+      <c r="AI65" s="77"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="35">
+      <c r="AN65" s="40">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7299,11 +7313,11 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="64"/>
-      <c r="BD65" s="64"/>
-    </row>
-    <row r="66" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I66" s="36"/>
+      <c r="BC65" s="35"/>
+      <c r="BD65" s="35"/>
+    </row>
+    <row r="66" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I66" s="41"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7324,10 +7338,10 @@
       <c r="U66" s="6"/>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="35" t="s">
+      <c r="X66" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="56">
+      <c r="Y66" s="54">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7358,7 +7372,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="36"/>
+      <c r="AN66" s="41"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7379,10 +7393,10 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="64"/>
-      <c r="BD66" s="64"/>
-    </row>
-    <row r="67" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC66" s="35"/>
+      <c r="BD66" s="35"/>
+    </row>
+    <row r="67" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
@@ -7406,8 +7420,8 @@
       <c r="U67" s="6"/>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="36"/>
-      <c r="Y67" s="57"/>
+      <c r="X67" s="41"/>
+      <c r="Y67" s="55"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7459,11 +7473,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="64"/>
-      <c r="BD67" s="64"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I68" s="35">
+      <c r="BC67" s="35"/>
+      <c r="BD67" s="35"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I68" s="40">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7496,17 +7510,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="44"/>
-      <c r="AE68" s="45"/>
-      <c r="AF68" s="45"/>
-      <c r="AG68" s="45"/>
-      <c r="AH68" s="45"/>
-      <c r="AI68" s="46"/>
+      <c r="AD68" s="75"/>
+      <c r="AE68" s="76"/>
+      <c r="AF68" s="76"/>
+      <c r="AG68" s="76"/>
+      <c r="AH68" s="76"/>
+      <c r="AI68" s="77"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="35">
+      <c r="AN68" s="40">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7529,11 +7543,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="64"/>
-      <c r="BD68" s="64"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I69" s="36"/>
+      <c r="BC68" s="35"/>
+      <c r="BD68" s="35"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I69" s="41"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7558,10 +7572,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="35" t="s">
+      <c r="X69" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="56">
+      <c r="Y69" s="54">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7592,7 +7606,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="36"/>
+      <c r="AN69" s="41"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7613,18 +7627,22 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="64"/>
-      <c r="BD69" s="64"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC69" s="35"/>
+      <c r="BD69" s="35"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
       <c r="J70" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K70" s="6"/>
-      <c r="L70" s="19"/>
+      <c r="K70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L70">
+        <v>2</v>
+      </c>
       <c r="M70" s="6" t="s">
         <v>13</v>
       </c>
@@ -7636,12 +7654,16 @@
       <c r="Q70" s="38"/>
       <c r="R70" s="38"/>
       <c r="S70" s="39"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="6"/>
+      <c r="T70" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U70" s="7">
+        <v>45912</v>
+      </c>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="36"/>
-      <c r="Y70" s="57"/>
+      <c r="X70" s="41"/>
+      <c r="Y70" s="55"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7693,18 +7715,22 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="64"/>
-      <c r="BD70" s="64"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I71" s="35">
+      <c r="BC70" s="35"/>
+      <c r="BD70" s="35"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="40">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K71" s="6"/>
-      <c r="L71" s="19"/>
+      <c r="K71" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L71" s="19">
+        <v>2</v>
+      </c>
       <c r="M71" s="6" t="s">
         <v>13</v>
       </c>
@@ -7716,8 +7742,12 @@
       <c r="Q71" s="38"/>
       <c r="R71" s="38"/>
       <c r="S71" s="39"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="6"/>
+      <c r="T71" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U71" s="7">
+        <v>45912</v>
+      </c>
       <c r="V71" s="20"/>
       <c r="W71" s="20"/>
       <c r="X71" s="6"/>
@@ -7726,17 +7756,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="44"/>
-      <c r="AE71" s="45"/>
-      <c r="AF71" s="45"/>
-      <c r="AG71" s="45"/>
-      <c r="AH71" s="45"/>
-      <c r="AI71" s="46"/>
+      <c r="AD71" s="75"/>
+      <c r="AE71" s="76"/>
+      <c r="AF71" s="76"/>
+      <c r="AG71" s="76"/>
+      <c r="AH71" s="76"/>
+      <c r="AI71" s="77"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="35">
+      <c r="AN71" s="40">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7759,16 +7789,20 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="64"/>
-      <c r="BD71" s="64"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I72" s="36"/>
+      <c r="BC71" s="35"/>
+      <c r="BD71" s="35"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I72" s="41"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K72" s="6"/>
-      <c r="L72" s="19"/>
+      <c r="K72" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L72" s="19">
+        <v>2</v>
+      </c>
       <c r="M72" s="6" t="s">
         <v>13</v>
       </c>
@@ -7780,14 +7814,18 @@
       <c r="Q72" s="38"/>
       <c r="R72" s="38"/>
       <c r="S72" s="39"/>
-      <c r="T72" s="7"/>
-      <c r="U72" s="6"/>
+      <c r="T72" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U72" s="7">
+        <v>45912</v>
+      </c>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="35">
+      <c r="X72" s="40">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="40">
+      <c r="Y72" s="52">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7802,14 +7840,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="47" t="s">
+      <c r="AD72" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="48"/>
-      <c r="AF72" s="48"/>
-      <c r="AG72" s="48"/>
-      <c r="AH72" s="48"/>
-      <c r="AI72" s="49"/>
+      <c r="AE72" s="44"/>
+      <c r="AF72" s="44"/>
+      <c r="AG72" s="44"/>
+      <c r="AH72" s="44"/>
+      <c r="AI72" s="45"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7818,7 +7856,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="36"/>
+      <c r="AN72" s="41"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7839,35 +7877,43 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="64"/>
-      <c r="BD72" s="64"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I73" s="35">
+      <c r="BC72" s="35"/>
+      <c r="BD72" s="35"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K73" s="6"/>
-      <c r="L73" s="19"/>
+      <c r="K73" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L73" s="19">
+        <v>3</v>
+      </c>
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="47" t="s">
+      <c r="N73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="48"/>
-      <c r="P73" s="48"/>
-      <c r="Q73" s="48"/>
-      <c r="R73" s="48"/>
-      <c r="S73" s="49"/>
-      <c r="T73" s="7"/>
-      <c r="U73" s="6"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="44"/>
+      <c r="S73" s="45"/>
+      <c r="T73" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U73" s="7">
+        <v>45912</v>
+      </c>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="36"/>
-      <c r="Y73" s="41"/>
+      <c r="X73" s="41"/>
+      <c r="Y73" s="53"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7880,14 +7926,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="47" t="s">
+      <c r="AD73" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="48"/>
-      <c r="AF73" s="48"/>
-      <c r="AG73" s="48"/>
-      <c r="AH73" s="48"/>
-      <c r="AI73" s="49"/>
+      <c r="AE73" s="44"/>
+      <c r="AF73" s="44"/>
+      <c r="AG73" s="44"/>
+      <c r="AH73" s="44"/>
+      <c r="AI73" s="45"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7896,7 +7942,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="35">
+      <c r="AN73" s="40">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7907,28 +7953,32 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="47" t="s">
+      <c r="AS73" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="48"/>
-      <c r="AU73" s="48"/>
-      <c r="AV73" s="48"/>
-      <c r="AW73" s="48"/>
-      <c r="AX73" s="49"/>
+      <c r="AT73" s="44"/>
+      <c r="AU73" s="44"/>
+      <c r="AV73" s="44"/>
+      <c r="AW73" s="44"/>
+      <c r="AX73" s="45"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="64"/>
-      <c r="BD73" s="64"/>
-    </row>
-    <row r="74" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I74" s="36"/>
+      <c r="BC73" s="35"/>
+      <c r="BD73" s="35"/>
+    </row>
+    <row r="74" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I74" s="41"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K74" s="6"/>
-      <c r="L74" s="19"/>
+      <c r="K74" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L74" s="19">
+        <v>3</v>
+      </c>
       <c r="M74" s="6" t="s">
         <v>13</v>
       </c>
@@ -7940,8 +7990,12 @@
       <c r="Q74" s="38"/>
       <c r="R74" s="38"/>
       <c r="S74" s="39"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="6"/>
+      <c r="T74" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U74" s="7">
+        <v>45912</v>
+      </c>
       <c r="V74" s="20"/>
       <c r="W74" s="20"/>
       <c r="X74" s="6"/>
@@ -7950,17 +8004,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="44"/>
-      <c r="AE74" s="45"/>
-      <c r="AF74" s="45"/>
-      <c r="AG74" s="45"/>
-      <c r="AH74" s="45"/>
-      <c r="AI74" s="46"/>
+      <c r="AD74" s="75"/>
+      <c r="AE74" s="76"/>
+      <c r="AF74" s="76"/>
+      <c r="AG74" s="76"/>
+      <c r="AH74" s="76"/>
+      <c r="AI74" s="77"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="36"/>
+      <c r="AN74" s="41"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -7981,37 +8035,45 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="64"/>
-      <c r="BD74" s="64"/>
-    </row>
-    <row r="75" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I75" s="35">
+      <c r="BC74" s="35"/>
+      <c r="BD74" s="35"/>
+    </row>
+    <row r="75" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="K75" s="6"/>
-      <c r="L75" s="19"/>
+      <c r="K75" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L75" s="19">
+        <v>3</v>
+      </c>
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="47" t="s">
+      <c r="N75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="49"/>
-      <c r="T75" s="7"/>
-      <c r="U75" s="6"/>
+      <c r="O75" s="44"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="44"/>
+      <c r="R75" s="44"/>
+      <c r="S75" s="45"/>
+      <c r="T75" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U75" s="7">
+        <v>45912</v>
+      </c>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="35">
+      <c r="X75" s="40">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="58">
+      <c r="Y75" s="60">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -8042,7 +8104,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="35">
+      <c r="AN75" s="40">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -8053,28 +8115,32 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="47" t="s">
+      <c r="AS75" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="48"/>
-      <c r="AU75" s="48"/>
-      <c r="AV75" s="48"/>
-      <c r="AW75" s="48"/>
-      <c r="AX75" s="49"/>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="44"/>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="44"/>
+      <c r="AX75" s="45"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="64"/>
-      <c r="BD75" s="64"/>
-    </row>
-    <row r="76" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I76" s="36"/>
+      <c r="BC75" s="35"/>
+      <c r="BD75" s="35"/>
+    </row>
+    <row r="76" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I76" s="41"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="K76" s="6"/>
-      <c r="L76" s="19"/>
+      <c r="K76" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L76" s="19">
+        <v>3</v>
+      </c>
       <c r="M76" s="6" t="s">
         <v>13</v>
       </c>
@@ -8086,12 +8152,16 @@
       <c r="Q76" s="38"/>
       <c r="R76" s="38"/>
       <c r="S76" s="39"/>
-      <c r="T76" s="7"/>
-      <c r="U76" s="6"/>
+      <c r="T76" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U76" s="7">
+        <v>45912</v>
+      </c>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="36"/>
-      <c r="Y76" s="59"/>
+      <c r="X76" s="41"/>
+      <c r="Y76" s="61"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8120,7 +8190,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="36"/>
+      <c r="AN76" s="41"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8141,18 +8211,22 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="65"/>
-      <c r="BD76" s="65"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I77" s="35">
+      <c r="BC76" s="36"/>
+      <c r="BD76" s="36"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I77" s="40">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K77" s="6"/>
-      <c r="L77" s="19"/>
+      <c r="K77" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L77" s="19">
+        <v>3</v>
+      </c>
       <c r="M77" s="6" t="s">
         <v>13</v>
       </c>
@@ -8164,8 +8238,12 @@
       <c r="Q77" s="38"/>
       <c r="R77" s="38"/>
       <c r="S77" s="39"/>
-      <c r="T77" s="7"/>
-      <c r="U77" s="6"/>
+      <c r="T77" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U77" s="7">
+        <v>45912</v>
+      </c>
       <c r="V77" s="20"/>
       <c r="W77" s="20"/>
       <c r="X77" s="6"/>
@@ -8174,17 +8252,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="44"/>
-      <c r="AE77" s="45"/>
-      <c r="AF77" s="45"/>
-      <c r="AG77" s="45"/>
-      <c r="AH77" s="45"/>
-      <c r="AI77" s="46"/>
+      <c r="AD77" s="75"/>
+      <c r="AE77" s="76"/>
+      <c r="AF77" s="76"/>
+      <c r="AG77" s="76"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="77"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="35">
+      <c r="AN77" s="40">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8207,16 +8285,20 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="64"/>
-      <c r="BD77" s="64"/>
-    </row>
-    <row r="78" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I78" s="36"/>
+      <c r="BC77" s="35"/>
+      <c r="BD77" s="35"/>
+    </row>
+    <row r="78" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I78" s="41"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K78" s="6"/>
-      <c r="L78" s="19"/>
+      <c r="K78" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L78" s="19">
+        <v>3</v>
+      </c>
       <c r="M78" s="6" t="s">
         <v>13</v>
       </c>
@@ -8228,14 +8310,18 @@
       <c r="Q78" s="38"/>
       <c r="R78" s="38"/>
       <c r="S78" s="39"/>
-      <c r="T78" s="7"/>
-      <c r="U78" s="6"/>
+      <c r="T78" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U78" s="7">
+        <v>45912</v>
+      </c>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="35">
+      <c r="X78" s="40">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="40">
+      <c r="Y78" s="52">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8266,7 +8352,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="36"/>
+      <c r="AN78" s="41"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8287,11 +8373,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="64"/>
-      <c r="BD78" s="64"/>
-    </row>
-    <row r="79" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I79" s="35">
+      <c r="BC78" s="35"/>
+      <c r="BD78" s="35"/>
+    </row>
+    <row r="79" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I79" s="40">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8304,22 +8390,22 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="47" t="s">
+      <c r="N79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="48"/>
-      <c r="P79" s="48"/>
-      <c r="Q79" s="48"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="49"/>
+      <c r="O79" s="44"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="44"/>
+      <c r="R79" s="44"/>
+      <c r="S79" s="45"/>
       <c r="T79" s="7">
         <v>45905</v>
       </c>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="36"/>
-      <c r="Y79" s="41"/>
+      <c r="X79" s="41"/>
+      <c r="Y79" s="53"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8348,7 +8434,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="35">
+      <c r="AN79" s="40">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8359,23 +8445,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="47" t="s">
+      <c r="AS79" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="48"/>
-      <c r="AU79" s="48"/>
-      <c r="AV79" s="48"/>
-      <c r="AW79" s="48"/>
-      <c r="AX79" s="49"/>
+      <c r="AT79" s="44"/>
+      <c r="AU79" s="44"/>
+      <c r="AV79" s="44"/>
+      <c r="AW79" s="44"/>
+      <c r="AX79" s="45"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="64"/>
-      <c r="BD79" s="64"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I80" s="36"/>
+      <c r="BC79" s="35"/>
+      <c r="BD79" s="35"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I80" s="41"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8406,17 +8492,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="44"/>
-      <c r="AE80" s="45"/>
-      <c r="AF80" s="45"/>
-      <c r="AG80" s="45"/>
-      <c r="AH80" s="45"/>
-      <c r="AI80" s="46"/>
+      <c r="AD80" s="75"/>
+      <c r="AE80" s="76"/>
+      <c r="AF80" s="76"/>
+      <c r="AG80" s="76"/>
+      <c r="AH80" s="76"/>
+      <c r="AI80" s="77"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="36"/>
+      <c r="AN80" s="41"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8437,11 +8523,11 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="64"/>
-      <c r="BD80" s="64"/>
-    </row>
-    <row r="81" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I81" s="35">
+      <c r="BC80" s="35"/>
+      <c r="BD80" s="35"/>
+    </row>
+    <row r="81" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I81" s="40">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -8498,7 +8584,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="35">
+      <c r="AN81" s="40">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8521,11 +8607,11 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="64"/>
-      <c r="BD81" s="64"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I82" s="36"/>
+      <c r="BC81" s="35"/>
+      <c r="BD81" s="35"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I82" s="41"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8534,14 +8620,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="47" t="s">
+      <c r="N82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="48"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="48"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="49"/>
+      <c r="O82" s="44"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="44"/>
+      <c r="R82" s="44"/>
+      <c r="S82" s="45"/>
       <c r="T82" s="7"/>
       <c r="U82" s="6"/>
       <c r="V82" s="20"/>
@@ -8552,17 +8638,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="44"/>
-      <c r="AE82" s="45"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="45"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
+      <c r="AD82" s="75"/>
+      <c r="AE82" s="76"/>
+      <c r="AF82" s="76"/>
+      <c r="AG82" s="76"/>
+      <c r="AH82" s="76"/>
+      <c r="AI82" s="77"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="36"/>
+      <c r="AN82" s="41"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8571,23 +8657,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="47" t="s">
+      <c r="AS82" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="48"/>
-      <c r="AU82" s="48"/>
-      <c r="AV82" s="48"/>
-      <c r="AW82" s="48"/>
-      <c r="AX82" s="49"/>
+      <c r="AT82" s="44"/>
+      <c r="AU82" s="44"/>
+      <c r="AV82" s="44"/>
+      <c r="AW82" s="44"/>
+      <c r="AX82" s="45"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="64"/>
-      <c r="BD82" s="64"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I83" s="35">
+      <c r="BC82" s="35"/>
+      <c r="BD82" s="35"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I83" s="40">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8618,10 +8704,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="35">
+      <c r="X83" s="40">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="56">
+      <c r="Y83" s="54">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8652,7 +8738,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="35">
+      <c r="AN83" s="40">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8681,11 +8767,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="64"/>
-      <c r="BD83" s="64"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I84" s="36"/>
+      <c r="BC83" s="35"/>
+      <c r="BD83" s="35"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I84" s="41"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8714,8 +8800,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="36"/>
-      <c r="Y84" s="57"/>
+      <c r="X84" s="41"/>
+      <c r="Y84" s="55"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8744,7 +8830,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="36"/>
+      <c r="AN84" s="41"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8771,10 +8857,10 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="64"/>
-      <c r="BD84" s="64"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BC84" s="35"/>
+      <c r="BD84" s="35"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
@@ -8804,12 +8890,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="44"/>
-      <c r="AE85" s="45"/>
-      <c r="AF85" s="45"/>
-      <c r="AG85" s="45"/>
-      <c r="AH85" s="45"/>
-      <c r="AI85" s="46"/>
+      <c r="AD85" s="75"/>
+      <c r="AE85" s="76"/>
+      <c r="AF85" s="76"/>
+      <c r="AG85" s="76"/>
+      <c r="AH85" s="76"/>
+      <c r="AI85" s="77"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8837,18 +8923,22 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="64"/>
-      <c r="BD85" s="64"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I86" s="35">
+      <c r="BC85" s="35"/>
+      <c r="BD85" s="35"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I86" s="40">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K86" s="6"/>
-      <c r="L86" s="19"/>
+      <c r="K86" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L86" s="19">
+        <v>3</v>
+      </c>
       <c r="M86" s="6" t="s">
         <v>13</v>
       </c>
@@ -8860,14 +8950,18 @@
       <c r="Q86" s="38"/>
       <c r="R86" s="38"/>
       <c r="S86" s="39"/>
-      <c r="T86" s="7"/>
-      <c r="U86" s="6"/>
+      <c r="T86" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U86" s="7">
+        <v>45912</v>
+      </c>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="35">
+      <c r="X86" s="40">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="50">
+      <c r="Y86" s="56">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8898,7 +8992,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="35">
+      <c r="AN86" s="40">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -8921,16 +9015,20 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="64"/>
-      <c r="BD86" s="64"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I87" s="36"/>
+      <c r="BC86" s="35"/>
+      <c r="BD86" s="35"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I87" s="41"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K87" s="6"/>
-      <c r="L87" s="19"/>
+      <c r="K87" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L87" s="19">
+        <v>3</v>
+      </c>
       <c r="M87" s="6" t="s">
         <v>13</v>
       </c>
@@ -8942,12 +9040,16 @@
       <c r="Q87" s="38"/>
       <c r="R87" s="38"/>
       <c r="S87" s="39"/>
-      <c r="T87" s="7"/>
-      <c r="U87" s="6"/>
+      <c r="T87" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U87" s="7">
+        <v>45912</v>
+      </c>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="36"/>
-      <c r="Y87" s="51"/>
+      <c r="X87" s="41"/>
+      <c r="Y87" s="57"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -8976,7 +9078,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="36"/>
+      <c r="AN87" s="41"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -8997,18 +9099,22 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="64"/>
-      <c r="BD87" s="64"/>
-    </row>
-    <row r="88" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I88" s="35" t="s">
+      <c r="BC87" s="35"/>
+      <c r="BD87" s="35"/>
+    </row>
+    <row r="88" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K88" s="6"/>
-      <c r="L88" s="19"/>
+      <c r="K88" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L88" s="19">
+        <v>3</v>
+      </c>
       <c r="M88" s="6" t="s">
         <v>13</v>
       </c>
@@ -9020,8 +9126,12 @@
       <c r="Q88" s="38"/>
       <c r="R88" s="38"/>
       <c r="S88" s="39"/>
-      <c r="T88" s="7"/>
-      <c r="U88" s="6"/>
+      <c r="T88" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U88" s="7">
+        <v>45912</v>
+      </c>
       <c r="V88" s="20"/>
       <c r="W88" s="20"/>
       <c r="X88" s="6"/>
@@ -9030,17 +9140,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="44"/>
-      <c r="AE88" s="45"/>
-      <c r="AF88" s="45"/>
-      <c r="AG88" s="45"/>
-      <c r="AH88" s="45"/>
-      <c r="AI88" s="46"/>
+      <c r="AD88" s="75"/>
+      <c r="AE88" s="76"/>
+      <c r="AF88" s="76"/>
+      <c r="AG88" s="76"/>
+      <c r="AH88" s="76"/>
+      <c r="AI88" s="77"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="35" t="s">
+      <c r="AN88" s="40" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -9063,16 +9173,20 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="65"/>
-      <c r="BD88" s="65"/>
-    </row>
-    <row r="89" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
-      <c r="I89" s="36"/>
+      <c r="BC88" s="36"/>
+      <c r="BD88" s="36"/>
+    </row>
+    <row r="89" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="I89" s="41"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="K89" s="6"/>
-      <c r="L89" s="19"/>
+      <c r="K89" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L89" s="19">
+        <v>3</v>
+      </c>
       <c r="M89" s="6" t="s">
         <v>13</v>
       </c>
@@ -9084,14 +9198,18 @@
       <c r="Q89" s="38"/>
       <c r="R89" s="38"/>
       <c r="S89" s="39"/>
-      <c r="T89" s="7"/>
-      <c r="U89" s="6"/>
+      <c r="T89" s="8">
+        <v>45844</v>
+      </c>
+      <c r="U89" s="7">
+        <v>45912</v>
+      </c>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="35" t="s">
+      <c r="X89" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="50">
+      <c r="Y89" s="56">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9122,7 +9240,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="36"/>
+      <c r="AN89" s="41"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9143,10 +9261,10 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="64"/>
-      <c r="BD89" s="64"/>
-    </row>
-    <row r="90" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC89" s="35"/>
+      <c r="BD89" s="35"/>
+    </row>
+    <row r="90" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
@@ -9158,20 +9276,20 @@
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="52" t="s">
+      <c r="N90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
+      <c r="O90" s="42"/>
+      <c r="P90" s="42"/>
+      <c r="Q90" s="42"/>
+      <c r="R90" s="42"/>
+      <c r="S90" s="42"/>
       <c r="T90" s="7"/>
       <c r="U90" s="6"/>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="36"/>
-      <c r="Y90" s="51"/>
+      <c r="X90" s="41"/>
+      <c r="Y90" s="57"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9211,22 +9329,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="52" t="s">
+      <c r="AS90" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
+      <c r="AT90" s="42"/>
+      <c r="AU90" s="42"/>
+      <c r="AV90" s="42"/>
+      <c r="AW90" s="42"/>
+      <c r="AX90" s="42"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="64"/>
-      <c r="BD90" s="64"/>
-    </row>
-    <row r="91" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+      <c r="BC90" s="35"/>
+      <c r="BD90" s="35"/>
+    </row>
+    <row r="91" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9248,12 +9366,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="44"/>
-      <c r="AE91" s="45"/>
-      <c r="AF91" s="45"/>
-      <c r="AG91" s="45"/>
-      <c r="AH91" s="45"/>
-      <c r="AI91" s="46"/>
+      <c r="AD91" s="75"/>
+      <c r="AE91" s="76"/>
+      <c r="AF91" s="76"/>
+      <c r="AG91" s="76"/>
+      <c r="AH91" s="76"/>
+      <c r="AI91" s="77"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9276,7 +9394,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9292,10 +9410,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="35">
+      <c r="X92" s="40">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="58">
+      <c r="Y92" s="60">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9344,7 +9462,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9360,8 +9478,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="36"/>
-      <c r="Y93" s="59"/>
+      <c r="X93" s="41"/>
+      <c r="Y93" s="61"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9408,7 +9526,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9430,12 +9548,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="44"/>
-      <c r="AE94" s="45"/>
-      <c r="AF94" s="45"/>
-      <c r="AG94" s="45"/>
-      <c r="AH94" s="45"/>
-      <c r="AI94" s="46"/>
+      <c r="AD94" s="75"/>
+      <c r="AE94" s="76"/>
+      <c r="AF94" s="76"/>
+      <c r="AG94" s="76"/>
+      <c r="AH94" s="76"/>
+      <c r="AI94" s="77"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9458,7 +9576,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9474,10 +9592,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="35">
+      <c r="X95" s="40">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="60">
+      <c r="Y95" s="58">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9518,7 +9636,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9534,8 +9652,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="36"/>
-      <c r="Y96" s="61"/>
+      <c r="X96" s="41"/>
+      <c r="Y96" s="59"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9574,7 +9692,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9596,12 +9714,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="44"/>
-      <c r="AE97" s="45"/>
-      <c r="AF97" s="45"/>
-      <c r="AG97" s="45"/>
-      <c r="AH97" s="45"/>
-      <c r="AI97" s="46"/>
+      <c r="AD97" s="75"/>
+      <c r="AE97" s="76"/>
+      <c r="AF97" s="76"/>
+      <c r="AG97" s="76"/>
+      <c r="AH97" s="76"/>
+      <c r="AI97" s="77"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9624,7 +9742,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9684,7 +9802,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9706,12 +9824,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="44"/>
-      <c r="AE99" s="45"/>
-      <c r="AF99" s="45"/>
-      <c r="AG99" s="45"/>
-      <c r="AH99" s="45"/>
-      <c r="AI99" s="46"/>
+      <c r="AD99" s="75"/>
+      <c r="AE99" s="76"/>
+      <c r="AF99" s="76"/>
+      <c r="AG99" s="76"/>
+      <c r="AH99" s="76"/>
+      <c r="AI99" s="77"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9734,7 +9852,7 @@
       <c r="BC99" s="20"/>
       <c r="BD99" s="20"/>
     </row>
-    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -9750,10 +9868,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="35">
+      <c r="X100" s="40">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="40">
+      <c r="Y100" s="52">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9802,7 +9920,7 @@
       <c r="BC100" s="20"/>
       <c r="BD100" s="20"/>
     </row>
-    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -9818,8 +9936,8 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="36"/>
-      <c r="Y101" s="41"/>
+      <c r="X101" s="41"/>
+      <c r="Y101" s="53"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
@@ -9866,7 +9984,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -9888,12 +10006,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="44"/>
-      <c r="AE102" s="45"/>
-      <c r="AF102" s="45"/>
-      <c r="AG102" s="45"/>
-      <c r="AH102" s="45"/>
-      <c r="AI102" s="46"/>
+      <c r="AD102" s="75"/>
+      <c r="AE102" s="76"/>
+      <c r="AF102" s="76"/>
+      <c r="AG102" s="76"/>
+      <c r="AH102" s="76"/>
+      <c r="AI102" s="77"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -9916,7 +10034,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -9976,7 +10094,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -9998,12 +10116,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="44"/>
-      <c r="AE104" s="45"/>
-      <c r="AF104" s="45"/>
-      <c r="AG104" s="45"/>
-      <c r="AH104" s="45"/>
-      <c r="AI104" s="46"/>
+      <c r="AD104" s="75"/>
+      <c r="AE104" s="76"/>
+      <c r="AF104" s="76"/>
+      <c r="AG104" s="76"/>
+      <c r="AH104" s="76"/>
+      <c r="AI104" s="77"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -10026,7 +10144,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -10043,10 +10161,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="35">
+      <c r="X105" s="40">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="50">
+      <c r="Y105" s="56">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -10087,7 +10205,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -10103,8 +10221,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="36"/>
-      <c r="Y106" s="51"/>
+      <c r="X106" s="41"/>
+      <c r="Y106" s="57"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10143,7 +10261,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10165,12 +10283,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="44"/>
-      <c r="AE107" s="45"/>
-      <c r="AF107" s="45"/>
-      <c r="AG107" s="45"/>
-      <c r="AH107" s="45"/>
-      <c r="AI107" s="46"/>
+      <c r="AD107" s="75"/>
+      <c r="AE107" s="76"/>
+      <c r="AF107" s="76"/>
+      <c r="AG107" s="76"/>
+      <c r="AH107" s="76"/>
+      <c r="AI107" s="77"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10193,7 +10311,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10209,10 +10327,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="35">
+      <c r="X108" s="40">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="50">
+      <c r="Y108" s="56">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10223,14 +10341,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="47" t="s">
+      <c r="AD108" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="48"/>
-      <c r="AF108" s="48"/>
-      <c r="AG108" s="48"/>
-      <c r="AH108" s="48"/>
-      <c r="AI108" s="49"/>
+      <c r="AE108" s="44"/>
+      <c r="AF108" s="44"/>
+      <c r="AG108" s="44"/>
+      <c r="AH108" s="44"/>
+      <c r="AI108" s="45"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10253,7 +10371,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10269,8 +10387,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="36"/>
-      <c r="Y109" s="51"/>
+      <c r="X109" s="41"/>
+      <c r="Y109" s="57"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10309,7 +10427,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10331,12 +10449,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="44"/>
-      <c r="AE110" s="45"/>
-      <c r="AF110" s="45"/>
-      <c r="AG110" s="45"/>
-      <c r="AH110" s="45"/>
-      <c r="AI110" s="46"/>
+      <c r="AD110" s="75"/>
+      <c r="AE110" s="76"/>
+      <c r="AF110" s="76"/>
+      <c r="AG110" s="76"/>
+      <c r="AH110" s="76"/>
+      <c r="AI110" s="77"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10359,7 +10477,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="8:56" x14ac:dyDescent="0.25">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10375,10 +10493,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="35">
+      <c r="X111" s="40">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="50">
+      <c r="Y111" s="56">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10389,14 +10507,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="47" t="s">
+      <c r="AD111" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="48"/>
-      <c r="AF111" s="48"/>
-      <c r="AG111" s="48"/>
-      <c r="AH111" s="48"/>
-      <c r="AI111" s="49"/>
+      <c r="AE111" s="44"/>
+      <c r="AF111" s="44"/>
+      <c r="AG111" s="44"/>
+      <c r="AH111" s="44"/>
+      <c r="AI111" s="45"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10419,7 +10537,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10435,8 +10553,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="36"/>
-      <c r="Y112" s="51"/>
+      <c r="X112" s="41"/>
+      <c r="Y112" s="57"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10475,7 +10593,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10497,12 +10615,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="44"/>
-      <c r="AE113" s="45"/>
-      <c r="AF113" s="45"/>
-      <c r="AG113" s="45"/>
-      <c r="AH113" s="45"/>
-      <c r="AI113" s="46"/>
+      <c r="AD113" s="75"/>
+      <c r="AE113" s="76"/>
+      <c r="AF113" s="76"/>
+      <c r="AG113" s="76"/>
+      <c r="AH113" s="76"/>
+      <c r="AI113" s="77"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10525,7 +10643,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10541,10 +10659,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="35">
+      <c r="X114" s="40">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="50">
+      <c r="Y114" s="56">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10585,7 +10703,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10601,8 +10719,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="36"/>
-      <c r="Y115" s="51"/>
+      <c r="X115" s="41"/>
+      <c r="Y115" s="57"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10641,7 +10759,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10663,12 +10781,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="44"/>
-      <c r="AE116" s="45"/>
-      <c r="AF116" s="45"/>
-      <c r="AG116" s="45"/>
-      <c r="AH116" s="45"/>
-      <c r="AI116" s="46"/>
+      <c r="AD116" s="75"/>
+      <c r="AE116" s="76"/>
+      <c r="AF116" s="76"/>
+      <c r="AG116" s="76"/>
+      <c r="AH116" s="76"/>
+      <c r="AI116" s="77"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10691,7 +10809,7 @@
       <c r="BC116" s="20"/>
       <c r="BD116" s="20"/>
     </row>
-    <row r="117" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="117" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I117" s="20"/>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -10707,10 +10825,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="35">
+      <c r="X117" s="40">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="50">
+      <c r="Y117" s="56">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10725,14 +10843,14 @@
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="47" t="s">
+      <c r="AD117" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="48"/>
-      <c r="AF117" s="48"/>
-      <c r="AG117" s="48"/>
-      <c r="AH117" s="48"/>
-      <c r="AI117" s="49"/>
+      <c r="AE117" s="44"/>
+      <c r="AF117" s="44"/>
+      <c r="AG117" s="44"/>
+      <c r="AH117" s="44"/>
+      <c r="AI117" s="45"/>
       <c r="AJ117" s="8">
         <v>45905</v>
       </c>
@@ -10759,7 +10877,7 @@
       <c r="BC117" s="20"/>
       <c r="BD117" s="20"/>
     </row>
-    <row r="118" spans="9:56" x14ac:dyDescent="0.2">
+    <row r="118" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I118" s="20"/>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -10775,8 +10893,8 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="36"/>
-      <c r="Y118" s="51"/>
+      <c r="X118" s="41"/>
+      <c r="Y118" s="57"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
@@ -10823,7 +10941,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10845,12 +10963,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="44"/>
-      <c r="AE119" s="45"/>
-      <c r="AF119" s="45"/>
-      <c r="AG119" s="45"/>
-      <c r="AH119" s="45"/>
-      <c r="AI119" s="46"/>
+      <c r="AD119" s="75"/>
+      <c r="AE119" s="76"/>
+      <c r="AF119" s="76"/>
+      <c r="AG119" s="76"/>
+      <c r="AH119" s="76"/>
+      <c r="AI119" s="77"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10873,7 +10991,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -10889,10 +11007,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="35">
+      <c r="X120" s="40">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="56">
+      <c r="Y120" s="54">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -10933,7 +11051,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -10949,8 +11067,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="36"/>
-      <c r="Y121" s="57"/>
+      <c r="X121" s="41"/>
+      <c r="Y121" s="55"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -10959,14 +11077,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="47" t="s">
+      <c r="AD121" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="48"/>
-      <c r="AF121" s="48"/>
-      <c r="AG121" s="48"/>
-      <c r="AH121" s="48"/>
-      <c r="AI121" s="49"/>
+      <c r="AE121" s="44"/>
+      <c r="AF121" s="44"/>
+      <c r="AG121" s="44"/>
+      <c r="AH121" s="44"/>
+      <c r="AI121" s="45"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -10989,7 +11107,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -11011,12 +11129,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="44"/>
-      <c r="AE122" s="45"/>
-      <c r="AF122" s="45"/>
-      <c r="AG122" s="45"/>
-      <c r="AH122" s="45"/>
-      <c r="AI122" s="46"/>
+      <c r="AD122" s="75"/>
+      <c r="AE122" s="76"/>
+      <c r="AF122" s="76"/>
+      <c r="AG122" s="76"/>
+      <c r="AH122" s="76"/>
+      <c r="AI122" s="77"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -11039,7 +11157,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -11055,10 +11173,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="35">
+      <c r="X123" s="40">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="42">
+      <c r="Y123" s="46">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -11107,7 +11225,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11123,8 +11241,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="36"/>
-      <c r="Y124" s="43"/>
+      <c r="X124" s="41"/>
+      <c r="Y124" s="47"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11171,7 +11289,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11193,12 +11311,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="44"/>
-      <c r="AE125" s="45"/>
-      <c r="AF125" s="45"/>
-      <c r="AG125" s="45"/>
-      <c r="AH125" s="45"/>
-      <c r="AI125" s="46"/>
+      <c r="AD125" s="75"/>
+      <c r="AE125" s="76"/>
+      <c r="AF125" s="76"/>
+      <c r="AG125" s="76"/>
+      <c r="AH125" s="76"/>
+      <c r="AI125" s="77"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11221,7 +11339,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11240,7 +11358,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="42">
+      <c r="Y126" s="46">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11281,7 +11399,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11298,17 +11416,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="43"/>
+      <c r="Y127" s="47"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="44"/>
-      <c r="AE127" s="45"/>
-      <c r="AF127" s="45"/>
-      <c r="AG127" s="45"/>
-      <c r="AH127" s="45"/>
-      <c r="AI127" s="46"/>
+      <c r="AD127" s="75"/>
+      <c r="AE127" s="76"/>
+      <c r="AF127" s="76"/>
+      <c r="AG127" s="76"/>
+      <c r="AH127" s="76"/>
+      <c r="AI127" s="77"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11331,7 +11449,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11347,10 +11465,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="35">
+      <c r="X128" s="40">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="40">
+      <c r="Y128" s="52">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11391,7 +11509,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11407,8 +11525,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="36"/>
-      <c r="Y129" s="41"/>
+      <c r="X129" s="41"/>
+      <c r="Y129" s="53"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11447,7 +11565,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11469,12 +11587,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="44"/>
-      <c r="AE130" s="45"/>
-      <c r="AF130" s="45"/>
-      <c r="AG130" s="45"/>
-      <c r="AH130" s="45"/>
-      <c r="AI130" s="46"/>
+      <c r="AD130" s="75"/>
+      <c r="AE130" s="76"/>
+      <c r="AF130" s="76"/>
+      <c r="AG130" s="76"/>
+      <c r="AH130" s="76"/>
+      <c r="AI130" s="77"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11497,7 +11615,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11513,10 +11631,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="35" t="s">
+      <c r="X131" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="42">
+      <c r="Y131" s="46">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11557,7 +11675,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11573,8 +11691,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="36"/>
-      <c r="Y132" s="43"/>
+      <c r="X132" s="41"/>
+      <c r="Y132" s="47"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11613,7 +11731,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11635,12 +11753,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="44"/>
-      <c r="AE133" s="45"/>
-      <c r="AF133" s="45"/>
-      <c r="AG133" s="45"/>
-      <c r="AH133" s="45"/>
-      <c r="AI133" s="46"/>
+      <c r="AD133" s="75"/>
+      <c r="AE133" s="76"/>
+      <c r="AF133" s="76"/>
+      <c r="AG133" s="76"/>
+      <c r="AH133" s="76"/>
+      <c r="AI133" s="77"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11663,7 +11781,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11693,14 +11811,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="52" t="s">
+      <c r="AD134" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="52"/>
-      <c r="AF134" s="52"/>
-      <c r="AG134" s="52"/>
-      <c r="AH134" s="52"/>
-      <c r="AI134" s="52"/>
+      <c r="AE134" s="42"/>
+      <c r="AF134" s="42"/>
+      <c r="AG134" s="42"/>
+      <c r="AH134" s="42"/>
+      <c r="AI134" s="42"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11723,121 +11841,535 @@
       <c r="BC134" s="20"/>
       <c r="BD134" s="20"/>
     </row>
-    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G153" s="67"/>
-      <c r="H153" s="67"/>
-    </row>
-    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G153" s="89"/>
+      <c r="H153" s="89"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W192" s="12"/>
     </row>
-    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Diego"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="X131:X132"/>
+    <mergeCell ref="X128:X129"/>
+    <mergeCell ref="AD129:AI129"/>
+    <mergeCell ref="AD132:AI132"/>
+    <mergeCell ref="Y128:Y129"/>
+    <mergeCell ref="Y131:Y132"/>
+    <mergeCell ref="AD115:AI115"/>
+    <mergeCell ref="AD116:AI116"/>
+    <mergeCell ref="AD117:AI117"/>
+    <mergeCell ref="AD118:AI118"/>
+    <mergeCell ref="AD119:AI119"/>
+    <mergeCell ref="AD120:AI120"/>
+    <mergeCell ref="AD109:AI109"/>
+    <mergeCell ref="AD110:AI110"/>
+    <mergeCell ref="AD111:AI111"/>
+    <mergeCell ref="AD104:AI104"/>
+    <mergeCell ref="AD105:AI105"/>
+    <mergeCell ref="AD106:AI106"/>
+    <mergeCell ref="X108:X109"/>
+    <mergeCell ref="Y108:Y109"/>
+    <mergeCell ref="X105:X106"/>
+    <mergeCell ref="AD88:AI88"/>
+    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
     <mergeCell ref="AS85:AX85"/>
     <mergeCell ref="AN86:AN87"/>
     <mergeCell ref="AS86:AX86"/>
@@ -11862,481 +12394,61 @@
     <mergeCell ref="BC33:BD33"/>
     <mergeCell ref="BC34:BD34"/>
     <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="X131:X132"/>
-    <mergeCell ref="X128:X129"/>
-    <mergeCell ref="AD129:AI129"/>
-    <mergeCell ref="AD132:AI132"/>
-    <mergeCell ref="Y128:Y129"/>
-    <mergeCell ref="Y131:Y132"/>
-    <mergeCell ref="AD115:AI115"/>
-    <mergeCell ref="AD116:AI116"/>
-    <mergeCell ref="AD117:AI117"/>
-    <mergeCell ref="AD118:AI118"/>
-    <mergeCell ref="AD119:AI119"/>
-    <mergeCell ref="AD120:AI120"/>
-    <mergeCell ref="AD109:AI109"/>
-    <mergeCell ref="AD110:AI110"/>
-    <mergeCell ref="AD111:AI111"/>
-    <mergeCell ref="AD104:AI104"/>
-    <mergeCell ref="AD105:AI105"/>
-    <mergeCell ref="AD106:AI106"/>
-    <mergeCell ref="X108:X109"/>
-    <mergeCell ref="Y108:Y109"/>
-    <mergeCell ref="X105:X106"/>
-    <mergeCell ref="AD88:AI88"/>
-    <mergeCell ref="AD89:AI89"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addan\OneDrive\Documentos\GitHub\ING-DE-SOFTWARE\INCREMENTO2\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uandresbelloedu-my.sharepoint.com/personal/c_vidalgallardo_uandresbello_edu/Documents/Documents/GitHub/ING-DE-SOFTWARE/INCREMENTO2/Excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65FECCC-2382-44BC-A71A-84A875C764F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{E65FECCC-2382-44BC-A71A-84A875C764F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553A7993-9B9B-495B-ADE9-8DE8E8AA10C9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="220">
   <si>
     <t>PILA DEL PRODUCTO</t>
   </si>
@@ -694,6 +694,9 @@
   </si>
   <si>
     <t>Vicente</t>
+  </si>
+  <si>
+    <t>Catalina</t>
   </si>
 </sst>
 </file>
@@ -1180,11 +1183,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1195,14 +1198,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1213,28 +1228,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1243,10 +1252,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1255,13 +1264,25 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1269,54 +1290,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1333,6 +1306,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1342,19 +1324,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1692,106 +1695,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="G2:BD230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="105.85546875" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" customWidth="1"/>
+    <col min="10" max="10" width="105.86328125" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.85546875" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="104.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.28515625" customWidth="1"/>
+    <col min="14" max="18" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.86328125" customWidth="1"/>
+    <col min="20" max="21" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.1328125" customWidth="1"/>
+    <col min="23" max="23" width="10.59765625" customWidth="1"/>
+    <col min="24" max="24" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.86328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="104.265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.265625" customWidth="1"/>
     <col min="35" max="35" width="37" customWidth="1"/>
-    <col min="36" max="36" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.85546875" customWidth="1"/>
-    <col min="39" max="39" width="6.85546875" customWidth="1"/>
-    <col min="40" max="40" width="13.5703125" customWidth="1"/>
-    <col min="41" max="41" width="105.5703125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.86328125" customWidth="1"/>
+    <col min="39" max="39" width="6.86328125" customWidth="1"/>
+    <col min="40" max="40" width="13.59765625" customWidth="1"/>
+    <col min="41" max="41" width="105.59765625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="45.85546875" customWidth="1"/>
-    <col min="51" max="51" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="16373" max="16373" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="45.86328125" customWidth="1"/>
+    <col min="51" max="51" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16373" max="16373" width="9.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I2" s="66" t="s">
+    <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="69" t="s">
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="82" t="s">
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="83"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="69" t="s">
+      <c r="U2" s="73"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="74"/>
+      <c r="AA2" s="74"/>
+      <c r="AB2" s="74"/>
+      <c r="AC2" s="74"/>
+      <c r="AD2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="81" t="s">
+      <c r="AE2" s="77"/>
+      <c r="AF2" s="77"/>
+      <c r="AG2" s="77"/>
+      <c r="AH2" s="77"/>
+      <c r="AI2" s="78"/>
+      <c r="AJ2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="81"/>
-      <c r="AN2" s="84" t="s">
+      <c r="AK2" s="71"/>
+      <c r="AN2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="84"/>
-      <c r="AP2" s="84"/>
-      <c r="AQ2" s="84"/>
-      <c r="AR2" s="84"/>
-      <c r="AS2" s="85" t="s">
+      <c r="AO2" s="74"/>
+      <c r="AP2" s="74"/>
+      <c r="AQ2" s="74"/>
+      <c r="AR2" s="74"/>
+      <c r="AS2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="85"/>
-      <c r="AU2" s="85"/>
-      <c r="AV2" s="85"/>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="85"/>
-      <c r="AY2" s="81" t="s">
+      <c r="AT2" s="75"/>
+      <c r="AU2" s="75"/>
+      <c r="AV2" s="75"/>
+      <c r="AW2" s="75"/>
+      <c r="AX2" s="75"/>
+      <c r="AY2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="81"/>
-      <c r="BA2" s="81" t="s">
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="81"/>
-      <c r="BC2" s="81" t="s">
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="81"/>
-    </row>
-    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BD2" s="71"/>
+    </row>
+    <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1807,12 +1810,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="72"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="74"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+      <c r="R3" s="86"/>
+      <c r="S3" s="87"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1837,12 +1840,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="86"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="88"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="81"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1864,12 +1867,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="85"/>
-      <c r="AT3" s="85"/>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
+      <c r="AS3" s="75"/>
+      <c r="AT3" s="75"/>
+      <c r="AU3" s="75"/>
+      <c r="AV3" s="75"/>
+      <c r="AW3" s="75"/>
+      <c r="AX3" s="75"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1882,13 +1885,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="81" t="s">
+      <c r="BC3" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="81"/>
-    </row>
-    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I4" s="62">
+      <c r="BD3" s="71"/>
+    </row>
+    <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="92">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1919,10 +1922,10 @@
       </c>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="40">
+      <c r="X4" s="35">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="50">
+      <c r="Y4" s="88">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -1953,7 +1956,7 @@
       </c>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="90">
+      <c r="AN4" s="68">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -1982,11 +1985,11 @@
       <c r="AZ4" s="19"/>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-    </row>
-    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I5" s="63"/>
+      <c r="BC4" s="64"/>
+      <c r="BD4" s="64"/>
+    </row>
+    <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I5" s="69"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -1999,7 +2002,7 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="O5" s="38"/>
@@ -2015,8 +2018,8 @@
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="51"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="89"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2029,14 +2032,14 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="80" t="s">
+      <c r="AD5" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="77"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="46"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
@@ -2045,7 +2048,7 @@
       </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="63"/>
+      <c r="AN5" s="69"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2058,7 +2061,7 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="65" t="s">
+      <c r="AS5" s="66" t="s">
         <v>89</v>
       </c>
       <c r="AT5" s="38"/>
@@ -2072,11 +2075,11 @@
       <c r="AZ5" s="19"/>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="75"/>
-      <c r="BD5" s="77"/>
-    </row>
-    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I6" s="64"/>
+      <c r="BC5" s="44"/>
+      <c r="BD5" s="46"/>
+    </row>
+    <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I6" s="70"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2105,8 +2108,8 @@
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="79"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="90"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2119,14 +2122,14 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="75" t="s">
+      <c r="AD6" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="76"/>
-      <c r="AI6" s="77"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="46"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
@@ -2135,7 +2138,7 @@
       </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="64"/>
+      <c r="AN6" s="70"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2162,11 +2165,11 @@
       <c r="AZ6" s="19"/>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-    </row>
-    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="40">
+      <c r="BC6" s="64"/>
+      <c r="BD6" s="64"/>
+    </row>
+    <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I7" s="35">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2203,17 +2206,17 @@
       <c r="AA7" s="33"/>
       <c r="AB7" s="33"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="76"/>
-      <c r="AG7" s="76"/>
-      <c r="AH7" s="76"/>
-      <c r="AI7" s="77"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="45"/>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="45"/>
+      <c r="AH7" s="45"/>
+      <c r="AI7" s="46"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="40">
+      <c r="AN7" s="35">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2242,11 +2245,11 @@
       <c r="AZ7" s="19"/>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="35"/>
-    </row>
-    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I8" s="41"/>
+      <c r="BC7" s="64"/>
+      <c r="BD7" s="64"/>
+    </row>
+    <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I8" s="36"/>
       <c r="J8" s="30" t="s">
         <v>172</v>
       </c>
@@ -2275,10 +2278,10 @@
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="42">
+      <c r="X8" s="52">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="50">
+      <c r="Y8" s="88">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2309,7 +2312,7 @@
       </c>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="48"/>
+      <c r="AN8" s="55"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2336,11 +2339,11 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="35"/>
-      <c r="BD8" s="35"/>
-    </row>
-    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="40">
+      <c r="BC8" s="64"/>
+      <c r="BD8" s="64"/>
+    </row>
+    <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2371,8 +2374,8 @@
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="51"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="89"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2401,7 +2404,7 @@
       </c>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="40">
+      <c r="AN9" s="35">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2430,11 +2433,11 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="35"/>
-    </row>
-    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I10" s="41"/>
+      <c r="BC9" s="64"/>
+      <c r="BD9" s="64"/>
+    </row>
+    <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I10" s="36"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2469,17 +2472,17 @@
       <c r="AA10" s="33"/>
       <c r="AB10" s="33"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="76"/>
-      <c r="AF10" s="76"/>
-      <c r="AG10" s="76"/>
-      <c r="AH10" s="76"/>
-      <c r="AI10" s="77"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="46"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="48"/>
+      <c r="AN10" s="55"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2506,11 +2509,11 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="35"/>
-      <c r="BD10" s="35"/>
-    </row>
-    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I11" s="40">
+      <c r="BC10" s="64"/>
+      <c r="BD10" s="64"/>
+    </row>
+    <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2525,7 +2528,7 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="65" t="s">
+      <c r="N11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="O11" s="38"/>
@@ -2541,10 +2544,10 @@
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="42">
+      <c r="X11" s="52">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="46">
+      <c r="Y11" s="42">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2575,7 +2578,7 @@
       </c>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="40">
+      <c r="AN11" s="35">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2590,7 +2593,7 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="65" t="s">
+      <c r="AS11" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AT11" s="38"/>
@@ -2604,11 +2607,11 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="35"/>
-      <c r="BD11" s="35"/>
-    </row>
-    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I12" s="48"/>
+      <c r="BC11" s="64"/>
+      <c r="BD11" s="64"/>
+    </row>
+    <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I12" s="55"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2621,7 +2624,7 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="65" t="s">
+      <c r="N12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="O12" s="38"/>
@@ -2637,8 +2640,8 @@
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="47"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="43"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2667,7 +2670,7 @@
       </c>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="48"/>
+      <c r="AN12" s="55"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2680,7 +2683,7 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="65" t="s">
+      <c r="AS12" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AT12" s="38"/>
@@ -2694,11 +2697,11 @@
       <c r="AZ12" s="19"/>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="35"/>
-      <c r="BD12" s="35"/>
-    </row>
-    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I13" s="41"/>
+      <c r="BC12" s="64"/>
+      <c r="BD12" s="64"/>
+    </row>
+    <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I13" s="36"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2733,17 +2736,17 @@
       <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="75"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="76"/>
-      <c r="AH13" s="76"/>
-      <c r="AI13" s="77"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="45"/>
+      <c r="AH13" s="45"/>
+      <c r="AI13" s="46"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="41"/>
+      <c r="AN13" s="36"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2770,11 +2773,11 @@
       <c r="AZ13" s="19"/>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="35"/>
-      <c r="BD13" s="35"/>
-    </row>
-    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I14" s="40">
+      <c r="BC13" s="64"/>
+      <c r="BD13" s="64"/>
+    </row>
+    <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I14" s="35">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2805,10 +2808,10 @@
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="42">
+      <c r="X14" s="52">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="52">
+      <c r="Y14" s="40">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2823,7 +2826,7 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="65" t="s">
+      <c r="AD14" s="66" t="s">
         <v>98</v>
       </c>
       <c r="AE14" s="38"/>
@@ -2839,7 +2842,7 @@
       </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="40">
+      <c r="AN14" s="35">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2868,11 +2871,11 @@
       <c r="AZ14" s="19"/>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="35"/>
-    </row>
-    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="48"/>
+      <c r="BC14" s="64"/>
+      <c r="BD14" s="64"/>
+    </row>
+    <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I15" s="55"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2901,8 +2904,8 @@
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="78"/>
+      <c r="X15" s="52"/>
+      <c r="Y15" s="62"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -2915,7 +2918,7 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="65" t="s">
+      <c r="AD15" s="66" t="s">
         <v>95</v>
       </c>
       <c r="AE15" s="38"/>
@@ -2931,7 +2934,7 @@
       </c>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="48"/>
+      <c r="AN15" s="55"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2958,11 +2961,11 @@
       <c r="AZ15" s="19"/>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="35"/>
-    </row>
-    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I16" s="41"/>
+      <c r="BC15" s="64"/>
+      <c r="BD15" s="64"/>
+    </row>
+    <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I16" s="36"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -2991,8 +2994,8 @@
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="53"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="41"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -3021,7 +3024,7 @@
       </c>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="48"/>
+      <c r="AN16" s="55"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3048,11 +3051,11 @@
       <c r="AZ16" s="25"/>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="36"/>
-      <c r="BD16" s="36"/>
-    </row>
-    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="92">
+      <c r="BC16" s="65"/>
+      <c r="BD16" s="65"/>
+    </row>
+    <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I17" s="53">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3089,17 +3092,17 @@
       <c r="AA17" s="33"/>
       <c r="AB17" s="33"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76"/>
-      <c r="AH17" s="76"/>
-      <c r="AI17" s="77"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="45"/>
+      <c r="AF17" s="45"/>
+      <c r="AG17" s="45"/>
+      <c r="AH17" s="45"/>
+      <c r="AI17" s="46"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="49">
+      <c r="AN17" s="93">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3128,11 +3131,11 @@
       <c r="AZ17" s="19"/>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="35"/>
-    </row>
-    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I18" s="93"/>
+      <c r="BC17" s="64"/>
+      <c r="BD17" s="64"/>
+    </row>
+    <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I18" s="54"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3161,10 +3164,10 @@
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="42">
+      <c r="X18" s="52">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="52">
+      <c r="Y18" s="40">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3195,7 +3198,7 @@
       </c>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="49"/>
+      <c r="AN18" s="93"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3222,11 +3225,11 @@
       <c r="AZ18" s="19"/>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="35"/>
-    </row>
-    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I19" s="40" t="s">
+      <c r="BC18" s="64"/>
+      <c r="BD18" s="64"/>
+    </row>
+    <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3257,8 +3260,8 @@
       </c>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="78"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="62"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3287,7 +3290,7 @@
       </c>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="40" t="s">
+      <c r="AN19" s="35" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3310,11 +3313,11 @@
       <c r="AZ19" s="6"/>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="35"/>
-    </row>
-    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I20" s="41"/>
+      <c r="BC19" s="64"/>
+      <c r="BD19" s="64"/>
+    </row>
+    <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I20" s="36"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3343,8 +3346,8 @@
       </c>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="53"/>
+      <c r="X20" s="52"/>
+      <c r="Y20" s="41"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3373,7 +3376,7 @@
       </c>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="41"/>
+      <c r="AN20" s="36"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3394,11 +3397,11 @@
       <c r="AZ20" s="7"/>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="35"/>
-      <c r="BD20" s="35"/>
-    </row>
-    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I21" s="40">
+      <c r="BC20" s="64"/>
+      <c r="BD20" s="64"/>
+    </row>
+    <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I21" s="35">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3435,17 +3438,17 @@
       <c r="AA21" s="33"/>
       <c r="AB21" s="33"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="75"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="76"/>
-      <c r="AG21" s="76"/>
-      <c r="AH21" s="76"/>
-      <c r="AI21" s="77"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="46"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="40">
+      <c r="AN21" s="35">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3476,11 +3479,11 @@
       </c>
       <c r="BA21" s="19"/>
       <c r="BB21" s="19"/>
-      <c r="BC21" s="35"/>
-      <c r="BD21" s="35"/>
-    </row>
-    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I22" s="48"/>
+      <c r="BC21" s="64"/>
+      <c r="BD21" s="64"/>
+    </row>
+    <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I22" s="55"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3509,10 +3512,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="49">
+      <c r="X22" s="93">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="52">
+      <c r="Y22" s="40">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3543,7 +3546,7 @@
       </c>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="48"/>
+      <c r="AN22" s="55"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3572,11 +3575,11 @@
       </c>
       <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
-      <c r="BC22" s="35"/>
-      <c r="BD22" s="35"/>
-    </row>
-    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I23" s="41"/>
+      <c r="BC22" s="64"/>
+      <c r="BD22" s="64"/>
+    </row>
+    <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I23" s="36"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3605,8 +3608,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="53"/>
+      <c r="X23" s="93"/>
+      <c r="Y23" s="41"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3635,7 +3638,7 @@
       </c>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="41"/>
+      <c r="AN23" s="36"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3664,11 +3667,11 @@
       </c>
       <c r="BA23" s="19"/>
       <c r="BB23" s="19"/>
-      <c r="BC23" s="35"/>
-      <c r="BD23" s="35"/>
-    </row>
-    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I24" s="40" t="s">
+      <c r="BC23" s="64"/>
+      <c r="BD23" s="64"/>
+    </row>
+    <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3705,17 +3708,17 @@
       <c r="AA24" s="33"/>
       <c r="AB24" s="33"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="75"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="76"/>
-      <c r="AG24" s="76"/>
-      <c r="AH24" s="76"/>
-      <c r="AI24" s="77"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="45"/>
+      <c r="AI24" s="46"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="40" t="s">
+      <c r="AN24" s="35" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3746,11 +3749,11 @@
       </c>
       <c r="BA24" s="19"/>
       <c r="BB24" s="19"/>
-      <c r="BC24" s="35"/>
-      <c r="BD24" s="35"/>
-    </row>
-    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I25" s="41"/>
+      <c r="BC24" s="64"/>
+      <c r="BD24" s="64"/>
+    </row>
+    <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I25" s="36"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3779,10 +3782,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="40" t="s">
+      <c r="X25" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="46">
+      <c r="Y25" s="42">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3805,7 +3808,7 @@
       <c r="AK25" s="7"/>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="41"/>
+      <c r="AN25" s="36"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3834,11 +3837,11 @@
       </c>
       <c r="BA25" s="19"/>
       <c r="BB25" s="19"/>
-      <c r="BC25" s="35"/>
-      <c r="BD25" s="35"/>
-    </row>
-    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I26" s="40" t="s">
+      <c r="BC25" s="64"/>
+      <c r="BD25" s="64"/>
+    </row>
+    <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3869,8 +3872,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="47"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="43"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -3891,7 +3894,7 @@
       <c r="AK26" s="7"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="40" t="s">
+      <c r="AN26" s="35" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -3922,11 +3925,11 @@
       </c>
       <c r="BA26" s="19"/>
       <c r="BB26" s="19"/>
-      <c r="BC26" s="35"/>
-      <c r="BD26" s="35"/>
-    </row>
-    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I27" s="41"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+    </row>
+    <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I27" s="36"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -3961,17 +3964,17 @@
       <c r="AA27" s="33"/>
       <c r="AB27" s="33"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="76"/>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="77"/>
+      <c r="AD27" s="44"/>
+      <c r="AE27" s="45"/>
+      <c r="AF27" s="45"/>
+      <c r="AG27" s="45"/>
+      <c r="AH27" s="45"/>
+      <c r="AI27" s="46"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="41"/>
+      <c r="AN27" s="36"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -4000,11 +4003,11 @@
       </c>
       <c r="BA27" s="19"/>
       <c r="BB27" s="19"/>
-      <c r="BC27" s="35"/>
-      <c r="BD27" s="35"/>
-    </row>
-    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I28" s="40" t="s">
+      <c r="BC27" s="64"/>
+      <c r="BD27" s="64"/>
+    </row>
+    <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -4035,10 +4038,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="40">
+      <c r="X28" s="35">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="60">
+      <c r="Y28" s="58">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -4069,7 +4072,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="40" t="s">
+      <c r="AN28" s="35" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4100,11 +4103,11 @@
       </c>
       <c r="BA28" s="25"/>
       <c r="BB28" s="25"/>
-      <c r="BC28" s="36"/>
-      <c r="BD28" s="36"/>
-    </row>
-    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I29" s="48"/>
+      <c r="BC28" s="65"/>
+      <c r="BD28" s="65"/>
+    </row>
+    <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I29" s="55"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4133,8 +4136,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="91"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="63"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4163,7 +4166,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="48"/>
+      <c r="AN29" s="55"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4192,11 +4195,11 @@
       </c>
       <c r="BA29" s="19"/>
       <c r="BB29" s="19"/>
-      <c r="BC29" s="35"/>
-      <c r="BD29" s="35"/>
-    </row>
-    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I30" s="41"/>
+      <c r="BC29" s="64"/>
+      <c r="BD29" s="64"/>
+    </row>
+    <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I30" s="36"/>
       <c r="J30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4225,8 +4228,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="61"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="59"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4255,7 +4258,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="41"/>
+      <c r="AN30" s="36"/>
       <c r="AO30" s="6" t="s">
         <v>192</v>
       </c>
@@ -4284,11 +4287,11 @@
       </c>
       <c r="BA30" s="19"/>
       <c r="BB30" s="19"/>
-      <c r="BC30" s="35"/>
-      <c r="BD30" s="35"/>
-    </row>
-    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I31" s="40">
+      <c r="BC30" s="64"/>
+      <c r="BD30" s="64"/>
+    </row>
+    <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I31" s="35">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4325,17 +4328,17 @@
       <c r="AA31" s="33"/>
       <c r="AB31" s="33"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="76"/>
-      <c r="AG31" s="76"/>
-      <c r="AH31" s="76"/>
-      <c r="AI31" s="77"/>
+      <c r="AD31" s="44"/>
+      <c r="AE31" s="45"/>
+      <c r="AF31" s="45"/>
+      <c r="AG31" s="45"/>
+      <c r="AH31" s="45"/>
+      <c r="AI31" s="46"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="40">
+      <c r="AN31" s="35">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4366,11 +4369,11 @@
       </c>
       <c r="BA31" s="19"/>
       <c r="BB31" s="19"/>
-      <c r="BC31" s="35"/>
-      <c r="BD31" s="35"/>
-    </row>
-    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="41"/>
+      <c r="BC31" s="64"/>
+      <c r="BD31" s="64"/>
+    </row>
+    <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I32" s="36"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4399,10 +4402,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="40">
+      <c r="X32" s="35">
         <v>3.1</v>
       </c>
-      <c r="Y32" s="60">
+      <c r="Y32" s="58">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4433,7 +4436,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="41"/>
+      <c r="AN32" s="36"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4462,11 +4465,11 @@
       </c>
       <c r="BA32" s="19"/>
       <c r="BB32" s="19"/>
-      <c r="BC32" s="35"/>
-      <c r="BD32" s="35"/>
-    </row>
-    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I33" s="40">
+      <c r="BC32" s="64"/>
+      <c r="BD32" s="64"/>
+    </row>
+    <row r="33" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I33" s="35">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4497,8 +4500,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="61"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="59"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4527,7 +4530,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="40">
+      <c r="AN33" s="35">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4558,11 +4561,11 @@
       </c>
       <c r="BA33" s="19"/>
       <c r="BB33" s="19"/>
-      <c r="BC33" s="35"/>
-      <c r="BD33" s="35"/>
-    </row>
-    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I34" s="41"/>
+      <c r="BC33" s="64"/>
+      <c r="BD33" s="64"/>
+    </row>
+    <row r="34" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I34" s="36"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4597,17 +4600,17 @@
       <c r="AA34" s="33"/>
       <c r="AB34" s="33"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="75"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
-      <c r="AI34" s="77"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="45"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="45"/>
+      <c r="AI34" s="46"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="41"/>
+      <c r="AN34" s="36"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4636,11 +4639,11 @@
       </c>
       <c r="BA34" s="19"/>
       <c r="BB34" s="19"/>
-      <c r="BC34" s="35"/>
-      <c r="BD34" s="35"/>
-    </row>
-    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I35" s="40">
+      <c r="BC34" s="64"/>
+      <c r="BD34" s="64"/>
+    </row>
+    <row r="35" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4671,10 +4674,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="40" t="s">
+      <c r="X35" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="46">
+      <c r="Y35" s="42">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4705,7 +4708,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="40">
+      <c r="AN35" s="35">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4736,11 +4739,11 @@
       </c>
       <c r="BA35" s="19"/>
       <c r="BB35" s="19"/>
-      <c r="BC35" s="35"/>
-      <c r="BD35" s="35"/>
-    </row>
-    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I36" s="41"/>
+      <c r="BC35" s="64"/>
+      <c r="BD35" s="64"/>
+    </row>
+    <row r="36" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I36" s="36"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4769,8 +4772,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="47"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="43"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4799,7 +4802,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="41"/>
+      <c r="AN36" s="36"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4828,11 +4831,11 @@
       </c>
       <c r="BA36" s="19"/>
       <c r="BB36" s="19"/>
-      <c r="BC36" s="35"/>
-      <c r="BD36" s="35"/>
-    </row>
-    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I37" s="40">
+      <c r="BC36" s="64"/>
+      <c r="BD36" s="64"/>
+    </row>
+    <row r="37" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -4869,17 +4872,17 @@
       <c r="AA37" s="33"/>
       <c r="AB37" s="33"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="75"/>
-      <c r="AE37" s="76"/>
-      <c r="AF37" s="76"/>
-      <c r="AG37" s="76"/>
-      <c r="AH37" s="76"/>
-      <c r="AI37" s="77"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="45"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="46"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="40">
+      <c r="AN37" s="35">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -4910,11 +4913,11 @@
       </c>
       <c r="BA37" s="19"/>
       <c r="BB37" s="19"/>
-      <c r="BC37" s="35"/>
-      <c r="BD37" s="35"/>
-    </row>
-    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I38" s="41"/>
+      <c r="BC37" s="64"/>
+      <c r="BD37" s="64"/>
+    </row>
+    <row r="38" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I38" s="36"/>
       <c r="J38" s="6" t="s">
         <v>194</v>
       </c>
@@ -4943,10 +4946,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="40" t="s">
+      <c r="X38" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="52">
+      <c r="Y38" s="40">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -4977,7 +4980,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="41"/>
+      <c r="AN38" s="36"/>
       <c r="AO38" s="6" t="s">
         <v>194</v>
       </c>
@@ -5006,10 +5009,10 @@
       </c>
       <c r="BA38" s="19"/>
       <c r="BB38" s="19"/>
-      <c r="BC38" s="35"/>
-      <c r="BD38" s="35"/>
-    </row>
-    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC38" s="64"/>
+      <c r="BD38" s="64"/>
+    </row>
+    <row r="39" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I39" s="9">
         <v>4.7</v>
       </c>
@@ -5041,8 +5044,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="78"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="62"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5102,11 +5105,11 @@
       </c>
       <c r="BA39" s="19"/>
       <c r="BB39" s="19"/>
-      <c r="BC39" s="35"/>
-      <c r="BD39" s="35"/>
-    </row>
-    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I40" s="40">
+      <c r="BC39" s="64"/>
+      <c r="BD39" s="64"/>
+    </row>
+    <row r="40" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5137,8 +5140,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="41"/>
-      <c r="Y40" s="53"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="41"/>
       <c r="Z40" s="6" t="s">
         <v>192</v>
       </c>
@@ -5167,7 +5170,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="40">
+      <c r="AN40" s="35">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5198,11 +5201,11 @@
       </c>
       <c r="BA40" s="25"/>
       <c r="BB40" s="25"/>
-      <c r="BC40" s="36"/>
-      <c r="BD40" s="36"/>
-    </row>
-    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="41"/>
+      <c r="BC40" s="65"/>
+      <c r="BD40" s="65"/>
+    </row>
+    <row r="41" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I41" s="36"/>
       <c r="J41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5215,14 +5218,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="45"/>
+      <c r="O41" s="48"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="49"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5237,17 +5240,17 @@
       <c r="AA41" s="33"/>
       <c r="AB41" s="33"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="75"/>
-      <c r="AE41" s="76"/>
-      <c r="AF41" s="76"/>
-      <c r="AG41" s="76"/>
-      <c r="AH41" s="76"/>
-      <c r="AI41" s="77"/>
+      <c r="AD41" s="44"/>
+      <c r="AE41" s="45"/>
+      <c r="AF41" s="45"/>
+      <c r="AG41" s="45"/>
+      <c r="AH41" s="45"/>
+      <c r="AI41" s="46"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="41"/>
+      <c r="AN41" s="36"/>
       <c r="AO41" s="6" t="s">
         <v>201</v>
       </c>
@@ -5260,14 +5263,14 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="43" t="s">
+      <c r="AS41" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AT41" s="44"/>
-      <c r="AU41" s="44"/>
-      <c r="AV41" s="44"/>
-      <c r="AW41" s="44"/>
-      <c r="AX41" s="45"/>
+      <c r="AT41" s="48"/>
+      <c r="AU41" s="48"/>
+      <c r="AV41" s="48"/>
+      <c r="AW41" s="48"/>
+      <c r="AX41" s="49"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
@@ -5276,10 +5279,10 @@
       </c>
       <c r="BA41" s="19"/>
       <c r="BB41" s="19"/>
-      <c r="BC41" s="35"/>
-      <c r="BD41" s="35"/>
-    </row>
-    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC41" s="64"/>
+      <c r="BD41" s="64"/>
+    </row>
+    <row r="42" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I42" s="9">
         <v>6.1</v>
       </c>
@@ -5311,10 +5314,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="40">
+      <c r="X42" s="35">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="52">
+      <c r="Y42" s="40">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5376,11 +5379,11 @@
       </c>
       <c r="BA42" s="19"/>
       <c r="BB42" s="19"/>
-      <c r="BC42" s="35"/>
-      <c r="BD42" s="35"/>
-    </row>
-    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="40">
+      <c r="BC42" s="64"/>
+      <c r="BD42" s="64"/>
+    </row>
+    <row r="43" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I43" s="35">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5411,8 +5414,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="53"/>
+      <c r="X43" s="36"/>
+      <c r="Y43" s="41"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5441,7 +5444,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="40">
+      <c r="AN43" s="35">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5472,11 +5475,11 @@
       </c>
       <c r="BA43" s="19"/>
       <c r="BB43" s="19"/>
-      <c r="BC43" s="35"/>
-      <c r="BD43" s="35"/>
-    </row>
-    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="41"/>
+      <c r="BC43" s="64"/>
+      <c r="BD43" s="64"/>
+    </row>
+    <row r="44" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I44" s="36"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5511,17 +5514,17 @@
       <c r="AA44" s="33"/>
       <c r="AB44" s="33"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="75"/>
-      <c r="AE44" s="76"/>
-      <c r="AF44" s="76"/>
-      <c r="AG44" s="76"/>
-      <c r="AH44" s="76"/>
-      <c r="AI44" s="77"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="45"/>
+      <c r="AG44" s="45"/>
+      <c r="AH44" s="45"/>
+      <c r="AI44" s="46"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="41"/>
+      <c r="AN44" s="36"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5550,10 +5553,10 @@
       </c>
       <c r="BA44" s="19"/>
       <c r="BB44" s="19"/>
-      <c r="BC44" s="35"/>
-      <c r="BD44" s="35"/>
-    </row>
-    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC44" s="64"/>
+      <c r="BD44" s="64"/>
+    </row>
+    <row r="45" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I45" s="9">
         <v>2.2999999999999998</v>
       </c>
@@ -5585,10 +5588,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="40">
+      <c r="X45" s="35">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="60">
+      <c r="Y45" s="58">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5650,11 +5653,11 @@
       </c>
       <c r="BA45" s="19"/>
       <c r="BB45" s="19"/>
-      <c r="BC45" s="35"/>
-      <c r="BD45" s="35"/>
-    </row>
-    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="40" t="s">
+      <c r="BC45" s="64"/>
+      <c r="BD45" s="64"/>
+    </row>
+    <row r="46" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5685,8 +5688,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="61"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="59"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5715,7 +5718,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="40" t="s">
+      <c r="AN46" s="35" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5746,11 +5749,11 @@
       </c>
       <c r="BA46" s="19"/>
       <c r="BB46" s="19"/>
-      <c r="BC46" s="35"/>
-      <c r="BD46" s="35"/>
-    </row>
-    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="41"/>
+      <c r="BC46" s="64"/>
+      <c r="BD46" s="64"/>
+    </row>
+    <row r="47" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I47" s="36"/>
       <c r="J47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5785,17 +5788,17 @@
       <c r="AA47" s="33"/>
       <c r="AB47" s="33"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="75"/>
-      <c r="AE47" s="76"/>
-      <c r="AF47" s="76"/>
-      <c r="AG47" s="76"/>
-      <c r="AH47" s="76"/>
-      <c r="AI47" s="77"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="45"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="45"/>
+      <c r="AI47" s="46"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="41"/>
+      <c r="AN47" s="36"/>
       <c r="AO47" s="6" t="s">
         <v>185</v>
       </c>
@@ -5824,11 +5827,11 @@
       </c>
       <c r="BA47" s="19"/>
       <c r="BB47" s="19"/>
-      <c r="BC47" s="35"/>
-      <c r="BD47" s="35"/>
-    </row>
-    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="40" t="s">
+      <c r="BC47" s="64"/>
+      <c r="BD47" s="64"/>
+    </row>
+    <row r="48" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -5859,10 +5862,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="40">
+      <c r="X48" s="35">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="46">
+      <c r="Y48" s="42">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -5893,7 +5896,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="40" t="s">
+      <c r="AN48" s="35" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -5924,11 +5927,11 @@
       </c>
       <c r="BA48" s="19"/>
       <c r="BB48" s="19"/>
-      <c r="BC48" s="35"/>
-      <c r="BD48" s="35"/>
-    </row>
-    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="41"/>
+      <c r="BC48" s="64"/>
+      <c r="BD48" s="64"/>
+    </row>
+    <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I49" s="36"/>
       <c r="J49" s="6" t="s">
         <v>186</v>
       </c>
@@ -5957,8 +5960,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="41"/>
-      <c r="Y49" s="47"/>
+      <c r="X49" s="36"/>
+      <c r="Y49" s="43"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -5987,7 +5990,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="41"/>
+      <c r="AN49" s="36"/>
       <c r="AO49" s="6" t="s">
         <v>186</v>
       </c>
@@ -6016,12 +6019,12 @@
       </c>
       <c r="BA49" s="19"/>
       <c r="BB49" s="19"/>
-      <c r="BC49" s="35"/>
-      <c r="BD49" s="35"/>
-    </row>
-    <row r="50" spans="8:56" x14ac:dyDescent="0.25">
+      <c r="BC49" s="64"/>
+      <c r="BD49" s="64"/>
+    </row>
+    <row r="50" spans="8:56" x14ac:dyDescent="0.45">
       <c r="H50" s="10"/>
-      <c r="I50" s="40">
+      <c r="I50" s="35">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -6036,14 +6039,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="43" t="s">
+      <c r="N50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="45"/>
+      <c r="O50" s="48"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="48"/>
+      <c r="R50" s="48"/>
+      <c r="S50" s="49"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -6058,17 +6061,17 @@
       <c r="AA50" s="33"/>
       <c r="AB50" s="33"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="75"/>
-      <c r="AE50" s="76"/>
-      <c r="AF50" s="76"/>
-      <c r="AG50" s="76"/>
-      <c r="AH50" s="76"/>
-      <c r="AI50" s="77"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="45"/>
+      <c r="AI50" s="46"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="40">
+      <c r="AN50" s="35">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6079,23 +6082,23 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="43" t="s">
+      <c r="AS50" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="AT50" s="44"/>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="44"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="45"/>
+      <c r="AT50" s="48"/>
+      <c r="AU50" s="48"/>
+      <c r="AV50" s="48"/>
+      <c r="AW50" s="48"/>
+      <c r="AX50" s="49"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="6"/>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="35"/>
-      <c r="BD50" s="35"/>
-    </row>
-    <row r="51" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I51" s="41"/>
+      <c r="BC50" s="64"/>
+      <c r="BD50" s="64"/>
+    </row>
+    <row r="51" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I51" s="36"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6108,14 +6111,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="43" t="s">
+      <c r="N51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="45"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="49"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6124,10 +6127,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="40">
+      <c r="X51" s="35">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="52">
+      <c r="Y51" s="40">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6158,7 +6161,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="41"/>
+      <c r="AN51" s="36"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6167,23 +6170,23 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="43" t="s">
+      <c r="AS51" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="44"/>
-      <c r="AU51" s="44"/>
-      <c r="AV51" s="44"/>
-      <c r="AW51" s="44"/>
-      <c r="AX51" s="45"/>
+      <c r="AT51" s="48"/>
+      <c r="AU51" s="48"/>
+      <c r="AV51" s="48"/>
+      <c r="AW51" s="48"/>
+      <c r="AX51" s="49"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="35"/>
-      <c r="BD51" s="35"/>
-    </row>
-    <row r="52" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I52" s="40">
+      <c r="BC51" s="64"/>
+      <c r="BD51" s="64"/>
+    </row>
+    <row r="52" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I52" s="35">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6214,8 +6217,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="41"/>
-      <c r="Y52" s="53"/>
+      <c r="X52" s="36"/>
+      <c r="Y52" s="41"/>
       <c r="Z52" s="6" t="s">
         <v>194</v>
       </c>
@@ -6244,7 +6247,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="40">
+      <c r="AN52" s="35">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6267,11 +6270,11 @@
       <c r="AZ52" s="6"/>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="36"/>
-      <c r="BD52" s="36"/>
-    </row>
-    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I53" s="41"/>
+      <c r="BC52" s="65"/>
+      <c r="BD52" s="65"/>
+    </row>
+    <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I53" s="36"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6306,17 +6309,17 @@
       <c r="AA53" s="33"/>
       <c r="AB53" s="33"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="75"/>
-      <c r="AE53" s="76"/>
-      <c r="AF53" s="76"/>
-      <c r="AG53" s="76"/>
-      <c r="AH53" s="76"/>
-      <c r="AI53" s="77"/>
+      <c r="AD53" s="44"/>
+      <c r="AE53" s="45"/>
+      <c r="AF53" s="45"/>
+      <c r="AG53" s="45"/>
+      <c r="AH53" s="45"/>
+      <c r="AI53" s="46"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="41"/>
+      <c r="AN53" s="36"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6337,11 +6340,11 @@
       <c r="AZ53" s="6"/>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="35"/>
-      <c r="BD53" s="35"/>
-    </row>
-    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I54" s="40">
+      <c r="BC53" s="64"/>
+      <c r="BD53" s="64"/>
+    </row>
+    <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I54" s="35">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6406,7 +6409,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="40">
+      <c r="AN54" s="35">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6429,11 +6432,11 @@
       <c r="AZ54" s="6"/>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="35"/>
-      <c r="BD54" s="35"/>
-    </row>
-    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I55" s="41"/>
+      <c r="BC54" s="64"/>
+      <c r="BD54" s="64"/>
+    </row>
+    <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I55" s="36"/>
       <c r="J55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6468,17 +6471,17 @@
       <c r="AA55" s="33"/>
       <c r="AB55" s="33"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="75"/>
-      <c r="AE55" s="76"/>
-      <c r="AF55" s="76"/>
-      <c r="AG55" s="76"/>
-      <c r="AH55" s="76"/>
-      <c r="AI55" s="77"/>
+      <c r="AD55" s="44"/>
+      <c r="AE55" s="45"/>
+      <c r="AF55" s="45"/>
+      <c r="AG55" s="45"/>
+      <c r="AH55" s="45"/>
+      <c r="AI55" s="46"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="41"/>
+      <c r="AN55" s="36"/>
       <c r="AO55" s="18" t="s">
         <v>196</v>
       </c>
@@ -6499,10 +6502,10 @@
       <c r="AZ55" s="6"/>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="35"/>
-      <c r="BD55" s="35"/>
-    </row>
-    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC55" s="64"/>
+      <c r="BD55" s="64"/>
+    </row>
+    <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I56" s="9">
         <v>3.5</v>
       </c>
@@ -6534,10 +6537,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="40">
+      <c r="X56" s="35">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="60">
+      <c r="Y56" s="58">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6591,11 +6594,11 @@
       <c r="AZ56" s="6"/>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="35"/>
-      <c r="BD56" s="35"/>
-    </row>
-    <row r="57" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I57" s="40">
+      <c r="BC56" s="64"/>
+      <c r="BD56" s="64"/>
+    </row>
+    <row r="57" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I57" s="35">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6626,8 +6629,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="41"/>
-      <c r="Y57" s="61"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="59"/>
       <c r="Z57" s="6" t="s">
         <v>201</v>
       </c>
@@ -6638,14 +6641,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="43" t="s">
+      <c r="AD57" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="AE57" s="44"/>
-      <c r="AF57" s="44"/>
-      <c r="AG57" s="44"/>
-      <c r="AH57" s="44"/>
-      <c r="AI57" s="45"/>
+      <c r="AE57" s="48"/>
+      <c r="AF57" s="48"/>
+      <c r="AG57" s="48"/>
+      <c r="AH57" s="48"/>
+      <c r="AI57" s="49"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6654,7 +6657,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="40">
+      <c r="AN57" s="35">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6677,11 +6680,11 @@
       <c r="AZ57" s="6"/>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="35"/>
-      <c r="BD57" s="35"/>
-    </row>
-    <row r="58" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I58" s="41"/>
+      <c r="BC57" s="64"/>
+      <c r="BD57" s="64"/>
+    </row>
+    <row r="58" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I58" s="36"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6716,17 +6719,17 @@
       <c r="AA58" s="33"/>
       <c r="AB58" s="33"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="75"/>
-      <c r="AE58" s="76"/>
-      <c r="AF58" s="76"/>
-      <c r="AG58" s="76"/>
-      <c r="AH58" s="76"/>
-      <c r="AI58" s="77"/>
+      <c r="AD58" s="44"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="46"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="41"/>
+      <c r="AN58" s="36"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6747,11 +6750,11 @@
       <c r="AZ58" s="6"/>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="35"/>
-      <c r="BD58" s="35"/>
-    </row>
-    <row r="59" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I59" s="40">
+      <c r="BC58" s="64"/>
+      <c r="BD58" s="64"/>
+    </row>
+    <row r="59" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I59" s="35">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6816,7 +6819,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="40">
+      <c r="AN59" s="35">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -6839,11 +6842,11 @@
       <c r="AZ59" s="6"/>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="35"/>
-      <c r="BD59" s="35"/>
-    </row>
-    <row r="60" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I60" s="41"/>
+      <c r="BC59" s="64"/>
+      <c r="BD59" s="64"/>
+    </row>
+    <row r="60" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I60" s="36"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6878,17 +6881,17 @@
       <c r="AA60" s="33"/>
       <c r="AB60" s="33"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="75"/>
-      <c r="AE60" s="76"/>
-      <c r="AF60" s="76"/>
-      <c r="AG60" s="76"/>
-      <c r="AH60" s="76"/>
-      <c r="AI60" s="77"/>
+      <c r="AD60" s="44"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="45"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="45"/>
+      <c r="AI60" s="46"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="41"/>
+      <c r="AN60" s="36"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -6909,11 +6912,11 @@
       <c r="AZ60" s="6"/>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="35"/>
-      <c r="BD60" s="35"/>
-    </row>
-    <row r="61" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I61" s="40" t="s">
+      <c r="BC60" s="64"/>
+      <c r="BD60" s="64"/>
+    </row>
+    <row r="61" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6944,10 +6947,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="40">
+      <c r="X61" s="35">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="58">
+      <c r="Y61" s="60">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -6978,7 +6981,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="40" t="s">
+      <c r="AN61" s="35" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -7001,11 +7004,11 @@
       <c r="AZ61" s="6"/>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="35"/>
-      <c r="BD61" s="35"/>
-    </row>
-    <row r="62" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I62" s="41"/>
+      <c r="BC61" s="64"/>
+      <c r="BD61" s="64"/>
+    </row>
+    <row r="62" spans="8:56" x14ac:dyDescent="0.45">
+      <c r="I62" s="36"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7034,8 +7037,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="41"/>
-      <c r="Y62" s="59"/>
+      <c r="X62" s="36"/>
+      <c r="Y62" s="61"/>
       <c r="Z62" s="15" t="s">
         <v>184</v>
       </c>
@@ -7064,7 +7067,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="41"/>
+      <c r="AN62" s="36"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7085,11 +7088,11 @@
       <c r="AZ62" s="6"/>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="35"/>
-      <c r="BD62" s="35"/>
-    </row>
-    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I63" s="40">
+      <c r="BC62" s="64"/>
+      <c r="BD62" s="64"/>
+    </row>
+    <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I63" s="35">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7126,17 +7129,17 @@
       <c r="AA63" s="33"/>
       <c r="AB63" s="33"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="75"/>
-      <c r="AE63" s="76"/>
-      <c r="AF63" s="76"/>
-      <c r="AG63" s="76"/>
-      <c r="AH63" s="76"/>
-      <c r="AI63" s="77"/>
+      <c r="AD63" s="44"/>
+      <c r="AE63" s="45"/>
+      <c r="AF63" s="45"/>
+      <c r="AG63" s="45"/>
+      <c r="AH63" s="45"/>
+      <c r="AI63" s="46"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="40">
+      <c r="AN63" s="35">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7159,11 +7162,11 @@
       <c r="AZ63" s="6"/>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="35"/>
-      <c r="BD63" s="35"/>
-    </row>
-    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I64" s="41"/>
+      <c r="BC63" s="64"/>
+      <c r="BD63" s="64"/>
+    </row>
+    <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I64" s="36"/>
       <c r="J64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7226,7 +7229,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="41"/>
+      <c r="AN64" s="36"/>
       <c r="AO64" s="6" t="s">
         <v>200</v>
       </c>
@@ -7247,18 +7250,22 @@
       <c r="AZ64" s="6"/>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="36"/>
-      <c r="BD64" s="36"/>
-    </row>
-    <row r="65" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I65" s="40">
+      <c r="BC64" s="65"/>
+      <c r="BD64" s="65"/>
+    </row>
+    <row r="65" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I65" s="35">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="K65" s="6"/>
-      <c r="L65" s="19"/>
+      <c r="K65" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L65" s="19">
+        <v>4</v>
+      </c>
       <c r="M65" s="6" t="s">
         <v>13</v>
       </c>
@@ -7270,8 +7277,12 @@
       <c r="Q65" s="38"/>
       <c r="R65" s="38"/>
       <c r="S65" s="39"/>
-      <c r="T65" s="7"/>
-      <c r="U65" s="6"/>
+      <c r="T65" s="7">
+        <v>45908</v>
+      </c>
+      <c r="U65" s="7">
+        <v>45914</v>
+      </c>
       <c r="V65" s="20"/>
       <c r="W65" s="20"/>
       <c r="X65" s="6"/>
@@ -7280,17 +7291,17 @@
       <c r="AA65" s="33"/>
       <c r="AB65" s="33"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="75"/>
-      <c r="AE65" s="76"/>
-      <c r="AF65" s="76"/>
-      <c r="AG65" s="76"/>
-      <c r="AH65" s="76"/>
-      <c r="AI65" s="77"/>
+      <c r="AD65" s="44"/>
+      <c r="AE65" s="45"/>
+      <c r="AF65" s="45"/>
+      <c r="AG65" s="45"/>
+      <c r="AH65" s="45"/>
+      <c r="AI65" s="46"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="40">
+      <c r="AN65" s="35">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7313,16 +7324,20 @@
       <c r="AZ65" s="6"/>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="35"/>
-      <c r="BD65" s="35"/>
-    </row>
-    <row r="66" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I66" s="41"/>
+      <c r="BC65" s="64"/>
+      <c r="BD65" s="64"/>
+    </row>
+    <row r="66" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I66" s="36"/>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K66" s="6"/>
-      <c r="L66" s="19"/>
+      <c r="K66" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L66" s="19">
+        <v>3</v>
+      </c>
       <c r="M66" s="6" t="s">
         <v>13</v>
       </c>
@@ -7334,14 +7349,18 @@
       <c r="Q66" s="38"/>
       <c r="R66" s="38"/>
       <c r="S66" s="39"/>
-      <c r="T66" s="7"/>
-      <c r="U66" s="6"/>
+      <c r="T66" s="7">
+        <v>45908</v>
+      </c>
+      <c r="U66" s="7">
+        <v>45914</v>
+      </c>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="40" t="s">
+      <c r="X66" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="54">
+      <c r="Y66" s="56">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7372,7 +7391,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="41"/>
+      <c r="AN66" s="36"/>
       <c r="AO66" s="6" t="s">
         <v>211</v>
       </c>
@@ -7393,18 +7412,22 @@
       <c r="AZ66" s="6"/>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="35"/>
-      <c r="BD66" s="35"/>
-    </row>
-    <row r="67" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC66" s="64"/>
+      <c r="BD66" s="64"/>
+    </row>
+    <row r="67" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I67" s="9">
         <v>6.3</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K67" s="6"/>
-      <c r="L67" s="19"/>
+      <c r="K67" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L67" s="19">
+        <v>3</v>
+      </c>
       <c r="M67" s="6" t="s">
         <v>13</v>
       </c>
@@ -7416,12 +7439,16 @@
       <c r="Q67" s="38"/>
       <c r="R67" s="38"/>
       <c r="S67" s="39"/>
-      <c r="T67" s="7"/>
-      <c r="U67" s="6"/>
+      <c r="T67" s="7">
+        <v>45908</v>
+      </c>
+      <c r="U67" s="7">
+        <v>45914</v>
+      </c>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="41"/>
-      <c r="Y67" s="55"/>
+      <c r="X67" s="36"/>
+      <c r="Y67" s="57"/>
       <c r="Z67" s="6" t="s">
         <v>185</v>
       </c>
@@ -7473,11 +7500,11 @@
       <c r="AZ67" s="6"/>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="35"/>
-      <c r="BD67" s="35"/>
-    </row>
-    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I68" s="40">
+      <c r="BC67" s="64"/>
+      <c r="BD67" s="64"/>
+    </row>
+    <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I68" s="35">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7510,17 +7537,17 @@
       <c r="AA68" s="33"/>
       <c r="AB68" s="33"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="75"/>
-      <c r="AE68" s="76"/>
-      <c r="AF68" s="76"/>
-      <c r="AG68" s="76"/>
-      <c r="AH68" s="76"/>
-      <c r="AI68" s="77"/>
+      <c r="AD68" s="44"/>
+      <c r="AE68" s="45"/>
+      <c r="AF68" s="45"/>
+      <c r="AG68" s="45"/>
+      <c r="AH68" s="45"/>
+      <c r="AI68" s="46"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="40">
+      <c r="AN68" s="35">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7543,11 +7570,11 @@
       <c r="AZ68" s="6"/>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="35"/>
-      <c r="BD68" s="35"/>
-    </row>
-    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I69" s="41"/>
+      <c r="BC68" s="64"/>
+      <c r="BD68" s="64"/>
+    </row>
+    <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I69" s="36"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7572,10 +7599,10 @@
       <c r="U69" s="6"/>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="40" t="s">
+      <c r="X69" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="54">
+      <c r="Y69" s="56">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7606,7 +7633,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="41"/>
+      <c r="AN69" s="36"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7627,10 +7654,10 @@
       <c r="AZ69" s="6"/>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="35"/>
-      <c r="BD69" s="35"/>
-    </row>
-    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC69" s="64"/>
+      <c r="BD69" s="64"/>
+    </row>
+    <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I70" s="9">
         <v>6.6</v>
       </c>
@@ -7662,8 +7689,8 @@
       </c>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="41"/>
-      <c r="Y70" s="55"/>
+      <c r="X70" s="36"/>
+      <c r="Y70" s="57"/>
       <c r="Z70" s="6" t="s">
         <v>186</v>
       </c>
@@ -7715,11 +7742,11 @@
       <c r="AZ70" s="6"/>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="35"/>
-      <c r="BD70" s="35"/>
-    </row>
-    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I71" s="40">
+      <c r="BC70" s="64"/>
+      <c r="BD70" s="64"/>
+    </row>
+    <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I71" s="35">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7756,17 +7783,17 @@
       <c r="AA71" s="33"/>
       <c r="AB71" s="33"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="75"/>
-      <c r="AE71" s="76"/>
-      <c r="AF71" s="76"/>
-      <c r="AG71" s="76"/>
-      <c r="AH71" s="76"/>
-      <c r="AI71" s="77"/>
+      <c r="AD71" s="44"/>
+      <c r="AE71" s="45"/>
+      <c r="AF71" s="45"/>
+      <c r="AG71" s="45"/>
+      <c r="AH71" s="45"/>
+      <c r="AI71" s="46"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="40">
+      <c r="AN71" s="35">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -7789,11 +7816,11 @@
       <c r="AZ71" s="6"/>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="35"/>
-      <c r="BD71" s="35"/>
-    </row>
-    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I72" s="41"/>
+      <c r="BC71" s="64"/>
+      <c r="BD71" s="64"/>
+    </row>
+    <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I72" s="36"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7822,10 +7849,10 @@
       </c>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="40">
+      <c r="X72" s="35">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="52">
+      <c r="Y72" s="40">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -7840,14 +7867,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="43" t="s">
+      <c r="AD72" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
-      <c r="AH72" s="44"/>
-      <c r="AI72" s="45"/>
+      <c r="AE72" s="48"/>
+      <c r="AF72" s="48"/>
+      <c r="AG72" s="48"/>
+      <c r="AH72" s="48"/>
+      <c r="AI72" s="49"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -7856,7 +7883,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="41"/>
+      <c r="AN72" s="36"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -7877,11 +7904,11 @@
       <c r="AZ72" s="6"/>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="35"/>
-      <c r="BD72" s="35"/>
-    </row>
-    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I73" s="40">
+      <c r="BC72" s="64"/>
+      <c r="BD72" s="64"/>
+    </row>
+    <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7896,14 +7923,14 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="43" t="s">
+      <c r="N73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
-      <c r="R73" s="44"/>
-      <c r="S73" s="45"/>
+      <c r="O73" s="48"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="48"/>
+      <c r="R73" s="48"/>
+      <c r="S73" s="49"/>
       <c r="T73" s="8">
         <v>45844</v>
       </c>
@@ -7912,8 +7939,8 @@
       </c>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="41"/>
-      <c r="Y73" s="53"/>
+      <c r="X73" s="36"/>
+      <c r="Y73" s="41"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -7926,14 +7953,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="43" t="s">
+      <c r="AD73" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
-      <c r="AH73" s="44"/>
-      <c r="AI73" s="45"/>
+      <c r="AE73" s="48"/>
+      <c r="AF73" s="48"/>
+      <c r="AG73" s="48"/>
+      <c r="AH73" s="48"/>
+      <c r="AI73" s="49"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -7942,7 +7969,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="40">
+      <c r="AN73" s="35">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -7953,23 +7980,23 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="43" t="s">
+      <c r="AS73" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="44"/>
-      <c r="AU73" s="44"/>
-      <c r="AV73" s="44"/>
-      <c r="AW73" s="44"/>
-      <c r="AX73" s="45"/>
+      <c r="AT73" s="48"/>
+      <c r="AU73" s="48"/>
+      <c r="AV73" s="48"/>
+      <c r="AW73" s="48"/>
+      <c r="AX73" s="49"/>
       <c r="AY73" s="7"/>
       <c r="AZ73" s="6"/>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="35"/>
-      <c r="BD73" s="35"/>
-    </row>
-    <row r="74" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I74" s="41"/>
+      <c r="BC73" s="64"/>
+      <c r="BD73" s="64"/>
+    </row>
+    <row r="74" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I74" s="36"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -8004,17 +8031,17 @@
       <c r="AA74" s="33"/>
       <c r="AB74" s="33"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="75"/>
-      <c r="AE74" s="76"/>
-      <c r="AF74" s="76"/>
-      <c r="AG74" s="76"/>
-      <c r="AH74" s="76"/>
-      <c r="AI74" s="77"/>
+      <c r="AD74" s="44"/>
+      <c r="AE74" s="45"/>
+      <c r="AF74" s="45"/>
+      <c r="AG74" s="45"/>
+      <c r="AH74" s="45"/>
+      <c r="AI74" s="46"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="41"/>
+      <c r="AN74" s="36"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -8035,11 +8062,11 @@
       <c r="AZ74" s="6"/>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="35"/>
-      <c r="BD74" s="35"/>
-    </row>
-    <row r="75" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I75" s="40">
+      <c r="BC74" s="64"/>
+      <c r="BD74" s="64"/>
+    </row>
+    <row r="75" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -8054,14 +8081,14 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="43" t="s">
+      <c r="N75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="44"/>
-      <c r="P75" s="44"/>
-      <c r="Q75" s="44"/>
-      <c r="R75" s="44"/>
-      <c r="S75" s="45"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="49"/>
       <c r="T75" s="8">
         <v>45844</v>
       </c>
@@ -8070,10 +8097,10 @@
       </c>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="40">
+      <c r="X75" s="35">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="60">
+      <c r="Y75" s="58">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -8104,7 +8131,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="40">
+      <c r="AN75" s="35">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -8115,23 +8142,23 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="43" t="s">
+      <c r="AS75" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="44"/>
-      <c r="AU75" s="44"/>
-      <c r="AV75" s="44"/>
-      <c r="AW75" s="44"/>
-      <c r="AX75" s="45"/>
+      <c r="AT75" s="48"/>
+      <c r="AU75" s="48"/>
+      <c r="AV75" s="48"/>
+      <c r="AW75" s="48"/>
+      <c r="AX75" s="49"/>
       <c r="AY75" s="7"/>
       <c r="AZ75" s="6"/>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="35"/>
-      <c r="BD75" s="35"/>
-    </row>
-    <row r="76" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I76" s="41"/>
+      <c r="BC75" s="64"/>
+      <c r="BD75" s="64"/>
+    </row>
+    <row r="76" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I76" s="36"/>
       <c r="J76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8160,8 +8187,8 @@
       </c>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="41"/>
-      <c r="Y76" s="61"/>
+      <c r="X76" s="36"/>
+      <c r="Y76" s="59"/>
       <c r="Z76" s="6" t="s">
         <v>198</v>
       </c>
@@ -8190,7 +8217,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="41"/>
+      <c r="AN76" s="36"/>
       <c r="AO76" s="6" t="s">
         <v>213</v>
       </c>
@@ -8211,11 +8238,11 @@
       <c r="AZ76" s="6"/>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="36"/>
-      <c r="BD76" s="36"/>
-    </row>
-    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I77" s="40">
+      <c r="BC76" s="65"/>
+      <c r="BD76" s="65"/>
+    </row>
+    <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I77" s="35">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8252,17 +8279,17 @@
       <c r="AA77" s="33"/>
       <c r="AB77" s="33"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="75"/>
-      <c r="AE77" s="76"/>
-      <c r="AF77" s="76"/>
-      <c r="AG77" s="76"/>
-      <c r="AH77" s="76"/>
-      <c r="AI77" s="77"/>
+      <c r="AD77" s="44"/>
+      <c r="AE77" s="45"/>
+      <c r="AF77" s="45"/>
+      <c r="AG77" s="45"/>
+      <c r="AH77" s="45"/>
+      <c r="AI77" s="46"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="40">
+      <c r="AN77" s="35">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8285,11 +8312,11 @@
       <c r="AZ77" s="6"/>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="35"/>
-      <c r="BD77" s="35"/>
-    </row>
-    <row r="78" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I78" s="41"/>
+      <c r="BC77" s="64"/>
+      <c r="BD77" s="64"/>
+    </row>
+    <row r="78" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I78" s="36"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8318,10 +8345,10 @@
       </c>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="40">
+      <c r="X78" s="35">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="52">
+      <c r="Y78" s="40">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8352,7 +8379,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="41"/>
+      <c r="AN78" s="36"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8373,11 +8400,11 @@
       <c r="AZ78" s="6"/>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="35"/>
-      <c r="BD78" s="35"/>
-    </row>
-    <row r="79" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I79" s="40">
+      <c r="BC78" s="64"/>
+      <c r="BD78" s="64"/>
+    </row>
+    <row r="79" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I79" s="35">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8390,22 +8417,22 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="43" t="s">
+      <c r="N79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
-      <c r="R79" s="44"/>
-      <c r="S79" s="45"/>
+      <c r="O79" s="48"/>
+      <c r="P79" s="48"/>
+      <c r="Q79" s="48"/>
+      <c r="R79" s="48"/>
+      <c r="S79" s="49"/>
       <c r="T79" s="7">
         <v>45905</v>
       </c>
       <c r="U79" s="6"/>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="41"/>
-      <c r="Y79" s="53"/>
+      <c r="X79" s="36"/>
+      <c r="Y79" s="41"/>
       <c r="Z79" s="18" t="s">
         <v>196</v>
       </c>
@@ -8434,7 +8461,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="40">
+      <c r="AN79" s="35">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8445,23 +8472,23 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="43" t="s">
+      <c r="AS79" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="44"/>
-      <c r="AU79" s="44"/>
-      <c r="AV79" s="44"/>
-      <c r="AW79" s="44"/>
-      <c r="AX79" s="45"/>
+      <c r="AT79" s="48"/>
+      <c r="AU79" s="48"/>
+      <c r="AV79" s="48"/>
+      <c r="AW79" s="48"/>
+      <c r="AX79" s="49"/>
       <c r="AY79" s="7"/>
       <c r="AZ79" s="6"/>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="35"/>
-      <c r="BD79" s="35"/>
-    </row>
-    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I80" s="41"/>
+      <c r="BC79" s="64"/>
+      <c r="BD79" s="64"/>
+    </row>
+    <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I80" s="36"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8492,17 +8519,17 @@
       <c r="AA80" s="33"/>
       <c r="AB80" s="33"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="75"/>
-      <c r="AE80" s="76"/>
-      <c r="AF80" s="76"/>
-      <c r="AG80" s="76"/>
-      <c r="AH80" s="76"/>
-      <c r="AI80" s="77"/>
+      <c r="AD80" s="44"/>
+      <c r="AE80" s="45"/>
+      <c r="AF80" s="45"/>
+      <c r="AG80" s="45"/>
+      <c r="AH80" s="45"/>
+      <c r="AI80" s="46"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="41"/>
+      <c r="AN80" s="36"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8523,18 +8550,22 @@
       <c r="AZ80" s="6"/>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="35"/>
-      <c r="BD80" s="35"/>
-    </row>
-    <row r="81" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I81" s="40">
+      <c r="BC80" s="64"/>
+      <c r="BD80" s="64"/>
+    </row>
+    <row r="81" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I81" s="35">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K81" s="6"/>
-      <c r="L81" s="19"/>
+      <c r="K81" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L81" s="19">
+        <v>3</v>
+      </c>
       <c r="M81" s="6" t="s">
         <v>13</v>
       </c>
@@ -8546,8 +8577,12 @@
       <c r="Q81" s="38"/>
       <c r="R81" s="38"/>
       <c r="S81" s="39"/>
-      <c r="T81" s="7"/>
-      <c r="U81" s="6"/>
+      <c r="T81" s="7">
+        <v>45911</v>
+      </c>
+      <c r="U81" s="7">
+        <v>45917</v>
+      </c>
       <c r="V81" s="20"/>
       <c r="W81" s="20"/>
       <c r="X81" s="9">
@@ -8584,7 +8619,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="40">
+      <c r="AN81" s="35">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -8607,29 +8642,37 @@
       <c r="AZ81" s="6"/>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="35"/>
-      <c r="BD81" s="35"/>
-    </row>
-    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I82" s="41"/>
+      <c r="BC81" s="64"/>
+      <c r="BD81" s="64"/>
+    </row>
+    <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I82" s="36"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K82" s="6"/>
-      <c r="L82" s="19"/>
+      <c r="K82" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L82" s="19">
+        <v>4</v>
+      </c>
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="43" t="s">
+      <c r="N82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="44"/>
-      <c r="P82" s="44"/>
-      <c r="Q82" s="44"/>
-      <c r="R82" s="44"/>
-      <c r="S82" s="45"/>
-      <c r="T82" s="7"/>
-      <c r="U82" s="6"/>
+      <c r="O82" s="48"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="48"/>
+      <c r="R82" s="48"/>
+      <c r="S82" s="49"/>
+      <c r="T82" s="7">
+        <v>45911</v>
+      </c>
+      <c r="U82" s="7">
+        <v>45917</v>
+      </c>
       <c r="V82" s="20"/>
       <c r="W82" s="20"/>
       <c r="X82" s="6"/>
@@ -8638,17 +8681,17 @@
       <c r="AA82" s="33"/>
       <c r="AB82" s="33"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="75"/>
-      <c r="AE82" s="76"/>
-      <c r="AF82" s="76"/>
-      <c r="AG82" s="76"/>
-      <c r="AH82" s="76"/>
-      <c r="AI82" s="77"/>
+      <c r="AD82" s="44"/>
+      <c r="AE82" s="45"/>
+      <c r="AF82" s="45"/>
+      <c r="AG82" s="45"/>
+      <c r="AH82" s="45"/>
+      <c r="AI82" s="46"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="41"/>
+      <c r="AN82" s="36"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -8657,23 +8700,23 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="43" t="s">
+      <c r="AS82" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="44"/>
-      <c r="AU82" s="44"/>
-      <c r="AV82" s="44"/>
-      <c r="AW82" s="44"/>
-      <c r="AX82" s="45"/>
+      <c r="AT82" s="48"/>
+      <c r="AU82" s="48"/>
+      <c r="AV82" s="48"/>
+      <c r="AW82" s="48"/>
+      <c r="AX82" s="49"/>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="6"/>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="35"/>
-      <c r="BD82" s="35"/>
-    </row>
-    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I83" s="40">
+      <c r="BC82" s="64"/>
+      <c r="BD82" s="64"/>
+    </row>
+    <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I83" s="35">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -8704,10 +8747,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="40">
+      <c r="X83" s="35">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="54">
+      <c r="Y83" s="56">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -8738,7 +8781,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="40">
+      <c r="AN83" s="35">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -8767,11 +8810,11 @@
       </c>
       <c r="BA83" s="19"/>
       <c r="BB83" s="19"/>
-      <c r="BC83" s="35"/>
-      <c r="BD83" s="35"/>
-    </row>
-    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I84" s="41"/>
+      <c r="BC83" s="64"/>
+      <c r="BD83" s="64"/>
+    </row>
+    <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I84" s="36"/>
       <c r="J84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8800,8 +8843,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="41"/>
-      <c r="Y84" s="55"/>
+      <c r="X84" s="36"/>
+      <c r="Y84" s="57"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -8830,7 +8873,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="41"/>
+      <c r="AN84" s="36"/>
       <c r="AO84" s="6" t="s">
         <v>214</v>
       </c>
@@ -8857,18 +8900,22 @@
       </c>
       <c r="BA84" s="19"/>
       <c r="BB84" s="19"/>
-      <c r="BC84" s="35"/>
-      <c r="BD84" s="35"/>
-    </row>
-    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BC84" s="64"/>
+      <c r="BD84" s="64"/>
+    </row>
+    <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I85" s="9">
         <v>5.4</v>
       </c>
       <c r="J85" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="K85" s="6"/>
-      <c r="L85" s="19"/>
+      <c r="K85" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L85" s="19">
+        <v>3</v>
+      </c>
       <c r="M85" s="6" t="s">
         <v>13</v>
       </c>
@@ -8880,8 +8927,12 @@
       <c r="Q85" s="38"/>
       <c r="R85" s="38"/>
       <c r="S85" s="39"/>
-      <c r="T85" s="7"/>
-      <c r="U85" s="6"/>
+      <c r="T85" s="7">
+        <v>45913</v>
+      </c>
+      <c r="U85" s="7">
+        <v>45917</v>
+      </c>
       <c r="V85" s="20"/>
       <c r="W85" s="20"/>
       <c r="X85" s="6"/>
@@ -8890,12 +8941,12 @@
       <c r="AA85" s="33"/>
       <c r="AB85" s="33"/>
       <c r="AC85" s="4"/>
-      <c r="AD85" s="75"/>
-      <c r="AE85" s="76"/>
-      <c r="AF85" s="76"/>
-      <c r="AG85" s="76"/>
-      <c r="AH85" s="76"/>
-      <c r="AI85" s="77"/>
+      <c r="AD85" s="44"/>
+      <c r="AE85" s="45"/>
+      <c r="AF85" s="45"/>
+      <c r="AG85" s="45"/>
+      <c r="AH85" s="45"/>
+      <c r="AI85" s="46"/>
       <c r="AJ85" s="19"/>
       <c r="AK85" s="19"/>
       <c r="AL85" s="20"/>
@@ -8923,11 +8974,11 @@
       <c r="AZ85" s="6"/>
       <c r="BA85" s="19"/>
       <c r="BB85" s="19"/>
-      <c r="BC85" s="35"/>
-      <c r="BD85" s="35"/>
-    </row>
-    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I86" s="40">
+      <c r="BC85" s="64"/>
+      <c r="BD85" s="64"/>
+    </row>
+    <row r="86" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I86" s="35">
         <v>1.2</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -8958,10 +9009,10 @@
       </c>
       <c r="V86" s="20"/>
       <c r="W86" s="20"/>
-      <c r="X86" s="40">
+      <c r="X86" s="35">
         <v>3.7</v>
       </c>
-      <c r="Y86" s="56">
+      <c r="Y86" s="50">
         <v>4</v>
       </c>
       <c r="Z86" s="6" t="s">
@@ -8992,7 +9043,7 @@
       </c>
       <c r="AL86" s="20"/>
       <c r="AM86" s="20"/>
-      <c r="AN86" s="40">
+      <c r="AN86" s="35">
         <v>1.2</v>
       </c>
       <c r="AO86" s="6" t="s">
@@ -9015,11 +9066,11 @@
       <c r="AZ86" s="6"/>
       <c r="BA86" s="19"/>
       <c r="BB86" s="19"/>
-      <c r="BC86" s="35"/>
-      <c r="BD86" s="35"/>
-    </row>
-    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I87" s="41"/>
+      <c r="BC86" s="64"/>
+      <c r="BD86" s="64"/>
+    </row>
+    <row r="87" spans="9:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I87" s="36"/>
       <c r="J87" s="6" t="s">
         <v>85</v>
       </c>
@@ -9048,8 +9099,8 @@
       </c>
       <c r="V87" s="20"/>
       <c r="W87" s="20"/>
-      <c r="X87" s="41"/>
-      <c r="Y87" s="57"/>
+      <c r="X87" s="36"/>
+      <c r="Y87" s="51"/>
       <c r="Z87" s="6" t="s">
         <v>74</v>
       </c>
@@ -9078,7 +9129,7 @@
       </c>
       <c r="AL87" s="20"/>
       <c r="AM87" s="20"/>
-      <c r="AN87" s="41"/>
+      <c r="AN87" s="36"/>
       <c r="AO87" s="6" t="s">
         <v>85</v>
       </c>
@@ -9099,11 +9150,11 @@
       <c r="AZ87" s="6"/>
       <c r="BA87" s="19"/>
       <c r="BB87" s="19"/>
-      <c r="BC87" s="35"/>
-      <c r="BD87" s="35"/>
-    </row>
-    <row r="88" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I88" s="40" t="s">
+      <c r="BC87" s="64"/>
+      <c r="BD87" s="64"/>
+    </row>
+    <row r="88" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -9140,17 +9191,17 @@
       <c r="AA88" s="33"/>
       <c r="AB88" s="33"/>
       <c r="AC88" s="4"/>
-      <c r="AD88" s="75"/>
-      <c r="AE88" s="76"/>
-      <c r="AF88" s="76"/>
-      <c r="AG88" s="76"/>
-      <c r="AH88" s="76"/>
-      <c r="AI88" s="77"/>
+      <c r="AD88" s="44"/>
+      <c r="AE88" s="45"/>
+      <c r="AF88" s="45"/>
+      <c r="AG88" s="45"/>
+      <c r="AH88" s="45"/>
+      <c r="AI88" s="46"/>
       <c r="AJ88" s="19"/>
       <c r="AK88" s="19"/>
       <c r="AL88" s="20"/>
       <c r="AM88" s="20"/>
-      <c r="AN88" s="40" t="s">
+      <c r="AN88" s="35" t="s">
         <v>83</v>
       </c>
       <c r="AO88" s="6" t="s">
@@ -9173,11 +9224,11 @@
       <c r="AZ88" s="6"/>
       <c r="BA88" s="25"/>
       <c r="BB88" s="25"/>
-      <c r="BC88" s="36"/>
-      <c r="BD88" s="36"/>
-    </row>
-    <row r="89" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I89" s="41"/>
+      <c r="BC88" s="65"/>
+      <c r="BD88" s="65"/>
+    </row>
+    <row r="89" spans="9:56" x14ac:dyDescent="0.45">
+      <c r="I89" s="36"/>
       <c r="J89" s="14" t="s">
         <v>168</v>
       </c>
@@ -9206,10 +9257,10 @@
       </c>
       <c r="V89" s="20"/>
       <c r="W89" s="20"/>
-      <c r="X89" s="40" t="s">
+      <c r="X89" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="Y89" s="56">
+      <c r="Y89" s="50">
         <v>4</v>
       </c>
       <c r="Z89" s="6" t="s">
@@ -9240,7 +9291,7 @@
       </c>
       <c r="AL89" s="20"/>
       <c r="AM89" s="20"/>
-      <c r="AN89" s="41"/>
+      <c r="AN89" s="36"/>
       <c r="AO89" s="14" t="s">
         <v>86</v>
       </c>
@@ -9261,35 +9312,43 @@
       <c r="AZ89" s="6"/>
       <c r="BA89" s="19"/>
       <c r="BB89" s="19"/>
-      <c r="BC89" s="35"/>
-      <c r="BD89" s="35"/>
-    </row>
-    <row r="90" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC89" s="64"/>
+      <c r="BD89" s="64"/>
+    </row>
+    <row r="90" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I90" s="6">
         <v>5.8</v>
       </c>
       <c r="J90" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K90" s="6"/>
-      <c r="L90" s="19"/>
+      <c r="K90" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L90" s="19">
+        <v>3</v>
+      </c>
       <c r="M90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N90" s="42" t="s">
+      <c r="N90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="O90" s="42"/>
-      <c r="P90" s="42"/>
-      <c r="Q90" s="42"/>
-      <c r="R90" s="42"/>
-      <c r="S90" s="42"/>
-      <c r="T90" s="7"/>
-      <c r="U90" s="6"/>
+      <c r="O90" s="52"/>
+      <c r="P90" s="52"/>
+      <c r="Q90" s="52"/>
+      <c r="R90" s="52"/>
+      <c r="S90" s="52"/>
+      <c r="T90" s="7">
+        <v>45913</v>
+      </c>
+      <c r="U90" s="7">
+        <v>45917</v>
+      </c>
       <c r="V90" s="20"/>
       <c r="W90" s="20"/>
-      <c r="X90" s="41"/>
-      <c r="Y90" s="57"/>
+      <c r="X90" s="36"/>
+      <c r="Y90" s="51"/>
       <c r="Z90" s="6" t="s">
         <v>75</v>
       </c>
@@ -9329,22 +9388,22 @@
       <c r="AR90" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS90" s="42" t="s">
+      <c r="AS90" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AT90" s="42"/>
-      <c r="AU90" s="42"/>
-      <c r="AV90" s="42"/>
-      <c r="AW90" s="42"/>
-      <c r="AX90" s="42"/>
+      <c r="AT90" s="52"/>
+      <c r="AU90" s="52"/>
+      <c r="AV90" s="52"/>
+      <c r="AW90" s="52"/>
+      <c r="AX90" s="52"/>
       <c r="AY90" s="7"/>
       <c r="AZ90" s="6"/>
       <c r="BA90" s="19"/>
       <c r="BB90" s="19"/>
-      <c r="BC90" s="35"/>
-      <c r="BD90" s="35"/>
-    </row>
-    <row r="91" spans="9:56" x14ac:dyDescent="0.25">
+      <c r="BC90" s="64"/>
+      <c r="BD90" s="64"/>
+    </row>
+    <row r="91" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
       <c r="K91" s="20"/>
@@ -9366,12 +9425,12 @@
       <c r="AA91" s="33"/>
       <c r="AB91" s="33"/>
       <c r="AC91" s="4"/>
-      <c r="AD91" s="75"/>
-      <c r="AE91" s="76"/>
-      <c r="AF91" s="76"/>
-      <c r="AG91" s="76"/>
-      <c r="AH91" s="76"/>
-      <c r="AI91" s="77"/>
+      <c r="AD91" s="44"/>
+      <c r="AE91" s="45"/>
+      <c r="AF91" s="45"/>
+      <c r="AG91" s="45"/>
+      <c r="AH91" s="45"/>
+      <c r="AI91" s="46"/>
       <c r="AJ91" s="19"/>
       <c r="AK91" s="19"/>
       <c r="AL91" s="20"/>
@@ -9394,7 +9453,7 @@
       <c r="BC91" s="20"/>
       <c r="BD91" s="20"/>
     </row>
-    <row r="92" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="92" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
       <c r="K92" s="20"/>
@@ -9410,10 +9469,10 @@
       <c r="U92" s="20"/>
       <c r="V92" s="20"/>
       <c r="W92" s="20"/>
-      <c r="X92" s="40">
+      <c r="X92" s="35">
         <v>5.5</v>
       </c>
-      <c r="Y92" s="60">
+      <c r="Y92" s="58">
         <v>2</v>
       </c>
       <c r="Z92" s="6" t="s">
@@ -9462,7 +9521,7 @@
       <c r="BC92" s="20"/>
       <c r="BD92" s="20"/>
     </row>
-    <row r="93" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="93" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
       <c r="K93" s="20"/>
@@ -9478,8 +9537,8 @@
       <c r="U93" s="20"/>
       <c r="V93" s="20"/>
       <c r="W93" s="20"/>
-      <c r="X93" s="41"/>
-      <c r="Y93" s="61"/>
+      <c r="X93" s="36"/>
+      <c r="Y93" s="59"/>
       <c r="Z93" s="6" t="s">
         <v>200</v>
       </c>
@@ -9526,7 +9585,7 @@
       <c r="BC93" s="20"/>
       <c r="BD93" s="20"/>
     </row>
-    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
       <c r="K94" s="20"/>
@@ -9548,12 +9607,12 @@
       <c r="AA94" s="33"/>
       <c r="AB94" s="33"/>
       <c r="AC94" s="4"/>
-      <c r="AD94" s="75"/>
-      <c r="AE94" s="76"/>
-      <c r="AF94" s="76"/>
-      <c r="AG94" s="76"/>
-      <c r="AH94" s="76"/>
-      <c r="AI94" s="77"/>
+      <c r="AD94" s="44"/>
+      <c r="AE94" s="45"/>
+      <c r="AF94" s="45"/>
+      <c r="AG94" s="45"/>
+      <c r="AH94" s="45"/>
+      <c r="AI94" s="46"/>
       <c r="AJ94" s="19"/>
       <c r="AK94" s="19"/>
       <c r="AL94" s="20"/>
@@ -9576,7 +9635,7 @@
       <c r="BC94" s="20"/>
       <c r="BD94" s="20"/>
     </row>
-    <row r="95" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="95" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
       <c r="K95" s="20"/>
@@ -9592,10 +9651,10 @@
       <c r="U95" s="20"/>
       <c r="V95" s="20"/>
       <c r="W95" s="20"/>
-      <c r="X95" s="40">
+      <c r="X95" s="35">
         <v>6.2</v>
       </c>
-      <c r="Y95" s="58">
+      <c r="Y95" s="60">
         <v>4</v>
       </c>
       <c r="Z95" s="6" t="s">
@@ -9636,7 +9695,7 @@
       <c r="BC95" s="20"/>
       <c r="BD95" s="20"/>
     </row>
-    <row r="96" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="96" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
       <c r="K96" s="20"/>
@@ -9652,8 +9711,8 @@
       <c r="U96" s="20"/>
       <c r="V96" s="20"/>
       <c r="W96" s="20"/>
-      <c r="X96" s="41"/>
-      <c r="Y96" s="59"/>
+      <c r="X96" s="36"/>
+      <c r="Y96" s="61"/>
       <c r="Z96" s="6" t="s">
         <v>211</v>
       </c>
@@ -9692,7 +9751,7 @@
       <c r="BC96" s="20"/>
       <c r="BD96" s="20"/>
     </row>
-    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
@@ -9714,12 +9773,12 @@
       <c r="AA97" s="33"/>
       <c r="AB97" s="33"/>
       <c r="AC97" s="4"/>
-      <c r="AD97" s="75"/>
-      <c r="AE97" s="76"/>
-      <c r="AF97" s="76"/>
-      <c r="AG97" s="76"/>
-      <c r="AH97" s="76"/>
-      <c r="AI97" s="77"/>
+      <c r="AD97" s="44"/>
+      <c r="AE97" s="45"/>
+      <c r="AF97" s="45"/>
+      <c r="AG97" s="45"/>
+      <c r="AH97" s="45"/>
+      <c r="AI97" s="46"/>
       <c r="AJ97" s="19"/>
       <c r="AK97" s="19"/>
       <c r="AL97" s="20"/>
@@ -9742,7 +9801,7 @@
       <c r="BC97" s="20"/>
       <c r="BD97" s="20"/>
     </row>
-    <row r="98" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
@@ -9802,7 +9861,7 @@
       <c r="BC98" s="20"/>
       <c r="BD98" s="20"/>
     </row>
-    <row r="99" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
@@ -9824,12 +9883,12 @@
       <c r="AA99" s="33"/>
       <c r="AB99" s="33"/>
       <c r="AC99" s="4"/>
-      <c r="AD99" s="75"/>
-      <c r="AE99" s="76"/>
-      <c r="AF99" s="76"/>
-      <c r="AG99" s="76"/>
-      <c r="AH99" s="76"/>
-      <c r="AI99" s="77"/>
+      <c r="AD99" s="44"/>
+      <c r="AE99" s="45"/>
+      <c r="AF99" s="45"/>
+      <c r="AG99" s="45"/>
+      <c r="AH99" s="45"/>
+      <c r="AI99" s="46"/>
       <c r="AJ99" s="19"/>
       <c r="AK99" s="19"/>
       <c r="AL99" s="20"/>
@@ -9852,7 +9911,7 @@
       <c r="BC99" s="20"/>
       <c r="BD99" s="20"/>
     </row>
-    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
@@ -9868,10 +9927,10 @@
       <c r="U100" s="20"/>
       <c r="V100" s="20"/>
       <c r="W100" s="20"/>
-      <c r="X100" s="40">
+      <c r="X100" s="35">
         <v>6.4</v>
       </c>
-      <c r="Y100" s="52">
+      <c r="Y100" s="40">
         <v>1</v>
       </c>
       <c r="Z100" s="6" t="s">
@@ -9920,7 +9979,7 @@
       <c r="BC100" s="20"/>
       <c r="BD100" s="20"/>
     </row>
-    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:56" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
@@ -9936,8 +9995,8 @@
       <c r="U101" s="20"/>
       <c r="V101" s="20"/>
       <c r="W101" s="20"/>
-      <c r="X101" s="41"/>
-      <c r="Y101" s="53"/>
+      <c r="X101" s="36"/>
+      <c r="Y101" s="41"/>
       <c r="Z101" s="6" t="s">
         <v>77</v>
       </c>
@@ -9984,7 +10043,7 @@
       <c r="BC101" s="20"/>
       <c r="BD101" s="20"/>
     </row>
-    <row r="102" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
@@ -10006,12 +10065,12 @@
       <c r="AA102" s="33"/>
       <c r="AB102" s="33"/>
       <c r="AC102" s="4"/>
-      <c r="AD102" s="75"/>
-      <c r="AE102" s="76"/>
-      <c r="AF102" s="76"/>
-      <c r="AG102" s="76"/>
-      <c r="AH102" s="76"/>
-      <c r="AI102" s="77"/>
+      <c r="AD102" s="44"/>
+      <c r="AE102" s="45"/>
+      <c r="AF102" s="45"/>
+      <c r="AG102" s="45"/>
+      <c r="AH102" s="45"/>
+      <c r="AI102" s="46"/>
       <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="20"/>
@@ -10034,7 +10093,7 @@
       <c r="BC102" s="20"/>
       <c r="BD102" s="20"/>
     </row>
-    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
       <c r="K103" s="20"/>
@@ -10094,7 +10153,7 @@
       <c r="BC103" s="20"/>
       <c r="BD103" s="20"/>
     </row>
-    <row r="104" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
       <c r="K104" s="20"/>
@@ -10116,12 +10175,12 @@
       <c r="AA104" s="33"/>
       <c r="AB104" s="33"/>
       <c r="AC104" s="4"/>
-      <c r="AD104" s="75"/>
-      <c r="AE104" s="76"/>
-      <c r="AF104" s="76"/>
-      <c r="AG104" s="76"/>
-      <c r="AH104" s="76"/>
-      <c r="AI104" s="77"/>
+      <c r="AD104" s="44"/>
+      <c r="AE104" s="45"/>
+      <c r="AF104" s="45"/>
+      <c r="AG104" s="45"/>
+      <c r="AH104" s="45"/>
+      <c r="AI104" s="46"/>
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="20"/>
@@ -10144,7 +10203,7 @@
       <c r="BC104" s="20"/>
       <c r="BD104" s="20"/>
     </row>
-    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="H105" s="10"/>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -10161,10 +10220,10 @@
       <c r="U105" s="20"/>
       <c r="V105" s="20"/>
       <c r="W105" s="20"/>
-      <c r="X105" s="40">
+      <c r="X105" s="35">
         <v>1.9</v>
       </c>
-      <c r="Y105" s="56">
+      <c r="Y105" s="50">
         <v>4</v>
       </c>
       <c r="Z105" s="6" t="s">
@@ -10205,7 +10264,7 @@
       <c r="BC105" s="20"/>
       <c r="BD105" s="20"/>
     </row>
-    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
       <c r="K106" s="20"/>
@@ -10221,8 +10280,8 @@
       <c r="U106" s="20"/>
       <c r="V106" s="20"/>
       <c r="W106" s="20"/>
-      <c r="X106" s="41"/>
-      <c r="Y106" s="57"/>
+      <c r="X106" s="36"/>
+      <c r="Y106" s="51"/>
       <c r="Z106" s="6" t="s">
         <v>78</v>
       </c>
@@ -10261,7 +10320,7 @@
       <c r="BC106" s="20"/>
       <c r="BD106" s="20"/>
     </row>
-    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
       <c r="K107" s="20"/>
@@ -10283,12 +10342,12 @@
       <c r="AA107" s="33"/>
       <c r="AB107" s="33"/>
       <c r="AC107" s="4"/>
-      <c r="AD107" s="75"/>
-      <c r="AE107" s="76"/>
-      <c r="AF107" s="76"/>
-      <c r="AG107" s="76"/>
-      <c r="AH107" s="76"/>
-      <c r="AI107" s="77"/>
+      <c r="AD107" s="44"/>
+      <c r="AE107" s="45"/>
+      <c r="AF107" s="45"/>
+      <c r="AG107" s="45"/>
+      <c r="AH107" s="45"/>
+      <c r="AI107" s="46"/>
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="20"/>
@@ -10311,7 +10370,7 @@
       <c r="BC107" s="20"/>
       <c r="BD107" s="20"/>
     </row>
-    <row r="108" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
       <c r="K108" s="20"/>
@@ -10327,10 +10386,10 @@
       <c r="U108" s="20"/>
       <c r="V108" s="20"/>
       <c r="W108" s="20"/>
-      <c r="X108" s="40">
+      <c r="X108" s="35">
         <v>1.1200000000000001</v>
       </c>
-      <c r="Y108" s="56">
+      <c r="Y108" s="50">
         <v>4</v>
       </c>
       <c r="Z108" s="6" t="s">
@@ -10341,14 +10400,14 @@
       <c r="AC108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD108" s="43" t="s">
+      <c r="AD108" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="AE108" s="44"/>
-      <c r="AF108" s="44"/>
-      <c r="AG108" s="44"/>
-      <c r="AH108" s="44"/>
-      <c r="AI108" s="45"/>
+      <c r="AE108" s="48"/>
+      <c r="AF108" s="48"/>
+      <c r="AG108" s="48"/>
+      <c r="AH108" s="48"/>
+      <c r="AI108" s="49"/>
       <c r="AJ108" s="19"/>
       <c r="AK108" s="19"/>
       <c r="AL108" s="20"/>
@@ -10371,7 +10430,7 @@
       <c r="BC108" s="20"/>
       <c r="BD108" s="20"/>
     </row>
-    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I109" s="20"/>
       <c r="J109" s="20"/>
       <c r="K109" s="20"/>
@@ -10387,8 +10446,8 @@
       <c r="U109" s="20"/>
       <c r="V109" s="20"/>
       <c r="W109" s="20"/>
-      <c r="X109" s="41"/>
-      <c r="Y109" s="57"/>
+      <c r="X109" s="36"/>
+      <c r="Y109" s="51"/>
       <c r="Z109" s="6" t="s">
         <v>79</v>
       </c>
@@ -10427,7 +10486,7 @@
       <c r="BC109" s="20"/>
       <c r="BD109" s="20"/>
     </row>
-    <row r="110" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I110" s="20"/>
       <c r="J110" s="20"/>
       <c r="K110" s="20"/>
@@ -10449,12 +10508,12 @@
       <c r="AA110" s="33"/>
       <c r="AB110" s="33"/>
       <c r="AC110" s="4"/>
-      <c r="AD110" s="75"/>
-      <c r="AE110" s="76"/>
-      <c r="AF110" s="76"/>
-      <c r="AG110" s="76"/>
-      <c r="AH110" s="76"/>
-      <c r="AI110" s="77"/>
+      <c r="AD110" s="44"/>
+      <c r="AE110" s="45"/>
+      <c r="AF110" s="45"/>
+      <c r="AG110" s="45"/>
+      <c r="AH110" s="45"/>
+      <c r="AI110" s="46"/>
       <c r="AJ110" s="19"/>
       <c r="AK110" s="19"/>
       <c r="AL110" s="20"/>
@@ -10477,7 +10536,7 @@
       <c r="BC110" s="20"/>
       <c r="BD110" s="20"/>
     </row>
-    <row r="111" spans="8:56" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:56" x14ac:dyDescent="0.45">
       <c r="I111" s="20"/>
       <c r="J111" s="20"/>
       <c r="K111" s="20"/>
@@ -10493,10 +10552,10 @@
       <c r="U111" s="20"/>
       <c r="V111" s="20"/>
       <c r="W111" s="20"/>
-      <c r="X111" s="40">
+      <c r="X111" s="35">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Y111" s="56">
+      <c r="Y111" s="50">
         <v>4</v>
       </c>
       <c r="Z111" s="6" t="s">
@@ -10507,14 +10566,14 @@
       <c r="AC111" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD111" s="43" t="s">
+      <c r="AD111" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="AE111" s="44"/>
-      <c r="AF111" s="44"/>
-      <c r="AG111" s="44"/>
-      <c r="AH111" s="44"/>
-      <c r="AI111" s="45"/>
+      <c r="AE111" s="48"/>
+      <c r="AF111" s="48"/>
+      <c r="AG111" s="48"/>
+      <c r="AH111" s="48"/>
+      <c r="AI111" s="49"/>
       <c r="AJ111" s="19"/>
       <c r="AK111" s="19"/>
       <c r="AL111" s="20"/>
@@ -10537,7 +10596,7 @@
       <c r="BC111" s="20"/>
       <c r="BD111" s="20"/>
     </row>
-    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I112" s="20"/>
       <c r="J112" s="20"/>
       <c r="K112" s="20"/>
@@ -10553,8 +10612,8 @@
       <c r="U112" s="20"/>
       <c r="V112" s="20"/>
       <c r="W112" s="20"/>
-      <c r="X112" s="41"/>
-      <c r="Y112" s="57"/>
+      <c r="X112" s="36"/>
+      <c r="Y112" s="51"/>
       <c r="Z112" s="6" t="s">
         <v>213</v>
       </c>
@@ -10593,7 +10652,7 @@
       <c r="BC112" s="20"/>
       <c r="BD112" s="20"/>
     </row>
-    <row r="113" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="113" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I113" s="20"/>
       <c r="J113" s="20"/>
       <c r="K113" s="20"/>
@@ -10615,12 +10674,12 @@
       <c r="AA113" s="33"/>
       <c r="AB113" s="33"/>
       <c r="AC113" s="4"/>
-      <c r="AD113" s="75"/>
-      <c r="AE113" s="76"/>
-      <c r="AF113" s="76"/>
-      <c r="AG113" s="76"/>
-      <c r="AH113" s="76"/>
-      <c r="AI113" s="77"/>
+      <c r="AD113" s="44"/>
+      <c r="AE113" s="45"/>
+      <c r="AF113" s="45"/>
+      <c r="AG113" s="45"/>
+      <c r="AH113" s="45"/>
+      <c r="AI113" s="46"/>
       <c r="AJ113" s="19"/>
       <c r="AK113" s="19"/>
       <c r="AL113" s="20"/>
@@ -10643,7 +10702,7 @@
       <c r="BC113" s="20"/>
       <c r="BD113" s="20"/>
     </row>
-    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I114" s="20"/>
       <c r="J114" s="20"/>
       <c r="K114" s="20"/>
@@ -10659,10 +10718,10 @@
       <c r="U114" s="20"/>
       <c r="V114" s="20"/>
       <c r="W114" s="20"/>
-      <c r="X114" s="40">
+      <c r="X114" s="35">
         <v>1.18</v>
       </c>
-      <c r="Y114" s="56">
+      <c r="Y114" s="50">
         <v>4</v>
       </c>
       <c r="Z114" s="6" t="s">
@@ -10703,7 +10762,7 @@
       <c r="BC114" s="20"/>
       <c r="BD114" s="20"/>
     </row>
-    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="9:56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I115" s="20"/>
       <c r="J115" s="20"/>
       <c r="K115" s="20"/>
@@ -10719,8 +10778,8 @@
       <c r="U115" s="20"/>
       <c r="V115" s="20"/>
       <c r="W115" s="20"/>
-      <c r="X115" s="41"/>
-      <c r="Y115" s="57"/>
+      <c r="X115" s="36"/>
+      <c r="Y115" s="51"/>
       <c r="Z115" s="6" t="s">
         <v>80</v>
       </c>
@@ -10759,7 +10818,7 @@
       <c r="BC115" s="20"/>
       <c r="BD115" s="20"/>
     </row>
-    <row r="116" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="116" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I116" s="20"/>
       <c r="J116" s="20"/>
       <c r="K116" s="20"/>
@@ -10781,12 +10840,12 @@
       <c r="AA116" s="33"/>
       <c r="AB116" s="33"/>
       <c r="AC116" s="4"/>
-      <c r="AD116" s="75"/>
-      <c r="AE116" s="76"/>
-      <c r="AF116" s="76"/>
-      <c r="AG116" s="76"/>
-      <c r="AH116" s="76"/>
-      <c r="AI116" s="77"/>
+      <c r="AD116" s="44"/>
+      <c r="AE116" s="45"/>
+      <c r="AF116" s="45"/>
+      <c r="AG116" s="45"/>
+      <c r="AH116" s="45"/>
+      <c r="AI116" s="46"/>
       <c r="AJ116" s="19"/>
       <c r="AK116" s="19"/>
       <c r="AL116" s="20"/>
@@ -10809,7 +10868,7 @@
       <c r="BC116" s="20"/>
       <c r="BD116" s="20"/>
     </row>
-    <row r="117" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="117" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I117" s="20"/>
       <c r="J117" s="20"/>
       <c r="K117" s="20"/>
@@ -10825,10 +10884,10 @@
       <c r="U117" s="20"/>
       <c r="V117" s="20"/>
       <c r="W117" s="20"/>
-      <c r="X117" s="40">
+      <c r="X117" s="35">
         <v>1.21</v>
       </c>
-      <c r="Y117" s="56">
+      <c r="Y117" s="50">
         <v>4</v>
       </c>
       <c r="Z117" s="6" t="s">
@@ -10843,14 +10902,14 @@
       <c r="AC117" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD117" s="43" t="s">
+      <c r="AD117" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="AE117" s="44"/>
-      <c r="AF117" s="44"/>
-      <c r="AG117" s="44"/>
-      <c r="AH117" s="44"/>
-      <c r="AI117" s="45"/>
+      <c r="AE117" s="48"/>
+      <c r="AF117" s="48"/>
+      <c r="AG117" s="48"/>
+      <c r="AH117" s="48"/>
+      <c r="AI117" s="49"/>
       <c r="AJ117" s="8">
         <v>45905</v>
       </c>
@@ -10877,7 +10936,7 @@
       <c r="BC117" s="20"/>
       <c r="BD117" s="20"/>
     </row>
-    <row r="118" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="118" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I118" s="20"/>
       <c r="J118" s="20"/>
       <c r="K118" s="20"/>
@@ -10893,8 +10952,8 @@
       <c r="U118" s="20"/>
       <c r="V118" s="20"/>
       <c r="W118" s="20"/>
-      <c r="X118" s="41"/>
-      <c r="Y118" s="57"/>
+      <c r="X118" s="36"/>
+      <c r="Y118" s="51"/>
       <c r="Z118" s="6" t="s">
         <v>81</v>
       </c>
@@ -10941,7 +11000,7 @@
       <c r="BC118" s="20"/>
       <c r="BD118" s="20"/>
     </row>
-    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I119" s="20"/>
       <c r="J119" s="20"/>
       <c r="K119" s="20"/>
@@ -10963,12 +11022,12 @@
       <c r="AA119" s="33"/>
       <c r="AB119" s="33"/>
       <c r="AC119" s="4"/>
-      <c r="AD119" s="75"/>
-      <c r="AE119" s="76"/>
-      <c r="AF119" s="76"/>
-      <c r="AG119" s="76"/>
-      <c r="AH119" s="76"/>
-      <c r="AI119" s="77"/>
+      <c r="AD119" s="44"/>
+      <c r="AE119" s="45"/>
+      <c r="AF119" s="45"/>
+      <c r="AG119" s="45"/>
+      <c r="AH119" s="45"/>
+      <c r="AI119" s="46"/>
       <c r="AJ119" s="19"/>
       <c r="AK119" s="19"/>
       <c r="AL119" s="20"/>
@@ -10991,7 +11050,7 @@
       <c r="BC119" s="20"/>
       <c r="BD119" s="20"/>
     </row>
-    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I120" s="20"/>
       <c r="J120" s="20"/>
       <c r="K120" s="20"/>
@@ -11007,10 +11066,10 @@
       <c r="U120" s="20"/>
       <c r="V120" s="20"/>
       <c r="W120" s="20"/>
-      <c r="X120" s="40">
+      <c r="X120" s="35">
         <v>5.2</v>
       </c>
-      <c r="Y120" s="54">
+      <c r="Y120" s="56">
         <v>5</v>
       </c>
       <c r="Z120" s="6" t="s">
@@ -11051,7 +11110,7 @@
       <c r="BC120" s="20"/>
       <c r="BD120" s="20"/>
     </row>
-    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I121" s="20"/>
       <c r="J121" s="20"/>
       <c r="K121" s="20"/>
@@ -11067,8 +11126,8 @@
       <c r="U121" s="20"/>
       <c r="V121" s="20"/>
       <c r="W121" s="20"/>
-      <c r="X121" s="41"/>
-      <c r="Y121" s="55"/>
+      <c r="X121" s="36"/>
+      <c r="Y121" s="57"/>
       <c r="Z121" s="6" t="s">
         <v>82</v>
       </c>
@@ -11077,14 +11136,14 @@
       <c r="AC121" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD121" s="43" t="s">
+      <c r="AD121" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="AE121" s="44"/>
-      <c r="AF121" s="44"/>
-      <c r="AG121" s="44"/>
-      <c r="AH121" s="44"/>
-      <c r="AI121" s="45"/>
+      <c r="AE121" s="48"/>
+      <c r="AF121" s="48"/>
+      <c r="AG121" s="48"/>
+      <c r="AH121" s="48"/>
+      <c r="AI121" s="49"/>
       <c r="AJ121" s="19"/>
       <c r="AK121" s="19"/>
       <c r="AL121" s="20"/>
@@ -11107,7 +11166,7 @@
       <c r="BC121" s="20"/>
       <c r="BD121" s="20"/>
     </row>
-    <row r="122" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="122" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I122" s="20"/>
       <c r="J122" s="20"/>
       <c r="K122" s="20"/>
@@ -11129,12 +11188,12 @@
       <c r="AA122" s="33"/>
       <c r="AB122" s="33"/>
       <c r="AC122" s="4"/>
-      <c r="AD122" s="75"/>
-      <c r="AE122" s="76"/>
-      <c r="AF122" s="76"/>
-      <c r="AG122" s="76"/>
-      <c r="AH122" s="76"/>
-      <c r="AI122" s="77"/>
+      <c r="AD122" s="44"/>
+      <c r="AE122" s="45"/>
+      <c r="AF122" s="45"/>
+      <c r="AG122" s="45"/>
+      <c r="AH122" s="45"/>
+      <c r="AI122" s="46"/>
       <c r="AJ122" s="19"/>
       <c r="AK122" s="19"/>
       <c r="AL122" s="20"/>
@@ -11157,7 +11216,7 @@
       <c r="BC122" s="20"/>
       <c r="BD122" s="20"/>
     </row>
-    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I123" s="20"/>
       <c r="J123" s="20"/>
       <c r="K123" s="20"/>
@@ -11173,10 +11232,10 @@
       <c r="U123" s="20"/>
       <c r="V123" s="20"/>
       <c r="W123" s="20"/>
-      <c r="X123" s="40">
+      <c r="X123" s="35">
         <v>5.3</v>
       </c>
-      <c r="Y123" s="46">
+      <c r="Y123" s="42">
         <v>3</v>
       </c>
       <c r="Z123" s="6" t="s">
@@ -11225,7 +11284,7 @@
       <c r="BC123" s="20"/>
       <c r="BD123" s="20"/>
     </row>
-    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I124" s="20"/>
       <c r="J124" s="20"/>
       <c r="K124" s="20"/>
@@ -11241,8 +11300,8 @@
       <c r="U124" s="20"/>
       <c r="V124" s="20"/>
       <c r="W124" s="20"/>
-      <c r="X124" s="41"/>
-      <c r="Y124" s="47"/>
+      <c r="X124" s="36"/>
+      <c r="Y124" s="43"/>
       <c r="Z124" s="6" t="s">
         <v>214</v>
       </c>
@@ -11289,7 +11348,7 @@
       <c r="BC124" s="20"/>
       <c r="BD124" s="20"/>
     </row>
-    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="9:56" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I125" s="20"/>
       <c r="J125" s="20"/>
       <c r="K125" s="20"/>
@@ -11311,12 +11370,12 @@
       <c r="AA125" s="33"/>
       <c r="AB125" s="33"/>
       <c r="AC125" s="4"/>
-      <c r="AD125" s="75"/>
-      <c r="AE125" s="76"/>
-      <c r="AF125" s="76"/>
-      <c r="AG125" s="76"/>
-      <c r="AH125" s="76"/>
-      <c r="AI125" s="77"/>
+      <c r="AD125" s="44"/>
+      <c r="AE125" s="45"/>
+      <c r="AF125" s="45"/>
+      <c r="AG125" s="45"/>
+      <c r="AH125" s="45"/>
+      <c r="AI125" s="46"/>
       <c r="AJ125" s="19"/>
       <c r="AK125" s="19"/>
       <c r="AL125" s="20"/>
@@ -11339,7 +11398,7 @@
       <c r="BC125" s="20"/>
       <c r="BD125" s="20"/>
     </row>
-    <row r="126" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="126" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I126" s="20"/>
       <c r="J126" s="20"/>
       <c r="K126" s="20"/>
@@ -11358,7 +11417,7 @@
       <c r="X126" s="9">
         <v>5.4</v>
       </c>
-      <c r="Y126" s="46">
+      <c r="Y126" s="42">
         <v>3</v>
       </c>
       <c r="Z126" s="6" t="s">
@@ -11399,7 +11458,7 @@
       <c r="BC126" s="20"/>
       <c r="BD126" s="20"/>
     </row>
-    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
       <c r="K127" s="20"/>
@@ -11416,17 +11475,17 @@
       <c r="V127" s="20"/>
       <c r="W127" s="20"/>
       <c r="X127" s="6"/>
-      <c r="Y127" s="47"/>
+      <c r="Y127" s="43"/>
       <c r="Z127" s="6"/>
       <c r="AA127" s="33"/>
       <c r="AB127" s="33"/>
       <c r="AC127" s="4"/>
-      <c r="AD127" s="75"/>
-      <c r="AE127" s="76"/>
-      <c r="AF127" s="76"/>
-      <c r="AG127" s="76"/>
-      <c r="AH127" s="76"/>
-      <c r="AI127" s="77"/>
+      <c r="AD127" s="44"/>
+      <c r="AE127" s="45"/>
+      <c r="AF127" s="45"/>
+      <c r="AG127" s="45"/>
+      <c r="AH127" s="45"/>
+      <c r="AI127" s="46"/>
       <c r="AJ127" s="19"/>
       <c r="AK127" s="19"/>
       <c r="AL127" s="20"/>
@@ -11449,7 +11508,7 @@
       <c r="BC127" s="20"/>
       <c r="BD127" s="20"/>
     </row>
-    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="9:56" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
       <c r="K128" s="20"/>
@@ -11465,10 +11524,10 @@
       <c r="U128" s="20"/>
       <c r="V128" s="20"/>
       <c r="W128" s="20"/>
-      <c r="X128" s="40">
+      <c r="X128" s="35">
         <v>1.2</v>
       </c>
-      <c r="Y128" s="52">
+      <c r="Y128" s="40">
         <v>1</v>
       </c>
       <c r="Z128" s="19" t="s">
@@ -11509,7 +11568,7 @@
       <c r="BC128" s="20"/>
       <c r="BD128" s="20"/>
     </row>
-    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
       <c r="K129" s="20"/>
@@ -11525,8 +11584,8 @@
       <c r="U129" s="20"/>
       <c r="V129" s="20"/>
       <c r="W129" s="20"/>
-      <c r="X129" s="41"/>
-      <c r="Y129" s="53"/>
+      <c r="X129" s="36"/>
+      <c r="Y129" s="41"/>
       <c r="Z129" s="19" t="s">
         <v>85</v>
       </c>
@@ -11565,7 +11624,7 @@
       <c r="BC129" s="20"/>
       <c r="BD129" s="20"/>
     </row>
-    <row r="130" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
       <c r="K130" s="20"/>
@@ -11587,12 +11646,12 @@
       <c r="AA130" s="33"/>
       <c r="AB130" s="33"/>
       <c r="AC130" s="4"/>
-      <c r="AD130" s="75"/>
-      <c r="AE130" s="76"/>
-      <c r="AF130" s="76"/>
-      <c r="AG130" s="76"/>
-      <c r="AH130" s="76"/>
-      <c r="AI130" s="77"/>
+      <c r="AD130" s="44"/>
+      <c r="AE130" s="45"/>
+      <c r="AF130" s="45"/>
+      <c r="AG130" s="45"/>
+      <c r="AH130" s="45"/>
+      <c r="AI130" s="46"/>
       <c r="AJ130" s="19"/>
       <c r="AK130" s="19"/>
       <c r="AL130" s="20"/>
@@ -11615,7 +11674,7 @@
       <c r="BC130" s="20"/>
       <c r="BD130" s="20"/>
     </row>
-    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
       <c r="K131" s="20"/>
@@ -11631,10 +11690,10 @@
       <c r="U131" s="20"/>
       <c r="V131" s="20"/>
       <c r="W131" s="20"/>
-      <c r="X131" s="40" t="s">
+      <c r="X131" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="Y131" s="46">
+      <c r="Y131" s="42">
         <v>3</v>
       </c>
       <c r="Z131" s="19" t="s">
@@ -11675,7 +11734,7 @@
       <c r="BC131" s="20"/>
       <c r="BD131" s="20"/>
     </row>
-    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
@@ -11691,8 +11750,8 @@
       <c r="U132" s="20"/>
       <c r="V132" s="20"/>
       <c r="W132" s="20"/>
-      <c r="X132" s="41"/>
-      <c r="Y132" s="47"/>
+      <c r="X132" s="36"/>
+      <c r="Y132" s="43"/>
       <c r="Z132" s="16" t="s">
         <v>168</v>
       </c>
@@ -11731,7 +11790,7 @@
       <c r="BC132" s="20"/>
       <c r="BD132" s="20"/>
     </row>
-    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
       <c r="K133" s="20"/>
@@ -11753,12 +11812,12 @@
       <c r="AA133" s="33"/>
       <c r="AB133" s="33"/>
       <c r="AC133" s="11"/>
-      <c r="AD133" s="75"/>
-      <c r="AE133" s="76"/>
-      <c r="AF133" s="76"/>
-      <c r="AG133" s="76"/>
-      <c r="AH133" s="76"/>
-      <c r="AI133" s="77"/>
+      <c r="AD133" s="44"/>
+      <c r="AE133" s="45"/>
+      <c r="AF133" s="45"/>
+      <c r="AG133" s="45"/>
+      <c r="AH133" s="45"/>
+      <c r="AI133" s="46"/>
       <c r="AJ133" s="19"/>
       <c r="AK133" s="19"/>
       <c r="AL133" s="20"/>
@@ -11781,7 +11840,7 @@
       <c r="BC133" s="20"/>
       <c r="BD133" s="20"/>
     </row>
-    <row r="134" spans="9:56" x14ac:dyDescent="0.25">
+    <row r="134" spans="9:56" x14ac:dyDescent="0.45">
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
       <c r="K134" s="20"/>
@@ -11811,14 +11870,14 @@
       <c r="AC134" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD134" s="42" t="s">
+      <c r="AD134" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="AE134" s="42"/>
-      <c r="AF134" s="42"/>
-      <c r="AG134" s="42"/>
-      <c r="AH134" s="42"/>
-      <c r="AI134" s="42"/>
+      <c r="AE134" s="52"/>
+      <c r="AF134" s="52"/>
+      <c r="AG134" s="52"/>
+      <c r="AH134" s="52"/>
+      <c r="AI134" s="52"/>
       <c r="AJ134" s="19"/>
       <c r="AK134" s="19"/>
       <c r="AL134" s="20"/>
@@ -11841,60 +11900,590 @@
       <c r="BC134" s="20"/>
       <c r="BD134" s="20"/>
     </row>
-    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G153" s="89"/>
-      <c r="H153" s="89"/>
-    </row>
-    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="136" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="137" spans="9:56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="139" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="140" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="141" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="143" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="144" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="145" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="147" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="148" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="149" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="151" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="152" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="153" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G153" s="67"/>
+      <c r="H153" s="67"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="156" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="157" spans="7:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" spans="7:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="159" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="160" spans="7:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="164" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="165" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="166" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="167" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="168" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="170" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="171" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="172" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="173" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="174" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="176" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="177" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="178" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="183" spans="23:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="192" spans="23:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="W192" s="12"/>
     </row>
-    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="25.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" ht="22.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="228" ht="21.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="230" ht="22.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <autoFilter ref="AA3:AA134" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ8:AJ46">
     <sortCondition descending="1" ref="AJ8:AJ46"/>
   </sortState>
   <mergeCells count="554">
+    <mergeCell ref="BC90:BD90"/>
+    <mergeCell ref="BC81:BD81"/>
+    <mergeCell ref="BC82:BD82"/>
+    <mergeCell ref="BC83:BD83"/>
+    <mergeCell ref="BC84:BD84"/>
+    <mergeCell ref="BC85:BD85"/>
+    <mergeCell ref="BC86:BD86"/>
+    <mergeCell ref="BC87:BD87"/>
+    <mergeCell ref="BC88:BD88"/>
+    <mergeCell ref="BC89:BD89"/>
+    <mergeCell ref="BC72:BD72"/>
+    <mergeCell ref="BC73:BD73"/>
+    <mergeCell ref="BC74:BD74"/>
+    <mergeCell ref="BC75:BD75"/>
+    <mergeCell ref="BC76:BD76"/>
+    <mergeCell ref="BC77:BD77"/>
+    <mergeCell ref="BC78:BD78"/>
+    <mergeCell ref="BC79:BD79"/>
+    <mergeCell ref="BC80:BD80"/>
+    <mergeCell ref="BC63:BD63"/>
+    <mergeCell ref="BC64:BD64"/>
+    <mergeCell ref="BC65:BD65"/>
+    <mergeCell ref="BC66:BD66"/>
+    <mergeCell ref="BC67:BD67"/>
+    <mergeCell ref="BC68:BD68"/>
+    <mergeCell ref="BC69:BD69"/>
+    <mergeCell ref="BC70:BD70"/>
+    <mergeCell ref="BC71:BD71"/>
+    <mergeCell ref="BC54:BD54"/>
+    <mergeCell ref="BC55:BD55"/>
+    <mergeCell ref="BC56:BD56"/>
+    <mergeCell ref="BC57:BD57"/>
+    <mergeCell ref="BC58:BD58"/>
+    <mergeCell ref="BC59:BD59"/>
+    <mergeCell ref="BC60:BD60"/>
+    <mergeCell ref="BC61:BD61"/>
+    <mergeCell ref="BC62:BD62"/>
+    <mergeCell ref="BC45:BD45"/>
+    <mergeCell ref="BC46:BD46"/>
+    <mergeCell ref="BC47:BD47"/>
+    <mergeCell ref="BC48:BD48"/>
+    <mergeCell ref="BC49:BD49"/>
+    <mergeCell ref="BC50:BD50"/>
+    <mergeCell ref="BC51:BD51"/>
+    <mergeCell ref="BC52:BD52"/>
+    <mergeCell ref="BC53:BD53"/>
+    <mergeCell ref="BC36:BD36"/>
+    <mergeCell ref="BC37:BD37"/>
+    <mergeCell ref="BC38:BD38"/>
+    <mergeCell ref="BC39:BD39"/>
+    <mergeCell ref="BC40:BD40"/>
+    <mergeCell ref="BC41:BD41"/>
+    <mergeCell ref="BC42:BD42"/>
+    <mergeCell ref="BC43:BD43"/>
+    <mergeCell ref="BC44:BD44"/>
+    <mergeCell ref="AS85:AX85"/>
+    <mergeCell ref="AN86:AN87"/>
+    <mergeCell ref="AS86:AX86"/>
+    <mergeCell ref="AS87:AX87"/>
+    <mergeCell ref="AN88:AN89"/>
+    <mergeCell ref="AS88:AX88"/>
+    <mergeCell ref="AS89:AX89"/>
+    <mergeCell ref="AS90:AX90"/>
+    <mergeCell ref="BC19:BD19"/>
+    <mergeCell ref="BC21:BD21"/>
+    <mergeCell ref="BC22:BD22"/>
+    <mergeCell ref="BC23:BD23"/>
+    <mergeCell ref="BC24:BD24"/>
+    <mergeCell ref="BC25:BD25"/>
+    <mergeCell ref="BC26:BD26"/>
+    <mergeCell ref="BC27:BD27"/>
+    <mergeCell ref="BC28:BD28"/>
+    <mergeCell ref="BC29:BD29"/>
+    <mergeCell ref="BC30:BD30"/>
+    <mergeCell ref="BC31:BD31"/>
+    <mergeCell ref="BC32:BD32"/>
+    <mergeCell ref="BC33:BD33"/>
+    <mergeCell ref="BC34:BD34"/>
+    <mergeCell ref="BC35:BD35"/>
+    <mergeCell ref="AN79:AN80"/>
+    <mergeCell ref="AS79:AX79"/>
+    <mergeCell ref="AS80:AX80"/>
+    <mergeCell ref="AN81:AN82"/>
+    <mergeCell ref="AS81:AX81"/>
+    <mergeCell ref="AS82:AX82"/>
+    <mergeCell ref="AN83:AN84"/>
+    <mergeCell ref="AS83:AX83"/>
+    <mergeCell ref="AS84:AX84"/>
+    <mergeCell ref="AN73:AN74"/>
+    <mergeCell ref="AS73:AX73"/>
+    <mergeCell ref="AS74:AX74"/>
+    <mergeCell ref="AN75:AN76"/>
+    <mergeCell ref="AS75:AX75"/>
+    <mergeCell ref="AS76:AX76"/>
+    <mergeCell ref="AN77:AN78"/>
+    <mergeCell ref="AS77:AX77"/>
+    <mergeCell ref="AS78:AX78"/>
+    <mergeCell ref="AN65:AN66"/>
+    <mergeCell ref="AS65:AX65"/>
+    <mergeCell ref="AS66:AX66"/>
+    <mergeCell ref="AS67:AX67"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="AS68:AX68"/>
+    <mergeCell ref="AS69:AX69"/>
+    <mergeCell ref="AS70:AX70"/>
+    <mergeCell ref="AN71:AN72"/>
+    <mergeCell ref="AS71:AX71"/>
+    <mergeCell ref="AS72:AX72"/>
+    <mergeCell ref="AN59:AN60"/>
+    <mergeCell ref="AS59:AX59"/>
+    <mergeCell ref="AS60:AX60"/>
+    <mergeCell ref="AN61:AN62"/>
+    <mergeCell ref="AS61:AX61"/>
+    <mergeCell ref="AS62:AX62"/>
+    <mergeCell ref="AN63:AN64"/>
+    <mergeCell ref="AS63:AX63"/>
+    <mergeCell ref="AS64:AX64"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AS52:AX52"/>
+    <mergeCell ref="AS53:AX53"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="AS54:AX54"/>
+    <mergeCell ref="AS55:AX55"/>
+    <mergeCell ref="AS56:AX56"/>
+    <mergeCell ref="AN57:AN58"/>
+    <mergeCell ref="AS57:AX57"/>
+    <mergeCell ref="AS58:AX58"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AS46:AX46"/>
+    <mergeCell ref="AS47:AX47"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="AS48:AX48"/>
+    <mergeCell ref="AS49:AX49"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="AS50:AX50"/>
+    <mergeCell ref="AS51:AX51"/>
+    <mergeCell ref="AS39:AX39"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="AS40:AX40"/>
+    <mergeCell ref="AS41:AX41"/>
+    <mergeCell ref="AS42:AX42"/>
+    <mergeCell ref="AN43:AN44"/>
+    <mergeCell ref="AS43:AX43"/>
+    <mergeCell ref="AS44:AX44"/>
+    <mergeCell ref="AS45:AX45"/>
+    <mergeCell ref="AS32:AX32"/>
+    <mergeCell ref="AN33:AN34"/>
+    <mergeCell ref="AS33:AX33"/>
+    <mergeCell ref="AS34:AX34"/>
+    <mergeCell ref="AN35:AN36"/>
+    <mergeCell ref="AS35:AX35"/>
+    <mergeCell ref="AS36:AX36"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AS37:AX37"/>
+    <mergeCell ref="AS38:AX38"/>
+    <mergeCell ref="Y126:Y127"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AS19:AX19"/>
+    <mergeCell ref="AN21:AN23"/>
+    <mergeCell ref="AS21:AX21"/>
+    <mergeCell ref="AS22:AX22"/>
+    <mergeCell ref="AS23:AX23"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="AS24:AX24"/>
+    <mergeCell ref="AS25:AX25"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="AS26:AX26"/>
+    <mergeCell ref="AS27:AX27"/>
+    <mergeCell ref="AN28:AN30"/>
+    <mergeCell ref="AS28:AX28"/>
+    <mergeCell ref="AS29:AX29"/>
+    <mergeCell ref="AS30:AX30"/>
+    <mergeCell ref="AN31:AN32"/>
+    <mergeCell ref="AS31:AX31"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AD23:AI23"/>
+    <mergeCell ref="X72:X73"/>
+    <mergeCell ref="Y72:Y73"/>
+    <mergeCell ref="X123:X124"/>
+    <mergeCell ref="Y123:Y124"/>
+    <mergeCell ref="X120:X121"/>
+    <mergeCell ref="Y120:Y121"/>
+    <mergeCell ref="X117:X118"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="X114:X115"/>
+    <mergeCell ref="Y114:Y115"/>
+    <mergeCell ref="X111:X112"/>
+    <mergeCell ref="Y111:Y112"/>
+    <mergeCell ref="X95:X96"/>
+    <mergeCell ref="Y95:Y96"/>
+    <mergeCell ref="X92:X93"/>
+    <mergeCell ref="Y92:Y93"/>
+    <mergeCell ref="X89:X90"/>
+    <mergeCell ref="Y89:Y90"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="X100:X101"/>
+    <mergeCell ref="Y100:Y101"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I79:I80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="X42:X43"/>
+    <mergeCell ref="Y42:Y43"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Y33"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="N83:S83"/>
+    <mergeCell ref="N84:S84"/>
+    <mergeCell ref="N85:S85"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="N77:S77"/>
+    <mergeCell ref="N78:S78"/>
+    <mergeCell ref="N79:S79"/>
+    <mergeCell ref="N80:S80"/>
+    <mergeCell ref="N81:S81"/>
+    <mergeCell ref="N82:S82"/>
+    <mergeCell ref="N71:S71"/>
+    <mergeCell ref="N72:S72"/>
+    <mergeCell ref="N73:S73"/>
+    <mergeCell ref="N74:S74"/>
+    <mergeCell ref="N75:S75"/>
+    <mergeCell ref="N76:S76"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="N67:S67"/>
+    <mergeCell ref="N68:S68"/>
+    <mergeCell ref="N69:S69"/>
+    <mergeCell ref="N70:S70"/>
+    <mergeCell ref="N61:S61"/>
+    <mergeCell ref="N62:S62"/>
+    <mergeCell ref="N63:S63"/>
+    <mergeCell ref="N64:S64"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="N66:S66"/>
+    <mergeCell ref="N57:S57"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="N59:S59"/>
+    <mergeCell ref="N60:S60"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N53:S53"/>
+    <mergeCell ref="N54:S54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="N49:S49"/>
+    <mergeCell ref="N50:S50"/>
+    <mergeCell ref="N51:S51"/>
+    <mergeCell ref="N52:S52"/>
+    <mergeCell ref="N44:S44"/>
+    <mergeCell ref="N45:S45"/>
+    <mergeCell ref="N46:S46"/>
+    <mergeCell ref="N47:S47"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="N56:S56"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N39:S39"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N32:S32"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="N34:S34"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="N48:S48"/>
+    <mergeCell ref="N40:S40"/>
+    <mergeCell ref="N41:S41"/>
+    <mergeCell ref="N42:S42"/>
+    <mergeCell ref="N43:S43"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:S36"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="N25:S25"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:S27"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:S3"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S29"/>
+    <mergeCell ref="N30:S30"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="X14:X16"/>
+    <mergeCell ref="Y14:Y16"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="AD4:AI4"/>
+    <mergeCell ref="AD5:AI5"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AX3"/>
+    <mergeCell ref="AD2:AI3"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="AN4:AN6"/>
+    <mergeCell ref="AS4:AX4"/>
+    <mergeCell ref="AS5:AX5"/>
+    <mergeCell ref="AS6:AX6"/>
+    <mergeCell ref="AS7:AX7"/>
+    <mergeCell ref="AS8:AX8"/>
+    <mergeCell ref="AS9:AX9"/>
+    <mergeCell ref="AS10:AX10"/>
+    <mergeCell ref="AN11:AN13"/>
+    <mergeCell ref="AS11:AX11"/>
+    <mergeCell ref="AS12:AX12"/>
+    <mergeCell ref="AS13:AX13"/>
+    <mergeCell ref="AN14:AN16"/>
+    <mergeCell ref="AS14:AX14"/>
+    <mergeCell ref="AS15:AX15"/>
+    <mergeCell ref="AS16:AX16"/>
+    <mergeCell ref="AS17:AX17"/>
+    <mergeCell ref="AS18:AX18"/>
+    <mergeCell ref="AS20:AX20"/>
+    <mergeCell ref="X18:X20"/>
+    <mergeCell ref="Y18:Y20"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="BC4:BD4"/>
+    <mergeCell ref="BC5:BD5"/>
+    <mergeCell ref="BC6:BD6"/>
+    <mergeCell ref="BC7:BD7"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BC9:BD9"/>
+    <mergeCell ref="BC10:BD10"/>
+    <mergeCell ref="BC11:BD11"/>
+    <mergeCell ref="BC12:BD12"/>
+    <mergeCell ref="BC13:BD13"/>
+    <mergeCell ref="BC14:BD14"/>
+    <mergeCell ref="BC15:BD15"/>
+    <mergeCell ref="BC16:BD16"/>
+    <mergeCell ref="BC17:BD17"/>
+    <mergeCell ref="BC18:BD18"/>
+    <mergeCell ref="BC20:BD20"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AD24:AI24"/>
+    <mergeCell ref="AD25:AI25"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="X28:X30"/>
+    <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="AD41:AI41"/>
+    <mergeCell ref="AD42:AI42"/>
+    <mergeCell ref="AD43:AI43"/>
+    <mergeCell ref="AD44:AI44"/>
+    <mergeCell ref="AD45:AI45"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="X38:X40"/>
+    <mergeCell ref="Y38:Y40"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="AD50:AI50"/>
+    <mergeCell ref="AD51:AI51"/>
+    <mergeCell ref="AD52:AI52"/>
+    <mergeCell ref="AD53:AI53"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="Y48:Y49"/>
+    <mergeCell ref="AD62:AI62"/>
+    <mergeCell ref="AD63:AI63"/>
+    <mergeCell ref="AD64:AI64"/>
+    <mergeCell ref="X69:X70"/>
+    <mergeCell ref="Y69:Y70"/>
+    <mergeCell ref="X66:X67"/>
+    <mergeCell ref="Y66:Y67"/>
+    <mergeCell ref="AD54:AI54"/>
+    <mergeCell ref="AD46:AI46"/>
+    <mergeCell ref="AD47:AI47"/>
+    <mergeCell ref="AD48:AI48"/>
+    <mergeCell ref="AD49:AI49"/>
+    <mergeCell ref="AD58:AI58"/>
+    <mergeCell ref="AD59:AI59"/>
+    <mergeCell ref="AD60:AI60"/>
+    <mergeCell ref="AD61:AI61"/>
+    <mergeCell ref="AD55:AI55"/>
+    <mergeCell ref="AD56:AI56"/>
+    <mergeCell ref="AD57:AI57"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="Y56:Y57"/>
+    <mergeCell ref="X61:X62"/>
+    <mergeCell ref="Y61:Y62"/>
+    <mergeCell ref="AD70:AI70"/>
+    <mergeCell ref="AD71:AI71"/>
+    <mergeCell ref="AD72:AI72"/>
+    <mergeCell ref="AD73:AI73"/>
+    <mergeCell ref="AD65:AI65"/>
+    <mergeCell ref="AD66:AI66"/>
+    <mergeCell ref="AD67:AI67"/>
+    <mergeCell ref="AD68:AI68"/>
+    <mergeCell ref="AD69:AI69"/>
+    <mergeCell ref="AD79:AI79"/>
+    <mergeCell ref="AD80:AI80"/>
+    <mergeCell ref="AD81:AI81"/>
+    <mergeCell ref="X86:X87"/>
+    <mergeCell ref="Y86:Y87"/>
+    <mergeCell ref="X83:X84"/>
+    <mergeCell ref="Y83:Y84"/>
+    <mergeCell ref="AD74:AI74"/>
+    <mergeCell ref="AD75:AI75"/>
+    <mergeCell ref="AD76:AI76"/>
+    <mergeCell ref="AD77:AI77"/>
+    <mergeCell ref="AD78:AI78"/>
+    <mergeCell ref="X78:X79"/>
+    <mergeCell ref="Y78:Y79"/>
+    <mergeCell ref="X75:X76"/>
+    <mergeCell ref="Y75:Y76"/>
+    <mergeCell ref="AD87:AI87"/>
+    <mergeCell ref="AD90:AI90"/>
+    <mergeCell ref="AD82:AI82"/>
+    <mergeCell ref="AD83:AI83"/>
+    <mergeCell ref="AD84:AI84"/>
+    <mergeCell ref="AD85:AI85"/>
+    <mergeCell ref="AD86:AI86"/>
+    <mergeCell ref="AD108:AI108"/>
+    <mergeCell ref="AD99:AI99"/>
+    <mergeCell ref="AD100:AI100"/>
+    <mergeCell ref="AD101:AI101"/>
+    <mergeCell ref="AD91:AI91"/>
+    <mergeCell ref="AD92:AI92"/>
+    <mergeCell ref="AD93:AI93"/>
+    <mergeCell ref="AD94:AI94"/>
+    <mergeCell ref="AD95:AI95"/>
+    <mergeCell ref="AD102:AI102"/>
+    <mergeCell ref="AD103:AI103"/>
+    <mergeCell ref="AD96:AI96"/>
+    <mergeCell ref="AD97:AI97"/>
+    <mergeCell ref="AD98:AI98"/>
+    <mergeCell ref="AD107:AI107"/>
+    <mergeCell ref="AD134:AI134"/>
+    <mergeCell ref="AD130:AI130"/>
+    <mergeCell ref="AD131:AI131"/>
+    <mergeCell ref="AD128:AI128"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="AD133:AI133"/>
+    <mergeCell ref="AD125:AI125"/>
+    <mergeCell ref="AD126:AI126"/>
+    <mergeCell ref="AD127:AI127"/>
+    <mergeCell ref="AD121:AI121"/>
+    <mergeCell ref="AD122:AI122"/>
+    <mergeCell ref="AD123:AI123"/>
+    <mergeCell ref="AD124:AI124"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="AD112:AI112"/>
+    <mergeCell ref="AD113:AI113"/>
+    <mergeCell ref="AD114:AI114"/>
     <mergeCell ref="I86:I87"/>
     <mergeCell ref="X131:X132"/>
     <mergeCell ref="X128:X129"/>
@@ -11919,536 +12508,6 @@
     <mergeCell ref="X105:X106"/>
     <mergeCell ref="AD88:AI88"/>
     <mergeCell ref="AD89:AI89"/>
-    <mergeCell ref="AD134:AI134"/>
-    <mergeCell ref="AD130:AI130"/>
-    <mergeCell ref="AD131:AI131"/>
-    <mergeCell ref="AD128:AI128"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="AD133:AI133"/>
-    <mergeCell ref="AD125:AI125"/>
-    <mergeCell ref="AD126:AI126"/>
-    <mergeCell ref="AD127:AI127"/>
-    <mergeCell ref="AD121:AI121"/>
-    <mergeCell ref="AD122:AI122"/>
-    <mergeCell ref="AD123:AI123"/>
-    <mergeCell ref="AD124:AI124"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="AD112:AI112"/>
-    <mergeCell ref="AD113:AI113"/>
-    <mergeCell ref="AD114:AI114"/>
-    <mergeCell ref="AD90:AI90"/>
-    <mergeCell ref="AD82:AI82"/>
-    <mergeCell ref="AD83:AI83"/>
-    <mergeCell ref="AD84:AI84"/>
-    <mergeCell ref="AD85:AI85"/>
-    <mergeCell ref="AD86:AI86"/>
-    <mergeCell ref="AD108:AI108"/>
-    <mergeCell ref="AD99:AI99"/>
-    <mergeCell ref="AD100:AI100"/>
-    <mergeCell ref="AD101:AI101"/>
-    <mergeCell ref="AD91:AI91"/>
-    <mergeCell ref="AD92:AI92"/>
-    <mergeCell ref="AD93:AI93"/>
-    <mergeCell ref="AD94:AI94"/>
-    <mergeCell ref="AD95:AI95"/>
-    <mergeCell ref="AD102:AI102"/>
-    <mergeCell ref="AD103:AI103"/>
-    <mergeCell ref="AD96:AI96"/>
-    <mergeCell ref="AD97:AI97"/>
-    <mergeCell ref="AD98:AI98"/>
-    <mergeCell ref="AD107:AI107"/>
-    <mergeCell ref="AD80:AI80"/>
-    <mergeCell ref="AD81:AI81"/>
-    <mergeCell ref="X86:X87"/>
-    <mergeCell ref="Y86:Y87"/>
-    <mergeCell ref="X83:X84"/>
-    <mergeCell ref="Y83:Y84"/>
-    <mergeCell ref="AD74:AI74"/>
-    <mergeCell ref="AD75:AI75"/>
-    <mergeCell ref="AD76:AI76"/>
-    <mergeCell ref="AD77:AI77"/>
-    <mergeCell ref="AD78:AI78"/>
-    <mergeCell ref="X78:X79"/>
-    <mergeCell ref="Y78:Y79"/>
-    <mergeCell ref="X75:X76"/>
-    <mergeCell ref="Y75:Y76"/>
-    <mergeCell ref="AD87:AI87"/>
-    <mergeCell ref="AD71:AI71"/>
-    <mergeCell ref="AD72:AI72"/>
-    <mergeCell ref="AD73:AI73"/>
-    <mergeCell ref="AD65:AI65"/>
-    <mergeCell ref="AD66:AI66"/>
-    <mergeCell ref="AD67:AI67"/>
-    <mergeCell ref="AD68:AI68"/>
-    <mergeCell ref="AD69:AI69"/>
-    <mergeCell ref="AD79:AI79"/>
-    <mergeCell ref="AD62:AI62"/>
-    <mergeCell ref="AD63:AI63"/>
-    <mergeCell ref="AD64:AI64"/>
-    <mergeCell ref="X69:X70"/>
-    <mergeCell ref="Y69:Y70"/>
-    <mergeCell ref="X66:X67"/>
-    <mergeCell ref="Y66:Y67"/>
-    <mergeCell ref="AD54:AI54"/>
-    <mergeCell ref="AD46:AI46"/>
-    <mergeCell ref="AD47:AI47"/>
-    <mergeCell ref="AD48:AI48"/>
-    <mergeCell ref="AD49:AI49"/>
-    <mergeCell ref="AD58:AI58"/>
-    <mergeCell ref="AD59:AI59"/>
-    <mergeCell ref="AD60:AI60"/>
-    <mergeCell ref="AD61:AI61"/>
-    <mergeCell ref="AD55:AI55"/>
-    <mergeCell ref="AD56:AI56"/>
-    <mergeCell ref="AD57:AI57"/>
-    <mergeCell ref="X56:X57"/>
-    <mergeCell ref="Y56:Y57"/>
-    <mergeCell ref="X61:X62"/>
-    <mergeCell ref="Y61:Y62"/>
-    <mergeCell ref="AD70:AI70"/>
-    <mergeCell ref="X38:X40"/>
-    <mergeCell ref="Y38:Y40"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="AD50:AI50"/>
-    <mergeCell ref="AD51:AI51"/>
-    <mergeCell ref="AD52:AI52"/>
-    <mergeCell ref="AD53:AI53"/>
-    <mergeCell ref="X51:X52"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="AD41:AI41"/>
-    <mergeCell ref="AD42:AI42"/>
-    <mergeCell ref="AD43:AI43"/>
-    <mergeCell ref="AD44:AI44"/>
-    <mergeCell ref="AD45:AI45"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="AD24:AI24"/>
-    <mergeCell ref="AD25:AI25"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="X28:X30"/>
-    <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="BC13:BD13"/>
-    <mergeCell ref="BC14:BD14"/>
-    <mergeCell ref="BC15:BD15"/>
-    <mergeCell ref="BC16:BD16"/>
-    <mergeCell ref="BC17:BD17"/>
-    <mergeCell ref="BC18:BD18"/>
-    <mergeCell ref="BC20:BD20"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="BC4:BD4"/>
-    <mergeCell ref="BC5:BD5"/>
-    <mergeCell ref="BC6:BD6"/>
-    <mergeCell ref="BC7:BD7"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BC9:BD9"/>
-    <mergeCell ref="BC10:BD10"/>
-    <mergeCell ref="BC11:BD11"/>
-    <mergeCell ref="BC12:BD12"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="AN4:AN6"/>
-    <mergeCell ref="AS4:AX4"/>
-    <mergeCell ref="AS5:AX5"/>
-    <mergeCell ref="AS6:AX6"/>
-    <mergeCell ref="AS7:AX7"/>
-    <mergeCell ref="AS8:AX8"/>
-    <mergeCell ref="AS9:AX9"/>
-    <mergeCell ref="AS10:AX10"/>
-    <mergeCell ref="AN11:AN13"/>
-    <mergeCell ref="AS11:AX11"/>
-    <mergeCell ref="AS12:AX12"/>
-    <mergeCell ref="AS13:AX13"/>
-    <mergeCell ref="AN14:AN16"/>
-    <mergeCell ref="AS14:AX14"/>
-    <mergeCell ref="AS15:AX15"/>
-    <mergeCell ref="AS16:AX16"/>
-    <mergeCell ref="AS17:AX17"/>
-    <mergeCell ref="AS18:AX18"/>
-    <mergeCell ref="AS20:AX20"/>
-    <mergeCell ref="X18:X20"/>
-    <mergeCell ref="Y18:Y20"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AX3"/>
-    <mergeCell ref="AD2:AI3"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="N2:S3"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S29"/>
-    <mergeCell ref="N30:S30"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="X14:X16"/>
-    <mergeCell ref="Y14:Y16"/>
-    <mergeCell ref="X4:X6"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="AD4:AI4"/>
-    <mergeCell ref="AD5:AI5"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:S36"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="N25:S25"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:S27"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="N48:S48"/>
-    <mergeCell ref="N40:S40"/>
-    <mergeCell ref="N41:S41"/>
-    <mergeCell ref="N42:S42"/>
-    <mergeCell ref="N43:S43"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="N56:S56"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="N20:S20"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N39:S39"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N32:S32"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="N34:S34"/>
-    <mergeCell ref="N57:S57"/>
-    <mergeCell ref="N58:S58"/>
-    <mergeCell ref="N59:S59"/>
-    <mergeCell ref="N60:S60"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N53:S53"/>
-    <mergeCell ref="N54:S54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="N49:S49"/>
-    <mergeCell ref="N50:S50"/>
-    <mergeCell ref="N51:S51"/>
-    <mergeCell ref="N52:S52"/>
-    <mergeCell ref="N44:S44"/>
-    <mergeCell ref="N45:S45"/>
-    <mergeCell ref="N46:S46"/>
-    <mergeCell ref="N47:S47"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="N21:S21"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N67:S67"/>
-    <mergeCell ref="N68:S68"/>
-    <mergeCell ref="N69:S69"/>
-    <mergeCell ref="N70:S70"/>
-    <mergeCell ref="N61:S61"/>
-    <mergeCell ref="N62:S62"/>
-    <mergeCell ref="N63:S63"/>
-    <mergeCell ref="N64:S64"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="N66:S66"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="N83:S83"/>
-    <mergeCell ref="N84:S84"/>
-    <mergeCell ref="N85:S85"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="N77:S77"/>
-    <mergeCell ref="N78:S78"/>
-    <mergeCell ref="N79:S79"/>
-    <mergeCell ref="N80:S80"/>
-    <mergeCell ref="N81:S81"/>
-    <mergeCell ref="N82:S82"/>
-    <mergeCell ref="N71:S71"/>
-    <mergeCell ref="N72:S72"/>
-    <mergeCell ref="N73:S73"/>
-    <mergeCell ref="N74:S74"/>
-    <mergeCell ref="N75:S75"/>
-    <mergeCell ref="N76:S76"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I79:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="X25:X26"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="X45:X46"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="X42:X43"/>
-    <mergeCell ref="Y42:Y43"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Y33"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="X72:X73"/>
-    <mergeCell ref="Y72:Y73"/>
-    <mergeCell ref="X123:X124"/>
-    <mergeCell ref="Y123:Y124"/>
-    <mergeCell ref="X120:X121"/>
-    <mergeCell ref="Y120:Y121"/>
-    <mergeCell ref="X117:X118"/>
-    <mergeCell ref="Y117:Y118"/>
-    <mergeCell ref="X114:X115"/>
-    <mergeCell ref="Y114:Y115"/>
-    <mergeCell ref="X111:X112"/>
-    <mergeCell ref="Y111:Y112"/>
-    <mergeCell ref="X95:X96"/>
-    <mergeCell ref="Y95:Y96"/>
-    <mergeCell ref="X92:X93"/>
-    <mergeCell ref="Y92:Y93"/>
-    <mergeCell ref="X89:X90"/>
-    <mergeCell ref="Y89:Y90"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="X100:X101"/>
-    <mergeCell ref="Y100:Y101"/>
-    <mergeCell ref="Y126:Y127"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="AN17:AN18"/>
-    <mergeCell ref="AN19:AN20"/>
-    <mergeCell ref="AS19:AX19"/>
-    <mergeCell ref="AN21:AN23"/>
-    <mergeCell ref="AS21:AX21"/>
-    <mergeCell ref="AS22:AX22"/>
-    <mergeCell ref="AS23:AX23"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="AS24:AX24"/>
-    <mergeCell ref="AS25:AX25"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="AS26:AX26"/>
-    <mergeCell ref="AS27:AX27"/>
-    <mergeCell ref="AN28:AN30"/>
-    <mergeCell ref="AS28:AX28"/>
-    <mergeCell ref="AS29:AX29"/>
-    <mergeCell ref="AS30:AX30"/>
-    <mergeCell ref="AN31:AN32"/>
-    <mergeCell ref="AS31:AX31"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AD23:AI23"/>
-    <mergeCell ref="AS32:AX32"/>
-    <mergeCell ref="AN33:AN34"/>
-    <mergeCell ref="AS33:AX33"/>
-    <mergeCell ref="AS34:AX34"/>
-    <mergeCell ref="AN35:AN36"/>
-    <mergeCell ref="AS35:AX35"/>
-    <mergeCell ref="AS36:AX36"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AS37:AX37"/>
-    <mergeCell ref="AS38:AX38"/>
-    <mergeCell ref="AS39:AX39"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="AS40:AX40"/>
-    <mergeCell ref="AS41:AX41"/>
-    <mergeCell ref="AS42:AX42"/>
-    <mergeCell ref="AN43:AN44"/>
-    <mergeCell ref="AS43:AX43"/>
-    <mergeCell ref="AS44:AX44"/>
-    <mergeCell ref="AS45:AX45"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AS46:AX46"/>
-    <mergeCell ref="AS47:AX47"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="AS48:AX48"/>
-    <mergeCell ref="AS49:AX49"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="AS50:AX50"/>
-    <mergeCell ref="AS51:AX51"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AS52:AX52"/>
-    <mergeCell ref="AS53:AX53"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="AS54:AX54"/>
-    <mergeCell ref="AS55:AX55"/>
-    <mergeCell ref="AS56:AX56"/>
-    <mergeCell ref="AN57:AN58"/>
-    <mergeCell ref="AS57:AX57"/>
-    <mergeCell ref="AS58:AX58"/>
-    <mergeCell ref="AN59:AN60"/>
-    <mergeCell ref="AS59:AX59"/>
-    <mergeCell ref="AS60:AX60"/>
-    <mergeCell ref="AN61:AN62"/>
-    <mergeCell ref="AS61:AX61"/>
-    <mergeCell ref="AS62:AX62"/>
-    <mergeCell ref="AN63:AN64"/>
-    <mergeCell ref="AS63:AX63"/>
-    <mergeCell ref="AS64:AX64"/>
-    <mergeCell ref="AN65:AN66"/>
-    <mergeCell ref="AS65:AX65"/>
-    <mergeCell ref="AS66:AX66"/>
-    <mergeCell ref="AS67:AX67"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="AS68:AX68"/>
-    <mergeCell ref="AS69:AX69"/>
-    <mergeCell ref="AS70:AX70"/>
-    <mergeCell ref="AN71:AN72"/>
-    <mergeCell ref="AS71:AX71"/>
-    <mergeCell ref="AS72:AX72"/>
-    <mergeCell ref="AN73:AN74"/>
-    <mergeCell ref="AS73:AX73"/>
-    <mergeCell ref="AS74:AX74"/>
-    <mergeCell ref="AN75:AN76"/>
-    <mergeCell ref="AS75:AX75"/>
-    <mergeCell ref="AS76:AX76"/>
-    <mergeCell ref="AN77:AN78"/>
-    <mergeCell ref="AS77:AX77"/>
-    <mergeCell ref="AS78:AX78"/>
-    <mergeCell ref="AN79:AN80"/>
-    <mergeCell ref="AS79:AX79"/>
-    <mergeCell ref="AS80:AX80"/>
-    <mergeCell ref="AN81:AN82"/>
-    <mergeCell ref="AS81:AX81"/>
-    <mergeCell ref="AS82:AX82"/>
-    <mergeCell ref="AN83:AN84"/>
-    <mergeCell ref="AS83:AX83"/>
-    <mergeCell ref="AS84:AX84"/>
-    <mergeCell ref="AS85:AX85"/>
-    <mergeCell ref="AN86:AN87"/>
-    <mergeCell ref="AS86:AX86"/>
-    <mergeCell ref="AS87:AX87"/>
-    <mergeCell ref="AN88:AN89"/>
-    <mergeCell ref="AS88:AX88"/>
-    <mergeCell ref="AS89:AX89"/>
-    <mergeCell ref="AS90:AX90"/>
-    <mergeCell ref="BC19:BD19"/>
-    <mergeCell ref="BC21:BD21"/>
-    <mergeCell ref="BC22:BD22"/>
-    <mergeCell ref="BC23:BD23"/>
-    <mergeCell ref="BC24:BD24"/>
-    <mergeCell ref="BC25:BD25"/>
-    <mergeCell ref="BC26:BD26"/>
-    <mergeCell ref="BC27:BD27"/>
-    <mergeCell ref="BC28:BD28"/>
-    <mergeCell ref="BC29:BD29"/>
-    <mergeCell ref="BC30:BD30"/>
-    <mergeCell ref="BC31:BD31"/>
-    <mergeCell ref="BC32:BD32"/>
-    <mergeCell ref="BC33:BD33"/>
-    <mergeCell ref="BC34:BD34"/>
-    <mergeCell ref="BC35:BD35"/>
-    <mergeCell ref="BC36:BD36"/>
-    <mergeCell ref="BC37:BD37"/>
-    <mergeCell ref="BC38:BD38"/>
-    <mergeCell ref="BC39:BD39"/>
-    <mergeCell ref="BC40:BD40"/>
-    <mergeCell ref="BC41:BD41"/>
-    <mergeCell ref="BC42:BD42"/>
-    <mergeCell ref="BC43:BD43"/>
-    <mergeCell ref="BC44:BD44"/>
-    <mergeCell ref="BC45:BD45"/>
-    <mergeCell ref="BC46:BD46"/>
-    <mergeCell ref="BC47:BD47"/>
-    <mergeCell ref="BC48:BD48"/>
-    <mergeCell ref="BC49:BD49"/>
-    <mergeCell ref="BC50:BD50"/>
-    <mergeCell ref="BC51:BD51"/>
-    <mergeCell ref="BC52:BD52"/>
-    <mergeCell ref="BC53:BD53"/>
-    <mergeCell ref="BC54:BD54"/>
-    <mergeCell ref="BC55:BD55"/>
-    <mergeCell ref="BC56:BD56"/>
-    <mergeCell ref="BC57:BD57"/>
-    <mergeCell ref="BC58:BD58"/>
-    <mergeCell ref="BC59:BD59"/>
-    <mergeCell ref="BC60:BD60"/>
-    <mergeCell ref="BC61:BD61"/>
-    <mergeCell ref="BC62:BD62"/>
-    <mergeCell ref="BC63:BD63"/>
-    <mergeCell ref="BC64:BD64"/>
-    <mergeCell ref="BC65:BD65"/>
-    <mergeCell ref="BC66:BD66"/>
-    <mergeCell ref="BC67:BD67"/>
-    <mergeCell ref="BC68:BD68"/>
-    <mergeCell ref="BC69:BD69"/>
-    <mergeCell ref="BC70:BD70"/>
-    <mergeCell ref="BC71:BD71"/>
-    <mergeCell ref="BC72:BD72"/>
-    <mergeCell ref="BC73:BD73"/>
-    <mergeCell ref="BC74:BD74"/>
-    <mergeCell ref="BC75:BD75"/>
-    <mergeCell ref="BC76:BD76"/>
-    <mergeCell ref="BC77:BD77"/>
-    <mergeCell ref="BC78:BD78"/>
-    <mergeCell ref="BC79:BD79"/>
-    <mergeCell ref="BC80:BD80"/>
-    <mergeCell ref="BC90:BD90"/>
-    <mergeCell ref="BC81:BD81"/>
-    <mergeCell ref="BC82:BD82"/>
-    <mergeCell ref="BC83:BD83"/>
-    <mergeCell ref="BC84:BD84"/>
-    <mergeCell ref="BC85:BD85"/>
-    <mergeCell ref="BC86:BD86"/>
-    <mergeCell ref="BC87:BD87"/>
-    <mergeCell ref="BC88:BD88"/>
-    <mergeCell ref="BC89:BD89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
+++ b/INCREMENTO2/Excels/Backlog sprint - Sprint backlog - Sprint Review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addan\OneDrive\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FC8FFB-528A-4791-B76E-3B86413DA1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278830C4-5AF0-4414-85C6-D32BBF431DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1210,6 +1210,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1291,10 +1298,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1400,22 +1416,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1789,70 +1789,70 @@
   </cols>
   <sheetData>
     <row r="2" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="81" t="s">
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="77" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="78"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="79"/>
-      <c r="AD2" s="81" t="s">
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="84"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="85"/>
+      <c r="AB2" s="85"/>
+      <c r="AC2" s="85"/>
+      <c r="AD2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="82"/>
-      <c r="AF2" s="82"/>
-      <c r="AG2" s="82"/>
-      <c r="AH2" s="82"/>
-      <c r="AI2" s="83"/>
-      <c r="AJ2" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK2" s="76"/>
-      <c r="AN2" s="79" t="s">
+      <c r="AE2" s="88"/>
+      <c r="AF2" s="88"/>
+      <c r="AG2" s="88"/>
+      <c r="AH2" s="88"/>
+      <c r="AI2" s="89"/>
+      <c r="AJ2" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK2" s="82"/>
+      <c r="AN2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="AO2" s="79"/>
-      <c r="AP2" s="79"/>
-      <c r="AQ2" s="79"/>
-      <c r="AR2" s="79"/>
-      <c r="AS2" s="80" t="s">
+      <c r="AO2" s="85"/>
+      <c r="AP2" s="85"/>
+      <c r="AQ2" s="85"/>
+      <c r="AR2" s="85"/>
+      <c r="AS2" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="80"/>
-      <c r="AU2" s="80"/>
-      <c r="AV2" s="80"/>
-      <c r="AW2" s="80"/>
-      <c r="AX2" s="80"/>
-      <c r="AY2" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="AZ2" s="76"/>
-      <c r="BA2" s="76" t="s">
+      <c r="AT2" s="86"/>
+      <c r="AU2" s="86"/>
+      <c r="AV2" s="86"/>
+      <c r="AW2" s="86"/>
+      <c r="AX2" s="86"/>
+      <c r="AY2" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="AZ2" s="82"/>
+      <c r="BA2" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="BB2" s="76"/>
-      <c r="BC2" s="76" t="s">
+      <c r="BB2" s="82"/>
+      <c r="BC2" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="76"/>
+      <c r="BD2" s="82"/>
     </row>
     <row r="3" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I3" s="1" t="s">
@@ -1870,12 +1870,12 @@
       <c r="M3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="90"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="92"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="98"/>
       <c r="T3" s="13" t="s">
         <v>8</v>
       </c>
@@ -1900,12 +1900,12 @@
       <c r="AC3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD3" s="84"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="85"/>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="86"/>
+      <c r="AD3" s="90"/>
+      <c r="AE3" s="91"/>
+      <c r="AF3" s="91"/>
+      <c r="AG3" s="91"/>
+      <c r="AH3" s="91"/>
+      <c r="AI3" s="92"/>
       <c r="AJ3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1927,12 +1927,12 @@
       <c r="AR3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AS3" s="80"/>
-      <c r="AT3" s="80"/>
-      <c r="AU3" s="80"/>
-      <c r="AV3" s="80"/>
-      <c r="AW3" s="80"/>
-      <c r="AX3" s="80"/>
+      <c r="AS3" s="86"/>
+      <c r="AT3" s="86"/>
+      <c r="AU3" s="86"/>
+      <c r="AV3" s="86"/>
+      <c r="AW3" s="86"/>
+      <c r="AX3" s="86"/>
       <c r="AY3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1945,13 +1945,13 @@
       <c r="BB3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="76" t="s">
+      <c r="BC3" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="BD3" s="76"/>
+      <c r="BD3" s="82"/>
     </row>
     <row r="4" spans="9:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I4" s="97">
+      <c r="I4" s="103">
         <v>1.5</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1966,14 +1966,14 @@
       <c r="M4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="39"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="42"/>
       <c r="T4" s="7">
         <v>45839</v>
       </c>
@@ -1982,10 +1982,10 @@
       </c>
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
-      <c r="X4" s="46">
+      <c r="X4" s="49">
         <v>1.5</v>
       </c>
-      <c r="Y4" s="93">
+      <c r="Y4" s="99">
         <v>1</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -2000,14 +2000,14 @@
       <c r="AC4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD4" s="37" t="s">
+      <c r="AD4" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="39"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="42"/>
       <c r="AJ4" s="7">
         <v>45839</v>
       </c>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
-      <c r="AN4" s="71">
+      <c r="AN4" s="77">
         <v>1.5</v>
       </c>
       <c r="AO4" s="6" t="s">
@@ -2031,14 +2031,14 @@
       <c r="AR4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS4" s="37" t="s">
+      <c r="AS4" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="39"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="42"/>
       <c r="AY4" s="7">
         <v>45839</v>
       </c>
@@ -2047,11 +2047,11 @@
       </c>
       <c r="BA4" s="19"/>
       <c r="BB4" s="19"/>
-      <c r="BC4" s="67"/>
-      <c r="BD4" s="67"/>
+      <c r="BC4" s="73"/>
+      <c r="BD4" s="73"/>
     </row>
     <row r="5" spans="9:56" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I5" s="98"/>
+      <c r="I5" s="104"/>
       <c r="J5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2064,14 +2064,14 @@
       <c r="M5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="69" t="s">
+      <c r="N5" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="39"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="42"/>
       <c r="T5" s="7">
         <v>45839</v>
       </c>
@@ -2080,8 +2080,8 @@
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="94"/>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="100"/>
       <c r="Z5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2094,14 +2094,14 @@
       <c r="AC5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="96" t="s">
+      <c r="AD5" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="AE5" s="41"/>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="41"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="42"/>
+      <c r="AE5" s="44"/>
+      <c r="AF5" s="44"/>
+      <c r="AG5" s="44"/>
+      <c r="AH5" s="44"/>
+      <c r="AI5" s="45"/>
       <c r="AJ5" s="7">
         <v>45839</v>
       </c>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
-      <c r="AN5" s="72"/>
+      <c r="AN5" s="78"/>
       <c r="AO5" s="6" t="s">
         <v>56</v>
       </c>
@@ -2123,14 +2123,14 @@
       <c r="AR5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="69" t="s">
+      <c r="AS5" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="39"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="42"/>
       <c r="AY5" s="7">
         <v>45839</v>
       </c>
@@ -2139,11 +2139,11 @@
       </c>
       <c r="BA5" s="19"/>
       <c r="BB5" s="19"/>
-      <c r="BC5" s="40"/>
-      <c r="BD5" s="42"/>
+      <c r="BC5" s="43"/>
+      <c r="BD5" s="45"/>
     </row>
     <row r="6" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I6" s="99"/>
+      <c r="I6" s="105"/>
       <c r="J6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2156,14 +2156,14 @@
       <c r="M6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="39"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="42"/>
       <c r="T6" s="7">
         <v>45839</v>
       </c>
@@ -2172,8 +2172,8 @@
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="95"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="101"/>
       <c r="Z6" s="6" t="s">
         <v>169</v>
       </c>
@@ -2186,14 +2186,14 @@
       <c r="AC6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="40" t="s">
+      <c r="AD6" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="41"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="42"/>
+      <c r="AE6" s="44"/>
+      <c r="AF6" s="44"/>
+      <c r="AG6" s="44"/>
+      <c r="AH6" s="44"/>
+      <c r="AI6" s="45"/>
       <c r="AJ6" s="7">
         <v>45839</v>
       </c>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
-      <c r="AN6" s="73"/>
+      <c r="AN6" s="79"/>
       <c r="AO6" s="6" t="s">
         <v>55</v>
       </c>
@@ -2215,14 +2215,14 @@
       <c r="AR6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS6" s="37" t="s">
+      <c r="AS6" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="39"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="41"/>
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="42"/>
       <c r="AY6" s="7">
         <v>45839</v>
       </c>
@@ -2231,11 +2231,11 @@
       </c>
       <c r="BA6" s="19"/>
       <c r="BB6" s="19"/>
-      <c r="BC6" s="67"/>
-      <c r="BD6" s="67"/>
+      <c r="BC6" s="73"/>
+      <c r="BD6" s="73"/>
     </row>
     <row r="7" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="57">
+      <c r="I7" s="60">
         <v>1.8</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2250,14 +2250,14 @@
       <c r="M7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="39"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="42"/>
       <c r="T7" s="8">
         <v>45840</v>
       </c>
@@ -2272,17 +2272,17 @@
       <c r="AA7" s="19"/>
       <c r="AB7" s="19"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="42"/>
+      <c r="AD7" s="43"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
+      <c r="AH7" s="44"/>
+      <c r="AI7" s="45"/>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
-      <c r="AN7" s="46">
+      <c r="AN7" s="49">
         <v>1.8</v>
       </c>
       <c r="AO7" s="6" t="s">
@@ -2297,14 +2297,14 @@
       <c r="AR7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS7" s="37" t="s">
+      <c r="AS7" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AT7" s="38"/>
-      <c r="AU7" s="38"/>
-      <c r="AV7" s="38"/>
-      <c r="AW7" s="38"/>
-      <c r="AX7" s="39"/>
+      <c r="AT7" s="41"/>
+      <c r="AU7" s="41"/>
+      <c r="AV7" s="41"/>
+      <c r="AW7" s="41"/>
+      <c r="AX7" s="42"/>
       <c r="AY7" s="8">
         <v>45840</v>
       </c>
@@ -2313,11 +2313,11 @@
       </c>
       <c r="BA7" s="19"/>
       <c r="BB7" s="19"/>
-      <c r="BC7" s="67"/>
-      <c r="BD7" s="67"/>
+      <c r="BC7" s="73"/>
+      <c r="BD7" s="73"/>
     </row>
     <row r="8" spans="9:56" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I8" s="58"/>
+      <c r="I8" s="61"/>
       <c r="J8" s="35" t="s">
         <v>172</v>
       </c>
@@ -2330,14 +2330,14 @@
       <c r="M8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="39"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="42"/>
       <c r="T8" s="8">
         <v>45840</v>
       </c>
@@ -2346,10 +2346,10 @@
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="56">
+      <c r="X8" s="59">
         <v>1.8</v>
       </c>
-      <c r="Y8" s="93">
+      <c r="Y8" s="99">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
@@ -2364,14 +2364,14 @@
       <c r="AC8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD8" s="37" t="s">
+      <c r="AD8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="38"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="39"/>
+      <c r="AE8" s="41"/>
+      <c r="AF8" s="41"/>
+      <c r="AG8" s="41"/>
+      <c r="AH8" s="41"/>
+      <c r="AI8" s="42"/>
       <c r="AJ8" s="8">
         <v>45840</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
-      <c r="AN8" s="74"/>
+      <c r="AN8" s="80"/>
       <c r="AO8" s="9" t="s">
         <v>170</v>
       </c>
@@ -2393,14 +2393,14 @@
       <c r="AR8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="37" t="s">
+      <c r="AS8" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AT8" s="38"/>
-      <c r="AU8" s="38"/>
-      <c r="AV8" s="38"/>
-      <c r="AW8" s="38"/>
-      <c r="AX8" s="39"/>
+      <c r="AT8" s="41"/>
+      <c r="AU8" s="41"/>
+      <c r="AV8" s="41"/>
+      <c r="AW8" s="41"/>
+      <c r="AX8" s="42"/>
       <c r="AY8" s="8">
         <v>45840</v>
       </c>
@@ -2409,11 +2409,11 @@
       </c>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="67"/>
-      <c r="BD8" s="67"/>
+      <c r="BC8" s="73"/>
+      <c r="BD8" s="73"/>
     </row>
     <row r="9" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="57">
+      <c r="I9" s="60">
         <v>1.1100000000000001</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2428,14 +2428,14 @@
       <c r="M9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="37" t="s">
+      <c r="N9" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="39"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="42"/>
       <c r="T9" s="8">
         <v>45841</v>
       </c>
@@ -2444,8 +2444,8 @@
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="56"/>
-      <c r="Y9" s="94"/>
+      <c r="X9" s="59"/>
+      <c r="Y9" s="100"/>
       <c r="Z9" s="9" t="s">
         <v>170</v>
       </c>
@@ -2458,14 +2458,14 @@
       <c r="AC9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD9" s="37" t="s">
+      <c r="AD9" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="AE9" s="38"/>
-      <c r="AF9" s="38"/>
-      <c r="AG9" s="38"/>
-      <c r="AH9" s="38"/>
-      <c r="AI9" s="39"/>
+      <c r="AE9" s="41"/>
+      <c r="AF9" s="41"/>
+      <c r="AG9" s="41"/>
+      <c r="AH9" s="41"/>
+      <c r="AI9" s="42"/>
       <c r="AJ9" s="8">
         <v>45840</v>
       </c>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
-      <c r="AN9" s="46">
+      <c r="AN9" s="49">
         <v>1.1100000000000001</v>
       </c>
       <c r="AO9" s="6" t="s">
@@ -2489,14 +2489,14 @@
       <c r="AR9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS9" s="37" t="s">
+      <c r="AS9" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AT9" s="38"/>
-      <c r="AU9" s="38"/>
-      <c r="AV9" s="38"/>
-      <c r="AW9" s="38"/>
-      <c r="AX9" s="39"/>
+      <c r="AT9" s="41"/>
+      <c r="AU9" s="41"/>
+      <c r="AV9" s="41"/>
+      <c r="AW9" s="41"/>
+      <c r="AX9" s="42"/>
       <c r="AY9" s="8">
         <v>45841</v>
       </c>
@@ -2505,11 +2505,11 @@
       </c>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="67"/>
-      <c r="BD9" s="67"/>
+      <c r="BC9" s="73"/>
+      <c r="BD9" s="73"/>
     </row>
     <row r="10" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I10" s="58"/>
+      <c r="I10" s="61"/>
       <c r="J10" s="6" t="s">
         <v>175</v>
       </c>
@@ -2522,14 +2522,14 @@
       <c r="M10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="39"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="42"/>
       <c r="T10" s="8">
         <v>45841</v>
       </c>
@@ -2544,17 +2544,17 @@
       <c r="AA10" s="19"/>
       <c r="AB10" s="19"/>
       <c r="AC10" s="4"/>
-      <c r="AD10" s="40"/>
-      <c r="AE10" s="41"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="41"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="42"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="44"/>
+      <c r="AF10" s="44"/>
+      <c r="AG10" s="44"/>
+      <c r="AH10" s="44"/>
+      <c r="AI10" s="45"/>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
-      <c r="AN10" s="74"/>
+      <c r="AN10" s="80"/>
       <c r="AO10" s="6" t="s">
         <v>57</v>
       </c>
@@ -2567,14 +2567,14 @@
       <c r="AR10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS10" s="37" t="s">
+      <c r="AS10" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AT10" s="38"/>
-      <c r="AU10" s="38"/>
-      <c r="AV10" s="38"/>
-      <c r="AW10" s="38"/>
-      <c r="AX10" s="39"/>
+      <c r="AT10" s="41"/>
+      <c r="AU10" s="41"/>
+      <c r="AV10" s="41"/>
+      <c r="AW10" s="41"/>
+      <c r="AX10" s="42"/>
       <c r="AY10" s="8">
         <v>45841</v>
       </c>
@@ -2583,11 +2583,11 @@
       </c>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="67"/>
-      <c r="BD10" s="67"/>
+      <c r="BC10" s="73"/>
+      <c r="BD10" s="73"/>
     </row>
     <row r="11" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I11" s="57">
+      <c r="I11" s="60">
         <v>1.1399999999999999</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2602,14 +2602,14 @@
       <c r="M11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="69" t="s">
+      <c r="N11" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="39"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="42"/>
       <c r="T11" s="8">
         <v>45842</v>
       </c>
@@ -2618,10 +2618,10 @@
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="56">
+      <c r="X11" s="59">
         <v>1.1100000000000001</v>
       </c>
-      <c r="Y11" s="52">
+      <c r="Y11" s="55">
         <v>3</v>
       </c>
       <c r="Z11" s="6" t="s">
@@ -2636,14 +2636,14 @@
       <c r="AC11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD11" s="37" t="s">
+      <c r="AD11" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AE11" s="38"/>
-      <c r="AF11" s="38"/>
-      <c r="AG11" s="38"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="39"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="42"/>
       <c r="AJ11" s="8">
         <v>45841</v>
       </c>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
-      <c r="AN11" s="46">
+      <c r="AN11" s="49">
         <v>1.1399999999999999</v>
       </c>
       <c r="AO11" s="6" t="s">
@@ -2667,14 +2667,14 @@
       <c r="AR11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS11" s="69" t="s">
+      <c r="AS11" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="AT11" s="38"/>
-      <c r="AU11" s="38"/>
-      <c r="AV11" s="38"/>
-      <c r="AW11" s="38"/>
-      <c r="AX11" s="39"/>
+      <c r="AT11" s="41"/>
+      <c r="AU11" s="41"/>
+      <c r="AV11" s="41"/>
+      <c r="AW11" s="41"/>
+      <c r="AX11" s="42"/>
       <c r="AY11" s="8">
         <v>45842</v>
       </c>
@@ -2683,11 +2683,11 @@
       </c>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="67"/>
-      <c r="BD11" s="67"/>
+      <c r="BC11" s="73"/>
+      <c r="BD11" s="73"/>
     </row>
     <row r="12" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I12" s="61"/>
+      <c r="I12" s="64"/>
       <c r="J12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2700,14 +2700,14 @@
       <c r="M12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="69" t="s">
+      <c r="N12" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="39"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="42"/>
       <c r="T12" s="8">
         <v>45842</v>
       </c>
@@ -2716,8 +2716,8 @@
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="21"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="53"/>
+      <c r="X12" s="59"/>
+      <c r="Y12" s="56"/>
       <c r="Z12" s="6" t="s">
         <v>57</v>
       </c>
@@ -2730,14 +2730,14 @@
       <c r="AC12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD12" s="37" t="s">
+      <c r="AD12" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="39"/>
+      <c r="AE12" s="41"/>
+      <c r="AF12" s="41"/>
+      <c r="AG12" s="41"/>
+      <c r="AH12" s="41"/>
+      <c r="AI12" s="42"/>
       <c r="AJ12" s="8">
         <v>45841</v>
       </c>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
-      <c r="AN12" s="74"/>
+      <c r="AN12" s="80"/>
       <c r="AO12" s="6" t="s">
         <v>58</v>
       </c>
@@ -2759,14 +2759,14 @@
       <c r="AR12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS12" s="69" t="s">
+      <c r="AS12" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="38"/>
-      <c r="AX12" s="39"/>
+      <c r="AT12" s="41"/>
+      <c r="AU12" s="41"/>
+      <c r="AV12" s="41"/>
+      <c r="AW12" s="41"/>
+      <c r="AX12" s="42"/>
       <c r="AY12" s="8">
         <v>45842</v>
       </c>
@@ -2775,11 +2775,11 @@
       </c>
       <c r="BA12" s="19"/>
       <c r="BB12" s="19"/>
-      <c r="BC12" s="67"/>
-      <c r="BD12" s="67"/>
+      <c r="BC12" s="73"/>
+      <c r="BD12" s="73"/>
     </row>
     <row r="13" spans="9:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I13" s="58"/>
+      <c r="I13" s="61"/>
       <c r="J13" s="6" t="s">
         <v>96</v>
       </c>
@@ -2792,14 +2792,14 @@
       <c r="M13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="37" t="s">
+      <c r="N13" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="39"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="42"/>
       <c r="T13" s="8">
         <v>45842</v>
       </c>
@@ -2814,17 +2814,17 @@
       <c r="AA13" s="19"/>
       <c r="AB13" s="19"/>
       <c r="AC13" s="4"/>
-      <c r="AD13" s="40"/>
-      <c r="AE13" s="41"/>
-      <c r="AF13" s="41"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="42"/>
+      <c r="AD13" s="43"/>
+      <c r="AE13" s="44"/>
+      <c r="AF13" s="44"/>
+      <c r="AG13" s="44"/>
+      <c r="AH13" s="44"/>
+      <c r="AI13" s="45"/>
       <c r="AJ13" s="7"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
-      <c r="AN13" s="47"/>
+      <c r="AN13" s="50"/>
       <c r="AO13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2837,14 +2837,14 @@
       <c r="AR13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS13" s="37" t="s">
+      <c r="AS13" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="AT13" s="38"/>
-      <c r="AU13" s="38"/>
-      <c r="AV13" s="38"/>
-      <c r="AW13" s="38"/>
-      <c r="AX13" s="39"/>
+      <c r="AT13" s="41"/>
+      <c r="AU13" s="41"/>
+      <c r="AV13" s="41"/>
+      <c r="AW13" s="41"/>
+      <c r="AX13" s="42"/>
       <c r="AY13" s="8">
         <v>45842</v>
       </c>
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
-      <c r="BC13" s="67"/>
-      <c r="BD13" s="67"/>
+      <c r="BC13" s="73"/>
+      <c r="BD13" s="73"/>
     </row>
     <row r="14" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I14" s="57">
+      <c r="I14" s="60">
         <v>1.17</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2872,14 +2872,14 @@
       <c r="M14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N14" s="37" t="s">
+      <c r="N14" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="39"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="42"/>
       <c r="T14" s="8">
         <v>45843</v>
       </c>
@@ -2888,10 +2888,10 @@
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="56">
+      <c r="X14" s="59">
         <v>1.1399999999999999</v>
       </c>
-      <c r="Y14" s="50">
+      <c r="Y14" s="53">
         <v>1</v>
       </c>
       <c r="Z14" s="6" t="s">
@@ -2906,14 +2906,14 @@
       <c r="AC14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD14" s="69" t="s">
+      <c r="AD14" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="AE14" s="38"/>
-      <c r="AF14" s="38"/>
-      <c r="AG14" s="38"/>
-      <c r="AH14" s="38"/>
-      <c r="AI14" s="39"/>
+      <c r="AE14" s="41"/>
+      <c r="AF14" s="41"/>
+      <c r="AG14" s="41"/>
+      <c r="AH14" s="41"/>
+      <c r="AI14" s="42"/>
       <c r="AJ14" s="8">
         <v>45842</v>
       </c>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
-      <c r="AN14" s="46">
+      <c r="AN14" s="49">
         <v>1.17</v>
       </c>
       <c r="AO14" s="6" t="s">
@@ -2937,14 +2937,14 @@
       <c r="AR14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS14" s="37" t="s">
+      <c r="AS14" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="AT14" s="38"/>
-      <c r="AU14" s="38"/>
-      <c r="AV14" s="38"/>
-      <c r="AW14" s="38"/>
-      <c r="AX14" s="39"/>
+      <c r="AT14" s="41"/>
+      <c r="AU14" s="41"/>
+      <c r="AV14" s="41"/>
+      <c r="AW14" s="41"/>
+      <c r="AX14" s="42"/>
       <c r="AY14" s="8">
         <v>45843</v>
       </c>
@@ -2953,11 +2953,11 @@
       </c>
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
-      <c r="BC14" s="67"/>
-      <c r="BD14" s="67"/>
+      <c r="BC14" s="73"/>
+      <c r="BD14" s="73"/>
     </row>
     <row r="15" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="61"/>
+      <c r="I15" s="64"/>
       <c r="J15" s="6" t="s">
         <v>59</v>
       </c>
@@ -2970,14 +2970,14 @@
       <c r="M15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N15" s="37" t="s">
+      <c r="N15" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="39"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="42"/>
       <c r="T15" s="8">
         <v>45843</v>
       </c>
@@ -2986,8 +2986,8 @@
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="21"/>
-      <c r="X15" s="56"/>
-      <c r="Y15" s="75"/>
+      <c r="X15" s="59"/>
+      <c r="Y15" s="81"/>
       <c r="Z15" s="6" t="s">
         <v>58</v>
       </c>
@@ -3000,14 +3000,14 @@
       <c r="AC15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD15" s="69" t="s">
+      <c r="AD15" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="38"/>
-      <c r="AH15" s="38"/>
-      <c r="AI15" s="39"/>
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="41"/>
+      <c r="AH15" s="41"/>
+      <c r="AI15" s="42"/>
       <c r="AJ15" s="8">
         <v>45842</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
-      <c r="AN15" s="74"/>
+      <c r="AN15" s="80"/>
       <c r="AO15" s="6" t="s">
         <v>59</v>
       </c>
@@ -3029,14 +3029,14 @@
       <c r="AR15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AS15" s="37" t="s">
+      <c r="AS15" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="AT15" s="38"/>
-      <c r="AU15" s="38"/>
-      <c r="AV15" s="38"/>
-      <c r="AW15" s="38"/>
-      <c r="AX15" s="39"/>
+      <c r="AT15" s="41"/>
+      <c r="AU15" s="41"/>
+      <c r="AV15" s="41"/>
+      <c r="AW15" s="41"/>
+      <c r="AX15" s="42"/>
       <c r="AY15" s="8">
         <v>45843</v>
       </c>
@@ -3045,11 +3045,11 @@
       </c>
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
-      <c r="BC15" s="67"/>
-      <c r="BD15" s="67"/>
+      <c r="BC15" s="73"/>
+      <c r="BD15" s="73"/>
     </row>
     <row r="16" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I16" s="58"/>
+      <c r="I16" s="61"/>
       <c r="J16" s="6" t="s">
         <v>60</v>
       </c>
@@ -3062,14 +3062,14 @@
       <c r="M16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="37" t="s">
+      <c r="N16" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="39"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="42"/>
       <c r="T16" s="17">
         <v>45843</v>
       </c>
@@ -3078,8 +3078,8 @@
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="56"/>
-      <c r="Y16" s="51"/>
+      <c r="X16" s="59"/>
+      <c r="Y16" s="54"/>
       <c r="Z16" s="6" t="s">
         <v>62</v>
       </c>
@@ -3092,14 +3092,14 @@
       <c r="AC16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD16" s="37" t="s">
+      <c r="AD16" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="AE16" s="38"/>
-      <c r="AF16" s="38"/>
-      <c r="AG16" s="38"/>
-      <c r="AH16" s="38"/>
-      <c r="AI16" s="39"/>
+      <c r="AE16" s="41"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="41"/>
+      <c r="AI16" s="42"/>
       <c r="AJ16" s="8">
         <v>45842</v>
       </c>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
-      <c r="AN16" s="74"/>
+      <c r="AN16" s="80"/>
       <c r="AO16" s="9" t="s">
         <v>60</v>
       </c>
@@ -3121,14 +3121,14 @@
       <c r="AR16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AS16" s="37" t="s">
+      <c r="AS16" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="AT16" s="38"/>
-      <c r="AU16" s="38"/>
-      <c r="AV16" s="38"/>
-      <c r="AW16" s="38"/>
-      <c r="AX16" s="39"/>
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="41"/>
+      <c r="AV16" s="41"/>
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="42"/>
       <c r="AY16" s="17">
         <v>45843</v>
       </c>
@@ -3137,11 +3137,11 @@
       </c>
       <c r="BA16" s="25"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="68"/>
-      <c r="BD16" s="68"/>
+      <c r="BC16" s="74"/>
+      <c r="BD16" s="74"/>
     </row>
     <row r="17" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I17" s="59">
+      <c r="I17" s="62">
         <v>1.2</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -3156,14 +3156,14 @@
       <c r="M17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="39"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="42"/>
       <c r="T17" s="8">
         <v>45844</v>
       </c>
@@ -3178,17 +3178,17 @@
       <c r="AA17" s="19"/>
       <c r="AB17" s="19"/>
       <c r="AC17" s="4"/>
-      <c r="AD17" s="40"/>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="42"/>
+      <c r="AD17" s="43"/>
+      <c r="AE17" s="44"/>
+      <c r="AF17" s="44"/>
+      <c r="AG17" s="44"/>
+      <c r="AH17" s="44"/>
+      <c r="AI17" s="45"/>
       <c r="AJ17" s="7"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
-      <c r="AN17" s="100">
+      <c r="AN17" s="106">
         <v>1.2</v>
       </c>
       <c r="AO17" s="6" t="s">
@@ -3203,14 +3203,14 @@
       <c r="AR17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS17" s="37" t="s">
+      <c r="AS17" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="AT17" s="38"/>
-      <c r="AU17" s="38"/>
-      <c r="AV17" s="38"/>
-      <c r="AW17" s="38"/>
-      <c r="AX17" s="39"/>
+      <c r="AT17" s="41"/>
+      <c r="AU17" s="41"/>
+      <c r="AV17" s="41"/>
+      <c r="AW17" s="41"/>
+      <c r="AX17" s="42"/>
       <c r="AY17" s="8">
         <v>45844</v>
       </c>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="BA17" s="19"/>
       <c r="BB17" s="19"/>
-      <c r="BC17" s="67"/>
-      <c r="BD17" s="67"/>
+      <c r="BC17" s="73"/>
+      <c r="BD17" s="73"/>
     </row>
     <row r="18" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I18" s="60"/>
+      <c r="I18" s="63"/>
       <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
@@ -3236,14 +3236,14 @@
       <c r="M18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N18" s="37" t="s">
+      <c r="N18" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="39"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="42"/>
       <c r="T18" s="8">
         <v>45844</v>
       </c>
@@ -3252,10 +3252,10 @@
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="21"/>
-      <c r="X18" s="56">
+      <c r="X18" s="59">
         <v>1.17</v>
       </c>
-      <c r="Y18" s="50">
+      <c r="Y18" s="53">
         <v>1</v>
       </c>
       <c r="Z18" s="6" t="s">
@@ -3270,14 +3270,14 @@
       <c r="AC18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD18" s="37" t="s">
+      <c r="AD18" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="AE18" s="38"/>
-      <c r="AF18" s="38"/>
-      <c r="AG18" s="38"/>
-      <c r="AH18" s="38"/>
-      <c r="AI18" s="39"/>
+      <c r="AE18" s="41"/>
+      <c r="AF18" s="41"/>
+      <c r="AG18" s="41"/>
+      <c r="AH18" s="41"/>
+      <c r="AI18" s="42"/>
       <c r="AJ18" s="8">
         <v>45843</v>
       </c>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AN18" s="100"/>
+      <c r="AN18" s="106"/>
       <c r="AO18" s="6" t="s">
         <v>61</v>
       </c>
@@ -3299,14 +3299,14 @@
       <c r="AR18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS18" s="37" t="s">
+      <c r="AS18" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="AT18" s="38"/>
-      <c r="AU18" s="38"/>
-      <c r="AV18" s="38"/>
-      <c r="AW18" s="38"/>
-      <c r="AX18" s="39"/>
+      <c r="AT18" s="41"/>
+      <c r="AU18" s="41"/>
+      <c r="AV18" s="41"/>
+      <c r="AW18" s="41"/>
+      <c r="AX18" s="42"/>
       <c r="AY18" s="8">
         <v>45844</v>
       </c>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="BA18" s="19"/>
       <c r="BB18" s="19"/>
-      <c r="BC18" s="67"/>
-      <c r="BD18" s="67"/>
+      <c r="BC18" s="73"/>
+      <c r="BD18" s="73"/>
     </row>
     <row r="19" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I19" s="57" t="s">
+      <c r="I19" s="60" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3334,14 +3334,14 @@
       <c r="M19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N19" s="37" t="s">
+      <c r="N19" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="39"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="42"/>
       <c r="T19" s="8">
         <v>45844</v>
       </c>
@@ -3350,8 +3350,8 @@
       </c>
       <c r="V19" s="20"/>
       <c r="W19" s="21"/>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="75"/>
+      <c r="X19" s="59"/>
+      <c r="Y19" s="81"/>
       <c r="Z19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3364,14 +3364,14 @@
       <c r="AC19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD19" s="37" t="s">
+      <c r="AD19" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="AE19" s="38"/>
-      <c r="AF19" s="38"/>
-      <c r="AG19" s="38"/>
-      <c r="AH19" s="38"/>
-      <c r="AI19" s="39"/>
+      <c r="AE19" s="41"/>
+      <c r="AF19" s="41"/>
+      <c r="AG19" s="41"/>
+      <c r="AH19" s="41"/>
+      <c r="AI19" s="42"/>
       <c r="AJ19" s="8">
         <v>45843</v>
       </c>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AN19" s="46" t="s">
+      <c r="AN19" s="49" t="s">
         <v>19</v>
       </c>
       <c r="AO19" s="6" t="s">
@@ -3395,14 +3395,14 @@
       <c r="AR19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS19" s="37" t="s">
+      <c r="AS19" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="AT19" s="38"/>
-      <c r="AU19" s="38"/>
-      <c r="AV19" s="38"/>
-      <c r="AW19" s="38"/>
-      <c r="AX19" s="39"/>
+      <c r="AT19" s="41"/>
+      <c r="AU19" s="41"/>
+      <c r="AV19" s="41"/>
+      <c r="AW19" s="41"/>
+      <c r="AX19" s="42"/>
       <c r="AY19" s="8">
         <v>45844</v>
       </c>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="BA19" s="19"/>
       <c r="BB19" s="19"/>
-      <c r="BC19" s="67"/>
-      <c r="BD19" s="67"/>
+      <c r="BC19" s="73"/>
+      <c r="BD19" s="73"/>
     </row>
     <row r="20" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I20" s="58"/>
+      <c r="I20" s="61"/>
       <c r="J20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3428,14 +3428,14 @@
       <c r="M20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N20" s="37" t="s">
+      <c r="N20" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="39"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="42"/>
       <c r="T20" s="8">
         <v>45844</v>
       </c>
@@ -3444,8 +3444,8 @@
       </c>
       <c r="V20" s="20"/>
       <c r="W20" s="21"/>
-      <c r="X20" s="56"/>
-      <c r="Y20" s="51"/>
+      <c r="X20" s="59"/>
+      <c r="Y20" s="54"/>
       <c r="Z20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3458,14 +3458,14 @@
       <c r="AC20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD20" s="37" t="s">
+      <c r="AD20" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="AE20" s="38"/>
-      <c r="AF20" s="38"/>
-      <c r="AG20" s="38"/>
-      <c r="AH20" s="38"/>
-      <c r="AI20" s="39"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="42"/>
       <c r="AJ20" s="17">
         <v>45843</v>
       </c>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
-      <c r="AN20" s="47"/>
+      <c r="AN20" s="50"/>
       <c r="AO20" s="6" t="s">
         <v>63</v>
       </c>
@@ -3487,14 +3487,14 @@
       <c r="AR20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS20" s="37" t="s">
+      <c r="AS20" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="AT20" s="38"/>
-      <c r="AU20" s="38"/>
-      <c r="AV20" s="38"/>
-      <c r="AW20" s="38"/>
-      <c r="AX20" s="39"/>
+      <c r="AT20" s="41"/>
+      <c r="AU20" s="41"/>
+      <c r="AV20" s="41"/>
+      <c r="AW20" s="41"/>
+      <c r="AX20" s="42"/>
       <c r="AY20" s="8">
         <v>45844</v>
       </c>
@@ -3503,11 +3503,11 @@
       </c>
       <c r="BA20" s="19"/>
       <c r="BB20" s="19"/>
-      <c r="BC20" s="67"/>
-      <c r="BD20" s="67"/>
+      <c r="BC20" s="73"/>
+      <c r="BD20" s="73"/>
     </row>
     <row r="21" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I21" s="57">
+      <c r="I21" s="60">
         <v>2.5</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3522,14 +3522,14 @@
       <c r="M21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N21" s="37" t="s">
+      <c r="N21" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="39"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="42"/>
       <c r="T21" s="7">
         <v>45844</v>
       </c>
@@ -3544,17 +3544,17 @@
       <c r="AA21" s="19"/>
       <c r="AB21" s="19"/>
       <c r="AC21" s="4"/>
-      <c r="AD21" s="40"/>
-      <c r="AE21" s="41"/>
-      <c r="AF21" s="41"/>
-      <c r="AG21" s="41"/>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="42"/>
+      <c r="AD21" s="43"/>
+      <c r="AE21" s="44"/>
+      <c r="AF21" s="44"/>
+      <c r="AG21" s="44"/>
+      <c r="AH21" s="44"/>
+      <c r="AI21" s="45"/>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
-      <c r="AN21" s="46">
+      <c r="AN21" s="49">
         <v>2.5</v>
       </c>
       <c r="AO21" s="6" t="s">
@@ -3569,14 +3569,14 @@
       <c r="AR21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS21" s="37" t="s">
+      <c r="AS21" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="AT21" s="38"/>
-      <c r="AU21" s="38"/>
-      <c r="AV21" s="38"/>
-      <c r="AW21" s="38"/>
-      <c r="AX21" s="39"/>
+      <c r="AT21" s="41"/>
+      <c r="AU21" s="41"/>
+      <c r="AV21" s="41"/>
+      <c r="AW21" s="41"/>
+      <c r="AX21" s="42"/>
       <c r="AY21" s="7">
         <v>45844</v>
       </c>
@@ -3589,13 +3589,13 @@
       <c r="BB21" s="8">
         <v>45910</v>
       </c>
-      <c r="BC21" s="67">
-        <v>3</v>
-      </c>
-      <c r="BD21" s="67"/>
+      <c r="BC21" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD21" s="73"/>
     </row>
     <row r="22" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I22" s="61"/>
+      <c r="I22" s="64"/>
       <c r="J22" s="6" t="s">
         <v>177</v>
       </c>
@@ -3608,14 +3608,14 @@
       <c r="M22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N22" s="37" t="s">
+      <c r="N22" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="39"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="42"/>
       <c r="T22" s="7">
         <v>45844</v>
       </c>
@@ -3624,10 +3624,10 @@
       </c>
       <c r="V22" s="20"/>
       <c r="W22" s="21"/>
-      <c r="X22" s="100">
+      <c r="X22" s="106">
         <v>1.2</v>
       </c>
-      <c r="Y22" s="50">
+      <c r="Y22" s="53">
         <v>1</v>
       </c>
       <c r="Z22" s="6" t="s">
@@ -3642,14 +3642,14 @@
       <c r="AC22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD22" s="37" t="s">
+      <c r="AD22" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="AE22" s="38"/>
-      <c r="AF22" s="38"/>
-      <c r="AG22" s="38"/>
-      <c r="AH22" s="38"/>
-      <c r="AI22" s="39"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="42"/>
       <c r="AJ22" s="8">
         <v>45844</v>
       </c>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
-      <c r="AN22" s="74"/>
+      <c r="AN22" s="80"/>
       <c r="AO22" s="6" t="s">
         <v>64</v>
       </c>
@@ -3671,14 +3671,14 @@
       <c r="AR22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS22" s="37" t="s">
+      <c r="AS22" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="AT22" s="38"/>
-      <c r="AU22" s="38"/>
-      <c r="AV22" s="38"/>
-      <c r="AW22" s="38"/>
-      <c r="AX22" s="39"/>
+      <c r="AT22" s="41"/>
+      <c r="AU22" s="41"/>
+      <c r="AV22" s="41"/>
+      <c r="AW22" s="41"/>
+      <c r="AX22" s="42"/>
       <c r="AY22" s="7">
         <v>45844</v>
       </c>
@@ -3691,13 +3691,13 @@
       <c r="BB22" s="8">
         <v>45910</v>
       </c>
-      <c r="BC22" s="67">
-        <v>3</v>
-      </c>
-      <c r="BD22" s="67"/>
+      <c r="BC22" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD22" s="73"/>
     </row>
     <row r="23" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I23" s="58"/>
+      <c r="I23" s="61"/>
       <c r="J23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3710,14 +3710,14 @@
       <c r="M23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="37" t="s">
+      <c r="N23" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="39"/>
+      <c r="O23" s="41"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="42"/>
       <c r="T23" s="7">
         <v>45844</v>
       </c>
@@ -3726,8 +3726,8 @@
       </c>
       <c r="V23" s="20"/>
       <c r="W23" s="21"/>
-      <c r="X23" s="100"/>
-      <c r="Y23" s="51"/>
+      <c r="X23" s="106"/>
+      <c r="Y23" s="54"/>
       <c r="Z23" s="15" t="s">
         <v>61</v>
       </c>
@@ -3740,14 +3740,14 @@
       <c r="AC23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD23" s="37" t="s">
+      <c r="AD23" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="AE23" s="38"/>
-      <c r="AF23" s="38"/>
-      <c r="AG23" s="38"/>
-      <c r="AH23" s="38"/>
-      <c r="AI23" s="39"/>
+      <c r="AE23" s="41"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="41"/>
+      <c r="AH23" s="41"/>
+      <c r="AI23" s="42"/>
       <c r="AJ23" s="8">
         <v>45844</v>
       </c>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
-      <c r="AN23" s="47"/>
+      <c r="AN23" s="50"/>
       <c r="AO23" s="6" t="s">
         <v>65</v>
       </c>
@@ -3769,14 +3769,14 @@
       <c r="AR23" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS23" s="37" t="s">
+      <c r="AS23" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="AT23" s="38"/>
-      <c r="AU23" s="38"/>
-      <c r="AV23" s="38"/>
-      <c r="AW23" s="38"/>
-      <c r="AX23" s="39"/>
+      <c r="AT23" s="41"/>
+      <c r="AU23" s="41"/>
+      <c r="AV23" s="41"/>
+      <c r="AW23" s="41"/>
+      <c r="AX23" s="42"/>
       <c r="AY23" s="7">
         <v>45844</v>
       </c>
@@ -3789,13 +3789,13 @@
       <c r="BB23" s="8">
         <v>45910</v>
       </c>
-      <c r="BC23" s="67">
-        <v>3</v>
-      </c>
-      <c r="BD23" s="67"/>
+      <c r="BC23" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD23" s="73"/>
     </row>
     <row r="24" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I24" s="57" t="s">
+      <c r="I24" s="60" t="s">
         <v>87</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3810,14 +3810,14 @@
       <c r="M24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N24" s="37" t="s">
+      <c r="N24" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="39"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="41"/>
+      <c r="S24" s="42"/>
       <c r="T24" s="7">
         <v>45908</v>
       </c>
@@ -3832,17 +3832,17 @@
       <c r="AA24" s="19"/>
       <c r="AB24" s="19"/>
       <c r="AC24" s="4"/>
-      <c r="AD24" s="40"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="42"/>
+      <c r="AD24" s="43"/>
+      <c r="AE24" s="44"/>
+      <c r="AF24" s="44"/>
+      <c r="AG24" s="44"/>
+      <c r="AH24" s="44"/>
+      <c r="AI24" s="45"/>
       <c r="AJ24" s="7"/>
       <c r="AK24" s="7"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
-      <c r="AN24" s="46" t="s">
+      <c r="AN24" s="49" t="s">
         <v>87</v>
       </c>
       <c r="AO24" s="6" t="s">
@@ -3857,27 +3857,33 @@
       <c r="AR24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS24" s="37" t="s">
+      <c r="AS24" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="AT24" s="38"/>
-      <c r="AU24" s="38"/>
-      <c r="AV24" s="38"/>
-      <c r="AW24" s="38"/>
-      <c r="AX24" s="39"/>
+      <c r="AT24" s="41"/>
+      <c r="AU24" s="41"/>
+      <c r="AV24" s="41"/>
+      <c r="AW24" s="41"/>
+      <c r="AX24" s="42"/>
       <c r="AY24" s="7">
         <v>45908</v>
       </c>
       <c r="AZ24" s="7">
         <v>45910</v>
       </c>
-      <c r="BA24" s="19"/>
-      <c r="BB24" s="19"/>
-      <c r="BC24" s="67"/>
-      <c r="BD24" s="67"/>
+      <c r="BA24" s="7">
+        <v>45908</v>
+      </c>
+      <c r="BB24" s="7">
+        <v>45910</v>
+      </c>
+      <c r="BC24" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD24" s="73"/>
     </row>
     <row r="25" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I25" s="58"/>
+      <c r="I25" s="61"/>
       <c r="J25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3890,14 +3896,14 @@
       <c r="M25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N25" s="37" t="s">
+      <c r="N25" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="O25" s="38"/>
-      <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
-      <c r="R25" s="38"/>
-      <c r="S25" s="39"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="42"/>
       <c r="T25" s="7">
         <v>45908</v>
       </c>
@@ -3906,10 +3912,10 @@
       </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="46" t="s">
+      <c r="X25" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="Y25" s="52">
+      <c r="Y25" s="55">
         <v>3</v>
       </c>
       <c r="Z25" s="6" t="s">
@@ -3924,14 +3930,14 @@
       <c r="AC25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AD25" s="37" t="s">
+      <c r="AD25" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="AE25" s="38"/>
-      <c r="AF25" s="38"/>
-      <c r="AG25" s="38"/>
-      <c r="AH25" s="38"/>
-      <c r="AI25" s="39"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="42"/>
       <c r="AJ25" s="8">
         <v>45844</v>
       </c>
@@ -3940,7 +3946,7 @@
       </c>
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
-      <c r="AN25" s="47"/>
+      <c r="AN25" s="50"/>
       <c r="AO25" s="6" t="s">
         <v>178</v>
       </c>
@@ -3953,27 +3959,33 @@
       <c r="AR25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS25" s="37" t="s">
+      <c r="AS25" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="AT25" s="38"/>
-      <c r="AU25" s="38"/>
-      <c r="AV25" s="38"/>
-      <c r="AW25" s="38"/>
-      <c r="AX25" s="39"/>
+      <c r="AT25" s="41"/>
+      <c r="AU25" s="41"/>
+      <c r="AV25" s="41"/>
+      <c r="AW25" s="41"/>
+      <c r="AX25" s="42"/>
       <c r="AY25" s="7">
         <v>45908</v>
       </c>
       <c r="AZ25" s="7">
         <v>45910</v>
       </c>
-      <c r="BA25" s="19"/>
-      <c r="BB25" s="19"/>
-      <c r="BC25" s="67"/>
-      <c r="BD25" s="67"/>
+      <c r="BA25" s="7">
+        <v>45908</v>
+      </c>
+      <c r="BB25" s="7">
+        <v>45910</v>
+      </c>
+      <c r="BC25" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD25" s="73"/>
     </row>
     <row r="26" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="60" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -3988,14 +4000,14 @@
       <c r="M26" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N26" s="37" t="s">
+      <c r="N26" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="O26" s="38"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
-      <c r="S26" s="39"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="42"/>
       <c r="T26" s="7">
         <v>45908</v>
       </c>
@@ -4004,8 +4016,8 @@
       </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="53"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="56"/>
       <c r="Z26" s="6" t="s">
         <v>63</v>
       </c>
@@ -4018,14 +4030,14 @@
       <c r="AC26" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AD26" s="37" t="s">
+      <c r="AD26" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="AE26" s="38"/>
-      <c r="AF26" s="38"/>
-      <c r="AG26" s="38"/>
-      <c r="AH26" s="38"/>
-      <c r="AI26" s="39"/>
+      <c r="AE26" s="41"/>
+      <c r="AF26" s="41"/>
+      <c r="AG26" s="41"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="42"/>
       <c r="AJ26" s="8">
         <v>45844</v>
       </c>
@@ -4034,7 +4046,7 @@
       </c>
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
-      <c r="AN26" s="46" t="s">
+      <c r="AN26" s="49" t="s">
         <v>20</v>
       </c>
       <c r="AO26" s="6" t="s">
@@ -4049,14 +4061,14 @@
       <c r="AR26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS26" s="37" t="s">
+      <c r="AS26" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="AT26" s="38"/>
-      <c r="AU26" s="38"/>
-      <c r="AV26" s="38"/>
-      <c r="AW26" s="38"/>
-      <c r="AX26" s="39"/>
+      <c r="AT26" s="41"/>
+      <c r="AU26" s="41"/>
+      <c r="AV26" s="41"/>
+      <c r="AW26" s="41"/>
+      <c r="AX26" s="42"/>
       <c r="AY26" s="7">
         <v>45908</v>
       </c>
@@ -4069,13 +4081,13 @@
       <c r="BB26" s="8">
         <v>45911</v>
       </c>
-      <c r="BC26" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD26" s="67"/>
+      <c r="BC26" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD26" s="73"/>
     </row>
     <row r="27" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I27" s="58"/>
+      <c r="I27" s="61"/>
       <c r="J27" s="18" t="s">
         <v>176</v>
       </c>
@@ -4088,14 +4100,14 @@
       <c r="M27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N27" s="37" t="s">
+      <c r="N27" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="O27" s="38"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="39"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="42"/>
       <c r="T27" s="7">
         <v>45908</v>
       </c>
@@ -4110,17 +4122,17 @@
       <c r="AA27" s="19"/>
       <c r="AB27" s="19"/>
       <c r="AC27" s="4"/>
-      <c r="AD27" s="40"/>
-      <c r="AE27" s="41"/>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="41"/>
-      <c r="AH27" s="41"/>
-      <c r="AI27" s="42"/>
+      <c r="AD27" s="43"/>
+      <c r="AE27" s="44"/>
+      <c r="AF27" s="44"/>
+      <c r="AG27" s="44"/>
+      <c r="AH27" s="44"/>
+      <c r="AI27" s="45"/>
       <c r="AJ27" s="7"/>
       <c r="AK27" s="7"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
-      <c r="AN27" s="47"/>
+      <c r="AN27" s="50"/>
       <c r="AO27" s="18" t="s">
         <v>176</v>
       </c>
@@ -4133,14 +4145,14 @@
       <c r="AR27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS27" s="37" t="s">
+      <c r="AS27" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="AT27" s="38"/>
-      <c r="AU27" s="38"/>
-      <c r="AV27" s="38"/>
-      <c r="AW27" s="38"/>
-      <c r="AX27" s="39"/>
+      <c r="AT27" s="41"/>
+      <c r="AU27" s="41"/>
+      <c r="AV27" s="41"/>
+      <c r="AW27" s="41"/>
+      <c r="AX27" s="42"/>
       <c r="AY27" s="7">
         <v>45908</v>
       </c>
@@ -4153,13 +4165,13 @@
       <c r="BB27" s="8">
         <v>45911</v>
       </c>
-      <c r="BC27" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD27" s="67"/>
+      <c r="BC27" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD27" s="73"/>
     </row>
     <row r="28" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I28" s="57" t="s">
+      <c r="I28" s="60" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -4174,14 +4186,14 @@
       <c r="M28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N28" s="37" t="s">
+      <c r="N28" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="39"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="42"/>
       <c r="T28" s="7">
         <v>45904</v>
       </c>
@@ -4190,10 +4202,10 @@
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
-      <c r="X28" s="103">
+      <c r="X28" s="67">
         <v>2.5</v>
       </c>
-      <c r="Y28" s="62">
+      <c r="Y28" s="65">
         <v>2</v>
       </c>
       <c r="Z28" s="6" t="s">
@@ -4208,14 +4220,14 @@
       <c r="AC28" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD28" s="37" t="s">
+      <c r="AD28" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="AE28" s="38"/>
-      <c r="AF28" s="38"/>
-      <c r="AG28" s="38"/>
-      <c r="AH28" s="38"/>
-      <c r="AI28" s="39"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="42"/>
       <c r="AJ28" s="7">
         <v>45844</v>
       </c>
@@ -4224,7 +4236,7 @@
       </c>
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
-      <c r="AN28" s="46" t="s">
+      <c r="AN28" s="49" t="s">
         <v>21</v>
       </c>
       <c r="AO28" s="6" t="s">
@@ -4239,27 +4251,33 @@
       <c r="AR28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS28" s="37" t="s">
+      <c r="AS28" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="AT28" s="38"/>
-      <c r="AU28" s="38"/>
-      <c r="AV28" s="38"/>
-      <c r="AW28" s="38"/>
-      <c r="AX28" s="39"/>
+      <c r="AT28" s="41"/>
+      <c r="AU28" s="41"/>
+      <c r="AV28" s="41"/>
+      <c r="AW28" s="41"/>
+      <c r="AX28" s="42"/>
       <c r="AY28" s="7">
         <v>45904</v>
       </c>
       <c r="AZ28" s="7">
         <v>45905</v>
       </c>
-      <c r="BA28" s="25"/>
-      <c r="BB28" s="25"/>
-      <c r="BC28" s="68"/>
-      <c r="BD28" s="68"/>
+      <c r="BA28" s="17">
+        <v>45904</v>
+      </c>
+      <c r="BB28" s="17">
+        <v>45905</v>
+      </c>
+      <c r="BC28" s="74">
+        <v>3</v>
+      </c>
+      <c r="BD28" s="74"/>
     </row>
     <row r="29" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I29" s="61"/>
+      <c r="I29" s="64"/>
       <c r="J29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4272,14 +4290,14 @@
       <c r="M29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="37" t="s">
+      <c r="N29" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="39"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="42"/>
       <c r="T29" s="7">
         <v>45904</v>
       </c>
@@ -4288,8 +4306,8 @@
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
-      <c r="X29" s="106"/>
-      <c r="Y29" s="66"/>
+      <c r="X29" s="71"/>
+      <c r="Y29" s="72"/>
       <c r="Z29" s="6" t="s">
         <v>167</v>
       </c>
@@ -4302,14 +4320,14 @@
       <c r="AC29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD29" s="37" t="s">
+      <c r="AD29" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="38"/>
-      <c r="AG29" s="38"/>
-      <c r="AH29" s="38"/>
-      <c r="AI29" s="39"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41"/>
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="42"/>
       <c r="AJ29" s="7">
         <v>45844</v>
       </c>
@@ -4318,7 +4336,7 @@
       </c>
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
-      <c r="AN29" s="74"/>
+      <c r="AN29" s="80"/>
       <c r="AO29" s="6" t="s">
         <v>67</v>
       </c>
@@ -4331,27 +4349,33 @@
       <c r="AR29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS29" s="37" t="s">
+      <c r="AS29" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="AT29" s="38"/>
-      <c r="AU29" s="38"/>
-      <c r="AV29" s="38"/>
-      <c r="AW29" s="38"/>
-      <c r="AX29" s="39"/>
+      <c r="AT29" s="41"/>
+      <c r="AU29" s="41"/>
+      <c r="AV29" s="41"/>
+      <c r="AW29" s="41"/>
+      <c r="AX29" s="42"/>
       <c r="AY29" s="7">
         <v>45904</v>
       </c>
       <c r="AZ29" s="7">
         <v>45905</v>
       </c>
-      <c r="BA29" s="19"/>
-      <c r="BB29" s="19"/>
-      <c r="BC29" s="67"/>
-      <c r="BD29" s="67"/>
+      <c r="BA29" s="17">
+        <v>45904</v>
+      </c>
+      <c r="BB29" s="8">
+        <v>45905</v>
+      </c>
+      <c r="BC29" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD29" s="73"/>
     </row>
     <row r="30" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I30" s="58"/>
+      <c r="I30" s="61"/>
       <c r="J30" s="6" t="s">
         <v>191</v>
       </c>
@@ -4364,14 +4388,14 @@
       <c r="M30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N30" s="37" t="s">
+      <c r="N30" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="O30" s="38"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="39"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="42"/>
       <c r="T30" s="7">
         <v>45904</v>
       </c>
@@ -4380,8 +4404,8 @@
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="63"/>
+      <c r="X30" s="68"/>
+      <c r="Y30" s="66"/>
       <c r="Z30" s="6" t="s">
         <v>65</v>
       </c>
@@ -4394,14 +4418,14 @@
       <c r="AC30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD30" s="37" t="s">
+      <c r="AD30" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="AE30" s="38"/>
-      <c r="AF30" s="38"/>
-      <c r="AG30" s="38"/>
-      <c r="AH30" s="38"/>
-      <c r="AI30" s="39"/>
+      <c r="AE30" s="41"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="41"/>
+      <c r="AH30" s="41"/>
+      <c r="AI30" s="42"/>
       <c r="AJ30" s="7">
         <v>45844</v>
       </c>
@@ -4410,7 +4434,7 @@
       </c>
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
-      <c r="AN30" s="47"/>
+      <c r="AN30" s="50"/>
       <c r="AO30" s="6" t="s">
         <v>191</v>
       </c>
@@ -4423,27 +4447,33 @@
       <c r="AR30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS30" s="37" t="s">
+      <c r="AS30" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="AT30" s="38"/>
-      <c r="AU30" s="38"/>
-      <c r="AV30" s="38"/>
-      <c r="AW30" s="38"/>
-      <c r="AX30" s="39"/>
+      <c r="AT30" s="41"/>
+      <c r="AU30" s="41"/>
+      <c r="AV30" s="41"/>
+      <c r="AW30" s="41"/>
+      <c r="AX30" s="42"/>
       <c r="AY30" s="7">
         <v>45904</v>
       </c>
       <c r="AZ30" s="7">
         <v>45905</v>
       </c>
-      <c r="BA30" s="19"/>
-      <c r="BB30" s="19"/>
-      <c r="BC30" s="67"/>
-      <c r="BD30" s="67"/>
+      <c r="BA30" s="17">
+        <v>45904</v>
+      </c>
+      <c r="BB30" s="8">
+        <v>45905</v>
+      </c>
+      <c r="BC30" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD30" s="73"/>
     </row>
     <row r="31" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I31" s="57">
+      <c r="I31" s="60">
         <v>4.2</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -4458,14 +4488,14 @@
       <c r="M31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N31" s="37" t="s">
+      <c r="N31" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="O31" s="38"/>
-      <c r="P31" s="38"/>
-      <c r="Q31" s="38"/>
-      <c r="R31" s="38"/>
-      <c r="S31" s="39"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="42"/>
       <c r="T31" s="7">
         <v>45907.041666666599</v>
       </c>
@@ -4480,17 +4510,17 @@
       <c r="AA31" s="19"/>
       <c r="AB31" s="19"/>
       <c r="AC31" s="4"/>
-      <c r="AD31" s="40"/>
-      <c r="AE31" s="41"/>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="41"/>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="42"/>
+      <c r="AD31" s="43"/>
+      <c r="AE31" s="44"/>
+      <c r="AF31" s="44"/>
+      <c r="AG31" s="44"/>
+      <c r="AH31" s="44"/>
+      <c r="AI31" s="45"/>
       <c r="AJ31" s="7"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
-      <c r="AN31" s="46">
+      <c r="AN31" s="49">
         <v>4.2</v>
       </c>
       <c r="AO31" s="6" t="s">
@@ -4505,27 +4535,33 @@
       <c r="AR31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS31" s="37" t="s">
+      <c r="AS31" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="AT31" s="38"/>
-      <c r="AU31" s="38"/>
-      <c r="AV31" s="38"/>
-      <c r="AW31" s="38"/>
-      <c r="AX31" s="39"/>
+      <c r="AT31" s="41"/>
+      <c r="AU31" s="41"/>
+      <c r="AV31" s="41"/>
+      <c r="AW31" s="41"/>
+      <c r="AX31" s="42"/>
       <c r="AY31" s="7">
         <v>45907.041666666599</v>
       </c>
       <c r="AZ31" s="7">
         <v>45909</v>
       </c>
-      <c r="BA31" s="19"/>
-      <c r="BB31" s="19"/>
-      <c r="BC31" s="67"/>
-      <c r="BD31" s="67"/>
+      <c r="BA31" s="17">
+        <v>45907</v>
+      </c>
+      <c r="BB31" s="8">
+        <v>45909</v>
+      </c>
+      <c r="BC31" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD31" s="73"/>
     </row>
     <row r="32" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="58"/>
+      <c r="I32" s="61"/>
       <c r="J32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4538,14 +4574,14 @@
       <c r="M32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N32" s="37" t="s">
+      <c r="N32" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="O32" s="38"/>
-      <c r="P32" s="38"/>
-      <c r="Q32" s="38"/>
-      <c r="R32" s="38"/>
-      <c r="S32" s="39"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="42"/>
       <c r="T32" s="7">
         <v>45910</v>
       </c>
@@ -4554,10 +4590,10 @@
       </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="103" t="s">
+      <c r="X32" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="Y32" s="62">
+      <c r="Y32" s="65">
         <v>2</v>
       </c>
       <c r="Z32" s="6" t="s">
@@ -4572,14 +4608,14 @@
       <c r="AC32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD32" s="37" t="s">
+      <c r="AD32" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="AE32" s="38"/>
-      <c r="AF32" s="38"/>
-      <c r="AG32" s="38"/>
-      <c r="AH32" s="38"/>
-      <c r="AI32" s="39"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="41"/>
+      <c r="AI32" s="42"/>
       <c r="AJ32" s="7">
         <v>45908</v>
       </c>
@@ -4588,7 +4624,7 @@
       </c>
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
-      <c r="AN32" s="47"/>
+      <c r="AN32" s="50"/>
       <c r="AO32" s="6" t="s">
         <v>68</v>
       </c>
@@ -4601,27 +4637,33 @@
       <c r="AR32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS32" s="37" t="s">
+      <c r="AS32" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="AT32" s="38"/>
-      <c r="AU32" s="38"/>
-      <c r="AV32" s="38"/>
-      <c r="AW32" s="38"/>
-      <c r="AX32" s="39"/>
+      <c r="AT32" s="41"/>
+      <c r="AU32" s="41"/>
+      <c r="AV32" s="41"/>
+      <c r="AW32" s="41"/>
+      <c r="AX32" s="42"/>
       <c r="AY32" s="7">
         <v>45910</v>
       </c>
       <c r="AZ32" s="7">
         <v>45912</v>
       </c>
-      <c r="BA32" s="19"/>
-      <c r="BB32" s="19"/>
-      <c r="BC32" s="67"/>
-      <c r="BD32" s="67"/>
+      <c r="BA32" s="8">
+        <v>45910</v>
+      </c>
+      <c r="BB32" s="8">
+        <v>45912</v>
+      </c>
+      <c r="BC32" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD32" s="73"/>
     </row>
     <row r="33" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I33" s="57">
+      <c r="I33" s="60">
         <v>4.3</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -4636,14 +4678,14 @@
       <c r="M33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N33" s="37" t="s">
+      <c r="N33" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="O33" s="38"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="38"/>
-      <c r="R33" s="38"/>
-      <c r="S33" s="39"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="42"/>
       <c r="T33" s="7">
         <v>45910</v>
       </c>
@@ -4652,8 +4694,8 @@
       </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="104"/>
-      <c r="Y33" s="63"/>
+      <c r="X33" s="68"/>
+      <c r="Y33" s="66"/>
       <c r="Z33" s="6" t="s">
         <v>66</v>
       </c>
@@ -4666,14 +4708,14 @@
       <c r="AC33" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD33" s="37" t="s">
+      <c r="AD33" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="AE33" s="38"/>
-      <c r="AF33" s="38"/>
-      <c r="AG33" s="38"/>
-      <c r="AH33" s="38"/>
-      <c r="AI33" s="39"/>
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="41"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="41"/>
+      <c r="AI33" s="42"/>
       <c r="AJ33" s="7">
         <v>45908</v>
       </c>
@@ -4682,7 +4724,7 @@
       </c>
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
-      <c r="AN33" s="46">
+      <c r="AN33" s="49">
         <v>4.3</v>
       </c>
       <c r="AO33" s="6" t="s">
@@ -4697,27 +4739,33 @@
       <c r="AR33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS33" s="37" t="s">
+      <c r="AS33" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="AT33" s="38"/>
-      <c r="AU33" s="38"/>
-      <c r="AV33" s="38"/>
-      <c r="AW33" s="38"/>
-      <c r="AX33" s="39"/>
+      <c r="AT33" s="41"/>
+      <c r="AU33" s="41"/>
+      <c r="AV33" s="41"/>
+      <c r="AW33" s="41"/>
+      <c r="AX33" s="42"/>
       <c r="AY33" s="7">
         <v>45910</v>
       </c>
       <c r="AZ33" s="7">
         <v>45912</v>
       </c>
-      <c r="BA33" s="19"/>
-      <c r="BB33" s="19"/>
-      <c r="BC33" s="67"/>
-      <c r="BD33" s="67"/>
+      <c r="BA33" s="8">
+        <v>45910</v>
+      </c>
+      <c r="BB33" s="8">
+        <v>45912</v>
+      </c>
+      <c r="BC33" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD33" s="73"/>
     </row>
     <row r="34" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I34" s="58"/>
+      <c r="I34" s="61"/>
       <c r="J34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4730,14 +4778,14 @@
       <c r="M34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N34" s="37" t="s">
+      <c r="N34" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="39"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="42"/>
       <c r="T34" s="7">
         <v>45910</v>
       </c>
@@ -4752,17 +4800,17 @@
       <c r="AA34" s="19"/>
       <c r="AB34" s="19"/>
       <c r="AC34" s="4"/>
-      <c r="AD34" s="40"/>
-      <c r="AE34" s="41"/>
-      <c r="AF34" s="41"/>
-      <c r="AG34" s="41"/>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="42"/>
+      <c r="AD34" s="43"/>
+      <c r="AE34" s="44"/>
+      <c r="AF34" s="44"/>
+      <c r="AG34" s="44"/>
+      <c r="AH34" s="44"/>
+      <c r="AI34" s="45"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
-      <c r="AN34" s="47"/>
+      <c r="AN34" s="50"/>
       <c r="AO34" s="6" t="s">
         <v>180</v>
       </c>
@@ -4775,27 +4823,33 @@
       <c r="AR34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS34" s="37" t="s">
+      <c r="AS34" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="AT34" s="38"/>
-      <c r="AU34" s="38"/>
-      <c r="AV34" s="38"/>
-      <c r="AW34" s="38"/>
-      <c r="AX34" s="39"/>
+      <c r="AT34" s="41"/>
+      <c r="AU34" s="41"/>
+      <c r="AV34" s="41"/>
+      <c r="AW34" s="41"/>
+      <c r="AX34" s="42"/>
       <c r="AY34" s="7">
         <v>45910</v>
       </c>
       <c r="AZ34" s="7">
         <v>45912</v>
       </c>
-      <c r="BA34" s="19"/>
-      <c r="BB34" s="19"/>
-      <c r="BC34" s="67"/>
-      <c r="BD34" s="67"/>
+      <c r="BA34" s="8">
+        <v>45910</v>
+      </c>
+      <c r="BB34" s="8">
+        <v>45912</v>
+      </c>
+      <c r="BC34" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD34" s="73"/>
     </row>
     <row r="35" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I35" s="57">
+      <c r="I35" s="60">
         <v>4.4000000000000004</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -4810,14 +4864,14 @@
       <c r="M35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N35" s="37" t="s">
+      <c r="N35" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="O35" s="38"/>
-      <c r="P35" s="38"/>
-      <c r="Q35" s="38"/>
-      <c r="R35" s="38"/>
-      <c r="S35" s="39"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="42"/>
       <c r="T35" s="7">
         <v>45910</v>
       </c>
@@ -4826,10 +4880,10 @@
       </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="103" t="s">
+      <c r="X35" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="52">
+      <c r="Y35" s="55">
         <v>3</v>
       </c>
       <c r="Z35" s="6" t="s">
@@ -4844,14 +4898,14 @@
       <c r="AC35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD35" s="37" t="s">
+      <c r="AD35" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="AE35" s="38"/>
-      <c r="AF35" s="38"/>
-      <c r="AG35" s="38"/>
-      <c r="AH35" s="38"/>
-      <c r="AI35" s="39"/>
+      <c r="AE35" s="41"/>
+      <c r="AF35" s="41"/>
+      <c r="AG35" s="41"/>
+      <c r="AH35" s="41"/>
+      <c r="AI35" s="42"/>
       <c r="AJ35" s="7">
         <v>45908</v>
       </c>
@@ -4860,7 +4914,7 @@
       </c>
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
-      <c r="AN35" s="46">
+      <c r="AN35" s="49">
         <v>4.4000000000000004</v>
       </c>
       <c r="AO35" s="6" t="s">
@@ -4875,27 +4929,33 @@
       <c r="AR35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS35" s="37" t="s">
+      <c r="AS35" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="AT35" s="38"/>
-      <c r="AU35" s="38"/>
-      <c r="AV35" s="38"/>
-      <c r="AW35" s="38"/>
-      <c r="AX35" s="39"/>
+      <c r="AT35" s="41"/>
+      <c r="AU35" s="41"/>
+      <c r="AV35" s="41"/>
+      <c r="AW35" s="41"/>
+      <c r="AX35" s="42"/>
       <c r="AY35" s="7">
         <v>45910</v>
       </c>
       <c r="AZ35" s="7">
         <v>45915</v>
       </c>
-      <c r="BA35" s="19"/>
-      <c r="BB35" s="19"/>
-      <c r="BC35" s="67"/>
-      <c r="BD35" s="67"/>
+      <c r="BA35" s="8">
+        <v>45910</v>
+      </c>
+      <c r="BB35" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BC35" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD35" s="73"/>
     </row>
     <row r="36" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I36" s="58"/>
+      <c r="I36" s="61"/>
       <c r="J36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4908,14 +4968,14 @@
       <c r="M36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N36" s="37" t="s">
+      <c r="N36" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="O36" s="38"/>
-      <c r="P36" s="38"/>
-      <c r="Q36" s="38"/>
-      <c r="R36" s="38"/>
-      <c r="S36" s="39"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="42"/>
       <c r="T36" s="7">
         <v>45910</v>
       </c>
@@ -4924,8 +4984,8 @@
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
-      <c r="X36" s="104"/>
-      <c r="Y36" s="53"/>
+      <c r="X36" s="68"/>
+      <c r="Y36" s="56"/>
       <c r="Z36" s="18" t="s">
         <v>176</v>
       </c>
@@ -4938,14 +4998,14 @@
       <c r="AC36" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD36" s="37" t="s">
+      <c r="AD36" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="AE36" s="38"/>
-      <c r="AF36" s="38"/>
-      <c r="AG36" s="38"/>
-      <c r="AH36" s="38"/>
-      <c r="AI36" s="39"/>
+      <c r="AE36" s="41"/>
+      <c r="AF36" s="41"/>
+      <c r="AG36" s="41"/>
+      <c r="AH36" s="41"/>
+      <c r="AI36" s="42"/>
       <c r="AJ36" s="7">
         <v>45908</v>
       </c>
@@ -4954,7 +5014,7 @@
       </c>
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
-      <c r="AN36" s="47"/>
+      <c r="AN36" s="50"/>
       <c r="AO36" s="6" t="s">
         <v>70</v>
       </c>
@@ -4967,27 +5027,33 @@
       <c r="AR36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS36" s="37" t="s">
+      <c r="AS36" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="AT36" s="38"/>
-      <c r="AU36" s="38"/>
-      <c r="AV36" s="38"/>
-      <c r="AW36" s="38"/>
-      <c r="AX36" s="39"/>
+      <c r="AT36" s="41"/>
+      <c r="AU36" s="41"/>
+      <c r="AV36" s="41"/>
+      <c r="AW36" s="41"/>
+      <c r="AX36" s="42"/>
       <c r="AY36" s="7">
         <v>45910</v>
       </c>
       <c r="AZ36" s="7">
         <v>45915</v>
       </c>
-      <c r="BA36" s="19"/>
-      <c r="BB36" s="19"/>
-      <c r="BC36" s="67"/>
-      <c r="BD36" s="67"/>
+      <c r="BA36" s="8">
+        <v>45910</v>
+      </c>
+      <c r="BB36" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BC36" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD36" s="73"/>
     </row>
     <row r="37" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I37" s="57">
+      <c r="I37" s="60">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -5002,14 +5068,14 @@
       <c r="M37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N37" s="37" t="s">
+      <c r="N37" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="O37" s="38"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="38"/>
-      <c r="R37" s="38"/>
-      <c r="S37" s="39"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="42"/>
       <c r="T37" s="7">
         <v>45915</v>
       </c>
@@ -5024,17 +5090,17 @@
       <c r="AA37" s="19"/>
       <c r="AB37" s="19"/>
       <c r="AC37" s="4"/>
-      <c r="AD37" s="40"/>
-      <c r="AE37" s="41"/>
-      <c r="AF37" s="41"/>
-      <c r="AG37" s="41"/>
-      <c r="AH37" s="41"/>
-      <c r="AI37" s="42"/>
+      <c r="AD37" s="43"/>
+      <c r="AE37" s="44"/>
+      <c r="AF37" s="44"/>
+      <c r="AG37" s="44"/>
+      <c r="AH37" s="44"/>
+      <c r="AI37" s="45"/>
       <c r="AJ37" s="7"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
-      <c r="AN37" s="46">
+      <c r="AN37" s="49">
         <v>4.5999999999999996</v>
       </c>
       <c r="AO37" s="6" t="s">
@@ -5049,27 +5115,33 @@
       <c r="AR37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS37" s="37" t="s">
+      <c r="AS37" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="AT37" s="38"/>
-      <c r="AU37" s="38"/>
-      <c r="AV37" s="38"/>
-      <c r="AW37" s="38"/>
-      <c r="AX37" s="39"/>
+      <c r="AT37" s="41"/>
+      <c r="AU37" s="41"/>
+      <c r="AV37" s="41"/>
+      <c r="AW37" s="41"/>
+      <c r="AX37" s="42"/>
       <c r="AY37" s="7">
         <v>45915</v>
       </c>
       <c r="AZ37" s="7">
         <v>45916</v>
       </c>
-      <c r="BA37" s="19"/>
-      <c r="BB37" s="19"/>
-      <c r="BC37" s="67"/>
-      <c r="BD37" s="67"/>
+      <c r="BA37" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BB37" s="7">
+        <v>45916</v>
+      </c>
+      <c r="BC37" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD37" s="73"/>
     </row>
     <row r="38" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I38" s="58"/>
+      <c r="I38" s="61"/>
       <c r="J38" s="6" t="s">
         <v>193</v>
       </c>
@@ -5082,14 +5154,14 @@
       <c r="M38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N38" s="37" t="s">
+      <c r="N38" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="O38" s="38"/>
-      <c r="P38" s="38"/>
-      <c r="Q38" s="38"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="39"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="42"/>
       <c r="T38" s="7">
         <v>45915</v>
       </c>
@@ -5098,10 +5170,10 @@
       </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
-      <c r="X38" s="103" t="s">
+      <c r="X38" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="Y38" s="50">
+      <c r="Y38" s="53">
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="s">
@@ -5116,14 +5188,14 @@
       <c r="AC38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD38" s="37" t="s">
+      <c r="AD38" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="AE38" s="38"/>
-      <c r="AF38" s="38"/>
-      <c r="AG38" s="38"/>
-      <c r="AH38" s="38"/>
-      <c r="AI38" s="39"/>
+      <c r="AE38" s="41"/>
+      <c r="AF38" s="41"/>
+      <c r="AG38" s="41"/>
+      <c r="AH38" s="41"/>
+      <c r="AI38" s="42"/>
       <c r="AJ38" s="7">
         <v>45904</v>
       </c>
@@ -5132,7 +5204,7 @@
       </c>
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
-      <c r="AN38" s="47"/>
+      <c r="AN38" s="50"/>
       <c r="AO38" s="6" t="s">
         <v>193</v>
       </c>
@@ -5145,24 +5217,30 @@
       <c r="AR38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS38" s="37" t="s">
+      <c r="AS38" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="AT38" s="38"/>
-      <c r="AU38" s="38"/>
-      <c r="AV38" s="38"/>
-      <c r="AW38" s="38"/>
-      <c r="AX38" s="39"/>
+      <c r="AT38" s="41"/>
+      <c r="AU38" s="41"/>
+      <c r="AV38" s="41"/>
+      <c r="AW38" s="41"/>
+      <c r="AX38" s="42"/>
       <c r="AY38" s="7">
         <v>45915</v>
       </c>
       <c r="AZ38" s="7">
         <v>45917.041666666599</v>
       </c>
-      <c r="BA38" s="19"/>
-      <c r="BB38" s="19"/>
-      <c r="BC38" s="67"/>
-      <c r="BD38" s="67"/>
+      <c r="BA38" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BB38" s="7">
+        <v>45918.041666666664</v>
+      </c>
+      <c r="BC38" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD38" s="73"/>
     </row>
     <row r="39" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I39" s="36">
@@ -5180,14 +5258,14 @@
       <c r="M39" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N39" s="37" t="s">
+      <c r="N39" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="O39" s="38"/>
-      <c r="P39" s="38"/>
-      <c r="Q39" s="38"/>
-      <c r="R39" s="38"/>
-      <c r="S39" s="39"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="42"/>
       <c r="T39" s="7">
         <v>45915</v>
       </c>
@@ -5196,8 +5274,8 @@
       </c>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="106"/>
-      <c r="Y39" s="75"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="81"/>
       <c r="Z39" s="6" t="s">
         <v>67</v>
       </c>
@@ -5210,14 +5288,14 @@
       <c r="AC39" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD39" s="37" t="s">
+      <c r="AD39" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="AE39" s="38"/>
-      <c r="AF39" s="38"/>
-      <c r="AG39" s="38"/>
-      <c r="AH39" s="38"/>
-      <c r="AI39" s="39"/>
+      <c r="AE39" s="41"/>
+      <c r="AF39" s="41"/>
+      <c r="AG39" s="41"/>
+      <c r="AH39" s="41"/>
+      <c r="AI39" s="42"/>
       <c r="AJ39" s="7">
         <v>45904</v>
       </c>
@@ -5241,27 +5319,33 @@
       <c r="AR39" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS39" s="37" t="s">
+      <c r="AS39" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="AT39" s="38"/>
-      <c r="AU39" s="38"/>
-      <c r="AV39" s="38"/>
-      <c r="AW39" s="38"/>
-      <c r="AX39" s="39"/>
+      <c r="AT39" s="41"/>
+      <c r="AU39" s="41"/>
+      <c r="AV39" s="41"/>
+      <c r="AW39" s="41"/>
+      <c r="AX39" s="42"/>
       <c r="AY39" s="7">
         <v>45915</v>
       </c>
       <c r="AZ39" s="7">
         <v>45917.041666666599</v>
       </c>
-      <c r="BA39" s="19"/>
-      <c r="BB39" s="19"/>
-      <c r="BC39" s="67"/>
-      <c r="BD39" s="67"/>
+      <c r="BA39" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BB39" s="7">
+        <v>45918.041666666664</v>
+      </c>
+      <c r="BC39" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD39" s="73"/>
     </row>
     <row r="40" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I40" s="57">
+      <c r="I40" s="60">
         <v>5.0999999999999996</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -5276,14 +5360,14 @@
       <c r="M40" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N40" s="37" t="s">
+      <c r="N40" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="O40" s="38"/>
-      <c r="P40" s="38"/>
-      <c r="Q40" s="38"/>
-      <c r="R40" s="38"/>
-      <c r="S40" s="39"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="41"/>
+      <c r="S40" s="42"/>
       <c r="T40" s="7">
         <v>45915</v>
       </c>
@@ -5292,8 +5376,8 @@
       </c>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="104"/>
-      <c r="Y40" s="51"/>
+      <c r="X40" s="68"/>
+      <c r="Y40" s="54"/>
       <c r="Z40" s="6" t="s">
         <v>191</v>
       </c>
@@ -5306,14 +5390,14 @@
       <c r="AC40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD40" s="37" t="s">
+      <c r="AD40" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="AE40" s="38"/>
-      <c r="AF40" s="38"/>
-      <c r="AG40" s="38"/>
-      <c r="AH40" s="38"/>
-      <c r="AI40" s="39"/>
+      <c r="AE40" s="41"/>
+      <c r="AF40" s="41"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="41"/>
+      <c r="AI40" s="42"/>
       <c r="AJ40" s="7">
         <v>45904</v>
       </c>
@@ -5322,7 +5406,7 @@
       </c>
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
-      <c r="AN40" s="46">
+      <c r="AN40" s="49">
         <v>5.0999999999999996</v>
       </c>
       <c r="AO40" s="6" t="s">
@@ -5337,27 +5421,33 @@
       <c r="AR40" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS40" s="37" t="s">
+      <c r="AS40" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="AT40" s="38"/>
-      <c r="AU40" s="38"/>
-      <c r="AV40" s="38"/>
-      <c r="AW40" s="38"/>
-      <c r="AX40" s="39"/>
+      <c r="AT40" s="41"/>
+      <c r="AU40" s="41"/>
+      <c r="AV40" s="41"/>
+      <c r="AW40" s="41"/>
+      <c r="AX40" s="42"/>
       <c r="AY40" s="7">
         <v>45915</v>
       </c>
       <c r="AZ40" s="7">
         <v>45917.041666666599</v>
       </c>
-      <c r="BA40" s="25"/>
-      <c r="BB40" s="25"/>
-      <c r="BC40" s="68"/>
-      <c r="BD40" s="68"/>
+      <c r="BA40" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BB40" s="7">
+        <v>45918.041666666664</v>
+      </c>
+      <c r="BC40" s="74">
+        <v>4</v>
+      </c>
+      <c r="BD40" s="74"/>
     </row>
     <row r="41" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="58"/>
+      <c r="I41" s="61"/>
       <c r="J41" s="6" t="s">
         <v>200</v>
       </c>
@@ -5370,14 +5460,14 @@
       <c r="M41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N41" s="43" t="s">
+      <c r="N41" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="45"/>
+      <c r="O41" s="47"/>
+      <c r="P41" s="47"/>
+      <c r="Q41" s="47"/>
+      <c r="R41" s="47"/>
+      <c r="S41" s="48"/>
       <c r="T41" s="7">
         <v>45915</v>
       </c>
@@ -5392,17 +5482,17 @@
       <c r="AA41" s="19"/>
       <c r="AB41" s="19"/>
       <c r="AC41" s="4"/>
-      <c r="AD41" s="40"/>
-      <c r="AE41" s="41"/>
-      <c r="AF41" s="41"/>
-      <c r="AG41" s="41"/>
-      <c r="AH41" s="41"/>
-      <c r="AI41" s="42"/>
+      <c r="AD41" s="43"/>
+      <c r="AE41" s="44"/>
+      <c r="AF41" s="44"/>
+      <c r="AG41" s="44"/>
+      <c r="AH41" s="44"/>
+      <c r="AI41" s="45"/>
       <c r="AJ41" s="7"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="20"/>
       <c r="AM41" s="20"/>
-      <c r="AN41" s="47"/>
+      <c r="AN41" s="50"/>
       <c r="AO41" s="6" t="s">
         <v>200</v>
       </c>
@@ -5415,24 +5505,30 @@
       <c r="AR41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS41" s="43" t="s">
+      <c r="AS41" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="AT41" s="44"/>
-      <c r="AU41" s="44"/>
-      <c r="AV41" s="44"/>
-      <c r="AW41" s="44"/>
-      <c r="AX41" s="45"/>
+      <c r="AT41" s="47"/>
+      <c r="AU41" s="47"/>
+      <c r="AV41" s="47"/>
+      <c r="AW41" s="47"/>
+      <c r="AX41" s="48"/>
       <c r="AY41" s="7">
         <v>45915</v>
       </c>
       <c r="AZ41" s="7">
         <v>45917.041666666599</v>
       </c>
-      <c r="BA41" s="19"/>
-      <c r="BB41" s="19"/>
-      <c r="BC41" s="67"/>
-      <c r="BD41" s="67"/>
+      <c r="BA41" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BB41" s="7">
+        <v>45918.041666666664</v>
+      </c>
+      <c r="BC41" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD41" s="73"/>
     </row>
     <row r="42" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I42" s="36">
@@ -5450,14 +5546,14 @@
       <c r="M42" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N42" s="37" t="s">
+      <c r="N42" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="O42" s="38"/>
-      <c r="P42" s="38"/>
-      <c r="Q42" s="38"/>
-      <c r="R42" s="38"/>
-      <c r="S42" s="39"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="42"/>
       <c r="T42" s="7">
         <v>45910</v>
       </c>
@@ -5466,10 +5562,10 @@
       </c>
       <c r="V42" s="20"/>
       <c r="W42" s="20"/>
-      <c r="X42" s="46">
+      <c r="X42" s="49">
         <v>4.2</v>
       </c>
-      <c r="Y42" s="50">
+      <c r="Y42" s="53">
         <v>1</v>
       </c>
       <c r="Z42" s="6" t="s">
@@ -5484,14 +5580,14 @@
       <c r="AC42" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD42" s="37" t="s">
+      <c r="AD42" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="AE42" s="38"/>
-      <c r="AF42" s="38"/>
-      <c r="AG42" s="38"/>
-      <c r="AH42" s="38"/>
-      <c r="AI42" s="39"/>
+      <c r="AE42" s="41"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="41"/>
+      <c r="AI42" s="42"/>
       <c r="AJ42" s="7">
         <v>45907.041666666599</v>
       </c>
@@ -5515,27 +5611,33 @@
       <c r="AR42" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS42" s="37" t="s">
+      <c r="AS42" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="AT42" s="38"/>
-      <c r="AU42" s="38"/>
-      <c r="AV42" s="38"/>
-      <c r="AW42" s="38"/>
-      <c r="AX42" s="39"/>
+      <c r="AT42" s="41"/>
+      <c r="AU42" s="41"/>
+      <c r="AV42" s="41"/>
+      <c r="AW42" s="41"/>
+      <c r="AX42" s="42"/>
       <c r="AY42" s="7">
         <v>45910</v>
       </c>
       <c r="AZ42" s="7">
         <v>45911</v>
       </c>
-      <c r="BA42" s="19"/>
-      <c r="BB42" s="19"/>
-      <c r="BC42" s="67"/>
-      <c r="BD42" s="67"/>
+      <c r="BA42" s="7">
+        <v>45910</v>
+      </c>
+      <c r="BB42" s="7">
+        <v>45911</v>
+      </c>
+      <c r="BC42" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD42" s="73"/>
     </row>
     <row r="43" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I43" s="57">
+      <c r="I43" s="60">
         <v>1.6</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -5550,14 +5652,14 @@
       <c r="M43" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N43" s="37" t="s">
+      <c r="N43" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="O43" s="38"/>
-      <c r="P43" s="38"/>
-      <c r="Q43" s="38"/>
-      <c r="R43" s="38"/>
-      <c r="S43" s="39"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="41"/>
+      <c r="S43" s="42"/>
       <c r="T43" s="7">
         <v>45911</v>
       </c>
@@ -5566,8 +5668,8 @@
       </c>
       <c r="V43" s="20"/>
       <c r="W43" s="20"/>
-      <c r="X43" s="47"/>
-      <c r="Y43" s="51"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="54"/>
       <c r="Z43" s="6" t="s">
         <v>68</v>
       </c>
@@ -5580,14 +5682,14 @@
       <c r="AC43" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD43" s="37" t="s">
+      <c r="AD43" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="AE43" s="38"/>
-      <c r="AF43" s="38"/>
-      <c r="AG43" s="38"/>
-      <c r="AH43" s="38"/>
-      <c r="AI43" s="39"/>
+      <c r="AE43" s="41"/>
+      <c r="AF43" s="41"/>
+      <c r="AG43" s="41"/>
+      <c r="AH43" s="41"/>
+      <c r="AI43" s="42"/>
       <c r="AJ43" s="7">
         <v>45910</v>
       </c>
@@ -5596,7 +5698,7 @@
       </c>
       <c r="AL43" s="20"/>
       <c r="AM43" s="20"/>
-      <c r="AN43" s="46">
+      <c r="AN43" s="49">
         <v>1.6</v>
       </c>
       <c r="AO43" s="6" t="s">
@@ -5611,27 +5713,33 @@
       <c r="AR43" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS43" s="37" t="s">
+      <c r="AS43" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="AT43" s="38"/>
-      <c r="AU43" s="38"/>
-      <c r="AV43" s="38"/>
-      <c r="AW43" s="38"/>
-      <c r="AX43" s="39"/>
+      <c r="AT43" s="41"/>
+      <c r="AU43" s="41"/>
+      <c r="AV43" s="41"/>
+      <c r="AW43" s="41"/>
+      <c r="AX43" s="42"/>
       <c r="AY43" s="7">
         <v>45911</v>
       </c>
       <c r="AZ43" s="7">
         <v>45913</v>
       </c>
-      <c r="BA43" s="19"/>
-      <c r="BB43" s="19"/>
-      <c r="BC43" s="67"/>
-      <c r="BD43" s="67"/>
+      <c r="BA43" s="7">
+        <v>45911</v>
+      </c>
+      <c r="BB43" s="7">
+        <v>45913</v>
+      </c>
+      <c r="BC43" s="73">
+        <v>3</v>
+      </c>
+      <c r="BD43" s="73"/>
     </row>
     <row r="44" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I44" s="58"/>
+      <c r="I44" s="61"/>
       <c r="J44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5644,14 +5752,14 @@
       <c r="M44" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N44" s="37" t="s">
+      <c r="N44" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="O44" s="38"/>
-      <c r="P44" s="38"/>
-      <c r="Q44" s="38"/>
-      <c r="R44" s="38"/>
-      <c r="S44" s="39"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="41"/>
+      <c r="S44" s="42"/>
       <c r="T44" s="7">
         <v>45911</v>
       </c>
@@ -5666,17 +5774,17 @@
       <c r="AA44" s="19"/>
       <c r="AB44" s="19"/>
       <c r="AC44" s="4"/>
-      <c r="AD44" s="40"/>
-      <c r="AE44" s="41"/>
-      <c r="AF44" s="41"/>
-      <c r="AG44" s="41"/>
-      <c r="AH44" s="41"/>
-      <c r="AI44" s="42"/>
+      <c r="AD44" s="43"/>
+      <c r="AE44" s="44"/>
+      <c r="AF44" s="44"/>
+      <c r="AG44" s="44"/>
+      <c r="AH44" s="44"/>
+      <c r="AI44" s="45"/>
       <c r="AJ44" s="7"/>
       <c r="AK44" s="7"/>
       <c r="AL44" s="20"/>
       <c r="AM44" s="20"/>
-      <c r="AN44" s="47"/>
+      <c r="AN44" s="50"/>
       <c r="AO44" s="15" t="s">
         <v>183</v>
       </c>
@@ -5689,24 +5797,30 @@
       <c r="AR44" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS44" s="37" t="s">
+      <c r="AS44" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="AT44" s="38"/>
-      <c r="AU44" s="38"/>
-      <c r="AV44" s="38"/>
-      <c r="AW44" s="38"/>
-      <c r="AX44" s="39"/>
+      <c r="AT44" s="41"/>
+      <c r="AU44" s="41"/>
+      <c r="AV44" s="41"/>
+      <c r="AW44" s="41"/>
+      <c r="AX44" s="42"/>
       <c r="AY44" s="7">
         <v>45911</v>
       </c>
       <c r="AZ44" s="7">
         <v>45913</v>
       </c>
-      <c r="BA44" s="19"/>
-      <c r="BB44" s="19"/>
-      <c r="BC44" s="67"/>
-      <c r="BD44" s="67"/>
+      <c r="BA44" s="7">
+        <v>45911</v>
+      </c>
+      <c r="BB44" s="7">
+        <v>45913</v>
+      </c>
+      <c r="BC44" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD44" s="73"/>
     </row>
     <row r="45" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I45" s="36">
@@ -5724,14 +5838,14 @@
       <c r="M45" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N45" s="37" t="s">
+      <c r="N45" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="O45" s="38"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
-      <c r="R45" s="38"/>
-      <c r="S45" s="39"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="41"/>
+      <c r="S45" s="42"/>
       <c r="T45" s="7">
         <v>45911</v>
       </c>
@@ -5740,10 +5854,10 @@
       </c>
       <c r="V45" s="20"/>
       <c r="W45" s="20"/>
-      <c r="X45" s="46">
+      <c r="X45" s="49">
         <v>4.3</v>
       </c>
-      <c r="Y45" s="62">
+      <c r="Y45" s="65">
         <v>2</v>
       </c>
       <c r="Z45" s="6" t="s">
@@ -5758,14 +5872,14 @@
       <c r="AC45" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD45" s="37" t="s">
+      <c r="AD45" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="AE45" s="38"/>
-      <c r="AF45" s="38"/>
-      <c r="AG45" s="38"/>
-      <c r="AH45" s="38"/>
-      <c r="AI45" s="39"/>
+      <c r="AE45" s="41"/>
+      <c r="AF45" s="41"/>
+      <c r="AG45" s="41"/>
+      <c r="AH45" s="41"/>
+      <c r="AI45" s="42"/>
       <c r="AJ45" s="7">
         <v>45910</v>
       </c>
@@ -5789,14 +5903,14 @@
       <c r="AR45" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS45" s="37" t="s">
+      <c r="AS45" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="AT45" s="38"/>
-      <c r="AU45" s="38"/>
-      <c r="AV45" s="38"/>
-      <c r="AW45" s="38"/>
-      <c r="AX45" s="39"/>
+      <c r="AT45" s="41"/>
+      <c r="AU45" s="41"/>
+      <c r="AV45" s="41"/>
+      <c r="AW45" s="41"/>
+      <c r="AX45" s="42"/>
       <c r="AY45" s="7">
         <v>45911</v>
       </c>
@@ -5809,14 +5923,14 @@
       <c r="BB45" s="8">
         <v>45915</v>
       </c>
-      <c r="BC45" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD45" s="67"/>
-      <c r="BG45" s="101"/>
+      <c r="BC45" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD45" s="73"/>
+      <c r="BG45" s="37"/>
     </row>
     <row r="46" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I46" s="57" t="s">
+      <c r="I46" s="60" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -5831,14 +5945,14 @@
       <c r="M46" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N46" s="37" t="s">
+      <c r="N46" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="O46" s="38"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="38"/>
-      <c r="R46" s="38"/>
-      <c r="S46" s="39"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="42"/>
       <c r="T46" s="7">
         <v>45913</v>
       </c>
@@ -5847,8 +5961,8 @@
       </c>
       <c r="V46" s="20"/>
       <c r="W46" s="20"/>
-      <c r="X46" s="47"/>
-      <c r="Y46" s="63"/>
+      <c r="X46" s="50"/>
+      <c r="Y46" s="66"/>
       <c r="Z46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5861,14 +5975,14 @@
       <c r="AC46" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD46" s="37" t="s">
+      <c r="AD46" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="AE46" s="38"/>
-      <c r="AF46" s="38"/>
-      <c r="AG46" s="38"/>
-      <c r="AH46" s="38"/>
-      <c r="AI46" s="39"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="41"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="41"/>
+      <c r="AI46" s="42"/>
       <c r="AJ46" s="7">
         <v>45910</v>
       </c>
@@ -5877,7 +5991,7 @@
       </c>
       <c r="AL46" s="20"/>
       <c r="AM46" s="20"/>
-      <c r="AN46" s="46" t="s">
+      <c r="AN46" s="49" t="s">
         <v>22</v>
       </c>
       <c r="AO46" s="6" t="s">
@@ -5892,14 +6006,14 @@
       <c r="AR46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS46" s="37" t="s">
+      <c r="AS46" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="AT46" s="38"/>
-      <c r="AU46" s="38"/>
-      <c r="AV46" s="38"/>
-      <c r="AW46" s="38"/>
-      <c r="AX46" s="39"/>
+      <c r="AT46" s="41"/>
+      <c r="AU46" s="41"/>
+      <c r="AV46" s="41"/>
+      <c r="AW46" s="41"/>
+      <c r="AX46" s="42"/>
       <c r="AY46" s="7">
         <v>45913</v>
       </c>
@@ -5912,13 +6026,13 @@
       <c r="BB46" s="8">
         <v>45909</v>
       </c>
-      <c r="BC46" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD46" s="67"/>
+      <c r="BC46" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD46" s="73"/>
     </row>
     <row r="47" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I47" s="58"/>
+      <c r="I47" s="61"/>
       <c r="J47" s="6" t="s">
         <v>184</v>
       </c>
@@ -5931,14 +6045,14 @@
       <c r="M47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N47" s="37" t="s">
+      <c r="N47" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="O47" s="38"/>
-      <c r="P47" s="38"/>
-      <c r="Q47" s="38"/>
-      <c r="R47" s="38"/>
-      <c r="S47" s="39"/>
+      <c r="O47" s="41"/>
+      <c r="P47" s="41"/>
+      <c r="Q47" s="41"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="42"/>
       <c r="T47" s="7">
         <v>45913</v>
       </c>
@@ -5953,17 +6067,17 @@
       <c r="AA47" s="19"/>
       <c r="AB47" s="19"/>
       <c r="AC47" s="4"/>
-      <c r="AD47" s="40"/>
-      <c r="AE47" s="41"/>
-      <c r="AF47" s="41"/>
-      <c r="AG47" s="41"/>
-      <c r="AH47" s="41"/>
-      <c r="AI47" s="42"/>
+      <c r="AD47" s="43"/>
+      <c r="AE47" s="44"/>
+      <c r="AF47" s="44"/>
+      <c r="AG47" s="44"/>
+      <c r="AH47" s="44"/>
+      <c r="AI47" s="45"/>
       <c r="AJ47" s="7"/>
       <c r="AK47" s="7"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="20"/>
-      <c r="AN47" s="47"/>
+      <c r="AN47" s="50"/>
       <c r="AO47" s="6" t="s">
         <v>184</v>
       </c>
@@ -5976,14 +6090,14 @@
       <c r="AR47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS47" s="37" t="s">
+      <c r="AS47" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="AT47" s="38"/>
-      <c r="AU47" s="38"/>
-      <c r="AV47" s="38"/>
-      <c r="AW47" s="38"/>
-      <c r="AX47" s="39"/>
+      <c r="AT47" s="41"/>
+      <c r="AU47" s="41"/>
+      <c r="AV47" s="41"/>
+      <c r="AW47" s="41"/>
+      <c r="AX47" s="42"/>
       <c r="AY47" s="7">
         <v>45913</v>
       </c>
@@ -5996,13 +6110,13 @@
       <c r="BB47" s="34">
         <v>45909</v>
       </c>
-      <c r="BC47" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD47" s="67"/>
+      <c r="BC47" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD47" s="73"/>
     </row>
     <row r="48" spans="9:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I48" s="57" t="s">
+      <c r="I48" s="60" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -6017,14 +6131,14 @@
       <c r="M48" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="37" t="s">
+      <c r="N48" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="O48" s="38"/>
-      <c r="P48" s="38"/>
-      <c r="Q48" s="38"/>
-      <c r="R48" s="38"/>
-      <c r="S48" s="39"/>
+      <c r="O48" s="41"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="41"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="42"/>
       <c r="T48" s="7">
         <v>45914</v>
       </c>
@@ -6033,10 +6147,10 @@
       </c>
       <c r="V48" s="20"/>
       <c r="W48" s="20"/>
-      <c r="X48" s="46">
+      <c r="X48" s="49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="Y48" s="52">
+      <c r="Y48" s="55">
         <v>3</v>
       </c>
       <c r="Z48" s="6" t="s">
@@ -6051,14 +6165,14 @@
       <c r="AC48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD48" s="37" t="s">
+      <c r="AD48" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="AE48" s="38"/>
-      <c r="AF48" s="38"/>
-      <c r="AG48" s="38"/>
-      <c r="AH48" s="38"/>
-      <c r="AI48" s="39"/>
+      <c r="AE48" s="41"/>
+      <c r="AF48" s="41"/>
+      <c r="AG48" s="41"/>
+      <c r="AH48" s="41"/>
+      <c r="AI48" s="42"/>
       <c r="AJ48" s="7">
         <v>45910</v>
       </c>
@@ -6067,7 +6181,7 @@
       </c>
       <c r="AL48" s="20"/>
       <c r="AM48" s="20"/>
-      <c r="AN48" s="46" t="s">
+      <c r="AN48" s="49" t="s">
         <v>23</v>
       </c>
       <c r="AO48" s="6" t="s">
@@ -6082,14 +6196,14 @@
       <c r="AR48" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS48" s="37" t="s">
+      <c r="AS48" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="AT48" s="38"/>
-      <c r="AU48" s="38"/>
-      <c r="AV48" s="38"/>
-      <c r="AW48" s="38"/>
-      <c r="AX48" s="39"/>
+      <c r="AT48" s="41"/>
+      <c r="AU48" s="41"/>
+      <c r="AV48" s="41"/>
+      <c r="AW48" s="41"/>
+      <c r="AX48" s="42"/>
       <c r="AY48" s="7">
         <v>45914</v>
       </c>
@@ -6102,13 +6216,13 @@
       <c r="BB48" s="8">
         <v>45909</v>
       </c>
-      <c r="BC48" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD48" s="67"/>
+      <c r="BC48" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD48" s="73"/>
     </row>
     <row r="49" spans="8:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="58"/>
+      <c r="I49" s="61"/>
       <c r="J49" s="6" t="s">
         <v>185</v>
       </c>
@@ -6121,14 +6235,14 @@
       <c r="M49" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N49" s="37" t="s">
+      <c r="N49" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="O49" s="38"/>
-      <c r="P49" s="38"/>
-      <c r="Q49" s="38"/>
-      <c r="R49" s="38"/>
-      <c r="S49" s="39"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="41"/>
+      <c r="S49" s="42"/>
       <c r="T49" s="7">
         <v>45914</v>
       </c>
@@ -6137,8 +6251,8 @@
       </c>
       <c r="V49" s="20"/>
       <c r="W49" s="20"/>
-      <c r="X49" s="47"/>
-      <c r="Y49" s="53"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="56"/>
       <c r="Z49" s="6" t="s">
         <v>70</v>
       </c>
@@ -6151,14 +6265,14 @@
       <c r="AC49" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD49" s="37" t="s">
+      <c r="AD49" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="AE49" s="38"/>
-      <c r="AF49" s="38"/>
-      <c r="AG49" s="38"/>
-      <c r="AH49" s="38"/>
-      <c r="AI49" s="39"/>
+      <c r="AE49" s="41"/>
+      <c r="AF49" s="41"/>
+      <c r="AG49" s="41"/>
+      <c r="AH49" s="41"/>
+      <c r="AI49" s="42"/>
       <c r="AJ49" s="7">
         <v>45910</v>
       </c>
@@ -6167,7 +6281,7 @@
       </c>
       <c r="AL49" s="20"/>
       <c r="AM49" s="20"/>
-      <c r="AN49" s="47"/>
+      <c r="AN49" s="50"/>
       <c r="AO49" s="6" t="s">
         <v>185</v>
       </c>
@@ -6180,14 +6294,14 @@
       <c r="AR49" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AS49" s="37" t="s">
+      <c r="AS49" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="AT49" s="38"/>
-      <c r="AU49" s="38"/>
-      <c r="AV49" s="38"/>
-      <c r="AW49" s="38"/>
-      <c r="AX49" s="39"/>
+      <c r="AT49" s="41"/>
+      <c r="AU49" s="41"/>
+      <c r="AV49" s="41"/>
+      <c r="AW49" s="41"/>
+      <c r="AX49" s="42"/>
       <c r="AY49" s="7">
         <v>45914</v>
       </c>
@@ -6200,14 +6314,14 @@
       <c r="BB49" s="8">
         <v>45909</v>
       </c>
-      <c r="BC49" s="67">
-        <v>2</v>
-      </c>
-      <c r="BD49" s="67"/>
+      <c r="BC49" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD49" s="73"/>
     </row>
     <row r="50" spans="8:56" x14ac:dyDescent="0.25">
       <c r="H50" s="10"/>
-      <c r="I50" s="57">
+      <c r="I50" s="60">
         <v>3.2</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -6222,14 +6336,14 @@
       <c r="M50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N50" s="43" t="s">
+      <c r="N50" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="45"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="47"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="48"/>
       <c r="T50" s="7">
         <v>45907</v>
       </c>
@@ -6244,17 +6358,17 @@
       <c r="AA50" s="19"/>
       <c r="AB50" s="19"/>
       <c r="AC50" s="4"/>
-      <c r="AD50" s="40"/>
-      <c r="AE50" s="41"/>
-      <c r="AF50" s="41"/>
-      <c r="AG50" s="41"/>
-      <c r="AH50" s="41"/>
-      <c r="AI50" s="42"/>
+      <c r="AD50" s="43"/>
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="44"/>
+      <c r="AG50" s="44"/>
+      <c r="AH50" s="44"/>
+      <c r="AI50" s="45"/>
       <c r="AJ50" s="19"/>
       <c r="AK50" s="19"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="20"/>
-      <c r="AN50" s="46">
+      <c r="AN50" s="49">
         <v>3.2</v>
       </c>
       <c r="AO50" s="6" t="s">
@@ -6269,14 +6383,14 @@
       <c r="AR50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS50" s="43" t="s">
+      <c r="AS50" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="AT50" s="44"/>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="44"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="45"/>
+      <c r="AT50" s="47"/>
+      <c r="AU50" s="47"/>
+      <c r="AV50" s="47"/>
+      <c r="AW50" s="47"/>
+      <c r="AX50" s="48"/>
       <c r="AY50" s="7">
         <v>45907</v>
       </c>
@@ -6285,11 +6399,11 @@
       </c>
       <c r="BA50" s="19"/>
       <c r="BB50" s="19"/>
-      <c r="BC50" s="67"/>
-      <c r="BD50" s="67"/>
+      <c r="BC50" s="73"/>
+      <c r="BD50" s="73"/>
     </row>
     <row r="51" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I51" s="58"/>
+      <c r="I51" s="61"/>
       <c r="J51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6302,14 +6416,14 @@
       <c r="M51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N51" s="43" t="s">
+      <c r="N51" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="45"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="47"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47"/>
+      <c r="S51" s="48"/>
       <c r="T51" s="7">
         <v>45907</v>
       </c>
@@ -6318,10 +6432,10 @@
       </c>
       <c r="V51" s="20"/>
       <c r="W51" s="20"/>
-      <c r="X51" s="46">
+      <c r="X51" s="49">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y51" s="50">
+      <c r="Y51" s="53">
         <v>1</v>
       </c>
       <c r="Z51" s="6" t="s">
@@ -6336,14 +6450,14 @@
       <c r="AC51" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD51" s="37" t="s">
+      <c r="AD51" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="AE51" s="38"/>
-      <c r="AF51" s="38"/>
-      <c r="AG51" s="38"/>
-      <c r="AH51" s="38"/>
-      <c r="AI51" s="39"/>
+      <c r="AE51" s="41"/>
+      <c r="AF51" s="41"/>
+      <c r="AG51" s="41"/>
+      <c r="AH51" s="41"/>
+      <c r="AI51" s="42"/>
       <c r="AJ51" s="7">
         <v>45915</v>
       </c>
@@ -6352,7 +6466,7 @@
       </c>
       <c r="AL51" s="20"/>
       <c r="AM51" s="20"/>
-      <c r="AN51" s="47"/>
+      <c r="AN51" s="50"/>
       <c r="AO51" s="6" t="s">
         <v>71</v>
       </c>
@@ -6365,14 +6479,14 @@
       <c r="AR51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS51" s="43" t="s">
+      <c r="AS51" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="AT51" s="44"/>
-      <c r="AU51" s="44"/>
-      <c r="AV51" s="44"/>
-      <c r="AW51" s="44"/>
-      <c r="AX51" s="45"/>
+      <c r="AT51" s="47"/>
+      <c r="AU51" s="47"/>
+      <c r="AV51" s="47"/>
+      <c r="AW51" s="47"/>
+      <c r="AX51" s="48"/>
       <c r="AY51" s="7">
         <v>45907</v>
       </c>
@@ -6381,11 +6495,11 @@
       </c>
       <c r="BA51" s="19"/>
       <c r="BB51" s="19"/>
-      <c r="BC51" s="67"/>
-      <c r="BD51" s="67"/>
+      <c r="BC51" s="73"/>
+      <c r="BD51" s="73"/>
     </row>
     <row r="52" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I52" s="57">
+      <c r="I52" s="60">
         <v>3.3</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6400,14 +6514,14 @@
       <c r="M52" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N52" s="37" t="s">
+      <c r="N52" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="O52" s="38"/>
-      <c r="P52" s="38"/>
-      <c r="Q52" s="38"/>
-      <c r="R52" s="38"/>
-      <c r="S52" s="39"/>
+      <c r="O52" s="41"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="41"/>
+      <c r="R52" s="41"/>
+      <c r="S52" s="42"/>
       <c r="T52" s="7">
         <v>45907</v>
       </c>
@@ -6416,8 +6530,8 @@
       </c>
       <c r="V52" s="20"/>
       <c r="W52" s="20"/>
-      <c r="X52" s="47"/>
-      <c r="Y52" s="51"/>
+      <c r="X52" s="50"/>
+      <c r="Y52" s="54"/>
       <c r="Z52" s="6" t="s">
         <v>193</v>
       </c>
@@ -6430,14 +6544,14 @@
       <c r="AC52" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD52" s="37" t="s">
+      <c r="AD52" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="AE52" s="38"/>
-      <c r="AF52" s="38"/>
-      <c r="AG52" s="38"/>
-      <c r="AH52" s="38"/>
-      <c r="AI52" s="39"/>
+      <c r="AE52" s="41"/>
+      <c r="AF52" s="41"/>
+      <c r="AG52" s="41"/>
+      <c r="AH52" s="41"/>
+      <c r="AI52" s="42"/>
       <c r="AJ52" s="7">
         <v>45915</v>
       </c>
@@ -6446,7 +6560,7 @@
       </c>
       <c r="AL52" s="20"/>
       <c r="AM52" s="20"/>
-      <c r="AN52" s="46">
+      <c r="AN52" s="49">
         <v>3.3</v>
       </c>
       <c r="AO52" s="6" t="s">
@@ -6461,14 +6575,14 @@
       <c r="AR52" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS52" s="37" t="s">
+      <c r="AS52" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="AT52" s="38"/>
-      <c r="AU52" s="38"/>
-      <c r="AV52" s="38"/>
-      <c r="AW52" s="38"/>
-      <c r="AX52" s="39"/>
+      <c r="AT52" s="41"/>
+      <c r="AU52" s="41"/>
+      <c r="AV52" s="41"/>
+      <c r="AW52" s="41"/>
+      <c r="AX52" s="42"/>
       <c r="AY52" s="7">
         <v>45907</v>
       </c>
@@ -6477,11 +6591,11 @@
       </c>
       <c r="BA52" s="25"/>
       <c r="BB52" s="25"/>
-      <c r="BC52" s="68"/>
-      <c r="BD52" s="68"/>
+      <c r="BC52" s="74"/>
+      <c r="BD52" s="74"/>
     </row>
     <row r="53" spans="8:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I53" s="58"/>
+      <c r="I53" s="61"/>
       <c r="J53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6494,14 +6608,14 @@
       <c r="M53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N53" s="37" t="s">
+      <c r="N53" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="O53" s="38"/>
-      <c r="P53" s="38"/>
-      <c r="Q53" s="38"/>
-      <c r="R53" s="38"/>
-      <c r="S53" s="39"/>
+      <c r="O53" s="41"/>
+      <c r="P53" s="41"/>
+      <c r="Q53" s="41"/>
+      <c r="R53" s="41"/>
+      <c r="S53" s="42"/>
       <c r="T53" s="7">
         <v>45907</v>
       </c>
@@ -6516,17 +6630,17 @@
       <c r="AA53" s="19"/>
       <c r="AB53" s="19"/>
       <c r="AC53" s="4"/>
-      <c r="AD53" s="40"/>
-      <c r="AE53" s="41"/>
-      <c r="AF53" s="41"/>
-      <c r="AG53" s="41"/>
-      <c r="AH53" s="41"/>
-      <c r="AI53" s="42"/>
+      <c r="AD53" s="43"/>
+      <c r="AE53" s="44"/>
+      <c r="AF53" s="44"/>
+      <c r="AG53" s="44"/>
+      <c r="AH53" s="44"/>
+      <c r="AI53" s="45"/>
       <c r="AJ53" s="19"/>
       <c r="AK53" s="19"/>
       <c r="AL53" s="20"/>
       <c r="AM53" s="20"/>
-      <c r="AN53" s="47"/>
+      <c r="AN53" s="50"/>
       <c r="AO53" s="6" t="s">
         <v>72</v>
       </c>
@@ -6539,14 +6653,14 @@
       <c r="AR53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS53" s="37" t="s">
+      <c r="AS53" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="AT53" s="38"/>
-      <c r="AU53" s="38"/>
-      <c r="AV53" s="38"/>
-      <c r="AW53" s="38"/>
-      <c r="AX53" s="39"/>
+      <c r="AT53" s="41"/>
+      <c r="AU53" s="41"/>
+      <c r="AV53" s="41"/>
+      <c r="AW53" s="41"/>
+      <c r="AX53" s="42"/>
       <c r="AY53" s="7">
         <v>45907</v>
       </c>
@@ -6555,11 +6669,11 @@
       </c>
       <c r="BA53" s="19"/>
       <c r="BB53" s="19"/>
-      <c r="BC53" s="67"/>
-      <c r="BD53" s="67"/>
+      <c r="BC53" s="73"/>
+      <c r="BD53" s="73"/>
     </row>
     <row r="54" spans="8:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I54" s="57">
+      <c r="I54" s="60">
         <v>3.4</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6574,14 +6688,14 @@
       <c r="M54" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N54" s="37" t="s">
+      <c r="N54" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="O54" s="38"/>
-      <c r="P54" s="38"/>
-      <c r="Q54" s="38"/>
-      <c r="R54" s="38"/>
-      <c r="S54" s="39"/>
+      <c r="O54" s="41"/>
+      <c r="P54" s="41"/>
+      <c r="Q54" s="41"/>
+      <c r="R54" s="41"/>
+      <c r="S54" s="42"/>
       <c r="T54" s="7">
         <v>45908</v>
       </c>
@@ -6608,14 +6722,14 @@
       <c r="AC54" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD54" s="37" t="s">
+      <c r="AD54" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="AE54" s="38"/>
-      <c r="AF54" s="38"/>
-      <c r="AG54" s="38"/>
-      <c r="AH54" s="38"/>
-      <c r="AI54" s="39"/>
+      <c r="AE54" s="41"/>
+      <c r="AF54" s="41"/>
+      <c r="AG54" s="41"/>
+      <c r="AH54" s="41"/>
+      <c r="AI54" s="42"/>
       <c r="AJ54" s="7">
         <v>45915</v>
       </c>
@@ -6624,7 +6738,7 @@
       </c>
       <c r="AL54" s="20"/>
       <c r="AM54" s="20"/>
-      <c r="AN54" s="46">
+      <c r="AN54" s="49">
         <v>3.4</v>
       </c>
       <c r="AO54" s="6" t="s">
@@ -6639,14 +6753,14 @@
       <c r="AR54" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS54" s="37" t="s">
+      <c r="AS54" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="AT54" s="38"/>
-      <c r="AU54" s="38"/>
-      <c r="AV54" s="38"/>
-      <c r="AW54" s="38"/>
-      <c r="AX54" s="39"/>
+      <c r="AT54" s="41"/>
+      <c r="AU54" s="41"/>
+      <c r="AV54" s="41"/>
+      <c r="AW54" s="41"/>
+      <c r="AX54" s="42"/>
       <c r="AY54" s="7">
         <v>45908</v>
       </c>
@@ -6655,11 +6769,11 @@
       </c>
       <c r="BA54" s="19"/>
       <c r="BB54" s="19"/>
-      <c r="BC54" s="67"/>
-      <c r="BD54" s="67"/>
+      <c r="BC54" s="73"/>
+      <c r="BD54" s="73"/>
     </row>
     <row r="55" spans="8:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I55" s="58"/>
+      <c r="I55" s="61"/>
       <c r="J55" s="18" t="s">
         <v>195</v>
       </c>
@@ -6672,14 +6786,14 @@
       <c r="M55" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N55" s="37" t="s">
+      <c r="N55" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="O55" s="38"/>
-      <c r="P55" s="38"/>
-      <c r="Q55" s="38"/>
-      <c r="R55" s="38"/>
-      <c r="S55" s="39"/>
+      <c r="O55" s="41"/>
+      <c r="P55" s="41"/>
+      <c r="Q55" s="41"/>
+      <c r="R55" s="41"/>
+      <c r="S55" s="42"/>
       <c r="T55" s="7">
         <v>45908</v>
       </c>
@@ -6694,17 +6808,17 @@
       <c r="AA55" s="19"/>
       <c r="AB55" s="19"/>
       <c r="AC55" s="4"/>
-      <c r="AD55" s="40"/>
-      <c r="AE55" s="41"/>
-      <c r="AF55" s="41"/>
-      <c r="AG55" s="41"/>
-      <c r="AH55" s="41"/>
-      <c r="AI55" s="42"/>
+      <c r="AD55" s="43"/>
+      <c r="AE55" s="44"/>
+      <c r="AF55" s="44"/>
+      <c r="AG55" s="44"/>
+      <c r="AH55" s="44"/>
+      <c r="AI55" s="45"/>
       <c r="AJ55" s="19"/>
       <c r="AK55" s="19"/>
       <c r="AL55" s="20"/>
       <c r="AM55" s="20"/>
-      <c r="AN55" s="47"/>
+      <c r="AN55" s="50"/>
       <c r="AO55" s="18" t="s">
         <v>195</v>
       </c>
@@ -6717,14 +6831,14 @@
       <c r="AR55" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS55" s="37" t="s">
+      <c r="AS55" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="AT55" s="38"/>
-      <c r="AU55" s="38"/>
-      <c r="AV55" s="38"/>
-      <c r="AW55" s="38"/>
-      <c r="AX55" s="39"/>
+      <c r="AT55" s="41"/>
+      <c r="AU55" s="41"/>
+      <c r="AV55" s="41"/>
+      <c r="AW55" s="41"/>
+      <c r="AX55" s="42"/>
       <c r="AY55" s="7">
         <v>45908</v>
       </c>
@@ -6733,8 +6847,8 @@
       </c>
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
-      <c r="BC55" s="67"/>
-      <c r="BD55" s="67"/>
+      <c r="BC55" s="73"/>
+      <c r="BD55" s="73"/>
     </row>
     <row r="56" spans="8:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I56" s="36">
@@ -6752,14 +6866,14 @@
       <c r="M56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N56" s="37" t="s">
+      <c r="N56" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="O56" s="38"/>
-      <c r="P56" s="38"/>
-      <c r="Q56" s="38"/>
-      <c r="R56" s="38"/>
-      <c r="S56" s="39"/>
+      <c r="O56" s="41"/>
+      <c r="P56" s="41"/>
+      <c r="Q56" s="41"/>
+      <c r="R56" s="41"/>
+      <c r="S56" s="42"/>
       <c r="T56" s="7">
         <v>45908</v>
       </c>
@@ -6768,10 +6882,10 @@
       </c>
       <c r="V56" s="20"/>
       <c r="W56" s="20"/>
-      <c r="X56" s="46">
+      <c r="X56" s="49">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Y56" s="62">
+      <c r="Y56" s="65">
         <v>2</v>
       </c>
       <c r="Z56" s="6" t="s">
@@ -6786,14 +6900,14 @@
       <c r="AC56" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD56" s="37" t="s">
+      <c r="AD56" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="AE56" s="38"/>
-      <c r="AF56" s="38"/>
-      <c r="AG56" s="38"/>
-      <c r="AH56" s="38"/>
-      <c r="AI56" s="39"/>
+      <c r="AE56" s="41"/>
+      <c r="AF56" s="41"/>
+      <c r="AG56" s="41"/>
+      <c r="AH56" s="41"/>
+      <c r="AI56" s="42"/>
       <c r="AJ56" s="7">
         <v>45915</v>
       </c>
@@ -6817,14 +6931,14 @@
       <c r="AR56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS56" s="37" t="s">
+      <c r="AS56" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="AT56" s="38"/>
-      <c r="AU56" s="38"/>
-      <c r="AV56" s="38"/>
-      <c r="AW56" s="38"/>
-      <c r="AX56" s="39"/>
+      <c r="AT56" s="41"/>
+      <c r="AU56" s="41"/>
+      <c r="AV56" s="41"/>
+      <c r="AW56" s="41"/>
+      <c r="AX56" s="42"/>
       <c r="AY56" s="7">
         <v>45908</v>
       </c>
@@ -6833,11 +6947,11 @@
       </c>
       <c r="BA56" s="19"/>
       <c r="BB56" s="19"/>
-      <c r="BC56" s="67"/>
-      <c r="BD56" s="67"/>
+      <c r="BC56" s="73"/>
+      <c r="BD56" s="73"/>
     </row>
     <row r="57" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I57" s="57">
+      <c r="I57" s="60">
         <v>3.6</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6852,14 +6966,14 @@
       <c r="M57" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N57" s="37" t="s">
+      <c r="N57" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="O57" s="38"/>
-      <c r="P57" s="38"/>
-      <c r="Q57" s="38"/>
-      <c r="R57" s="38"/>
-      <c r="S57" s="39"/>
+      <c r="O57" s="41"/>
+      <c r="P57" s="41"/>
+      <c r="Q57" s="41"/>
+      <c r="R57" s="41"/>
+      <c r="S57" s="42"/>
       <c r="T57" s="7">
         <v>45909</v>
       </c>
@@ -6868,8 +6982,8 @@
       </c>
       <c r="V57" s="20"/>
       <c r="W57" s="20"/>
-      <c r="X57" s="47"/>
-      <c r="Y57" s="63"/>
+      <c r="X57" s="50"/>
+      <c r="Y57" s="66"/>
       <c r="Z57" s="6" t="s">
         <v>200</v>
       </c>
@@ -6880,14 +6994,14 @@
       <c r="AC57" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD57" s="43" t="s">
+      <c r="AD57" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="AE57" s="44"/>
-      <c r="AF57" s="44"/>
-      <c r="AG57" s="44"/>
-      <c r="AH57" s="44"/>
-      <c r="AI57" s="45"/>
+      <c r="AE57" s="47"/>
+      <c r="AF57" s="47"/>
+      <c r="AG57" s="47"/>
+      <c r="AH57" s="47"/>
+      <c r="AI57" s="48"/>
       <c r="AJ57" s="7">
         <v>45915</v>
       </c>
@@ -6896,7 +7010,7 @@
       </c>
       <c r="AL57" s="20"/>
       <c r="AM57" s="20"/>
-      <c r="AN57" s="46">
+      <c r="AN57" s="49">
         <v>3.6</v>
       </c>
       <c r="AO57" s="6" t="s">
@@ -6911,14 +7025,14 @@
       <c r="AR57" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS57" s="37" t="s">
+      <c r="AS57" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="AT57" s="38"/>
-      <c r="AU57" s="38"/>
-      <c r="AV57" s="38"/>
-      <c r="AW57" s="38"/>
-      <c r="AX57" s="39"/>
+      <c r="AT57" s="41"/>
+      <c r="AU57" s="41"/>
+      <c r="AV57" s="41"/>
+      <c r="AW57" s="41"/>
+      <c r="AX57" s="42"/>
       <c r="AY57" s="7">
         <v>45909</v>
       </c>
@@ -6927,11 +7041,11 @@
       </c>
       <c r="BA57" s="19"/>
       <c r="BB57" s="19"/>
-      <c r="BC57" s="67"/>
-      <c r="BD57" s="67"/>
+      <c r="BC57" s="73"/>
+      <c r="BD57" s="73"/>
     </row>
     <row r="58" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I58" s="58"/>
+      <c r="I58" s="61"/>
       <c r="J58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6944,14 +7058,14 @@
       <c r="M58" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N58" s="37" t="s">
+      <c r="N58" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="O58" s="38"/>
-      <c r="P58" s="38"/>
-      <c r="Q58" s="38"/>
-      <c r="R58" s="38"/>
-      <c r="S58" s="39"/>
+      <c r="O58" s="41"/>
+      <c r="P58" s="41"/>
+      <c r="Q58" s="41"/>
+      <c r="R58" s="41"/>
+      <c r="S58" s="42"/>
       <c r="T58" s="7">
         <v>45909</v>
       </c>
@@ -6966,17 +7080,17 @@
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
       <c r="AC58" s="4"/>
-      <c r="AD58" s="40"/>
-      <c r="AE58" s="41"/>
-      <c r="AF58" s="41"/>
-      <c r="AG58" s="41"/>
-      <c r="AH58" s="41"/>
-      <c r="AI58" s="42"/>
+      <c r="AD58" s="43"/>
+      <c r="AE58" s="44"/>
+      <c r="AF58" s="44"/>
+      <c r="AG58" s="44"/>
+      <c r="AH58" s="44"/>
+      <c r="AI58" s="45"/>
       <c r="AJ58" s="19"/>
       <c r="AK58" s="19"/>
       <c r="AL58" s="20"/>
       <c r="AM58" s="20"/>
-      <c r="AN58" s="47"/>
+      <c r="AN58" s="50"/>
       <c r="AO58" s="6" t="s">
         <v>73</v>
       </c>
@@ -6989,14 +7103,14 @@
       <c r="AR58" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS58" s="37" t="s">
+      <c r="AS58" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="AT58" s="38"/>
-      <c r="AU58" s="38"/>
-      <c r="AV58" s="38"/>
-      <c r="AW58" s="38"/>
-      <c r="AX58" s="39"/>
+      <c r="AT58" s="41"/>
+      <c r="AU58" s="41"/>
+      <c r="AV58" s="41"/>
+      <c r="AW58" s="41"/>
+      <c r="AX58" s="42"/>
       <c r="AY58" s="7">
         <v>45909</v>
       </c>
@@ -7005,11 +7119,11 @@
       </c>
       <c r="BA58" s="19"/>
       <c r="BB58" s="19"/>
-      <c r="BC58" s="67"/>
-      <c r="BD58" s="67"/>
+      <c r="BC58" s="73"/>
+      <c r="BD58" s="73"/>
     </row>
     <row r="59" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I59" s="57">
+      <c r="I59" s="60">
         <v>3.7</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -7024,14 +7138,14 @@
       <c r="M59" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N59" s="37" t="s">
+      <c r="N59" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="O59" s="38"/>
-      <c r="P59" s="38"/>
-      <c r="Q59" s="38"/>
-      <c r="R59" s="38"/>
-      <c r="S59" s="39"/>
+      <c r="O59" s="41"/>
+      <c r="P59" s="41"/>
+      <c r="Q59" s="41"/>
+      <c r="R59" s="41"/>
+      <c r="S59" s="42"/>
       <c r="T59" s="7">
         <v>45909</v>
       </c>
@@ -7040,7 +7154,7 @@
       </c>
       <c r="V59" s="20"/>
       <c r="W59" s="20"/>
-      <c r="X59" s="102">
+      <c r="X59" s="38">
         <v>6.1</v>
       </c>
       <c r="Y59" s="26">
@@ -7058,14 +7172,14 @@
       <c r="AC59" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD59" s="37" t="s">
+      <c r="AD59" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="AE59" s="38"/>
-      <c r="AF59" s="38"/>
-      <c r="AG59" s="38"/>
-      <c r="AH59" s="38"/>
-      <c r="AI59" s="39"/>
+      <c r="AE59" s="41"/>
+      <c r="AF59" s="41"/>
+      <c r="AG59" s="41"/>
+      <c r="AH59" s="41"/>
+      <c r="AI59" s="42"/>
       <c r="AJ59" s="7">
         <v>45910</v>
       </c>
@@ -7074,7 +7188,7 @@
       </c>
       <c r="AL59" s="20"/>
       <c r="AM59" s="20"/>
-      <c r="AN59" s="46">
+      <c r="AN59" s="49">
         <v>3.7</v>
       </c>
       <c r="AO59" s="6" t="s">
@@ -7089,14 +7203,14 @@
       <c r="AR59" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS59" s="37" t="s">
+      <c r="AS59" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="AT59" s="38"/>
-      <c r="AU59" s="38"/>
-      <c r="AV59" s="38"/>
-      <c r="AW59" s="38"/>
-      <c r="AX59" s="39"/>
+      <c r="AT59" s="41"/>
+      <c r="AU59" s="41"/>
+      <c r="AV59" s="41"/>
+      <c r="AW59" s="41"/>
+      <c r="AX59" s="42"/>
       <c r="AY59" s="7">
         <v>45909</v>
       </c>
@@ -7105,11 +7219,11 @@
       </c>
       <c r="BA59" s="19"/>
       <c r="BB59" s="19"/>
-      <c r="BC59" s="67"/>
-      <c r="BD59" s="67"/>
+      <c r="BC59" s="73"/>
+      <c r="BD59" s="73"/>
     </row>
     <row r="60" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I60" s="58"/>
+      <c r="I60" s="61"/>
       <c r="J60" s="6" t="s">
         <v>74</v>
       </c>
@@ -7122,14 +7236,14 @@
       <c r="M60" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N60" s="37" t="s">
+      <c r="N60" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="O60" s="38"/>
-      <c r="P60" s="38"/>
-      <c r="Q60" s="38"/>
-      <c r="R60" s="38"/>
-      <c r="S60" s="39"/>
+      <c r="O60" s="41"/>
+      <c r="P60" s="41"/>
+      <c r="Q60" s="41"/>
+      <c r="R60" s="41"/>
+      <c r="S60" s="42"/>
       <c r="T60" s="7">
         <v>45909</v>
       </c>
@@ -7144,17 +7258,17 @@
       <c r="AA60" s="19"/>
       <c r="AB60" s="19"/>
       <c r="AC60" s="4"/>
-      <c r="AD60" s="40"/>
-      <c r="AE60" s="41"/>
-      <c r="AF60" s="41"/>
-      <c r="AG60" s="41"/>
-      <c r="AH60" s="41"/>
-      <c r="AI60" s="42"/>
+      <c r="AD60" s="43"/>
+      <c r="AE60" s="44"/>
+      <c r="AF60" s="44"/>
+      <c r="AG60" s="44"/>
+      <c r="AH60" s="44"/>
+      <c r="AI60" s="45"/>
       <c r="AJ60" s="19"/>
       <c r="AK60" s="19"/>
       <c r="AL60" s="20"/>
       <c r="AM60" s="20"/>
-      <c r="AN60" s="47"/>
+      <c r="AN60" s="50"/>
       <c r="AO60" s="6" t="s">
         <v>74</v>
       </c>
@@ -7167,14 +7281,14 @@
       <c r="AR60" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS60" s="37" t="s">
+      <c r="AS60" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="AT60" s="38"/>
-      <c r="AU60" s="38"/>
-      <c r="AV60" s="38"/>
-      <c r="AW60" s="38"/>
-      <c r="AX60" s="39"/>
+      <c r="AT60" s="41"/>
+      <c r="AU60" s="41"/>
+      <c r="AV60" s="41"/>
+      <c r="AW60" s="41"/>
+      <c r="AX60" s="42"/>
       <c r="AY60" s="7">
         <v>45909</v>
       </c>
@@ -7183,11 +7297,11 @@
       </c>
       <c r="BA60" s="19"/>
       <c r="BB60" s="19"/>
-      <c r="BC60" s="67"/>
-      <c r="BD60" s="67"/>
+      <c r="BC60" s="73"/>
+      <c r="BD60" s="73"/>
     </row>
     <row r="61" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I61" s="57" t="s">
+      <c r="I61" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -7202,14 +7316,14 @@
       <c r="M61" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N61" s="37" t="s">
+      <c r="N61" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="O61" s="38"/>
-      <c r="P61" s="38"/>
-      <c r="Q61" s="38"/>
-      <c r="R61" s="38"/>
-      <c r="S61" s="39"/>
+      <c r="O61" s="41"/>
+      <c r="P61" s="41"/>
+      <c r="Q61" s="41"/>
+      <c r="R61" s="41"/>
+      <c r="S61" s="42"/>
       <c r="T61" s="7">
         <v>45909</v>
       </c>
@@ -7218,10 +7332,10 @@
       </c>
       <c r="V61" s="20"/>
       <c r="W61" s="20"/>
-      <c r="X61" s="103">
+      <c r="X61" s="67">
         <v>1.6</v>
       </c>
-      <c r="Y61" s="64">
+      <c r="Y61" s="69">
         <v>4</v>
       </c>
       <c r="Z61" s="6" t="s">
@@ -7236,14 +7350,14 @@
       <c r="AC61" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD61" s="37" t="s">
+      <c r="AD61" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="AE61" s="38"/>
-      <c r="AF61" s="38"/>
-      <c r="AG61" s="38"/>
-      <c r="AH61" s="38"/>
-      <c r="AI61" s="39"/>
+      <c r="AE61" s="41"/>
+      <c r="AF61" s="41"/>
+      <c r="AG61" s="41"/>
+      <c r="AH61" s="41"/>
+      <c r="AI61" s="42"/>
       <c r="AJ61" s="7">
         <v>45911</v>
       </c>
@@ -7252,7 +7366,7 @@
       </c>
       <c r="AL61" s="20"/>
       <c r="AM61" s="20"/>
-      <c r="AN61" s="46" t="s">
+      <c r="AN61" s="49" t="s">
         <v>24</v>
       </c>
       <c r="AO61" s="6" t="s">
@@ -7267,14 +7381,14 @@
       <c r="AR61" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS61" s="37" t="s">
+      <c r="AS61" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="AT61" s="38"/>
-      <c r="AU61" s="38"/>
-      <c r="AV61" s="38"/>
-      <c r="AW61" s="38"/>
-      <c r="AX61" s="39"/>
+      <c r="AT61" s="41"/>
+      <c r="AU61" s="41"/>
+      <c r="AV61" s="41"/>
+      <c r="AW61" s="41"/>
+      <c r="AX61" s="42"/>
       <c r="AY61" s="7">
         <v>45909</v>
       </c>
@@ -7283,11 +7397,11 @@
       </c>
       <c r="BA61" s="19"/>
       <c r="BB61" s="19"/>
-      <c r="BC61" s="67"/>
-      <c r="BD61" s="67"/>
+      <c r="BC61" s="73"/>
+      <c r="BD61" s="73"/>
     </row>
     <row r="62" spans="8:56" x14ac:dyDescent="0.25">
-      <c r="I62" s="58"/>
+      <c r="I62" s="61"/>
       <c r="J62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7300,14 +7414,14 @@
       <c r="M62" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N62" s="37" t="s">
+      <c r="N62" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="O62" s="38"/>
-      <c r="P62" s="38"/>
-      <c r="Q62" s="38"/>
-      <c r="R62" s="38"/>
-      <c r="S62" s="39"/>
+      <c r="O62" s="41"/>
+      <c r="P62" s="41"/>
+      <c r="Q62" s="41"/>
+      <c r="R62" s="41"/>
+      <c r="S62" s="42"/>
       <c r="T62" s="7">
         <v>45910</v>
       </c>
@@ -7316,8 +7430,8 @@
       </c>
       <c r="V62" s="20"/>
       <c r="W62" s="20"/>
-      <c r="X62" s="104"/>
-      <c r="Y62" s="65"/>
+      <c r="X62" s="68"/>
+      <c r="Y62" s="70"/>
       <c r="Z62" s="15" t="s">
         <v>183</v>
       </c>
@@ -7330,14 +7444,14 @@
       <c r="AC62" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD62" s="37" t="s">
+      <c r="AD62" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="AE62" s="38"/>
-      <c r="AF62" s="38"/>
-      <c r="AG62" s="38"/>
-      <c r="AH62" s="38"/>
-      <c r="AI62" s="39"/>
+      <c r="AE62" s="41"/>
+      <c r="AF62" s="41"/>
+      <c r="AG62" s="41"/>
+      <c r="AH62" s="41"/>
+      <c r="AI62" s="42"/>
       <c r="AJ62" s="7">
         <v>45911</v>
       </c>
@@ -7346,7 +7460,7 @@
       </c>
       <c r="AL62" s="20"/>
       <c r="AM62" s="20"/>
-      <c r="AN62" s="47"/>
+      <c r="AN62" s="50"/>
       <c r="AO62" s="6" t="s">
         <v>75</v>
       </c>
@@ -7359,14 +7473,14 @@
       <c r="AR62" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS62" s="37" t="s">
+      <c r="AS62" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="AT62" s="38"/>
-      <c r="AU62" s="38"/>
-      <c r="AV62" s="38"/>
-      <c r="AW62" s="38"/>
-      <c r="AX62" s="39"/>
+      <c r="AT62" s="41"/>
+      <c r="AU62" s="41"/>
+      <c r="AV62" s="41"/>
+      <c r="AW62" s="41"/>
+      <c r="AX62" s="42"/>
       <c r="AY62" s="7">
         <v>45910</v>
       </c>
@@ -7375,11 +7489,11 @@
       </c>
       <c r="BA62" s="19"/>
       <c r="BB62" s="19"/>
-      <c r="BC62" s="67"/>
-      <c r="BD62" s="67"/>
+      <c r="BC62" s="73"/>
+      <c r="BD62" s="73"/>
     </row>
     <row r="63" spans="8:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I63" s="57">
+      <c r="I63" s="60">
         <v>5.5</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -7394,14 +7508,14 @@
       <c r="M63" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N63" s="37" t="s">
+      <c r="N63" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="O63" s="38"/>
-      <c r="P63" s="38"/>
-      <c r="Q63" s="38"/>
-      <c r="R63" s="38"/>
-      <c r="S63" s="39"/>
+      <c r="O63" s="41"/>
+      <c r="P63" s="41"/>
+      <c r="Q63" s="41"/>
+      <c r="R63" s="41"/>
+      <c r="S63" s="42"/>
       <c r="T63" s="7">
         <v>45910</v>
       </c>
@@ -7416,17 +7530,17 @@
       <c r="AA63" s="19"/>
       <c r="AB63" s="19"/>
       <c r="AC63" s="4"/>
-      <c r="AD63" s="40"/>
-      <c r="AE63" s="41"/>
-      <c r="AF63" s="41"/>
-      <c r="AG63" s="41"/>
-      <c r="AH63" s="41"/>
-      <c r="AI63" s="42"/>
+      <c r="AD63" s="43"/>
+      <c r="AE63" s="44"/>
+      <c r="AF63" s="44"/>
+      <c r="AG63" s="44"/>
+      <c r="AH63" s="44"/>
+      <c r="AI63" s="45"/>
       <c r="AJ63" s="19"/>
       <c r="AK63" s="19"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="20"/>
-      <c r="AN63" s="46">
+      <c r="AN63" s="49">
         <v>5.5</v>
       </c>
       <c r="AO63" s="6" t="s">
@@ -7441,14 +7555,14 @@
       <c r="AR63" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS63" s="37" t="s">
+      <c r="AS63" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="AT63" s="38"/>
-      <c r="AU63" s="38"/>
-      <c r="AV63" s="38"/>
-      <c r="AW63" s="38"/>
-      <c r="AX63" s="39"/>
+      <c r="AT63" s="41"/>
+      <c r="AU63" s="41"/>
+      <c r="AV63" s="41"/>
+      <c r="AW63" s="41"/>
+      <c r="AX63" s="42"/>
       <c r="AY63" s="7">
         <v>45910</v>
       </c>
@@ -7457,11 +7571,11 @@
       </c>
       <c r="BA63" s="19"/>
       <c r="BB63" s="19"/>
-      <c r="BC63" s="67"/>
-      <c r="BD63" s="67"/>
+      <c r="BC63" s="73"/>
+      <c r="BD63" s="73"/>
     </row>
     <row r="64" spans="8:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I64" s="58"/>
+      <c r="I64" s="61"/>
       <c r="J64" s="6" t="s">
         <v>199</v>
       </c>
@@ -7474,14 +7588,14 @@
       <c r="M64" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N64" s="37" t="s">
+      <c r="N64" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="O64" s="38"/>
-      <c r="P64" s="38"/>
-      <c r="Q64" s="38"/>
-      <c r="R64" s="38"/>
-      <c r="S64" s="39"/>
+      <c r="O64" s="41"/>
+      <c r="P64" s="41"/>
+      <c r="Q64" s="41"/>
+      <c r="R64" s="41"/>
+      <c r="S64" s="42"/>
       <c r="T64" s="7">
         <v>45911</v>
       </c>
@@ -7490,7 +7604,7 @@
       </c>
       <c r="V64" s="20"/>
       <c r="W64" s="20"/>
-      <c r="X64" s="105">
+      <c r="X64" s="39">
         <v>2.2999999999999998</v>
       </c>
       <c r="Y64" s="24">
@@ -7508,14 +7622,14 @@
       <c r="AC64" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD64" s="37" t="s">
+      <c r="AD64" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="AE64" s="38"/>
-      <c r="AF64" s="38"/>
-      <c r="AG64" s="38"/>
-      <c r="AH64" s="38"/>
-      <c r="AI64" s="39"/>
+      <c r="AE64" s="41"/>
+      <c r="AF64" s="41"/>
+      <c r="AG64" s="41"/>
+      <c r="AH64" s="41"/>
+      <c r="AI64" s="42"/>
       <c r="AJ64" s="7">
         <v>45911</v>
       </c>
@@ -7524,7 +7638,7 @@
       </c>
       <c r="AL64" s="20"/>
       <c r="AM64" s="20"/>
-      <c r="AN64" s="47"/>
+      <c r="AN64" s="50"/>
       <c r="AO64" s="6" t="s">
         <v>199</v>
       </c>
@@ -7537,14 +7651,14 @@
       <c r="AR64" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS64" s="37" t="s">
+      <c r="AS64" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="AT64" s="38"/>
-      <c r="AU64" s="38"/>
-      <c r="AV64" s="38"/>
-      <c r="AW64" s="38"/>
-      <c r="AX64" s="39"/>
+      <c r="AT64" s="41"/>
+      <c r="AU64" s="41"/>
+      <c r="AV64" s="41"/>
+      <c r="AW64" s="41"/>
+      <c r="AX64" s="42"/>
       <c r="AY64" s="7">
         <v>45911</v>
       </c>
@@ -7553,11 +7667,11 @@
       </c>
       <c r="BA64" s="25"/>
       <c r="BB64" s="25"/>
-      <c r="BC64" s="68"/>
-      <c r="BD64" s="68"/>
+      <c r="BC64" s="74"/>
+      <c r="BD64" s="74"/>
     </row>
     <row r="65" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I65" s="57">
+      <c r="I65" s="60">
         <v>6.2</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7572,14 +7686,14 @@
       <c r="M65" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N65" s="37" t="s">
+      <c r="N65" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="O65" s="38"/>
-      <c r="P65" s="38"/>
-      <c r="Q65" s="38"/>
-      <c r="R65" s="38"/>
-      <c r="S65" s="39"/>
+      <c r="O65" s="41"/>
+      <c r="P65" s="41"/>
+      <c r="Q65" s="41"/>
+      <c r="R65" s="41"/>
+      <c r="S65" s="42"/>
       <c r="T65" s="7">
         <v>45908</v>
       </c>
@@ -7594,17 +7708,17 @@
       <c r="AA65" s="19"/>
       <c r="AB65" s="19"/>
       <c r="AC65" s="4"/>
-      <c r="AD65" s="40"/>
-      <c r="AE65" s="41"/>
-      <c r="AF65" s="41"/>
-      <c r="AG65" s="41"/>
-      <c r="AH65" s="41"/>
-      <c r="AI65" s="42"/>
+      <c r="AD65" s="43"/>
+      <c r="AE65" s="44"/>
+      <c r="AF65" s="44"/>
+      <c r="AG65" s="44"/>
+      <c r="AH65" s="44"/>
+      <c r="AI65" s="45"/>
       <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="20"/>
       <c r="AM65" s="20"/>
-      <c r="AN65" s="46">
+      <c r="AN65" s="49">
         <v>6.2</v>
       </c>
       <c r="AO65" s="6" t="s">
@@ -7619,14 +7733,14 @@
       <c r="AR65" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS65" s="37" t="s">
+      <c r="AS65" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="AT65" s="38"/>
-      <c r="AU65" s="38"/>
-      <c r="AV65" s="38"/>
-      <c r="AW65" s="38"/>
-      <c r="AX65" s="39"/>
+      <c r="AT65" s="41"/>
+      <c r="AU65" s="41"/>
+      <c r="AV65" s="41"/>
+      <c r="AW65" s="41"/>
+      <c r="AX65" s="42"/>
       <c r="AY65" s="7">
         <v>45908</v>
       </c>
@@ -7635,11 +7749,11 @@
       </c>
       <c r="BA65" s="19"/>
       <c r="BB65" s="19"/>
-      <c r="BC65" s="67"/>
-      <c r="BD65" s="67"/>
+      <c r="BC65" s="73"/>
+      <c r="BD65" s="73"/>
     </row>
     <row r="66" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I66" s="58"/>
+      <c r="I66" s="61"/>
       <c r="J66" s="6" t="s">
         <v>210</v>
       </c>
@@ -7652,14 +7766,14 @@
       <c r="M66" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N66" s="37" t="s">
+      <c r="N66" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="O66" s="38"/>
-      <c r="P66" s="38"/>
-      <c r="Q66" s="38"/>
-      <c r="R66" s="38"/>
-      <c r="S66" s="39"/>
+      <c r="O66" s="41"/>
+      <c r="P66" s="41"/>
+      <c r="Q66" s="41"/>
+      <c r="R66" s="41"/>
+      <c r="S66" s="42"/>
       <c r="T66" s="7">
         <v>45908</v>
       </c>
@@ -7668,10 +7782,10 @@
       </c>
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
-      <c r="X66" s="103" t="s">
+      <c r="X66" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="Y66" s="54">
+      <c r="Y66" s="57">
         <v>5</v>
       </c>
       <c r="Z66" s="6" t="s">
@@ -7686,14 +7800,14 @@
       <c r="AC66" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD66" s="37" t="s">
+      <c r="AD66" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="AE66" s="38"/>
-      <c r="AF66" s="38"/>
-      <c r="AG66" s="38"/>
-      <c r="AH66" s="38"/>
-      <c r="AI66" s="39"/>
+      <c r="AE66" s="41"/>
+      <c r="AF66" s="41"/>
+      <c r="AG66" s="41"/>
+      <c r="AH66" s="41"/>
+      <c r="AI66" s="42"/>
       <c r="AJ66" s="7">
         <v>45913</v>
       </c>
@@ -7702,7 +7816,7 @@
       </c>
       <c r="AL66" s="20"/>
       <c r="AM66" s="20"/>
-      <c r="AN66" s="47"/>
+      <c r="AN66" s="50"/>
       <c r="AO66" s="6" t="s">
         <v>210</v>
       </c>
@@ -7715,14 +7829,14 @@
       <c r="AR66" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS66" s="37" t="s">
+      <c r="AS66" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="AT66" s="38"/>
-      <c r="AU66" s="38"/>
-      <c r="AV66" s="38"/>
-      <c r="AW66" s="38"/>
-      <c r="AX66" s="39"/>
+      <c r="AT66" s="41"/>
+      <c r="AU66" s="41"/>
+      <c r="AV66" s="41"/>
+      <c r="AW66" s="41"/>
+      <c r="AX66" s="42"/>
       <c r="AY66" s="7">
         <v>45908</v>
       </c>
@@ -7731,8 +7845,8 @@
       </c>
       <c r="BA66" s="19"/>
       <c r="BB66" s="19"/>
-      <c r="BC66" s="67"/>
-      <c r="BD66" s="67"/>
+      <c r="BC66" s="73"/>
+      <c r="BD66" s="73"/>
     </row>
     <row r="67" spans="9:56" x14ac:dyDescent="0.25">
       <c r="I67" s="36">
@@ -7750,14 +7864,14 @@
       <c r="M67" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N67" s="37" t="s">
+      <c r="N67" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="O67" s="38"/>
-      <c r="P67" s="38"/>
-      <c r="Q67" s="38"/>
-      <c r="R67" s="38"/>
-      <c r="S67" s="39"/>
+      <c r="O67" s="41"/>
+      <c r="P67" s="41"/>
+      <c r="Q67" s="41"/>
+      <c r="R67" s="41"/>
+      <c r="S67" s="42"/>
       <c r="T67" s="7">
         <v>45908</v>
       </c>
@@ -7766,8 +7880,8 @@
       </c>
       <c r="V67" s="20"/>
       <c r="W67" s="20"/>
-      <c r="X67" s="104"/>
-      <c r="Y67" s="55"/>
+      <c r="X67" s="68"/>
+      <c r="Y67" s="58"/>
       <c r="Z67" s="6" t="s">
         <v>184</v>
       </c>
@@ -7780,14 +7894,14 @@
       <c r="AC67" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD67" s="37" t="s">
+      <c r="AD67" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="AE67" s="38"/>
-      <c r="AF67" s="38"/>
-      <c r="AG67" s="38"/>
-      <c r="AH67" s="38"/>
-      <c r="AI67" s="39"/>
+      <c r="AE67" s="41"/>
+      <c r="AF67" s="41"/>
+      <c r="AG67" s="41"/>
+      <c r="AH67" s="41"/>
+      <c r="AI67" s="42"/>
       <c r="AJ67" s="7">
         <v>45913</v>
       </c>
@@ -7811,14 +7925,14 @@
       <c r="AR67" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS67" s="37" t="s">
+      <c r="AS67" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="AT67" s="38"/>
-      <c r="AU67" s="38"/>
-      <c r="AV67" s="38"/>
-      <c r="AW67" s="38"/>
-      <c r="AX67" s="39"/>
+      <c r="AT67" s="41"/>
+      <c r="AU67" s="41"/>
+      <c r="AV67" s="41"/>
+      <c r="AW67" s="41"/>
+      <c r="AX67" s="42"/>
       <c r="AY67" s="7">
         <v>45908</v>
       </c>
@@ -7827,11 +7941,11 @@
       </c>
       <c r="BA67" s="19"/>
       <c r="BB67" s="19"/>
-      <c r="BC67" s="67"/>
-      <c r="BD67" s="67"/>
+      <c r="BC67" s="73"/>
+      <c r="BD67" s="73"/>
     </row>
     <row r="68" spans="9:56" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I68" s="57">
+      <c r="I68" s="60">
         <v>6.4</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -7846,14 +7960,14 @@
       <c r="M68" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N68" s="37" t="s">
+      <c r="N68" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="O68" s="38"/>
-      <c r="P68" s="38"/>
-      <c r="Q68" s="38"/>
-      <c r="R68" s="38"/>
-      <c r="S68" s="39"/>
+      <c r="O68" s="41"/>
+      <c r="P68" s="41"/>
+      <c r="Q68" s="41"/>
+      <c r="R68" s="41"/>
+      <c r="S68" s="42"/>
       <c r="T68" s="8">
         <v>45903</v>
       </c>
@@ -7868,17 +7982,17 @@
       <c r="AA68" s="19"/>
       <c r="AB68" s="19"/>
       <c r="AC68" s="4"/>
-      <c r="AD68" s="40"/>
-      <c r="AE68" s="41"/>
-      <c r="AF68" s="41"/>
-      <c r="AG68" s="41"/>
-      <c r="AH68" s="41"/>
-      <c r="AI68" s="42"/>
+      <c r="AD68" s="43"/>
+      <c r="AE68" s="44"/>
+      <c r="AF68" s="44"/>
+      <c r="AG68" s="44"/>
+      <c r="AH68" s="44"/>
+      <c r="AI68" s="45"/>
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="20"/>
       <c r="AM68" s="20"/>
-      <c r="AN68" s="46">
+      <c r="AN68" s="49">
         <v>6.4</v>
       </c>
       <c r="AO68" s="6" t="s">
@@ -7893,14 +8007,14 @@
       <c r="AR68" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS68" s="37" t="s">
+      <c r="AS68" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="AT68" s="38"/>
-      <c r="AU68" s="38"/>
-      <c r="AV68" s="38"/>
-      <c r="AW68" s="38"/>
-      <c r="AX68" s="39"/>
+      <c r="AT68" s="41"/>
+      <c r="AU68" s="41"/>
+      <c r="AV68" s="41"/>
+      <c r="AW68" s="41"/>
+      <c r="AX68" s="42"/>
       <c r="AY68" s="8">
         <v>45903</v>
       </c>
@@ -7909,11 +8023,11 @@
       </c>
       <c r="BA68" s="19"/>
       <c r="BB68" s="19"/>
-      <c r="BC68" s="67"/>
-      <c r="BD68" s="67"/>
+      <c r="BC68" s="73"/>
+      <c r="BD68" s="73"/>
     </row>
     <row r="69" spans="9:56" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I69" s="58"/>
+      <c r="I69" s="61"/>
       <c r="J69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7926,14 +8040,14 @@
       <c r="M69" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N69" s="37" t="s">
+      <c r="N69" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="O69" s="38"/>
-      <c r="P69" s="38"/>
-      <c r="Q69" s="38"/>
-      <c r="R69" s="38"/>
-      <c r="S69" s="39"/>
+      <c r="O69" s="41"/>
+      <c r="P69" s="41"/>
+      <c r="Q69" s="41"/>
+      <c r="R69" s="41"/>
+      <c r="S69" s="42"/>
       <c r="T69" s="8">
         <v>45903</v>
       </c>
@@ -7942,10 +8056,10 @@
       </c>
       <c r="V69" s="20"/>
       <c r="W69" s="20"/>
-      <c r="X69" s="103" t="s">
+      <c r="X69" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="Y69" s="54">
+      <c r="Y69" s="57">
         <v>5</v>
       </c>
       <c r="Z69" s="6" t="s">
@@ -7960,14 +8074,14 @@
       <c r="AC69" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD69" s="37" t="s">
+      <c r="AD69" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="AE69" s="38"/>
-      <c r="AF69" s="38"/>
-      <c r="AG69" s="38"/>
-      <c r="AH69" s="38"/>
-      <c r="AI69" s="39"/>
+      <c r="AE69" s="41"/>
+      <c r="AF69" s="41"/>
+      <c r="AG69" s="41"/>
+      <c r="AH69" s="41"/>
+      <c r="AI69" s="42"/>
       <c r="AJ69" s="7">
         <v>45914</v>
       </c>
@@ -7976,7 +8090,7 @@
       </c>
       <c r="AL69" s="20"/>
       <c r="AM69" s="20"/>
-      <c r="AN69" s="47"/>
+      <c r="AN69" s="50"/>
       <c r="AO69" s="6" t="s">
         <v>77</v>
       </c>
@@ -7989,14 +8103,14 @@
       <c r="AR69" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS69" s="37" t="s">
+      <c r="AS69" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="AT69" s="38"/>
-      <c r="AU69" s="38"/>
-      <c r="AV69" s="38"/>
-      <c r="AW69" s="38"/>
-      <c r="AX69" s="39"/>
+      <c r="AT69" s="41"/>
+      <c r="AU69" s="41"/>
+      <c r="AV69" s="41"/>
+      <c r="AW69" s="41"/>
+      <c r="AX69" s="42"/>
       <c r="AY69" s="8">
         <v>45903</v>
       </c>
@@ -8005,8 +8119,8 @@
       </c>
       <c r="BA69" s="19"/>
       <c r="BB69" s="19"/>
-      <c r="BC69" s="67"/>
-      <c r="BD69" s="67"/>
+      <c r="BC69" s="73"/>
+      <c r="BD69" s="73"/>
     </row>
     <row r="70" spans="9:56" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I70" s="36">
@@ -8024,14 +8138,14 @@
       <c r="M70" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N70" s="37" t="s">
+      <c r="N70" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="O70" s="38"/>
-      <c r="P70" s="38"/>
-      <c r="Q70" s="38"/>
-      <c r="R70" s="38"/>
-      <c r="S70" s="39"/>
+      <c r="O70" s="41"/>
+      <c r="P70" s="41"/>
+      <c r="Q70" s="41"/>
+      <c r="R70" s="41"/>
+      <c r="S70" s="42"/>
       <c r="T70" s="8">
         <v>45844</v>
       </c>
@@ -8040,8 +8154,8 @@
       </c>
       <c r="V70" s="20"/>
       <c r="W70" s="20"/>
-      <c r="X70" s="104"/>
-      <c r="Y70" s="55"/>
+      <c r="X70" s="68"/>
+      <c r="Y70" s="58"/>
       <c r="Z70" s="6" t="s">
         <v>185</v>
       </c>
@@ -8054,14 +8168,14 @@
       <c r="AC70" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD70" s="37" t="s">
+      <c r="AD70" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="AE70" s="38"/>
-      <c r="AF70" s="38"/>
-      <c r="AG70" s="38"/>
-      <c r="AH70" s="38"/>
-      <c r="AI70" s="39"/>
+      <c r="AE70" s="41"/>
+      <c r="AF70" s="41"/>
+      <c r="AG70" s="41"/>
+      <c r="AH70" s="41"/>
+      <c r="AI70" s="42"/>
       <c r="AJ70" s="7">
         <v>45914</v>
       </c>
@@ -8085,14 +8199,14 @@
       <c r="AR70" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS70" s="37" t="s">
+      <c r="AS70" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="AT70" s="38"/>
-      <c r="AU70" s="38"/>
-      <c r="AV70" s="38"/>
-      <c r="AW70" s="38"/>
-      <c r="AX70" s="39"/>
+      <c r="AT70" s="41"/>
+      <c r="AU70" s="41"/>
+      <c r="AV70" s="41"/>
+      <c r="AW70" s="41"/>
+      <c r="AX70" s="42"/>
       <c r="AY70" s="8">
         <v>45844</v>
       </c>
@@ -8101,11 +8215,11 @@
       </c>
       <c r="BA70" s="19"/>
       <c r="BB70" s="19"/>
-      <c r="BC70" s="67"/>
-      <c r="BD70" s="67"/>
+      <c r="BC70" s="73"/>
+      <c r="BD70" s="73"/>
     </row>
     <row r="71" spans="9:56" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I71" s="57">
+      <c r="I71" s="60">
         <v>1.9</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -8120,14 +8234,14 @@
       <c r="M71" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N71" s="37" t="s">
+      <c r="N71" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="O71" s="38"/>
-      <c r="P71" s="38"/>
-      <c r="Q71" s="38"/>
-      <c r="R71" s="38"/>
-      <c r="S71" s="39"/>
+      <c r="O71" s="41"/>
+      <c r="P71" s="41"/>
+      <c r="Q71" s="41"/>
+      <c r="R71" s="41"/>
+      <c r="S71" s="42"/>
       <c r="T71" s="8">
         <v>45844</v>
       </c>
@@ -8142,17 +8256,17 @@
       <c r="AA71" s="19"/>
       <c r="AB71" s="19"/>
       <c r="AC71" s="4"/>
-      <c r="AD71" s="40"/>
-      <c r="AE71" s="41"/>
-      <c r="AF71" s="41"/>
-      <c r="AG71" s="41"/>
-      <c r="AH71" s="41"/>
-      <c r="AI71" s="42"/>
+      <c r="AD71" s="43"/>
+      <c r="AE71" s="44"/>
+      <c r="AF71" s="44"/>
+      <c r="AG71" s="44"/>
+      <c r="AH71" s="44"/>
+      <c r="AI71" s="45"/>
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="20"/>
       <c r="AM71" s="20"/>
-      <c r="AN71" s="46">
+      <c r="AN71" s="49">
         <v>1.9</v>
       </c>
       <c r="AO71" s="6" t="s">
@@ -8167,14 +8281,14 @@
       <c r="AR71" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS71" s="37" t="s">
+      <c r="AS71" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="AT71" s="38"/>
-      <c r="AU71" s="38"/>
-      <c r="AV71" s="38"/>
-      <c r="AW71" s="38"/>
-      <c r="AX71" s="39"/>
+      <c r="AT71" s="41"/>
+      <c r="AU71" s="41"/>
+      <c r="AV71" s="41"/>
+      <c r="AW71" s="41"/>
+      <c r="AX71" s="42"/>
       <c r="AY71" s="8">
         <v>45844</v>
       </c>
@@ -8183,11 +8297,11 @@
       </c>
       <c r="BA71" s="19"/>
       <c r="BB71" s="19"/>
-      <c r="BC71" s="67"/>
-      <c r="BD71" s="67"/>
+      <c r="BC71" s="73"/>
+      <c r="BD71" s="73"/>
     </row>
     <row r="72" spans="9:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I72" s="58"/>
+      <c r="I72" s="61"/>
       <c r="J72" s="6" t="s">
         <v>78</v>
       </c>
@@ -8200,14 +8314,14 @@
       <c r="M72" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N72" s="37" t="s">
+      <c r="N72" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="O72" s="38"/>
-      <c r="P72" s="38"/>
-      <c r="Q72" s="38"/>
-      <c r="R72" s="38"/>
-      <c r="S72" s="39"/>
+      <c r="O72" s="41"/>
+      <c r="P72" s="41"/>
+      <c r="Q72" s="41"/>
+      <c r="R72" s="41"/>
+      <c r="S72" s="42"/>
       <c r="T72" s="8">
         <v>45844</v>
       </c>
@@ -8216,10 +8330,10 @@
       </c>
       <c r="V72" s="20"/>
       <c r="W72" s="20"/>
-      <c r="X72" s="103">
+      <c r="X72" s="67">
         <v>3.2</v>
       </c>
-      <c r="Y72" s="50">
+      <c r="Y72" s="53">
         <v>1</v>
       </c>
       <c r="Z72" s="6" t="s">
@@ -8234,14 +8348,14 @@
       <c r="AC72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD72" s="43" t="s">
+      <c r="AD72" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
-      <c r="AH72" s="44"/>
-      <c r="AI72" s="45"/>
+      <c r="AE72" s="47"/>
+      <c r="AF72" s="47"/>
+      <c r="AG72" s="47"/>
+      <c r="AH72" s="47"/>
+      <c r="AI72" s="48"/>
       <c r="AJ72" s="7">
         <v>45907</v>
       </c>
@@ -8250,7 +8364,7 @@
       </c>
       <c r="AL72" s="20"/>
       <c r="AM72" s="20"/>
-      <c r="AN72" s="47"/>
+      <c r="AN72" s="50"/>
       <c r="AO72" s="6" t="s">
         <v>78</v>
       </c>
@@ -8263,14 +8377,14 @@
       <c r="AR72" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS72" s="37" t="s">
+      <c r="AS72" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="AT72" s="38"/>
-      <c r="AU72" s="38"/>
-      <c r="AV72" s="38"/>
-      <c r="AW72" s="38"/>
-      <c r="AX72" s="39"/>
+      <c r="AT72" s="41"/>
+      <c r="AU72" s="41"/>
+      <c r="AV72" s="41"/>
+      <c r="AW72" s="41"/>
+      <c r="AX72" s="42"/>
       <c r="AY72" s="8">
         <v>45844</v>
       </c>
@@ -8279,11 +8393,11 @@
       </c>
       <c r="BA72" s="19"/>
       <c r="BB72" s="19"/>
-      <c r="BC72" s="67"/>
-      <c r="BD72" s="67"/>
+      <c r="BC72" s="73"/>
+      <c r="BD72" s="73"/>
     </row>
     <row r="73" spans="9:56" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I73" s="57">
+      <c r="I73" s="60">
         <v>1.1200000000000001</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -8298,14 +8412,14 @@
       <c r="M73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N73" s="43" t="s">
+      <c r="N73" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
-      <c r="R73" s="44"/>
-      <c r="S73" s="45"/>
+      <c r="O73" s="47"/>
+      <c r="P73" s="47"/>
+      <c r="Q73" s="47"/>
+      <c r="R73" s="47"/>
+      <c r="S73" s="48"/>
       <c r="T73" s="8">
         <v>45844</v>
       </c>
@@ -8314,8 +8428,8 @@
       </c>
       <c r="V73" s="20"/>
       <c r="W73" s="20"/>
-      <c r="X73" s="104"/>
-      <c r="Y73" s="51"/>
+      <c r="X73" s="68"/>
+      <c r="Y73" s="54"/>
       <c r="Z73" s="6" t="s">
         <v>71</v>
       </c>
@@ -8328,14 +8442,14 @@
       <c r="AC73" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD73" s="43" t="s">
+      <c r="AD73" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
-      <c r="AH73" s="44"/>
-      <c r="AI73" s="45"/>
+      <c r="AE73" s="47"/>
+      <c r="AF73" s="47"/>
+      <c r="AG73" s="47"/>
+      <c r="AH73" s="47"/>
+      <c r="AI73" s="48"/>
       <c r="AJ73" s="7">
         <v>45907</v>
       </c>
@@ -8344,7 +8458,7 @@
       </c>
       <c r="AL73" s="20"/>
       <c r="AM73" s="20"/>
-      <c r="AN73" s="46">
+      <c r="AN73" s="49">
         <v>1.1200000000000001</v>
       </c>
       <c r="AO73" s="6" t="s">
@@ -8359,14 +8473,14 @@
       <c r="AR73" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS73" s="43" t="s">
+      <c r="AS73" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="AT73" s="44"/>
-      <c r="AU73" s="44"/>
-      <c r="AV73" s="44"/>
-      <c r="AW73" s="44"/>
-      <c r="AX73" s="45"/>
+      <c r="AT73" s="47"/>
+      <c r="AU73" s="47"/>
+      <c r="AV73" s="47"/>
+      <c r="AW73" s="47"/>
+      <c r="AX73" s="48"/>
       <c r="AY73" s="8">
         <v>45844</v>
       </c>
@@ -8375,11 +8489,11 @@
       </c>
       <c r="BA73" s="19"/>
       <c r="BB73" s="19"/>
-      <c r="BC73" s="67"/>
-      <c r="BD73" s="67"/>
+      <c r="BC73" s="73"/>
+      <c r="BD73" s="73"/>
     </row>
     <row r="74" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I74" s="58"/>
+      <c r="I74" s="61"/>
       <c r="J74" s="6" t="s">
         <v>79</v>
       </c>
@@ -8392,14 +8506,14 @@
       <c r="M74" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N74" s="37" t="s">
+      <c r="N74" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="O74" s="38"/>
-      <c r="P74" s="38"/>
-      <c r="Q74" s="38"/>
-      <c r="R74" s="38"/>
-      <c r="S74" s="39"/>
+      <c r="O74" s="41"/>
+      <c r="P74" s="41"/>
+      <c r="Q74" s="41"/>
+      <c r="R74" s="41"/>
+      <c r="S74" s="42"/>
       <c r="T74" s="8">
         <v>45844</v>
       </c>
@@ -8414,17 +8528,17 @@
       <c r="AA74" s="19"/>
       <c r="AB74" s="19"/>
       <c r="AC74" s="4"/>
-      <c r="AD74" s="40"/>
-      <c r="AE74" s="41"/>
-      <c r="AF74" s="41"/>
-      <c r="AG74" s="41"/>
-      <c r="AH74" s="41"/>
-      <c r="AI74" s="42"/>
+      <c r="AD74" s="43"/>
+      <c r="AE74" s="44"/>
+      <c r="AF74" s="44"/>
+      <c r="AG74" s="44"/>
+      <c r="AH74" s="44"/>
+      <c r="AI74" s="45"/>
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
-      <c r="AN74" s="47"/>
+      <c r="AN74" s="50"/>
       <c r="AO74" s="6" t="s">
         <v>79</v>
       </c>
@@ -8437,14 +8551,14 @@
       <c r="AR74" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS74" s="37" t="s">
+      <c r="AS74" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="AT74" s="38"/>
-      <c r="AU74" s="38"/>
-      <c r="AV74" s="38"/>
-      <c r="AW74" s="38"/>
-      <c r="AX74" s="39"/>
+      <c r="AT74" s="41"/>
+      <c r="AU74" s="41"/>
+      <c r="AV74" s="41"/>
+      <c r="AW74" s="41"/>
+      <c r="AX74" s="42"/>
       <c r="AY74" s="8">
         <v>45844</v>
       </c>
@@ -8453,11 +8567,11 @@
       </c>
       <c r="BA74" s="19"/>
       <c r="BB74" s="19"/>
-      <c r="BC74" s="67"/>
-      <c r="BD74" s="67"/>
+      <c r="BC74" s="73"/>
+      <c r="BD74" s="73"/>
     </row>
     <row r="75" spans="9:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I75" s="57">
+      <c r="I75" s="60">
         <v>1.1499999999999999</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -8472,14 +8586,14 @@
       <c r="M75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N75" s="43" t="s">
+      <c r="N75" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="O75" s="44"/>
-      <c r="P75" s="44"/>
-      <c r="Q75" s="44"/>
-      <c r="R75" s="44"/>
-      <c r="S75" s="45"/>
+      <c r="O75" s="47"/>
+      <c r="P75" s="47"/>
+      <c r="Q75" s="47"/>
+      <c r="R75" s="47"/>
+      <c r="S75" s="48"/>
       <c r="T75" s="8">
         <v>45844</v>
       </c>
@@ -8488,10 +8602,10 @@
       </c>
       <c r="V75" s="20"/>
       <c r="W75" s="20"/>
-      <c r="X75" s="46">
+      <c r="X75" s="49">
         <v>3.3</v>
       </c>
-      <c r="Y75" s="62">
+      <c r="Y75" s="65">
         <v>2</v>
       </c>
       <c r="Z75" s="6" t="s">
@@ -8506,14 +8620,14 @@
       <c r="AC75" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD75" s="37" t="s">
+      <c r="AD75" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="AE75" s="38"/>
-      <c r="AF75" s="38"/>
-      <c r="AG75" s="38"/>
-      <c r="AH75" s="38"/>
-      <c r="AI75" s="39"/>
+      <c r="AE75" s="41"/>
+      <c r="AF75" s="41"/>
+      <c r="AG75" s="41"/>
+      <c r="AH75" s="41"/>
+      <c r="AI75" s="42"/>
       <c r="AJ75" s="7">
         <v>45907</v>
       </c>
@@ -8522,7 +8636,7 @@
       </c>
       <c r="AL75" s="20"/>
       <c r="AM75" s="20"/>
-      <c r="AN75" s="46">
+      <c r="AN75" s="49">
         <v>1.1499999999999999</v>
       </c>
       <c r="AO75" s="6" t="s">
@@ -8537,14 +8651,14 @@
       <c r="AR75" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS75" s="43" t="s">
+      <c r="AS75" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="AT75" s="44"/>
-      <c r="AU75" s="44"/>
-      <c r="AV75" s="44"/>
-      <c r="AW75" s="44"/>
-      <c r="AX75" s="45"/>
+      <c r="AT75" s="47"/>
+      <c r="AU75" s="47"/>
+      <c r="AV75" s="47"/>
+      <c r="AW75" s="47"/>
+      <c r="AX75" s="48"/>
       <c r="AY75" s="8">
         <v>45844</v>
       </c>
@@ -8553,11 +8667,11 @@
       </c>
       <c r="BA75" s="19"/>
       <c r="BB75" s="19"/>
-      <c r="BC75" s="67"/>
-      <c r="BD75" s="67"/>
+      <c r="BC75" s="73"/>
+      <c r="BD75" s="73"/>
     </row>
     <row r="76" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I76" s="58"/>
+      <c r="I76" s="61"/>
       <c r="J76" s="6" t="s">
         <v>212</v>
       </c>
@@ -8570,14 +8684,14 @@
       <c r="M76" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N76" s="37" t="s">
+      <c r="N76" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="O76" s="38"/>
-      <c r="P76" s="38"/>
-      <c r="Q76" s="38"/>
-      <c r="R76" s="38"/>
-      <c r="S76" s="39"/>
+      <c r="O76" s="41"/>
+      <c r="P76" s="41"/>
+      <c r="Q76" s="41"/>
+      <c r="R76" s="41"/>
+      <c r="S76" s="42"/>
       <c r="T76" s="8">
         <v>45844</v>
       </c>
@@ -8586,8 +8700,8 @@
       </c>
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
-      <c r="X76" s="47"/>
-      <c r="Y76" s="63"/>
+      <c r="X76" s="50"/>
+      <c r="Y76" s="66"/>
       <c r="Z76" s="6" t="s">
         <v>197</v>
       </c>
@@ -8600,14 +8714,14 @@
       <c r="AC76" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD76" s="37" t="s">
+      <c r="AD76" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="AE76" s="38"/>
-      <c r="AF76" s="38"/>
-      <c r="AG76" s="38"/>
-      <c r="AH76" s="38"/>
-      <c r="AI76" s="39"/>
+      <c r="AE76" s="41"/>
+      <c r="AF76" s="41"/>
+      <c r="AG76" s="41"/>
+      <c r="AH76" s="41"/>
+      <c r="AI76" s="42"/>
       <c r="AJ76" s="7">
         <v>45907</v>
       </c>
@@ -8616,7 +8730,7 @@
       </c>
       <c r="AL76" s="20"/>
       <c r="AM76" s="20"/>
-      <c r="AN76" s="47"/>
+      <c r="AN76" s="50"/>
       <c r="AO76" s="6" t="s">
         <v>212</v>
       </c>
@@ -8629,14 +8743,14 @@
       <c r="AR76" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS76" s="37" t="s">
+      <c r="AS76" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="AT76" s="38"/>
-      <c r="AU76" s="38"/>
-      <c r="AV76" s="38"/>
-      <c r="AW76" s="38"/>
-      <c r="AX76" s="39"/>
+      <c r="AT76" s="41"/>
+      <c r="AU76" s="41"/>
+      <c r="AV76" s="41"/>
+      <c r="AW76" s="41"/>
+      <c r="AX76" s="42"/>
       <c r="AY76" s="8">
         <v>45844</v>
       </c>
@@ -8645,11 +8759,11 @@
       </c>
       <c r="BA76" s="25"/>
       <c r="BB76" s="25"/>
-      <c r="BC76" s="68"/>
-      <c r="BD76" s="68"/>
+      <c r="BC76" s="74"/>
+      <c r="BD76" s="74"/>
     </row>
     <row r="77" spans="9:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I77" s="57">
+      <c r="I77" s="60">
         <v>1.18</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -8664,14 +8778,14 @@
       <c r="M77" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N77" s="37" t="s">
+      <c r="N77" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="O77" s="38"/>
-      <c r="P77" s="38"/>
-      <c r="Q77" s="38"/>
-      <c r="R77" s="38"/>
-      <c r="S77" s="39"/>
+      <c r="O77" s="41"/>
+      <c r="P77" s="41"/>
+      <c r="Q77" s="41"/>
+      <c r="R77" s="41"/>
+      <c r="S77" s="42"/>
       <c r="T77" s="8">
         <v>45844</v>
       </c>
@@ -8686,17 +8800,17 @@
       <c r="AA77" s="19"/>
       <c r="AB77" s="19"/>
       <c r="AC77" s="4"/>
-      <c r="AD77" s="40"/>
-      <c r="AE77" s="41"/>
-      <c r="AF77" s="41"/>
-      <c r="AG77" s="41"/>
-      <c r="AH77" s="41"/>
-      <c r="AI77" s="42"/>
+      <c r="AD77" s="43"/>
+      <c r="AE77" s="44"/>
+      <c r="AF77" s="44"/>
+      <c r="AG77" s="44"/>
+      <c r="AH77" s="44"/>
+      <c r="AI77" s="45"/>
       <c r="AJ77" s="19"/>
       <c r="AK77" s="19"/>
       <c r="AL77" s="20"/>
       <c r="AM77" s="20"/>
-      <c r="AN77" s="46">
+      <c r="AN77" s="49">
         <v>1.18</v>
       </c>
       <c r="AO77" s="6" t="s">
@@ -8711,14 +8825,14 @@
       <c r="AR77" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS77" s="37" t="s">
+      <c r="AS77" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="AT77" s="38"/>
-      <c r="AU77" s="38"/>
-      <c r="AV77" s="38"/>
-      <c r="AW77" s="38"/>
-      <c r="AX77" s="39"/>
+      <c r="AT77" s="41"/>
+      <c r="AU77" s="41"/>
+      <c r="AV77" s="41"/>
+      <c r="AW77" s="41"/>
+      <c r="AX77" s="42"/>
       <c r="AY77" s="8">
         <v>45844</v>
       </c>
@@ -8727,11 +8841,11 @@
       </c>
       <c r="BA77" s="19"/>
       <c r="BB77" s="19"/>
-      <c r="BC77" s="67"/>
-      <c r="BD77" s="67"/>
+      <c r="BC77" s="73"/>
+      <c r="BD77" s="73"/>
     </row>
     <row r="78" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I78" s="58"/>
+      <c r="I78" s="61"/>
       <c r="J78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8744,14 +8858,14 @@
       <c r="M78" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N78" s="37" t="s">
+      <c r="N78" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="O78" s="38"/>
-      <c r="P78" s="38"/>
-      <c r="Q78" s="38"/>
-      <c r="R78" s="38"/>
-      <c r="S78" s="39"/>
+      <c r="O78" s="41"/>
+      <c r="P78" s="41"/>
+      <c r="Q78" s="41"/>
+      <c r="R78" s="41"/>
+      <c r="S78" s="42"/>
       <c r="T78" s="8">
         <v>45844</v>
       </c>
@@ -8760,10 +8874,10 @@
       </c>
       <c r="V78" s="20"/>
       <c r="W78" s="20"/>
-      <c r="X78" s="46">
+      <c r="X78" s="49">
         <v>3.4</v>
       </c>
-      <c r="Y78" s="50">
+      <c r="Y78" s="53">
         <v>1</v>
       </c>
       <c r="Z78" s="6" t="s">
@@ -8778,14 +8892,14 @@
       <c r="AC78" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD78" s="37" t="s">
+      <c r="AD78" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="AE78" s="38"/>
-      <c r="AF78" s="38"/>
-      <c r="AG78" s="38"/>
-      <c r="AH78" s="38"/>
-      <c r="AI78" s="39"/>
+      <c r="AE78" s="41"/>
+      <c r="AF78" s="41"/>
+      <c r="AG78" s="41"/>
+      <c r="AH78" s="41"/>
+      <c r="AI78" s="42"/>
       <c r="AJ78" s="7">
         <v>45908</v>
       </c>
@@ -8794,7 +8908,7 @@
       </c>
       <c r="AL78" s="20"/>
       <c r="AM78" s="20"/>
-      <c r="AN78" s="47"/>
+      <c r="AN78" s="50"/>
       <c r="AO78" s="6" t="s">
         <v>80</v>
       </c>
@@ -8807,14 +8921,14 @@
       <c r="AR78" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS78" s="37" t="s">
+      <c r="AS78" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="AT78" s="38"/>
-      <c r="AU78" s="38"/>
-      <c r="AV78" s="38"/>
-      <c r="AW78" s="38"/>
-      <c r="AX78" s="39"/>
+      <c r="AT78" s="41"/>
+      <c r="AU78" s="41"/>
+      <c r="AV78" s="41"/>
+      <c r="AW78" s="41"/>
+      <c r="AX78" s="42"/>
       <c r="AY78" s="8">
         <v>45844</v>
       </c>
@@ -8823,11 +8937,11 @@
       </c>
       <c r="BA78" s="19"/>
       <c r="BB78" s="19"/>
-      <c r="BC78" s="67"/>
-      <c r="BD78" s="67"/>
+      <c r="BC78" s="73"/>
+      <c r="BD78" s="73"/>
     </row>
     <row r="79" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I79" s="57">
+      <c r="I79" s="60">
         <v>1.21</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -8840,14 +8954,14 @@
       <c r="M79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N79" s="43" t="s">
+      <c r="N79" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
-      <c r="R79" s="44"/>
-      <c r="S79" s="45"/>
+      <c r="O79" s="47"/>
+      <c r="P79" s="47"/>
+      <c r="Q79" s="47"/>
+      <c r="R79" s="47"/>
+      <c r="S79" s="48"/>
       <c r="T79" s="8">
         <v>45905</v>
       </c>
@@ -8856,8 +8970,8 @@
       </c>
       <c r="V79" s="20"/>
       <c r="W79" s="20"/>
-      <c r="X79" s="47"/>
-      <c r="Y79" s="51"/>
+      <c r="X79" s="50"/>
+      <c r="Y79" s="54"/>
       <c r="Z79" s="18" t="s">
         <v>195</v>
       </c>
@@ -8870,14 +8984,14 @@
       <c r="AC79" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD79" s="37" t="s">
+      <c r="AD79" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="AE79" s="38"/>
-      <c r="AF79" s="38"/>
-      <c r="AG79" s="38"/>
-      <c r="AH79" s="38"/>
-      <c r="AI79" s="39"/>
+      <c r="AE79" s="41"/>
+      <c r="AF79" s="41"/>
+      <c r="AG79" s="41"/>
+      <c r="AH79" s="41"/>
+      <c r="AI79" s="42"/>
       <c r="AJ79" s="7">
         <v>45908</v>
       </c>
@@ -8886,7 +9000,7 @@
       </c>
       <c r="AL79" s="20"/>
       <c r="AM79" s="20"/>
-      <c r="AN79" s="46">
+      <c r="AN79" s="49">
         <v>1.21</v>
       </c>
       <c r="AO79" s="6" t="s">
@@ -8899,14 +9013,14 @@
       <c r="AR79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS79" s="43" t="s">
+      <c r="AS79" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="AT79" s="44"/>
-      <c r="AU79" s="44"/>
-      <c r="AV79" s="44"/>
-      <c r="AW79" s="44"/>
-      <c r="AX79" s="45"/>
+      <c r="AT79" s="47"/>
+      <c r="AU79" s="47"/>
+      <c r="AV79" s="47"/>
+      <c r="AW79" s="47"/>
+      <c r="AX79" s="48"/>
       <c r="AY79" s="8">
         <v>45905</v>
       </c>
@@ -8915,11 +9029,11 @@
       </c>
       <c r="BA79" s="19"/>
       <c r="BB79" s="19"/>
-      <c r="BC79" s="67"/>
-      <c r="BD79" s="67"/>
+      <c r="BC79" s="73"/>
+      <c r="BD79" s="73"/>
     </row>
     <row r="80" spans="9:56" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I80" s="58"/>
+      <c r="I80" s="61"/>
       <c r="J80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8930,14 +9044,14 @@
       <c r="M80" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N80" s="37" t="s">
+      <c r="N80" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="O80" s="38"/>
-      <c r="P80" s="38"/>
-      <c r="Q80" s="38"/>
-      <c r="R80" s="38"/>
-      <c r="S80" s="39"/>
+      <c r="O80" s="41"/>
+      <c r="P80" s="41"/>
+      <c r="Q80" s="41"/>
+      <c r="R80" s="41"/>
+      <c r="S80" s="42"/>
       <c r="T80" s="8">
         <v>45905</v>
       </c>
@@ -8952,17 +9066,17 @@
       <c r="AA80" s="19"/>
       <c r="AB80" s="19"/>
       <c r="AC80" s="4"/>
-      <c r="AD80" s="40"/>
-      <c r="AE80" s="41"/>
-      <c r="AF80" s="41"/>
-      <c r="AG80" s="41"/>
-      <c r="AH80" s="41"/>
-      <c r="AI80" s="42"/>
+      <c r="AD80" s="43"/>
+      <c r="AE80" s="44"/>
+      <c r="AF80" s="44"/>
+      <c r="AG80" s="44"/>
+      <c r="AH80" s="44"/>
+      <c r="AI80" s="45"/>
       <c r="AJ80" s="19"/>
       <c r="AK80" s="19"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="20"/>
-      <c r="AN80" s="47"/>
+      <c r="AN80" s="50"/>
       <c r="AO80" s="6" t="s">
         <v>81</v>
       </c>
@@ -8973,14 +9087,14 @@
       <c r="AR80" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS80" s="37" t="s">
+      <c r="AS80" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="AT80" s="38"/>
-      <c r="AU80" s="38"/>
-      <c r="AV80" s="38"/>
-      <c r="AW80" s="38"/>
-      <c r="AX80" s="39"/>
+      <c r="AT80" s="41"/>
+      <c r="AU80" s="41"/>
+      <c r="AV80" s="41"/>
+      <c r="AW80" s="41"/>
+      <c r="AX80" s="42"/>
       <c r="AY80" s="8">
         <v>45905</v>
       </c>
@@ -8989,11 +9103,11 @@
       </c>
       <c r="BA80" s="19"/>
       <c r="BB80" s="19"/>
-      <c r="BC80" s="67"/>
-      <c r="BD80" s="67"/>
+      <c r="BC80" s="73"/>
+      <c r="BD80" s="73"/>
     </row>
     <row r="81" spans="9:56" x14ac:dyDescent="0.25">
-      <c r="I81" s="57">
+      <c r="I81" s="60">
         <v>5.2</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -9008,14 +9122,14 @@
       <c r="M81" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N81" s="37" t="s">
+      <c r="N81" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="O81" s="38"/>
-      <c r="P81" s="38"/>
-      <c r="Q81" s="38"/>
-      <c r="R81" s="38"/>
-      <c r="S81" s="39"/>
+      <c r="O81" s="41"/>
+      <c r="P81" s="41"/>
+      <c r="Q81" s="41"/>
+      <c r="R81" s="41"/>
+      <c r="S81" s="42"/>
       <c r="T81" s="7">
         <v>45911</v>
       </c>
@@ -9042,14 +9156,14 @@
       <c r="AC81" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD81" s="37" t="s">
+      <c r="AD81" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="AE81" s="38"/>
-      <c r="AF81" s="38"/>
-      <c r="AG81" s="38"/>
-      <c r="AH81" s="38"/>
-      <c r="AI81" s="39"/>
+      <c r="AE81" s="41"/>
+      <c r="AF81" s="41"/>
+      <c r="AG81" s="41"/>
+      <c r="AH81" s="41"/>
+      <c r="AI81" s="42"/>
       <c r="AJ81" s="7">
         <v>45908</v>
       </c>
@@ -9058,7 +9172,7 @@
       </c>
       <c r="AL81" s="20"/>
       <c r="AM81" s="20"/>
-      <c r="AN81" s="46">
+      <c r="AN81" s="49">
         <v>5.2</v>
       </c>
       <c r="AO81" s="6" t="s">
@@ -9073,14 +9187,14 @@
       <c r="AR81" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS81" s="37" t="s">
+      <c r="AS81" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="AT81" s="38"/>
-      <c r="AU81" s="38"/>
-      <c r="AV81" s="38"/>
-      <c r="AW81" s="38"/>
-      <c r="AX81" s="39"/>
+      <c r="AT81" s="41"/>
+      <c r="AU81" s="41"/>
+      <c r="AV81" s="41"/>
+      <c r="AW81" s="41"/>
+      <c r="AX81" s="42"/>
       <c r="AY81" s="7">
         <v>45911</v>
       </c>
@@ -9089,11 +9203,11 @@
       </c>
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
-      <c r="BC81" s="67"/>
-      <c r="BD81" s="67"/>
+      <c r="BC81" s="73"/>
+      <c r="BD81" s="73"/>
     </row>
     <row r="82" spans="9:56" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I82" s="58"/>
+      <c r="I82" s="61"/>
       <c r="J82" s="6" t="s">
         <v>82</v>
       </c>
@@ -9106,14 +9220,14 @@
       <c r="M82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N82" s="43" t="s">
+      <c r="N82" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="O82" s="44"/>
-      <c r="P82" s="44"/>
-      <c r="Q82" s="44"/>
-      <c r="R82" s="44"/>
-      <c r="S82" s="45"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="47"/>
+      <c r="Q82" s="47"/>
+      <c r="R82" s="47"/>
+      <c r="S82" s="48"/>
       <c r="T82" s="7">
         <v>45911</v>
       </c>
@@ -9128,17 +9242,17 @@
       <c r="AA82" s="19"/>
       <c r="AB82" s="19"/>
       <c r="AC82" s="4"/>
-      <c r="AD82" s="40"/>
-      <c r="AE82" s="41"/>
-      <c r="AF82" s="41"/>
-      <c r="AG82" s="41"/>
-      <c r="AH82" s="41"/>
-      <c r="AI82" s="42"/>
+      <c r="AD82" s="43"/>
+      <c r="AE82" s="44"/>
+      <c r="AF82" s="44"/>
+      <c r="AG82" s="44"/>
+      <c r="AH82" s="44"/>
+      <c r="AI82" s="45"/>
       <c r="AJ82" s="19"/>
       <c r="AK82" s="19"/>
       <c r="AL82" s="20"/>
       <c r="AM82" s="20"/>
-      <c r="AN82" s="47"/>
+      <c r="AN82" s="50"/>
       <c r="AO82" s="6" t="s">
         <v>82</v>
       </c>
@@ -9151,14 +9265,14 @@
       <c r="AR82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS82" s="43" t="s">
+      <c r="AS82" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="AT82" s="44"/>
-      <c r="AU82" s="44"/>
-      <c r="AV82" s="44"/>
-      <c r="AW82" s="44"/>
-      <c r="AX82" s="45"/>
+      <c r="AT82" s="47"/>
+      <c r="AU82" s="47"/>
+      <c r="AV82" s="47"/>
+      <c r="AW82" s="47"/>
+      <c r="AX82" s="48"/>
       <c r="AY82" s="7">
         <v>45911</v>
       </c>
@@ -9167,11 +9281,11 @@
       </c>
       <c r="BA82" s="19"/>
       <c r="BB82" s="19"/>
-      <c r="BC82" s="67"/>
-      <c r="BD82" s="67"/>
+      <c r="BC82" s="73"/>
+      <c r="BD82" s="73"/>
     </row>
     <row r="83" spans="9:56" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I83" s="57">
+      <c r="I83" s="60">
         <v>5.3</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -9186,14 +9300,14 @@
       <c r="M83" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N83" s="37" t="s">
+      <c r="N83" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="O83" s="38"/>
-      <c r="P83" s="38"/>
-      <c r="Q83" s="38"/>
-      <c r="R83" s="38"/>
-      <c r="S83" s="39"/>
+      <c r="O83" s="41"/>
+      <c r="P83" s="41"/>
+      <c r="Q83" s="41"/>
+      <c r="R83" s="41"/>
+      <c r="S83" s="42"/>
       <c r="T83" s="7">
         <v>45910</v>
       </c>
@@ -9202,10 +9316,10 @@
       </c>
       <c r="V83" s="20"/>
       <c r="W83" s="20"/>
-      <c r="X83" s="46">
+      <c r="X83" s="49">
         <v>3.6</v>
       </c>
-      <c r="Y83" s="54">
+      <c r="Y83" s="57">
         <v>5</v>
       </c>
       <c r="Z83" s="6" t="s">
@@ -9220,14 +9334,14 @@
       <c r="AC83" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD83" s="37" t="s">
+      <c r="AD83" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="AE83" s="38"/>
-      <c r="AF83" s="38"/>
-      <c r="AG83" s="38"/>
-      <c r="AH83" s="38"/>
-      <c r="AI83" s="39"/>
+      <c r="AE83" s="41"/>
+      <c r="AF83" s="41"/>
+      <c r="AG83" s="41"/>
+      <c r="AH83" s="41"/>
+      <c r="AI83" s="42"/>
       <c r="AJ83" s="7">
         <v>45909</v>
       </c>
@@ -9236,7 +9350,7 @@
       </c>
       <c r="AL83" s="20"/>
       <c r="AM83" s="20"/>
-      <c r="AN83" s="46">
+      <c r="AN83" s="49">
         <v>5.3</v>
       </c>
       <c r="AO83" s="6" t="s">
@@ -9251,27 +9365,33 @@
       <c r="AR83" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS83" s="37" t="s">
+      <c r="AS83" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="AT83" s="38"/>
-      <c r="AU83" s="38"/>
-      <c r="AV83" s="38"/>
-      <c r="AW83" s="38"/>
-      <c r="AX83" s="39"/>
+      <c r="AT83" s="41"/>
+      <c r="AU83" s="41"/>
+      <c r="AV83" s="41"/>
+      <c r="AW83" s="41"/>
+      <c r="AX83" s="42"/>
       <c r="AY83" s="7">
         <v>45910</v>
       </c>
       <c r="AZ83" s="7">
         <v>45912</v>
       </c>
-      <c r="BA83" s="19"/>
-      <c r="BB83" s="19"/>
-      <c r="BC83" s="67"/>
-      <c r="BD83" s="67"/>
+      <c r="BA83" s="7">
+        <v>45910</v>
+      </c>
+      <c r="BB83" s="7">
+        <v>45912</v>
+      </c>
+      <c r="BC83" s="73">
+        <v>2</v>
+      </c>
+      <c r="BD83" s="73"/>
     </row>
     <row r="84" spans="9:56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I84" s="58"/>
+      <c r="I84" s="61"/>
       <c r="J84" s="6" t="s">
         <v>213</v>
       </c>
@@ -9284,14 +9404,14 @@
       <c r="M84" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N84" s="37" t="s">
+      <c r="N84" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="O84" s="38"/>
-      <c r="P84" s="38"/>
-      <c r="Q84" s="38"/>
-      <c r="R84" s="38"/>
-      <c r="S84" s="39"/>
+      <c r="O84" s="41"/>
+      <c r="P84" s="41"/>
+      <c r="Q84" s="41"/>
+      <c r="R84" s="41"/>
+      <c r="S84" s="42"/>
       <c r="T84" s="7">
         <v>45910</v>
       </c>
@@ -9300,8 +9420,8 @@
       </c>
       <c r="V84" s="20"/>
       <c r="W84" s="20"/>
-      <c r="X84" s="47"/>
-      <c r="Y84" s="55"/>
+      <c r="X84" s="50"/>
+      <c r="Y84" s="58"/>
       <c r="Z84" s="6" t="s">
         <v>73</v>
       </c>
@@ -9314,14 +9434,14 @@
       <c r="AC84" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AD84" s="37" t="s">
+      <c r="AD84" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="AE84" s="38"/>
-      <c r="AF84" s="38"/>
-      <c r="AG84" s="38"/>
-      <c r="AH84" s="38"/>
-      <c r="AI84" s="39"/>
+      <c r="AE84" s="41"/>
+      <c r="AF84" s="41"/>
+      <c r="AG84" s="41"/>
+      <c r="AH84" s="41"/>
+      <c r="AI84" s="42"/>
       <c r="AJ84" s="7">
         <v>45909</v>
       </c>
@@ -9330,7 +9450,7 @@
       </c>
       <c r="AL84" s="20"/>
       <c r="AM84" s="20"/>
-      <c r="AN84" s="47"/>
+      <c r="AN84" s="50"/>
       <c r="AO84" s="6" t="s">
         <v>213</v>
       </c>
@@ -9343,24 +9463,30 @@
       <c r="AR84" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AS84" s="37" t="s">
+      <c r="AS84" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="AT84" s="38"/>
-      <c r="AU84" s="38"/>
-      <c r="AV84" s="38"/>
-      <c r="AW84" s="38"/>
-      <c r="AX84" s="39"/>
+      <c r="AT84" s="41"/>
+      <c r="AU84" s="41"/>
+      <c r="AV84" s="41"/>
+      <c r="AW84" s="41"/>
+      <c r="AX84" s="42"/>
       <c r="AY84" s="7">
         <v>45910</v>
       </c>
       <c r="AZ84" s="7">
         <v>45915</v>
       </c>
-      <c r="BA84" s="19"/>
-      <c r="BB84" s="19"/>
-      <c r="BC84" s="67"/>
-      <c r="BD84" s="67"/>
+      <c r="BA84" s="7">
+        <v>45910</v>
+      </c>
+      <c r="BB84" s="7">
+        <v>45915</v>
+      </c>
+      <c r="BC84" s="73">
+        <v>4</v>
+      </c>
+      <c r="BD84" s="73"/>
     </row>
     <row r="85" spans="9:56" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I85" s="36">
@@ -9378,14 +9504,14 @@
       <c r="M85" s="6" t=